--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="1174">
   <si>
     <t>Geração:</t>
   </si>
@@ -1155,6 +1155,9 @@
     <t>IBB9E64</t>
   </si>
   <si>
+    <t>Bloqueio temporário</t>
+  </si>
+  <si>
     <t>JEA1J35</t>
   </si>
   <si>
@@ -2169,9 +2172,6 @@
     <t>ILQ8746</t>
   </si>
   <si>
-    <t>Bloqueio temporário / Documento ConsultaCRLV vencendo, Documento CRLV vencendo</t>
-  </si>
-  <si>
     <t>MRS9A23</t>
   </si>
   <si>
@@ -2682,6 +2682,9 @@
     <t>BAB6B26</t>
   </si>
   <si>
+    <t>Inspeção Checklist de Segurança SESMT vencida</t>
+  </si>
+  <si>
     <t>OLH1F20</t>
   </si>
   <si>
@@ -2787,9 +2790,6 @@
     <t>059434911</t>
   </si>
   <si>
-    <t>Bloqueio temporário</t>
-  </si>
-  <si>
     <t>NLQ1200</t>
   </si>
   <si>
@@ -3535,63 +3535,6 @@
   </si>
   <si>
     <t>SCANIA/R124 GA6X4NZ 400 / SCANIA/R124 GA6X4NZ 400</t>
-  </si>
-  <si>
-    <t>M.BENZ/ACTROS 2651S6X4 / M.BENZ/ACTROS 2651S6X4</t>
-  </si>
-  <si>
-    <t>SCANIA / T113 H 4X2 320</t>
-  </si>
-  <si>
-    <t>SCANIA / R124 GA4X2NZ 420</t>
-  </si>
-  <si>
-    <t>SR/FACCHINI / SRF RT</t>
-  </si>
-  <si>
-    <t>SCANIA / R 470 A6X2</t>
-  </si>
-  <si>
-    <t>REB / SCHIFFER SSC3E CA</t>
-  </si>
-  <si>
-    <t>SCANIA / T113 H 4X2 360</t>
-  </si>
-  <si>
-    <t>SR/LIBRELATO SRCS 3E / SR/LIBRELATO SRCS 3E</t>
-  </si>
-  <si>
-    <t>IVECO / STRALIS 740S46TZ</t>
-  </si>
-  <si>
-    <t>Paulo Jesus</t>
-  </si>
-  <si>
-    <t>SR / RANDON SR CS TR</t>
-  </si>
-  <si>
-    <t>SCHIFFER / REB</t>
-  </si>
-  <si>
-    <t>SCANIA / R113 H 4X2 360</t>
-  </si>
-  <si>
-    <t>SCANIA/R124 GA4X2NZ 400 / SCANIA/R124 GA4X2NZ 400</t>
-  </si>
-  <si>
-    <t>M BENZ / L 1418</t>
-  </si>
-  <si>
-    <t>SCANIA / G 420 A6X2</t>
-  </si>
-  <si>
-    <t>VW/23.220 / VW/23.220</t>
-  </si>
-  <si>
-    <t>Jaqueline</t>
-  </si>
-  <si>
-    <t>GUERRA / REB A GUERRA</t>
   </si>
 </sst>
 </file>
@@ -3783,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46297.57635491898</v>
+        <v>46300.34739778935</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -6479,10 +6422,10 @@
         <v>46310.125</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="M32" s="0" t="s">
         <v>39</v>
@@ -6912,10 +6855,10 @@
         <v>46310.125</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M37" s="0" t="s">
         <v>39</v>
@@ -15708,14 +15651,12 @@
       <c r="H139" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="J139" s="11">
-        <v>46357.125</v>
-      </c>
+      <c r="J139" s="11"/>
       <c r="K139" s="0" t="s">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="L139" s="0" t="s">
-        <v>39</v>
+        <v>380</v>
       </c>
       <c r="M139" s="0" t="s">
         <v>39</v>
@@ -15777,13 +15718,13 @@
         <v>48</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F140" s="0" t="s">
         <v>53</v>
@@ -15863,7 +15804,7 @@
         <v>34</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D141" s="0" t="s">
         <v>362</v>
@@ -15878,7 +15819,7 @@
         <v>92</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J141" s="11">
         <v>46310.125</v>
@@ -15949,7 +15890,7 @@
         <v>34</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D142" s="0" t="s">
         <v>364</v>
@@ -15964,7 +15905,7 @@
         <v>92</v>
       </c>
       <c r="H142" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J142" s="11">
         <v>46310.125</v>
@@ -16035,7 +15976,7 @@
         <v>48</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D143" s="0" t="s">
         <v>316</v>
@@ -16121,7 +16062,7 @@
         <v>48</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D144" s="0" t="s">
         <v>316</v>
@@ -16207,19 +16148,19 @@
         <v>48</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E145" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H145" s="0" t="s">
         <v>39</v>
@@ -16293,7 +16234,7 @@
         <v>48</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D146" s="0" t="s">
         <v>316</v>
@@ -16379,7 +16320,7 @@
         <v>48</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D147" s="0" t="s">
         <v>316</v>
@@ -16465,13 +16406,13 @@
         <v>48</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F148" s="0" t="s">
         <v>92</v>
@@ -16551,13 +16492,13 @@
         <v>48</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F149" s="0" t="s">
         <v>165</v>
@@ -16637,7 +16578,7 @@
         <v>34</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D150" s="0" t="s">
         <v>298</v>
@@ -16652,7 +16593,7 @@
         <v>63</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J150" s="11">
         <v>46310.125</v>
@@ -16723,7 +16664,7 @@
         <v>34</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D151" s="0" t="s">
         <v>298</v>
@@ -16738,14 +16679,14 @@
         <v>63</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J151" s="11"/>
       <c r="K151" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L151" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M151" s="0" t="s">
         <v>39</v>
@@ -16807,7 +16748,7 @@
         <v>59</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D152" s="0" t="s">
         <v>159</v>
@@ -16822,7 +16763,7 @@
         <v>83</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J152" s="11">
         <v>46310.125</v>
@@ -16893,7 +16834,7 @@
         <v>34</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D153" s="0" t="s">
         <v>371</v>
@@ -16979,13 +16920,13 @@
         <v>34</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F154" s="0" t="s">
         <v>333</v>
@@ -17065,13 +17006,13 @@
         <v>48</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F155" s="0" t="s">
         <v>127</v>
@@ -17080,7 +17021,7 @@
         <v>127</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J155" s="11">
         <v>46305.125</v>
@@ -17151,7 +17092,7 @@
         <v>48</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D156" s="0" t="s">
         <v>75</v>
@@ -17166,7 +17107,7 @@
         <v>52</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J156" s="11">
         <v>46311.125</v>
@@ -17240,7 +17181,7 @@
         <v>48</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D157" s="0" t="s">
         <v>339</v>
@@ -17326,7 +17267,7 @@
         <v>48</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D158" s="0" t="s">
         <v>313</v>
@@ -17335,10 +17276,10 @@
         <v>313</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H158" s="0" t="s">
         <v>39</v>
@@ -17412,7 +17353,7 @@
         <v>59</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D159" s="0" t="s">
         <v>325</v>
@@ -17501,13 +17442,13 @@
         <v>48</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D160" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F160" s="0" t="s">
         <v>134</v>
@@ -17587,7 +17528,7 @@
         <v>48</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D161" s="0" t="s">
         <v>325</v>
@@ -17673,7 +17614,7 @@
         <v>34</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D162" s="0" t="s">
         <v>119</v>
@@ -17695,7 +17636,7 @@
         <v>211</v>
       </c>
       <c r="L162" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M162" s="0" t="s">
         <v>39</v>
@@ -17757,19 +17698,19 @@
         <v>48</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D163" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E163" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G163" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H163" s="0" t="s">
         <v>39</v>
@@ -17843,13 +17784,13 @@
         <v>34</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D164" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E164" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F164" s="0" t="s">
         <v>121</v>
@@ -17929,7 +17870,7 @@
         <v>34</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D165" s="0" t="s">
         <v>305</v>
@@ -18015,13 +17956,13 @@
         <v>59</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D166" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E166" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F166" s="0" t="s">
         <v>63</v>
@@ -18030,7 +17971,7 @@
         <v>63</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J166" s="11">
         <v>46310.125</v>
@@ -18101,19 +18042,19 @@
         <v>48</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H167" s="0" t="s">
         <v>39</v>
@@ -18187,7 +18128,7 @@
         <v>48</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D168" s="0" t="s">
         <v>316</v>
@@ -18273,13 +18214,13 @@
         <v>48</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E169" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F169" s="0" t="s">
         <v>53</v>
@@ -18359,7 +18300,7 @@
         <v>48</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D170" s="0" t="s">
         <v>339</v>
@@ -18368,10 +18309,10 @@
         <v>339</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H170" s="0" t="s">
         <v>39</v>
@@ -18445,13 +18386,13 @@
         <v>48</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F171" s="0" t="s">
         <v>190</v>
@@ -18531,7 +18472,7 @@
         <v>48</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D172" s="0" t="s">
         <v>371</v>
@@ -18552,10 +18493,10 @@
         <v>46310.125</v>
       </c>
       <c r="K172" s="0" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="L172" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M172" s="0" t="s">
         <v>39</v>
@@ -18617,13 +18558,13 @@
         <v>48</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D173" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F173" s="0" t="s">
         <v>186</v>
@@ -18703,7 +18644,7 @@
         <v>48</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D174" s="0" t="s">
         <v>307</v>
@@ -18789,7 +18730,7 @@
         <v>48</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D175" s="0" t="s">
         <v>305</v>
@@ -18875,7 +18816,7 @@
         <v>48</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D176" s="0" t="s">
         <v>298</v>
@@ -18961,7 +18902,7 @@
         <v>48</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D177" s="0" t="s">
         <v>298</v>
@@ -19047,7 +18988,7 @@
         <v>48</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D178" s="0" t="s">
         <v>329</v>
@@ -19133,19 +19074,19 @@
         <v>48</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D179" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H179" s="0" t="s">
         <v>39</v>
@@ -19219,13 +19160,13 @@
         <v>48</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D180" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E180" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F180" s="0" t="s">
         <v>190</v>
@@ -19305,13 +19246,13 @@
         <v>48</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D181" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>92</v>
@@ -19391,7 +19332,7 @@
         <v>48</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D182" s="0" t="s">
         <v>298</v>
@@ -19477,13 +19418,13 @@
         <v>48</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>52</v>
@@ -19563,13 +19504,13 @@
         <v>48</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D184" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F184" s="0" t="s">
         <v>240</v>
@@ -19649,13 +19590,13 @@
         <v>48</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D185" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>92</v>
@@ -19738,7 +19679,7 @@
         <v>48</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D186" s="0" t="s">
         <v>298</v>
@@ -19824,13 +19765,13 @@
         <v>48</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F187" s="0" t="s">
         <v>53</v>
@@ -19910,22 +19851,22 @@
         <v>34</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D188" s="0" t="s">
         <v>75</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G188" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J188" s="11">
         <v>46310.125</v>
@@ -19996,13 +19937,13 @@
         <v>34</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D189" s="0" t="s">
         <v>256</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F189" s="0" t="s">
         <v>139</v>
@@ -20011,7 +19952,7 @@
         <v>139</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J189" s="11">
         <v>46306.125</v>
@@ -20082,7 +20023,7 @@
         <v>34</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D190" s="0" t="s">
         <v>159</v>
@@ -20097,7 +20038,7 @@
         <v>139</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J190" s="11">
         <v>46361.125</v>
@@ -20168,13 +20109,13 @@
         <v>59</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D191" s="0" t="s">
         <v>246</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F191" s="0" t="s">
         <v>52</v>
@@ -20183,7 +20124,7 @@
         <v>52</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J191" s="11">
         <v>46373.125</v>
@@ -20254,13 +20195,13 @@
         <v>59</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D192" s="0" t="s">
         <v>75</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F192" s="0" t="s">
         <v>254</v>
@@ -20269,7 +20210,7 @@
         <v>254</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J192" s="11">
         <v>46373.125</v>
@@ -20340,13 +20281,13 @@
         <v>59</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D193" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F193" s="0" t="s">
         <v>174</v>
@@ -20355,7 +20296,7 @@
         <v>174</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J193" s="11">
         <v>46310.125</v>
@@ -20417,19 +20358,19 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B194" s="0" t="s">
         <v>48</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F194" s="0" t="s">
         <v>127</v>
@@ -20438,7 +20379,7 @@
         <v>127</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J194" s="11">
         <v>46349.125</v>
@@ -20509,13 +20450,13 @@
         <v>34</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D195" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>152</v>
@@ -20524,7 +20465,7 @@
         <v>152</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J195" s="11">
         <v>46311.125</v>
@@ -20595,13 +20536,13 @@
         <v>34</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D196" s="0" t="s">
         <v>225</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F196" s="0" t="s">
         <v>139</v>
@@ -20610,7 +20551,7 @@
         <v>139</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J196" s="11">
         <v>46306.125</v>
@@ -20681,7 +20622,7 @@
         <v>34</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D197" s="0" t="s">
         <v>119</v>
@@ -20767,7 +20708,7 @@
         <v>34</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D198" s="0" t="s">
         <v>119</v>
@@ -20853,13 +20794,13 @@
         <v>59</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D199" s="0" t="s">
         <v>246</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F199" s="0" t="s">
         <v>53</v>
@@ -20868,7 +20809,7 @@
         <v>83</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J199" s="11">
         <v>46310.125</v>
@@ -20942,13 +20883,13 @@
         <v>59</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D200" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E200" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F200" s="0" t="s">
         <v>72</v>
@@ -20957,7 +20898,7 @@
         <v>63</v>
       </c>
       <c r="H200" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J200" s="11">
         <v>46310.125</v>
@@ -21031,13 +20972,13 @@
         <v>59</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D201" s="0" t="s">
         <v>256</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F201" s="0" t="s">
         <v>52</v>
@@ -21046,7 +20987,7 @@
         <v>52</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J201" s="11">
         <v>46310.125</v>
@@ -21117,7 +21058,7 @@
         <v>59</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D202" s="0" t="s">
         <v>75</v>
@@ -21132,7 +21073,7 @@
         <v>139</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J202" s="11">
         <v>46310.125</v>
@@ -21203,7 +21144,7 @@
         <v>59</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D203" s="0" t="s">
         <v>159</v>
@@ -21212,13 +21153,13 @@
         <v>181</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G203" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J203" s="11">
         <v>46346.125</v>
@@ -21289,7 +21230,7 @@
         <v>59</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D204" s="0" t="s">
         <v>75</v>
@@ -21304,7 +21245,7 @@
         <v>333</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J204" s="11">
         <v>46310.125</v>
@@ -21375,7 +21316,7 @@
         <v>59</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D205" s="0" t="s">
         <v>159</v>
@@ -21384,13 +21325,13 @@
         <v>173</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J205" s="11">
         <v>46373.125</v>
@@ -21461,13 +21402,13 @@
         <v>59</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D206" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F206" s="0" t="s">
         <v>147</v>
@@ -21476,7 +21417,7 @@
         <v>121</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J206" s="11">
         <v>46310.125</v>
@@ -21547,13 +21488,13 @@
         <v>48</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D207" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F207" s="0" t="s">
         <v>182</v>
@@ -21633,7 +21574,7 @@
         <v>59</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D208" s="0" t="s">
         <v>159</v>
@@ -21642,13 +21583,13 @@
         <v>173</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J208" s="11">
         <v>46310.125</v>
@@ -21719,13 +21660,13 @@
         <v>48</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D209" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F209" s="0" t="s">
         <v>127</v>
@@ -21799,28 +21740,28 @@
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B210" s="0" t="s">
         <v>59</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D210" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J210" s="11">
         <v>46373.125</v>
@@ -21894,13 +21835,13 @@
         <v>34</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D211" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F211" s="0" t="s">
         <v>146</v>
@@ -21909,7 +21850,7 @@
         <v>146</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J211" s="11">
         <v>46304.125</v>
@@ -21980,7 +21921,7 @@
         <v>34</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D212" s="0" t="s">
         <v>137</v>
@@ -21989,13 +21930,13 @@
         <v>138</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G212" s="0" t="s">
         <v>152</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J212" s="11">
         <v>46397.125</v>
@@ -22066,10 +22007,10 @@
         <v>34</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E213" s="0" t="s">
         <v>185</v>
@@ -22081,7 +22022,7 @@
         <v>139</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J213" s="11">
         <v>46304.125</v>
@@ -22152,13 +22093,13 @@
         <v>34</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D214" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F214" s="0" t="s">
         <v>121</v>
@@ -22167,7 +22108,7 @@
         <v>121</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J214" s="11">
         <v>46310.125</v>
@@ -22238,7 +22179,7 @@
         <v>34</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D215" s="0" t="s">
         <v>75</v>
@@ -22253,7 +22194,7 @@
         <v>52</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J215" s="11">
         <v>46365.125</v>
@@ -22324,13 +22265,13 @@
         <v>34</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D216" s="0" t="s">
         <v>225</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F216" s="0" t="s">
         <v>166</v>
@@ -22339,7 +22280,7 @@
         <v>166</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J216" s="11">
         <v>46310.125</v>
@@ -22348,7 +22289,7 @@
         <v>40</v>
       </c>
       <c r="L216" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M216" s="0" t="s">
         <v>39</v>
@@ -22410,13 +22351,13 @@
         <v>34</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D217" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F217" s="0" t="s">
         <v>63</v>
@@ -22425,7 +22366,7 @@
         <v>63</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J217" s="11">
         <v>46387.125</v>
@@ -22496,13 +22437,13 @@
         <v>59</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D218" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F218" s="0" t="s">
         <v>134</v>
@@ -22582,7 +22523,7 @@
         <v>34</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D219" s="0" t="s">
         <v>119</v>
@@ -22597,7 +22538,7 @@
         <v>72</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J219" s="11">
         <v>46305.125</v>
@@ -22668,7 +22609,7 @@
         <v>34</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D220" s="0" t="s">
         <v>119</v>
@@ -22683,7 +22624,7 @@
         <v>72</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J220" s="11">
         <v>46305.125</v>
@@ -22754,7 +22695,7 @@
         <v>34</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D221" s="0" t="s">
         <v>119</v>
@@ -22769,7 +22710,7 @@
         <v>320</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J221" s="11">
         <v>46310.125</v>
@@ -22840,13 +22781,13 @@
         <v>34</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D222" s="0" t="s">
         <v>75</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F222" s="0" t="s">
         <v>326</v>
@@ -22855,7 +22796,7 @@
         <v>186</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J222" s="11">
         <v>46310.125</v>
@@ -22926,13 +22867,13 @@
         <v>34</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D223" s="0" t="s">
         <v>36</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F223" s="0" t="s">
         <v>182</v>
@@ -22941,7 +22882,7 @@
         <v>182</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J223" s="11">
         <v>46310.125</v>
@@ -22980,7 +22921,7 @@
         <v>43</v>
       </c>
       <c r="AC223" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AD223" s="11">
         <v>45469.764935231484</v>
@@ -23012,7 +22953,7 @@
         <v>34</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D224" s="0" t="s">
         <v>137</v>
@@ -23027,7 +22968,7 @@
         <v>333</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J224" s="11">
         <v>46310.125</v>
@@ -23066,7 +23007,7 @@
         <v>43</v>
       </c>
       <c r="AC224" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AD224" s="11">
         <v>45469.782337986115</v>
@@ -23098,7 +23039,7 @@
         <v>48</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D225" s="0" t="s">
         <v>291</v>
@@ -23184,7 +23125,7 @@
         <v>34</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D226" s="0" t="s">
         <v>215</v>
@@ -23199,7 +23140,7 @@
         <v>38</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J226" s="11">
         <v>46310.125</v>
@@ -23238,7 +23179,7 @@
         <v>44</v>
       </c>
       <c r="AC226" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AD226" s="11">
         <v>45471.71127222222</v>
@@ -23270,7 +23211,7 @@
         <v>34</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D227" s="0" t="s">
         <v>215</v>
@@ -23285,7 +23226,7 @@
         <v>38</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J227" s="11">
         <v>46310.125</v>
@@ -23324,7 +23265,7 @@
         <v>44</v>
       </c>
       <c r="AC227" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AD227" s="11">
         <v>45471.728454502314</v>
@@ -23356,13 +23297,13 @@
         <v>34</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D228" s="0" t="s">
         <v>215</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F228" s="0" t="s">
         <v>72</v>
@@ -23442,7 +23383,7 @@
         <v>59</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D229" s="0" t="s">
         <v>50</v>
@@ -23457,7 +23398,7 @@
         <v>127</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J229" s="11">
         <v>46373.125</v>
@@ -23528,13 +23469,13 @@
         <v>59</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D230" s="0" t="s">
         <v>75</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F230" s="0" t="s">
         <v>139</v>
@@ -23617,13 +23558,13 @@
         <v>34</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D231" s="0" t="s">
         <v>177</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F231" s="0" t="s">
         <v>240</v>
@@ -23632,7 +23573,7 @@
         <v>240</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J231" s="11">
         <v>46318.125</v>
@@ -23700,13 +23641,13 @@
         <v>59</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D232" s="0" t="s">
         <v>75</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F232" s="0" t="s">
         <v>147</v>
@@ -23783,7 +23724,7 @@
         <v>59</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D233" s="0" t="s">
         <v>266</v>
@@ -23869,13 +23810,13 @@
         <v>48</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D234" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F234" s="0" t="s">
         <v>92</v>
@@ -23884,7 +23825,7 @@
         <v>38</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J234" s="11">
         <v>46310.125</v>
@@ -23955,7 +23896,7 @@
         <v>48</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D235" s="0" t="s">
         <v>298</v>
@@ -23970,7 +23911,7 @@
         <v>320</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J235" s="11">
         <v>46310.125</v>
@@ -24041,7 +23982,7 @@
         <v>48</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D236" s="0" t="s">
         <v>298</v>
@@ -24056,7 +23997,7 @@
         <v>320</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J236" s="11">
         <v>46311.125</v>
@@ -24127,13 +24068,13 @@
         <v>48</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F237" s="0" t="s">
         <v>147</v>
@@ -24142,7 +24083,7 @@
         <v>147</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J237" s="11">
         <v>46340.125</v>
@@ -24213,13 +24154,13 @@
         <v>48</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D238" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F238" s="0" t="s">
         <v>146</v>
@@ -24228,7 +24169,7 @@
         <v>146</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J238" s="11">
         <v>46311.125</v>
@@ -24299,13 +24240,13 @@
         <v>48</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D239" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F239" s="0" t="s">
         <v>146</v>
@@ -24314,7 +24255,7 @@
         <v>146</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J239" s="11">
         <v>46311.125</v>
@@ -24385,7 +24326,7 @@
         <v>48</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D240" s="0" t="s">
         <v>291</v>
@@ -24400,7 +24341,7 @@
         <v>198</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="J240" s="11">
         <v>46374.125</v>
@@ -24471,13 +24412,13 @@
         <v>34</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D241" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F241" s="0" t="s">
         <v>146</v>
@@ -24554,13 +24495,13 @@
         <v>34</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D242" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F242" s="0" t="s">
         <v>198</v>
@@ -24569,7 +24510,7 @@
         <v>205</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="J242" s="11">
         <v>46309.125</v>
@@ -24640,7 +24581,7 @@
         <v>34</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D243" s="0" t="s">
         <v>119</v>
@@ -24655,7 +24596,7 @@
         <v>121</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="J243" s="11">
         <v>46305.125</v>
@@ -24726,7 +24667,7 @@
         <v>34</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D244" s="0" t="s">
         <v>119</v>
@@ -24741,7 +24682,7 @@
         <v>121</v>
       </c>
       <c r="H244" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="J244" s="11">
         <v>46306.125</v>
@@ -24812,7 +24753,7 @@
         <v>34</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D245" s="0" t="s">
         <v>36</v>
@@ -24827,20 +24768,20 @@
         <v>77</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J245" s="11"/>
       <c r="K245" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L245" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M245" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N245" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O245" s="11">
         <v>46660.125</v>
@@ -24892,13 +24833,13 @@
         <v>59</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D246" s="0" t="s">
         <v>75</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F246" s="0" t="s">
         <v>92</v>
@@ -24975,13 +24916,13 @@
         <v>34</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D247" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E247" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F247" s="0" t="s">
         <v>121</v>
@@ -24990,7 +24931,7 @@
         <v>121</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J247" s="11">
         <v>46367.125</v>
@@ -25058,10 +24999,10 @@
         <v>48</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E248" s="0" t="s">
         <v>216</v>
@@ -25073,7 +25014,7 @@
         <v>92</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J248" s="11">
         <v>46425.125</v>
@@ -25144,13 +25085,13 @@
         <v>59</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D249" s="0" t="s">
         <v>75</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F249" s="0" t="s">
         <v>72</v>
@@ -25159,7 +25100,7 @@
         <v>72</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J249" s="11">
         <v>46310.125</v>
@@ -25233,7 +25174,7 @@
         <v>34</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D250" s="0" t="s">
         <v>50</v>
@@ -25248,7 +25189,7 @@
         <v>92</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J250" s="11">
         <v>46310.125</v>
@@ -25319,7 +25260,7 @@
         <v>34</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D251" s="0" t="s">
         <v>246</v>
@@ -25334,7 +25275,7 @@
         <v>134</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J251" s="11">
         <v>46310.125</v>
@@ -25405,13 +25346,13 @@
         <v>59</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D252" s="0" t="s">
         <v>215</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F252" s="0" t="s">
         <v>198</v>
@@ -25456,7 +25397,7 @@
         <v>43</v>
       </c>
       <c r="AC252" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AD252" s="11">
         <v>45580.69804725694</v>
@@ -25482,25 +25423,25 @@
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B253" s="0" t="s">
         <v>223</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D253" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H253" s="0" t="s">
         <v>39</v>
@@ -25571,13 +25512,13 @@
         <v>223</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D254" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E254" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F254" s="0" t="s">
         <v>254</v>
@@ -25654,13 +25595,13 @@
         <v>223</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D255" s="0" t="s">
         <v>75</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F255" s="0" t="s">
         <v>38</v>
@@ -25737,10 +25678,10 @@
         <v>223</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D256" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E256" s="0" t="s">
         <v>256</v>
@@ -25820,7 +25761,7 @@
         <v>223</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D257" s="0" t="s">
         <v>50</v>
@@ -25897,19 +25838,19 @@
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B258" s="0" t="s">
         <v>223</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D258" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E258" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F258" s="0" t="s">
         <v>72</v>
@@ -25980,19 +25921,19 @@
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B259" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D259" s="0" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F259" s="0" t="s">
         <v>63</v>
@@ -26035,7 +25976,7 @@
         <v>43</v>
       </c>
       <c r="AC259" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AD259" s="11">
         <v>45707.53582697917</v>
@@ -26061,19 +26002,19 @@
     </row>
     <row r="260">
       <c r="A260" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B260" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D260" s="0" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F260" s="0" t="s">
         <v>72</v>
@@ -26118,7 +26059,7 @@
         <v>43</v>
       </c>
       <c r="AC260" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AD260" s="11">
         <v>45707.53582697917</v>
@@ -26144,19 +26085,19 @@
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B261" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D261" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F261" s="0" t="s">
         <v>38</v>
@@ -26167,20 +26108,18 @@
       <c r="H261" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="J261" s="11">
-        <v>46297.125</v>
-      </c>
+      <c r="J261" s="11"/>
       <c r="K261" s="0" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="L261" s="0" t="s">
-        <v>41</v>
+        <v>212</v>
       </c>
       <c r="M261" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N261" s="0" t="s">
-        <v>42</v>
+        <v>213</v>
       </c>
       <c r="O261" s="11">
         <v>46297.125</v>
@@ -26201,7 +26140,7 @@
         <v>43</v>
       </c>
       <c r="AC261" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AD261" s="11">
         <v>45707.53582697917</v>
@@ -26227,19 +26166,19 @@
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B262" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F262" s="0" t="s">
         <v>58</v>
@@ -26284,7 +26223,7 @@
         <v>43</v>
       </c>
       <c r="AC262" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AD262" s="11">
         <v>45707.53582697917</v>
@@ -26313,22 +26252,22 @@
         <v>242</v>
       </c>
       <c r="B263" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D263" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F263" s="0" t="s">
         <v>240</v>
       </c>
       <c r="G263" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H263" s="0" t="s">
         <v>39</v>
@@ -26367,7 +26306,7 @@
         <v>44</v>
       </c>
       <c r="AC263" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AD263" s="11">
         <v>45707.53582697917</v>
@@ -26393,19 +26332,19 @@
     </row>
     <row r="264">
       <c r="A264" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B264" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D264" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F264" s="0" t="s">
         <v>165</v>
@@ -26450,7 +26389,7 @@
         <v>43</v>
       </c>
       <c r="AC264" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AD264" s="11">
         <v>45707.56401729167</v>
@@ -26476,19 +26415,19 @@
     </row>
     <row r="265">
       <c r="A265" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B265" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D265" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F265" s="0" t="s">
         <v>63</v>
@@ -26533,7 +26472,7 @@
         <v>43</v>
       </c>
       <c r="AC265" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AD265" s="11">
         <v>45707.56401729167</v>
@@ -26559,19 +26498,19 @@
     </row>
     <row r="266">
       <c r="A266" s="0" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B266" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E266" s="0" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F266" s="0" t="s">
         <v>131</v>
@@ -26616,7 +26555,7 @@
         <v>43</v>
       </c>
       <c r="AC266" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AD266" s="11">
         <v>45707.56401729167</v>
@@ -26642,19 +26581,19 @@
     </row>
     <row r="267">
       <c r="A267" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B267" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E267" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F267" s="0" t="s">
         <v>72</v>
@@ -26699,7 +26638,7 @@
         <v>43</v>
       </c>
       <c r="AC267" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AD267" s="11">
         <v>45707.56401729167</v>
@@ -26725,19 +26664,19 @@
     </row>
     <row r="268">
       <c r="A268" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B268" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E268" s="0" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F268" s="0" t="s">
         <v>131</v>
@@ -26785,7 +26724,7 @@
         <v>43</v>
       </c>
       <c r="AC268" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD268" s="11">
         <v>45709.67990524306</v>
@@ -26811,19 +26750,19 @@
     </row>
     <row r="269">
       <c r="A269" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B269" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D269" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E269" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F269" s="0" t="s">
         <v>72</v>
@@ -26871,7 +26810,7 @@
         <v>43</v>
       </c>
       <c r="AC269" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD269" s="11">
         <v>45709.67990524306</v>
@@ -26903,13 +26842,13 @@
         <v>59</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D270" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E270" s="0" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F270" s="0" t="s">
         <v>205</v>
@@ -26954,7 +26893,7 @@
         <v>44</v>
       </c>
       <c r="AC270" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AD270" s="11">
         <v>45712.43438770833</v>
@@ -26986,7 +26925,7 @@
         <v>59</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D271" s="0" t="s">
         <v>196</v>
@@ -27005,7 +26944,7 @@
         <v>211</v>
       </c>
       <c r="L271" s="0" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M271" s="0" t="s">
         <v>39</v>
@@ -27035,7 +26974,7 @@
         <v>43</v>
       </c>
       <c r="AC271" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AD271" s="11">
         <v>45741.81156357639</v>
@@ -27061,19 +27000,19 @@
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B272" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D272" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F272" s="0" t="s">
         <v>38</v>
@@ -27081,20 +27020,18 @@
       <c r="G272" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="J272" s="11">
-        <v>46297.125</v>
-      </c>
+      <c r="J272" s="11"/>
       <c r="K272" s="0" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="L272" s="0" t="s">
-        <v>41</v>
+        <v>212</v>
       </c>
       <c r="M272" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N272" s="0" t="s">
-        <v>42</v>
+        <v>213</v>
       </c>
       <c r="O272" s="11">
         <v>46297.125</v>
@@ -27115,7 +27052,7 @@
         <v>43</v>
       </c>
       <c r="AC272" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AD272" s="11">
         <v>45777.62400894676</v>
@@ -27147,7 +27084,7 @@
         <v>34</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D273" s="0" t="s">
         <v>50</v>
@@ -27227,32 +27164,32 @@
     </row>
     <row r="274">
       <c r="A274" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B274" s="0" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D274" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G274" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="J274" s="11"/>
       <c r="K274" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L274" s="0" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M274" s="0" t="s">
         <v>39</v>
@@ -27276,7 +27213,7 @@
         <v>44</v>
       </c>
       <c r="AC274" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AD274" s="11">
         <v>45817.61092795139</v>
@@ -27302,32 +27239,32 @@
     </row>
     <row r="275">
       <c r="A275" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B275" s="0" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D275" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F275" s="0" t="s">
         <v>166</v>
       </c>
       <c r="G275" s="0" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J275" s="11"/>
       <c r="K275" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L275" s="0" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M275" s="0" t="s">
         <v>39</v>
@@ -27354,7 +27291,7 @@
         <v>44</v>
       </c>
       <c r="AC275" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AD275" s="11">
         <v>45817.61552398148</v>
@@ -27386,7 +27323,7 @@
         <v>48</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D276" s="0" t="s">
         <v>307</v>
@@ -27401,7 +27338,7 @@
         <v>127</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J276" s="11">
         <v>46310.125</v>
@@ -27472,7 +27409,7 @@
         <v>48</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D277" s="0" t="s">
         <v>305</v>
@@ -27484,10 +27421,10 @@
         <v>127</v>
       </c>
       <c r="G277" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J277" s="11">
         <v>46310.125</v>
@@ -27558,13 +27495,13 @@
         <v>59</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D278" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E278" s="0" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F278" s="0" t="s">
         <v>63</v>
@@ -27573,7 +27510,7 @@
         <v>63</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="J278" s="11">
         <v>46357.125</v>
@@ -27644,7 +27581,7 @@
         <v>34</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D279" s="0" t="s">
         <v>159</v>
@@ -27659,14 +27596,14 @@
         <v>333</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="J279" s="11"/>
       <c r="K279" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L279" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M279" s="0" t="s">
         <v>39</v>
@@ -27725,13 +27662,13 @@
         <v>48</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D280" s="0" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E280" s="0" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F280" s="0" t="s">
         <v>165</v>
@@ -27740,7 +27677,7 @@
         <v>165</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="J280" s="11">
         <v>46306.125</v>
@@ -27811,13 +27748,13 @@
         <v>34</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D281" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F281" s="0" t="s">
         <v>198</v>
@@ -27826,14 +27763,14 @@
         <v>198</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="J281" s="11"/>
       <c r="K281" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L281" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M281" s="0" t="s">
         <v>39</v>
@@ -27895,13 +27832,13 @@
         <v>48</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D282" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F282" s="0" t="s">
         <v>72</v>
@@ -27910,7 +27847,7 @@
         <v>72</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J282" s="11">
         <v>46310.125</v>
@@ -27981,7 +27918,7 @@
         <v>48</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D283" s="0" t="s">
         <v>362</v>
@@ -27996,7 +27933,7 @@
         <v>206</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J283" s="11">
         <v>46304.125</v>
@@ -28067,7 +28004,7 @@
         <v>48</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D284" s="0" t="s">
         <v>364</v>
@@ -28082,7 +28019,7 @@
         <v>206</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J284" s="11">
         <v>46304.125</v>
@@ -28147,19 +28084,19 @@
     </row>
     <row r="285">
       <c r="A285" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B285" s="0" t="s">
         <v>48</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D285" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F285" s="0" t="s">
         <v>228</v>
@@ -28168,7 +28105,7 @@
         <v>228</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J285" s="11">
         <v>46374.125</v>
@@ -28239,7 +28176,7 @@
         <v>34</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D286" s="0" t="s">
         <v>50</v>
@@ -28254,7 +28191,7 @@
         <v>72</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J286" s="11">
         <v>46306.125</v>
@@ -28325,13 +28262,13 @@
         <v>48</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D287" s="0" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F287" s="0" t="s">
         <v>166</v>
@@ -28408,7 +28345,7 @@
         <v>48</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D288" s="0" t="s">
         <v>298</v>
@@ -28494,7 +28431,7 @@
         <v>48</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D289" s="0" t="s">
         <v>298</v>
@@ -28580,7 +28517,7 @@
         <v>34</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D290" s="0" t="s">
         <v>119</v>
@@ -28666,7 +28603,7 @@
         <v>34</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D291" s="0" t="s">
         <v>119</v>
@@ -28752,7 +28689,7 @@
         <v>34</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D292" s="0" t="s">
         <v>70</v>
@@ -28838,7 +28775,7 @@
         <v>34</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D293" s="0" t="s">
         <v>70</v>
@@ -28924,7 +28861,7 @@
         <v>34</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D294" s="0" t="s">
         <v>50</v>
@@ -28939,7 +28876,7 @@
         <v>131</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J294" s="11">
         <v>46310.125</v>
@@ -29010,13 +28947,13 @@
         <v>59</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D295" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F295" s="0" t="s">
         <v>165</v>
@@ -29025,7 +28962,7 @@
         <v>165</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J295" s="11">
         <v>46373.125</v>
@@ -29096,7 +29033,7 @@
         <v>59</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D296" s="0" t="s">
         <v>36</v>
@@ -29111,7 +29048,7 @@
         <v>38</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J296" s="11">
         <v>46373.125</v>
@@ -29182,7 +29119,7 @@
         <v>59</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D297" s="0" t="s">
         <v>36</v>
@@ -29197,7 +29134,7 @@
         <v>38</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J297" s="11">
         <v>46373.125</v>
@@ -29268,13 +29205,13 @@
         <v>34</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D298" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F298" s="0" t="s">
         <v>165</v>
@@ -29283,7 +29220,7 @@
         <v>166</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="J298" s="11">
         <v>46311.125</v>
@@ -29354,7 +29291,7 @@
         <v>34</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D299" s="0" t="s">
         <v>75</v>
@@ -29369,7 +29306,7 @@
         <v>134</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J299" s="11">
         <v>46304.125</v>
@@ -29440,13 +29377,13 @@
         <v>34</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D300" s="0" t="s">
         <v>108</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F300" s="0" t="s">
         <v>146</v>
@@ -29455,7 +29392,7 @@
         <v>146</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J300" s="11">
         <v>46365.125</v>
@@ -29526,13 +29463,13 @@
         <v>34</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D301" s="0" t="s">
         <v>108</v>
       </c>
       <c r="E301" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F301" s="0" t="s">
         <v>146</v>
@@ -29541,14 +29478,16 @@
         <v>146</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>714</v>
-      </c>
-      <c r="J301" s="11"/>
+        <v>715</v>
+      </c>
+      <c r="J301" s="11">
+        <v>46304.125</v>
+      </c>
       <c r="K301" s="0" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="L301" s="0" t="s">
-        <v>718</v>
+        <v>106</v>
       </c>
       <c r="M301" s="0" t="s">
         <v>39</v>
@@ -29616,7 +29555,7 @@
         <v>159</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F302" s="0" t="s">
         <v>127</v>
@@ -29690,16 +29629,16 @@
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B303" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C303" s="0" t="s">
         <v>721</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E303" s="0" t="s">
         <v>722</v>
@@ -29750,7 +29689,7 @@
         <v>43</v>
       </c>
       <c r="AC303" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD303" s="11">
         <v>45824.65492918981</v>
@@ -29969,7 +29908,7 @@
         <v>63</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J306" s="11">
         <v>46310.125</v>
@@ -30213,7 +30152,7 @@
         <v>731</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E309" s="0" t="s">
         <v>71</v>
@@ -30658,7 +30597,7 @@
         <v>63</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J314" s="11">
         <v>46310.125</v>
@@ -30904,7 +30843,7 @@
         <v>742</v>
       </c>
       <c r="D317" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E317" s="0" t="s">
         <v>85</v>
@@ -31435,7 +31374,7 @@
         <v>92</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J323" s="11">
         <v>46310.125</v>
@@ -31500,7 +31439,7 @@
     </row>
     <row r="324">
       <c r="A324" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B324" s="0" t="s">
         <v>48</v>
@@ -31509,10 +31448,10 @@
         <v>751</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E324" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F324" s="0" t="s">
         <v>92</v>
@@ -31598,7 +31537,7 @@
         <v>159</v>
       </c>
       <c r="E325" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F325" s="0" t="s">
         <v>240</v>
@@ -32022,7 +31961,7 @@
         <v>763</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E330" s="0" t="s">
         <v>85</v>
@@ -32108,7 +32047,7 @@
         <v>764</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E331" s="0" t="s">
         <v>71</v>
@@ -32464,7 +32403,7 @@
         <v>121</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J335" s="11">
         <v>46373.125</v>
@@ -32550,7 +32489,7 @@
         <v>121</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J336" s="11">
         <v>46373.125</v>
@@ -32636,7 +32575,7 @@
         <v>127</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J337" s="11">
         <v>46373.125</v>
@@ -32722,7 +32661,7 @@
         <v>127</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J338" s="11">
         <v>46373.125</v>
@@ -32980,7 +32919,7 @@
         <v>92</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J341" s="11">
         <v>46310.125</v>
@@ -33066,7 +33005,7 @@
         <v>92</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J342" s="11">
         <v>46310.125</v>
@@ -33312,7 +33251,7 @@
         <v>783</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E345" s="0" t="s">
         <v>209</v>
@@ -33561,7 +33500,7 @@
         <v>788</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E348" s="0" t="s">
         <v>71</v>
@@ -33752,7 +33691,7 @@
         <v>211</v>
       </c>
       <c r="L350" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M350" s="0" t="s">
         <v>39</v>
@@ -33915,7 +33854,7 @@
         <v>92</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J352" s="11">
         <v>46310.125</v>
@@ -34250,10 +34189,10 @@
         <v>209</v>
       </c>
       <c r="F356" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G356" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H356" s="0" t="s">
         <v>799</v>
@@ -34339,7 +34278,7 @@
         <v>240</v>
       </c>
       <c r="G357" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H357" s="0" t="s">
         <v>799</v>
@@ -34579,7 +34518,7 @@
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B360" s="0" t="s">
         <v>223</v>
@@ -34588,16 +34527,16 @@
         <v>804</v>
       </c>
       <c r="D360" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E360" s="0" t="s">
         <v>805</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G360" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J360" s="11">
         <v>46325.125</v>
@@ -34920,7 +34859,7 @@
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B364" s="0" t="s">
         <v>812</v>
@@ -35000,7 +34939,7 @@
         <v>815</v>
       </c>
       <c r="B365" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C365" s="0" t="s">
         <v>816</v>
@@ -35054,7 +34993,7 @@
         <v>44</v>
       </c>
       <c r="AC365" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD365" s="11">
         <v>45848.39273826389</v>
@@ -35083,7 +35022,7 @@
         <v>815</v>
       </c>
       <c r="B366" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C366" s="0" t="s">
         <v>818</v>
@@ -35137,7 +35076,7 @@
         <v>44</v>
       </c>
       <c r="AC366" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD366" s="11">
         <v>45848.397211875</v>
@@ -35166,13 +35105,13 @@
         <v>819</v>
       </c>
       <c r="B367" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C367" s="0" t="s">
         <v>820</v>
       </c>
       <c r="D367" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E367" s="0" t="s">
         <v>821</v>
@@ -35220,7 +35159,7 @@
         <v>43</v>
       </c>
       <c r="AC367" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD367" s="11">
         <v>45848.4186587963</v>
@@ -35249,7 +35188,7 @@
         <v>819</v>
       </c>
       <c r="B368" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C368" s="0" t="s">
         <v>822</v>
@@ -35303,7 +35242,7 @@
         <v>43</v>
       </c>
       <c r="AC368" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD368" s="11">
         <v>45848.43242736111</v>
@@ -35332,7 +35271,7 @@
         <v>819</v>
       </c>
       <c r="B369" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C369" s="0" t="s">
         <v>824</v>
@@ -35386,7 +35325,7 @@
         <v>43</v>
       </c>
       <c r="AC369" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD369" s="11">
         <v>45848.43568380787</v>
@@ -35415,7 +35354,7 @@
         <v>242</v>
       </c>
       <c r="B370" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C370" s="0" t="s">
         <v>826</v>
@@ -35466,7 +35405,7 @@
         <v>44</v>
       </c>
       <c r="AC370" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AD370" s="11">
         <v>45849.59990366898</v>
@@ -35673,7 +35612,7 @@
         <v>75</v>
       </c>
       <c r="E373" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F373" s="0" t="s">
         <v>190</v>
@@ -35934,7 +35873,7 @@
         <v>75</v>
       </c>
       <c r="E376" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F376" s="0" t="s">
         <v>182</v>
@@ -36023,10 +35962,10 @@
         <v>138</v>
       </c>
       <c r="F377" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G377" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H377" s="0" t="s">
         <v>837</v>
@@ -36358,7 +36297,7 @@
         <v>50</v>
       </c>
       <c r="E381" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F381" s="0" t="s">
         <v>121</v>
@@ -36435,7 +36374,7 @@
         <v>815</v>
       </c>
       <c r="B382" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C382" s="0" t="s">
         <v>847</v>
@@ -36492,7 +36431,7 @@
         <v>44</v>
       </c>
       <c r="AC382" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD382" s="11">
         <v>45915.382719849535</v>
@@ -36518,16 +36457,16 @@
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B383" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C383" s="0" t="s">
         <v>849</v>
       </c>
       <c r="D383" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E383" s="0" t="s">
         <v>722</v>
@@ -36578,7 +36517,7 @@
         <v>43</v>
       </c>
       <c r="AC383" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD383" s="11">
         <v>45943.61639740741</v>
@@ -36607,7 +36546,7 @@
         <v>815</v>
       </c>
       <c r="B384" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C384" s="0" t="s">
         <v>850</v>
@@ -36664,7 +36603,7 @@
         <v>44</v>
       </c>
       <c r="AC384" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD384" s="11">
         <v>45947.41143024305</v>
@@ -36690,10 +36629,10 @@
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B385" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C385" s="0" t="s">
         <v>851</v>
@@ -36750,7 +36689,7 @@
         <v>43</v>
       </c>
       <c r="AC385" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD385" s="11">
         <v>45986.447999421296</v>
@@ -36862,7 +36801,7 @@
     </row>
     <row r="387">
       <c r="A387" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B387" s="0" t="s">
         <v>855</v>
@@ -36948,7 +36887,7 @@
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B388" s="0" t="s">
         <v>855</v>
@@ -37032,7 +36971,7 @@
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B389" s="0" t="s">
         <v>855</v>
@@ -37202,7 +37141,7 @@
         <v>869</v>
       </c>
       <c r="D391" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E391" s="0" t="s">
         <v>870</v>
@@ -37279,7 +37218,7 @@
         <v>873</v>
       </c>
       <c r="D392" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E392" s="0" t="s">
         <v>874</v>
@@ -37569,7 +37508,7 @@
         <v>43</v>
       </c>
       <c r="AC395" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AD395" s="11">
         <v>46076.3667846875</v>
@@ -37646,7 +37585,7 @@
         <v>43</v>
       </c>
       <c r="AC396" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AD396" s="11">
         <v>46076.369408252314</v>
@@ -37677,7 +37616,7 @@
         <v>883</v>
       </c>
       <c r="D397" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E397" s="0" t="s">
         <v>884</v>
@@ -37748,7 +37687,7 @@
         <v>815</v>
       </c>
       <c r="B398" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C398" s="0" t="s">
         <v>887</v>
@@ -37805,7 +37744,7 @@
         <v>44</v>
       </c>
       <c r="AC398" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD398" s="11">
         <v>46111.572644050924</v>
@@ -37831,10 +37770,10 @@
     </row>
     <row r="399">
       <c r="A399" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B399" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C399" s="0" t="s">
         <v>888</v>
@@ -37854,14 +37793,12 @@
       <c r="H399" s="0" t="s">
         <v>723</v>
       </c>
-      <c r="J399" s="11">
-        <v>46298.125</v>
-      </c>
+      <c r="J399" s="11"/>
       <c r="K399" s="0" t="s">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="L399" s="0" t="s">
-        <v>39</v>
+        <v>889</v>
       </c>
       <c r="M399" s="0" t="s">
         <v>39</v>
@@ -37891,7 +37828,7 @@
         <v>43</v>
       </c>
       <c r="AC399" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD399" s="11">
         <v>46118.470583483795</v>
@@ -37906,13 +37843,13 @@
         <v>43</v>
       </c>
       <c r="AH399" s="0" t="s">
-        <v>42</v>
+        <v>213</v>
       </c>
       <c r="AI399" s="3">
         <v>46118.47197717593</v>
       </c>
       <c r="AJ399" s="3">
-        <v>46298.125</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="400">
@@ -37923,13 +37860,13 @@
         <v>59</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E400" s="0" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="F400" s="0" t="s">
         <v>58</v>
@@ -37974,7 +37911,7 @@
         <v>44</v>
       </c>
       <c r="AC400" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AD400" s="11">
         <v>46119.44647047454</v>
@@ -38003,10 +37940,10 @@
         <v>815</v>
       </c>
       <c r="B401" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>108</v>
@@ -38060,7 +37997,7 @@
         <v>44</v>
       </c>
       <c r="AC401" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD401" s="11">
         <v>46132.56225560185</v>
@@ -38092,7 +38029,7 @@
         <v>34</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>196</v>
@@ -38178,13 +38115,13 @@
         <v>48</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D403" s="0" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E403" s="0" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F403" s="0" t="s">
         <v>240</v>
@@ -38193,7 +38130,7 @@
         <v>240</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="J403" s="11">
         <v>46302.125</v>
@@ -38264,13 +38201,13 @@
         <v>48</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D404" s="0" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E404" s="0" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F404" s="0" t="s">
         <v>52</v>
@@ -38279,7 +38216,7 @@
         <v>53</v>
       </c>
       <c r="H404" s="0" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="J404" s="11">
         <v>46357.125</v>
@@ -38350,13 +38287,13 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E405" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F405" s="0" t="s">
         <v>53</v>
@@ -38365,7 +38302,7 @@
         <v>53</v>
       </c>
       <c r="H405" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="J405" s="11">
         <v>46361.125</v>
@@ -38436,13 +38373,13 @@
         <v>34</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E406" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F406" s="0" t="s">
         <v>146</v>
@@ -38451,7 +38388,7 @@
         <v>147</v>
       </c>
       <c r="H406" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J406" s="11">
         <v>46365.125</v>
@@ -38522,7 +38459,7 @@
         <v>34</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>50</v>
@@ -38537,7 +38474,7 @@
         <v>131</v>
       </c>
       <c r="H407" s="0" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="J407" s="11">
         <v>46365.125</v>
@@ -38608,7 +38545,7 @@
         <v>34</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>36</v>
@@ -38623,7 +38560,7 @@
         <v>131</v>
       </c>
       <c r="H408" s="0" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="J408" s="11">
         <v>46305.125</v>
@@ -38694,13 +38631,13 @@
         <v>48</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D409" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E409" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="F409" s="0" t="s">
         <v>53</v>
@@ -38709,7 +38646,7 @@
         <v>53</v>
       </c>
       <c r="H409" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="J409" s="11">
         <v>46365.125</v>
@@ -38780,7 +38717,7 @@
         <v>48</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>316</v>
@@ -38795,7 +38732,7 @@
         <v>131</v>
       </c>
       <c r="H410" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="J410" s="11">
         <v>46362.125</v>
@@ -38866,13 +38803,13 @@
         <v>34</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>75</v>
       </c>
       <c r="E411" s="0" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F411" s="0" t="s">
         <v>63</v>
@@ -38952,7 +38889,7 @@
         <v>34</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>36</v>
@@ -39038,7 +38975,7 @@
         <v>34</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>36</v>
@@ -39124,22 +39061,22 @@
         <v>34</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>75</v>
       </c>
       <c r="E414" s="0" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F414" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G414" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="J414" s="11">
         <v>46305.125</v>
@@ -39210,13 +39147,13 @@
         <v>34</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>70</v>
       </c>
       <c r="E415" s="0" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F415" s="0" t="s">
         <v>131</v>
@@ -39225,7 +39162,7 @@
         <v>131</v>
       </c>
       <c r="H415" s="0" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="J415" s="11">
         <v>46310.125</v>
@@ -39296,13 +39233,13 @@
         <v>34</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D416" s="0" t="s">
         <v>70</v>
       </c>
       <c r="E416" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F416" s="0" t="s">
         <v>166</v>
@@ -39385,7 +39322,7 @@
         <v>34</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>50</v>
@@ -39400,7 +39337,7 @@
         <v>333</v>
       </c>
       <c r="H417" s="0" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="J417" s="11">
         <v>46356.125</v>
@@ -39474,13 +39411,13 @@
         <v>34</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>137</v>
       </c>
       <c r="E418" s="0" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F418" s="0" t="s">
         <v>139</v>
@@ -39489,14 +39426,14 @@
         <v>139</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="J418" s="11"/>
       <c r="K418" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L418" s="0" t="s">
-        <v>924</v>
+        <v>380</v>
       </c>
       <c r="M418" s="0" t="s">
         <v>39</v>
@@ -39920,7 +39857,7 @@
         <v>127</v>
       </c>
       <c r="H423" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J423" s="11">
         <v>46380.125</v>
@@ -40421,10 +40358,10 @@
         <v>943</v>
       </c>
       <c r="D429" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E429" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F429" s="0" t="s">
         <v>333</v>
@@ -40590,7 +40527,7 @@
         <v>50</v>
       </c>
       <c r="E431" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F431" s="0" t="s">
         <v>165</v>
@@ -40762,13 +40699,13 @@
         <v>75</v>
       </c>
       <c r="E433" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F433" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G433" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H433" s="0" t="s">
         <v>952</v>
@@ -41467,12 +41404,14 @@
       <c r="H441" s="0" t="s">
         <v>952</v>
       </c>
-      <c r="J441" s="11"/>
+      <c r="J441" s="11">
+        <v>46310.125</v>
+      </c>
       <c r="K441" s="0" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="L441" s="0" t="s">
-        <v>682</v>
+        <v>41</v>
       </c>
       <c r="M441" s="0" t="s">
         <v>39</v>
@@ -41804,7 +41743,7 @@
         <v>973</v>
       </c>
       <c r="D445" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E445" s="0" t="s">
         <v>71</v>
@@ -42062,10 +42001,10 @@
         <v>977</v>
       </c>
       <c r="D448" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E448" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F448" s="0" t="s">
         <v>321</v>
@@ -42323,7 +42262,7 @@
         <v>980</v>
       </c>
       <c r="D451" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E451" s="0" t="s">
         <v>85</v>
@@ -42587,10 +42526,10 @@
         <v>985</v>
       </c>
       <c r="F454" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G454" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H454" s="0" t="s">
         <v>986</v>
@@ -42673,10 +42612,10 @@
         <v>173</v>
       </c>
       <c r="F455" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G455" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H455" s="0" t="s">
         <v>988</v>
@@ -42861,7 +42800,7 @@
         <v>211</v>
       </c>
       <c r="L457" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M457" s="0" t="s">
         <v>39</v>
@@ -42994,10 +42933,10 @@
     </row>
     <row r="459">
       <c r="A459" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B459" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C459" s="0" t="s">
         <v>996</v>
@@ -43054,7 +42993,7 @@
         <v>43</v>
       </c>
       <c r="AC459" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD459" s="11">
         <v>46206.62628596065</v>
@@ -43083,7 +43022,7 @@
         <v>815</v>
       </c>
       <c r="B460" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C460" s="0" t="s">
         <v>997</v>
@@ -43140,7 +43079,7 @@
         <v>44</v>
       </c>
       <c r="AC460" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD460" s="11">
         <v>46206.62972253472</v>
@@ -43332,7 +43271,7 @@
     </row>
     <row r="463">
       <c r="A463" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B463" s="0" t="s">
         <v>812</v>
@@ -43685,7 +43624,7 @@
         <v>127</v>
       </c>
       <c r="H467" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J467" s="11">
         <v>46310.125</v>
@@ -43851,10 +43790,10 @@
         <v>1014</v>
       </c>
       <c r="F469" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G469" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H469" s="0" t="s">
         <v>1015</v>
@@ -43931,7 +43870,7 @@
         <v>75</v>
       </c>
       <c r="E470" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F470" s="0" t="s">
         <v>326</v>
@@ -44690,7 +44629,7 @@
     </row>
     <row r="479">
       <c r="A479" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B479" s="0" t="s">
         <v>812</v>
@@ -44865,7 +44804,7 @@
         <v>50</v>
       </c>
       <c r="E481" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F481" s="0" t="s">
         <v>77</v>
@@ -44951,7 +44890,7 @@
         <v>246</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F482" s="0" t="s">
         <v>333</v>
@@ -45372,7 +45311,7 @@
         <v>838</v>
       </c>
       <c r="B487" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C487" s="0" t="s">
         <v>1047</v>
@@ -45387,7 +45326,7 @@
         <v>240</v>
       </c>
       <c r="G487" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J487" s="11">
         <v>46352.125</v>
@@ -45423,7 +45362,7 @@
         <v>44</v>
       </c>
       <c r="AC487" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AD487" s="11">
         <v>46229.825602557874</v>
@@ -45449,10 +45388,10 @@
     </row>
     <row r="488">
       <c r="A488" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B488" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C488" s="0" t="s">
         <v>1048</v>
@@ -45464,10 +45403,10 @@
         <v>1049</v>
       </c>
       <c r="F488" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G488" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J488" s="11">
         <v>46409.125</v>
@@ -45503,7 +45442,7 @@
         <v>43</v>
       </c>
       <c r="AC488" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AD488" s="11">
         <v>46229.83053608796</v>
@@ -45550,7 +45489,7 @@
         <v>198</v>
       </c>
       <c r="H489" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J489" s="11">
         <v>46310.125</v>
@@ -45971,7 +45910,7 @@
         <v>38</v>
       </c>
       <c r="H494" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J494" s="11">
         <v>46362.125</v>
@@ -46057,7 +45996,7 @@
         <v>38</v>
       </c>
       <c r="H495" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J495" s="11">
         <v>46362.125</v>
@@ -46463,7 +46402,7 @@
         <v>1068</v>
       </c>
       <c r="D500" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E500" s="0" t="s">
         <v>1069</v>
@@ -46543,7 +46482,7 @@
         <v>815</v>
       </c>
       <c r="B501" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C501" s="0" t="s">
         <v>1070</v>
@@ -46600,7 +46539,7 @@
         <v>44</v>
       </c>
       <c r="AC501" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AD501" s="11">
         <v>46275.669610046294</v>
@@ -46635,7 +46574,7 @@
         <v>1072</v>
       </c>
       <c r="D502" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E502" s="0" t="s">
         <v>1073</v>
@@ -46721,7 +46660,7 @@
         <v>1075</v>
       </c>
       <c r="D503" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E503" s="0" t="s">
         <v>1073</v>
@@ -46798,7 +46737,7 @@
     </row>
     <row r="504">
       <c r="A504" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B504" s="0" t="s">
         <v>223</v>
@@ -46807,16 +46746,16 @@
         <v>1076</v>
       </c>
       <c r="D504" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E504" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F504" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G504" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J504" s="11">
         <v>46419.125</v>
@@ -46912,7 +46851,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J239"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -47086,7 +47025,7 @@
         <v>1089</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>30</v>
@@ -47107,7 +47046,7 @@
         <v>1084</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7">
@@ -47118,7 +47057,7 @@
         <v>1089</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>29</v>
@@ -47139,7 +47078,7 @@
         <v>1084</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8">
@@ -47150,7 +47089,7 @@
         <v>1091</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>30</v>
@@ -47171,7 +47110,7 @@
         <v>1084</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9">
@@ -47182,7 +47121,7 @@
         <v>1091</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>29</v>
@@ -47203,7 +47142,7 @@
         <v>1084</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="10">
@@ -47278,7 +47217,7 @@
         <v>1097</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>30</v>
@@ -47299,7 +47238,7 @@
         <v>1084</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="13">
@@ -47310,7 +47249,7 @@
         <v>1097</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>29</v>
@@ -47331,7 +47270,7 @@
         <v>1084</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="14">
@@ -47432,7 +47371,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>1100</v>
@@ -47464,7 +47403,7 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>1100</v>
@@ -47523,7 +47462,7 @@
         <v>1088</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="20">
@@ -47555,12 +47494,12 @@
         <v>1088</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>1103</v>
@@ -47688,7 +47627,7 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>1108</v>
@@ -47752,7 +47691,7 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>1109</v>
@@ -47779,7 +47718,7 @@
         <v>1088</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="28">
@@ -47816,7 +47755,7 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>1111</v>
@@ -47848,7 +47787,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>1111</v>
@@ -47880,7 +47819,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>1112</v>
@@ -47907,12 +47846,12 @@
         <v>1088</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>1113</v>
@@ -47939,12 +47878,12 @@
         <v>1088</v>
       </c>
       <c r="J32" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>1114</v>
@@ -48008,7 +47947,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>1114</v>
@@ -48136,7 +48075,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>1119</v>
@@ -48168,7 +48107,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>1120</v>
@@ -48200,7 +48139,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>1108</v>
@@ -48552,7 +48491,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>1119</v>
@@ -48584,7 +48523,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B53" s="0" t="s">
         <v>1120</v>
@@ -48616,7 +48555,7 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>1126</v>
@@ -48648,7 +48587,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>1127</v>
@@ -48808,7 +48747,7 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B60" s="0" t="s">
         <v>1130</v>
@@ -48872,7 +48811,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>1127</v>
@@ -48904,7 +48843,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B63" s="0" t="s">
         <v>1126</v>
@@ -49064,7 +49003,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>1135</v>
@@ -49128,7 +49067,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>1135</v>
@@ -49192,7 +49131,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>1135</v>
@@ -49256,7 +49195,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>1135</v>
@@ -49352,7 +49291,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>1141</v>
@@ -49384,7 +49323,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>1142</v>
@@ -49416,7 +49355,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>1141</v>
@@ -49448,7 +49387,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>1143</v>
@@ -49480,7 +49419,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>1143</v>
@@ -49576,7 +49515,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>1142</v>
@@ -49608,7 +49547,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>1145</v>
@@ -49640,7 +49579,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>1143</v>
@@ -49672,7 +49611,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>1143</v>
@@ -50056,7 +49995,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>1152</v>
@@ -50152,7 +50091,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B102" s="0" t="s">
         <v>1153</v>
@@ -50184,7 +50123,7 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B103" s="0" t="s">
         <v>1153</v>
@@ -50248,7 +50187,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B105" s="0" t="s">
         <v>1153</v>
@@ -51048,7 +50987,7 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B130" s="0" t="s">
         <v>1121</v>
@@ -51176,7 +51115,7 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B134" s="0" t="s">
         <v>1124</v>
@@ -51208,7 +51147,7 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B135" s="0" t="s">
         <v>1121</v>
@@ -51240,7 +51179,7 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B136" s="0" t="s">
         <v>1144</v>
@@ -51528,7 +51467,7 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B145" s="0" t="s">
         <v>1133</v>
@@ -51560,7 +51499,7 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B146" s="0" t="s">
         <v>1133</v>
@@ -51720,7 +51659,7 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B151" s="0" t="s">
         <v>1120</v>
@@ -51752,7 +51691,7 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B152" s="0" t="s">
         <v>1119</v>
@@ -51784,7 +51723,7 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B153" s="0" t="s">
         <v>1165</v>
@@ -51816,7 +51755,7 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B154" s="0" t="s">
         <v>1165</v>
@@ -51848,7 +51787,7 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B155" s="0" t="s">
         <v>1166</v>
@@ -51944,7 +51883,7 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B158" s="0" t="s">
         <v>1165</v>
@@ -51976,7 +51915,7 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B159" s="0" t="s">
         <v>1165</v>
@@ -52104,7 +52043,7 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B163" s="0" t="s">
         <v>1133</v>
@@ -52136,7 +52075,7 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B164" s="0" t="s">
         <v>1133</v>
@@ -52168,7 +52107,7 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B165" s="0" t="s">
         <v>1133</v>
@@ -52424,7 +52363,7 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B173" s="0" t="s">
         <v>1119</v>
@@ -52456,7 +52395,7 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B174" s="0" t="s">
         <v>1120</v>
@@ -52744,7 +52683,7 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B183" s="0" t="s">
         <v>1172</v>
@@ -52868,1702 +52807,6 @@
       </c>
       <c r="J186" s="0" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="0" t="s">
-        <v>788</v>
-      </c>
-      <c r="B187" s="0" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C187" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D187" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E187" s="11">
-        <v>46240</v>
-      </c>
-      <c r="F187" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G187" s="11">
-        <v>46420.125</v>
-      </c>
-      <c r="H187" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="I187" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J187" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="0" t="s">
-        <v>787</v>
-      </c>
-      <c r="B188" s="0" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C188" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D188" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E188" s="11">
-        <v>46240</v>
-      </c>
-      <c r="F188" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G188" s="11">
-        <v>46420.125</v>
-      </c>
-      <c r="H188" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="I188" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J188" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="0" t="s">
-        <v>733</v>
-      </c>
-      <c r="B189" s="0" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C189" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D189" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E189" s="11">
-        <v>46240</v>
-      </c>
-      <c r="F189" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G189" s="11">
-        <v>46420.125</v>
-      </c>
-      <c r="H189" s="0" t="s">
-        <v>1104</v>
-      </c>
-      <c r="I189" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J189" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="0" t="s">
-        <v>743</v>
-      </c>
-      <c r="B190" s="0" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C190" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D190" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E190" s="11">
-        <v>46240</v>
-      </c>
-      <c r="F190" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G190" s="11">
-        <v>46420.125</v>
-      </c>
-      <c r="H190" s="0" t="s">
-        <v>1104</v>
-      </c>
-      <c r="I190" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J190" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="B191" s="0" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C191" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D191" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E191" s="11">
-        <v>46240</v>
-      </c>
-      <c r="F191" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G191" s="11">
-        <v>46420.125</v>
-      </c>
-      <c r="H191" s="0" t="s">
-        <v>1104</v>
-      </c>
-      <c r="I191" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J191" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="0" t="s">
-        <v>742</v>
-      </c>
-      <c r="B192" s="0" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C192" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D192" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E192" s="11">
-        <v>46240</v>
-      </c>
-      <c r="F192" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G192" s="11">
-        <v>46420.125</v>
-      </c>
-      <c r="H192" s="0" t="s">
-        <v>1104</v>
-      </c>
-      <c r="I192" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J192" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B193" s="0" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C193" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D193" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E193" s="11">
-        <v>46240</v>
-      </c>
-      <c r="F193" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G193" s="11">
-        <v>46420.125</v>
-      </c>
-      <c r="H193" s="0" t="s">
-        <v>1117</v>
-      </c>
-      <c r="I193" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J193" s="0" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="0" t="s">
-        <v>788</v>
-      </c>
-      <c r="B194" s="0" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C194" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D194" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E194" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F194" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G194" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H194" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I194" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J194" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="0" t="s">
-        <v>787</v>
-      </c>
-      <c r="B195" s="0" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C195" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D195" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E195" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F195" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G195" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H195" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I195" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J195" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="0" t="s">
-        <v>559</v>
-      </c>
-      <c r="B196" s="0" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C196" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D196" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E196" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F196" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G196" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H196" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I196" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J196" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="0" t="s">
-        <v>564</v>
-      </c>
-      <c r="B197" s="0" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C197" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D197" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E197" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F197" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G197" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H197" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I197" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J197" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="0" t="s">
-        <v>743</v>
-      </c>
-      <c r="B198" s="0" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C198" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D198" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E198" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F198" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G198" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H198" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I198" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J198" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="0" t="s">
-        <v>733</v>
-      </c>
-      <c r="B199" s="0" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C199" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D199" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E199" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F199" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G199" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H199" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I199" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J199" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="B200" s="0" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C200" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D200" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E200" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F200" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G200" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H200" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I200" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J200" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="0" t="s">
-        <v>742</v>
-      </c>
-      <c r="B201" s="0" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C201" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D201" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E201" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F201" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G201" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H201" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I201" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J201" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="B202" s="0" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C202" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D202" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E202" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F202" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G202" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H202" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="I202" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J202" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="B203" s="0" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C203" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D203" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E203" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F203" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G203" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H203" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="I203" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J203" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="0" t="s">
-        <v>594</v>
-      </c>
-      <c r="B204" s="0" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C204" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D204" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E204" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F204" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G204" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H204" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I204" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J204" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="0" t="s">
-        <v>594</v>
-      </c>
-      <c r="B205" s="0" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C205" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D205" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E205" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F205" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G205" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H205" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I205" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J205" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="0" t="s">
-        <v>530</v>
-      </c>
-      <c r="B206" s="0" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C206" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D206" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E206" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F206" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G206" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H206" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="I206" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J206" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="0" t="s">
-        <v>530</v>
-      </c>
-      <c r="B207" s="0" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C207" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D207" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E207" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F207" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G207" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H207" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I207" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J207" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="0" t="s">
-        <v>528</v>
-      </c>
-      <c r="B208" s="0" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C208" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D208" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E208" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F208" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G208" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H208" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I208" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J208" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="0" t="s">
-        <v>370</v>
-      </c>
-      <c r="B209" s="0" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C209" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D209" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E209" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F209" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G209" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H209" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="I209" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J209" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="B210" s="0" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C210" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D210" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E210" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F210" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G210" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H210" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I210" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J210" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="B211" s="0" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C211" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D211" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E211" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F211" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G211" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H211" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I211" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J211" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="B212" s="0" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C212" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D212" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E212" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F212" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G212" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H212" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I212" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J212" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="0" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B213" s="0" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C213" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D213" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E213" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F213" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G213" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H213" s="0" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I213" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J213" s="0" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="0" t="s">
-        <v>233</v>
-      </c>
-      <c r="B214" s="0" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C214" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D214" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E214" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F214" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G214" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H214" s="0" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I214" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J214" s="0" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="0" t="s">
-        <v>566</v>
-      </c>
-      <c r="B215" s="0" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C215" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D215" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E215" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F215" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G215" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H215" s="0" t="s">
-        <v>1104</v>
-      </c>
-      <c r="I215" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J215" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="B216" s="0" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C216" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D216" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E216" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F216" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G216" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H216" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I216" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J216" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="0" t="s">
-        <v>566</v>
-      </c>
-      <c r="B217" s="0" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C217" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D217" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E217" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F217" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G217" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H217" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I217" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J217" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="0" t="s">
-        <v>370</v>
-      </c>
-      <c r="B218" s="0" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C218" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D218" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E218" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F218" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G218" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H218" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I218" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J218" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="0" t="s">
-        <v>340</v>
-      </c>
-      <c r="B219" s="0" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C219" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D219" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E219" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F219" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G219" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H219" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I219" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J219" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="0" t="s">
-        <v>233</v>
-      </c>
-      <c r="B220" s="0" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C220" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D220" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E220" s="11">
-        <v>46239</v>
-      </c>
-      <c r="F220" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G220" s="11">
-        <v>46419.125</v>
-      </c>
-      <c r="H220" s="0" t="s">
-        <v>1104</v>
-      </c>
-      <c r="I220" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J220" s="0" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="0" t="s">
-        <v>968</v>
-      </c>
-      <c r="B221" s="0" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C221" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D221" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E221" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F221" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G221" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H221" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="I221" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J221" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="0" t="s">
-        <v>227</v>
-      </c>
-      <c r="B222" s="0" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C222" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D222" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E222" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F222" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G222" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H222" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I222" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J222" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="0" t="s">
-        <v>968</v>
-      </c>
-      <c r="B223" s="0" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C223" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D223" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E223" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F223" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G223" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H223" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I223" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J223" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="B224" s="0" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C224" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D224" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E224" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F224" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G224" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H224" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="I224" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J224" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="B225" s="0" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C225" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D225" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E225" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F225" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G225" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H225" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I225" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J225" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="0" t="s">
-        <v>778</v>
-      </c>
-      <c r="B226" s="0" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C226" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D226" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E226" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F226" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G226" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H226" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="I226" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J226" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="0" t="s">
-        <v>779</v>
-      </c>
-      <c r="B227" s="0" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C227" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D227" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E227" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F227" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G227" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H227" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="I227" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J227" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="0" t="s">
-        <v>779</v>
-      </c>
-      <c r="B228" s="0" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C228" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D228" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E228" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F228" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G228" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H228" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I228" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J228" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="0" t="s">
-        <v>778</v>
-      </c>
-      <c r="B229" s="0" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C229" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D229" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E229" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F229" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G229" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H229" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I229" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J229" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="0" t="s">
-        <v>601</v>
-      </c>
-      <c r="B230" s="0" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C230" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D230" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E230" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F230" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G230" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H230" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I230" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J230" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="B231" s="0" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C231" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D231" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E231" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F231" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G231" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H231" s="0" t="s">
-        <v>1122</v>
-      </c>
-      <c r="I231" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J231" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="B232" s="0" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C232" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D232" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E232" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F232" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G232" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H232" s="0" t="s">
-        <v>1087</v>
-      </c>
-      <c r="I232" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J232" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="0" t="s">
-        <v>317</v>
-      </c>
-      <c r="B233" s="0" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C233" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D233" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E233" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F233" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G233" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H233" s="0" t="s">
-        <v>1087</v>
-      </c>
-      <c r="I233" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J233" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="0" t="s">
-        <v>582</v>
-      </c>
-      <c r="B234" s="0" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C234" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D234" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E234" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F234" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G234" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H234" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I234" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J234" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="B235" s="0" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C235" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D235" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E235" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F235" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G235" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H235" s="0" t="s">
-        <v>1191</v>
-      </c>
-      <c r="I235" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J235" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="B236" s="0" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C236" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D236" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E236" s="11">
-        <v>46238</v>
-      </c>
-      <c r="F236" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G236" s="11">
-        <v>46418.125</v>
-      </c>
-      <c r="H236" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="I236" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J236" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="0" t="s">
-        <v>489</v>
-      </c>
-      <c r="B237" s="0" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C237" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D237" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E237" s="11">
-        <v>46237</v>
-      </c>
-      <c r="F237" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G237" s="11">
-        <v>46417.125</v>
-      </c>
-      <c r="H237" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="I237" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J237" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="0" t="s">
-        <v>489</v>
-      </c>
-      <c r="B238" s="0" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C238" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D238" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E238" s="11">
-        <v>46237</v>
-      </c>
-      <c r="F238" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G238" s="11">
-        <v>46417.125</v>
-      </c>
-      <c r="H238" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I238" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J238" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="0" t="s">
-        <v>492</v>
-      </c>
-      <c r="B239" s="0" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C239" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="D239" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E239" s="11">
-        <v>46237</v>
-      </c>
-      <c r="F239" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G239" s="11">
-        <v>46417.125</v>
-      </c>
-      <c r="H239" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I239" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J239" s="0" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="1164">
   <si>
     <t>Geração:</t>
   </si>
@@ -2217,12 +2217,6 @@
     <t>NWP8C88</t>
   </si>
   <si>
-    <t>Documento DETRAN aguardando validação</t>
-  </si>
-  <si>
-    <t>AV</t>
-  </si>
-  <si>
     <t>NSZ4798</t>
   </si>
   <si>
@@ -2268,9 +2262,6 @@
     <t>047840574</t>
   </si>
   <si>
-    <t>Documento Arrendamento aguardando validação</t>
-  </si>
-  <si>
     <t>NBG3C42</t>
   </si>
   <si>
@@ -3240,6 +3231,15 @@
     <t>GNB6192</t>
   </si>
   <si>
+    <t>RXU3A18</t>
+  </si>
+  <si>
+    <t>M.BENZ/ATEGO 2426</t>
+  </si>
+  <si>
+    <t>Inspeções Checklist de Qualidade, Checklist de Segurança SESMT pendentes</t>
+  </si>
+  <si>
     <t>Marca / Modelo</t>
   </si>
   <si>
@@ -3505,21 +3505,6 @@
   </si>
   <si>
     <t>SCANIA / R124 LA6X2NA 400</t>
-  </si>
-  <si>
-    <t>SR / RANDON SR CA</t>
-  </si>
-  <si>
-    <t>VOLVO / FH 12 380 4X2T</t>
-  </si>
-  <si>
-    <t>SCANIA / G 420 A4X2</t>
-  </si>
-  <si>
-    <t>SCANIA/T113 H 4X2 360 / SCANIA/T113 H 4X2 360</t>
-  </si>
-  <si>
-    <t>VOLVO / NL12 360 4X2</t>
   </si>
 </sst>
 </file>
@@ -3700,7 +3685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ502"/>
+  <dimension ref="A1:AJ503"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -3711,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46301.35283488426</v>
+        <v>46301.619618171295</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -6665,10 +6650,10 @@
         <v>46310.125</v>
       </c>
       <c r="K35" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M35" s="0" t="s">
         <v>39</v>
@@ -7875,10 +7860,10 @@
         <v>46310.125</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M49" s="0" t="s">
         <v>39</v>
@@ -10115,7 +10100,7 @@
         <v>268</v>
       </c>
       <c r="J75" s="11">
-        <v>46358.125</v>
+        <v>46417.125</v>
       </c>
       <c r="K75" s="0" t="s">
         <v>55</v>
@@ -10136,7 +10121,7 @@
         <v>42</v>
       </c>
       <c r="R75" s="11">
-        <v>46358.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T75" s="0" t="s">
         <v>43</v>
@@ -10287,7 +10272,7 @@
         <v>268</v>
       </c>
       <c r="J77" s="11">
-        <v>46358.125</v>
+        <v>46417.125</v>
       </c>
       <c r="K77" s="0" t="s">
         <v>55</v>
@@ -10308,7 +10293,7 @@
         <v>42</v>
       </c>
       <c r="R77" s="11">
-        <v>46358.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T77" s="0" t="s">
         <v>43</v>
@@ -12704,7 +12689,7 @@
         <v>39</v>
       </c>
       <c r="J105" s="11">
-        <v>46310.125</v>
+        <v>46415.125</v>
       </c>
       <c r="K105" s="0" t="s">
         <v>55</v>
@@ -12725,7 +12710,7 @@
         <v>42</v>
       </c>
       <c r="R105" s="11">
-        <v>46310.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T105" s="0" t="s">
         <v>43</v>
@@ -12897,7 +12882,7 @@
         <v>42</v>
       </c>
       <c r="R107" s="11">
-        <v>46365.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T107" s="0" t="s">
         <v>43</v>
@@ -12962,7 +12947,7 @@
         <v>39</v>
       </c>
       <c r="J108" s="11">
-        <v>46358.125</v>
+        <v>46417.125</v>
       </c>
       <c r="K108" s="0" t="s">
         <v>55</v>
@@ -12983,7 +12968,7 @@
         <v>42</v>
       </c>
       <c r="R108" s="11">
-        <v>46358.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T108" s="0" t="s">
         <v>43</v>
@@ -17184,7 +17169,7 @@
         <v>39</v>
       </c>
       <c r="J157" s="11">
-        <v>46304.125</v>
+        <v>46424.125</v>
       </c>
       <c r="K157" s="0" t="s">
         <v>55</v>
@@ -17205,7 +17190,7 @@
         <v>42</v>
       </c>
       <c r="R157" s="11">
-        <v>46304.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T157" s="0" t="s">
         <v>43</v>
@@ -17359,10 +17344,10 @@
         <v>46310.125</v>
       </c>
       <c r="K159" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L159" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M159" s="0" t="s">
         <v>39</v>
@@ -19012,7 +18997,7 @@
         <v>42</v>
       </c>
       <c r="R178" s="11">
-        <v>46400.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T178" s="0" t="s">
         <v>43</v>
@@ -19163,7 +19148,7 @@
         <v>39</v>
       </c>
       <c r="J180" s="11">
-        <v>46311.125</v>
+        <v>46396.125</v>
       </c>
       <c r="K180" s="0" t="s">
         <v>55</v>
@@ -19184,7 +19169,7 @@
         <v>42</v>
       </c>
       <c r="R180" s="11">
-        <v>46311.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T180" s="0" t="s">
         <v>44</v>
@@ -19249,7 +19234,7 @@
         <v>39</v>
       </c>
       <c r="J181" s="11">
-        <v>46340.125</v>
+        <v>46405.125</v>
       </c>
       <c r="K181" s="0" t="s">
         <v>55</v>
@@ -19270,7 +19255,7 @@
         <v>42</v>
       </c>
       <c r="R181" s="11">
-        <v>46340.125</v>
+        <v>46492.125</v>
       </c>
       <c r="T181" s="0" t="s">
         <v>43</v>
@@ -19507,7 +19492,7 @@
         <v>39</v>
       </c>
       <c r="J184" s="11">
-        <v>46311.125</v>
+        <v>46393.125</v>
       </c>
       <c r="K184" s="0" t="s">
         <v>55</v>
@@ -19522,13 +19507,13 @@
         <v>42</v>
       </c>
       <c r="O184" s="11">
-        <v>46676.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q184" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R184" s="11">
-        <v>46311.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T184" s="0" t="s">
         <v>42</v>
@@ -19596,7 +19581,7 @@
         <v>39</v>
       </c>
       <c r="J185" s="11">
-        <v>46340.125</v>
+        <v>46399.125</v>
       </c>
       <c r="K185" s="0" t="s">
         <v>55</v>
@@ -19617,7 +19602,7 @@
         <v>42</v>
       </c>
       <c r="R185" s="11">
-        <v>46340.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T185" s="0" t="s">
         <v>43</v>
@@ -19682,7 +19667,7 @@
         <v>39</v>
       </c>
       <c r="J186" s="11">
-        <v>46340.125</v>
+        <v>46399.125</v>
       </c>
       <c r="K186" s="0" t="s">
         <v>55</v>
@@ -19703,7 +19688,7 @@
         <v>42</v>
       </c>
       <c r="R186" s="11">
-        <v>46340.125</v>
+        <v>46423.125</v>
       </c>
       <c r="T186" s="0" t="s">
         <v>43</v>
@@ -23834,7 +23819,7 @@
         <v>42</v>
       </c>
       <c r="R234" s="11">
-        <v>46365.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T234" s="0" t="s">
         <v>43</v>
@@ -23920,7 +23905,7 @@
         <v>42</v>
       </c>
       <c r="R235" s="11">
-        <v>46365.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T235" s="0" t="s">
         <v>43</v>
@@ -24937,7 +24922,7 @@
         <v>42</v>
       </c>
       <c r="R247" s="11">
-        <v>46428.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T247" s="0" t="s">
         <v>43</v>
@@ -26594,7 +26579,7 @@
         <v>39</v>
       </c>
       <c r="J267" s="11">
-        <v>46311.125</v>
+        <v>46372.125</v>
       </c>
       <c r="K267" s="0" t="s">
         <v>55</v>
@@ -26615,7 +26600,7 @@
         <v>42</v>
       </c>
       <c r="R267" s="11">
-        <v>46311.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T267" s="0" t="s">
         <v>43</v>
@@ -27670,7 +27655,7 @@
         <v>568</v>
       </c>
       <c r="J280" s="11">
-        <v>46365.125</v>
+        <v>46420.125</v>
       </c>
       <c r="K280" s="0" t="s">
         <v>55</v>
@@ -27691,7 +27676,7 @@
         <v>42</v>
       </c>
       <c r="R280" s="11">
-        <v>46365.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T280" s="0" t="s">
         <v>43</v>
@@ -27756,7 +27741,7 @@
         <v>568</v>
       </c>
       <c r="J281" s="11">
-        <v>46304.125</v>
+        <v>46421.125</v>
       </c>
       <c r="K281" s="0" t="s">
         <v>55</v>
@@ -27777,7 +27762,7 @@
         <v>42</v>
       </c>
       <c r="R281" s="11">
-        <v>46304.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T281" s="0" t="s">
         <v>43</v>
@@ -27842,7 +27827,7 @@
         <v>568</v>
       </c>
       <c r="J282" s="11">
-        <v>46304.125</v>
+        <v>46421.125</v>
       </c>
       <c r="K282" s="0" t="s">
         <v>55</v>
@@ -27863,7 +27848,7 @@
         <v>42</v>
       </c>
       <c r="R282" s="11">
-        <v>46304.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T282" s="0" t="s">
         <v>43</v>
@@ -29731,7 +29716,7 @@
         <v>428</v>
       </c>
       <c r="J304" s="11">
-        <v>46310.125</v>
+        <v>46381.125</v>
       </c>
       <c r="K304" s="0" t="s">
         <v>55</v>
@@ -29746,7 +29731,7 @@
         <v>42</v>
       </c>
       <c r="O304" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q304" s="0" t="s">
         <v>42</v>
@@ -30335,12 +30320,14 @@
       <c r="H311" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="J311" s="11"/>
+      <c r="J311" s="11">
+        <v>46407.125</v>
+      </c>
       <c r="K311" s="0" t="s">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="L311" s="0" t="s">
-        <v>734</v>
+        <v>39</v>
       </c>
       <c r="M311" s="0" t="s">
         <v>39</v>
@@ -30352,10 +30339,10 @@
         <v>46655.125</v>
       </c>
       <c r="Q311" s="0" t="s">
-        <v>735</v>
+        <v>42</v>
       </c>
       <c r="R311" s="11">
-        <v>46675.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T311" s="0" t="s">
         <v>43</v>
@@ -30402,13 +30389,13 @@
         <v>60</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D312" s="0" t="s">
         <v>723</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="F312" s="0" t="s">
         <v>73</v>
@@ -30488,7 +30475,7 @@
         <v>60</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D313" s="0" t="s">
         <v>256</v>
@@ -30574,7 +30561,7 @@
         <v>60</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D314" s="0" t="s">
         <v>256</v>
@@ -30660,7 +30647,7 @@
         <v>60</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D315" s="0" t="s">
         <v>406</v>
@@ -30746,7 +30733,7 @@
         <v>60</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D316" s="0" t="s">
         <v>256</v>
@@ -30832,7 +30819,7 @@
         <v>60</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D317" s="0" t="s">
         <v>731</v>
@@ -30921,7 +30908,7 @@
         <v>60</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D318" s="0" t="s">
         <v>50</v>
@@ -30936,7 +30923,7 @@
         <v>166</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="J318" s="11">
         <v>46310.125</v>
@@ -31007,7 +30994,7 @@
         <v>60</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D319" s="0" t="s">
         <v>50</v>
@@ -31093,10 +31080,10 @@
         <v>60</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D320" s="0" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E320" s="0" t="s">
         <v>225</v>
@@ -31179,7 +31166,7 @@
         <v>60</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D321" s="0" t="s">
         <v>246</v>
@@ -31265,7 +31252,7 @@
         <v>48</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D322" s="0" t="s">
         <v>474</v>
@@ -31280,14 +31267,16 @@
         <v>92</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>750</v>
-      </c>
-      <c r="J322" s="11"/>
+        <v>748</v>
+      </c>
+      <c r="J322" s="11">
+        <v>46370.125</v>
+      </c>
       <c r="K322" s="0" t="s">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="L322" s="0" t="s">
-        <v>751</v>
+        <v>39</v>
       </c>
       <c r="M322" s="0" t="s">
         <v>39</v>
@@ -31296,7 +31285,7 @@
         <v>42</v>
       </c>
       <c r="O322" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q322" s="0" t="s">
         <v>42</v>
@@ -31305,10 +31294,7 @@
         <v>46370.125</v>
       </c>
       <c r="T322" s="0" t="s">
-        <v>735</v>
-      </c>
-      <c r="U322" s="11">
-        <v>46675.125</v>
+        <v>44</v>
       </c>
       <c r="W322" s="0" t="s">
         <v>42</v>
@@ -31352,7 +31338,7 @@
         <v>34</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D323" s="0" t="s">
         <v>159</v>
@@ -31367,7 +31353,7 @@
         <v>240</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="J323" s="11">
         <v>46367.125</v>
@@ -31435,7 +31421,7 @@
         <v>48</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D324" s="0" t="s">
         <v>305</v>
@@ -31450,10 +31436,10 @@
         <v>64</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="J324" s="11">
-        <v>46358.125</v>
+        <v>46415.125</v>
       </c>
       <c r="K324" s="0" t="s">
         <v>55</v>
@@ -31474,7 +31460,7 @@
         <v>42</v>
       </c>
       <c r="R324" s="11">
-        <v>46358.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T324" s="0" t="s">
         <v>43</v>
@@ -31521,7 +31507,7 @@
         <v>48</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D325" s="0" t="s">
         <v>307</v>
@@ -31536,10 +31522,10 @@
         <v>64</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="J325" s="11">
-        <v>46358.125</v>
+        <v>46415.125</v>
       </c>
       <c r="K325" s="0" t="s">
         <v>55</v>
@@ -31560,7 +31546,7 @@
         <v>42</v>
       </c>
       <c r="R325" s="11">
-        <v>46358.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T325" s="0" t="s">
         <v>43</v>
@@ -31607,13 +31593,13 @@
         <v>48</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D326" s="0" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E326" s="0" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="F326" s="0" t="s">
         <v>166</v>
@@ -31622,7 +31608,7 @@
         <v>166</v>
       </c>
       <c r="H326" s="0" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="J326" s="11">
         <v>46358.125</v>
@@ -31693,13 +31679,13 @@
         <v>48</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D327" s="0" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="E327" s="0" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="F327" s="0" t="s">
         <v>64</v>
@@ -31708,7 +31694,7 @@
         <v>64</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="J327" s="11">
         <v>46358.125</v>
@@ -31779,7 +31765,7 @@
         <v>48</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D328" s="0" t="s">
         <v>406</v>
@@ -31797,7 +31783,7 @@
         <v>378</v>
       </c>
       <c r="J328" s="11">
-        <v>46349.125</v>
+        <v>46426.125</v>
       </c>
       <c r="K328" s="0" t="s">
         <v>55</v>
@@ -31818,7 +31804,7 @@
         <v>42</v>
       </c>
       <c r="R328" s="11">
-        <v>46349.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T328" s="0" t="s">
         <v>43</v>
@@ -31865,7 +31851,7 @@
         <v>48</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D329" s="0" t="s">
         <v>406</v>
@@ -31883,7 +31869,7 @@
         <v>378</v>
       </c>
       <c r="J329" s="11">
-        <v>46310.125</v>
+        <v>46423.125</v>
       </c>
       <c r="K329" s="0" t="s">
         <v>55</v>
@@ -31898,13 +31884,13 @@
         <v>42</v>
       </c>
       <c r="O329" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q329" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R329" s="11">
-        <v>46349.125</v>
+        <v>46423.125</v>
       </c>
       <c r="T329" s="0" t="s">
         <v>43</v>
@@ -31951,7 +31937,7 @@
         <v>60</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D330" s="0" t="s">
         <v>50</v>
@@ -31966,7 +31952,7 @@
         <v>73</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="J330" s="11">
         <v>46310.125</v>
@@ -32037,7 +32023,7 @@
         <v>60</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D331" s="0" t="s">
         <v>36</v>
@@ -32052,7 +32038,7 @@
         <v>320</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="J331" s="11">
         <v>46373.125</v>
@@ -32123,7 +32109,7 @@
         <v>60</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D332" s="0" t="s">
         <v>36</v>
@@ -32138,7 +32124,7 @@
         <v>320</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="J332" s="11">
         <v>46373.125</v>
@@ -32209,7 +32195,7 @@
         <v>60</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D333" s="0" t="s">
         <v>246</v>
@@ -32295,7 +32281,7 @@
         <v>60</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D334" s="0" t="s">
         <v>246</v>
@@ -32381,7 +32367,7 @@
         <v>60</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D335" s="0" t="s">
         <v>246</v>
@@ -32467,7 +32453,7 @@
         <v>60</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="D336" s="0" t="s">
         <v>246</v>
@@ -32553,13 +32539,13 @@
         <v>48</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E337" s="0" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F337" s="0" t="s">
         <v>165</v>
@@ -32568,10 +32554,10 @@
         <v>165</v>
       </c>
       <c r="H337" s="0" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="J337" s="11">
-        <v>46358.125</v>
+        <v>46421.125</v>
       </c>
       <c r="K337" s="0" t="s">
         <v>55</v>
@@ -32592,7 +32578,7 @@
         <v>42</v>
       </c>
       <c r="R337" s="11">
-        <v>46358.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T337" s="0" t="s">
         <v>43</v>
@@ -32639,13 +32625,13 @@
         <v>48</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E338" s="0" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F338" s="0" t="s">
         <v>165</v>
@@ -32654,10 +32640,10 @@
         <v>165</v>
       </c>
       <c r="H338" s="0" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="J338" s="11">
-        <v>46358.125</v>
+        <v>46421.125</v>
       </c>
       <c r="K338" s="0" t="s">
         <v>55</v>
@@ -32678,7 +32664,7 @@
         <v>42</v>
       </c>
       <c r="R338" s="11">
-        <v>46358.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T338" s="0" t="s">
         <v>43</v>
@@ -32725,7 +32711,7 @@
         <v>60</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D339" s="0" t="s">
         <v>246</v>
@@ -32811,7 +32797,7 @@
         <v>60</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="D340" s="0" t="s">
         <v>246</v>
@@ -32897,7 +32883,7 @@
         <v>60</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D341" s="0" t="s">
         <v>256</v>
@@ -32912,16 +32898,16 @@
         <v>92</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="J341" s="11">
         <v>46310.125</v>
       </c>
       <c r="K341" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L341" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M341" s="0" t="s">
         <v>39</v>
@@ -32983,7 +32969,7 @@
         <v>60</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D342" s="0" t="s">
         <v>256</v>
@@ -32998,16 +32984,16 @@
         <v>92</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="J342" s="11">
         <v>46310.125</v>
       </c>
       <c r="K342" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L342" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M342" s="0" t="s">
         <v>39</v>
@@ -33069,7 +33055,7 @@
         <v>223</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D343" s="0" t="s">
         <v>522</v>
@@ -33149,13 +33135,13 @@
         <v>223</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D344" s="0" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="E344" s="0" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="F344" s="0" t="s">
         <v>146</v>
@@ -33229,7 +33215,7 @@
         <v>60</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D345" s="0" t="s">
         <v>71</v>
@@ -33318,7 +33304,7 @@
         <v>60</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D346" s="0" t="s">
         <v>406</v>
@@ -33404,7 +33390,7 @@
         <v>34</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D347" s="0" t="s">
         <v>76</v>
@@ -33419,7 +33405,7 @@
         <v>134</v>
       </c>
       <c r="H347" s="0" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="J347" s="11">
         <v>46366.125</v>
@@ -33490,7 +33476,7 @@
         <v>34</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D348" s="0" t="s">
         <v>95</v>
@@ -33505,7 +33491,7 @@
         <v>73</v>
       </c>
       <c r="H348" s="0" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="J348" s="11"/>
       <c r="K348" s="0" t="s">
@@ -33574,7 +33560,7 @@
         <v>34</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D349" s="0" t="s">
         <v>95</v>
@@ -33589,7 +33575,7 @@
         <v>73</v>
       </c>
       <c r="H349" s="0" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="J349" s="11">
         <v>46303.125</v>
@@ -33660,7 +33646,7 @@
         <v>48</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D350" s="0" t="s">
         <v>298</v>
@@ -33746,13 +33732,13 @@
         <v>48</v>
       </c>
       <c r="C351" s="0" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D351" s="0" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E351" s="0" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="F351" s="0" t="s">
         <v>146</v>
@@ -33829,7 +33815,7 @@
         <v>48</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D352" s="0" t="s">
         <v>298</v>
@@ -33915,7 +33901,7 @@
         <v>48</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D353" s="0" t="s">
         <v>298</v>
@@ -34001,7 +33987,7 @@
         <v>34</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D354" s="0" t="s">
         <v>159</v>
@@ -34016,7 +34002,7 @@
         <v>520</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="J354" s="11">
         <v>46302.125</v>
@@ -34087,7 +34073,7 @@
         <v>34</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D355" s="0" t="s">
         <v>137</v>
@@ -34102,7 +34088,7 @@
         <v>435</v>
       </c>
       <c r="H355" s="0" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="J355" s="11">
         <v>46311.125</v>
@@ -34173,7 +34159,7 @@
         <v>60</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D356" s="0" t="s">
         <v>159</v>
@@ -34188,7 +34174,7 @@
         <v>53</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="J356" s="11">
         <v>46373.125</v>
@@ -34259,7 +34245,7 @@
         <v>60</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D357" s="0" t="s">
         <v>246</v>
@@ -34274,7 +34260,7 @@
         <v>320</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="J357" s="11">
         <v>46373.125</v>
@@ -34345,13 +34331,13 @@
         <v>223</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="D358" s="0" t="s">
         <v>522</v>
       </c>
       <c r="E358" s="0" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="F358" s="0" t="s">
         <v>498</v>
@@ -34425,7 +34411,7 @@
         <v>60</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D359" s="0" t="s">
         <v>159</v>
@@ -34440,7 +34426,7 @@
         <v>53</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="J359" s="11">
         <v>46373.125</v>
@@ -34511,13 +34497,13 @@
         <v>60</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="D360" s="0" t="s">
         <v>731</v>
       </c>
       <c r="E360" s="0" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="F360" s="0" t="s">
         <v>59</v>
@@ -34526,7 +34512,7 @@
         <v>131</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="J360" s="11">
         <v>46373.125</v>
@@ -34600,7 +34586,7 @@
         <v>60</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D361" s="0" t="s">
         <v>50</v>
@@ -34615,7 +34601,7 @@
         <v>127</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="J361" s="11">
         <v>46310.125</v>
@@ -34683,16 +34669,16 @@
         <v>659</v>
       </c>
       <c r="B362" s="0" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D362" s="0" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="E362" s="0" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F362" s="0" t="s">
         <v>288</v>
@@ -34731,7 +34717,7 @@
         <v>44</v>
       </c>
       <c r="AC362" s="0" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="AD362" s="11">
         <v>45847.61793511574</v>
@@ -34757,19 +34743,19 @@
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B363" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D363" s="0" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E363" s="0" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="F363" s="0" t="s">
         <v>206</v>
@@ -34840,19 +34826,19 @@
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B364" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D364" s="0" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E364" s="0" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="F364" s="0" t="s">
         <v>205</v>
@@ -34923,19 +34909,19 @@
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B365" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="D365" s="0" t="s">
         <v>406</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F365" s="0" t="s">
         <v>131</v>
@@ -35006,19 +34992,19 @@
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B366" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D366" s="0" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="F366" s="0" t="s">
         <v>321</v>
@@ -35089,19 +35075,19 @@
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B367" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D367" s="0" t="s">
         <v>246</v>
       </c>
       <c r="E367" s="0" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F367" s="0" t="s">
         <v>205</v>
@@ -35178,13 +35164,13 @@
         <v>622</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D368" s="0" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="E368" s="0" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="F368" s="0" t="s">
         <v>165</v>
@@ -35258,7 +35244,7 @@
         <v>34</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D369" s="0" t="s">
         <v>62</v>
@@ -35344,7 +35330,7 @@
         <v>48</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D370" s="0" t="s">
         <v>225</v>
@@ -35380,7 +35366,7 @@
         <v>42</v>
       </c>
       <c r="R370" s="11">
-        <v>46400.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T370" s="0" t="s">
         <v>43</v>
@@ -35427,7 +35413,7 @@
         <v>48</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="D371" s="0" t="s">
         <v>76</v>
@@ -35510,7 +35496,7 @@
         <v>60</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D372" s="0" t="s">
         <v>50</v>
@@ -35525,7 +35511,7 @@
         <v>78</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="J372" s="11">
         <v>46356.125</v>
@@ -35599,13 +35585,13 @@
         <v>60</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="D373" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E373" s="0" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="F373" s="0" t="s">
         <v>146</v>
@@ -35614,16 +35600,16 @@
         <v>146</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="J373" s="11">
         <v>46310.125</v>
       </c>
       <c r="K373" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L373" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M373" s="0" t="s">
         <v>39</v>
@@ -35688,7 +35674,7 @@
         <v>223</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="D374" s="0" t="s">
         <v>76</v>
@@ -35703,7 +35689,7 @@
         <v>182</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="J374" s="11">
         <v>46310.125</v>
@@ -35768,16 +35754,16 @@
     </row>
     <row r="375">
       <c r="A375" s="0" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B375" s="0" t="s">
         <v>223</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D375" s="0" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E375" s="0" t="s">
         <v>138</v>
@@ -35789,7 +35775,7 @@
         <v>435</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="J375" s="11">
         <v>46392.125</v>
@@ -35854,7 +35840,7 @@
         <v>60</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D376" s="0" t="s">
         <v>159</v>
@@ -35869,7 +35855,7 @@
         <v>333</v>
       </c>
       <c r="H376" s="0" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="J376" s="11">
         <v>46326.125</v>
@@ -35940,7 +35926,7 @@
         <v>34</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="D377" s="0" t="s">
         <v>76</v>
@@ -35955,7 +35941,7 @@
         <v>53</v>
       </c>
       <c r="H377" s="0" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="J377" s="11">
         <v>46306.125</v>
@@ -36026,7 +36012,7 @@
         <v>34</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D378" s="0" t="s">
         <v>36</v>
@@ -36041,7 +36027,7 @@
         <v>59</v>
       </c>
       <c r="H378" s="0" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="J378" s="11">
         <v>46304.125</v>
@@ -36112,7 +36098,7 @@
         <v>60</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>50</v>
@@ -36192,19 +36178,19 @@
     </row>
     <row r="380">
       <c r="A380" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B380" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>246</v>
       </c>
       <c r="E380" s="0" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="F380" s="0" t="s">
         <v>205</v>
@@ -36284,7 +36270,7 @@
         <v>644</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>627</v>
@@ -36364,19 +36350,19 @@
     </row>
     <row r="382">
       <c r="A382" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B382" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D382" s="0" t="s">
         <v>108</v>
       </c>
       <c r="E382" s="0" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="F382" s="0" t="s">
         <v>206</v>
@@ -36456,13 +36442,13 @@
         <v>644</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D383" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E383" s="0" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="F383" s="0" t="s">
         <v>131</v>
@@ -36471,7 +36457,7 @@
         <v>320</v>
       </c>
       <c r="H383" s="0" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="J383" s="11">
         <v>46341.125</v>
@@ -36542,7 +36528,7 @@
         <v>48</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D384" s="0" t="s">
         <v>196</v>
@@ -36625,10 +36611,10 @@
         <v>643</v>
       </c>
       <c r="B385" s="0" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D385" s="0" t="s">
         <v>62</v>
@@ -36682,7 +36668,7 @@
         <v>43</v>
       </c>
       <c r="AC385" s="0" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="AD385" s="11">
         <v>46037.467388136574</v>
@@ -36711,16 +36697,16 @@
         <v>643</v>
       </c>
       <c r="B386" s="0" t="s">
+        <v>851</v>
+      </c>
+      <c r="C386" s="0" t="s">
         <v>854</v>
-      </c>
-      <c r="C386" s="0" t="s">
-        <v>857</v>
       </c>
       <c r="D386" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="F386" s="0" t="s">
         <v>78</v>
@@ -36736,7 +36722,7 @@
         <v>211</v>
       </c>
       <c r="L386" s="0" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="M386" s="0" t="s">
         <v>39</v>
@@ -36766,7 +36752,7 @@
         <v>43</v>
       </c>
       <c r="AC386" s="0" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="AD386" s="11">
         <v>46037.467388136574</v>
@@ -36795,16 +36781,16 @@
         <v>643</v>
       </c>
       <c r="B387" s="0" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="D387" s="0" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="E387" s="0" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="F387" s="0" t="s">
         <v>59</v>
@@ -36813,14 +36799,14 @@
         <v>131</v>
       </c>
       <c r="H387" s="0" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="J387" s="11"/>
       <c r="K387" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L387" s="0" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="M387" s="0" t="s">
         <v>39</v>
@@ -36841,7 +36827,7 @@
         <v>43</v>
       </c>
       <c r="AC387" s="0" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="AD387" s="11">
         <v>46038.63016152778</v>
@@ -36873,19 +36859,19 @@
         <v>48</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="D388" s="0" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="E388" s="0" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="F388" s="0" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="G388" s="0" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="H388" s="0" t="s">
         <v>128</v>
@@ -36953,25 +36939,25 @@
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B389" s="0" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>522</v>
       </c>
       <c r="E389" s="0" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F389" s="0" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="G389" s="0" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="J389" s="11">
         <v>46409.125</v>
@@ -37004,7 +36990,7 @@
         <v>44</v>
       </c>
       <c r="AC389" s="0" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="AD389" s="11">
         <v>46051.66783503472</v>
@@ -37030,25 +37016,25 @@
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="B390" s="0" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>522</v>
       </c>
       <c r="E390" s="0" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="F390" s="0" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="G390" s="0" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="J390" s="11">
         <v>46413.125</v>
@@ -37078,7 +37064,7 @@
         <v>44</v>
       </c>
       <c r="AC390" s="0" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="AD390" s="11">
         <v>46052.455825081015</v>
@@ -37110,7 +37096,7 @@
         <v>34</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>50</v>
@@ -37194,7 +37180,7 @@
         <v>34</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>36</v>
@@ -37280,13 +37266,13 @@
         <v>60</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>215</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="F393" s="0" t="s">
         <v>198</v>
@@ -37299,7 +37285,7 @@
         <v>211</v>
       </c>
       <c r="L393" s="0" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="M393" s="0" t="s">
         <v>39</v>
@@ -37357,13 +37343,13 @@
         <v>60</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>215</v>
       </c>
       <c r="E394" s="0" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="F394" s="0" t="s">
         <v>198</v>
@@ -37376,7 +37362,7 @@
         <v>211</v>
       </c>
       <c r="L394" s="0" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="M394" s="0" t="s">
         <v>39</v>
@@ -37428,25 +37414,25 @@
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B395" s="0" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>584</v>
       </c>
       <c r="E395" s="0" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="F395" s="0" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="G395" s="0" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="J395" s="11">
         <v>46401.125</v>
@@ -37479,7 +37465,7 @@
         <v>44</v>
       </c>
       <c r="AC395" s="0" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="AD395" s="11">
         <v>46104.56253545139</v>
@@ -37505,19 +37491,19 @@
     </row>
     <row r="396">
       <c r="A396" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B396" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>108</v>
       </c>
       <c r="E396" s="0" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="F396" s="0" t="s">
         <v>206</v>
@@ -37597,13 +37583,13 @@
         <v>644</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="D397" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="F397" s="0" t="s">
         <v>321</v>
@@ -37683,13 +37669,13 @@
         <v>60</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="D398" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="F398" s="0" t="s">
         <v>59</v>
@@ -37760,19 +37746,19 @@
     </row>
     <row r="399">
       <c r="A399" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B399" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>108</v>
       </c>
       <c r="E399" s="0" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="F399" s="0" t="s">
         <v>206</v>
@@ -37852,7 +37838,7 @@
         <v>34</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>196</v>
@@ -37938,13 +37924,13 @@
         <v>48</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D401" s="0" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="E401" s="0" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F401" s="0" t="s">
         <v>240</v>
@@ -37953,10 +37939,10 @@
         <v>240</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="J401" s="11">
-        <v>46357.125</v>
+        <v>46413.125</v>
       </c>
       <c r="K401" s="0" t="s">
         <v>55</v>
@@ -37977,7 +37963,7 @@
         <v>42</v>
       </c>
       <c r="R401" s="11">
-        <v>46357.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T401" s="0" t="s">
         <v>43</v>
@@ -38024,13 +38010,13 @@
         <v>48</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D402" s="0" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="E402" s="0" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="F402" s="0" t="s">
         <v>52</v>
@@ -38039,7 +38025,7 @@
         <v>53</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="J402" s="11">
         <v>46357.125</v>
@@ -38110,7 +38096,7 @@
         <v>34</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="D403" s="0" t="s">
         <v>159</v>
@@ -38125,7 +38111,7 @@
         <v>53</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="J403" s="11">
         <v>46361.125</v>
@@ -38196,7 +38182,7 @@
         <v>34</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>50</v>
@@ -38211,7 +38197,7 @@
         <v>147</v>
       </c>
       <c r="H404" s="0" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="J404" s="11">
         <v>46365.125</v>
@@ -38282,7 +38268,7 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>50</v>
@@ -38297,7 +38283,7 @@
         <v>131</v>
       </c>
       <c r="H405" s="0" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="J405" s="11">
         <v>46365.125</v>
@@ -38368,7 +38354,7 @@
         <v>34</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>36</v>
@@ -38383,7 +38369,7 @@
         <v>131</v>
       </c>
       <c r="H406" s="0" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="J406" s="11">
         <v>46305.125</v>
@@ -38454,13 +38440,13 @@
         <v>48</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D407" s="0" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="E407" s="0" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="F407" s="0" t="s">
         <v>53</v>
@@ -38469,7 +38455,7 @@
         <v>53</v>
       </c>
       <c r="H407" s="0" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="J407" s="11">
         <v>46365.125</v>
@@ -38540,7 +38526,7 @@
         <v>48</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>316</v>
@@ -38555,7 +38541,7 @@
         <v>131</v>
       </c>
       <c r="H408" s="0" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="J408" s="11">
         <v>46362.125</v>
@@ -38626,13 +38612,13 @@
         <v>34</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E409" s="0" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="F409" s="0" t="s">
         <v>64</v>
@@ -38712,7 +38698,7 @@
         <v>34</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>36</v>
@@ -38798,7 +38784,7 @@
         <v>34</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>36</v>
@@ -38884,13 +38870,13 @@
         <v>34</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="F412" s="0" t="s">
         <v>435</v>
@@ -38899,7 +38885,7 @@
         <v>435</v>
       </c>
       <c r="H412" s="0" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="J412" s="11">
         <v>46305.125</v>
@@ -38970,13 +38956,13 @@
         <v>34</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>71</v>
       </c>
       <c r="E413" s="0" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="F413" s="0" t="s">
         <v>131</v>
@@ -38985,7 +38971,7 @@
         <v>131</v>
       </c>
       <c r="H413" s="0" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="J413" s="11">
         <v>46310.125</v>
@@ -39056,7 +39042,7 @@
         <v>34</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>71</v>
@@ -39145,7 +39131,7 @@
         <v>34</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>50</v>
@@ -39160,7 +39146,7 @@
         <v>333</v>
       </c>
       <c r="H415" s="0" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="J415" s="11">
         <v>46356.125</v>
@@ -39234,13 +39220,13 @@
         <v>34</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="D416" s="0" t="s">
         <v>137</v>
       </c>
       <c r="E416" s="0" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="F416" s="0" t="s">
         <v>139</v>
@@ -39249,7 +39235,7 @@
         <v>139</v>
       </c>
       <c r="H416" s="0" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="J416" s="11"/>
       <c r="K416" s="0" t="s">
@@ -39321,13 +39307,13 @@
         <v>34</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E417" s="0" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="F417" s="0" t="s">
         <v>92</v>
@@ -39336,7 +39322,7 @@
         <v>92</v>
       </c>
       <c r="H417" s="0" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="J417" s="11">
         <v>46310.125</v>
@@ -39410,7 +39396,7 @@
         <v>34</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>119</v>
@@ -39425,7 +39411,7 @@
         <v>59</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="J418" s="11">
         <v>46310.125</v>
@@ -39496,7 +39482,7 @@
         <v>34</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>119</v>
@@ -39511,7 +39497,7 @@
         <v>59</v>
       </c>
       <c r="H419" s="0" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="J419" s="11">
         <v>46310.125</v>
@@ -39582,13 +39568,13 @@
         <v>48</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="D420" s="0" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="E420" s="0" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="F420" s="0" t="s">
         <v>198</v>
@@ -39665,7 +39651,7 @@
         <v>34</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>62</v>
@@ -39751,7 +39737,7 @@
         <v>34</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>36</v>
@@ -39766,14 +39752,14 @@
         <v>38</v>
       </c>
       <c r="H422" s="0" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="J422" s="11"/>
       <c r="K422" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L422" s="0" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="M422" s="0" t="s">
         <v>39</v>
@@ -39838,7 +39824,7 @@
         <v>34</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>36</v>
@@ -39853,14 +39839,14 @@
         <v>38</v>
       </c>
       <c r="H423" s="0" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="J423" s="11"/>
       <c r="K423" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L423" s="0" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="M423" s="0" t="s">
         <v>39</v>
@@ -39925,13 +39911,13 @@
         <v>48</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D424" s="0" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="E424" s="0" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="F424" s="0" t="s">
         <v>64</v>
@@ -39940,7 +39926,7 @@
         <v>64</v>
       </c>
       <c r="J424" s="11">
-        <v>46333.125</v>
+        <v>46407.125</v>
       </c>
       <c r="K424" s="0" t="s">
         <v>55</v>
@@ -39961,7 +39947,7 @@
         <v>42</v>
       </c>
       <c r="R424" s="11">
-        <v>46333.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T424" s="0" t="s">
         <v>43</v>
@@ -40008,7 +39994,7 @@
         <v>48</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>316</v>
@@ -40023,7 +40009,7 @@
         <v>127</v>
       </c>
       <c r="J425" s="11">
-        <v>46333.125</v>
+        <v>46407.125</v>
       </c>
       <c r="K425" s="0" t="s">
         <v>55</v>
@@ -40044,7 +40030,7 @@
         <v>42</v>
       </c>
       <c r="R425" s="11">
-        <v>46333.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T425" s="0" t="s">
         <v>43</v>
@@ -40091,13 +40077,13 @@
         <v>34</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>309</v>
       </c>
       <c r="E426" s="0" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="F426" s="0" t="s">
         <v>92</v>
@@ -40106,14 +40092,14 @@
         <v>38</v>
       </c>
       <c r="H426" s="0" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="J426" s="11"/>
       <c r="K426" s="0" t="s">
         <v>211</v>
       </c>
       <c r="L426" s="0" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="M426" s="0" t="s">
         <v>39</v>
@@ -40178,7 +40164,7 @@
         <v>48</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>382</v>
@@ -40261,13 +40247,13 @@
         <v>48</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="D428" s="0" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="E428" s="0" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="F428" s="0" t="s">
         <v>147</v>
@@ -40276,7 +40262,7 @@
         <v>147</v>
       </c>
       <c r="J428" s="11">
-        <v>46332.125</v>
+        <v>46399.125</v>
       </c>
       <c r="K428" s="0" t="s">
         <v>55</v>
@@ -40297,7 +40283,7 @@
         <v>42</v>
       </c>
       <c r="R428" s="11">
-        <v>46332.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T428" s="0" t="s">
         <v>43</v>
@@ -40344,7 +40330,7 @@
         <v>60</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>50</v>
@@ -40359,7 +40345,7 @@
         <v>165</v>
       </c>
       <c r="H429" s="0" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="J429" s="11">
         <v>46310.125</v>
@@ -40430,13 +40416,13 @@
         <v>60</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E430" s="0" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="F430" s="0" t="s">
         <v>326</v>
@@ -40445,7 +40431,7 @@
         <v>326</v>
       </c>
       <c r="H430" s="0" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="J430" s="11">
         <v>46373.125</v>
@@ -40516,7 +40502,7 @@
         <v>60</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>76</v>
@@ -40531,7 +40517,7 @@
         <v>520</v>
       </c>
       <c r="H431" s="0" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="J431" s="11">
         <v>46310.125</v>
@@ -40605,13 +40591,13 @@
         <v>60</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E432" s="0" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="F432" s="0" t="s">
         <v>166</v>
@@ -40694,7 +40680,7 @@
         <v>60</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="D433" s="0" t="s">
         <v>76</v>
@@ -40709,7 +40695,7 @@
         <v>53</v>
       </c>
       <c r="H433" s="0" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="J433" s="11">
         <v>46373.125</v>
@@ -40780,13 +40766,13 @@
         <v>60</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E434" s="0" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="F434" s="0" t="s">
         <v>254</v>
@@ -40795,7 +40781,7 @@
         <v>254</v>
       </c>
       <c r="H434" s="0" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="J434" s="11">
         <v>46310.125</v>
@@ -40866,7 +40852,7 @@
         <v>60</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>50</v>
@@ -40881,7 +40867,7 @@
         <v>147</v>
       </c>
       <c r="H435" s="0" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="J435" s="11">
         <v>46373.125</v>
@@ -40952,13 +40938,13 @@
         <v>60</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>731</v>
       </c>
       <c r="E436" s="0" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="F436" s="0" t="s">
         <v>206</v>
@@ -40967,7 +40953,7 @@
         <v>206</v>
       </c>
       <c r="H436" s="0" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="J436" s="11">
         <v>46310.125</v>
@@ -41038,7 +41024,7 @@
         <v>60</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="D437" s="0" t="s">
         <v>246</v>
@@ -41053,7 +41039,7 @@
         <v>321</v>
       </c>
       <c r="H437" s="0" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="J437" s="11">
         <v>46310.125</v>
@@ -41124,7 +41110,7 @@
         <v>60</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>256</v>
@@ -41139,7 +41125,7 @@
         <v>92</v>
       </c>
       <c r="H438" s="0" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="J438" s="11">
         <v>46310.125</v>
@@ -41210,13 +41196,13 @@
         <v>60</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>256</v>
       </c>
       <c r="E439" s="0" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="F439" s="0" t="s">
         <v>165</v>
@@ -41225,7 +41211,7 @@
         <v>165</v>
       </c>
       <c r="H439" s="0" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="J439" s="11">
         <v>46310.125</v>
@@ -41299,7 +41285,7 @@
         <v>60</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="D440" s="0" t="s">
         <v>246</v>
@@ -41388,13 +41374,13 @@
         <v>60</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D441" s="0" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="E441" s="0" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="F441" s="0" t="s">
         <v>289</v>
@@ -41474,7 +41460,7 @@
         <v>60</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>256</v>
@@ -41489,7 +41475,7 @@
         <v>320</v>
       </c>
       <c r="H442" s="0" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="J442" s="11">
         <v>46310.125</v>
@@ -41563,7 +41549,7 @@
         <v>60</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>406</v>
@@ -41578,7 +41564,7 @@
         <v>166</v>
       </c>
       <c r="H443" s="0" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="J443" s="11">
         <v>46373.125</v>
@@ -41649,7 +41635,7 @@
         <v>60</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>256</v>
@@ -41735,7 +41721,7 @@
         <v>60</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>256</v>
@@ -41750,7 +41736,7 @@
         <v>53</v>
       </c>
       <c r="H445" s="0" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="J445" s="11">
         <v>46310.125</v>
@@ -41821,7 +41807,7 @@
         <v>60</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>406</v>
@@ -41836,7 +41822,7 @@
         <v>321</v>
       </c>
       <c r="H446" s="0" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="J446" s="11">
         <v>46373.125</v>
@@ -41907,7 +41893,7 @@
         <v>60</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>256</v>
@@ -41922,7 +41908,7 @@
         <v>73</v>
       </c>
       <c r="H447" s="0" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="J447" s="11">
         <v>46310.125</v>
@@ -41993,7 +41979,7 @@
         <v>60</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>256</v>
@@ -42008,7 +41994,7 @@
         <v>320</v>
       </c>
       <c r="H448" s="0" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="J448" s="11">
         <v>46310.125</v>
@@ -42082,7 +42068,7 @@
         <v>60</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>406</v>
@@ -42097,7 +42083,7 @@
         <v>166</v>
       </c>
       <c r="H449" s="0" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="J449" s="11">
         <v>46373.125</v>
@@ -42168,7 +42154,7 @@
         <v>60</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>256</v>
@@ -42254,7 +42240,7 @@
         <v>60</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>159</v>
@@ -42269,7 +42255,7 @@
         <v>174</v>
       </c>
       <c r="H451" s="0" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="J451" s="11">
         <v>46310.125</v>
@@ -42340,13 +42326,13 @@
         <v>60</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="D452" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E452" s="0" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="F452" s="0" t="s">
         <v>498</v>
@@ -42355,7 +42341,7 @@
         <v>498</v>
       </c>
       <c r="H452" s="0" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="J452" s="11">
         <v>46373.125</v>
@@ -42426,7 +42412,7 @@
         <v>60</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>159</v>
@@ -42441,7 +42427,7 @@
         <v>514</v>
       </c>
       <c r="H453" s="0" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="J453" s="11">
         <v>46310.125</v>
@@ -42512,13 +42498,13 @@
         <v>60</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>159</v>
       </c>
       <c r="E454" s="0" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="F454" s="0" t="s">
         <v>326</v>
@@ -42527,7 +42513,7 @@
         <v>326</v>
       </c>
       <c r="H454" s="0" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="J454" s="11">
         <v>46310.125</v>
@@ -42601,7 +42587,7 @@
         <v>60</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>159</v>
@@ -42616,7 +42602,7 @@
         <v>326</v>
       </c>
       <c r="H455" s="0" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="J455" s="11"/>
       <c r="K455" s="0" t="s">
@@ -42679,25 +42665,25 @@
     </row>
     <row r="456">
       <c r="A456" s="0" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B456" s="0" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="D456" s="0" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="E456" s="0" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="F456" s="0" t="s">
         <v>294</v>
       </c>
       <c r="G456" s="0" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="J456" s="11">
         <v>46310.125</v>
@@ -42730,7 +42716,7 @@
         <v>44</v>
       </c>
       <c r="AC456" s="0" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="AD456" s="11">
         <v>46203.65469700231</v>
@@ -42762,13 +42748,13 @@
         <v>644</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E457" s="0" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="F457" s="0" t="s">
         <v>321</v>
@@ -42777,7 +42763,7 @@
         <v>321</v>
       </c>
       <c r="H457" s="0" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="J457" s="11">
         <v>46365.125</v>
@@ -42842,19 +42828,19 @@
     </row>
     <row r="458">
       <c r="A458" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B458" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="D458" s="0" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E458" s="0" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="F458" s="0" t="s">
         <v>205</v>
@@ -42863,7 +42849,7 @@
         <v>206</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="J458" s="11">
         <v>46365.125</v>
@@ -42934,13 +42920,13 @@
         <v>34</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E459" s="0" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="F459" s="0" t="s">
         <v>84</v>
@@ -43017,7 +43003,7 @@
         <v>34</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>36</v>
@@ -43097,16 +43083,16 @@
         <v>659</v>
       </c>
       <c r="B461" s="0" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="D461" s="0" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="F461" s="0" t="s">
         <v>198</v>
@@ -43142,7 +43128,7 @@
         <v>44</v>
       </c>
       <c r="AC461" s="0" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="AD461" s="11">
         <v>46209.58030755787</v>
@@ -43174,7 +43160,7 @@
         <v>34</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="D462" s="0" t="s">
         <v>119</v>
@@ -43189,7 +43175,7 @@
         <v>73</v>
       </c>
       <c r="H462" s="0" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J462" s="11">
         <v>46387.125</v>
@@ -43260,7 +43246,7 @@
         <v>34</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>119</v>
@@ -43275,7 +43261,7 @@
         <v>73</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J463" s="11">
         <v>46326.125</v>
@@ -43346,7 +43332,7 @@
         <v>34</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>50</v>
@@ -43361,7 +43347,7 @@
         <v>320</v>
       </c>
       <c r="H464" s="0" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="J464" s="11">
         <v>46326.125</v>
@@ -43432,13 +43418,13 @@
         <v>34</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E465" s="0" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="F465" s="0" t="s">
         <v>127</v>
@@ -43518,13 +43504,13 @@
         <v>34</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>177</v>
       </c>
       <c r="E466" s="0" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="F466" s="0" t="s">
         <v>146</v>
@@ -43533,7 +43519,7 @@
         <v>146</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="J466" s="11">
         <v>46310.125</v>
@@ -43604,13 +43590,13 @@
         <v>60</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="D467" s="0" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="E467" s="0" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="F467" s="0" t="s">
         <v>412</v>
@@ -43619,7 +43605,7 @@
         <v>412</v>
       </c>
       <c r="H467" s="0" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="J467" s="11">
         <v>46310.125</v>
@@ -43687,7 +43673,7 @@
         <v>60</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>76</v>
@@ -43702,7 +43688,7 @@
         <v>326</v>
       </c>
       <c r="H468" s="0" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="J468" s="11">
         <v>46406.125</v>
@@ -43773,13 +43759,13 @@
         <v>60</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E469" s="0" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="F469" s="0" t="s">
         <v>78</v>
@@ -43788,7 +43774,7 @@
         <v>228</v>
       </c>
       <c r="H469" s="0" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="J469" s="11">
         <v>46407.125</v>
@@ -43859,7 +43845,7 @@
         <v>60</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="D470" s="0" t="s">
         <v>246</v>
@@ -43874,7 +43860,7 @@
         <v>131</v>
       </c>
       <c r="H470" s="0" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="J470" s="11">
         <v>46407.125</v>
@@ -43945,7 +43931,7 @@
         <v>60</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="D471" s="0" t="s">
         <v>246</v>
@@ -43960,7 +43946,7 @@
         <v>131</v>
       </c>
       <c r="H471" s="0" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="J471" s="11">
         <v>46407.125</v>
@@ -44031,13 +44017,13 @@
         <v>60</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="D472" s="0" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E472" s="0" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F472" s="0" t="s">
         <v>53</v>
@@ -44046,7 +44032,7 @@
         <v>53</v>
       </c>
       <c r="H472" s="0" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="J472" s="11">
         <v>46406.125</v>
@@ -44117,7 +44103,7 @@
         <v>60</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>256</v>
@@ -44132,7 +44118,7 @@
         <v>73</v>
       </c>
       <c r="H473" s="0" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="J473" s="11">
         <v>46373.125</v>
@@ -44203,7 +44189,7 @@
         <v>48</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>50</v>
@@ -44289,10 +44275,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="D475" s="0" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E475" s="0" t="s">
         <v>225</v>
@@ -44304,7 +44290,7 @@
         <v>53</v>
       </c>
       <c r="H475" s="0" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="J475" s="11">
         <v>46310.125</v>
@@ -44375,13 +44361,13 @@
         <v>223</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="D476" s="0" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="E476" s="0" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="F476" s="0" t="s">
         <v>139</v>
@@ -44390,7 +44376,7 @@
         <v>139</v>
       </c>
       <c r="H476" s="0" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="J476" s="11">
         <v>46310.125</v>
@@ -44455,16 +44441,16 @@
         <v>659</v>
       </c>
       <c r="B477" s="0" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="D477" s="0" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="E477" s="0" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="F477" s="0" t="s">
         <v>198</v>
@@ -44503,7 +44489,7 @@
         <v>44</v>
       </c>
       <c r="AC477" s="0" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="AD477" s="11">
         <v>46219.55652277778</v>
@@ -44535,7 +44521,7 @@
         <v>48</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="D478" s="0" t="s">
         <v>376</v>
@@ -44550,7 +44536,7 @@
         <v>333</v>
       </c>
       <c r="H478" s="0" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="J478" s="11">
         <v>46402.125</v>
@@ -44621,7 +44607,7 @@
         <v>60</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="D479" s="0" t="s">
         <v>50</v>
@@ -44636,7 +44622,7 @@
         <v>78</v>
       </c>
       <c r="H479" s="0" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="J479" s="11">
         <v>46346.125</v>
@@ -44707,7 +44693,7 @@
         <v>60</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="D480" s="0" t="s">
         <v>246</v>
@@ -44722,7 +44708,7 @@
         <v>52</v>
       </c>
       <c r="H480" s="0" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="J480" s="11">
         <v>46346.125</v>
@@ -44793,7 +44779,7 @@
         <v>60</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="D481" s="0" t="s">
         <v>246</v>
@@ -44808,7 +44794,7 @@
         <v>205</v>
       </c>
       <c r="H481" s="0" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="J481" s="11">
         <v>46310.125</v>
@@ -44879,7 +44865,7 @@
         <v>60</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>50</v>
@@ -44894,7 +44880,7 @@
         <v>147</v>
       </c>
       <c r="H482" s="0" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="J482" s="11">
         <v>46407.125</v>
@@ -44965,7 +44951,7 @@
         <v>60</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="D483" s="0" t="s">
         <v>256</v>
@@ -44980,7 +44966,7 @@
         <v>228</v>
       </c>
       <c r="H483" s="0" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="J483" s="11">
         <v>46407.125</v>
@@ -45051,7 +45037,7 @@
         <v>60</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>256</v>
@@ -45066,7 +45052,7 @@
         <v>228</v>
       </c>
       <c r="H484" s="0" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="J484" s="11">
         <v>46407.125</v>
@@ -45131,13 +45117,13 @@
     </row>
     <row r="485">
       <c r="A485" s="0" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B485" s="0" t="s">
         <v>622</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>215</v>
@@ -45217,13 +45203,13 @@
         <v>622</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="D486" s="0" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="E486" s="0" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="F486" s="0" t="s">
         <v>435</v>
@@ -45297,13 +45283,13 @@
         <v>48</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="E487" s="0" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="F487" s="0" t="s">
         <v>97</v>
@@ -45383,13 +45369,13 @@
         <v>34</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E488" s="0" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="F488" s="0" t="s">
         <v>38</v>
@@ -45398,7 +45384,7 @@
         <v>38</v>
       </c>
       <c r="H488" s="0" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="J488" s="11">
         <v>46310.125</v>
@@ -45469,13 +45455,13 @@
         <v>48</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="D489" s="0" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="E489" s="0" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="F489" s="0" t="s">
         <v>134</v>
@@ -45552,7 +45538,7 @@
         <v>48</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="D490" s="0" t="s">
         <v>339</v>
@@ -45635,7 +45621,7 @@
         <v>48</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="D491" s="0" t="s">
         <v>339</v>
@@ -45718,7 +45704,7 @@
         <v>34</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>246</v>
@@ -45733,7 +45719,7 @@
         <v>38</v>
       </c>
       <c r="H492" s="0" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="J492" s="11">
         <v>46362.125</v>
@@ -45804,7 +45790,7 @@
         <v>34</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>246</v>
@@ -45819,7 +45805,7 @@
         <v>38</v>
       </c>
       <c r="H493" s="0" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="J493" s="11">
         <v>46362.125</v>
@@ -45890,7 +45876,7 @@
         <v>48</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>360</v>
@@ -45973,13 +45959,13 @@
         <v>48</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="D495" s="0" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="E495" s="0" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="F495" s="0" t="s">
         <v>254</v>
@@ -46056,13 +46042,13 @@
         <v>48</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="D496" s="0" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="E496" s="0" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="F496" s="0" t="s">
         <v>127</v>
@@ -46139,13 +46125,13 @@
         <v>48</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="D497" s="0" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="E497" s="0" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="F497" s="0" t="s">
         <v>289</v>
@@ -46222,13 +46208,13 @@
         <v>60</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D498" s="0" t="s">
         <v>522</v>
       </c>
       <c r="E498" s="0" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="F498" s="0" t="s">
         <v>104</v>
@@ -46302,19 +46288,19 @@
     </row>
     <row r="499">
       <c r="A499" s="0" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B499" s="0" t="s">
         <v>644</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="D499" s="0" t="s">
         <v>71</v>
       </c>
       <c r="E499" s="0" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F499" s="0" t="s">
         <v>288</v>
@@ -46323,7 +46309,7 @@
         <v>288</v>
       </c>
       <c r="H499" s="0" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="J499" s="11">
         <v>46372.125</v>
@@ -46394,19 +46380,19 @@
         <v>34</v>
       </c>
       <c r="C500" s="0" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="D500" s="0" t="s">
         <v>584</v>
       </c>
       <c r="E500" s="0" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F500" s="0" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="G500" s="0" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="H500" s="0" t="s">
         <v>199</v>
@@ -46480,19 +46466,19 @@
         <v>34</v>
       </c>
       <c r="C501" s="0" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="D501" s="0" t="s">
         <v>584</v>
       </c>
       <c r="E501" s="0" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F501" s="0" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="G501" s="0" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="H501" s="0" t="s">
         <v>199</v>
@@ -46566,7 +46552,7 @@
         <v>223</v>
       </c>
       <c r="C502" s="0" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="D502" s="0" t="s">
         <v>522</v>
@@ -46637,6 +46623,70 @@
       <c r="AJ502" s="3">
         <v>46476.125</v>
       </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="0" t="s">
+        <v>659</v>
+      </c>
+      <c r="B503" s="0" t="s">
+        <v>808</v>
+      </c>
+      <c r="C503" s="0" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D503" s="0" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E503" s="0" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F503" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="G503" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="J503" s="11"/>
+      <c r="K503" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="L503" s="0" t="s">
+        <v>1074</v>
+      </c>
+      <c r="M503" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="N503" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q503" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="T503" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="W503" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z503" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC503" s="0" t="s">
+        <v>808</v>
+      </c>
+      <c r="AD503" s="11">
+        <v>46301.476280462964</v>
+      </c>
+      <c r="AE503" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="AF503" s="3"/>
+      <c r="AG503" s="3"/>
+      <c r="AH503" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="AI503" s="3"/>
+      <c r="AJ503" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -46674,7 +46724,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J173"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -46714,7 +46764,7 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>1080</v>
@@ -46746,7 +46796,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>1083</v>
@@ -46778,7 +46828,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>1083</v>
@@ -46810,7 +46860,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>1086</v>
@@ -46842,7 +46892,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>1086</v>
@@ -46874,7 +46924,7 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>1089</v>
@@ -46906,7 +46956,7 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>1089</v>
@@ -46938,7 +46988,7 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>1090</v>
@@ -46970,7 +47020,7 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>1090</v>
@@ -47002,7 +47052,7 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>1091</v>
@@ -47034,7 +47084,7 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>1091</v>
@@ -47066,7 +47116,7 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>1096</v>
@@ -47098,7 +47148,7 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>1096</v>
@@ -47130,13 +47180,13 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>1097</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>30</v>
@@ -47157,18 +47207,18 @@
         <v>1082</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>1097</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>29</v>
@@ -47189,18 +47239,18 @@
         <v>1082</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>1097</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>30</v>
@@ -47221,7 +47271,7 @@
         <v>1082</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="18">
@@ -47290,7 +47340,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>1101</v>
@@ -47322,7 +47372,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>1101</v>
@@ -47386,7 +47436,7 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>1105</v>
@@ -47418,7 +47468,7 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>1106</v>
@@ -47450,7 +47500,7 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>1107</v>
@@ -47514,7 +47564,7 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>1105</v>
@@ -47770,7 +47820,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>1114</v>
@@ -47834,7 +47884,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>1115</v>
@@ -47866,7 +47916,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>1115</v>
@@ -47898,7 +47948,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>1117</v>
@@ -48026,7 +48076,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>1120</v>
@@ -48058,7 +48108,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="B44" s="0" t="s">
         <v>1120</v>
@@ -48090,7 +48140,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>1122</v>
@@ -48122,7 +48172,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="B46" s="0" t="s">
         <v>1120</v>
@@ -48154,7 +48204,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>1120</v>
@@ -48474,7 +48524,7 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B57" s="0" t="s">
         <v>1127</v>
@@ -48506,7 +48556,7 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B58" s="0" t="s">
         <v>1128</v>
@@ -48634,7 +48684,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>1127</v>
@@ -48730,7 +48780,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>1130</v>
@@ -48794,7 +48844,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>1130</v>
@@ -48826,7 +48876,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>1133</v>
@@ -48890,7 +48940,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>1135</v>
@@ -48954,7 +49004,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>1136</v>
@@ -49082,7 +49132,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B76" s="0" t="s">
         <v>1138</v>
@@ -49114,7 +49164,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>1139</v>
@@ -49562,7 +49612,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B91" s="0" t="s">
         <v>1147</v>
@@ -49594,7 +49644,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B92" s="0" t="s">
         <v>1139</v>
@@ -49626,7 +49676,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B93" s="0" t="s">
         <v>1139</v>
@@ -49658,7 +49708,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="B94" s="0" t="s">
         <v>1138</v>
@@ -49690,7 +49740,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>1139</v>
@@ -49722,7 +49772,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>1138</v>
@@ -50010,7 +50060,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B105" s="0" t="s">
         <v>1132</v>
@@ -50074,7 +50124,7 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B107" s="0" t="s">
         <v>1132</v>
@@ -50170,7 +50220,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B110" s="0" t="s">
         <v>1155</v>
@@ -50202,7 +50252,7 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B111" s="0" t="s">
         <v>1155</v>
@@ -50234,7 +50284,7 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B112" s="0" t="s">
         <v>1123</v>
@@ -50266,7 +50316,7 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B113" s="0" t="s">
         <v>1123</v>
@@ -50394,7 +50444,7 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="B117" s="0" t="s">
         <v>1157</v>
@@ -50426,7 +50476,7 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B118" s="0" t="s">
         <v>1123</v>
@@ -50458,7 +50508,7 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B119" s="0" t="s">
         <v>1123</v>
@@ -50490,7 +50540,7 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B120" s="0" t="s">
         <v>1146</v>
@@ -50522,7 +50572,7 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B121" s="0" t="s">
         <v>1146</v>
@@ -50554,7 +50604,7 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B122" s="0" t="s">
         <v>1146</v>
@@ -50586,7 +50636,7 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B123" s="0" t="s">
         <v>1146</v>
@@ -50650,7 +50700,7 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B125" s="0" t="s">
         <v>1146</v>
@@ -50682,7 +50732,7 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B126" s="0" t="s">
         <v>1146</v>
@@ -50746,7 +50796,7 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B128" s="0" t="s">
         <v>1159</v>
@@ -50778,7 +50828,7 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B129" s="0" t="s">
         <v>1146</v>
@@ -50810,7 +50860,7 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B130" s="0" t="s">
         <v>1146</v>
@@ -51386,7 +51436,7 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="B148" s="0" t="s">
         <v>1160</v>
@@ -51418,7 +51468,7 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="B149" s="0" t="s">
         <v>1160</v>
@@ -51509,710 +51559,6 @@
         <v>1094</v>
       </c>
       <c r="J151" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="0" t="s">
-        <v>689</v>
-      </c>
-      <c r="B152" s="0" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C152" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D152" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E152" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F152" s="0" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G152" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H152" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="I152" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J152" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="0" t="s">
-        <v>688</v>
-      </c>
-      <c r="B153" s="0" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C153" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D153" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E153" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F153" s="0" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G153" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H153" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="I153" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J153" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="0" t="s">
-        <v>553</v>
-      </c>
-      <c r="B154" s="0" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C154" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D154" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E154" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F154" s="0" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G154" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H154" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="I154" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J154" s="0" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="B155" s="0" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C155" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D155" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E155" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F155" s="0" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G155" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H155" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="I155" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J155" s="0" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="0" t="s">
-        <v>899</v>
-      </c>
-      <c r="B156" s="0" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C156" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D156" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E156" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F156" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G156" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H156" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="I156" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J156" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="0" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B157" s="0" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C157" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D157" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E157" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F157" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G157" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H157" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="I157" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J157" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="0" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B158" s="0" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C158" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D158" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E158" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F158" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G158" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H158" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="I158" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J158" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="0" t="s">
-        <v>551</v>
-      </c>
-      <c r="B159" s="0" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C159" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D159" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E159" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F159" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G159" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H159" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="I159" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J159" s="0" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="0" t="s">
-        <v>553</v>
-      </c>
-      <c r="B160" s="0" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C160" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D160" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E160" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F160" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G160" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H160" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="I160" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J160" s="0" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B161" s="0" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C161" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D161" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E161" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F161" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G161" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H161" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="I161" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J161" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="0" t="s">
-        <v>302</v>
-      </c>
-      <c r="B162" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C162" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D162" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E162" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F162" s="0" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G162" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H162" s="0" t="s">
-        <v>1131</v>
-      </c>
-      <c r="I162" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J162" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="B163" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C163" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D163" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E163" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F163" s="0" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G163" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H163" s="0" t="s">
-        <v>1131</v>
-      </c>
-      <c r="I163" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J163" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="B164" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C164" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D164" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E164" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F164" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G164" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H164" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I164" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J164" s="0" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="0" t="s">
-        <v>569</v>
-      </c>
-      <c r="B165" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C165" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D165" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E165" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F165" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G165" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H165" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I165" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J165" s="0" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="0" t="s">
-        <v>569</v>
-      </c>
-      <c r="B166" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C166" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D166" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E166" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F166" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G166" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H166" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I166" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J166" s="0" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="B167" s="0" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C167" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D167" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E167" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F167" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G167" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H167" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I167" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J167" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="0" t="s">
-        <v>375</v>
-      </c>
-      <c r="B168" s="0" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C168" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D168" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E168" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F168" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G168" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H168" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I168" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J168" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="0" t="s">
-        <v>374</v>
-      </c>
-      <c r="B169" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C169" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D169" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E169" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F169" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G169" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H169" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I169" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J169" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="0" t="s">
-        <v>373</v>
-      </c>
-      <c r="B170" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C170" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D170" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E170" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F170" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G170" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H170" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I170" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J170" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="B171" s="0" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C171" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D171" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E171" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F171" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G171" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H171" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I171" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J171" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="0" t="s">
-        <v>776</v>
-      </c>
-      <c r="B172" s="0" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C172" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D172" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E172" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F172" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G172" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H172" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I172" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J172" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="0" t="s">
-        <v>772</v>
-      </c>
-      <c r="B173" s="0" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C173" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D173" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E173" s="11">
-        <v>46241</v>
-      </c>
-      <c r="F173" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G173" s="11">
-        <v>46421.125</v>
-      </c>
-      <c r="H173" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I173" s="0" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J173" s="0" t="s">
         <v>56</v>
       </c>
     </row>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="1165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="1172">
   <si>
     <t>Geração:</t>
   </si>
@@ -2424,6 +2424,9 @@
     <t>LK 1113</t>
   </si>
   <si>
+    <t>Bloqueio temporário / Documento ConsultaCRLV vencendo</t>
+  </si>
+  <si>
     <t>JJZ7H52</t>
   </si>
   <si>
@@ -3241,6 +3244,24 @@
   </si>
   <si>
     <t>Inspeções Checklist de Qualidade, Checklist de Segurança SESMT pendentes</t>
+  </si>
+  <si>
+    <t>KEA6J64</t>
+  </si>
+  <si>
+    <t>RANDON SR FG</t>
+  </si>
+  <si>
+    <t>Documento CRLV reprovado / Documentos ConsultaCRLV, ExtratoANTT ausentes ou vencidos / Inspeções Checklist de Qualidade, Checklist de Segurança SESMT pendentes</t>
+  </si>
+  <si>
+    <t>MBQ6J91</t>
+  </si>
+  <si>
+    <t>REB/FACCHINI-IR RER FR</t>
+  </si>
+  <si>
+    <t>Documento CRLV reprovado / Documentos ConsultaCRLV, ExtratoANTT ausentes ou vencidos / Inspeções Checklist de Qualidade, Checklist de Segurança SESMT pendentes / Documento CRLV vencendo</t>
   </si>
   <si>
     <t>Marca / Modelo</t>
@@ -3688,7 +3709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ501"/>
+  <dimension ref="A1:AJ503"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -3699,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46303.368016643515</v>
+        <v>46303.63262681713</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -11224,13 +11245,13 @@
         <v>39</v>
       </c>
       <c r="J88" s="11">
-        <v>46310.125</v>
+        <v>46391.125</v>
       </c>
       <c r="K88" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L88" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M88" s="0" t="s">
         <v>39</v>
@@ -11239,13 +11260,13 @@
         <v>42</v>
       </c>
       <c r="O88" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q88" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R88" s="11">
-        <v>46341.125</v>
+        <v>46485.125</v>
       </c>
       <c r="T88" s="0" t="s">
         <v>43</v>
@@ -11396,13 +11417,13 @@
         <v>39</v>
       </c>
       <c r="J90" s="11">
-        <v>46310.125</v>
+        <v>46391.125</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M90" s="0" t="s">
         <v>39</v>
@@ -11411,13 +11432,13 @@
         <v>42</v>
       </c>
       <c r="O90" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q90" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R90" s="11">
-        <v>46334.125</v>
+        <v>46485.125</v>
       </c>
       <c r="T90" s="0" t="s">
         <v>43</v>
@@ -11568,13 +11589,13 @@
         <v>39</v>
       </c>
       <c r="J92" s="11">
-        <v>46310.125</v>
+        <v>46391.125</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L92" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M92" s="0" t="s">
         <v>39</v>
@@ -11583,13 +11604,13 @@
         <v>42</v>
       </c>
       <c r="O92" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q92" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R92" s="11">
-        <v>46414.125</v>
+        <v>46485.125</v>
       </c>
       <c r="T92" s="0" t="s">
         <v>43</v>
@@ -16133,7 +16154,7 @@
         <v>39</v>
       </c>
       <c r="J145" s="11">
-        <v>46310.125</v>
+        <v>46413.125</v>
       </c>
       <c r="K145" s="0" t="s">
         <v>55</v>
@@ -16148,13 +16169,13 @@
         <v>42</v>
       </c>
       <c r="O145" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q145" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R145" s="11">
-        <v>46423.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T145" s="0" t="s">
         <v>44</v>
@@ -16305,7 +16326,7 @@
         <v>39</v>
       </c>
       <c r="J147" s="11">
-        <v>46310.125</v>
+        <v>46405.125</v>
       </c>
       <c r="K147" s="0" t="s">
         <v>55</v>
@@ -16320,13 +16341,13 @@
         <v>42</v>
       </c>
       <c r="O147" s="11">
-        <v>46310.125</v>
+        <v>46645.125</v>
       </c>
       <c r="Q147" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R147" s="11">
-        <v>46364.125</v>
+        <v>46485.125</v>
       </c>
       <c r="T147" s="0" t="s">
         <v>43</v>
@@ -33577,7 +33598,7 @@
         <v>602</v>
       </c>
       <c r="J349" s="11">
-        <v>46310.125</v>
+        <v>46425.125</v>
       </c>
       <c r="K349" s="0" t="s">
         <v>55</v>
@@ -33592,13 +33613,13 @@
         <v>42</v>
       </c>
       <c r="O349" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q349" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R349" s="11">
-        <v>46428.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T349" s="0" t="s">
         <v>43</v>
@@ -34256,14 +34277,12 @@
       <c r="G357" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="J357" s="11">
-        <v>46325.125</v>
-      </c>
+      <c r="J357" s="11"/>
       <c r="K357" s="0" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="L357" s="0" t="s">
-        <v>80</v>
+        <v>803</v>
       </c>
       <c r="M357" s="0" t="s">
         <v>39</v>
@@ -34322,7 +34341,7 @@
         <v>60</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D358" s="0" t="s">
         <v>162</v>
@@ -34337,7 +34356,7 @@
         <v>53</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J358" s="11">
         <v>46373.125</v>
@@ -34408,13 +34427,13 @@
         <v>60</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D359" s="0" t="s">
         <v>733</v>
       </c>
       <c r="E359" s="0" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F359" s="0" t="s">
         <v>59</v>
@@ -34423,7 +34442,7 @@
         <v>134</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J359" s="11">
         <v>46373.125</v>
@@ -34497,7 +34516,7 @@
         <v>60</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D360" s="0" t="s">
         <v>50</v>
@@ -34512,7 +34531,7 @@
         <v>131</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="J360" s="11">
         <v>46310.125</v>
@@ -34580,16 +34599,16 @@
         <v>661</v>
       </c>
       <c r="B361" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D361" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E361" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F361" s="0" t="s">
         <v>288</v>
@@ -34628,7 +34647,7 @@
         <v>44</v>
       </c>
       <c r="AC361" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AD361" s="11">
         <v>45847.61793511574</v>
@@ -34654,19 +34673,19 @@
     </row>
     <row r="362">
       <c r="A362" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B362" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D362" s="0" t="s">
         <v>772</v>
       </c>
       <c r="E362" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F362" s="0" t="s">
         <v>209</v>
@@ -34737,19 +34756,19 @@
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B363" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D363" s="0" t="s">
         <v>772</v>
       </c>
       <c r="E363" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F363" s="0" t="s">
         <v>208</v>
@@ -34820,19 +34839,19 @@
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B364" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D364" s="0" t="s">
         <v>408</v>
       </c>
       <c r="E364" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F364" s="0" t="s">
         <v>134</v>
@@ -34903,19 +34922,19 @@
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B365" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D365" s="0" t="s">
         <v>772</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F365" s="0" t="s">
         <v>322</v>
@@ -34986,19 +35005,19 @@
     </row>
     <row r="366">
       <c r="A366" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B366" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D366" s="0" t="s">
         <v>246</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F366" s="0" t="s">
         <v>208</v>
@@ -35075,13 +35094,13 @@
         <v>624</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D367" s="0" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E367" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F367" s="0" t="s">
         <v>168</v>
@@ -35155,7 +35174,7 @@
         <v>34</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D368" s="0" t="s">
         <v>62</v>
@@ -35241,7 +35260,7 @@
         <v>48</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D369" s="0" t="s">
         <v>225</v>
@@ -35324,7 +35343,7 @@
         <v>48</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D370" s="0" t="s">
         <v>76</v>
@@ -35407,7 +35426,7 @@
         <v>60</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D371" s="0" t="s">
         <v>50</v>
@@ -35422,7 +35441,7 @@
         <v>78</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J371" s="11">
         <v>46356.125</v>
@@ -35496,13 +35515,13 @@
         <v>60</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D372" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E372" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F372" s="0" t="s">
         <v>149</v>
@@ -35585,7 +35604,7 @@
         <v>223</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D373" s="0" t="s">
         <v>76</v>
@@ -35600,7 +35619,7 @@
         <v>185</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="J373" s="11">
         <v>46310.125</v>
@@ -35665,16 +35684,16 @@
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B374" s="0" t="s">
         <v>223</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D374" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E374" s="0" t="s">
         <v>141</v>
@@ -35686,7 +35705,7 @@
         <v>437</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="J374" s="11">
         <v>46392.125</v>
@@ -35751,7 +35770,7 @@
         <v>60</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D375" s="0" t="s">
         <v>162</v>
@@ -35766,7 +35785,7 @@
         <v>335</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="J375" s="11">
         <v>46326.125</v>
@@ -35837,7 +35856,7 @@
         <v>34</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D376" s="0" t="s">
         <v>76</v>
@@ -35852,7 +35871,7 @@
         <v>53</v>
       </c>
       <c r="H376" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="J376" s="11">
         <v>46306.125</v>
@@ -35923,7 +35942,7 @@
         <v>34</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D377" s="0" t="s">
         <v>36</v>
@@ -35938,7 +35957,7 @@
         <v>59</v>
       </c>
       <c r="H377" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="J377" s="11">
         <v>46304.125</v>
@@ -36009,7 +36028,7 @@
         <v>60</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D378" s="0" t="s">
         <v>50</v>
@@ -36089,19 +36108,19 @@
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B379" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>246</v>
       </c>
       <c r="E379" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F379" s="0" t="s">
         <v>208</v>
@@ -36181,7 +36200,7 @@
         <v>646</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>629</v>
@@ -36261,19 +36280,19 @@
     </row>
     <row r="381">
       <c r="A381" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B381" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>108</v>
       </c>
       <c r="E381" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F381" s="0" t="s">
         <v>209</v>
@@ -36353,13 +36372,13 @@
         <v>646</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D382" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E382" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F382" s="0" t="s">
         <v>134</v>
@@ -36368,7 +36387,7 @@
         <v>321</v>
       </c>
       <c r="H382" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="J382" s="11">
         <v>46341.125</v>
@@ -36439,7 +36458,7 @@
         <v>48</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D383" s="0" t="s">
         <v>199</v>
@@ -36522,10 +36541,10 @@
         <v>645</v>
       </c>
       <c r="B384" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D384" s="0" t="s">
         <v>62</v>
@@ -36579,7 +36598,7 @@
         <v>43</v>
       </c>
       <c r="AC384" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AD384" s="11">
         <v>46037.467388136574</v>
@@ -36608,16 +36627,16 @@
         <v>645</v>
       </c>
       <c r="B385" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D385" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E385" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F385" s="0" t="s">
         <v>78</v>
@@ -36633,7 +36652,7 @@
         <v>110</v>
       </c>
       <c r="L385" s="0" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="M385" s="0" t="s">
         <v>39</v>
@@ -36663,7 +36682,7 @@
         <v>43</v>
       </c>
       <c r="AC385" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AD385" s="11">
         <v>46037.467388136574</v>
@@ -36692,16 +36711,16 @@
         <v>645</v>
       </c>
       <c r="B386" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D386" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F386" s="0" t="s">
         <v>59</v>
@@ -36710,14 +36729,14 @@
         <v>134</v>
       </c>
       <c r="H386" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="J386" s="11"/>
       <c r="K386" s="0" t="s">
         <v>110</v>
       </c>
       <c r="L386" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M386" s="0" t="s">
         <v>39</v>
@@ -36738,7 +36757,7 @@
         <v>43</v>
       </c>
       <c r="AC386" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AD386" s="11">
         <v>46038.63016152778</v>
@@ -36770,31 +36789,31 @@
         <v>48</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D387" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E387" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F387" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G387" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H387" s="0" t="s">
         <v>132</v>
       </c>
       <c r="J387" s="11">
-        <v>46311.125</v>
+        <v>46391.125</v>
       </c>
       <c r="K387" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L387" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M387" s="0" t="s">
         <v>39</v>
@@ -36803,13 +36822,13 @@
         <v>42</v>
       </c>
       <c r="O387" s="11">
-        <v>46311.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q387" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R387" s="11">
-        <v>46334.125</v>
+        <v>46485.125</v>
       </c>
       <c r="T387" s="0" t="s">
         <v>43</v>
@@ -36850,25 +36869,25 @@
     </row>
     <row r="388">
       <c r="A388" s="0" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B388" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D388" s="0" t="s">
         <v>524</v>
       </c>
       <c r="E388" s="0" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F388" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G388" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="J388" s="11">
         <v>46409.125</v>
@@ -36901,7 +36920,7 @@
         <v>44</v>
       </c>
       <c r="AC388" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AD388" s="11">
         <v>46051.66783503472</v>
@@ -36927,25 +36946,25 @@
     </row>
     <row r="389">
       <c r="A389" s="0" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B389" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>524</v>
       </c>
       <c r="E389" s="0" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F389" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G389" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="J389" s="11">
         <v>46413.125</v>
@@ -36975,7 +36994,7 @@
         <v>44</v>
       </c>
       <c r="AC389" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AD389" s="11">
         <v>46052.455825081015</v>
@@ -37007,7 +37026,7 @@
         <v>34</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>50</v>
@@ -37091,7 +37110,7 @@
         <v>34</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>36</v>
@@ -37177,13 +37196,13 @@
         <v>60</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>215</v>
       </c>
       <c r="E392" s="0" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F392" s="0" t="s">
         <v>201</v>
@@ -37196,7 +37215,7 @@
         <v>110</v>
       </c>
       <c r="L392" s="0" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="M392" s="0" t="s">
         <v>39</v>
@@ -37254,13 +37273,13 @@
         <v>60</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>215</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F393" s="0" t="s">
         <v>201</v>
@@ -37273,7 +37292,7 @@
         <v>110</v>
       </c>
       <c r="L393" s="0" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M393" s="0" t="s">
         <v>39</v>
@@ -37325,25 +37344,25 @@
     </row>
     <row r="394">
       <c r="A394" s="0" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B394" s="0" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>586</v>
       </c>
       <c r="E394" s="0" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="F394" s="0" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G394" s="0" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="J394" s="11">
         <v>46401.125</v>
@@ -37376,7 +37395,7 @@
         <v>44</v>
       </c>
       <c r="AC394" s="0" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AD394" s="11">
         <v>46104.56253545139</v>
@@ -37402,19 +37421,19 @@
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B395" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>108</v>
       </c>
       <c r="E395" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F395" s="0" t="s">
         <v>209</v>
@@ -37494,13 +37513,13 @@
         <v>646</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E396" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F396" s="0" t="s">
         <v>322</v>
@@ -37580,13 +37599,13 @@
         <v>60</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D397" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F397" s="0" t="s">
         <v>59</v>
@@ -37599,7 +37618,7 @@
         <v>110</v>
       </c>
       <c r="L397" s="0" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="M397" s="0" t="s">
         <v>39</v>
@@ -37655,19 +37674,19 @@
     </row>
     <row r="398">
       <c r="A398" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B398" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D398" s="0" t="s">
         <v>108</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F398" s="0" t="s">
         <v>209</v>
@@ -37747,7 +37766,7 @@
         <v>34</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>199</v>
@@ -37833,13 +37852,13 @@
         <v>48</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D400" s="0" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E400" s="0" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F400" s="0" t="s">
         <v>240</v>
@@ -37848,7 +37867,7 @@
         <v>240</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="J400" s="11">
         <v>46413.125</v>
@@ -37919,13 +37938,13 @@
         <v>48</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D401" s="0" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E401" s="0" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="F401" s="0" t="s">
         <v>52</v>
@@ -37934,7 +37953,7 @@
         <v>53</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="J401" s="11">
         <v>46357.125</v>
@@ -38005,7 +38024,7 @@
         <v>34</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>162</v>
@@ -38020,7 +38039,7 @@
         <v>53</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="J402" s="11">
         <v>46361.125</v>
@@ -38091,7 +38110,7 @@
         <v>34</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D403" s="0" t="s">
         <v>50</v>
@@ -38106,7 +38125,7 @@
         <v>150</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="J403" s="11">
         <v>46365.125</v>
@@ -38177,7 +38196,7 @@
         <v>34</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>50</v>
@@ -38192,7 +38211,7 @@
         <v>134</v>
       </c>
       <c r="H404" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J404" s="11">
         <v>46365.125</v>
@@ -38263,7 +38282,7 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>36</v>
@@ -38278,7 +38297,7 @@
         <v>134</v>
       </c>
       <c r="H405" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="J405" s="11">
         <v>46305.125</v>
@@ -38349,13 +38368,13 @@
         <v>48</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D406" s="0" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E406" s="0" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F406" s="0" t="s">
         <v>53</v>
@@ -38364,7 +38383,7 @@
         <v>53</v>
       </c>
       <c r="H406" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J406" s="11">
         <v>46365.125</v>
@@ -38435,7 +38454,7 @@
         <v>48</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>317</v>
@@ -38450,7 +38469,7 @@
         <v>134</v>
       </c>
       <c r="H407" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="J407" s="11">
         <v>46362.125</v>
@@ -38521,13 +38540,13 @@
         <v>34</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E408" s="0" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F408" s="0" t="s">
         <v>64</v>
@@ -38607,7 +38626,7 @@
         <v>34</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>36</v>
@@ -38693,7 +38712,7 @@
         <v>34</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>36</v>
@@ -38779,13 +38798,13 @@
         <v>34</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E411" s="0" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F411" s="0" t="s">
         <v>437</v>
@@ -38794,7 +38813,7 @@
         <v>437</v>
       </c>
       <c r="H411" s="0" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J411" s="11">
         <v>46305.125</v>
@@ -38865,13 +38884,13 @@
         <v>34</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>71</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F412" s="0" t="s">
         <v>134</v>
@@ -38880,7 +38899,7 @@
         <v>134</v>
       </c>
       <c r="H412" s="0" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J412" s="11">
         <v>46310.125</v>
@@ -38951,7 +38970,7 @@
         <v>34</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>71</v>
@@ -39040,7 +39059,7 @@
         <v>34</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>50</v>
@@ -39055,7 +39074,7 @@
         <v>335</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="J414" s="11">
         <v>46356.125</v>
@@ -39129,13 +39148,13 @@
         <v>34</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>140</v>
       </c>
       <c r="E415" s="0" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F415" s="0" t="s">
         <v>142</v>
@@ -39144,7 +39163,7 @@
         <v>142</v>
       </c>
       <c r="H415" s="0" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="J415" s="11"/>
       <c r="K415" s="0" t="s">
@@ -39216,13 +39235,13 @@
         <v>34</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D416" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E416" s="0" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F416" s="0" t="s">
         <v>92</v>
@@ -39231,7 +39250,7 @@
         <v>92</v>
       </c>
       <c r="H416" s="0" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="J416" s="11">
         <v>46310.125</v>
@@ -39305,7 +39324,7 @@
         <v>34</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>122</v>
@@ -39320,7 +39339,7 @@
         <v>59</v>
       </c>
       <c r="H417" s="0" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="J417" s="11">
         <v>46310.125</v>
@@ -39391,7 +39410,7 @@
         <v>34</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>122</v>
@@ -39406,7 +39425,7 @@
         <v>59</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="J418" s="11">
         <v>46310.125</v>
@@ -39477,13 +39496,13 @@
         <v>48</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D419" s="0" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E419" s="0" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F419" s="0" t="s">
         <v>201</v>
@@ -39560,7 +39579,7 @@
         <v>34</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D420" s="0" t="s">
         <v>62</v>
@@ -39646,7 +39665,7 @@
         <v>34</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>36</v>
@@ -39661,14 +39680,14 @@
         <v>38</v>
       </c>
       <c r="H421" s="0" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J421" s="11"/>
       <c r="K421" s="0" t="s">
         <v>110</v>
       </c>
       <c r="L421" s="0" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M421" s="0" t="s">
         <v>39</v>
@@ -39733,7 +39752,7 @@
         <v>34</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>36</v>
@@ -39748,14 +39767,14 @@
         <v>38</v>
       </c>
       <c r="H422" s="0" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J422" s="11"/>
       <c r="K422" s="0" t="s">
         <v>110</v>
       </c>
       <c r="L422" s="0" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M422" s="0" t="s">
         <v>39</v>
@@ -39820,13 +39839,13 @@
         <v>48</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D423" s="0" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E423" s="0" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F423" s="0" t="s">
         <v>64</v>
@@ -39903,7 +39922,7 @@
         <v>48</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D424" s="0" t="s">
         <v>317</v>
@@ -39986,13 +40005,13 @@
         <v>34</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>310</v>
       </c>
       <c r="E425" s="0" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F425" s="0" t="s">
         <v>92</v>
@@ -40001,14 +40020,14 @@
         <v>38</v>
       </c>
       <c r="H425" s="0" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="J425" s="11"/>
       <c r="K425" s="0" t="s">
         <v>110</v>
       </c>
       <c r="L425" s="0" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="M425" s="0" t="s">
         <v>39</v>
@@ -40073,7 +40092,7 @@
         <v>48</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>384</v>
@@ -40088,7 +40107,7 @@
         <v>52</v>
       </c>
       <c r="J426" s="11">
-        <v>46332.125</v>
+        <v>46399.125</v>
       </c>
       <c r="K426" s="0" t="s">
         <v>55</v>
@@ -40109,7 +40128,7 @@
         <v>42</v>
       </c>
       <c r="R426" s="11">
-        <v>46332.125</v>
+        <v>46482.125</v>
       </c>
       <c r="T426" s="0" t="s">
         <v>43</v>
@@ -40156,13 +40175,13 @@
         <v>48</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D427" s="0" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="E427" s="0" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F427" s="0" t="s">
         <v>150</v>
@@ -40239,7 +40258,7 @@
         <v>60</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>50</v>
@@ -40254,7 +40273,7 @@
         <v>168</v>
       </c>
       <c r="H428" s="0" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J428" s="11">
         <v>46310.125</v>
@@ -40325,13 +40344,13 @@
         <v>60</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E429" s="0" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F429" s="0" t="s">
         <v>327</v>
@@ -40340,7 +40359,7 @@
         <v>327</v>
       </c>
       <c r="H429" s="0" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="J429" s="11">
         <v>46373.125</v>
@@ -40411,7 +40430,7 @@
         <v>60</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>76</v>
@@ -40426,7 +40445,7 @@
         <v>522</v>
       </c>
       <c r="H430" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="J430" s="11">
         <v>46310.125</v>
@@ -40500,13 +40519,13 @@
         <v>60</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E431" s="0" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F431" s="0" t="s">
         <v>169</v>
@@ -40589,7 +40608,7 @@
         <v>60</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>76</v>
@@ -40604,7 +40623,7 @@
         <v>53</v>
       </c>
       <c r="H432" s="0" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="J432" s="11">
         <v>46373.125</v>
@@ -40675,13 +40694,13 @@
         <v>60</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D433" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E433" s="0" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F433" s="0" t="s">
         <v>254</v>
@@ -40690,7 +40709,7 @@
         <v>254</v>
       </c>
       <c r="H433" s="0" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="J433" s="11">
         <v>46310.125</v>
@@ -40761,7 +40780,7 @@
         <v>60</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>50</v>
@@ -40776,7 +40795,7 @@
         <v>150</v>
       </c>
       <c r="H434" s="0" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="J434" s="11">
         <v>46373.125</v>
@@ -40847,13 +40866,13 @@
         <v>60</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>733</v>
       </c>
       <c r="E435" s="0" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F435" s="0" t="s">
         <v>209</v>
@@ -40862,7 +40881,7 @@
         <v>209</v>
       </c>
       <c r="H435" s="0" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="J435" s="11">
         <v>46310.125</v>
@@ -40933,7 +40952,7 @@
         <v>60</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>246</v>
@@ -40948,7 +40967,7 @@
         <v>322</v>
       </c>
       <c r="H436" s="0" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J436" s="11">
         <v>46310.125</v>
@@ -41019,7 +41038,7 @@
         <v>60</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D437" s="0" t="s">
         <v>256</v>
@@ -41034,7 +41053,7 @@
         <v>92</v>
       </c>
       <c r="H437" s="0" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="J437" s="11">
         <v>46310.125</v>
@@ -41105,13 +41124,13 @@
         <v>60</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>256</v>
       </c>
       <c r="E438" s="0" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F438" s="0" t="s">
         <v>168</v>
@@ -41120,7 +41139,7 @@
         <v>168</v>
       </c>
       <c r="H438" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="J438" s="11">
         <v>46310.125</v>
@@ -41194,7 +41213,7 @@
         <v>60</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>246</v>
@@ -41283,13 +41302,13 @@
         <v>60</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="D440" s="0" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="E440" s="0" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F440" s="0" t="s">
         <v>289</v>
@@ -41369,7 +41388,7 @@
         <v>60</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>256</v>
@@ -41384,7 +41403,7 @@
         <v>321</v>
       </c>
       <c r="H441" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J441" s="11">
         <v>46310.125</v>
@@ -41458,7 +41477,7 @@
         <v>60</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>408</v>
@@ -41473,7 +41492,7 @@
         <v>169</v>
       </c>
       <c r="H442" s="0" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="J442" s="11">
         <v>46373.125</v>
@@ -41544,7 +41563,7 @@
         <v>60</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>256</v>
@@ -41630,7 +41649,7 @@
         <v>60</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>256</v>
@@ -41645,7 +41664,7 @@
         <v>53</v>
       </c>
       <c r="H444" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="J444" s="11">
         <v>46310.125</v>
@@ -41716,7 +41735,7 @@
         <v>60</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>408</v>
@@ -41731,7 +41750,7 @@
         <v>322</v>
       </c>
       <c r="H445" s="0" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="J445" s="11">
         <v>46373.125</v>
@@ -41802,7 +41821,7 @@
         <v>60</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>256</v>
@@ -41817,7 +41836,7 @@
         <v>73</v>
       </c>
       <c r="H446" s="0" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="J446" s="11">
         <v>46310.125</v>
@@ -41888,7 +41907,7 @@
         <v>60</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>256</v>
@@ -41903,7 +41922,7 @@
         <v>321</v>
       </c>
       <c r="H447" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="J447" s="11">
         <v>46310.125</v>
@@ -41977,7 +41996,7 @@
         <v>60</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>408</v>
@@ -41992,7 +42011,7 @@
         <v>169</v>
       </c>
       <c r="H448" s="0" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="J448" s="11">
         <v>46373.125</v>
@@ -42063,7 +42082,7 @@
         <v>60</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>256</v>
@@ -42149,7 +42168,7 @@
         <v>60</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>162</v>
@@ -42164,7 +42183,7 @@
         <v>177</v>
       </c>
       <c r="H450" s="0" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="J450" s="11">
         <v>46310.125</v>
@@ -42235,13 +42254,13 @@
         <v>60</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E451" s="0" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F451" s="0" t="s">
         <v>500</v>
@@ -42250,7 +42269,7 @@
         <v>500</v>
       </c>
       <c r="H451" s="0" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="J451" s="11">
         <v>46373.125</v>
@@ -42321,7 +42340,7 @@
         <v>60</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D452" s="0" t="s">
         <v>162</v>
@@ -42336,7 +42355,7 @@
         <v>516</v>
       </c>
       <c r="H452" s="0" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="J452" s="11">
         <v>46310.125</v>
@@ -42407,13 +42426,13 @@
         <v>60</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E453" s="0" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F453" s="0" t="s">
         <v>327</v>
@@ -42422,7 +42441,7 @@
         <v>327</v>
       </c>
       <c r="H453" s="0" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="J453" s="11">
         <v>46310.125</v>
@@ -42496,7 +42515,7 @@
         <v>60</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>162</v>
@@ -42511,7 +42530,7 @@
         <v>327</v>
       </c>
       <c r="H454" s="0" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="J454" s="11"/>
       <c r="K454" s="0" t="s">
@@ -42574,25 +42593,25 @@
     </row>
     <row r="455">
       <c r="A455" s="0" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B455" s="0" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D455" s="0" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E455" s="0" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F455" s="0" t="s">
         <v>295</v>
       </c>
       <c r="G455" s="0" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="J455" s="11">
         <v>46310.125</v>
@@ -42625,7 +42644,7 @@
         <v>44</v>
       </c>
       <c r="AC455" s="0" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="AD455" s="11">
         <v>46203.65469700231</v>
@@ -42657,13 +42676,13 @@
         <v>646</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E456" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F456" s="0" t="s">
         <v>322</v>
@@ -42672,7 +42691,7 @@
         <v>322</v>
       </c>
       <c r="H456" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="J456" s="11">
         <v>46365.125</v>
@@ -42737,19 +42756,19 @@
     </row>
     <row r="457">
       <c r="A457" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B457" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>772</v>
       </c>
       <c r="E457" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F457" s="0" t="s">
         <v>208</v>
@@ -42758,7 +42777,7 @@
         <v>209</v>
       </c>
       <c r="H457" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="J457" s="11">
         <v>46365.125</v>
@@ -42829,13 +42848,13 @@
         <v>34</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D458" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E458" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F458" s="0" t="s">
         <v>84</v>
@@ -42912,7 +42931,7 @@
         <v>34</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>36</v>
@@ -42992,16 +43011,16 @@
         <v>661</v>
       </c>
       <c r="B460" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D460" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E460" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F460" s="0" t="s">
         <v>201</v>
@@ -43037,7 +43056,7 @@
         <v>44</v>
       </c>
       <c r="AC460" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AD460" s="11">
         <v>46209.58030755787</v>
@@ -43069,7 +43088,7 @@
         <v>34</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>122</v>
@@ -43084,7 +43103,7 @@
         <v>73</v>
       </c>
       <c r="H461" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="J461" s="11">
         <v>46387.125</v>
@@ -43155,7 +43174,7 @@
         <v>34</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D462" s="0" t="s">
         <v>122</v>
@@ -43170,7 +43189,7 @@
         <v>73</v>
       </c>
       <c r="H462" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="J462" s="11">
         <v>46326.125</v>
@@ -43241,7 +43260,7 @@
         <v>34</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>50</v>
@@ -43256,7 +43275,7 @@
         <v>321</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="J463" s="11">
         <v>46326.125</v>
@@ -43327,13 +43346,13 @@
         <v>34</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F464" s="0" t="s">
         <v>131</v>
@@ -43413,13 +43432,13 @@
         <v>34</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>180</v>
       </c>
       <c r="E465" s="0" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F465" s="0" t="s">
         <v>149</v>
@@ -43428,7 +43447,7 @@
         <v>149</v>
       </c>
       <c r="H465" s="0" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="J465" s="11">
         <v>46310.125</v>
@@ -43499,13 +43518,13 @@
         <v>60</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D466" s="0" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E466" s="0" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F466" s="0" t="s">
         <v>414</v>
@@ -43514,7 +43533,7 @@
         <v>414</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="J466" s="11">
         <v>46310.125</v>
@@ -43582,7 +43601,7 @@
         <v>60</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>76</v>
@@ -43597,7 +43616,7 @@
         <v>327</v>
       </c>
       <c r="H467" s="0" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="J467" s="11">
         <v>46406.125</v>
@@ -43668,13 +43687,13 @@
         <v>60</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E468" s="0" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F468" s="0" t="s">
         <v>78</v>
@@ -43683,7 +43702,7 @@
         <v>228</v>
       </c>
       <c r="H468" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="J468" s="11">
         <v>46407.125</v>
@@ -43754,7 +43773,7 @@
         <v>60</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>246</v>
@@ -43769,7 +43788,7 @@
         <v>134</v>
       </c>
       <c r="H469" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="J469" s="11">
         <v>46407.125</v>
@@ -43840,7 +43859,7 @@
         <v>60</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D470" s="0" t="s">
         <v>246</v>
@@ -43855,7 +43874,7 @@
         <v>134</v>
       </c>
       <c r="H470" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="J470" s="11">
         <v>46407.125</v>
@@ -43926,7 +43945,7 @@
         <v>60</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D471" s="0" t="s">
         <v>772</v>
@@ -43941,7 +43960,7 @@
         <v>53</v>
       </c>
       <c r="H471" s="0" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="J471" s="11">
         <v>46406.125</v>
@@ -44012,7 +44031,7 @@
         <v>60</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>256</v>
@@ -44027,7 +44046,7 @@
         <v>73</v>
       </c>
       <c r="H472" s="0" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="J472" s="11">
         <v>46373.125</v>
@@ -44098,7 +44117,7 @@
         <v>48</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>50</v>
@@ -44184,13 +44203,13 @@
         <v>223</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D474" s="0" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E474" s="0" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F474" s="0" t="s">
         <v>142</v>
@@ -44199,7 +44218,7 @@
         <v>142</v>
       </c>
       <c r="H474" s="0" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J474" s="11">
         <v>46310.125</v>
@@ -44264,16 +44283,16 @@
         <v>661</v>
       </c>
       <c r="B475" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D475" s="0" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E475" s="0" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F475" s="0" t="s">
         <v>201</v>
@@ -44312,7 +44331,7 @@
         <v>44</v>
       </c>
       <c r="AC475" s="0" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="AD475" s="11">
         <v>46219.55652277778</v>
@@ -44344,7 +44363,7 @@
         <v>48</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>378</v>
@@ -44359,7 +44378,7 @@
         <v>335</v>
       </c>
       <c r="H476" s="0" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="J476" s="11">
         <v>46402.125</v>
@@ -44430,7 +44449,7 @@
         <v>60</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>50</v>
@@ -44445,7 +44464,7 @@
         <v>78</v>
       </c>
       <c r="H477" s="0" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="J477" s="11">
         <v>46346.125</v>
@@ -44516,7 +44535,7 @@
         <v>60</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D478" s="0" t="s">
         <v>246</v>
@@ -44531,7 +44550,7 @@
         <v>52</v>
       </c>
       <c r="H478" s="0" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="J478" s="11">
         <v>46346.125</v>
@@ -44602,7 +44621,7 @@
         <v>60</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D479" s="0" t="s">
         <v>246</v>
@@ -44617,7 +44636,7 @@
         <v>208</v>
       </c>
       <c r="H479" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="J479" s="11">
         <v>46310.125</v>
@@ -44688,7 +44707,7 @@
         <v>60</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D480" s="0" t="s">
         <v>50</v>
@@ -44703,7 +44722,7 @@
         <v>150</v>
       </c>
       <c r="H480" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="J480" s="11">
         <v>46407.125</v>
@@ -44774,7 +44793,7 @@
         <v>60</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D481" s="0" t="s">
         <v>256</v>
@@ -44789,7 +44808,7 @@
         <v>228</v>
       </c>
       <c r="H481" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="J481" s="11">
         <v>46407.125</v>
@@ -44860,7 +44879,7 @@
         <v>60</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>256</v>
@@ -44875,7 +44894,7 @@
         <v>228</v>
       </c>
       <c r="H482" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="J482" s="11">
         <v>46407.125</v>
@@ -44940,13 +44959,13 @@
     </row>
     <row r="483">
       <c r="A483" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B483" s="0" t="s">
         <v>624</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D483" s="0" t="s">
         <v>215</v>
@@ -45026,13 +45045,13 @@
         <v>624</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D484" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="E484" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F484" s="0" t="s">
         <v>437</v>
@@ -45106,13 +45125,13 @@
         <v>48</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D485" s="0" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E485" s="0" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F485" s="0" t="s">
         <v>97</v>
@@ -45192,13 +45211,13 @@
         <v>34</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D486" s="0" t="s">
         <v>76</v>
       </c>
       <c r="E486" s="0" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F486" s="0" t="s">
         <v>38</v>
@@ -45207,7 +45226,7 @@
         <v>38</v>
       </c>
       <c r="H486" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="J486" s="11">
         <v>46310.125</v>
@@ -45278,13 +45297,13 @@
         <v>48</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="E487" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F487" s="0" t="s">
         <v>137</v>
@@ -45361,7 +45380,7 @@
         <v>48</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>341</v>
@@ -45444,7 +45463,7 @@
         <v>48</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D489" s="0" t="s">
         <v>341</v>
@@ -45527,7 +45546,7 @@
         <v>34</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D490" s="0" t="s">
         <v>246</v>
@@ -45542,7 +45561,7 @@
         <v>38</v>
       </c>
       <c r="H490" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="J490" s="11">
         <v>46362.125</v>
@@ -45613,7 +45632,7 @@
         <v>34</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D491" s="0" t="s">
         <v>246</v>
@@ -45628,7 +45647,7 @@
         <v>38</v>
       </c>
       <c r="H491" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="J491" s="11">
         <v>46362.125</v>
@@ -45699,7 +45718,7 @@
         <v>48</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>362</v>
@@ -45782,13 +45801,13 @@
         <v>48</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D493" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E493" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F493" s="0" t="s">
         <v>254</v>
@@ -45865,13 +45884,13 @@
         <v>48</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D494" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="E494" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F494" s="0" t="s">
         <v>131</v>
@@ -45948,13 +45967,13 @@
         <v>48</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D495" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E495" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F495" s="0" t="s">
         <v>289</v>
@@ -46031,13 +46050,13 @@
         <v>60</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D496" s="0" t="s">
         <v>524</v>
       </c>
       <c r="E496" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F496" s="0" t="s">
         <v>104</v>
@@ -46111,19 +46130,19 @@
     </row>
     <row r="497">
       <c r="A497" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B497" s="0" t="s">
         <v>646</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D497" s="0" t="s">
         <v>71</v>
       </c>
       <c r="E497" s="0" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F497" s="0" t="s">
         <v>288</v>
@@ -46132,7 +46151,7 @@
         <v>288</v>
       </c>
       <c r="H497" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="J497" s="11">
         <v>46372.125</v>
@@ -46203,19 +46222,19 @@
         <v>34</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D498" s="0" t="s">
         <v>586</v>
       </c>
       <c r="E498" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F498" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G498" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H498" s="0" t="s">
         <v>202</v>
@@ -46289,19 +46308,19 @@
         <v>34</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D499" s="0" t="s">
         <v>586</v>
       </c>
       <c r="E499" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F499" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="G499" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H499" s="0" t="s">
         <v>202</v>
@@ -46375,7 +46394,7 @@
         <v>223</v>
       </c>
       <c r="C500" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D500" s="0" t="s">
         <v>524</v>
@@ -46452,16 +46471,16 @@
         <v>661</v>
       </c>
       <c r="B501" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C501" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D501" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E501" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F501" s="0" t="s">
         <v>289</v>
@@ -46474,7 +46493,7 @@
         <v>110</v>
       </c>
       <c r="L501" s="0" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="M501" s="0" t="s">
         <v>39</v>
@@ -46495,7 +46514,7 @@
         <v>44</v>
       </c>
       <c r="AC501" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AD501" s="11">
         <v>46301.476280462964</v>
@@ -46510,6 +46529,140 @@
       </c>
       <c r="AI501" s="3"/>
       <c r="AJ501" s="3"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="0" t="s">
+        <v>817</v>
+      </c>
+      <c r="B502" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="C502" s="0" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D502" s="0" t="s">
+        <v>943</v>
+      </c>
+      <c r="E502" s="0" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F502" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="G502" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="J502" s="11"/>
+      <c r="K502" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="L502" s="0" t="s">
+        <v>1079</v>
+      </c>
+      <c r="M502" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="N502" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="O502" s="11">
+        <v>45915.125</v>
+      </c>
+      <c r="Q502" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="T502" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="W502" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z502" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC502" s="0" t="s">
+        <v>855</v>
+      </c>
+      <c r="AD502" s="11">
+        <v>46303.38590450231</v>
+      </c>
+      <c r="AE502" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF502" s="3"/>
+      <c r="AG502" s="3"/>
+      <c r="AH502" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI502" s="3"/>
+      <c r="AJ502" s="3"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="0" t="s">
+        <v>817</v>
+      </c>
+      <c r="B503" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="C503" s="0" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D503" s="0" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E503" s="0" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F503" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="G503" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="J503" s="11"/>
+      <c r="K503" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="L503" s="0" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M503" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="N503" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="O503" s="11">
+        <v>46310.125</v>
+      </c>
+      <c r="Q503" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="T503" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="W503" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z503" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC503" s="0" t="s">
+        <v>855</v>
+      </c>
+      <c r="AD503" s="11">
+        <v>46303.38891412037</v>
+      </c>
+      <c r="AE503" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF503" s="3"/>
+      <c r="AG503" s="3"/>
+      <c r="AH503" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI503" s="3"/>
+      <c r="AJ503" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -46558,28 +46711,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -46587,10 +46740,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>646</v>
@@ -46608,10 +46761,10 @@
         <v>46480.125</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>650</v>
@@ -46619,10 +46772,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>223</v>
@@ -46640,10 +46793,10 @@
         <v>46476.125</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>223</v>
@@ -46651,10 +46804,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>223</v>
@@ -46666,16 +46819,16 @@
         <v>46296</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="G4" s="11">
         <v>46476.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>223</v>
@@ -46683,10 +46836,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>34</v>
@@ -46704,10 +46857,10 @@
         <v>46474.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>203</v>
@@ -46715,10 +46868,10 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>34</v>
@@ -46736,10 +46889,10 @@
         <v>46474.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>203</v>
@@ -46747,10 +46900,10 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>646</v>
@@ -46768,10 +46921,10 @@
         <v>46474.125</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>650</v>
@@ -46779,10 +46932,10 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>646</v>
@@ -46794,16 +46947,16 @@
         <v>46294</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="G8" s="11">
         <v>46474.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>650</v>
@@ -46811,10 +46964,10 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>646</v>
@@ -46832,10 +46985,10 @@
         <v>46474.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>650</v>
@@ -46843,10 +46996,10 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>646</v>
@@ -46858,16 +47011,16 @@
         <v>46294</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="G10" s="11">
         <v>46474.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>650</v>
@@ -46875,10 +47028,10 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>60</v>
@@ -46890,16 +47043,16 @@
         <v>46289</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G11" s="11">
         <v>46469.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>66</v>
@@ -46907,10 +47060,10 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>60</v>
@@ -46928,10 +47081,10 @@
         <v>46469.125</v>
       </c>
       <c r="H12" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I12" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I12" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>66</v>
@@ -46939,10 +47092,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>646</v>
@@ -46960,10 +47113,10 @@
         <v>46455.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>650</v>
@@ -46971,10 +47124,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>646</v>
@@ -46986,16 +47139,16 @@
         <v>46275</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="G14" s="11">
         <v>46455.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>650</v>
@@ -47003,13 +47156,13 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C15" s="0" t="s">
         <v>853</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>852</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>30</v>
@@ -47024,24 +47177,24 @@
         <v>46449.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C16" s="0" t="s">
         <v>853</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>852</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>29</v>
@@ -47050,30 +47203,30 @@
         <v>46269</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="G16" s="11">
         <v>46449.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C17" s="0" t="s">
         <v>853</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>852</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>30</v>
@@ -47088,13 +47241,13 @@
         <v>46268</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="18">
@@ -47102,7 +47255,7 @@
         <v>550</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>34</v>
@@ -47114,19 +47267,19 @@
         <v>46267</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G18" s="11">
         <v>46447.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="19">
@@ -47134,7 +47287,7 @@
         <v>550</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>34</v>
@@ -47152,21 +47305,21 @@
         <v>46447.125</v>
       </c>
       <c r="H19" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I19" s="0" t="s">
         <v>1096</v>
       </c>
-      <c r="I19" s="0" t="s">
-        <v>1089</v>
-      </c>
       <c r="J19" s="0" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>60</v>
@@ -47184,10 +47337,10 @@
         <v>46446.125</v>
       </c>
       <c r="H20" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I20" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I20" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>609</v>
@@ -47195,10 +47348,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>60</v>
@@ -47216,10 +47369,10 @@
         <v>46446.125</v>
       </c>
       <c r="H21" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I21" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I21" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J21" s="0" t="s">
         <v>609</v>
@@ -47230,7 +47383,7 @@
         <v>552</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>48</v>
@@ -47242,27 +47395,27 @@
         <v>46261</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G22" s="11">
         <v>46441.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>34</v>
@@ -47274,16 +47427,16 @@
         <v>46260</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G23" s="11">
         <v>46440.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>203</v>
@@ -47291,10 +47444,10 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>60</v>
@@ -47312,10 +47465,10 @@
         <v>46440.125</v>
       </c>
       <c r="H24" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I24" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I24" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J24" s="0" t="s">
         <v>66</v>
@@ -47323,10 +47476,10 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>34</v>
@@ -47344,10 +47497,10 @@
         <v>46439.125</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>203</v>
@@ -47358,7 +47511,7 @@
         <v>660</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>34</v>
@@ -47376,10 +47529,10 @@
         <v>46439.125</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J26" s="0" t="s">
         <v>203</v>
@@ -47387,10 +47540,10 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>34</v>
@@ -47408,10 +47561,10 @@
         <v>46439.125</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>203</v>
@@ -47422,7 +47575,7 @@
         <v>655</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>60</v>
@@ -47440,10 +47593,10 @@
         <v>46439.125</v>
       </c>
       <c r="H28" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I28" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I28" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>609</v>
@@ -47454,7 +47607,7 @@
         <v>339</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>60</v>
@@ -47472,10 +47625,10 @@
         <v>46439.125</v>
       </c>
       <c r="H29" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I29" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I29" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>66</v>
@@ -47486,7 +47639,7 @@
         <v>471</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>60</v>
@@ -47498,16 +47651,16 @@
         <v>46255</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G30" s="11">
         <v>46435.125</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>66</v>
@@ -47518,7 +47671,7 @@
         <v>471</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>60</v>
@@ -47536,10 +47689,10 @@
         <v>46435.125</v>
       </c>
       <c r="H31" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I31" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I31" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>66</v>
@@ -47550,7 +47703,7 @@
         <v>653</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>60</v>
@@ -47568,10 +47721,10 @@
         <v>46432.125</v>
       </c>
       <c r="H32" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I32" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I32" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>609</v>
@@ -47582,7 +47735,7 @@
         <v>607</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>60</v>
@@ -47600,10 +47753,10 @@
         <v>46432.125</v>
       </c>
       <c r="H33" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I33" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I33" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>609</v>
@@ -47614,7 +47767,7 @@
         <v>606</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>34</v>
@@ -47632,10 +47785,10 @@
         <v>46432.125</v>
       </c>
       <c r="H34" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I34" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I34" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>45</v>
@@ -47643,10 +47796,10 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>34</v>
@@ -47664,10 +47817,10 @@
         <v>46432.125</v>
       </c>
       <c r="H35" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I35" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I35" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>45</v>
@@ -47678,7 +47831,7 @@
         <v>606</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>34</v>
@@ -47690,16 +47843,16 @@
         <v>46252</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G36" s="11">
         <v>46432.125</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>45</v>
@@ -47707,10 +47860,10 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>48</v>
@@ -47722,16 +47875,16 @@
         <v>46251</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G37" s="11">
         <v>46431.125</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>56</v>
@@ -47739,10 +47892,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>48</v>
@@ -47760,10 +47913,10 @@
         <v>46431.125</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J38" s="0" t="s">
         <v>56</v>
@@ -47771,10 +47924,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>48</v>
@@ -47792,10 +47945,10 @@
         <v>46431.125</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J39" s="0" t="s">
         <v>56</v>
@@ -47806,7 +47959,7 @@
         <v>385</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>34</v>
@@ -47824,10 +47977,10 @@
         <v>46429.125</v>
       </c>
       <c r="H40" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I40" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I40" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J40" s="0" t="s">
         <v>45</v>
@@ -47838,7 +47991,7 @@
         <v>387</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>34</v>
@@ -47856,10 +48009,10 @@
         <v>46429.125</v>
       </c>
       <c r="H41" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I41" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I41" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J41" s="0" t="s">
         <v>45</v>
@@ -47870,7 +48023,7 @@
         <v>703</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>34</v>
@@ -47888,10 +48041,10 @@
         <v>46429.125</v>
       </c>
       <c r="H42" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I42" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I42" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J42" s="0" t="s">
         <v>45</v>
@@ -47899,10 +48052,10 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>48</v>
@@ -47914,16 +48067,16 @@
         <v>46249</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G43" s="11">
         <v>46429.125</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J43" s="0" t="s">
         <v>56</v>
@@ -47931,10 +48084,10 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>48</v>
@@ -47946,16 +48099,16 @@
         <v>46249</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G44" s="11">
         <v>46429.125</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J44" s="0" t="s">
         <v>56</v>
@@ -47963,10 +48116,10 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
       <c r="C45" s="0" t="s">
         <v>48</v>
@@ -47984,10 +48137,10 @@
         <v>46429.125</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J45" s="0" t="s">
         <v>56</v>
@@ -47995,10 +48148,10 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>48</v>
@@ -48016,10 +48169,10 @@
         <v>46429.125</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J46" s="0" t="s">
         <v>56</v>
@@ -48027,10 +48180,10 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>48</v>
@@ -48048,10 +48201,10 @@
         <v>46429.125</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J47" s="0" t="s">
         <v>56</v>
@@ -48062,7 +48215,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>34</v>
@@ -48074,16 +48227,16 @@
         <v>46249</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G48" s="11">
         <v>46429.125</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J48" s="0" t="s">
         <v>45</v>
@@ -48094,7 +48247,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C49" s="0" t="s">
         <v>34</v>
@@ -48106,16 +48259,16 @@
         <v>46249</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G49" s="11">
         <v>46429.125</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J49" s="0" t="s">
         <v>45</v>
@@ -48126,7 +48279,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C50" s="0" t="s">
         <v>34</v>
@@ -48144,10 +48297,10 @@
         <v>46429.125</v>
       </c>
       <c r="H50" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I50" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I50" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J50" s="0" t="s">
         <v>45</v>
@@ -48158,7 +48311,7 @@
         <v>35</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C51" s="0" t="s">
         <v>34</v>
@@ -48176,10 +48329,10 @@
         <v>46429.125</v>
       </c>
       <c r="H51" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I51" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I51" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J51" s="0" t="s">
         <v>45</v>
@@ -48190,7 +48343,7 @@
         <v>57</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="C52" s="0" t="s">
         <v>34</v>
@@ -48208,10 +48361,10 @@
         <v>46429.125</v>
       </c>
       <c r="H52" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I52" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I52" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J52" s="0" t="s">
         <v>45</v>
@@ -48222,7 +48375,7 @@
         <v>385</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="C53" s="0" t="s">
         <v>34</v>
@@ -48234,16 +48387,16 @@
         <v>46249</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G53" s="11">
         <v>46429.125</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J53" s="0" t="s">
         <v>45</v>
@@ -48254,7 +48407,7 @@
         <v>387</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="C54" s="0" t="s">
         <v>34</v>
@@ -48266,16 +48419,16 @@
         <v>46249</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G54" s="11">
         <v>46429.125</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J54" s="0" t="s">
         <v>45</v>
@@ -48286,7 +48439,7 @@
         <v>431</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
       <c r="C55" s="0" t="s">
         <v>48</v>
@@ -48298,16 +48451,16 @@
         <v>46249</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G55" s="11">
         <v>46429.125</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J55" s="0" t="s">
         <v>56</v>
@@ -48318,7 +48471,7 @@
         <v>422</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="C56" s="0" t="s">
         <v>48</v>
@@ -48330,16 +48483,16 @@
         <v>46248</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G56" s="11">
         <v>46428.125</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J56" s="0" t="s">
         <v>56</v>
@@ -48350,7 +48503,7 @@
         <v>749</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="C57" s="0" t="s">
         <v>48</v>
@@ -48362,16 +48515,16 @@
         <v>46248</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G57" s="11">
         <v>46428.125</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J57" s="0" t="s">
         <v>56</v>
@@ -48379,10 +48532,10 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
       <c r="C58" s="0" t="s">
         <v>60</v>
@@ -48400,10 +48553,10 @@
         <v>46428.125</v>
       </c>
       <c r="H58" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I58" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I58" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J58" s="0" t="s">
         <v>66</v>
@@ -48414,7 +48567,7 @@
         <v>139</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="C59" s="0" t="s">
         <v>60</v>
@@ -48426,16 +48579,16 @@
         <v>46248</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G59" s="11">
         <v>46428.125</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J59" s="0" t="s">
         <v>66</v>
@@ -48446,7 +48599,7 @@
         <v>139</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="C60" s="0" t="s">
         <v>60</v>
@@ -48464,10 +48617,10 @@
         <v>46428.125</v>
       </c>
       <c r="H60" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I60" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I60" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J60" s="0" t="s">
         <v>66</v>
@@ -48478,7 +48631,7 @@
         <v>416</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="C61" s="0" t="s">
         <v>60</v>
@@ -48496,10 +48649,10 @@
         <v>46428.125</v>
       </c>
       <c r="H61" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I61" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I61" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J61" s="0" t="s">
         <v>66</v>
@@ -48510,7 +48663,7 @@
         <v>749</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="C62" s="0" t="s">
         <v>48</v>
@@ -48528,10 +48681,10 @@
         <v>46428.125</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J62" s="0" t="s">
         <v>56</v>
@@ -48542,7 +48695,7 @@
         <v>422</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="C63" s="0" t="s">
         <v>48</v>
@@ -48560,10 +48713,10 @@
         <v>46428.125</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J63" s="0" t="s">
         <v>56</v>
@@ -48574,7 +48727,7 @@
         <v>431</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
       <c r="C64" s="0" t="s">
         <v>48</v>
@@ -48592,10 +48745,10 @@
         <v>46428.125</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J64" s="0" t="s">
         <v>56</v>
@@ -48603,10 +48756,10 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
       <c r="C65" s="0" t="s">
         <v>48</v>
@@ -48618,16 +48771,16 @@
         <v>46248</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G65" s="11">
         <v>46428.125</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J65" s="0" t="s">
         <v>56</v>
@@ -48638,7 +48791,7 @@
         <v>343</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
       <c r="C66" s="0" t="s">
         <v>34</v>
@@ -48650,16 +48803,16 @@
         <v>46248</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G66" s="11">
         <v>46428.125</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J66" s="0" t="s">
         <v>45</v>
@@ -48667,10 +48820,10 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
       <c r="C67" s="0" t="s">
         <v>48</v>
@@ -48688,10 +48841,10 @@
         <v>46428.125</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J67" s="0" t="s">
         <v>56</v>
@@ -48699,10 +48852,10 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>1134</v>
+        <v>1141</v>
       </c>
       <c r="C68" s="0" t="s">
         <v>48</v>
@@ -48720,10 +48873,10 @@
         <v>46428.125</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J68" s="0" t="s">
         <v>56</v>
@@ -48734,7 +48887,7 @@
         <v>542</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
       <c r="C69" s="0" t="s">
         <v>34</v>
@@ -48746,16 +48899,16 @@
         <v>46247</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G69" s="11">
         <v>46427.125</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J69" s="0" t="s">
         <v>45</v>
@@ -48763,10 +48916,10 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>1136</v>
+        <v>1143</v>
       </c>
       <c r="C70" s="0" t="s">
         <v>60</v>
@@ -48784,10 +48937,10 @@
         <v>46427.125</v>
       </c>
       <c r="H70" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I70" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I70" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J70" s="0" t="s">
         <v>66</v>
@@ -48798,7 +48951,7 @@
         <v>542</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
       <c r="C71" s="0" t="s">
         <v>34</v>
@@ -48816,10 +48969,10 @@
         <v>46427.125</v>
       </c>
       <c r="H71" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I71" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I71" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J71" s="0" t="s">
         <v>45</v>
@@ -48827,10 +48980,10 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="C72" s="0" t="s">
         <v>34</v>
@@ -48848,10 +49001,10 @@
         <v>46427.125</v>
       </c>
       <c r="H72" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I72" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I72" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J72" s="0" t="s">
         <v>45</v>
@@ -48862,7 +49015,7 @@
         <v>420</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
       <c r="C73" s="0" t="s">
         <v>34</v>
@@ -48880,10 +49033,10 @@
         <v>46427.125</v>
       </c>
       <c r="H73" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I73" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I73" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J73" s="0" t="s">
         <v>45</v>
@@ -48894,7 +49047,7 @@
         <v>309</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>1138</v>
+        <v>1145</v>
       </c>
       <c r="C74" s="0" t="s">
         <v>34</v>
@@ -48912,10 +49065,10 @@
         <v>46427.125</v>
       </c>
       <c r="H74" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I74" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I74" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>45</v>
@@ -48926,7 +49079,7 @@
         <v>420</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
       <c r="C75" s="0" t="s">
         <v>34</v>
@@ -48938,16 +49091,16 @@
         <v>46247</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G75" s="11">
         <v>46427.125</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J75" s="0" t="s">
         <v>45</v>
@@ -48958,7 +49111,7 @@
         <v>761</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="C76" s="0" t="s">
         <v>48</v>
@@ -48970,16 +49123,16 @@
         <v>46247</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G76" s="11">
         <v>46427.125</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>56</v>
@@ -48990,7 +49143,7 @@
         <v>762</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="C77" s="0" t="s">
         <v>48</v>
@@ -49002,16 +49155,16 @@
         <v>46247</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G77" s="11">
         <v>46427.125</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>56</v>
@@ -49022,7 +49175,7 @@
         <v>676</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="C78" s="0" t="s">
         <v>60</v>
@@ -49034,16 +49187,16 @@
         <v>46246</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G78" s="11">
         <v>46426.125</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>66</v>
@@ -49054,7 +49207,7 @@
         <v>547</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>1142</v>
+        <v>1149</v>
       </c>
       <c r="C79" s="0" t="s">
         <v>34</v>
@@ -49066,19 +49219,19 @@
         <v>46246</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G79" s="11">
         <v>46426.125</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J79" s="0" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="80">
@@ -49086,7 +49239,7 @@
         <v>676</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="C80" s="0" t="s">
         <v>60</v>
@@ -49104,10 +49257,10 @@
         <v>46426.125</v>
       </c>
       <c r="H80" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I80" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I80" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J80" s="0" t="s">
         <v>66</v>
@@ -49118,7 +49271,7 @@
         <v>388</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="C81" s="0" t="s">
         <v>48</v>
@@ -49130,16 +49283,16 @@
         <v>46246</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G81" s="11">
         <v>46426.125</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J81" s="0" t="s">
         <v>56</v>
@@ -49150,7 +49303,7 @@
         <v>389</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="C82" s="0" t="s">
         <v>48</v>
@@ -49162,16 +49315,16 @@
         <v>46246</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G82" s="11">
         <v>46426.125</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J82" s="0" t="s">
         <v>56</v>
@@ -49182,7 +49335,7 @@
         <v>343</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
       <c r="C83" s="0" t="s">
         <v>34</v>
@@ -49200,10 +49353,10 @@
         <v>46426.125</v>
       </c>
       <c r="H83" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I83" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I83" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J83" s="0" t="s">
         <v>45</v>
@@ -49214,7 +49367,7 @@
         <v>313</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="C84" s="0" t="s">
         <v>34</v>
@@ -49232,10 +49385,10 @@
         <v>46426.125</v>
       </c>
       <c r="H84" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I84" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I84" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J84" s="0" t="s">
         <v>45</v>
@@ -49246,7 +49399,7 @@
         <v>547</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>1142</v>
+        <v>1149</v>
       </c>
       <c r="C85" s="0" t="s">
         <v>34</v>
@@ -49264,13 +49417,13 @@
         <v>46426.125</v>
       </c>
       <c r="H85" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I85" s="0" t="s">
         <v>1096</v>
       </c>
-      <c r="I85" s="0" t="s">
-        <v>1089</v>
-      </c>
       <c r="J85" s="0" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="86">
@@ -49278,7 +49431,7 @@
         <v>544</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="C86" s="0" t="s">
         <v>34</v>
@@ -49296,10 +49449,10 @@
         <v>46426.125</v>
       </c>
       <c r="H86" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I86" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I86" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J86" s="0" t="s">
         <v>45</v>
@@ -49310,7 +49463,7 @@
         <v>388</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="C87" s="0" t="s">
         <v>48</v>
@@ -49328,10 +49481,10 @@
         <v>46426.125</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J87" s="0" t="s">
         <v>56</v>
@@ -49342,7 +49495,7 @@
         <v>389</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="C88" s="0" t="s">
         <v>48</v>
@@ -49360,10 +49513,10 @@
         <v>46426.125</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J88" s="0" t="s">
         <v>56</v>
@@ -49374,7 +49527,7 @@
         <v>49</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="C89" s="0" t="s">
         <v>48</v>
@@ -49392,10 +49545,10 @@
         <v>46426.125</v>
       </c>
       <c r="H89" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J89" s="0" t="s">
         <v>56</v>
@@ -49406,7 +49559,7 @@
         <v>255</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="C90" s="0" t="s">
         <v>60</v>
@@ -49424,10 +49577,10 @@
         <v>46426.125</v>
       </c>
       <c r="H90" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I90" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I90" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J90" s="0" t="s">
         <v>66</v>
@@ -49435,10 +49588,10 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B91" s="0" t="s">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="C91" s="0" t="s">
         <v>60</v>
@@ -49456,10 +49609,10 @@
         <v>46426.125</v>
       </c>
       <c r="H91" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I91" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I91" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J91" s="0" t="s">
         <v>66</v>
@@ -49467,10 +49620,10 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="C92" s="0" t="s">
         <v>60</v>
@@ -49488,10 +49641,10 @@
         <v>46426.125</v>
       </c>
       <c r="H92" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I92" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I92" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J92" s="0" t="s">
         <v>66</v>
@@ -49499,10 +49652,10 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="C93" s="0" t="s">
         <v>60</v>
@@ -49520,10 +49673,10 @@
         <v>46426.125</v>
       </c>
       <c r="H93" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I93" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I93" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J93" s="0" t="s">
         <v>66</v>
@@ -49531,10 +49684,10 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="C94" s="0" t="s">
         <v>60</v>
@@ -49552,10 +49705,10 @@
         <v>46426.125</v>
       </c>
       <c r="H94" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I94" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I94" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J94" s="0" t="s">
         <v>66</v>
@@ -49566,7 +49719,7 @@
         <v>762</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="C95" s="0" t="s">
         <v>48</v>
@@ -49584,10 +49737,10 @@
         <v>46426.125</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J95" s="0" t="s">
         <v>56</v>
@@ -49598,7 +49751,7 @@
         <v>761</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="C96" s="0" t="s">
         <v>48</v>
@@ -49616,10 +49769,10 @@
         <v>46426.125</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J96" s="0" t="s">
         <v>56</v>
@@ -49630,7 +49783,7 @@
         <v>379</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
       <c r="C97" s="0" t="s">
         <v>48</v>
@@ -49648,10 +49801,10 @@
         <v>46426.125</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J97" s="0" t="s">
         <v>56</v>
@@ -49662,7 +49815,7 @@
         <v>305</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>1150</v>
+        <v>1157</v>
       </c>
       <c r="C98" s="0" t="s">
         <v>48</v>
@@ -49674,16 +49827,16 @@
         <v>46245</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G98" s="11">
         <v>46425.125</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J98" s="0" t="s">
         <v>56</v>
@@ -49694,7 +49847,7 @@
         <v>307</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="C99" s="0" t="s">
         <v>48</v>
@@ -49706,16 +49859,16 @@
         <v>46245</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G99" s="11">
         <v>46425.125</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J99" s="0" t="s">
         <v>56</v>
@@ -49726,7 +49879,7 @@
         <v>568</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>1152</v>
+        <v>1159</v>
       </c>
       <c r="C100" s="0" t="s">
         <v>48</v>
@@ -49744,10 +49897,10 @@
         <v>46425.125</v>
       </c>
       <c r="H100" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J100" s="0" t="s">
         <v>56</v>
@@ -49758,7 +49911,7 @@
         <v>305</v>
       </c>
       <c r="B101" s="0" t="s">
-        <v>1150</v>
+        <v>1157</v>
       </c>
       <c r="C101" s="0" t="s">
         <v>48</v>
@@ -49776,10 +49929,10 @@
         <v>46425.125</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J101" s="0" t="s">
         <v>56</v>
@@ -49790,7 +49943,7 @@
         <v>307</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="C102" s="0" t="s">
         <v>48</v>
@@ -49808,10 +49961,10 @@
         <v>46425.125</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J102" s="0" t="s">
         <v>56</v>
@@ -49822,7 +49975,7 @@
         <v>599</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="C103" s="0" t="s">
         <v>48</v>
@@ -49834,16 +49987,16 @@
         <v>46245</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G103" s="11">
         <v>46425.125</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J103" s="0" t="s">
         <v>56</v>
@@ -49854,7 +50007,7 @@
         <v>599</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="C104" s="0" t="s">
         <v>48</v>
@@ -49866,16 +50019,16 @@
         <v>46245</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G104" s="11">
         <v>46425.125</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J104" s="0" t="s">
         <v>56</v>
@@ -49886,7 +50039,7 @@
         <v>790</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
       <c r="C105" s="0" t="s">
         <v>48</v>
@@ -49898,19 +50051,19 @@
         <v>46245</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G105" s="11">
         <v>46425.125</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J105" s="0" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="106">
@@ -49918,7 +50071,7 @@
         <v>599</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="C106" s="0" t="s">
         <v>48</v>
@@ -49936,10 +50089,10 @@
         <v>46425.125</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J106" s="0" t="s">
         <v>56</v>
@@ -49950,7 +50103,7 @@
         <v>790</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
       <c r="C107" s="0" t="s">
         <v>48</v>
@@ -49968,13 +50121,13 @@
         <v>46425.125</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J107" s="0" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="108">
@@ -49982,7 +50135,7 @@
         <v>116</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>34</v>
@@ -49994,16 +50147,16 @@
         <v>46245</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G108" s="11">
         <v>46425.125</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J108" s="0" t="s">
         <v>45</v>
@@ -50014,7 +50167,7 @@
         <v>114</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="C109" s="0" t="s">
         <v>34</v>
@@ -50026,16 +50179,16 @@
         <v>46245</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G109" s="11">
         <v>46425.125</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J109" s="0" t="s">
         <v>45</v>
@@ -50046,7 +50199,7 @@
         <v>771</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="C110" s="0" t="s">
         <v>48</v>
@@ -50058,16 +50211,16 @@
         <v>46245</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G110" s="11">
         <v>46425.125</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J110" s="0" t="s">
         <v>56</v>
@@ -50078,7 +50231,7 @@
         <v>775</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="C111" s="0" t="s">
         <v>48</v>
@@ -50090,16 +50243,16 @@
         <v>46245</v>
       </c>
       <c r="F111" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G111" s="11">
         <v>46425.125</v>
       </c>
       <c r="H111" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J111" s="0" t="s">
         <v>56</v>
@@ -50107,10 +50260,10 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C112" s="0" t="s">
         <v>34</v>
@@ -50122,16 +50275,16 @@
         <v>46245</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G112" s="11">
         <v>46425.125</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J112" s="0" t="s">
         <v>45</v>
@@ -50139,10 +50292,10 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>34</v>
@@ -50154,16 +50307,16 @@
         <v>46245</v>
       </c>
       <c r="F113" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G113" s="11">
         <v>46425.125</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J113" s="0" t="s">
         <v>45</v>
@@ -50174,7 +50327,7 @@
         <v>117</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="C114" s="0" t="s">
         <v>34</v>
@@ -50192,10 +50345,10 @@
         <v>46425.125</v>
       </c>
       <c r="H114" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I114" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I114" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J114" s="0" t="s">
         <v>45</v>
@@ -50206,7 +50359,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="C115" s="0" t="s">
         <v>34</v>
@@ -50224,10 +50377,10 @@
         <v>46425.125</v>
       </c>
       <c r="H115" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I115" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I115" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J115" s="0" t="s">
         <v>45</v>
@@ -50238,7 +50391,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="C116" s="0" t="s">
         <v>34</v>
@@ -50256,10 +50409,10 @@
         <v>46425.125</v>
       </c>
       <c r="H116" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I116" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I116" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J116" s="0" t="s">
         <v>45</v>
@@ -50267,10 +50420,10 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="C117" s="0" t="s">
         <v>34</v>
@@ -50288,10 +50441,10 @@
         <v>46425.125</v>
       </c>
       <c r="H117" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I117" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I117" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J117" s="0" t="s">
         <v>45</v>
@@ -50299,10 +50452,10 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C118" s="0" t="s">
         <v>34</v>
@@ -50320,10 +50473,10 @@
         <v>46425.125</v>
       </c>
       <c r="H118" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I118" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I118" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J118" s="0" t="s">
         <v>45</v>
@@ -50331,10 +50484,10 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C119" s="0" t="s">
         <v>34</v>
@@ -50352,10 +50505,10 @@
         <v>46425.125</v>
       </c>
       <c r="H119" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I119" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I119" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J119" s="0" t="s">
         <v>45</v>
@@ -50363,10 +50516,10 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="C120" s="0" t="s">
         <v>60</v>
@@ -50378,16 +50531,16 @@
         <v>46244</v>
       </c>
       <c r="F120" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G120" s="11">
         <v>46424.125</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J120" s="0" t="s">
         <v>66</v>
@@ -50395,10 +50548,10 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="C121" s="0" t="s">
         <v>60</v>
@@ -50410,16 +50563,16 @@
         <v>46244</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G121" s="11">
         <v>46424.125</v>
       </c>
       <c r="H121" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J121" s="0" t="s">
         <v>66</v>
@@ -50430,7 +50583,7 @@
         <v>780</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="C122" s="0" t="s">
         <v>60</v>
@@ -50442,16 +50595,16 @@
         <v>46244</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G122" s="11">
         <v>46424.125</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J122" s="0" t="s">
         <v>66</v>
@@ -50462,7 +50615,7 @@
         <v>778</v>
       </c>
       <c r="B123" s="0" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="C123" s="0" t="s">
         <v>60</v>
@@ -50474,16 +50627,16 @@
         <v>46244</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G123" s="11">
         <v>46424.125</v>
       </c>
       <c r="H123" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J123" s="0" t="s">
         <v>66</v>
@@ -50494,7 +50647,7 @@
         <v>211</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>1159</v>
+        <v>1166</v>
       </c>
       <c r="C124" s="0" t="s">
         <v>60</v>
@@ -50512,10 +50665,10 @@
         <v>46424.125</v>
       </c>
       <c r="H124" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I124" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I124" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J124" s="0" t="s">
         <v>66</v>
@@ -50523,10 +50676,10 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="C125" s="0" t="s">
         <v>60</v>
@@ -50544,10 +50697,10 @@
         <v>46424.125</v>
       </c>
       <c r="H125" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I125" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I125" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J125" s="0" t="s">
         <v>66</v>
@@ -50555,10 +50708,10 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="C126" s="0" t="s">
         <v>60</v>
@@ -50576,10 +50729,10 @@
         <v>46424.125</v>
       </c>
       <c r="H126" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I126" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I126" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J126" s="0" t="s">
         <v>66</v>
@@ -50590,7 +50743,7 @@
         <v>133</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C127" s="0" t="s">
         <v>34</v>
@@ -50602,16 +50755,16 @@
         <v>46244</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G127" s="11">
         <v>46424.125</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J127" s="0" t="s">
         <v>45</v>
@@ -50619,10 +50772,10 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>1160</v>
+        <v>1167</v>
       </c>
       <c r="C128" s="0" t="s">
         <v>60</v>
@@ -50640,10 +50793,10 @@
         <v>46424.125</v>
       </c>
       <c r="H128" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I128" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I128" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J128" s="0" t="s">
         <v>66</v>
@@ -50654,7 +50807,7 @@
         <v>778</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="C129" s="0" t="s">
         <v>60</v>
@@ -50672,10 +50825,10 @@
         <v>46424.125</v>
       </c>
       <c r="H129" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I129" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I129" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J129" s="0" t="s">
         <v>66</v>
@@ -50686,7 +50839,7 @@
         <v>780</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="C130" s="0" t="s">
         <v>60</v>
@@ -50704,10 +50857,10 @@
         <v>46424.125</v>
       </c>
       <c r="H130" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I130" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I130" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J130" s="0" t="s">
         <v>66</v>
@@ -50718,7 +50871,7 @@
         <v>412</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="C131" s="0" t="s">
         <v>48</v>
@@ -50730,16 +50883,16 @@
         <v>46244</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G131" s="11">
         <v>46424.125</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J131" s="0" t="s">
         <v>56</v>
@@ -50750,7 +50903,7 @@
         <v>722</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="C132" s="0" t="s">
         <v>60</v>
@@ -50762,16 +50915,16 @@
         <v>46244</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G132" s="11">
         <v>46424.125</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J132" s="0" t="s">
         <v>66</v>
@@ -50782,7 +50935,7 @@
         <v>734</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="C133" s="0" t="s">
         <v>60</v>
@@ -50794,16 +50947,16 @@
         <v>46244</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G133" s="11">
         <v>46424.125</v>
       </c>
       <c r="H133" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J133" s="0" t="s">
         <v>66</v>
@@ -50814,7 +50967,7 @@
         <v>90</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="C134" s="0" t="s">
         <v>34</v>
@@ -50832,10 +50985,10 @@
         <v>46424.125</v>
       </c>
       <c r="H134" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I134" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I134" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J134" s="0" t="s">
         <v>45</v>
@@ -50846,7 +50999,7 @@
         <v>591</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C135" s="0" t="s">
         <v>34</v>
@@ -50864,10 +51017,10 @@
         <v>46424.125</v>
       </c>
       <c r="H135" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I135" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I135" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J135" s="0" t="s">
         <v>45</v>
@@ -50878,7 +51031,7 @@
         <v>412</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="C136" s="0" t="s">
         <v>48</v>
@@ -50896,10 +51049,10 @@
         <v>46424.125</v>
       </c>
       <c r="H136" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I136" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I136" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J136" s="0" t="s">
         <v>56</v>
@@ -50910,7 +51063,7 @@
         <v>413</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="C137" s="0" t="s">
         <v>48</v>
@@ -50928,10 +51081,10 @@
         <v>46424.125</v>
       </c>
       <c r="H137" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I137" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I137" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J137" s="0" t="s">
         <v>56</v>
@@ -50942,7 +51095,7 @@
         <v>61</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>1162</v>
+        <v>1169</v>
       </c>
       <c r="C138" s="0" t="s">
         <v>60</v>
@@ -50960,10 +51113,10 @@
         <v>46424.125</v>
       </c>
       <c r="H138" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I138" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I138" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J138" s="0" t="s">
         <v>66</v>
@@ -50974,7 +51127,7 @@
         <v>734</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="C139" s="0" t="s">
         <v>60</v>
@@ -50992,10 +51145,10 @@
         <v>46424.125</v>
       </c>
       <c r="H139" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I139" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I139" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J139" s="0" t="s">
         <v>66</v>
@@ -51006,7 +51159,7 @@
         <v>722</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="C140" s="0" t="s">
         <v>60</v>
@@ -51024,10 +51177,10 @@
         <v>46424.125</v>
       </c>
       <c r="H140" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I140" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I140" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J140" s="0" t="s">
         <v>66</v>
@@ -51038,7 +51191,7 @@
         <v>133</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="C141" s="0" t="s">
         <v>34</v>
@@ -51056,10 +51209,10 @@
         <v>46424.125</v>
       </c>
       <c r="H141" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I141" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I141" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J141" s="0" t="s">
         <v>45</v>
@@ -51070,7 +51223,7 @@
         <v>136</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="C142" s="0" t="s">
         <v>34</v>
@@ -51088,10 +51241,10 @@
         <v>46424.125</v>
       </c>
       <c r="H142" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I142" s="0" t="s">
         <v>1096</v>
-      </c>
-      <c r="I142" s="0" t="s">
-        <v>1089</v>
       </c>
       <c r="J142" s="0" t="s">
         <v>45</v>
@@ -51102,7 +51255,7 @@
         <v>210</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
       <c r="C143" s="0" t="s">
         <v>48</v>
@@ -51114,16 +51267,16 @@
         <v>46244</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="G143" s="11">
         <v>46424.125</v>
       </c>
       <c r="H143" s="0" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="J143" s="0" t="s">
         <v>56</v>
@@ -51134,7 +51287,7 @@
         <v>147</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>1164</v>
+        <v>1171</v>
       </c>
       <c r="C144" s="0" t="s">
         <v>48</v>
@@ -51152,10 +51305,10 @@
         <v>46424.125</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J144" s="0" t="s">
         <v>56</v>
@@ -51166,7 +51319,7 @@
         <v>210</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
       <c r="C145" s="0" t="s">
         <v>48</v>
@@ -51184,10 +51337,10 @@
         <v>46424.125</v>
       </c>
       <c r="H145" s="0" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="J145" s="0" t="s">
         <v>56</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -642,6 +642,9 @@
     <t>EUC9I40</t>
   </si>
   <si>
+    <t>Documento ConsultaCRLV vencendo</t>
+  </si>
+  <si>
     <t>PRZ7999</t>
   </si>
   <si>
@@ -903,9 +906,6 @@
     <t>SR/IMPERIAL GR000227T0 1</t>
   </si>
   <si>
-    <t>Documento ConsultaCRLV vencendo</t>
-  </si>
-  <si>
     <t>MILHO | ITUM ARMAZENS GERAIS E SERVIÇOS LTDA, TOMATE | ITUM ARMAZENS GERAIS E SERVIÇOS LTDA</t>
   </si>
   <si>
@@ -2550,6 +2550,9 @@
     <t>AVV6018</t>
   </si>
   <si>
+    <t>Inspeções Checklist de Segurança SESMT a vencer / Documento CRLV vencendo</t>
+  </si>
+  <si>
     <t>BDV6I85</t>
   </si>
   <si>
@@ -3400,9 +3403,6 @@
   </si>
   <si>
     <t>VOLVO / FH 460 6X2T</t>
-  </si>
-  <si>
-    <t>M.BENZ/L 1113 / M.BENZ/L 1113</t>
   </si>
 </sst>
 </file>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46308.65539659722</v>
+        <v>46309.34970878472</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -7986,10 +7986,10 @@
         <v>46338.125</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>39</v>
+        <v>209</v>
       </c>
       <c r="M52" s="0" t="s">
         <v>39</v>
@@ -8051,7 +8051,7 @@
         <v>34</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D53" s="0" t="s">
         <v>50</v>
@@ -8060,10 +8060,10 @@
         <v>106</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H53" s="0" t="s">
         <v>39</v>
@@ -8137,7 +8137,7 @@
         <v>48</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D54" s="0" t="s">
         <v>74</v>
@@ -8223,13 +8223,13 @@
         <v>60</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D55" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F55" s="0" t="s">
         <v>52</v>
@@ -8238,7 +8238,7 @@
         <v>52</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J55" s="11"/>
       <c r="K55" s="0" t="s">
@@ -8307,13 +8307,13 @@
         <v>48</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F56" s="0" t="s">
         <v>139</v>
@@ -8393,7 +8393,7 @@
         <v>48</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>164</v>
@@ -8408,7 +8408,7 @@
         <v>170</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J57" s="11">
         <v>46407.125</v>
@@ -8479,13 +8479,13 @@
         <v>60</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F58" s="0" t="s">
         <v>133</v>
@@ -8494,7 +8494,7 @@
         <v>133</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J58" s="11">
         <v>46395.125</v>
@@ -8562,19 +8562,19 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F59" s="0" t="s">
         <v>52</v>
@@ -8619,7 +8619,7 @@
         <v>43</v>
       </c>
       <c r="AC59" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD59" s="11">
         <v>45435.49804712963</v>
@@ -8651,7 +8651,7 @@
         <v>60</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D60" s="0" t="s">
         <v>50</v>
@@ -8660,13 +8660,13 @@
         <v>167</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G60" s="0" t="s">
         <v>151</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J60" s="11">
         <v>46373.125</v>
@@ -8737,13 +8737,13 @@
         <v>60</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D61" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>52</v>
@@ -8752,7 +8752,7 @@
         <v>53</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J61" s="11">
         <v>46356.125</v>
@@ -8826,13 +8826,13 @@
         <v>48</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F62" s="0" t="s">
         <v>144</v>
@@ -8912,13 +8912,13 @@
         <v>60</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>52</v>
@@ -8927,7 +8927,7 @@
         <v>52</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J63" s="11">
         <v>46373.125</v>
@@ -8992,28 +8992,28 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J64" s="11">
         <v>46406.125</v>
@@ -9049,7 +9049,7 @@
         <v>43</v>
       </c>
       <c r="AC64" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD64" s="11">
         <v>45435.49804712963</v>
@@ -9075,19 +9075,19 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>95</v>
@@ -9096,7 +9096,7 @@
         <v>38</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J65" s="11">
         <v>46406.125</v>
@@ -9132,7 +9132,7 @@
         <v>44</v>
       </c>
       <c r="AC65" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD65" s="11">
         <v>45435.49804712963</v>
@@ -9164,10 +9164,10 @@
         <v>60</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E66" s="0" t="s">
         <v>37</v>
@@ -9179,7 +9179,7 @@
         <v>64</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J66" s="11">
         <v>46356.125</v>
@@ -9253,13 +9253,13 @@
         <v>60</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D67" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F67" s="0" t="s">
         <v>64</v>
@@ -9268,7 +9268,7 @@
         <v>64</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J67" s="11">
         <v>46356.125</v>
@@ -9342,10 +9342,10 @@
         <v>60</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E68" s="0" t="s">
         <v>37</v>
@@ -9357,7 +9357,7 @@
         <v>139</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J68" s="11">
         <v>46373.125</v>
@@ -9428,22 +9428,22 @@
         <v>60</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D69" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J69" s="11">
         <v>46310.125</v>
@@ -9514,22 +9514,22 @@
         <v>60</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J70" s="11">
         <v>46310.125</v>
@@ -9603,13 +9603,13 @@
         <v>60</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F71" s="0" t="s">
         <v>151</v>
@@ -9618,7 +9618,7 @@
         <v>151</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J71" s="11">
         <v>46310.125</v>
@@ -9692,13 +9692,13 @@
         <v>34</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F72" s="0" t="s">
         <v>95</v>
@@ -9707,14 +9707,14 @@
         <v>95</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J72" s="11"/>
       <c r="K72" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M72" s="0" t="s">
         <v>39</v>
@@ -9776,13 +9776,13 @@
         <v>34</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>95</v>
@@ -9791,14 +9791,14 @@
         <v>95</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J73" s="11"/>
       <c r="K73" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M73" s="0" t="s">
         <v>39</v>
@@ -9860,7 +9860,7 @@
         <v>34</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D74" s="0" t="s">
         <v>50</v>
@@ -9875,7 +9875,7 @@
         <v>133</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J74" s="11"/>
       <c r="K74" s="0" t="s">
@@ -9944,13 +9944,13 @@
         <v>48</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F75" s="0" t="s">
         <v>151</v>
@@ -9959,7 +9959,7 @@
         <v>151</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J75" s="11">
         <v>46417.125</v>
@@ -10030,13 +10030,13 @@
         <v>48</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F76" s="0" t="s">
         <v>151</v>
@@ -10045,7 +10045,7 @@
         <v>151</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J76" s="11">
         <v>46417.125</v>
@@ -10116,7 +10116,7 @@
         <v>48</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>50</v>
@@ -10131,7 +10131,7 @@
         <v>151</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J77" s="11">
         <v>46417.125</v>
@@ -10202,13 +10202,13 @@
         <v>60</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F78" s="0" t="s">
         <v>171</v>
@@ -10217,7 +10217,7 @@
         <v>171</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J78" s="11">
         <v>46373.125</v>
@@ -10288,13 +10288,13 @@
         <v>60</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F79" s="0" t="s">
         <v>171</v>
@@ -10303,7 +10303,7 @@
         <v>171</v>
       </c>
       <c r="H79" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J79" s="11">
         <v>46373.125</v>
@@ -10374,10 +10374,10 @@
         <v>60</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E80" s="0" t="s">
         <v>37</v>
@@ -10389,7 +10389,7 @@
         <v>76</v>
       </c>
       <c r="H80" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J80" s="11">
         <v>46310.125</v>
@@ -10460,10 +10460,10 @@
         <v>60</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E81" s="0" t="s">
         <v>37</v>
@@ -10475,7 +10475,7 @@
         <v>76</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J81" s="11">
         <v>46310.125</v>
@@ -10546,13 +10546,13 @@
         <v>60</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D82" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F82" s="0" t="s">
         <v>38</v>
@@ -10561,7 +10561,7 @@
         <v>76</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J82" s="11">
         <v>46310.125</v>
@@ -10632,13 +10632,13 @@
         <v>34</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F83" s="0" t="s">
         <v>95</v>
@@ -10647,7 +10647,7 @@
         <v>95</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J83" s="11">
         <v>46380.125</v>
@@ -10718,13 +10718,13 @@
         <v>34</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F84" s="0" t="s">
         <v>95</v>
@@ -10733,7 +10733,7 @@
         <v>95</v>
       </c>
       <c r="H84" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J84" s="11">
         <v>46380.125</v>
@@ -10804,13 +10804,13 @@
         <v>60</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F85" s="0" t="s">
         <v>76</v>
@@ -10819,7 +10819,7 @@
         <v>64</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J85" s="11">
         <v>46356.125</v>
@@ -10893,13 +10893,13 @@
         <v>60</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F86" s="0" t="s">
         <v>76</v>
@@ -10908,7 +10908,7 @@
         <v>64</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J86" s="11">
         <v>46356.125</v>
@@ -10982,13 +10982,13 @@
         <v>60</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D87" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F87" s="0" t="s">
         <v>76</v>
@@ -10997,7 +10997,7 @@
         <v>76</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J87" s="11">
         <v>46356.125</v>
@@ -11071,19 +11071,19 @@
         <v>48</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F88" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H88" s="0" t="s">
         <v>39</v>
@@ -11125,7 +11125,7 @@
         <v>44</v>
       </c>
       <c r="AC88" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AD88" s="11">
         <v>45436.4303603125</v>
@@ -11157,13 +11157,13 @@
         <v>48</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F89" s="0" t="s">
         <v>203</v>
@@ -11181,7 +11181,7 @@
         <v>40</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>296</v>
+        <v>209</v>
       </c>
       <c r="M89" s="0" t="s">
         <v>39</v>
@@ -11246,13 +11246,13 @@
         <v>298</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F90" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G90" s="0" t="s">
         <v>299</v>
@@ -11297,7 +11297,7 @@
         <v>44</v>
       </c>
       <c r="AC90" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AD90" s="11">
         <v>45436.4303603125</v>
@@ -11332,10 +11332,10 @@
         <v>300</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F91" s="0" t="s">
         <v>203</v>
@@ -11418,16 +11418,16 @@
         <v>301</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H92" s="0" t="s">
         <v>39</v>
@@ -11469,7 +11469,7 @@
         <v>44</v>
       </c>
       <c r="AC92" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AD92" s="11">
         <v>45436.4303603125</v>
@@ -12198,10 +12198,10 @@
         <v>318</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H101" s="0" t="s">
         <v>319</v>
@@ -12966,7 +12966,7 @@
         <v>339</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E110" s="0" t="s">
         <v>37</v>
@@ -13052,7 +13052,7 @@
         <v>341</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E111" s="0" t="s">
         <v>37</v>
@@ -13486,7 +13486,7 @@
         <v>79</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F116" s="0" t="s">
         <v>144</v>
@@ -14092,7 +14092,7 @@
         <v>167</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>151</v>
@@ -15041,7 +15041,7 @@
         <v>306</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>151</v>
@@ -15813,10 +15813,10 @@
         <v>321</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H143" s="0" t="s">
         <v>39</v>
@@ -15899,10 +15899,10 @@
         <v>321</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H144" s="0" t="s">
         <v>39</v>
@@ -16071,10 +16071,10 @@
         <v>321</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H146" s="0" t="s">
         <v>39</v>
@@ -16157,10 +16157,10 @@
         <v>321</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H147" s="0" t="s">
         <v>39</v>
@@ -16582,7 +16582,7 @@
         <v>164</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F152" s="0" t="s">
         <v>87</v>
@@ -16922,7 +16922,7 @@
         <v>79</v>
       </c>
       <c r="E156" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F156" s="0" t="s">
         <v>52</v>
@@ -17014,10 +17014,10 @@
         <v>344</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H157" s="0" t="s">
         <v>39</v>
@@ -18222,7 +18222,7 @@
         <v>191</v>
       </c>
       <c r="G171" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H171" s="0" t="s">
         <v>39</v>
@@ -19079,10 +19079,10 @@
         <v>456</v>
       </c>
       <c r="F181" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G181" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H181" s="0" t="s">
         <v>39</v>
@@ -19506,7 +19506,7 @@
         <v>463</v>
       </c>
       <c r="D186" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E186" s="0" t="s">
         <v>464</v>
@@ -19676,7 +19676,7 @@
         <v>467</v>
       </c>
       <c r="D188" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E188" s="0" t="s">
         <v>468</v>
@@ -19768,10 +19768,10 @@
         <v>471</v>
       </c>
       <c r="F189" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G189" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H189" s="0" t="s">
         <v>469</v>
@@ -20103,7 +20103,7 @@
         <v>483</v>
       </c>
       <c r="D193" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E193" s="0" t="s">
         <v>484</v>
@@ -20357,7 +20357,7 @@
         <v>487</v>
       </c>
       <c r="D196" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E196" s="0" t="s">
         <v>468</v>
@@ -20535,7 +20535,7 @@
         <v>491</v>
       </c>
       <c r="D198" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E198" s="0" t="s">
         <v>492</v>
@@ -20624,7 +20624,7 @@
         <v>79</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F199" s="0" t="s">
         <v>144</v>
@@ -20796,7 +20796,7 @@
         <v>79</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F201" s="0" t="s">
         <v>338</v>
@@ -21741,7 +21741,7 @@
         <v>79</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F212" s="0" t="s">
         <v>338</v>
@@ -21824,7 +21824,7 @@
         <v>532</v>
       </c>
       <c r="D213" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E213" s="0" t="s">
         <v>533</v>
@@ -22594,10 +22594,10 @@
         <v>553</v>
       </c>
       <c r="D222" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F222" s="0" t="s">
         <v>203</v>
@@ -22680,10 +22680,10 @@
         <v>554</v>
       </c>
       <c r="D223" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F223" s="0" t="s">
         <v>95</v>
@@ -22766,10 +22766,10 @@
         <v>556</v>
       </c>
       <c r="D224" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F224" s="0" t="s">
         <v>95</v>
@@ -22852,7 +22852,7 @@
         <v>557</v>
       </c>
       <c r="D225" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E225" s="0" t="s">
         <v>558</v>
@@ -23119,10 +23119,10 @@
         <v>564</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H228" s="0" t="s">
         <v>565</v>
@@ -23134,7 +23134,7 @@
         <v>40</v>
       </c>
       <c r="L228" s="0" t="s">
-        <v>296</v>
+        <v>209</v>
       </c>
       <c r="M228" s="0" t="s">
         <v>39</v>
@@ -23279,10 +23279,10 @@
         <v>568</v>
       </c>
       <c r="D230" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F230" s="0" t="s">
         <v>157</v>
@@ -23881,10 +23881,10 @@
         <v>582</v>
       </c>
       <c r="D237" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F237" s="0" t="s">
         <v>203</v>
@@ -24059,7 +24059,7 @@
         <v>203</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H239" s="0" t="s">
         <v>589</v>
@@ -24553,7 +24553,7 @@
         <v>601</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F245" s="0" t="s">
         <v>95</v>
@@ -24728,7 +24728,7 @@
         <v>50</v>
       </c>
       <c r="E247" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F247" s="0" t="s">
         <v>95</v>
@@ -24811,7 +24811,7 @@
         <v>607</v>
       </c>
       <c r="D248" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E248" s="0" t="s">
         <v>303</v>
@@ -24897,7 +24897,7 @@
         <v>608</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E249" s="0" t="s">
         <v>609</v>
@@ -24974,7 +24974,7 @@
         <v>611</v>
       </c>
       <c r="B250" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C250" s="0" t="s">
         <v>612</v>
@@ -25028,7 +25028,7 @@
         <v>43</v>
       </c>
       <c r="AC250" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD250" s="11">
         <v>45707.48365465278</v>
@@ -25054,10 +25054,10 @@
     </row>
     <row r="251">
       <c r="A251" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B251" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C251" s="0" t="s">
         <v>613</v>
@@ -25111,7 +25111,7 @@
         <v>44</v>
       </c>
       <c r="AC251" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD251" s="11">
         <v>45707.48365465278</v>
@@ -25137,10 +25137,10 @@
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B252" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C252" s="0" t="s">
         <v>615</v>
@@ -25149,7 +25149,7 @@
         <v>616</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F252" s="0" t="s">
         <v>157</v>
@@ -25194,7 +25194,7 @@
         <v>43</v>
       </c>
       <c r="AC252" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD252" s="11">
         <v>45707.48365465278</v>
@@ -25220,10 +25220,10 @@
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B253" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C253" s="0" t="s">
         <v>617</v>
@@ -25277,7 +25277,7 @@
         <v>44</v>
       </c>
       <c r="AC253" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD253" s="11">
         <v>45707.48365465278</v>
@@ -25306,7 +25306,7 @@
         <v>618</v>
       </c>
       <c r="B254" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C254" s="0" t="s">
         <v>619</v>
@@ -25360,7 +25360,7 @@
         <v>44</v>
       </c>
       <c r="AC254" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD254" s="11">
         <v>45707.48365465278</v>
@@ -25635,7 +25635,7 @@
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B258" s="0" t="s">
         <v>622</v>
@@ -25650,7 +25650,7 @@
         <v>633</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G258" s="0" t="s">
         <v>438</v>
@@ -26237,10 +26237,10 @@
         <v>652</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J265" s="11">
         <v>46317.125</v>
@@ -26330,7 +26330,7 @@
         <v>70</v>
       </c>
       <c r="L266" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M266" s="0" t="s">
         <v>39</v>
@@ -26479,10 +26479,10 @@
         <v>106</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H268" s="0" t="s">
         <v>204</v>
@@ -27308,10 +27308,10 @@
         <v>367</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H278" s="0" t="s">
         <v>571</v>
@@ -27394,10 +27394,10 @@
         <v>369</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H279" s="0" t="s">
         <v>571</v>
@@ -27480,10 +27480,10 @@
         <v>585</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G280" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H280" s="0" t="s">
         <v>690</v>
@@ -27563,7 +27563,7 @@
         <v>50</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F281" s="0" t="s">
         <v>76</v>
@@ -29025,10 +29025,10 @@
         <v>46338.125</v>
       </c>
       <c r="K298" s="0" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L298" s="0" t="s">
-        <v>39</v>
+        <v>209</v>
       </c>
       <c r="M298" s="0" t="s">
         <v>39</v>
@@ -29093,7 +29093,7 @@
         <v>719</v>
       </c>
       <c r="D299" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E299" s="0" t="s">
         <v>37</v>
@@ -29179,10 +29179,10 @@
         <v>720</v>
       </c>
       <c r="D300" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F300" s="0" t="s">
         <v>64</v>
@@ -29191,7 +29191,7 @@
         <v>64</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J300" s="11">
         <v>46407.125</v>
@@ -29351,10 +29351,10 @@
         <v>724</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F302" s="0" t="s">
         <v>59</v>
@@ -29363,7 +29363,7 @@
         <v>59</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J302" s="11">
         <v>46310.125</v>
@@ -29437,10 +29437,10 @@
         <v>725</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E303" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F303" s="0" t="s">
         <v>95</v>
@@ -29449,7 +29449,7 @@
         <v>95</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J303" s="11">
         <v>46373.125</v>
@@ -29609,10 +29609,10 @@
         <v>728</v>
       </c>
       <c r="D305" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F305" s="0" t="s">
         <v>59</v>
@@ -29784,7 +29784,7 @@
         <v>731</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E307" s="0" t="s">
         <v>37</v>
@@ -29870,10 +29870,10 @@
         <v>732</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F308" s="0" t="s">
         <v>64</v>
@@ -29882,7 +29882,7 @@
         <v>64</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J308" s="11">
         <v>46407.125</v>
@@ -30042,10 +30042,10 @@
         <v>735</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F310" s="0" t="s">
         <v>59</v>
@@ -30054,7 +30054,7 @@
         <v>59</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J310" s="11">
         <v>46373.125</v>
@@ -30128,10 +30128,10 @@
         <v>736</v>
       </c>
       <c r="D311" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F311" s="0" t="s">
         <v>95</v>
@@ -30140,7 +30140,7 @@
         <v>95</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J311" s="11">
         <v>46373.125</v>
@@ -30300,10 +30300,10 @@
         <v>738</v>
       </c>
       <c r="D313" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E313" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F313" s="0" t="s">
         <v>59</v>
@@ -30564,7 +30564,7 @@
         <v>50</v>
       </c>
       <c r="E316" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F316" s="0" t="s">
         <v>76</v>
@@ -30573,7 +30573,7 @@
         <v>76</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J316" s="11">
         <v>46373.125</v>
@@ -30650,7 +30650,7 @@
         <v>744</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F317" s="0" t="s">
         <v>144</v>
@@ -30659,7 +30659,7 @@
         <v>338</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J317" s="11">
         <v>46373.125</v>
@@ -30733,7 +30733,7 @@
         <v>745</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E318" s="0" t="s">
         <v>37</v>
@@ -30911,10 +30911,10 @@
         <v>564</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G320" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H320" s="0" t="s">
         <v>749</v>
@@ -31507,7 +31507,7 @@
         <v>50</v>
       </c>
       <c r="E327" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F327" s="0" t="s">
         <v>76</v>
@@ -31762,7 +31762,7 @@
         <v>764</v>
       </c>
       <c r="D330" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E330" s="0" t="s">
         <v>37</v>
@@ -31848,7 +31848,7 @@
         <v>765</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E331" s="0" t="s">
         <v>37</v>
@@ -31934,7 +31934,7 @@
         <v>766</v>
       </c>
       <c r="D332" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E332" s="0" t="s">
         <v>37</v>
@@ -32020,7 +32020,7 @@
         <v>767</v>
       </c>
       <c r="D333" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E333" s="0" t="s">
         <v>37</v>
@@ -32278,7 +32278,7 @@
         <v>773</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E336" s="0" t="s">
         <v>37</v>
@@ -32364,7 +32364,7 @@
         <v>774</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E337" s="0" t="s">
         <v>37</v>
@@ -32450,10 +32450,10 @@
         <v>775</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E338" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F338" s="0" t="s">
         <v>95</v>
@@ -32536,10 +32536,10 @@
         <v>777</v>
       </c>
       <c r="D339" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E339" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F339" s="0" t="s">
         <v>95</v>
@@ -32613,10 +32613,10 @@
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B340" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C340" s="0" t="s">
         <v>778</v>
@@ -32667,7 +32667,7 @@
         <v>43</v>
       </c>
       <c r="AC340" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD340" s="11">
         <v>45831.61245813657</v>
@@ -33475,7 +33475,7 @@
         <v>164</v>
       </c>
       <c r="E350" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F350" s="0" t="s">
         <v>523</v>
@@ -33562,7 +33562,7 @@
         <v>143</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>438</v>
@@ -33645,7 +33645,7 @@
         <v>164</v>
       </c>
       <c r="E352" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F352" s="0" t="s">
         <v>53</v>
@@ -33728,7 +33728,7 @@
         <v>798</v>
       </c>
       <c r="D353" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E353" s="0" t="s">
         <v>37</v>
@@ -33808,7 +33808,7 @@
         <v>611</v>
       </c>
       <c r="B354" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C354" s="0" t="s">
         <v>799</v>
@@ -33859,7 +33859,7 @@
         <v>43</v>
       </c>
       <c r="AC354" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD354" s="11">
         <v>45839.384970983796</v>
@@ -33897,7 +33897,7 @@
         <v>164</v>
       </c>
       <c r="E355" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F355" s="0" t="s">
         <v>53</v>
@@ -34161,10 +34161,10 @@
         <v>809</v>
       </c>
       <c r="F358" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G358" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J358" s="11">
         <v>46387.125</v>
@@ -34238,10 +34238,10 @@
         <v>812</v>
       </c>
       <c r="F359" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G359" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J359" s="11">
         <v>46341.125</v>
@@ -34321,10 +34321,10 @@
         <v>812</v>
       </c>
       <c r="F360" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G360" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J360" s="11">
         <v>46372.125</v>
@@ -34564,16 +34564,16 @@
         <v>819</v>
       </c>
       <c r="D363" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E363" s="0" t="s">
         <v>820</v>
       </c>
       <c r="F363" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G363" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J363" s="11">
         <v>46372.125</v>
@@ -34638,7 +34638,7 @@
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B364" s="0" t="s">
         <v>622</v>
@@ -34813,10 +34813,10 @@
         <v>825</v>
       </c>
       <c r="D366" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F366" s="0" t="s">
         <v>338</v>
@@ -35148,10 +35148,10 @@
     </row>
     <row r="370">
       <c r="A370" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B370" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C370" s="0" t="s">
         <v>831</v>
@@ -35208,7 +35208,7 @@
         <v>44</v>
       </c>
       <c r="AC370" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD370" s="11">
         <v>45876.367779733795</v>
@@ -35237,7 +35237,7 @@
         <v>833</v>
       </c>
       <c r="B371" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C371" s="0" t="s">
         <v>834</v>
@@ -35288,7 +35288,7 @@
         <v>44</v>
       </c>
       <c r="AC371" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD371" s="11">
         <v>45876.37944880787</v>
@@ -35326,7 +35326,7 @@
         <v>164</v>
       </c>
       <c r="E372" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F372" s="0" t="s">
         <v>338</v>
@@ -35412,7 +35412,7 @@
         <v>79</v>
       </c>
       <c r="E373" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F373" s="0" t="s">
         <v>53</v>
@@ -35589,7 +35589,7 @@
         <v>127</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J375" s="11">
         <v>46310.125</v>
@@ -35663,16 +35663,16 @@
         <v>842</v>
       </c>
       <c r="D376" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E376" s="0" t="s">
         <v>843</v>
       </c>
       <c r="F376" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G376" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H376" s="0" t="s">
         <v>718</v>
@@ -35764,13 +35764,13 @@
         <v>718</v>
       </c>
       <c r="J377" s="11">
-        <v>46309.125</v>
+        <v>46309</v>
       </c>
       <c r="K377" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L377" s="0" t="s">
-        <v>41</v>
+        <v>845</v>
       </c>
       <c r="M377" s="0" t="s">
         <v>39</v>
@@ -35815,13 +35815,13 @@
         <v>43</v>
       </c>
       <c r="AH377" s="0" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="AI377" s="3">
         <v>46129.41428105324</v>
       </c>
       <c r="AJ377" s="3">
-        <v>46309.125</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="378">
@@ -35832,7 +35832,7 @@
         <v>644</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D378" s="0" t="s">
         <v>111</v>
@@ -35841,10 +35841,10 @@
         <v>812</v>
       </c>
       <c r="F378" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G378" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H378" s="0" t="s">
         <v>718</v>
@@ -35918,13 +35918,13 @@
         <v>644</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E379" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F379" s="0" t="s">
         <v>136</v>
@@ -35933,7 +35933,7 @@
         <v>325</v>
       </c>
       <c r="H379" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J379" s="11">
         <v>46341.125</v>
@@ -36004,7 +36004,7 @@
         <v>48</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>201</v>
@@ -36058,7 +36058,7 @@
         <v>44</v>
       </c>
       <c r="AC380" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AD380" s="11">
         <v>46037.3696333912</v>
@@ -36087,10 +36087,10 @@
         <v>643</v>
       </c>
       <c r="B381" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>62</v>
@@ -36144,7 +36144,7 @@
         <v>43</v>
       </c>
       <c r="AC381" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AD381" s="11">
         <v>46037.467388136574</v>
@@ -36173,16 +36173,16 @@
         <v>643</v>
       </c>
       <c r="B382" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D382" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E382" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F382" s="0" t="s">
         <v>59</v>
@@ -36191,14 +36191,14 @@
         <v>136</v>
       </c>
       <c r="H382" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J382" s="11"/>
       <c r="K382" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L382" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M382" s="0" t="s">
         <v>39</v>
@@ -36219,7 +36219,7 @@
         <v>43</v>
       </c>
       <c r="AC382" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AD382" s="11">
         <v>46038.63016152778</v>
@@ -36251,19 +36251,19 @@
         <v>48</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D383" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E383" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F383" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G383" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H383" s="0" t="s">
         <v>134</v>
@@ -36305,7 +36305,7 @@
         <v>44</v>
       </c>
       <c r="AC383" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AD383" s="11">
         <v>46041.63219638889</v>
@@ -36331,25 +36331,25 @@
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B384" s="0" t="s">
         <v>807</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D384" s="0" t="s">
         <v>525</v>
       </c>
       <c r="E384" s="0" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F384" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G384" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J384" s="11">
         <v>46409.125</v>
@@ -36408,25 +36408,25 @@
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B385" s="0" t="s">
         <v>807</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D385" s="0" t="s">
         <v>525</v>
       </c>
       <c r="E385" s="0" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="F385" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G385" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="J385" s="11">
         <v>46413.125</v>
@@ -36488,7 +36488,7 @@
         <v>34</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D386" s="0" t="s">
         <v>50</v>
@@ -36497,10 +36497,10 @@
         <v>106</v>
       </c>
       <c r="F386" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G386" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H386" s="0" t="s">
         <v>204</v>
@@ -36572,7 +36572,7 @@
         <v>34</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D387" s="0" t="s">
         <v>36</v>
@@ -36658,13 +36658,13 @@
         <v>60</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D388" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E388" s="0" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="F388" s="0" t="s">
         <v>203</v>
@@ -36677,7 +36677,7 @@
         <v>70</v>
       </c>
       <c r="L388" s="0" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M388" s="0" t="s">
         <v>39</v>
@@ -36735,13 +36735,13 @@
         <v>60</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D389" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E389" s="0" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="F389" s="0" t="s">
         <v>203</v>
@@ -36754,7 +36754,7 @@
         <v>70</v>
       </c>
       <c r="L389" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="M389" s="0" t="s">
         <v>39</v>
@@ -36806,25 +36806,25 @@
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B390" s="0" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E390" s="0" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F390" s="0" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G390" s="0" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="J390" s="11">
         <v>46401.125</v>
@@ -36857,7 +36857,7 @@
         <v>44</v>
       </c>
       <c r="AC390" s="0" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AD390" s="11">
         <v>46104.56253545139</v>
@@ -36889,7 +36889,7 @@
         <v>644</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>111</v>
@@ -36898,10 +36898,10 @@
         <v>812</v>
       </c>
       <c r="F391" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G391" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H391" s="0" t="s">
         <v>718</v>
@@ -36975,13 +36975,13 @@
         <v>644</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E392" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F392" s="0" t="s">
         <v>326</v>
@@ -37061,13 +37061,13 @@
         <v>60</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F393" s="0" t="s">
         <v>59</v>
@@ -37080,7 +37080,7 @@
         <v>70</v>
       </c>
       <c r="L393" s="0" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="M393" s="0" t="s">
         <v>39</v>
@@ -37142,7 +37142,7 @@
         <v>644</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>111</v>
@@ -37151,10 +37151,10 @@
         <v>812</v>
       </c>
       <c r="F394" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G394" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H394" s="0" t="s">
         <v>718</v>
@@ -37228,7 +37228,7 @@
         <v>34</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>201</v>
@@ -37314,22 +37314,22 @@
         <v>48</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D396" s="0" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E396" s="0" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F396" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G396" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H396" s="0" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J396" s="11">
         <v>46413.125</v>
@@ -37400,13 +37400,13 @@
         <v>48</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D397" s="0" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="F397" s="0" t="s">
         <v>52</v>
@@ -37415,7 +37415,7 @@
         <v>53</v>
       </c>
       <c r="H397" s="0" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="J397" s="11">
         <v>46357.125</v>
@@ -37486,7 +37486,7 @@
         <v>34</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D398" s="0" t="s">
         <v>164</v>
@@ -37501,7 +37501,7 @@
         <v>53</v>
       </c>
       <c r="H398" s="0" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="J398" s="11">
         <v>46361.125</v>
@@ -37572,7 +37572,7 @@
         <v>34</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>50</v>
@@ -37587,7 +37587,7 @@
         <v>152</v>
       </c>
       <c r="H399" s="0" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J399" s="11">
         <v>46365.125</v>
@@ -37658,7 +37658,7 @@
         <v>34</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>50</v>
@@ -37673,7 +37673,7 @@
         <v>136</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J400" s="11">
         <v>46365.125</v>
@@ -37744,7 +37744,7 @@
         <v>34</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>36</v>
@@ -37759,7 +37759,7 @@
         <v>136</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J401" s="11"/>
       <c r="K401" s="0" t="s">
@@ -37828,13 +37828,13 @@
         <v>48</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D402" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E402" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F402" s="0" t="s">
         <v>53</v>
@@ -37843,7 +37843,7 @@
         <v>53</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="J402" s="11">
         <v>46365.125</v>
@@ -37914,7 +37914,7 @@
         <v>48</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D403" s="0" t="s">
         <v>321</v>
@@ -37929,7 +37929,7 @@
         <v>136</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="J403" s="11">
         <v>46362.125</v>
@@ -38000,13 +38000,13 @@
         <v>34</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E404" s="0" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="F404" s="0" t="s">
         <v>64</v>
@@ -38086,7 +38086,7 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>36</v>
@@ -38172,7 +38172,7 @@
         <v>34</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>36</v>
@@ -38258,13 +38258,13 @@
         <v>34</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E407" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F407" s="0" t="s">
         <v>438</v>
@@ -38273,7 +38273,7 @@
         <v>438</v>
       </c>
       <c r="H407" s="0" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J407" s="11"/>
       <c r="K407" s="0" t="s">
@@ -38342,13 +38342,13 @@
         <v>34</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>74</v>
       </c>
       <c r="E408" s="0" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F408" s="0" t="s">
         <v>136</v>
@@ -38357,7 +38357,7 @@
         <v>136</v>
       </c>
       <c r="H408" s="0" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J408" s="11">
         <v>46310.125</v>
@@ -38428,7 +38428,7 @@
         <v>34</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>74</v>
@@ -38517,7 +38517,7 @@
         <v>34</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>50</v>
@@ -38532,7 +38532,7 @@
         <v>338</v>
       </c>
       <c r="H410" s="0" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="J410" s="11">
         <v>46356.125</v>
@@ -38606,13 +38606,13 @@
         <v>34</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>142</v>
       </c>
       <c r="E411" s="0" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F411" s="0" t="s">
         <v>144</v>
@@ -38621,7 +38621,7 @@
         <v>144</v>
       </c>
       <c r="H411" s="0" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="J411" s="11"/>
       <c r="K411" s="0" t="s">
@@ -38693,13 +38693,13 @@
         <v>34</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="F412" s="0" t="s">
         <v>95</v>
@@ -38708,7 +38708,7 @@
         <v>95</v>
       </c>
       <c r="H412" s="0" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="J412" s="11">
         <v>46310.125</v>
@@ -38782,7 +38782,7 @@
         <v>34</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>125</v>
@@ -38797,7 +38797,7 @@
         <v>59</v>
       </c>
       <c r="H413" s="0" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="J413" s="11">
         <v>46310.125</v>
@@ -38806,7 +38806,7 @@
         <v>40</v>
       </c>
       <c r="L413" s="0" t="s">
-        <v>296</v>
+        <v>209</v>
       </c>
       <c r="M413" s="0" t="s">
         <v>39</v>
@@ -38868,7 +38868,7 @@
         <v>34</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>125</v>
@@ -38883,7 +38883,7 @@
         <v>59</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="J414" s="11">
         <v>46310.125</v>
@@ -38892,7 +38892,7 @@
         <v>40</v>
       </c>
       <c r="L414" s="0" t="s">
-        <v>296</v>
+        <v>209</v>
       </c>
       <c r="M414" s="0" t="s">
         <v>39</v>
@@ -38954,13 +38954,13 @@
         <v>48</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D415" s="0" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="E415" s="0" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F415" s="0" t="s">
         <v>203</v>
@@ -39037,7 +39037,7 @@
         <v>34</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D416" s="0" t="s">
         <v>62</v>
@@ -39123,7 +39123,7 @@
         <v>34</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>36</v>
@@ -39138,14 +39138,14 @@
         <v>38</v>
       </c>
       <c r="H417" s="0" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="J417" s="11"/>
       <c r="K417" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L417" s="0" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M417" s="0" t="s">
         <v>39</v>
@@ -39210,7 +39210,7 @@
         <v>34</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>36</v>
@@ -39225,14 +39225,14 @@
         <v>38</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="J418" s="11"/>
       <c r="K418" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L418" s="0" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M418" s="0" t="s">
         <v>39</v>
@@ -39297,13 +39297,13 @@
         <v>48</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D419" s="0" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E419" s="0" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F419" s="0" t="s">
         <v>64</v>
@@ -39380,7 +39380,7 @@
         <v>48</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D420" s="0" t="s">
         <v>321</v>
@@ -39463,13 +39463,13 @@
         <v>34</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>314</v>
       </c>
       <c r="E421" s="0" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F421" s="0" t="s">
         <v>95</v>
@@ -39478,14 +39478,14 @@
         <v>38</v>
       </c>
       <c r="H421" s="0" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="J421" s="11"/>
       <c r="K421" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L421" s="0" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M421" s="0" t="s">
         <v>39</v>
@@ -39550,7 +39550,7 @@
         <v>48</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>387</v>
@@ -39633,13 +39633,13 @@
         <v>48</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D423" s="0" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E423" s="0" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F423" s="0" t="s">
         <v>152</v>
@@ -39716,7 +39716,7 @@
         <v>60</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D424" s="0" t="s">
         <v>50</v>
@@ -39731,7 +39731,7 @@
         <v>170</v>
       </c>
       <c r="H424" s="0" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="J424" s="11">
         <v>46310.125</v>
@@ -39802,13 +39802,13 @@
         <v>60</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E425" s="0" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F425" s="0" t="s">
         <v>331</v>
@@ -39817,7 +39817,7 @@
         <v>331</v>
       </c>
       <c r="H425" s="0" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="J425" s="11">
         <v>46373.125</v>
@@ -39888,7 +39888,7 @@
         <v>60</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>79</v>
@@ -39903,7 +39903,7 @@
         <v>523</v>
       </c>
       <c r="H426" s="0" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J426" s="11">
         <v>46310.125</v>
@@ -39977,13 +39977,13 @@
         <v>60</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E427" s="0" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F427" s="0" t="s">
         <v>171</v>
@@ -39992,7 +39992,7 @@
         <v>171</v>
       </c>
       <c r="H427" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J427" s="11">
         <v>46373.125</v>
@@ -40066,13 +40066,13 @@
         <v>60</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E428" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F428" s="0" t="s">
         <v>53</v>
@@ -40081,7 +40081,7 @@
         <v>53</v>
       </c>
       <c r="H428" s="0" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="J428" s="11">
         <v>46373.125</v>
@@ -40152,22 +40152,22 @@
         <v>60</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E429" s="0" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F429" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G429" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H429" s="0" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="J429" s="11">
         <v>46310.125</v>
@@ -40238,7 +40238,7 @@
         <v>60</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>50</v>
@@ -40253,7 +40253,7 @@
         <v>152</v>
       </c>
       <c r="H430" s="0" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="J430" s="11">
         <v>46373.125</v>
@@ -40324,19 +40324,19 @@
         <v>60</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>730</v>
       </c>
       <c r="E431" s="0" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F431" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G431" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H431" s="0" t="s">
         <v>806</v>
@@ -40410,10 +40410,10 @@
         <v>60</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D432" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E432" s="0" t="s">
         <v>37</v>
@@ -40425,7 +40425,7 @@
         <v>326</v>
       </c>
       <c r="H432" s="0" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="J432" s="11">
         <v>46310.125</v>
@@ -40496,13 +40496,13 @@
         <v>60</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D433" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E433" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F433" s="0" t="s">
         <v>133</v>
@@ -40511,7 +40511,7 @@
         <v>95</v>
       </c>
       <c r="H433" s="0" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="J433" s="11">
         <v>46310.125</v>
@@ -40582,13 +40582,13 @@
         <v>60</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D434" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E434" s="0" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F434" s="0" t="s">
         <v>170</v>
@@ -40597,7 +40597,7 @@
         <v>170</v>
       </c>
       <c r="H434" s="0" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J434" s="11">
         <v>46310.125</v>
@@ -40671,10 +40671,10 @@
         <v>60</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="D435" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E435" s="0" t="s">
         <v>37</v>
@@ -40686,7 +40686,7 @@
         <v>64</v>
       </c>
       <c r="H435" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J435" s="11">
         <v>46310.125</v>
@@ -40760,16 +40760,16 @@
         <v>60</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D436" s="0" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="E436" s="0" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F436" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G436" s="0" t="s">
         <v>299</v>
@@ -40846,13 +40846,13 @@
         <v>60</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D437" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E437" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F437" s="0" t="s">
         <v>136</v>
@@ -40935,7 +40935,7 @@
         <v>60</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>411</v>
@@ -40950,7 +40950,7 @@
         <v>171</v>
       </c>
       <c r="H438" s="0" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="J438" s="11">
         <v>46373.125</v>
@@ -41021,13 +41021,13 @@
         <v>60</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D439" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E439" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F439" s="0" t="s">
         <v>76</v>
@@ -41036,7 +41036,7 @@
         <v>64</v>
       </c>
       <c r="H439" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J439" s="11">
         <v>46310.125</v>
@@ -41107,13 +41107,13 @@
         <v>60</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D440" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E440" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F440" s="0" t="s">
         <v>52</v>
@@ -41193,7 +41193,7 @@
         <v>60</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>411</v>
@@ -41208,7 +41208,7 @@
         <v>326</v>
       </c>
       <c r="H441" s="0" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="J441" s="11">
         <v>46373.125</v>
@@ -41279,13 +41279,13 @@
         <v>60</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D442" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E442" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F442" s="0" t="s">
         <v>38</v>
@@ -41294,7 +41294,7 @@
         <v>76</v>
       </c>
       <c r="H442" s="0" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="J442" s="11">
         <v>46310.125</v>
@@ -41365,13 +41365,13 @@
         <v>60</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D443" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E443" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F443" s="0" t="s">
         <v>136</v>
@@ -41454,7 +41454,7 @@
         <v>60</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>411</v>
@@ -41469,7 +41469,7 @@
         <v>171</v>
       </c>
       <c r="H444" s="0" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="J444" s="11">
         <v>46373.125</v>
@@ -41540,13 +41540,13 @@
         <v>60</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D445" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E445" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F445" s="0" t="s">
         <v>76</v>
@@ -41555,7 +41555,7 @@
         <v>64</v>
       </c>
       <c r="H445" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J445" s="11">
         <v>46310.125</v>
@@ -41626,7 +41626,7 @@
         <v>60</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>164</v>
@@ -41641,7 +41641,7 @@
         <v>179</v>
       </c>
       <c r="H446" s="0" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="J446" s="11">
         <v>46310.125</v>
@@ -41712,13 +41712,13 @@
         <v>60</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E447" s="0" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F447" s="0" t="s">
         <v>501</v>
@@ -41727,7 +41727,7 @@
         <v>501</v>
       </c>
       <c r="H447" s="0" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="J447" s="11">
         <v>46373.125</v>
@@ -41798,7 +41798,7 @@
         <v>60</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>164</v>
@@ -41813,7 +41813,7 @@
         <v>517</v>
       </c>
       <c r="H448" s="0" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="J448" s="11">
         <v>46310.125</v>
@@ -41884,13 +41884,13 @@
         <v>60</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E449" s="0" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F449" s="0" t="s">
         <v>331</v>
@@ -41899,7 +41899,7 @@
         <v>331</v>
       </c>
       <c r="H449" s="0" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="J449" s="11">
         <v>46310.125</v>
@@ -41973,7 +41973,7 @@
         <v>60</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>164</v>
@@ -41988,7 +41988,7 @@
         <v>331</v>
       </c>
       <c r="H450" s="0" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="J450" s="11"/>
       <c r="K450" s="0" t="s">
@@ -42051,25 +42051,25 @@
     </row>
     <row r="451">
       <c r="A451" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B451" s="0" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D451" s="0" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E451" s="0" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F451" s="0" t="s">
         <v>299</v>
       </c>
       <c r="G451" s="0" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="J451" s="11">
         <v>46310.125</v>
@@ -42102,7 +42102,7 @@
         <v>44</v>
       </c>
       <c r="AC451" s="0" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AD451" s="11">
         <v>46203.65469700231</v>
@@ -42134,13 +42134,13 @@
         <v>644</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D452" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E452" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F452" s="0" t="s">
         <v>326</v>
@@ -42149,7 +42149,7 @@
         <v>326</v>
       </c>
       <c r="H452" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J452" s="11">
         <v>46365.125</v>
@@ -42220,7 +42220,7 @@
         <v>644</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>769</v>
@@ -42229,13 +42229,13 @@
         <v>812</v>
       </c>
       <c r="F453" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G453" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H453" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J453" s="11">
         <v>46365.125</v>
@@ -42306,13 +42306,13 @@
         <v>34</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E454" s="0" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F454" s="0" t="s">
         <v>87</v>
@@ -42389,7 +42389,7 @@
         <v>34</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>36</v>
@@ -42472,19 +42472,19 @@
         <v>807</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D456" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E456" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F456" s="0" t="s">
         <v>203</v>
       </c>
       <c r="G456" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J456" s="11">
         <v>46390.125</v>
@@ -42546,7 +42546,7 @@
         <v>34</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>125</v>
@@ -42561,7 +42561,7 @@
         <v>76</v>
       </c>
       <c r="H457" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="J457" s="11">
         <v>46387.125</v>
@@ -42632,7 +42632,7 @@
         <v>34</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D458" s="0" t="s">
         <v>125</v>
@@ -42647,7 +42647,7 @@
         <v>76</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="J458" s="11">
         <v>46326.125</v>
@@ -42718,7 +42718,7 @@
         <v>34</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>50</v>
@@ -42733,7 +42733,7 @@
         <v>325</v>
       </c>
       <c r="H459" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="J459" s="11">
         <v>46326.125</v>
@@ -42804,13 +42804,13 @@
         <v>34</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E460" s="0" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F460" s="0" t="s">
         <v>133</v>
@@ -42890,13 +42890,13 @@
         <v>34</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>182</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F461" s="0" t="s">
         <v>151</v>
@@ -42905,7 +42905,7 @@
         <v>151</v>
       </c>
       <c r="H461" s="0" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="J461" s="11">
         <v>46310.125</v>
@@ -42914,7 +42914,7 @@
         <v>40</v>
       </c>
       <c r="L461" s="0" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="M461" s="0" t="s">
         <v>39</v>
@@ -42976,13 +42976,13 @@
         <v>60</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D462" s="0" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E462" s="0" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F462" s="0" t="s">
         <v>417</v>
@@ -42991,7 +42991,7 @@
         <v>417</v>
       </c>
       <c r="H462" s="0" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="J462" s="11">
         <v>46310.125</v>
@@ -43059,7 +43059,7 @@
         <v>60</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>79</v>
@@ -43074,7 +43074,7 @@
         <v>331</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="J463" s="11">
         <v>46406.125</v>
@@ -43145,22 +43145,22 @@
         <v>60</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F464" s="0" t="s">
         <v>81</v>
       </c>
       <c r="G464" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H464" s="0" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="J464" s="11">
         <v>46407.125</v>
@@ -43231,10 +43231,10 @@
         <v>60</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D465" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E465" s="0" t="s">
         <v>37</v>
@@ -43246,7 +43246,7 @@
         <v>136</v>
       </c>
       <c r="H465" s="0" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="J465" s="11">
         <v>46407.125</v>
@@ -43317,10 +43317,10 @@
         <v>60</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D466" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E466" s="0" t="s">
         <v>37</v>
@@ -43332,7 +43332,7 @@
         <v>136</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="J466" s="11">
         <v>46407.125</v>
@@ -43403,7 +43403,7 @@
         <v>60</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>769</v>
@@ -43418,7 +43418,7 @@
         <v>53</v>
       </c>
       <c r="H467" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="J467" s="11">
         <v>46406.125</v>
@@ -43489,13 +43489,13 @@
         <v>60</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="D468" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E468" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F468" s="0" t="s">
         <v>76</v>
@@ -43504,7 +43504,7 @@
         <v>76</v>
       </c>
       <c r="H468" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="J468" s="11">
         <v>46373.125</v>
@@ -43575,13 +43575,13 @@
         <v>48</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E469" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F469" s="0" t="s">
         <v>38</v>
@@ -43629,7 +43629,7 @@
         <v>44</v>
       </c>
       <c r="AC469" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AD469" s="11">
         <v>46218.47940927083</v>
@@ -43655,19 +43655,19 @@
     </row>
     <row r="470">
       <c r="A470" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B470" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D470" s="0" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E470" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F470" s="0" t="s">
         <v>144</v>
@@ -43676,7 +43676,7 @@
         <v>144</v>
       </c>
       <c r="H470" s="0" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="J470" s="11">
         <v>46398.125</v>
@@ -43712,7 +43712,7 @@
         <v>44</v>
       </c>
       <c r="AC470" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD470" s="11">
         <v>46218.81741611111</v>
@@ -43744,19 +43744,19 @@
         <v>807</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D471" s="0" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E471" s="0" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F471" s="0" t="s">
         <v>203</v>
       </c>
       <c r="G471" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J471" s="11">
         <v>46326.125</v>
@@ -43789,7 +43789,7 @@
         <v>44</v>
       </c>
       <c r="AC471" s="0" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AD471" s="11">
         <v>46219.55652277778</v>
@@ -43821,7 +43821,7 @@
         <v>48</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>381</v>
@@ -43836,7 +43836,7 @@
         <v>338</v>
       </c>
       <c r="H472" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="J472" s="11">
         <v>46402.125</v>
@@ -43907,7 +43907,7 @@
         <v>60</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>50</v>
@@ -43922,7 +43922,7 @@
         <v>81</v>
       </c>
       <c r="H473" s="0" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="J473" s="11">
         <v>46346.125</v>
@@ -43993,13 +43993,13 @@
         <v>60</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D474" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E474" s="0" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F474" s="0" t="s">
         <v>338</v>
@@ -44008,7 +44008,7 @@
         <v>52</v>
       </c>
       <c r="H474" s="0" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="J474" s="11">
         <v>46346.125</v>
@@ -44079,22 +44079,22 @@
         <v>60</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D475" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E475" s="0" t="s">
         <v>37</v>
       </c>
       <c r="F475" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G475" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H475" s="0" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="J475" s="11">
         <v>46310.125</v>
@@ -44165,7 +44165,7 @@
         <v>60</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>50</v>
@@ -44180,7 +44180,7 @@
         <v>152</v>
       </c>
       <c r="H476" s="0" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J476" s="11">
         <v>46407.125</v>
@@ -44251,22 +44251,22 @@
         <v>60</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D477" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E477" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F477" s="0" t="s">
         <v>81</v>
       </c>
       <c r="G477" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H477" s="0" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J477" s="11">
         <v>46407.125</v>
@@ -44337,22 +44337,22 @@
         <v>60</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D478" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E478" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F478" s="0" t="s">
         <v>81</v>
       </c>
       <c r="G478" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H478" s="0" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J478" s="11">
         <v>46407.125</v>
@@ -44423,16 +44423,16 @@
         <v>622</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D479" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E479" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F479" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G479" s="0" t="s">
         <v>438</v>
@@ -44503,13 +44503,13 @@
         <v>622</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D480" s="0" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E480" s="0" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F480" s="0" t="s">
         <v>438</v>
@@ -44583,13 +44583,13 @@
         <v>48</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D481" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E481" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F481" s="0" t="s">
         <v>100</v>
@@ -44669,13 +44669,13 @@
         <v>34</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F482" s="0" t="s">
         <v>38</v>
@@ -44684,7 +44684,7 @@
         <v>38</v>
       </c>
       <c r="H482" s="0" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="J482" s="11">
         <v>46310.125</v>
@@ -44755,13 +44755,13 @@
         <v>48</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D483" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E483" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F483" s="0" t="s">
         <v>139</v>
@@ -44838,7 +44838,7 @@
         <v>48</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>344</v>
@@ -44921,7 +44921,7 @@
         <v>48</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>344</v>
@@ -45004,10 +45004,10 @@
         <v>34</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D486" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E486" s="0" t="s">
         <v>37</v>
@@ -45019,7 +45019,7 @@
         <v>38</v>
       </c>
       <c r="H486" s="0" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J486" s="11">
         <v>46362.125</v>
@@ -45090,10 +45090,10 @@
         <v>34</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E487" s="0" t="s">
         <v>37</v>
@@ -45105,7 +45105,7 @@
         <v>38</v>
       </c>
       <c r="H487" s="0" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J487" s="11">
         <v>46362.125</v>
@@ -45176,7 +45176,7 @@
         <v>48</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>365</v>
@@ -45259,19 +45259,19 @@
         <v>48</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D489" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="E489" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F489" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G489" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J489" s="11">
         <v>46423.125</v>
@@ -45342,13 +45342,13 @@
         <v>48</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D490" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E490" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F490" s="0" t="s">
         <v>133</v>
@@ -45425,19 +45425,19 @@
         <v>48</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D491" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E491" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F491" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G491" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J491" s="11">
         <v>46369.125</v>
@@ -45508,13 +45508,13 @@
         <v>60</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>525</v>
       </c>
       <c r="E492" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F492" s="0" t="s">
         <v>107</v>
@@ -45594,22 +45594,22 @@
         <v>644</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>74</v>
       </c>
       <c r="E493" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F493" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G493" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H493" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="J493" s="11">
         <v>46372.125</v>
@@ -45680,19 +45680,19 @@
         <v>34</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E494" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F494" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G494" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H494" s="0" t="s">
         <v>204</v>
@@ -45766,19 +45766,19 @@
         <v>34</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D495" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E495" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F495" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G495" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H495" s="0" t="s">
         <v>204</v>
@@ -45849,10 +45849,10 @@
         <v>611</v>
       </c>
       <c r="B496" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D496" s="0" t="s">
         <v>525</v>
@@ -45900,7 +45900,7 @@
         <v>43</v>
       </c>
       <c r="AC496" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD496" s="11">
         <v>46296.42035898148</v>
@@ -45932,19 +45932,19 @@
         <v>807</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D497" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="E497" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F497" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G497" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J497" s="11">
         <v>46483.125</v>
@@ -46003,16 +46003,16 @@
         <v>814</v>
       </c>
       <c r="B498" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D498" s="0" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="E498" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F498" s="0" t="s">
         <v>170</v>
@@ -46025,7 +46025,7 @@
         <v>70</v>
       </c>
       <c r="L498" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="M498" s="0" t="s">
         <v>39</v>
@@ -46049,7 +46049,7 @@
         <v>43</v>
       </c>
       <c r="AC498" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AD498" s="11">
         <v>46303.38590450231</v>
@@ -46070,16 +46070,16 @@
         <v>814</v>
       </c>
       <c r="B499" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D499" s="0" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E499" s="0" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F499" s="0" t="s">
         <v>171</v>
@@ -46092,7 +46092,7 @@
         <v>70</v>
       </c>
       <c r="L499" s="0" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="M499" s="0" t="s">
         <v>39</v>
@@ -46116,7 +46116,7 @@
         <v>43</v>
       </c>
       <c r="AC499" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AD499" s="11">
         <v>46303.38891412037</v>
@@ -46168,7 +46168,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -46179,28 +46179,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -46208,10 +46208,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>807</v>
@@ -46229,10 +46229,10 @@
         <v>46483.125</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>807</v>
@@ -46240,10 +46240,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>807</v>
@@ -46255,16 +46255,16 @@
         <v>46303</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G3" s="11">
         <v>46483.125</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>807</v>
@@ -46272,10 +46272,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>644</v>
@@ -46293,10 +46293,10 @@
         <v>46480.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>648</v>
@@ -46304,13 +46304,13 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>30</v>
@@ -46325,24 +46325,24 @@
         <v>46476.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>29</v>
@@ -46351,27 +46351,27 @@
         <v>46296</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G6" s="11">
         <v>46476.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>34</v>
@@ -46389,10 +46389,10 @@
         <v>46474.125</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>205</v>
@@ -46400,10 +46400,10 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>34</v>
@@ -46421,10 +46421,10 @@
         <v>46474.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>205</v>
@@ -46432,10 +46432,10 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>644</v>
@@ -46453,10 +46453,10 @@
         <v>46474.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>648</v>
@@ -46464,10 +46464,10 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>644</v>
@@ -46479,16 +46479,16 @@
         <v>46294</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G10" s="11">
         <v>46474.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>648</v>
@@ -46499,7 +46499,7 @@
         <v>842</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>644</v>
@@ -46517,10 +46517,10 @@
         <v>46474.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>648</v>
@@ -46531,7 +46531,7 @@
         <v>842</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>644</v>
@@ -46543,16 +46543,16 @@
         <v>46294</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G12" s="11">
         <v>46474.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>648</v>
@@ -46560,10 +46560,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>60</v>
@@ -46575,16 +46575,16 @@
         <v>46289</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G13" s="11">
         <v>46469.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>66</v>
@@ -46592,10 +46592,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>60</v>
@@ -46613,10 +46613,10 @@
         <v>46469.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>66</v>
@@ -46624,10 +46624,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>644</v>
@@ -46645,10 +46645,10 @@
         <v>46455.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>648</v>
@@ -46656,10 +46656,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>644</v>
@@ -46671,16 +46671,16 @@
         <v>46275</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G16" s="11">
         <v>46455.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>648</v>
@@ -46688,13 +46688,13 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C17" s="0" t="s">
         <v>851</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>850</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>30</v>
@@ -46709,24 +46709,24 @@
         <v>46449.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C18" s="0" t="s">
         <v>851</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>850</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>29</v>
@@ -46735,30 +46735,30 @@
         <v>46269</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G18" s="11">
         <v>46449.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C19" s="0" t="s">
         <v>851</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>850</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>30</v>
@@ -46773,13 +46773,13 @@
         <v>46268</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="20">
@@ -46787,7 +46787,7 @@
         <v>551</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>34</v>
@@ -46799,19 +46799,19 @@
         <v>46267</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G20" s="11">
         <v>46447.125</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="21">
@@ -46819,7 +46819,7 @@
         <v>551</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>34</v>
@@ -46837,21 +46837,21 @@
         <v>46447.125</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>60</v>
@@ -46869,10 +46869,10 @@
         <v>46446.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>610</v>
@@ -46880,10 +46880,10 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>60</v>
@@ -46901,10 +46901,10 @@
         <v>46446.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>610</v>
@@ -46915,7 +46915,7 @@
         <v>553</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>48</v>
@@ -46927,27 +46927,27 @@
         <v>46261</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G24" s="11">
         <v>46441.125</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>34</v>
@@ -46959,16 +46959,16 @@
         <v>46260</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G25" s="11">
         <v>46440.125</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>205</v>
@@ -46976,10 +46976,10 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>60</v>
@@ -46997,10 +46997,10 @@
         <v>46440.125</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J26" s="0" t="s">
         <v>66</v>
@@ -47008,10 +47008,10 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>34</v>
@@ -47029,10 +47029,10 @@
         <v>46439.125</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>205</v>
@@ -47043,7 +47043,7 @@
         <v>657</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>34</v>
@@ -47061,10 +47061,10 @@
         <v>46439.125</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>205</v>
@@ -47072,10 +47072,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>34</v>
@@ -47093,10 +47093,10 @@
         <v>46439.125</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>205</v>
@@ -47107,7 +47107,7 @@
         <v>653</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>60</v>
@@ -47125,10 +47125,10 @@
         <v>46439.125</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>610</v>
@@ -47139,7 +47139,7 @@
         <v>342</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>60</v>
@@ -47157,10 +47157,10 @@
         <v>46439.125</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>66</v>
@@ -47171,7 +47171,7 @@
         <v>472</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>60</v>
@@ -47183,16 +47183,16 @@
         <v>46255</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G32" s="11">
         <v>46435.125</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>66</v>
@@ -47203,7 +47203,7 @@
         <v>472</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>60</v>
@@ -47221,10 +47221,10 @@
         <v>46435.125</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>66</v>
@@ -47235,7 +47235,7 @@
         <v>651</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>60</v>
@@ -47253,10 +47253,10 @@
         <v>46432.125</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>610</v>
@@ -47267,7 +47267,7 @@
         <v>608</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>60</v>
@@ -47285,10 +47285,10 @@
         <v>46432.125</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>610</v>
@@ -47299,7 +47299,7 @@
         <v>607</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>34</v>
@@ -47317,10 +47317,10 @@
         <v>46432.125</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>45</v>
@@ -47328,10 +47328,10 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>34</v>
@@ -47349,10 +47349,10 @@
         <v>46432.125</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>45</v>
@@ -47363,7 +47363,7 @@
         <v>607</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>34</v>
@@ -47375,16 +47375,16 @@
         <v>46252</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G38" s="11">
         <v>46432.125</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J38" s="0" t="s">
         <v>45</v>
@@ -47392,10 +47392,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>48</v>
@@ -47407,16 +47407,16 @@
         <v>46251</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G39" s="11">
         <v>46431.125</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J39" s="0" t="s">
         <v>56</v>
@@ -47424,10 +47424,10 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>48</v>
@@ -47445,10 +47445,10 @@
         <v>46431.125</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J40" s="0" t="s">
         <v>56</v>
@@ -47456,10 +47456,10 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>48</v>
@@ -47477,10 +47477,10 @@
         <v>46431.125</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J41" s="0" t="s">
         <v>56</v>
@@ -47491,7 +47491,7 @@
         <v>388</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>34</v>
@@ -47509,10 +47509,10 @@
         <v>46429.125</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J42" s="0" t="s">
         <v>45</v>
@@ -47523,7 +47523,7 @@
         <v>390</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>34</v>
@@ -47541,10 +47541,10 @@
         <v>46429.125</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J43" s="0" t="s">
         <v>45</v>
@@ -47555,7 +47555,7 @@
         <v>700</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>34</v>
@@ -47573,10 +47573,10 @@
         <v>46429.125</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J44" s="0" t="s">
         <v>45</v>
@@ -47584,10 +47584,10 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C45" s="0" t="s">
         <v>48</v>
@@ -47599,16 +47599,16 @@
         <v>46249</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G45" s="11">
         <v>46429.125</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J45" s="0" t="s">
         <v>56</v>
@@ -47616,10 +47616,10 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>48</v>
@@ -47631,16 +47631,16 @@
         <v>46249</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G46" s="11">
         <v>46429.125</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J46" s="0" t="s">
         <v>56</v>
@@ -47648,10 +47648,10 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>48</v>
@@ -47669,10 +47669,10 @@
         <v>46429.125</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J47" s="0" t="s">
         <v>56</v>
@@ -47680,10 +47680,10 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>48</v>
@@ -47701,10 +47701,10 @@
         <v>46429.125</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J48" s="0" t="s">
         <v>56</v>
@@ -47712,10 +47712,10 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C49" s="0" t="s">
         <v>48</v>
@@ -47733,10 +47733,10 @@
         <v>46429.125</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J49" s="0" t="s">
         <v>56</v>
@@ -47747,7 +47747,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C50" s="0" t="s">
         <v>34</v>
@@ -47759,16 +47759,16 @@
         <v>46249</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G50" s="11">
         <v>46429.125</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J50" s="0" t="s">
         <v>45</v>
@@ -47779,7 +47779,7 @@
         <v>35</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C51" s="0" t="s">
         <v>34</v>
@@ -47791,16 +47791,16 @@
         <v>46249</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G51" s="11">
         <v>46429.125</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J51" s="0" t="s">
         <v>45</v>
@@ -47811,7 +47811,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C52" s="0" t="s">
         <v>34</v>
@@ -47829,10 +47829,10 @@
         <v>46429.125</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J52" s="0" t="s">
         <v>45</v>
@@ -47843,7 +47843,7 @@
         <v>35</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C53" s="0" t="s">
         <v>34</v>
@@ -47861,10 +47861,10 @@
         <v>46429.125</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J53" s="0" t="s">
         <v>45</v>
@@ -47875,7 +47875,7 @@
         <v>57</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C54" s="0" t="s">
         <v>34</v>
@@ -47893,109 +47893,13 @@
         <v>46429.125</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="J54" s="0" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="0" t="s">
-        <v>388</v>
-      </c>
-      <c r="B55" s="0" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D55" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E55" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F55" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="G55" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H55" s="0" t="s">
-        <v>1107</v>
-      </c>
-      <c r="I55" s="0" t="s">
-        <v>1098</v>
-      </c>
-      <c r="J55" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="0" t="s">
-        <v>390</v>
-      </c>
-      <c r="B56" s="0" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D56" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E56" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F56" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="G56" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H56" s="0" t="s">
-        <v>1107</v>
-      </c>
-      <c r="I56" s="0" t="s">
-        <v>1098</v>
-      </c>
-      <c r="J56" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="0" t="s">
-        <v>434</v>
-      </c>
-      <c r="B57" s="0" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D57" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E57" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F57" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="G57" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H57" s="0" t="s">
-        <v>1107</v>
-      </c>
-      <c r="I57" s="0" t="s">
-        <v>1098</v>
-      </c>
-      <c r="J57" s="0" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="1123">
   <si>
     <t>Geração:</t>
   </si>
@@ -3382,27 +3382,6 @@
   </si>
   <si>
     <t>VOLVO/FH 400 6X2T / VOLVO/FH 400 6X2T</t>
-  </si>
-  <si>
-    <t>SR/LIBRELATO SRCT 2E / SR/LIBRELATO SRCT 2E</t>
-  </si>
-  <si>
-    <t>SR/LIBRELATO SRCD 2E / SR/LIBRELATO SRCD 2E</t>
-  </si>
-  <si>
-    <t>REB/RANDON SR GR TR / REB/RANDON SR GR TR</t>
-  </si>
-  <si>
-    <t>MARCONI BELO SOBRINHO</t>
-  </si>
-  <si>
-    <t>00729704203 / 00729704203</t>
-  </si>
-  <si>
-    <t>SR/RANDON / SR CA</t>
-  </si>
-  <si>
-    <t>VOLVO / FH 460 6X2T</t>
   </si>
 </sst>
 </file>
@@ -3594,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46309.34970878472</v>
+        <v>46309.58092883102</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -11175,13 +11154,13 @@
         <v>39</v>
       </c>
       <c r="J89" s="11">
-        <v>46335.125</v>
+        <v>46391.125</v>
       </c>
       <c r="K89" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L89" s="0" t="s">
-        <v>209</v>
+        <v>39</v>
       </c>
       <c r="M89" s="0" t="s">
         <v>39</v>
@@ -11190,13 +11169,13 @@
         <v>42</v>
       </c>
       <c r="O89" s="11">
-        <v>46751.125</v>
+        <v>46721.125</v>
       </c>
       <c r="Q89" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R89" s="11">
-        <v>46335.125</v>
+        <v>46491.125</v>
       </c>
       <c r="T89" s="0" t="s">
         <v>43</v>
@@ -46168,7 +46147,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -47486,422 +47465,6 @@
         <v>56</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
-        <v>388</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E42" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G42" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H42" s="0" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I42" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J42" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
-        <v>390</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E43" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F43" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G43" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H43" s="0" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I43" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J43" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
-        <v>700</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E44" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F44" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G44" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H44" s="0" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I44" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J44" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F45" s="0" t="s">
-        <v>1097</v>
-      </c>
-      <c r="G45" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H45" s="0" t="s">
-        <v>1126</v>
-      </c>
-      <c r="I45" s="0" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J45" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E46" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F46" s="0" t="s">
-        <v>1097</v>
-      </c>
-      <c r="G46" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H46" s="0" t="s">
-        <v>1126</v>
-      </c>
-      <c r="I46" s="0" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J46" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E47" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F47" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G47" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H47" s="0" t="s">
-        <v>1121</v>
-      </c>
-      <c r="I47" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J47" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D48" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E48" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F48" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G48" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H48" s="0" t="s">
-        <v>1121</v>
-      </c>
-      <c r="I48" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J48" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B49" s="0" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E49" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F49" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G49" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H49" s="0" t="s">
-        <v>1121</v>
-      </c>
-      <c r="I49" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J49" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" s="0" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D50" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E50" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F50" s="0" t="s">
-        <v>1097</v>
-      </c>
-      <c r="G50" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H50" s="0" t="s">
-        <v>1126</v>
-      </c>
-      <c r="I50" s="0" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J50" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E51" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F51" s="0" t="s">
-        <v>1097</v>
-      </c>
-      <c r="G51" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H51" s="0" t="s">
-        <v>1126</v>
-      </c>
-      <c r="I51" s="0" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J51" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D52" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E52" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F52" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G52" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H52" s="0" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I52" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J52" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B53" s="0" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D53" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E53" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F53" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G53" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H53" s="0" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I53" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J53" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="0" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D54" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E54" s="11">
-        <v>46249</v>
-      </c>
-      <c r="F54" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G54" s="11">
-        <v>46429.125</v>
-      </c>
-      <c r="H54" s="0" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I54" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J54" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="1122">
   <si>
     <t>Geração:</t>
   </si>
@@ -1230,7 +1230,7 @@
     <t>APK0H88</t>
   </si>
   <si>
-    <t>Inspeção Checklist de Qualidade vencida / Documento CRLV vencendo</t>
+    <t>Documento CRLV ausente ou vencido / Inspeção Checklist de Qualidade vencida</t>
   </si>
   <si>
     <t>KDH8F64</t>
@@ -2548,9 +2548,6 @@
   </si>
   <si>
     <t>AVV6018</t>
-  </si>
-  <si>
-    <t>Inspeções Checklist de Segurança SESMT a vencer / Documento CRLV vencendo</t>
   </si>
   <si>
     <t>BDV6I85</t>
@@ -3573,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46309.58092883102</v>
+        <v>46310.34958142361</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -8568,10 +8565,10 @@
         <v>46310.125</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M59" s="0" t="s">
         <v>39</v>
@@ -16499,7 +16496,7 @@
         <v>39</v>
       </c>
       <c r="N151" s="0" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="O151" s="11">
         <v>46309.125</v>
@@ -21396,13 +21393,13 @@
         <v>70</v>
       </c>
       <c r="L208" s="0" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M208" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N208" s="0" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="O208" s="11">
         <v>46309.125</v>
@@ -24043,20 +24040,18 @@
       <c r="H239" s="0" t="s">
         <v>589</v>
       </c>
-      <c r="J239" s="11">
-        <v>46309.125</v>
-      </c>
+      <c r="J239" s="11"/>
       <c r="K239" s="0" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="L239" s="0" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="M239" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N239" s="0" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="O239" s="11">
         <v>46309.125</v>
@@ -35154,10 +35149,10 @@
         <v>46310.125</v>
       </c>
       <c r="K370" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L370" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M370" s="0" t="s">
         <v>39</v>
@@ -35742,14 +35737,12 @@
       <c r="H377" s="0" t="s">
         <v>718</v>
       </c>
-      <c r="J377" s="11">
-        <v>46309</v>
-      </c>
+      <c r="J377" s="11"/>
       <c r="K377" s="0" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="L377" s="0" t="s">
-        <v>845</v>
+        <v>684</v>
       </c>
       <c r="M377" s="0" t="s">
         <v>39</v>
@@ -35811,7 +35804,7 @@
         <v>644</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D378" s="0" t="s">
         <v>111</v>
@@ -35897,13 +35890,13 @@
         <v>644</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E379" s="0" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F379" s="0" t="s">
         <v>136</v>
@@ -35912,7 +35905,7 @@
         <v>325</v>
       </c>
       <c r="H379" s="0" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J379" s="11">
         <v>46341.125</v>
@@ -35983,7 +35976,7 @@
         <v>48</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>201</v>
@@ -36066,10 +36059,10 @@
         <v>643</v>
       </c>
       <c r="B381" s="0" t="s">
+        <v>850</v>
+      </c>
+      <c r="C381" s="0" t="s">
         <v>851</v>
-      </c>
-      <c r="C381" s="0" t="s">
-        <v>852</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>62</v>
@@ -36123,7 +36116,7 @@
         <v>43</v>
       </c>
       <c r="AC381" s="0" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AD381" s="11">
         <v>46037.467388136574</v>
@@ -36152,16 +36145,16 @@
         <v>643</v>
       </c>
       <c r="B382" s="0" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C382" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="D382" s="0" t="s">
         <v>854</v>
       </c>
-      <c r="D382" s="0" t="s">
+      <c r="E382" s="0" t="s">
         <v>855</v>
-      </c>
-      <c r="E382" s="0" t="s">
-        <v>856</v>
       </c>
       <c r="F382" s="0" t="s">
         <v>59</v>
@@ -36170,14 +36163,14 @@
         <v>136</v>
       </c>
       <c r="H382" s="0" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J382" s="11"/>
       <c r="K382" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L382" s="0" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="M382" s="0" t="s">
         <v>39</v>
@@ -36198,7 +36191,7 @@
         <v>43</v>
       </c>
       <c r="AC382" s="0" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AD382" s="11">
         <v>46038.63016152778</v>
@@ -36230,19 +36223,19 @@
         <v>48</v>
       </c>
       <c r="C383" s="0" t="s">
+        <v>857</v>
+      </c>
+      <c r="D383" s="0" t="s">
         <v>858</v>
       </c>
-      <c r="D383" s="0" t="s">
+      <c r="E383" s="0" t="s">
+        <v>858</v>
+      </c>
+      <c r="F383" s="0" t="s">
         <v>859</v>
       </c>
-      <c r="E383" s="0" t="s">
+      <c r="G383" s="0" t="s">
         <v>859</v>
-      </c>
-      <c r="F383" s="0" t="s">
-        <v>860</v>
-      </c>
-      <c r="G383" s="0" t="s">
-        <v>860</v>
       </c>
       <c r="H383" s="0" t="s">
         <v>134</v>
@@ -36310,25 +36303,25 @@
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B384" s="0" t="s">
         <v>807</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D384" s="0" t="s">
         <v>525</v>
       </c>
       <c r="E384" s="0" t="s">
+        <v>862</v>
+      </c>
+      <c r="F384" s="0" t="s">
+        <v>859</v>
+      </c>
+      <c r="G384" s="0" t="s">
         <v>863</v>
-      </c>
-      <c r="F384" s="0" t="s">
-        <v>860</v>
-      </c>
-      <c r="G384" s="0" t="s">
-        <v>864</v>
       </c>
       <c r="J384" s="11">
         <v>46409.125</v>
@@ -36387,25 +36380,25 @@
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B385" s="0" t="s">
         <v>807</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D385" s="0" t="s">
         <v>525</v>
       </c>
       <c r="E385" s="0" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F385" s="0" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G385" s="0" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="J385" s="11">
         <v>46413.125</v>
@@ -36467,7 +36460,7 @@
         <v>34</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D386" s="0" t="s">
         <v>50</v>
@@ -36551,7 +36544,7 @@
         <v>34</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D387" s="0" t="s">
         <v>36</v>
@@ -36637,13 +36630,13 @@
         <v>60</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D388" s="0" t="s">
         <v>218</v>
       </c>
       <c r="E388" s="0" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F388" s="0" t="s">
         <v>203</v>
@@ -36656,7 +36649,7 @@
         <v>70</v>
       </c>
       <c r="L388" s="0" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="M388" s="0" t="s">
         <v>39</v>
@@ -36714,13 +36707,13 @@
         <v>60</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>218</v>
       </c>
       <c r="E389" s="0" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F389" s="0" t="s">
         <v>203</v>
@@ -36733,7 +36726,7 @@
         <v>70</v>
       </c>
       <c r="L389" s="0" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="M389" s="0" t="s">
         <v>39</v>
@@ -36785,25 +36778,25 @@
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B390" s="0" t="s">
+        <v>874</v>
+      </c>
+      <c r="C390" s="0" t="s">
         <v>875</v>
-      </c>
-      <c r="C390" s="0" t="s">
-        <v>876</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E390" s="0" t="s">
+        <v>876</v>
+      </c>
+      <c r="F390" s="0" t="s">
         <v>877</v>
       </c>
-      <c r="F390" s="0" t="s">
-        <v>878</v>
-      </c>
       <c r="G390" s="0" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="J390" s="11">
         <v>46401.125</v>
@@ -36836,7 +36829,7 @@
         <v>44</v>
       </c>
       <c r="AC390" s="0" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AD390" s="11">
         <v>46104.56253545139</v>
@@ -36868,7 +36861,7 @@
         <v>644</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>111</v>
@@ -36954,13 +36947,13 @@
         <v>644</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E392" s="0" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F392" s="0" t="s">
         <v>326</v>
@@ -37040,13 +37033,13 @@
         <v>60</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F393" s="0" t="s">
         <v>59</v>
@@ -37059,7 +37052,7 @@
         <v>70</v>
       </c>
       <c r="L393" s="0" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="M393" s="0" t="s">
         <v>39</v>
@@ -37121,7 +37114,7 @@
         <v>644</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>111</v>
@@ -37207,7 +37200,7 @@
         <v>34</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>201</v>
@@ -37293,13 +37286,13 @@
         <v>48</v>
       </c>
       <c r="C396" s="0" t="s">
+        <v>886</v>
+      </c>
+      <c r="D396" s="0" t="s">
         <v>887</v>
       </c>
-      <c r="D396" s="0" t="s">
-        <v>888</v>
-      </c>
       <c r="E396" s="0" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F396" s="0" t="s">
         <v>243</v>
@@ -37308,7 +37301,7 @@
         <v>243</v>
       </c>
       <c r="H396" s="0" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J396" s="11">
         <v>46413.125</v>
@@ -37379,13 +37372,13 @@
         <v>48</v>
       </c>
       <c r="C397" s="0" t="s">
+        <v>889</v>
+      </c>
+      <c r="D397" s="0" t="s">
         <v>890</v>
       </c>
-      <c r="D397" s="0" t="s">
-        <v>891</v>
-      </c>
       <c r="E397" s="0" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F397" s="0" t="s">
         <v>52</v>
@@ -37394,7 +37387,7 @@
         <v>53</v>
       </c>
       <c r="H397" s="0" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J397" s="11">
         <v>46357.125</v>
@@ -37465,7 +37458,7 @@
         <v>34</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D398" s="0" t="s">
         <v>164</v>
@@ -37480,7 +37473,7 @@
         <v>53</v>
       </c>
       <c r="H398" s="0" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="J398" s="11">
         <v>46361.125</v>
@@ -37551,7 +37544,7 @@
         <v>34</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>50</v>
@@ -37566,7 +37559,7 @@
         <v>152</v>
       </c>
       <c r="H399" s="0" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J399" s="11">
         <v>46365.125</v>
@@ -37637,7 +37630,7 @@
         <v>34</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>50</v>
@@ -37652,7 +37645,7 @@
         <v>136</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J400" s="11">
         <v>46365.125</v>
@@ -37723,7 +37716,7 @@
         <v>34</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>36</v>
@@ -37738,7 +37731,7 @@
         <v>136</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J401" s="11"/>
       <c r="K401" s="0" t="s">
@@ -37807,13 +37800,13 @@
         <v>48</v>
       </c>
       <c r="C402" s="0" t="s">
+        <v>898</v>
+      </c>
+      <c r="D402" s="0" t="s">
         <v>899</v>
       </c>
-      <c r="D402" s="0" t="s">
-        <v>900</v>
-      </c>
       <c r="E402" s="0" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F402" s="0" t="s">
         <v>53</v>
@@ -37822,7 +37815,7 @@
         <v>53</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J402" s="11">
         <v>46365.125</v>
@@ -37893,7 +37886,7 @@
         <v>48</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D403" s="0" t="s">
         <v>321</v>
@@ -37908,7 +37901,7 @@
         <v>136</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J403" s="11">
         <v>46362.125</v>
@@ -37979,13 +37972,13 @@
         <v>34</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E404" s="0" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F404" s="0" t="s">
         <v>64</v>
@@ -38065,7 +38058,7 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>36</v>
@@ -38151,7 +38144,7 @@
         <v>34</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>36</v>
@@ -38237,13 +38230,13 @@
         <v>34</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E407" s="0" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F407" s="0" t="s">
         <v>438</v>
@@ -38252,7 +38245,7 @@
         <v>438</v>
       </c>
       <c r="H407" s="0" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J407" s="11"/>
       <c r="K407" s="0" t="s">
@@ -38321,13 +38314,13 @@
         <v>34</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>74</v>
       </c>
       <c r="E408" s="0" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F408" s="0" t="s">
         <v>136</v>
@@ -38336,7 +38329,7 @@
         <v>136</v>
       </c>
       <c r="H408" s="0" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J408" s="11">
         <v>46310.125</v>
@@ -38407,7 +38400,7 @@
         <v>34</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>74</v>
@@ -38496,7 +38489,7 @@
         <v>34</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>50</v>
@@ -38511,7 +38504,7 @@
         <v>338</v>
       </c>
       <c r="H410" s="0" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="J410" s="11">
         <v>46356.125</v>
@@ -38585,13 +38578,13 @@
         <v>34</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>142</v>
       </c>
       <c r="E411" s="0" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F411" s="0" t="s">
         <v>144</v>
@@ -38600,7 +38593,7 @@
         <v>144</v>
       </c>
       <c r="H411" s="0" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="J411" s="11"/>
       <c r="K411" s="0" t="s">
@@ -38672,13 +38665,13 @@
         <v>34</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F412" s="0" t="s">
         <v>95</v>
@@ -38687,7 +38680,7 @@
         <v>95</v>
       </c>
       <c r="H412" s="0" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="J412" s="11">
         <v>46310.125</v>
@@ -38761,7 +38754,7 @@
         <v>34</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>125</v>
@@ -38776,7 +38769,7 @@
         <v>59</v>
       </c>
       <c r="H413" s="0" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="J413" s="11">
         <v>46310.125</v>
@@ -38847,7 +38840,7 @@
         <v>34</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>125</v>
@@ -38862,7 +38855,7 @@
         <v>59</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="J414" s="11">
         <v>46310.125</v>
@@ -38933,13 +38926,13 @@
         <v>48</v>
       </c>
       <c r="C415" s="0" t="s">
+        <v>922</v>
+      </c>
+      <c r="D415" s="0" t="s">
         <v>923</v>
       </c>
-      <c r="D415" s="0" t="s">
-        <v>924</v>
-      </c>
       <c r="E415" s="0" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F415" s="0" t="s">
         <v>203</v>
@@ -39016,7 +39009,7 @@
         <v>34</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D416" s="0" t="s">
         <v>62</v>
@@ -39102,7 +39095,7 @@
         <v>34</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>36</v>
@@ -39117,14 +39110,14 @@
         <v>38</v>
       </c>
       <c r="H417" s="0" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="J417" s="11"/>
       <c r="K417" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L417" s="0" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M417" s="0" t="s">
         <v>39</v>
@@ -39189,7 +39182,7 @@
         <v>34</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>36</v>
@@ -39204,14 +39197,14 @@
         <v>38</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="J418" s="11"/>
       <c r="K418" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L418" s="0" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M418" s="0" t="s">
         <v>39</v>
@@ -39276,13 +39269,13 @@
         <v>48</v>
       </c>
       <c r="C419" s="0" t="s">
+        <v>929</v>
+      </c>
+      <c r="D419" s="0" t="s">
         <v>930</v>
       </c>
-      <c r="D419" s="0" t="s">
-        <v>931</v>
-      </c>
       <c r="E419" s="0" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F419" s="0" t="s">
         <v>64</v>
@@ -39359,7 +39352,7 @@
         <v>48</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D420" s="0" t="s">
         <v>321</v>
@@ -39442,13 +39435,13 @@
         <v>34</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>314</v>
       </c>
       <c r="E421" s="0" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F421" s="0" t="s">
         <v>95</v>
@@ -39457,14 +39450,14 @@
         <v>38</v>
       </c>
       <c r="H421" s="0" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="J421" s="11"/>
       <c r="K421" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L421" s="0" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="M421" s="0" t="s">
         <v>39</v>
@@ -39529,7 +39522,7 @@
         <v>48</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>387</v>
@@ -39612,13 +39605,13 @@
         <v>48</v>
       </c>
       <c r="C423" s="0" t="s">
+        <v>936</v>
+      </c>
+      <c r="D423" s="0" t="s">
         <v>937</v>
       </c>
-      <c r="D423" s="0" t="s">
-        <v>938</v>
-      </c>
       <c r="E423" s="0" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F423" s="0" t="s">
         <v>152</v>
@@ -39695,7 +39688,7 @@
         <v>60</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D424" s="0" t="s">
         <v>50</v>
@@ -39710,7 +39703,7 @@
         <v>170</v>
       </c>
       <c r="H424" s="0" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="J424" s="11">
         <v>46310.125</v>
@@ -39781,13 +39774,13 @@
         <v>60</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E425" s="0" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F425" s="0" t="s">
         <v>331</v>
@@ -39796,7 +39789,7 @@
         <v>331</v>
       </c>
       <c r="H425" s="0" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="J425" s="11">
         <v>46373.125</v>
@@ -39867,7 +39860,7 @@
         <v>60</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>79</v>
@@ -39882,7 +39875,7 @@
         <v>523</v>
       </c>
       <c r="H426" s="0" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="J426" s="11">
         <v>46310.125</v>
@@ -39956,13 +39949,13 @@
         <v>60</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E427" s="0" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F427" s="0" t="s">
         <v>171</v>
@@ -40045,7 +40038,7 @@
         <v>60</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>79</v>
@@ -40060,7 +40053,7 @@
         <v>53</v>
       </c>
       <c r="H428" s="0" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="J428" s="11">
         <v>46373.125</v>
@@ -40131,13 +40124,13 @@
         <v>60</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E429" s="0" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="F429" s="0" t="s">
         <v>257</v>
@@ -40146,7 +40139,7 @@
         <v>257</v>
       </c>
       <c r="H429" s="0" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="J429" s="11">
         <v>46310.125</v>
@@ -40217,7 +40210,7 @@
         <v>60</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>50</v>
@@ -40232,7 +40225,7 @@
         <v>152</v>
       </c>
       <c r="H430" s="0" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="J430" s="11">
         <v>46373.125</v>
@@ -40303,13 +40296,13 @@
         <v>60</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>730</v>
       </c>
       <c r="E431" s="0" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F431" s="0" t="s">
         <v>212</v>
@@ -40389,7 +40382,7 @@
         <v>60</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>249</v>
@@ -40404,7 +40397,7 @@
         <v>326</v>
       </c>
       <c r="H432" s="0" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="J432" s="11">
         <v>46310.125</v>
@@ -40475,7 +40468,7 @@
         <v>60</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D433" s="0" t="s">
         <v>259</v>
@@ -40490,7 +40483,7 @@
         <v>95</v>
       </c>
       <c r="H433" s="0" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="J433" s="11">
         <v>46310.125</v>
@@ -40561,13 +40554,13 @@
         <v>60</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>259</v>
       </c>
       <c r="E434" s="0" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F434" s="0" t="s">
         <v>170</v>
@@ -40576,7 +40569,7 @@
         <v>170</v>
       </c>
       <c r="H434" s="0" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="J434" s="11">
         <v>46310.125</v>
@@ -40650,7 +40643,7 @@
         <v>60</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>249</v>
@@ -40739,13 +40732,13 @@
         <v>60</v>
       </c>
       <c r="C436" s="0" t="s">
+        <v>961</v>
+      </c>
+      <c r="D436" s="0" t="s">
         <v>962</v>
       </c>
-      <c r="D436" s="0" t="s">
+      <c r="E436" s="0" t="s">
         <v>963</v>
-      </c>
-      <c r="E436" s="0" t="s">
-        <v>964</v>
       </c>
       <c r="F436" s="0" t="s">
         <v>293</v>
@@ -40825,7 +40818,7 @@
         <v>60</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D437" s="0" t="s">
         <v>259</v>
@@ -40914,7 +40907,7 @@
         <v>60</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>411</v>
@@ -40929,7 +40922,7 @@
         <v>171</v>
       </c>
       <c r="H438" s="0" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="J438" s="11">
         <v>46373.125</v>
@@ -41000,7 +40993,7 @@
         <v>60</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>259</v>
@@ -41086,7 +41079,7 @@
         <v>60</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D440" s="0" t="s">
         <v>259</v>
@@ -41172,7 +41165,7 @@
         <v>60</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>411</v>
@@ -41187,7 +41180,7 @@
         <v>326</v>
       </c>
       <c r="H441" s="0" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="J441" s="11">
         <v>46373.125</v>
@@ -41258,7 +41251,7 @@
         <v>60</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>259</v>
@@ -41273,7 +41266,7 @@
         <v>76</v>
       </c>
       <c r="H442" s="0" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="J442" s="11">
         <v>46310.125</v>
@@ -41344,7 +41337,7 @@
         <v>60</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>259</v>
@@ -41433,7 +41426,7 @@
         <v>60</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>411</v>
@@ -41448,7 +41441,7 @@
         <v>171</v>
       </c>
       <c r="H444" s="0" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="J444" s="11">
         <v>46373.125</v>
@@ -41519,7 +41512,7 @@
         <v>60</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>259</v>
@@ -41605,7 +41598,7 @@
         <v>60</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>164</v>
@@ -41620,7 +41613,7 @@
         <v>179</v>
       </c>
       <c r="H446" s="0" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="J446" s="11">
         <v>46310.125</v>
@@ -41691,13 +41684,13 @@
         <v>60</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E447" s="0" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F447" s="0" t="s">
         <v>501</v>
@@ -41706,7 +41699,7 @@
         <v>501</v>
       </c>
       <c r="H447" s="0" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="J447" s="11">
         <v>46373.125</v>
@@ -41777,7 +41770,7 @@
         <v>60</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>164</v>
@@ -41792,7 +41785,7 @@
         <v>517</v>
       </c>
       <c r="H448" s="0" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="J448" s="11">
         <v>46310.125</v>
@@ -41863,13 +41856,13 @@
         <v>60</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>164</v>
       </c>
       <c r="E449" s="0" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F449" s="0" t="s">
         <v>331</v>
@@ -41878,7 +41871,7 @@
         <v>331</v>
       </c>
       <c r="H449" s="0" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="J449" s="11">
         <v>46310.125</v>
@@ -41952,7 +41945,7 @@
         <v>60</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>164</v>
@@ -41967,7 +41960,7 @@
         <v>331</v>
       </c>
       <c r="H450" s="0" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="J450" s="11"/>
       <c r="K450" s="0" t="s">
@@ -42030,25 +42023,25 @@
     </row>
     <row r="451">
       <c r="A451" s="0" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B451" s="0" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C451" s="0" t="s">
+        <v>986</v>
+      </c>
+      <c r="D451" s="0" t="s">
         <v>987</v>
       </c>
-      <c r="D451" s="0" t="s">
-        <v>988</v>
-      </c>
       <c r="E451" s="0" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F451" s="0" t="s">
         <v>299</v>
       </c>
       <c r="G451" s="0" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="J451" s="11">
         <v>46310.125</v>
@@ -42081,7 +42074,7 @@
         <v>44</v>
       </c>
       <c r="AC451" s="0" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AD451" s="11">
         <v>46203.65469700231</v>
@@ -42113,13 +42106,13 @@
         <v>644</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D452" s="0" t="s">
         <v>62</v>
       </c>
       <c r="E452" s="0" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F452" s="0" t="s">
         <v>326</v>
@@ -42128,7 +42121,7 @@
         <v>326</v>
       </c>
       <c r="H452" s="0" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J452" s="11">
         <v>46365.125</v>
@@ -42199,7 +42192,7 @@
         <v>644</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>769</v>
@@ -42214,7 +42207,7 @@
         <v>212</v>
       </c>
       <c r="H453" s="0" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J453" s="11">
         <v>46365.125</v>
@@ -42285,13 +42278,13 @@
         <v>34</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E454" s="0" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F454" s="0" t="s">
         <v>87</v>
@@ -42368,7 +42361,7 @@
         <v>34</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>36</v>
@@ -42451,13 +42444,13 @@
         <v>807</v>
       </c>
       <c r="C456" s="0" t="s">
+        <v>993</v>
+      </c>
+      <c r="D456" s="0" t="s">
         <v>994</v>
       </c>
-      <c r="D456" s="0" t="s">
-        <v>995</v>
-      </c>
       <c r="E456" s="0" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F456" s="0" t="s">
         <v>203</v>
@@ -42525,7 +42518,7 @@
         <v>34</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>125</v>
@@ -42540,7 +42533,7 @@
         <v>76</v>
       </c>
       <c r="H457" s="0" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="J457" s="11">
         <v>46387.125</v>
@@ -42611,7 +42604,7 @@
         <v>34</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D458" s="0" t="s">
         <v>125</v>
@@ -42626,7 +42619,7 @@
         <v>76</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="J458" s="11">
         <v>46326.125</v>
@@ -42697,7 +42690,7 @@
         <v>34</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>50</v>
@@ -42712,7 +42705,7 @@
         <v>325</v>
       </c>
       <c r="H459" s="0" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="J459" s="11">
         <v>46326.125</v>
@@ -42783,13 +42776,13 @@
         <v>34</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E460" s="0" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F460" s="0" t="s">
         <v>133</v>
@@ -42869,13 +42862,13 @@
         <v>34</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>182</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F461" s="0" t="s">
         <v>151</v>
@@ -42884,7 +42877,7 @@
         <v>151</v>
       </c>
       <c r="H461" s="0" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="J461" s="11">
         <v>46310.125</v>
@@ -42955,13 +42948,13 @@
         <v>60</v>
       </c>
       <c r="C462" s="0" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D462" s="0" t="s">
         <v>1005</v>
       </c>
-      <c r="D462" s="0" t="s">
+      <c r="E462" s="0" t="s">
         <v>1006</v>
-      </c>
-      <c r="E462" s="0" t="s">
-        <v>1007</v>
       </c>
       <c r="F462" s="0" t="s">
         <v>417</v>
@@ -42970,7 +42963,7 @@
         <v>417</v>
       </c>
       <c r="H462" s="0" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="J462" s="11">
         <v>46310.125</v>
@@ -43038,7 +43031,7 @@
         <v>60</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>79</v>
@@ -43053,7 +43046,7 @@
         <v>331</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="J463" s="11">
         <v>46406.125</v>
@@ -43124,13 +43117,13 @@
         <v>60</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F464" s="0" t="s">
         <v>81</v>
@@ -43139,7 +43132,7 @@
         <v>231</v>
       </c>
       <c r="H464" s="0" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="J464" s="11">
         <v>46407.125</v>
@@ -43210,7 +43203,7 @@
         <v>60</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>249</v>
@@ -43225,7 +43218,7 @@
         <v>136</v>
       </c>
       <c r="H465" s="0" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="J465" s="11">
         <v>46407.125</v>
@@ -43296,7 +43289,7 @@
         <v>60</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>249</v>
@@ -43311,7 +43304,7 @@
         <v>136</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="J466" s="11">
         <v>46407.125</v>
@@ -43382,7 +43375,7 @@
         <v>60</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>769</v>
@@ -43397,7 +43390,7 @@
         <v>53</v>
       </c>
       <c r="H467" s="0" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="J467" s="11">
         <v>46406.125</v>
@@ -43468,7 +43461,7 @@
         <v>60</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>259</v>
@@ -43483,7 +43476,7 @@
         <v>76</v>
       </c>
       <c r="H468" s="0" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="J468" s="11">
         <v>46373.125</v>
@@ -43554,7 +43547,7 @@
         <v>48</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>50</v>
@@ -43640,13 +43633,13 @@
         <v>226</v>
       </c>
       <c r="C470" s="0" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D470" s="0" t="s">
         <v>1020</v>
       </c>
-      <c r="D470" s="0" t="s">
+      <c r="E470" s="0" t="s">
         <v>1021</v>
-      </c>
-      <c r="E470" s="0" t="s">
-        <v>1022</v>
       </c>
       <c r="F470" s="0" t="s">
         <v>144</v>
@@ -43655,7 +43648,7 @@
         <v>144</v>
       </c>
       <c r="H470" s="0" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="J470" s="11">
         <v>46398.125</v>
@@ -43723,13 +43716,13 @@
         <v>807</v>
       </c>
       <c r="C471" s="0" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D471" s="0" t="s">
         <v>1024</v>
       </c>
-      <c r="D471" s="0" t="s">
+      <c r="E471" s="0" t="s">
         <v>1025</v>
-      </c>
-      <c r="E471" s="0" t="s">
-        <v>1026</v>
       </c>
       <c r="F471" s="0" t="s">
         <v>203</v>
@@ -43768,7 +43761,7 @@
         <v>44</v>
       </c>
       <c r="AC471" s="0" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AD471" s="11">
         <v>46219.55652277778</v>
@@ -43800,7 +43793,7 @@
         <v>48</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>381</v>
@@ -43815,7 +43808,7 @@
         <v>338</v>
       </c>
       <c r="H472" s="0" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="J472" s="11">
         <v>46402.125</v>
@@ -43886,7 +43879,7 @@
         <v>60</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>50</v>
@@ -43901,7 +43894,7 @@
         <v>81</v>
       </c>
       <c r="H473" s="0" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="J473" s="11">
         <v>46346.125</v>
@@ -43972,13 +43965,13 @@
         <v>60</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E474" s="0" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F474" s="0" t="s">
         <v>338</v>
@@ -43987,7 +43980,7 @@
         <v>52</v>
       </c>
       <c r="H474" s="0" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="J474" s="11">
         <v>46346.125</v>
@@ -44058,7 +44051,7 @@
         <v>60</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D475" s="0" t="s">
         <v>249</v>
@@ -44073,7 +44066,7 @@
         <v>211</v>
       </c>
       <c r="H475" s="0" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="J475" s="11">
         <v>46310.125</v>
@@ -44144,7 +44137,7 @@
         <v>60</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>50</v>
@@ -44159,7 +44152,7 @@
         <v>152</v>
       </c>
       <c r="H476" s="0" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="J476" s="11">
         <v>46407.125</v>
@@ -44230,7 +44223,7 @@
         <v>60</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>259</v>
@@ -44245,7 +44238,7 @@
         <v>231</v>
       </c>
       <c r="H477" s="0" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="J477" s="11">
         <v>46407.125</v>
@@ -44316,7 +44309,7 @@
         <v>60</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D478" s="0" t="s">
         <v>259</v>
@@ -44331,7 +44324,7 @@
         <v>231</v>
       </c>
       <c r="H478" s="0" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="J478" s="11">
         <v>46407.125</v>
@@ -44402,7 +44395,7 @@
         <v>622</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D479" s="0" t="s">
         <v>218</v>
@@ -44482,13 +44475,13 @@
         <v>622</v>
       </c>
       <c r="C480" s="0" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D480" s="0" t="s">
         <v>1041</v>
       </c>
-      <c r="D480" s="0" t="s">
-        <v>1042</v>
-      </c>
       <c r="E480" s="0" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F480" s="0" t="s">
         <v>438</v>
@@ -44562,13 +44555,13 @@
         <v>48</v>
       </c>
       <c r="C481" s="0" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D481" s="0" t="s">
         <v>1043</v>
       </c>
-      <c r="D481" s="0" t="s">
-        <v>1044</v>
-      </c>
       <c r="E481" s="0" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F481" s="0" t="s">
         <v>100</v>
@@ -44648,13 +44641,13 @@
         <v>34</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>79</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F482" s="0" t="s">
         <v>38</v>
@@ -44663,7 +44656,7 @@
         <v>38</v>
       </c>
       <c r="H482" s="0" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="J482" s="11">
         <v>46310.125</v>
@@ -44734,13 +44727,13 @@
         <v>48</v>
       </c>
       <c r="C483" s="0" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D483" s="0" t="s">
         <v>1048</v>
       </c>
-      <c r="D483" s="0" t="s">
-        <v>1049</v>
-      </c>
       <c r="E483" s="0" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F483" s="0" t="s">
         <v>139</v>
@@ -44817,7 +44810,7 @@
         <v>48</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>344</v>
@@ -44900,7 +44893,7 @@
         <v>48</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>344</v>
@@ -44983,7 +44976,7 @@
         <v>34</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D486" s="0" t="s">
         <v>249</v>
@@ -44998,7 +44991,7 @@
         <v>38</v>
       </c>
       <c r="H486" s="0" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J486" s="11">
         <v>46362.125</v>
@@ -45069,7 +45062,7 @@
         <v>34</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="D487" s="0" t="s">
         <v>249</v>
@@ -45084,7 +45077,7 @@
         <v>38</v>
       </c>
       <c r="H487" s="0" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J487" s="11">
         <v>46362.125</v>
@@ -45155,7 +45148,7 @@
         <v>48</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>365</v>
@@ -45238,13 +45231,13 @@
         <v>48</v>
       </c>
       <c r="C489" s="0" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D489" s="0" t="s">
         <v>1055</v>
       </c>
-      <c r="D489" s="0" t="s">
-        <v>1056</v>
-      </c>
       <c r="E489" s="0" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F489" s="0" t="s">
         <v>257</v>
@@ -45321,13 +45314,13 @@
         <v>48</v>
       </c>
       <c r="C490" s="0" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D490" s="0" t="s">
         <v>1057</v>
       </c>
-      <c r="D490" s="0" t="s">
-        <v>1058</v>
-      </c>
       <c r="E490" s="0" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F490" s="0" t="s">
         <v>133</v>
@@ -45404,13 +45397,13 @@
         <v>48</v>
       </c>
       <c r="C491" s="0" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D491" s="0" t="s">
         <v>1059</v>
       </c>
-      <c r="D491" s="0" t="s">
-        <v>1060</v>
-      </c>
       <c r="E491" s="0" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F491" s="0" t="s">
         <v>293</v>
@@ -45487,13 +45480,13 @@
         <v>60</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>525</v>
       </c>
       <c r="E492" s="0" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F492" s="0" t="s">
         <v>107</v>
@@ -45573,13 +45566,13 @@
         <v>644</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>74</v>
       </c>
       <c r="E493" s="0" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F493" s="0" t="s">
         <v>292</v>
@@ -45588,7 +45581,7 @@
         <v>292</v>
       </c>
       <c r="H493" s="0" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="J493" s="11">
         <v>46372.125</v>
@@ -45659,19 +45652,19 @@
         <v>34</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E494" s="0" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F494" s="0" t="s">
+        <v>863</v>
+      </c>
+      <c r="G494" s="0" t="s">
         <v>1066</v>
-      </c>
-      <c r="F494" s="0" t="s">
-        <v>864</v>
-      </c>
-      <c r="G494" s="0" t="s">
-        <v>1067</v>
       </c>
       <c r="H494" s="0" t="s">
         <v>204</v>
@@ -45745,19 +45738,19 @@
         <v>34</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D495" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E495" s="0" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F495" s="0" t="s">
+        <v>863</v>
+      </c>
+      <c r="G495" s="0" t="s">
         <v>1066</v>
-      </c>
-      <c r="F495" s="0" t="s">
-        <v>864</v>
-      </c>
-      <c r="G495" s="0" t="s">
-        <v>1067</v>
       </c>
       <c r="H495" s="0" t="s">
         <v>204</v>
@@ -45831,7 +45824,7 @@
         <v>226</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D496" s="0" t="s">
         <v>525</v>
@@ -45911,13 +45904,13 @@
         <v>807</v>
       </c>
       <c r="C497" s="0" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D497" s="0" t="s">
         <v>1070</v>
       </c>
-      <c r="D497" s="0" t="s">
-        <v>1071</v>
-      </c>
       <c r="E497" s="0" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F497" s="0" t="s">
         <v>293</v>
@@ -45982,16 +45975,16 @@
         <v>814</v>
       </c>
       <c r="B498" s="0" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C498" s="0" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D498" s="0" t="s">
+        <v>937</v>
+      </c>
+      <c r="E498" s="0" t="s">
         <v>1072</v>
-      </c>
-      <c r="D498" s="0" t="s">
-        <v>938</v>
-      </c>
-      <c r="E498" s="0" t="s">
-        <v>1073</v>
       </c>
       <c r="F498" s="0" t="s">
         <v>170</v>
@@ -46004,7 +45997,7 @@
         <v>70</v>
       </c>
       <c r="L498" s="0" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="M498" s="0" t="s">
         <v>39</v>
@@ -46028,7 +46021,7 @@
         <v>43</v>
       </c>
       <c r="AC498" s="0" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AD498" s="11">
         <v>46303.38590450231</v>
@@ -46049,16 +46042,16 @@
         <v>814</v>
       </c>
       <c r="B499" s="0" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C499" s="0" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D499" s="0" t="s">
         <v>1075</v>
       </c>
-      <c r="D499" s="0" t="s">
-        <v>1076</v>
-      </c>
       <c r="E499" s="0" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F499" s="0" t="s">
         <v>171</v>
@@ -46071,7 +46064,7 @@
         <v>70</v>
       </c>
       <c r="L499" s="0" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="M499" s="0" t="s">
         <v>39</v>
@@ -46095,7 +46088,7 @@
         <v>43</v>
       </c>
       <c r="AC499" s="0" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AD499" s="11">
         <v>46303.38891412037</v>
@@ -46158,28 +46151,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>1081</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>1082</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -46187,10 +46180,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>807</v>
@@ -46208,10 +46201,10 @@
         <v>46483.125</v>
       </c>
       <c r="H2" s="0" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I2" s="0" t="s">
         <v>1084</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>1085</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>807</v>
@@ -46219,10 +46212,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>807</v>
@@ -46234,16 +46227,16 @@
         <v>46303</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G3" s="11">
         <v>46483.125</v>
       </c>
       <c r="H3" s="0" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I3" s="0" t="s">
         <v>1084</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>1085</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>807</v>
@@ -46251,10 +46244,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>644</v>
@@ -46272,10 +46265,10 @@
         <v>46480.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>648</v>
@@ -46283,10 +46276,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>226</v>
@@ -46304,10 +46297,10 @@
         <v>46476.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>226</v>
@@ -46315,10 +46308,10 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>226</v>
@@ -46330,16 +46323,16 @@
         <v>46296</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G6" s="11">
         <v>46476.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>226</v>
@@ -46347,10 +46340,10 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>34</v>
@@ -46368,10 +46361,10 @@
         <v>46474.125</v>
       </c>
       <c r="H7" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I7" s="0" t="s">
         <v>1092</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>1093</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>205</v>
@@ -46379,10 +46372,10 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>34</v>
@@ -46400,10 +46393,10 @@
         <v>46474.125</v>
       </c>
       <c r="H8" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I8" s="0" t="s">
         <v>1092</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>1093</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>205</v>
@@ -46411,10 +46404,10 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>644</v>
@@ -46432,10 +46425,10 @@
         <v>46474.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>648</v>
@@ -46443,10 +46436,10 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>644</v>
@@ -46458,16 +46451,16 @@
         <v>46294</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G10" s="11">
         <v>46474.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>648</v>
@@ -46478,7 +46471,7 @@
         <v>842</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>644</v>
@@ -46496,10 +46489,10 @@
         <v>46474.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>648</v>
@@ -46510,7 +46503,7 @@
         <v>842</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>644</v>
@@ -46522,16 +46515,16 @@
         <v>46294</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G12" s="11">
         <v>46474.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>648</v>
@@ -46539,10 +46532,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>60</v>
@@ -46554,16 +46547,16 @@
         <v>46289</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G13" s="11">
         <v>46469.125</v>
       </c>
       <c r="H13" s="0" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I13" s="0" t="s">
         <v>1098</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>1099</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>66</v>
@@ -46571,10 +46564,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>60</v>
@@ -46592,10 +46585,10 @@
         <v>46469.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>66</v>
@@ -46603,10 +46596,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>644</v>
@@ -46624,10 +46617,10 @@
         <v>46455.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>648</v>
@@ -46635,10 +46628,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>644</v>
@@ -46650,16 +46643,16 @@
         <v>46275</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G16" s="11">
         <v>46455.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>648</v>
@@ -46667,13 +46660,13 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>30</v>
@@ -46688,24 +46681,24 @@
         <v>46449.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>29</v>
@@ -46714,30 +46707,30 @@
         <v>46269</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G18" s="11">
         <v>46449.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>30</v>
@@ -46752,13 +46745,13 @@
         <v>46268</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="20">
@@ -46766,7 +46759,7 @@
         <v>551</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>34</v>
@@ -46778,19 +46771,19 @@
         <v>46267</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G20" s="11">
         <v>46447.125</v>
       </c>
       <c r="H20" s="0" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I20" s="0" t="s">
         <v>1098</v>
       </c>
-      <c r="I20" s="0" t="s">
-        <v>1099</v>
-      </c>
       <c r="J20" s="0" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="21">
@@ -46798,7 +46791,7 @@
         <v>551</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>34</v>
@@ -46816,21 +46809,21 @@
         <v>46447.125</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>60</v>
@@ -46848,10 +46841,10 @@
         <v>46446.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>610</v>
@@ -46859,10 +46852,10 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>60</v>
@@ -46880,10 +46873,10 @@
         <v>46446.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>610</v>
@@ -46894,7 +46887,7 @@
         <v>553</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>48</v>
@@ -46906,27 +46899,27 @@
         <v>46261</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G24" s="11">
         <v>46441.125</v>
       </c>
       <c r="H24" s="0" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I24" s="0" t="s">
+        <v>1098</v>
+      </c>
+      <c r="J24" s="0" t="s">
         <v>1108</v>
-      </c>
-      <c r="I24" s="0" t="s">
-        <v>1099</v>
-      </c>
-      <c r="J24" s="0" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>34</v>
@@ -46938,16 +46931,16 @@
         <v>46260</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G25" s="11">
         <v>46440.125</v>
       </c>
       <c r="H25" s="0" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I25" s="0" t="s">
         <v>1098</v>
-      </c>
-      <c r="I25" s="0" t="s">
-        <v>1099</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>205</v>
@@ -46955,10 +46948,10 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>60</v>
@@ -46976,10 +46969,10 @@
         <v>46440.125</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J26" s="0" t="s">
         <v>66</v>
@@ -46987,10 +46980,10 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>34</v>
@@ -47008,10 +47001,10 @@
         <v>46439.125</v>
       </c>
       <c r="H27" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I27" s="0" t="s">
         <v>1092</v>
-      </c>
-      <c r="I27" s="0" t="s">
-        <v>1093</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>205</v>
@@ -47022,7 +47015,7 @@
         <v>657</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>34</v>
@@ -47040,10 +47033,10 @@
         <v>46439.125</v>
       </c>
       <c r="H28" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I28" s="0" t="s">
         <v>1092</v>
-      </c>
-      <c r="I28" s="0" t="s">
-        <v>1093</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>205</v>
@@ -47051,10 +47044,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>34</v>
@@ -47072,10 +47065,10 @@
         <v>46439.125</v>
       </c>
       <c r="H29" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I29" s="0" t="s">
         <v>1092</v>
-      </c>
-      <c r="I29" s="0" t="s">
-        <v>1093</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>205</v>
@@ -47086,7 +47079,7 @@
         <v>653</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>60</v>
@@ -47104,10 +47097,10 @@
         <v>46439.125</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>610</v>
@@ -47118,7 +47111,7 @@
         <v>342</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>60</v>
@@ -47136,10 +47129,10 @@
         <v>46439.125</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>66</v>
@@ -47150,7 +47143,7 @@
         <v>472</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>60</v>
@@ -47162,16 +47155,16 @@
         <v>46255</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G32" s="11">
         <v>46435.125</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>66</v>
@@ -47182,7 +47175,7 @@
         <v>472</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>60</v>
@@ -47200,10 +47193,10 @@
         <v>46435.125</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>66</v>
@@ -47214,7 +47207,7 @@
         <v>651</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>60</v>
@@ -47232,10 +47225,10 @@
         <v>46432.125</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>610</v>
@@ -47246,7 +47239,7 @@
         <v>608</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>60</v>
@@ -47264,10 +47257,10 @@
         <v>46432.125</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>610</v>
@@ -47278,7 +47271,7 @@
         <v>607</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>34</v>
@@ -47296,10 +47289,10 @@
         <v>46432.125</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>45</v>
@@ -47307,10 +47300,10 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>34</v>
@@ -47328,10 +47321,10 @@
         <v>46432.125</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>45</v>
@@ -47342,7 +47335,7 @@
         <v>607</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>34</v>
@@ -47354,16 +47347,16 @@
         <v>46252</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G38" s="11">
         <v>46432.125</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="J38" s="0" t="s">
         <v>45</v>
@@ -47371,10 +47364,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>48</v>
@@ -47386,16 +47379,16 @@
         <v>46251</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G39" s="11">
         <v>46431.125</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="J39" s="0" t="s">
         <v>56</v>
@@ -47403,10 +47396,10 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>48</v>
@@ -47424,10 +47417,10 @@
         <v>46431.125</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J40" s="0" t="s">
         <v>56</v>
@@ -47435,10 +47428,10 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>48</v>
@@ -47456,10 +47449,10 @@
         <v>46431.125</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="J41" s="0" t="s">
         <v>56</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46310.34958142361</v>
+        <v>46310.39970675926</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -8562,7 +8562,7 @@
         <v>39</v>
       </c>
       <c r="J59" s="11">
-        <v>46310.125</v>
+        <v>46399.125</v>
       </c>
       <c r="K59" s="0" t="s">
         <v>55</v>
@@ -8577,7 +8577,7 @@
         <v>42</v>
       </c>
       <c r="O59" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q59" s="0" t="s">
         <v>42</v>
@@ -35146,7 +35146,7 @@
         <v>832</v>
       </c>
       <c r="J370" s="11">
-        <v>46310.125</v>
+        <v>46392.125</v>
       </c>
       <c r="K370" s="0" t="s">
         <v>55</v>
@@ -35161,7 +35161,7 @@
         <v>42</v>
       </c>
       <c r="O370" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q370" s="0" t="s">
         <v>42</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -21,7 +21,7 @@
     <t>Usuário Geração:</t>
   </si>
   <si>
-    <t>Jadson Rubens Rocha de Oliveira</t>
+    <t>GABRIELLE MENDES DE ANDRADE</t>
   </si>
   <si>
     <t>Ambiente:</t>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46310.39970675926</v>
+        <v>46310.40229449074</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1120">
   <si>
     <t>Geração:</t>
   </si>
@@ -2992,12 +2992,6 @@
   </si>
   <si>
     <t>GYR7G61</t>
-  </si>
-  <si>
-    <t>BYJ1932</t>
-  </si>
-  <si>
-    <t>FORD/CARGO 1719 B</t>
   </si>
   <si>
     <t>HKE0E99</t>
@@ -3559,7 +3553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ499"/>
+  <dimension ref="A1:AJ498"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -3570,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46310.40229449074</v>
+        <v>46310.62605564815</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -42044,13 +42038,13 @@
         <v>877</v>
       </c>
       <c r="J451" s="11">
-        <v>46310.125</v>
+        <v>46383.125</v>
       </c>
       <c r="K451" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L451" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M451" s="0" t="s">
         <v>39</v>
@@ -42059,7 +42053,7 @@
         <v>42</v>
       </c>
       <c r="O451" s="11">
-        <v>46310.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q451" s="0" t="s">
         <v>44</v>
@@ -42438,28 +42432,31 @@
     </row>
     <row r="456">
       <c r="A456" s="0" t="s">
-        <v>658</v>
+        <v>33</v>
       </c>
       <c r="B456" s="0" t="s">
-        <v>807</v>
+        <v>34</v>
       </c>
       <c r="C456" s="0" t="s">
         <v>993</v>
       </c>
       <c r="D456" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="E456" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="F456" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G456" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="H456" s="0" t="s">
         <v>994</v>
       </c>
-      <c r="E456" s="0" t="s">
-        <v>994</v>
-      </c>
-      <c r="F456" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="G456" s="0" t="s">
-        <v>211</v>
-      </c>
       <c r="J456" s="11">
-        <v>46390.125</v>
+        <v>46387.125</v>
       </c>
       <c r="K456" s="0" t="s">
         <v>55</v>
@@ -42471,43 +42468,52 @@
         <v>39</v>
       </c>
       <c r="N456" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="O456" s="11">
+        <v>46387.125</v>
       </c>
       <c r="Q456" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="R456" s="11">
+        <v>46396.125</v>
       </c>
       <c r="T456" s="0" t="s">
         <v>43</v>
       </c>
       <c r="W456" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="X456" s="11">
+        <v>46568.125</v>
       </c>
       <c r="Z456" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC456" s="0" t="s">
-        <v>807</v>
+        <v>45</v>
       </c>
       <c r="AD456" s="11">
-        <v>46209.58030755787</v>
+        <v>46210.35791641204</v>
       </c>
       <c r="AE456" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF456" s="3">
-        <v>46210.620775462965</v>
+        <v>46218.460335648146</v>
       </c>
       <c r="AG456" s="3">
-        <v>46390.125</v>
+        <v>46398.125</v>
       </c>
       <c r="AH456" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI456" s="3">
-        <v>46211.25809027778</v>
+        <v>46240.66538194445</v>
       </c>
       <c r="AJ456" s="3">
-        <v>46391.125</v>
+        <v>46420.125</v>
       </c>
     </row>
     <row r="457">
@@ -42533,16 +42539,16 @@
         <v>76</v>
       </c>
       <c r="H457" s="0" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="J457" s="11">
-        <v>46387.125</v>
+        <v>46326.125</v>
       </c>
       <c r="K457" s="0" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L457" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M457" s="0" t="s">
         <v>39</v>
@@ -42551,7 +42557,7 @@
         <v>42</v>
       </c>
       <c r="O457" s="11">
-        <v>46387.125</v>
+        <v>46326.125</v>
       </c>
       <c r="Q457" s="0" t="s">
         <v>42</v>
@@ -42575,13 +42581,13 @@
         <v>45</v>
       </c>
       <c r="AD457" s="11">
-        <v>46210.35791641204</v>
+        <v>46210.35903236111</v>
       </c>
       <c r="AE457" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF457" s="3">
-        <v>46218.460335648146</v>
+        <v>46218.45748842593</v>
       </c>
       <c r="AG457" s="3">
         <v>46398.125</v>
@@ -42590,36 +42596,36 @@
         <v>42</v>
       </c>
       <c r="AI457" s="3">
-        <v>46240.66538194445</v>
+        <v>46218.35574074074</v>
       </c>
       <c r="AJ457" s="3">
-        <v>46420.125</v>
+        <v>46398.125</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="0" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B458" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D458" s="0" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="E458" s="0" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="F458" s="0" t="s">
-        <v>38</v>
+        <v>325</v>
       </c>
       <c r="G458" s="0" t="s">
-        <v>76</v>
+        <v>325</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="J458" s="11">
         <v>46326.125</v>
@@ -42643,7 +42649,7 @@
         <v>42</v>
       </c>
       <c r="R458" s="11">
-        <v>46396.125</v>
+        <v>46397.125</v>
       </c>
       <c r="T458" s="0" t="s">
         <v>43</v>
@@ -42661,22 +42667,22 @@
         <v>45</v>
       </c>
       <c r="AD458" s="11">
-        <v>46210.35903236111</v>
+        <v>46210.360465</v>
       </c>
       <c r="AE458" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF458" s="3">
-        <v>46218.45748842593</v>
-      </c>
-      <c r="AG458" s="3">
-        <v>46398.125</v>
+        <v>43</v>
+      </c>
+      <c r="AF458" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG458" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="AH458" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI458" s="3">
-        <v>46218.35574074074</v>
+        <v>46218.35209490741</v>
       </c>
       <c r="AJ458" s="3">
         <v>46398.125</v>
@@ -42690,25 +42696,25 @@
         <v>34</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>50</v>
       </c>
       <c r="E459" s="0" t="s">
-        <v>58</v>
+        <v>998</v>
       </c>
       <c r="F459" s="0" t="s">
-        <v>325</v>
+        <v>133</v>
       </c>
       <c r="G459" s="0" t="s">
-        <v>325</v>
+        <v>133</v>
       </c>
       <c r="H459" s="0" t="s">
-        <v>996</v>
+        <v>552</v>
       </c>
       <c r="J459" s="11">
-        <v>46326.125</v>
+        <v>46310.125</v>
       </c>
       <c r="K459" s="0" t="s">
         <v>40</v>
@@ -42723,13 +42729,13 @@
         <v>42</v>
       </c>
       <c r="O459" s="11">
-        <v>46326.125</v>
+        <v>46310.125</v>
       </c>
       <c r="Q459" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R459" s="11">
-        <v>46397.125</v>
+        <v>46394.125</v>
       </c>
       <c r="T459" s="0" t="s">
         <v>43</v>
@@ -42738,7 +42744,7 @@
         <v>42</v>
       </c>
       <c r="X459" s="11">
-        <v>46568.125</v>
+        <v>46561.125</v>
       </c>
       <c r="Z459" s="0" t="s">
         <v>44</v>
@@ -42747,7 +42753,7 @@
         <v>45</v>
       </c>
       <c r="AD459" s="11">
-        <v>46210.360465</v>
+        <v>46210.596557997684</v>
       </c>
       <c r="AE459" s="0" t="s">
         <v>43</v>
@@ -42762,15 +42768,15 @@
         <v>42</v>
       </c>
       <c r="AI459" s="3">
-        <v>46218.35209490741</v>
+        <v>46252.25362268519</v>
       </c>
       <c r="AJ459" s="3">
-        <v>46398.125</v>
+        <v>46432.125</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="0" t="s">
-        <v>47</v>
+        <v>176</v>
       </c>
       <c r="B460" s="0" t="s">
         <v>34</v>
@@ -42779,19 +42785,19 @@
         <v>999</v>
       </c>
       <c r="D460" s="0" t="s">
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="E460" s="0" t="s">
         <v>1000</v>
       </c>
       <c r="F460" s="0" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G460" s="0" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="H460" s="0" t="s">
-        <v>552</v>
+        <v>1001</v>
       </c>
       <c r="J460" s="11">
         <v>46310.125</v>
@@ -42800,7 +42806,7 @@
         <v>40</v>
       </c>
       <c r="L460" s="0" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="M460" s="0" t="s">
         <v>39</v>
@@ -42815,16 +42821,16 @@
         <v>42</v>
       </c>
       <c r="R460" s="11">
-        <v>46394.125</v>
+        <v>46339.125</v>
       </c>
       <c r="T460" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W460" s="0" t="s">
         <v>42</v>
       </c>
       <c r="X460" s="11">
-        <v>46561.125</v>
+        <v>46581.125</v>
       </c>
       <c r="Z460" s="0" t="s">
         <v>44</v>
@@ -42833,25 +42839,25 @@
         <v>45</v>
       </c>
       <c r="AD460" s="11">
-        <v>46210.596557997684</v>
+        <v>46216.637770243055</v>
       </c>
       <c r="AE460" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF460" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG460" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="AF460" s="3">
+        <v>46219.5914708912</v>
+      </c>
+      <c r="AG460" s="3">
+        <v>46399.125</v>
       </c>
       <c r="AH460" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI460" s="3">
-        <v>46252.25362268519</v>
+        <v>46219.38619212963</v>
       </c>
       <c r="AJ460" s="3">
-        <v>46432.125</v>
+        <v>46399.125</v>
       </c>
     </row>
     <row r="461">
@@ -42859,25 +42865,25 @@
         <v>176</v>
       </c>
       <c r="B461" s="0" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D461" s="0" t="s">
-        <v>182</v>
+        <v>1003</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="F461" s="0" t="s">
-        <v>151</v>
+        <v>417</v>
       </c>
       <c r="G461" s="0" t="s">
-        <v>151</v>
+        <v>417</v>
       </c>
       <c r="H461" s="0" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="J461" s="11">
         <v>46310.125</v>
@@ -42886,7 +42892,7 @@
         <v>40</v>
       </c>
       <c r="L461" s="0" t="s">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="M461" s="0" t="s">
         <v>39</v>
@@ -42901,78 +42907,75 @@
         <v>42</v>
       </c>
       <c r="R461" s="11">
-        <v>46339.125</v>
+        <v>46407.125</v>
       </c>
       <c r="T461" s="0" t="s">
         <v>44</v>
       </c>
       <c r="W461" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="X461" s="11">
-        <v>46581.125</v>
+        <v>44</v>
       </c>
       <c r="Z461" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC461" s="0" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="AD461" s="11">
-        <v>46216.637770243055</v>
+        <v>46218.44307796296</v>
       </c>
       <c r="AE461" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF461" s="3">
-        <v>46219.5914708912</v>
+        <v>46220.43489894676</v>
       </c>
       <c r="AG461" s="3">
-        <v>46399.125</v>
+        <v>46400.125</v>
       </c>
       <c r="AH461" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI461" s="3">
-        <v>46219.38619212963</v>
+        <v>46232.581296296295</v>
       </c>
       <c r="AJ461" s="3">
-        <v>46399.125</v>
+        <v>46412.125</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="0" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="B462" s="0" t="s">
         <v>60</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D462" s="0" t="s">
-        <v>1005</v>
+        <v>79</v>
       </c>
       <c r="E462" s="0" t="s">
-        <v>1006</v>
+        <v>546</v>
       </c>
       <c r="F462" s="0" t="s">
-        <v>417</v>
+        <v>331</v>
       </c>
       <c r="G462" s="0" t="s">
-        <v>417</v>
+        <v>331</v>
       </c>
       <c r="H462" s="0" t="s">
         <v>1007</v>
       </c>
       <c r="J462" s="11">
-        <v>46310.125</v>
+        <v>46406.125</v>
       </c>
       <c r="K462" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L462" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M462" s="0" t="s">
         <v>39</v>
@@ -42981,7 +42984,7 @@
         <v>42</v>
       </c>
       <c r="O462" s="11">
-        <v>46310.125</v>
+        <v>46645.125</v>
       </c>
       <c r="Q462" s="0" t="s">
         <v>42</v>
@@ -42990,10 +42993,13 @@
         <v>46407.125</v>
       </c>
       <c r="T462" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W462" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="X462" s="11">
+        <v>46574.125</v>
       </c>
       <c r="Z462" s="0" t="s">
         <v>44</v>
@@ -43002,25 +43008,25 @@
         <v>66</v>
       </c>
       <c r="AD462" s="11">
-        <v>46218.44307796296</v>
+        <v>46218.46306094907</v>
       </c>
       <c r="AE462" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF462" s="3">
-        <v>46220.43489894676</v>
-      </c>
-      <c r="AG462" s="3">
-        <v>46400.125</v>
+        <v>43</v>
+      </c>
+      <c r="AF462" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG462" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="AH462" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI462" s="3">
-        <v>46232.581296296295</v>
+        <v>46226.5053587963</v>
       </c>
       <c r="AJ462" s="3">
-        <v>46412.125</v>
+        <v>46406.125</v>
       </c>
     </row>
     <row r="463">
@@ -43037,19 +43043,19 @@
         <v>79</v>
       </c>
       <c r="E463" s="0" t="s">
-        <v>546</v>
+        <v>1009</v>
       </c>
       <c r="F463" s="0" t="s">
-        <v>331</v>
+        <v>81</v>
       </c>
       <c r="G463" s="0" t="s">
-        <v>331</v>
+        <v>231</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="J463" s="11">
-        <v>46406.125</v>
+        <v>46407.125</v>
       </c>
       <c r="K463" s="0" t="s">
         <v>55</v>
@@ -43064,7 +43070,7 @@
         <v>42</v>
       </c>
       <c r="O463" s="11">
-        <v>46645.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q463" s="0" t="s">
         <v>42</v>
@@ -43079,7 +43085,7 @@
         <v>42</v>
       </c>
       <c r="X463" s="11">
-        <v>46574.125</v>
+        <v>46520.125</v>
       </c>
       <c r="Z463" s="0" t="s">
         <v>44</v>
@@ -43088,7 +43094,7 @@
         <v>66</v>
       </c>
       <c r="AD463" s="11">
-        <v>46218.46306094907</v>
+        <v>46218.464618032405</v>
       </c>
       <c r="AE463" s="0" t="s">
         <v>43</v>
@@ -43103,36 +43109,36 @@
         <v>42</v>
       </c>
       <c r="AI463" s="3">
-        <v>46226.5053587963</v>
+        <v>46227.54025462963</v>
       </c>
       <c r="AJ463" s="3">
-        <v>46406.125</v>
+        <v>46407.125</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="0" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="B464" s="0" t="s">
         <v>60</v>
       </c>
       <c r="C464" s="0" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D464" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E464" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F464" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="G464" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="H464" s="0" t="s">
         <v>1010</v>
-      </c>
-      <c r="D464" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="E464" s="0" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F464" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="G464" s="0" t="s">
-        <v>231</v>
-      </c>
-      <c r="H464" s="0" t="s">
-        <v>1012</v>
       </c>
       <c r="J464" s="11">
         <v>46407.125</v>
@@ -43150,7 +43156,7 @@
         <v>42</v>
       </c>
       <c r="O464" s="11">
-        <v>46675.125</v>
+        <v>46645.125</v>
       </c>
       <c r="Q464" s="0" t="s">
         <v>42</v>
@@ -43168,28 +43174,28 @@
         <v>46520.125</v>
       </c>
       <c r="Z464" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC464" s="0" t="s">
         <v>66</v>
       </c>
       <c r="AD464" s="11">
-        <v>46218.464618032405</v>
+        <v>46218.46534241898</v>
       </c>
       <c r="AE464" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF464" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG464" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="AF464" s="3">
+        <v>46227.46511574074</v>
+      </c>
+      <c r="AG464" s="3">
+        <v>46407.125</v>
       </c>
       <c r="AH464" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI464" s="3">
-        <v>46227.54025462963</v>
+        <v>46227.54436342593</v>
       </c>
       <c r="AJ464" s="3">
         <v>46407.125</v>
@@ -43203,7 +43209,7 @@
         <v>60</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>249</v>
@@ -43218,7 +43224,7 @@
         <v>136</v>
       </c>
       <c r="H465" s="0" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="J465" s="11">
         <v>46407.125</v>
@@ -43260,13 +43266,13 @@
         <v>66</v>
       </c>
       <c r="AD465" s="11">
-        <v>46218.46534241898</v>
+        <v>46218.46588546296</v>
       </c>
       <c r="AE465" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF465" s="3">
-        <v>46227.46511574074</v>
+        <v>46227.46959490741</v>
       </c>
       <c r="AG465" s="3">
         <v>46407.125</v>
@@ -43275,7 +43281,7 @@
         <v>42</v>
       </c>
       <c r="AI465" s="3">
-        <v>46227.54436342593</v>
+        <v>46227.54728009259</v>
       </c>
       <c r="AJ465" s="3">
         <v>46407.125</v>
@@ -43289,25 +43295,25 @@
         <v>60</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D466" s="0" t="s">
-        <v>249</v>
+        <v>769</v>
       </c>
       <c r="E466" s="0" t="s">
-        <v>37</v>
+        <v>770</v>
       </c>
       <c r="F466" s="0" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="G466" s="0" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="J466" s="11">
-        <v>46407.125</v>
+        <v>46406.125</v>
       </c>
       <c r="K466" s="0" t="s">
         <v>55</v>
@@ -43337,7 +43343,7 @@
         <v>42</v>
       </c>
       <c r="X466" s="11">
-        <v>46520.125</v>
+        <v>46574.125</v>
       </c>
       <c r="Z466" s="0" t="s">
         <v>43</v>
@@ -43346,25 +43352,25 @@
         <v>66</v>
       </c>
       <c r="AD466" s="11">
-        <v>46218.46588546296</v>
+        <v>46218.468623078705</v>
       </c>
       <c r="AE466" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF466" s="3">
-        <v>46227.46959490741</v>
+        <v>46226.54440972222</v>
       </c>
       <c r="AG466" s="3">
-        <v>46407.125</v>
+        <v>46406.125</v>
       </c>
       <c r="AH466" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI466" s="3">
-        <v>46227.54728009259</v>
+        <v>46226.50953703704</v>
       </c>
       <c r="AJ466" s="3">
-        <v>46407.125</v>
+        <v>46406.125</v>
       </c>
     </row>
     <row r="467">
@@ -43375,25 +43381,25 @@
         <v>60</v>
       </c>
       <c r="C467" s="0" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D467" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E467" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="F467" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="G467" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="H467" s="0" t="s">
         <v>1015</v>
       </c>
-      <c r="D467" s="0" t="s">
-        <v>769</v>
-      </c>
-      <c r="E467" s="0" t="s">
-        <v>770</v>
-      </c>
-      <c r="F467" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="G467" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="H467" s="0" t="s">
-        <v>1009</v>
-      </c>
       <c r="J467" s="11">
-        <v>46406.125</v>
+        <v>46373.125</v>
       </c>
       <c r="K467" s="0" t="s">
         <v>55</v>
@@ -43408,13 +43414,13 @@
         <v>42</v>
       </c>
       <c r="O467" s="11">
-        <v>46645.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q467" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R467" s="11">
-        <v>46407.125</v>
+        <v>46373.125</v>
       </c>
       <c r="T467" s="0" t="s">
         <v>43</v>
@@ -43423,7 +43429,7 @@
         <v>42</v>
       </c>
       <c r="X467" s="11">
-        <v>46574.125</v>
+        <v>46534.125</v>
       </c>
       <c r="Z467" s="0" t="s">
         <v>43</v>
@@ -43432,54 +43438,54 @@
         <v>66</v>
       </c>
       <c r="AD467" s="11">
-        <v>46218.468623078705</v>
+        <v>46218.47871915509</v>
       </c>
       <c r="AE467" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF467" s="3">
-        <v>46226.54440972222</v>
+        <v>46235.23940972222</v>
       </c>
       <c r="AG467" s="3">
-        <v>46406.125</v>
+        <v>46415.125</v>
       </c>
       <c r="AH467" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI467" s="3">
-        <v>46226.50953703704</v>
+        <v>46234.70491898148</v>
       </c>
       <c r="AJ467" s="3">
-        <v>46406.125</v>
+        <v>46414.125</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="0" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="B468" s="0" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C468" s="0" t="s">
         <v>1016</v>
       </c>
       <c r="D468" s="0" t="s">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="E468" s="0" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F468" s="0" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="G468" s="0" t="s">
         <v>76</v>
       </c>
       <c r="H468" s="0" t="s">
-        <v>1017</v>
+        <v>134</v>
       </c>
       <c r="J468" s="11">
-        <v>46373.125</v>
+        <v>46399.125</v>
       </c>
       <c r="K468" s="0" t="s">
         <v>55</v>
@@ -43494,13 +43500,13 @@
         <v>42</v>
       </c>
       <c r="O468" s="11">
-        <v>46675.125</v>
+        <v>46617.125</v>
       </c>
       <c r="Q468" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R468" s="11">
-        <v>46373.125</v>
+        <v>46411.125</v>
       </c>
       <c r="T468" s="0" t="s">
         <v>43</v>
@@ -43509,63 +43515,63 @@
         <v>42</v>
       </c>
       <c r="X468" s="11">
-        <v>46534.125</v>
+        <v>46654.125</v>
       </c>
       <c r="Z468" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC468" s="0" t="s">
-        <v>66</v>
+        <v>294</v>
       </c>
       <c r="AD468" s="11">
-        <v>46218.47871915509</v>
+        <v>46218.47940927083</v>
       </c>
       <c r="AE468" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF468" s="3">
-        <v>46235.23940972222</v>
-      </c>
-      <c r="AG468" s="3">
-        <v>46415.125</v>
+        <v>43</v>
+      </c>
+      <c r="AF468" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG468" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="AH468" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI468" s="3">
-        <v>46234.70491898148</v>
+        <v>46219.58111111111</v>
       </c>
       <c r="AJ468" s="3">
-        <v>46414.125</v>
+        <v>46399.125</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="0" t="s">
-        <v>47</v>
+        <v>245</v>
       </c>
       <c r="B469" s="0" t="s">
-        <v>48</v>
+        <v>226</v>
       </c>
       <c r="C469" s="0" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D469" s="0" t="s">
         <v>1018</v>
       </c>
-      <c r="D469" s="0" t="s">
-        <v>50</v>
-      </c>
       <c r="E469" s="0" t="s">
-        <v>252</v>
+        <v>1019</v>
       </c>
       <c r="F469" s="0" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="G469" s="0" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="H469" s="0" t="s">
-        <v>134</v>
+        <v>1020</v>
       </c>
       <c r="J469" s="11">
-        <v>46399.125</v>
+        <v>46398.125</v>
       </c>
       <c r="K469" s="0" t="s">
         <v>55</v>
@@ -43580,31 +43586,28 @@
         <v>42</v>
       </c>
       <c r="O469" s="11">
-        <v>46617.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q469" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R469" s="11">
-        <v>46411.125</v>
+        <v>46402.125</v>
       </c>
       <c r="T469" s="0" t="s">
         <v>43</v>
       </c>
       <c r="W469" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="X469" s="11">
-        <v>46654.125</v>
+        <v>44</v>
       </c>
       <c r="Z469" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC469" s="0" t="s">
-        <v>294</v>
+        <v>226</v>
       </c>
       <c r="AD469" s="11">
-        <v>46218.47940927083</v>
+        <v>46218.81741611111</v>
       </c>
       <c r="AE469" s="0" t="s">
         <v>43</v>
@@ -43619,45 +43622,42 @@
         <v>42</v>
       </c>
       <c r="AI469" s="3">
-        <v>46219.58111111111</v>
+        <v>46218.82217137732</v>
       </c>
       <c r="AJ469" s="3">
-        <v>46399.125</v>
+        <v>46398.125</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="0" t="s">
-        <v>245</v>
+        <v>658</v>
       </c>
       <c r="B470" s="0" t="s">
-        <v>226</v>
+        <v>807</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D470" s="0" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="E470" s="0" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="F470" s="0" t="s">
-        <v>144</v>
+        <v>203</v>
       </c>
       <c r="G470" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="H470" s="0" t="s">
-        <v>1022</v>
+        <v>211</v>
       </c>
       <c r="J470" s="11">
-        <v>46398.125</v>
+        <v>46326.125</v>
       </c>
       <c r="K470" s="0" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L470" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M470" s="0" t="s">
         <v>39</v>
@@ -43666,78 +43666,78 @@
         <v>42</v>
       </c>
       <c r="O470" s="11">
-        <v>46675.125</v>
+        <v>46326.125</v>
       </c>
       <c r="Q470" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="R470" s="11">
-        <v>46402.125</v>
+        <v>44</v>
       </c>
       <c r="T470" s="0" t="s">
         <v>43</v>
       </c>
       <c r="W470" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z470" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC470" s="0" t="s">
-        <v>226</v>
+        <v>1024</v>
       </c>
       <c r="AD470" s="11">
-        <v>46218.81741611111</v>
+        <v>46219.55652277778</v>
       </c>
       <c r="AE470" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF470" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG470" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="AF470" s="3">
+        <v>46219.558236516204</v>
+      </c>
+      <c r="AG470" s="3">
+        <v>46399.125</v>
       </c>
       <c r="AH470" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI470" s="3">
-        <v>46218.82217137732</v>
+        <v>46219.563319699075</v>
       </c>
       <c r="AJ470" s="3">
-        <v>46398.125</v>
+        <v>46399.125</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="0" t="s">
-        <v>658</v>
+        <v>47</v>
       </c>
       <c r="B471" s="0" t="s">
-        <v>807</v>
+        <v>48</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D471" s="0" t="s">
-        <v>1024</v>
+        <v>381</v>
       </c>
       <c r="E471" s="0" t="s">
-        <v>1025</v>
+        <v>381</v>
       </c>
       <c r="F471" s="0" t="s">
-        <v>203</v>
+        <v>338</v>
       </c>
       <c r="G471" s="0" t="s">
-        <v>211</v>
+        <v>338</v>
+      </c>
+      <c r="H471" s="0" t="s">
+        <v>1026</v>
       </c>
       <c r="J471" s="11">
-        <v>46326.125</v>
+        <v>46402.125</v>
       </c>
       <c r="K471" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L471" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M471" s="0" t="s">
         <v>39</v>
@@ -43746,43 +43746,49 @@
         <v>42</v>
       </c>
       <c r="O471" s="11">
-        <v>46326.125</v>
+        <v>46752.125</v>
       </c>
       <c r="Q471" s="0" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="R471" s="11">
+        <v>46402.125</v>
       </c>
       <c r="T471" s="0" t="s">
         <v>43</v>
       </c>
       <c r="W471" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="X471" s="11">
+        <v>46402.125</v>
       </c>
       <c r="Z471" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC471" s="0" t="s">
-        <v>1026</v>
+        <v>56</v>
       </c>
       <c r="AD471" s="11">
-        <v>46219.55652277778</v>
+        <v>46220.63964091435</v>
       </c>
       <c r="AE471" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF471" s="3">
-        <v>46219.558236516204</v>
-      </c>
-      <c r="AG471" s="3">
-        <v>46399.125</v>
+        <v>43</v>
+      </c>
+      <c r="AF471" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG471" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="AH471" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI471" s="3">
-        <v>46219.563319699075</v>
+        <v>46239.3417350463</v>
       </c>
       <c r="AJ471" s="3">
-        <v>46399.125</v>
+        <v>46419.125</v>
       </c>
     </row>
     <row r="472">
@@ -43790,28 +43796,28 @@
         <v>47</v>
       </c>
       <c r="B472" s="0" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C472" s="0" t="s">
         <v>1027</v>
       </c>
       <c r="D472" s="0" t="s">
-        <v>381</v>
+        <v>50</v>
       </c>
       <c r="E472" s="0" t="s">
-        <v>381</v>
+        <v>539</v>
       </c>
       <c r="F472" s="0" t="s">
-        <v>338</v>
+        <v>81</v>
       </c>
       <c r="G472" s="0" t="s">
-        <v>338</v>
+        <v>81</v>
       </c>
       <c r="H472" s="0" t="s">
         <v>1028</v>
       </c>
       <c r="J472" s="11">
-        <v>46402.125</v>
+        <v>46346.125</v>
       </c>
       <c r="K472" s="0" t="s">
         <v>55</v>
@@ -43826,13 +43832,13 @@
         <v>42</v>
       </c>
       <c r="O472" s="11">
-        <v>46752.125</v>
+        <v>46498.125</v>
       </c>
       <c r="Q472" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R472" s="11">
-        <v>46402.125</v>
+        <v>46346.125</v>
       </c>
       <c r="T472" s="0" t="s">
         <v>43</v>
@@ -43841,16 +43847,16 @@
         <v>42</v>
       </c>
       <c r="X472" s="11">
-        <v>46402.125</v>
+        <v>46584.125</v>
       </c>
       <c r="Z472" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC472" s="0" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AD472" s="11">
-        <v>46220.63964091435</v>
+        <v>46223.43756657407</v>
       </c>
       <c r="AE472" s="0" t="s">
         <v>43</v>
@@ -43865,15 +43871,15 @@
         <v>42</v>
       </c>
       <c r="AI472" s="3">
-        <v>46239.3417350463</v>
+        <v>46226.55027777778</v>
       </c>
       <c r="AJ472" s="3">
-        <v>46419.125</v>
+        <v>46406.125</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="0" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="B473" s="0" t="s">
         <v>60</v>
@@ -43882,19 +43888,19 @@
         <v>1029</v>
       </c>
       <c r="D473" s="0" t="s">
-        <v>50</v>
+        <v>249</v>
       </c>
       <c r="E473" s="0" t="s">
-        <v>539</v>
+        <v>1030</v>
       </c>
       <c r="F473" s="0" t="s">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="G473" s="0" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H473" s="0" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="J473" s="11">
         <v>46346.125</v>
@@ -43912,7 +43918,7 @@
         <v>42</v>
       </c>
       <c r="O473" s="11">
-        <v>46498.125</v>
+        <v>46492.125</v>
       </c>
       <c r="Q473" s="0" t="s">
         <v>42</v>
@@ -43930,31 +43936,31 @@
         <v>46584.125</v>
       </c>
       <c r="Z473" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC473" s="0" t="s">
         <v>66</v>
       </c>
       <c r="AD473" s="11">
-        <v>46223.43756657407</v>
+        <v>46223.44143421296</v>
       </c>
       <c r="AE473" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF473" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG473" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="AF473" s="3">
+        <v>46227.258576388886</v>
+      </c>
+      <c r="AG473" s="3">
+        <v>46407.125</v>
       </c>
       <c r="AH473" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI473" s="3">
-        <v>46226.55027777778</v>
+        <v>46227.32655092593</v>
       </c>
       <c r="AJ473" s="3">
-        <v>46406.125</v>
+        <v>46407.125</v>
       </c>
     </row>
     <row r="474">
@@ -43971,25 +43977,25 @@
         <v>249</v>
       </c>
       <c r="E474" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F474" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="G474" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="H474" s="0" t="s">
         <v>1032</v>
       </c>
-      <c r="F474" s="0" t="s">
-        <v>338</v>
-      </c>
-      <c r="G474" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="H474" s="0" t="s">
-        <v>1030</v>
-      </c>
       <c r="J474" s="11">
-        <v>46346.125</v>
+        <v>46310.125</v>
       </c>
       <c r="K474" s="0" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L474" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M474" s="0" t="s">
         <v>39</v>
@@ -43998,7 +44004,7 @@
         <v>42</v>
       </c>
       <c r="O474" s="11">
-        <v>46492.125</v>
+        <v>46310.125</v>
       </c>
       <c r="Q474" s="0" t="s">
         <v>42</v>
@@ -44013,7 +44019,7 @@
         <v>42</v>
       </c>
       <c r="X474" s="11">
-        <v>46584.125</v>
+        <v>46589.125</v>
       </c>
       <c r="Z474" s="0" t="s">
         <v>43</v>
@@ -44022,30 +44028,30 @@
         <v>66</v>
       </c>
       <c r="AD474" s="11">
-        <v>46223.44143421296</v>
+        <v>46223.580042650465</v>
       </c>
       <c r="AE474" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF474" s="3">
-        <v>46227.258576388886</v>
+        <v>46226.28457175926</v>
       </c>
       <c r="AG474" s="3">
-        <v>46407.125</v>
+        <v>46406.125</v>
       </c>
       <c r="AH474" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI474" s="3">
-        <v>46227.32655092593</v>
+        <v>46226.298842592594</v>
       </c>
       <c r="AJ474" s="3">
-        <v>46407.125</v>
+        <v>46406.125</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="0" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="B475" s="0" t="s">
         <v>60</v>
@@ -44054,28 +44060,28 @@
         <v>1033</v>
       </c>
       <c r="D475" s="0" t="s">
-        <v>249</v>
+        <v>50</v>
       </c>
       <c r="E475" s="0" t="s">
-        <v>37</v>
+        <v>167</v>
       </c>
       <c r="F475" s="0" t="s">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="G475" s="0" t="s">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="H475" s="0" t="s">
         <v>1034</v>
       </c>
       <c r="J475" s="11">
-        <v>46310.125</v>
+        <v>46407.125</v>
       </c>
       <c r="K475" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L475" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M475" s="0" t="s">
         <v>39</v>
@@ -44084,13 +44090,13 @@
         <v>42</v>
       </c>
       <c r="O475" s="11">
-        <v>46310.125</v>
+        <v>46602.125</v>
       </c>
       <c r="Q475" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R475" s="11">
-        <v>46346.125</v>
+        <v>46407.125</v>
       </c>
       <c r="T475" s="0" t="s">
         <v>43</v>
@@ -44099,39 +44105,39 @@
         <v>42</v>
       </c>
       <c r="X475" s="11">
-        <v>46589.125</v>
+        <v>46518.125</v>
       </c>
       <c r="Z475" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC475" s="0" t="s">
         <v>66</v>
       </c>
       <c r="AD475" s="11">
-        <v>46223.580042650465</v>
+        <v>46223.60221962963</v>
       </c>
       <c r="AE475" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF475" s="3">
-        <v>46226.28457175926</v>
-      </c>
-      <c r="AG475" s="3">
-        <v>46406.125</v>
+        <v>43</v>
+      </c>
+      <c r="AF475" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG475" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="AH475" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI475" s="3">
-        <v>46226.298842592594</v>
+        <v>46227.55289351852</v>
       </c>
       <c r="AJ475" s="3">
-        <v>46406.125</v>
+        <v>46407.125</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="0" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="B476" s="0" t="s">
         <v>60</v>
@@ -44140,19 +44146,19 @@
         <v>1035</v>
       </c>
       <c r="D476" s="0" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="E476" s="0" t="s">
-        <v>167</v>
+        <v>260</v>
       </c>
       <c r="F476" s="0" t="s">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="G476" s="0" t="s">
-        <v>152</v>
+        <v>231</v>
       </c>
       <c r="H476" s="0" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J476" s="11">
         <v>46407.125</v>
@@ -44188,28 +44194,28 @@
         <v>46518.125</v>
       </c>
       <c r="Z476" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC476" s="0" t="s">
         <v>66</v>
       </c>
       <c r="AD476" s="11">
-        <v>46223.60221962963</v>
+        <v>46223.60276513889</v>
       </c>
       <c r="AE476" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF476" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG476" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="AF476" s="3">
+        <v>46230.356307870374</v>
+      </c>
+      <c r="AG476" s="3">
+        <v>46410.125</v>
       </c>
       <c r="AH476" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI476" s="3">
-        <v>46227.55289351852</v>
+        <v>46227.55725694444</v>
       </c>
       <c r="AJ476" s="3">
         <v>46407.125</v>
@@ -44223,7 +44229,7 @@
         <v>60</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>259</v>
@@ -44238,7 +44244,7 @@
         <v>231</v>
       </c>
       <c r="H477" s="0" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J477" s="11">
         <v>46407.125</v>
@@ -44280,13 +44286,13 @@
         <v>66</v>
       </c>
       <c r="AD477" s="11">
-        <v>46223.60276513889</v>
+        <v>46223.60341454861</v>
       </c>
       <c r="AE477" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF477" s="3">
-        <v>46230.356307870374</v>
+        <v>46230.355092592596</v>
       </c>
       <c r="AG477" s="3">
         <v>46410.125</v>
@@ -44295,7 +44301,7 @@
         <v>42</v>
       </c>
       <c r="AI477" s="3">
-        <v>46227.55725694444</v>
+        <v>46227.555983796294</v>
       </c>
       <c r="AJ477" s="3">
         <v>46407.125</v>
@@ -44303,31 +44309,28 @@
     </row>
     <row r="478">
       <c r="A478" s="0" t="s">
-        <v>123</v>
+        <v>833</v>
       </c>
       <c r="B478" s="0" t="s">
-        <v>60</v>
+        <v>622</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D478" s="0" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="E478" s="0" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="F478" s="0" t="s">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="G478" s="0" t="s">
-        <v>231</v>
-      </c>
-      <c r="H478" s="0" t="s">
-        <v>1036</v>
+        <v>438</v>
       </c>
       <c r="J478" s="11">
-        <v>46407.125</v>
+        <v>46352.125</v>
       </c>
       <c r="K478" s="0" t="s">
         <v>55</v>
@@ -44342,75 +44345,72 @@
         <v>42</v>
       </c>
       <c r="O478" s="11">
-        <v>46602.125</v>
+        <v>46585.125</v>
       </c>
       <c r="Q478" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R478" s="11">
-        <v>46407.125</v>
+        <v>46352.125</v>
       </c>
       <c r="T478" s="0" t="s">
         <v>43</v>
       </c>
       <c r="W478" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="X478" s="11">
-        <v>46518.125</v>
+        <v>44</v>
       </c>
       <c r="Z478" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC478" s="0" t="s">
-        <v>66</v>
+        <v>622</v>
       </c>
       <c r="AD478" s="11">
-        <v>46223.60341454861</v>
+        <v>46229.825602557874</v>
       </c>
       <c r="AE478" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF478" s="3">
-        <v>46230.355092592596</v>
+        <v>46229.832970752315</v>
       </c>
       <c r="AG478" s="3">
-        <v>46410.125</v>
+        <v>46409.125</v>
       </c>
       <c r="AH478" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI478" s="3">
-        <v>46227.555983796294</v>
+        <v>46229.83345427083</v>
       </c>
       <c r="AJ478" s="3">
-        <v>46407.125</v>
+        <v>46409.125</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="0" t="s">
-        <v>833</v>
+        <v>611</v>
       </c>
       <c r="B479" s="0" t="s">
         <v>622</v>
       </c>
       <c r="C479" s="0" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D479" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="D479" s="0" t="s">
-        <v>218</v>
-      </c>
       <c r="E479" s="0" t="s">
-        <v>249</v>
+        <v>1039</v>
       </c>
       <c r="F479" s="0" t="s">
-        <v>243</v>
+        <v>438</v>
       </c>
       <c r="G479" s="0" t="s">
-        <v>438</v>
+        <v>523</v>
       </c>
       <c r="J479" s="11">
-        <v>46352.125</v>
+        <v>46409.125</v>
       </c>
       <c r="K479" s="0" t="s">
         <v>55</v>
@@ -44425,13 +44425,13 @@
         <v>42</v>
       </c>
       <c r="O479" s="11">
-        <v>46585.125</v>
+        <v>46541.125</v>
       </c>
       <c r="Q479" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R479" s="11">
-        <v>46352.125</v>
+        <v>46717.125</v>
       </c>
       <c r="T479" s="0" t="s">
         <v>43</v>
@@ -44440,19 +44440,19 @@
         <v>44</v>
       </c>
       <c r="Z479" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC479" s="0" t="s">
         <v>622</v>
       </c>
       <c r="AD479" s="11">
-        <v>46229.825602557874</v>
+        <v>46229.83053608796</v>
       </c>
       <c r="AE479" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF479" s="3">
-        <v>46229.832970752315</v>
+        <v>46229.831278125</v>
       </c>
       <c r="AG479" s="3">
         <v>46409.125</v>
@@ -44461,7 +44461,7 @@
         <v>42</v>
       </c>
       <c r="AI479" s="3">
-        <v>46229.83345427083</v>
+        <v>46229.83233917824</v>
       </c>
       <c r="AJ479" s="3">
         <v>46409.125</v>
@@ -44469,10 +44469,10 @@
     </row>
     <row r="480">
       <c r="A480" s="0" t="s">
-        <v>611</v>
+        <v>47</v>
       </c>
       <c r="B480" s="0" t="s">
-        <v>622</v>
+        <v>48</v>
       </c>
       <c r="C480" s="0" t="s">
         <v>1040</v>
@@ -44484,13 +44484,16 @@
         <v>1041</v>
       </c>
       <c r="F480" s="0" t="s">
-        <v>438</v>
+        <v>100</v>
       </c>
       <c r="G480" s="0" t="s">
-        <v>523</v>
+        <v>203</v>
+      </c>
+      <c r="H480" s="0" t="s">
+        <v>605</v>
       </c>
       <c r="J480" s="11">
-        <v>46409.125</v>
+        <v>46417.125</v>
       </c>
       <c r="K480" s="0" t="s">
         <v>55</v>
@@ -44505,46 +44508,49 @@
         <v>42</v>
       </c>
       <c r="O480" s="11">
-        <v>46541.125</v>
+        <v>46675.125</v>
       </c>
       <c r="Q480" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R480" s="11">
-        <v>46717.125</v>
+        <v>46417.125</v>
       </c>
       <c r="T480" s="0" t="s">
         <v>43</v>
       </c>
       <c r="W480" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="X480" s="11">
+        <v>46597.125</v>
+      </c>
+      <c r="Z480" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="Z480" s="0" t="s">
-        <v>43</v>
-      </c>
       <c r="AC480" s="0" t="s">
-        <v>622</v>
+        <v>56</v>
       </c>
       <c r="AD480" s="11">
-        <v>46229.83053608796</v>
+        <v>46233.359299131946</v>
       </c>
       <c r="AE480" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF480" s="3">
-        <v>46229.831278125</v>
-      </c>
-      <c r="AG480" s="3">
-        <v>46409.125</v>
+        <v>43</v>
+      </c>
+      <c r="AF480" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG480" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="AH480" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI480" s="3">
-        <v>46229.83233917824</v>
+        <v>46240.16216435185</v>
       </c>
       <c r="AJ480" s="3">
-        <v>46409.125</v>
+        <v>46420.125</v>
       </c>
     </row>
     <row r="481">
@@ -44552,34 +44558,34 @@
         <v>47</v>
       </c>
       <c r="B481" s="0" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C481" s="0" t="s">
         <v>1042</v>
       </c>
       <c r="D481" s="0" t="s">
-        <v>1043</v>
+        <v>79</v>
       </c>
       <c r="E481" s="0" t="s">
         <v>1043</v>
       </c>
       <c r="F481" s="0" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="G481" s="0" t="s">
-        <v>203</v>
+        <v>38</v>
       </c>
       <c r="H481" s="0" t="s">
-        <v>605</v>
+        <v>1044</v>
       </c>
       <c r="J481" s="11">
-        <v>46417.125</v>
+        <v>46310.125</v>
       </c>
       <c r="K481" s="0" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L481" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M481" s="0" t="s">
         <v>39</v>
@@ -44588,13 +44594,13 @@
         <v>42</v>
       </c>
       <c r="O481" s="11">
-        <v>46675.125</v>
+        <v>46310.125</v>
       </c>
       <c r="Q481" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R481" s="11">
-        <v>46417.125</v>
+        <v>46360.125</v>
       </c>
       <c r="T481" s="0" t="s">
         <v>43</v>
@@ -44603,16 +44609,16 @@
         <v>42</v>
       </c>
       <c r="X481" s="11">
-        <v>46597.125</v>
+        <v>46602.125</v>
       </c>
       <c r="Z481" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC481" s="0" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AD481" s="11">
-        <v>46233.359299131946</v>
+        <v>46238.835610856484</v>
       </c>
       <c r="AE481" s="0" t="s">
         <v>43</v>
@@ -44627,10 +44633,10 @@
         <v>42</v>
       </c>
       <c r="AI481" s="3">
-        <v>46240.16216435185</v>
+        <v>46241.569444444445</v>
       </c>
       <c r="AJ481" s="3">
-        <v>46420.125</v>
+        <v>46421.125</v>
       </c>
     </row>
     <row r="482">
@@ -44638,34 +44644,31 @@
         <v>47</v>
       </c>
       <c r="B482" s="0" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D482" s="0" t="s">
-        <v>79</v>
+        <v>1046</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F482" s="0" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="G482" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="H482" s="0" t="s">
-        <v>1046</v>
+        <v>170</v>
       </c>
       <c r="J482" s="11">
-        <v>46310.125</v>
+        <v>46360.125</v>
       </c>
       <c r="K482" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L482" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M482" s="0" t="s">
         <v>39</v>
@@ -44674,7 +44677,7 @@
         <v>42</v>
       </c>
       <c r="O482" s="11">
-        <v>46310.125</v>
+        <v>46550.125</v>
       </c>
       <c r="Q482" s="0" t="s">
         <v>42</v>
@@ -44689,16 +44692,16 @@
         <v>42</v>
       </c>
       <c r="X482" s="11">
-        <v>46602.125</v>
+        <v>46576.125</v>
       </c>
       <c r="Z482" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC482" s="0" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AD482" s="11">
-        <v>46238.835610856484</v>
+        <v>46239.584635150466</v>
       </c>
       <c r="AE482" s="0" t="s">
         <v>43</v>
@@ -44713,15 +44716,15 @@
         <v>42</v>
       </c>
       <c r="AI482" s="3">
-        <v>46241.569444444445</v>
+        <v>46249.49712962963</v>
       </c>
       <c r="AJ482" s="3">
-        <v>46421.125</v>
+        <v>46429.125</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="0" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B483" s="0" t="s">
         <v>48</v>
@@ -44730,19 +44733,19 @@
         <v>1047</v>
       </c>
       <c r="D483" s="0" t="s">
-        <v>1048</v>
+        <v>344</v>
       </c>
       <c r="E483" s="0" t="s">
-        <v>1048</v>
+        <v>344</v>
       </c>
       <c r="F483" s="0" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G483" s="0" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="J483" s="11">
-        <v>46360.125</v>
+        <v>46356.125</v>
       </c>
       <c r="K483" s="0" t="s">
         <v>55</v>
@@ -44757,7 +44760,7 @@
         <v>42</v>
       </c>
       <c r="O483" s="11">
-        <v>46550.125</v>
+        <v>46356.125</v>
       </c>
       <c r="Q483" s="0" t="s">
         <v>42</v>
@@ -44781,22 +44784,22 @@
         <v>56</v>
       </c>
       <c r="AD483" s="11">
-        <v>46239.584635150466</v>
+        <v>46239.58566384259</v>
       </c>
       <c r="AE483" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF483" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG483" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="AF483" s="3">
+        <v>46249.52449074074</v>
+      </c>
+      <c r="AG483" s="3">
+        <v>46429.125</v>
       </c>
       <c r="AH483" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI483" s="3">
-        <v>46249.49712962963</v>
+        <v>46249.493946759256</v>
       </c>
       <c r="AJ483" s="3">
         <v>46429.125</v>
@@ -44810,7 +44813,7 @@
         <v>48</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>344</v>
@@ -44864,13 +44867,13 @@
         <v>56</v>
       </c>
       <c r="AD484" s="11">
-        <v>46239.58566384259</v>
+        <v>46239.58626928241</v>
       </c>
       <c r="AE484" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF484" s="3">
-        <v>46249.52449074074</v>
+        <v>46249.523148148146</v>
       </c>
       <c r="AG484" s="3">
         <v>46429.125</v>
@@ -44879,7 +44882,7 @@
         <v>42</v>
       </c>
       <c r="AI484" s="3">
-        <v>46249.493946759256</v>
+        <v>46249.49586805556</v>
       </c>
       <c r="AJ484" s="3">
         <v>46429.125</v>
@@ -44890,25 +44893,28 @@
         <v>33</v>
       </c>
       <c r="B485" s="0" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D485" s="0" t="s">
-        <v>344</v>
+        <v>249</v>
       </c>
       <c r="E485" s="0" t="s">
-        <v>344</v>
+        <v>37</v>
       </c>
       <c r="F485" s="0" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="G485" s="0" t="s">
-        <v>144</v>
+        <v>38</v>
+      </c>
+      <c r="H485" s="0" t="s">
+        <v>894</v>
       </c>
       <c r="J485" s="11">
-        <v>46356.125</v>
+        <v>46362.125</v>
       </c>
       <c r="K485" s="0" t="s">
         <v>55</v>
@@ -44923,13 +44929,13 @@
         <v>42</v>
       </c>
       <c r="O485" s="11">
-        <v>46356.125</v>
+        <v>46527.125</v>
       </c>
       <c r="Q485" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R485" s="11">
-        <v>46360.125</v>
+        <v>46362.125</v>
       </c>
       <c r="T485" s="0" t="s">
         <v>43</v>
@@ -44938,34 +44944,34 @@
         <v>42</v>
       </c>
       <c r="X485" s="11">
-        <v>46576.125</v>
+        <v>46603.125</v>
       </c>
       <c r="Z485" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC485" s="0" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="AD485" s="11">
-        <v>46239.58626928241</v>
+        <v>46240.46602104167</v>
       </c>
       <c r="AE485" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF485" s="3">
-        <v>46249.523148148146</v>
+        <v>46242.301840277774</v>
       </c>
       <c r="AG485" s="3">
-        <v>46429.125</v>
+        <v>46422.125</v>
       </c>
       <c r="AH485" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI485" s="3">
-        <v>46249.49586805556</v>
+        <v>46241.57849537037</v>
       </c>
       <c r="AJ485" s="3">
-        <v>46429.125</v>
+        <v>46421.125</v>
       </c>
     </row>
     <row r="486">
@@ -44976,7 +44982,7 @@
         <v>34</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D486" s="0" t="s">
         <v>249</v>
@@ -45033,13 +45039,13 @@
         <v>45</v>
       </c>
       <c r="AD486" s="11">
-        <v>46240.46602104167</v>
+        <v>46240.470631585646</v>
       </c>
       <c r="AE486" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF486" s="3">
-        <v>46242.301840277774</v>
+        <v>46242.303981481484</v>
       </c>
       <c r="AG486" s="3">
         <v>46422.125</v>
@@ -45048,7 +45054,7 @@
         <v>42</v>
       </c>
       <c r="AI486" s="3">
-        <v>46241.57849537037</v>
+        <v>46241.57649305555</v>
       </c>
       <c r="AJ486" s="3">
         <v>46421.125</v>
@@ -45056,31 +45062,28 @@
     </row>
     <row r="487">
       <c r="A487" s="0" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B487" s="0" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>249</v>
+        <v>365</v>
       </c>
       <c r="E487" s="0" t="s">
-        <v>37</v>
+        <v>365</v>
       </c>
       <c r="F487" s="0" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="G487" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="H487" s="0" t="s">
-        <v>894</v>
+        <v>95</v>
       </c>
       <c r="J487" s="11">
-        <v>46362.125</v>
+        <v>46423.125</v>
       </c>
       <c r="K487" s="0" t="s">
         <v>55</v>
@@ -45095,13 +45098,13 @@
         <v>42</v>
       </c>
       <c r="O487" s="11">
-        <v>46527.125</v>
+        <v>46624.125</v>
       </c>
       <c r="Q487" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R487" s="11">
-        <v>46362.125</v>
+        <v>46423.125</v>
       </c>
       <c r="T487" s="0" t="s">
         <v>43</v>
@@ -45110,57 +45113,57 @@
         <v>42</v>
       </c>
       <c r="X487" s="11">
-        <v>46603.125</v>
+        <v>46424.125</v>
       </c>
       <c r="Z487" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC487" s="0" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AD487" s="11">
-        <v>46240.470631585646</v>
+        <v>46247.378986828706</v>
       </c>
       <c r="AE487" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF487" s="3">
-        <v>46242.303981481484</v>
-      </c>
-      <c r="AG487" s="3">
-        <v>46422.125</v>
+        <v>43</v>
+      </c>
+      <c r="AF487" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG487" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="AH487" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI487" s="3">
-        <v>46241.57649305555</v>
+        <v>46251.136099537034</v>
       </c>
       <c r="AJ487" s="3">
-        <v>46421.125</v>
+        <v>46431.125</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="0" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B488" s="0" t="s">
         <v>48</v>
       </c>
       <c r="C488" s="0" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D488" s="0" t="s">
         <v>1053</v>
       </c>
-      <c r="D488" s="0" t="s">
-        <v>365</v>
-      </c>
       <c r="E488" s="0" t="s">
-        <v>365</v>
+        <v>1053</v>
       </c>
       <c r="F488" s="0" t="s">
-        <v>95</v>
+        <v>257</v>
       </c>
       <c r="G488" s="0" t="s">
-        <v>95</v>
+        <v>257</v>
       </c>
       <c r="J488" s="11">
         <v>46423.125</v>
@@ -45178,7 +45181,7 @@
         <v>42</v>
       </c>
       <c r="O488" s="11">
-        <v>46624.125</v>
+        <v>46657.125</v>
       </c>
       <c r="Q488" s="0" t="s">
         <v>42</v>
@@ -45202,22 +45205,22 @@
         <v>56</v>
       </c>
       <c r="AD488" s="11">
-        <v>46247.378986828706</v>
+        <v>46247.38072584491</v>
       </c>
       <c r="AE488" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF488" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG488" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="AF488" s="3">
+        <v>46251.1727662037</v>
+      </c>
+      <c r="AG488" s="3">
+        <v>46431.125</v>
       </c>
       <c r="AH488" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI488" s="3">
-        <v>46251.136099537034</v>
+        <v>46251.138078703705</v>
       </c>
       <c r="AJ488" s="3">
         <v>46431.125</v>
@@ -45225,7 +45228,7 @@
     </row>
     <row r="489">
       <c r="A489" s="0" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B489" s="0" t="s">
         <v>48</v>
@@ -45240,13 +45243,13 @@
         <v>1055</v>
       </c>
       <c r="F489" s="0" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="G489" s="0" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="J489" s="11">
-        <v>46423.125</v>
+        <v>46369.125</v>
       </c>
       <c r="K489" s="0" t="s">
         <v>55</v>
@@ -45261,13 +45264,13 @@
         <v>42</v>
       </c>
       <c r="O489" s="11">
-        <v>46657.125</v>
+        <v>46483.125</v>
       </c>
       <c r="Q489" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R489" s="11">
-        <v>46423.125</v>
+        <v>46369.125</v>
       </c>
       <c r="T489" s="0" t="s">
         <v>43</v>
@@ -45276,7 +45279,7 @@
         <v>42</v>
       </c>
       <c r="X489" s="11">
-        <v>46424.125</v>
+        <v>46610.125</v>
       </c>
       <c r="Z489" s="0" t="s">
         <v>44</v>
@@ -45285,30 +45288,30 @@
         <v>56</v>
       </c>
       <c r="AD489" s="11">
-        <v>46247.38072584491</v>
+        <v>46247.41001086806</v>
       </c>
       <c r="AE489" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF489" s="3">
-        <v>46251.1727662037</v>
-      </c>
-      <c r="AG489" s="3">
-        <v>46431.125</v>
+        <v>43</v>
+      </c>
+      <c r="AF489" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG489" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="AH489" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI489" s="3">
-        <v>46251.138078703705</v>
+        <v>46248.24575231481</v>
       </c>
       <c r="AJ489" s="3">
-        <v>46431.125</v>
+        <v>46428.125</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="0" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B490" s="0" t="s">
         <v>48</v>
@@ -45323,10 +45326,10 @@
         <v>1057</v>
       </c>
       <c r="F490" s="0" t="s">
-        <v>133</v>
+        <v>293</v>
       </c>
       <c r="G490" s="0" t="s">
-        <v>133</v>
+        <v>293</v>
       </c>
       <c r="J490" s="11">
         <v>46369.125</v>
@@ -45344,7 +45347,7 @@
         <v>42</v>
       </c>
       <c r="O490" s="11">
-        <v>46483.125</v>
+        <v>46569.125</v>
       </c>
       <c r="Q490" s="0" t="s">
         <v>42</v>
@@ -45368,22 +45371,22 @@
         <v>56</v>
       </c>
       <c r="AD490" s="11">
-        <v>46247.41001086806</v>
+        <v>46247.41167141204</v>
       </c>
       <c r="AE490" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF490" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG490" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="AF490" s="3">
+        <v>46248.27179398148</v>
+      </c>
+      <c r="AG490" s="3">
+        <v>46428.125</v>
       </c>
       <c r="AH490" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI490" s="3">
-        <v>46248.24575231481</v>
+        <v>46248.24664351852</v>
       </c>
       <c r="AJ490" s="3">
         <v>46428.125</v>
@@ -45391,34 +45394,34 @@
     </row>
     <row r="491">
       <c r="A491" s="0" t="s">
-        <v>33</v>
+        <v>154</v>
       </c>
       <c r="B491" s="0" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C491" s="0" t="s">
         <v>1058</v>
       </c>
       <c r="D491" s="0" t="s">
-        <v>1059</v>
+        <v>525</v>
       </c>
       <c r="E491" s="0" t="s">
         <v>1059</v>
       </c>
       <c r="F491" s="0" t="s">
-        <v>293</v>
+        <v>107</v>
       </c>
       <c r="G491" s="0" t="s">
-        <v>293</v>
+        <v>107</v>
       </c>
       <c r="J491" s="11">
-        <v>46369.125</v>
+        <v>46310.125</v>
       </c>
       <c r="K491" s="0" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L491" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M491" s="0" t="s">
         <v>39</v>
@@ -45427,81 +45430,87 @@
         <v>42</v>
       </c>
       <c r="O491" s="11">
-        <v>46569.125</v>
+        <v>46310.125</v>
       </c>
       <c r="Q491" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R491" s="11">
-        <v>46369.125</v>
+        <v>46381.125</v>
       </c>
       <c r="T491" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="U491" s="11">
+        <v>46366.125</v>
       </c>
       <c r="W491" s="0" t="s">
         <v>42</v>
       </c>
       <c r="X491" s="11">
-        <v>46610.125</v>
+        <v>46625.125</v>
       </c>
       <c r="Z491" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC491" s="0" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AD491" s="11">
-        <v>46247.41167141204</v>
+        <v>46259.72297328704</v>
       </c>
       <c r="AE491" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF491" s="3">
-        <v>46248.27179398148</v>
-      </c>
-      <c r="AG491" s="3">
-        <v>46428.125</v>
+        <v>43</v>
+      </c>
+      <c r="AF491" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG491" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="AH491" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI491" s="3">
-        <v>46248.24664351852</v>
+        <v>46260.55417824074</v>
       </c>
       <c r="AJ491" s="3">
-        <v>46428.125</v>
+        <v>46440.125</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="0" t="s">
-        <v>154</v>
+        <v>810</v>
       </c>
       <c r="B492" s="0" t="s">
-        <v>60</v>
+        <v>644</v>
       </c>
       <c r="C492" s="0" t="s">
         <v>1060</v>
       </c>
       <c r="D492" s="0" t="s">
-        <v>525</v>
+        <v>74</v>
       </c>
       <c r="E492" s="0" t="s">
         <v>1061</v>
       </c>
       <c r="F492" s="0" t="s">
-        <v>107</v>
+        <v>292</v>
       </c>
       <c r="G492" s="0" t="s">
-        <v>107</v>
+        <v>292</v>
+      </c>
+      <c r="H492" s="0" t="s">
+        <v>848</v>
       </c>
       <c r="J492" s="11">
-        <v>46310.125</v>
+        <v>46372.125</v>
       </c>
       <c r="K492" s="0" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="L492" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M492" s="0" t="s">
         <v>39</v>
@@ -45510,81 +45519,78 @@
         <v>42</v>
       </c>
       <c r="O492" s="11">
-        <v>46310.125</v>
+        <v>46641.125</v>
       </c>
       <c r="Q492" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R492" s="11">
-        <v>46381.125</v>
+        <v>46397.125</v>
       </c>
       <c r="T492" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="U492" s="11">
-        <v>46366.125</v>
+        <v>43</v>
       </c>
       <c r="W492" s="0" t="s">
         <v>42</v>
       </c>
       <c r="X492" s="11">
-        <v>46625.125</v>
+        <v>46372.125</v>
       </c>
       <c r="Z492" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC492" s="0" t="s">
-        <v>66</v>
+        <v>648</v>
       </c>
       <c r="AD492" s="11">
-        <v>46259.72297328704</v>
+        <v>46275.669610046294</v>
       </c>
       <c r="AE492" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF492" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG492" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="AF492" s="3">
+        <v>46275.67157890047</v>
+      </c>
+      <c r="AG492" s="3">
+        <v>46455.125</v>
       </c>
       <c r="AH492" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI492" s="3">
-        <v>46260.55417824074</v>
+        <v>46275.67245056713</v>
       </c>
       <c r="AJ492" s="3">
-        <v>46440.125</v>
+        <v>46455.125</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="0" t="s">
-        <v>810</v>
+        <v>47</v>
       </c>
       <c r="B493" s="0" t="s">
-        <v>644</v>
+        <v>34</v>
       </c>
       <c r="C493" s="0" t="s">
         <v>1062</v>
       </c>
       <c r="D493" s="0" t="s">
-        <v>74</v>
+        <v>587</v>
       </c>
       <c r="E493" s="0" t="s">
         <v>1063</v>
       </c>
       <c r="F493" s="0" t="s">
-        <v>292</v>
+        <v>863</v>
       </c>
       <c r="G493" s="0" t="s">
-        <v>292</v>
+        <v>1064</v>
       </c>
       <c r="H493" s="0" t="s">
-        <v>848</v>
+        <v>204</v>
       </c>
       <c r="J493" s="11">
-        <v>46372.125</v>
+        <v>46415.125</v>
       </c>
       <c r="K493" s="0" t="s">
         <v>55</v>
@@ -45599,13 +45605,13 @@
         <v>42</v>
       </c>
       <c r="O493" s="11">
-        <v>46641.125</v>
+        <v>46653.125</v>
       </c>
       <c r="Q493" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R493" s="11">
-        <v>46397.125</v>
+        <v>46415.125</v>
       </c>
       <c r="T493" s="0" t="s">
         <v>43</v>
@@ -45614,34 +45620,34 @@
         <v>42</v>
       </c>
       <c r="X493" s="11">
-        <v>46372.125</v>
+        <v>46656.125</v>
       </c>
       <c r="Z493" s="0" t="s">
         <v>44</v>
       </c>
       <c r="AC493" s="0" t="s">
-        <v>648</v>
+        <v>205</v>
       </c>
       <c r="AD493" s="11">
-        <v>46275.669610046294</v>
+        <v>46293.440021215276</v>
       </c>
       <c r="AE493" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF493" s="3">
-        <v>46275.67157890047</v>
-      </c>
-      <c r="AG493" s="3">
-        <v>46455.125</v>
+        <v>43</v>
+      </c>
+      <c r="AF493" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG493" s="0" t="s">
+        <v>43</v>
       </c>
       <c r="AH493" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI493" s="3">
-        <v>46275.67245056713</v>
+        <v>46294.65325231481</v>
       </c>
       <c r="AJ493" s="3">
-        <v>46455.125</v>
+        <v>46474.125</v>
       </c>
     </row>
     <row r="494">
@@ -45652,19 +45658,19 @@
         <v>34</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E494" s="0" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F494" s="0" t="s">
         <v>863</v>
       </c>
       <c r="G494" s="0" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="H494" s="0" t="s">
         <v>204</v>
@@ -45709,7 +45715,7 @@
         <v>205</v>
       </c>
       <c r="AD494" s="11">
-        <v>46293.440021215276</v>
+        <v>46293.44192613426</v>
       </c>
       <c r="AE494" s="0" t="s">
         <v>43</v>
@@ -45724,7 +45730,7 @@
         <v>42</v>
       </c>
       <c r="AI494" s="3">
-        <v>46294.65325231481</v>
+        <v>46294.6502662037</v>
       </c>
       <c r="AJ494" s="3">
         <v>46474.125</v>
@@ -45732,31 +45738,28 @@
     </row>
     <row r="495">
       <c r="A495" s="0" t="s">
-        <v>47</v>
+        <v>611</v>
       </c>
       <c r="B495" s="0" t="s">
-        <v>34</v>
+        <v>226</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="D495" s="0" t="s">
-        <v>587</v>
+        <v>525</v>
       </c>
       <c r="E495" s="0" t="s">
-        <v>1065</v>
+        <v>473</v>
       </c>
       <c r="F495" s="0" t="s">
-        <v>863</v>
+        <v>501</v>
       </c>
       <c r="G495" s="0" t="s">
-        <v>1066</v>
-      </c>
-      <c r="H495" s="0" t="s">
-        <v>204</v>
+        <v>501</v>
       </c>
       <c r="J495" s="11">
-        <v>46415.125</v>
+        <v>46419.125</v>
       </c>
       <c r="K495" s="0" t="s">
         <v>55</v>
@@ -45771,75 +45774,72 @@
         <v>42</v>
       </c>
       <c r="O495" s="11">
-        <v>46653.125</v>
+        <v>46644.125</v>
       </c>
       <c r="Q495" s="0" t="s">
         <v>42</v>
       </c>
       <c r="R495" s="11">
-        <v>46415.125</v>
+        <v>46419.125</v>
       </c>
       <c r="T495" s="0" t="s">
         <v>43</v>
       </c>
       <c r="W495" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="X495" s="11">
-        <v>46656.125</v>
+        <v>44</v>
       </c>
       <c r="Z495" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC495" s="0" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="AD495" s="11">
-        <v>46293.44192613426</v>
+        <v>46296.42035898148</v>
       </c>
       <c r="AE495" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF495" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG495" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="AF495" s="3">
+        <v>46296.422316944445</v>
+      </c>
+      <c r="AG495" s="3">
+        <v>46476.125</v>
       </c>
       <c r="AH495" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI495" s="3">
-        <v>46294.6502662037</v>
+        <v>46296.424317627316</v>
       </c>
       <c r="AJ495" s="3">
-        <v>46474.125</v>
+        <v>46476.125</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="0" t="s">
-        <v>611</v>
+        <v>658</v>
       </c>
       <c r="B496" s="0" t="s">
-        <v>226</v>
+        <v>807</v>
       </c>
       <c r="C496" s="0" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D496" s="0" t="s">
         <v>1068</v>
       </c>
-      <c r="D496" s="0" t="s">
-        <v>525</v>
-      </c>
       <c r="E496" s="0" t="s">
-        <v>473</v>
+        <v>1068</v>
       </c>
       <c r="F496" s="0" t="s">
-        <v>501</v>
+        <v>293</v>
       </c>
       <c r="G496" s="0" t="s">
-        <v>501</v>
+        <v>293</v>
       </c>
       <c r="J496" s="11">
-        <v>46419.125</v>
+        <v>46483.125</v>
       </c>
       <c r="K496" s="0" t="s">
         <v>55</v>
@@ -45851,124 +45851,111 @@
         <v>39</v>
       </c>
       <c r="N496" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="O496" s="11">
-        <v>46644.125</v>
+        <v>44</v>
       </c>
       <c r="Q496" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="R496" s="11">
-        <v>46419.125</v>
+        <v>44</v>
       </c>
       <c r="T496" s="0" t="s">
         <v>43</v>
       </c>
       <c r="W496" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z496" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="Z496" s="0" t="s">
-        <v>43</v>
-      </c>
       <c r="AC496" s="0" t="s">
-        <v>226</v>
+        <v>807</v>
       </c>
       <c r="AD496" s="11">
-        <v>46296.42035898148</v>
+        <v>46301.476280462964</v>
       </c>
       <c r="AE496" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AF496" s="3">
-        <v>46296.422316944445</v>
+        <v>46303.55599537037</v>
       </c>
       <c r="AG496" s="3">
-        <v>46476.125</v>
+        <v>46483.125</v>
       </c>
       <c r="AH496" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AI496" s="3">
-        <v>46296.424317627316</v>
+        <v>46303.56097222222</v>
       </c>
       <c r="AJ496" s="3">
-        <v>46476.125</v>
+        <v>46483.125</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="0" t="s">
-        <v>658</v>
+        <v>814</v>
       </c>
       <c r="B497" s="0" t="s">
-        <v>807</v>
+        <v>850</v>
       </c>
       <c r="C497" s="0" t="s">
         <v>1069</v>
       </c>
       <c r="D497" s="0" t="s">
-        <v>1070</v>
+        <v>937</v>
       </c>
       <c r="E497" s="0" t="s">
         <v>1070</v>
       </c>
       <c r="F497" s="0" t="s">
-        <v>293</v>
+        <v>170</v>
       </c>
       <c r="G497" s="0" t="s">
-        <v>293</v>
-      </c>
-      <c r="J497" s="11">
-        <v>46483.125</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="J497" s="11"/>
       <c r="K497" s="0" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="L497" s="0" t="s">
-        <v>39</v>
+        <v>1071</v>
       </c>
       <c r="M497" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N497" s="0" t="s">
-        <v>44</v>
+        <v>595</v>
+      </c>
+      <c r="O497" s="11">
+        <v>45915.125</v>
       </c>
       <c r="Q497" s="0" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="T497" s="0" t="s">
         <v>43</v>
       </c>
       <c r="W497" s="0" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="Z497" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC497" s="0" t="s">
-        <v>807</v>
+        <v>852</v>
       </c>
       <c r="AD497" s="11">
-        <v>46301.476280462964</v>
+        <v>46303.38590450231</v>
       </c>
       <c r="AE497" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF497" s="3">
-        <v>46303.55599537037</v>
-      </c>
-      <c r="AG497" s="3">
-        <v>46483.125</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="AF497" s="3"/>
+      <c r="AG497" s="3"/>
       <c r="AH497" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI497" s="3">
-        <v>46303.56097222222</v>
-      </c>
-      <c r="AJ497" s="3">
-        <v>46483.125</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="AI497" s="3"/>
+      <c r="AJ497" s="3"/>
     </row>
     <row r="498">
       <c r="A498" s="0" t="s">
@@ -45978,26 +45965,26 @@
         <v>850</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D498" s="0" t="s">
-        <v>937</v>
+        <v>1073</v>
       </c>
       <c r="E498" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F498" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G498" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J498" s="11"/>
       <c r="K498" s="0" t="s">
         <v>70</v>
       </c>
       <c r="L498" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="M498" s="0" t="s">
         <v>39</v>
@@ -46006,7 +45993,7 @@
         <v>595</v>
       </c>
       <c r="O498" s="11">
-        <v>45915.125</v>
+        <v>46310.125</v>
       </c>
       <c r="Q498" s="0" t="s">
         <v>72</v>
@@ -46024,7 +46011,7 @@
         <v>852</v>
       </c>
       <c r="AD498" s="11">
-        <v>46303.38590450231</v>
+        <v>46303.38891412037</v>
       </c>
       <c r="AE498" s="0" t="s">
         <v>72</v>
@@ -46036,73 +46023,6 @@
       </c>
       <c r="AI498" s="3"/>
       <c r="AJ498" s="3"/>
-    </row>
-    <row r="499">
-      <c r="A499" s="0" t="s">
-        <v>814</v>
-      </c>
-      <c r="B499" s="0" t="s">
-        <v>850</v>
-      </c>
-      <c r="C499" s="0" t="s">
-        <v>1074</v>
-      </c>
-      <c r="D499" s="0" t="s">
-        <v>1075</v>
-      </c>
-      <c r="E499" s="0" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F499" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="G499" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="J499" s="11"/>
-      <c r="K499" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="L499" s="0" t="s">
-        <v>1076</v>
-      </c>
-      <c r="M499" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="N499" s="0" t="s">
-        <v>595</v>
-      </c>
-      <c r="O499" s="11">
-        <v>46310.125</v>
-      </c>
-      <c r="Q499" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="T499" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="W499" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z499" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC499" s="0" t="s">
-        <v>852</v>
-      </c>
-      <c r="AD499" s="11">
-        <v>46303.38891412037</v>
-      </c>
-      <c r="AE499" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF499" s="3"/>
-      <c r="AG499" s="3"/>
-      <c r="AH499" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI499" s="3"/>
-      <c r="AJ499" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -46151,28 +46071,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -46180,10 +46100,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>807</v>
@@ -46201,10 +46121,10 @@
         <v>46483.125</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>807</v>
@@ -46212,10 +46132,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>807</v>
@@ -46227,16 +46147,16 @@
         <v>46303</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G3" s="11">
         <v>46483.125</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>807</v>
@@ -46247,7 +46167,7 @@
         <v>880</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>644</v>
@@ -46265,10 +46185,10 @@
         <v>46480.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>648</v>
@@ -46276,10 +46196,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>226</v>
@@ -46297,10 +46217,10 @@
         <v>46476.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>226</v>
@@ -46308,10 +46228,10 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>226</v>
@@ -46323,16 +46243,16 @@
         <v>46296</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G6" s="11">
         <v>46476.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>226</v>
@@ -46340,10 +46260,10 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>34</v>
@@ -46361,10 +46281,10 @@
         <v>46474.125</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>205</v>
@@ -46372,10 +46292,10 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>34</v>
@@ -46393,10 +46313,10 @@
         <v>46474.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>205</v>
@@ -46407,7 +46327,7 @@
         <v>879</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>644</v>
@@ -46425,10 +46345,10 @@
         <v>46474.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>648</v>
@@ -46439,7 +46359,7 @@
         <v>879</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>644</v>
@@ -46451,16 +46371,16 @@
         <v>46294</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G10" s="11">
         <v>46474.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>648</v>
@@ -46471,7 +46391,7 @@
         <v>842</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>644</v>
@@ -46489,10 +46409,10 @@
         <v>46474.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>648</v>
@@ -46503,7 +46423,7 @@
         <v>842</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>644</v>
@@ -46515,16 +46435,16 @@
         <v>46294</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G12" s="11">
         <v>46474.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>648</v>
@@ -46535,7 +46455,7 @@
         <v>974</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>60</v>
@@ -46547,16 +46467,16 @@
         <v>46289</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G13" s="11">
         <v>46469.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>66</v>
@@ -46567,7 +46487,7 @@
         <v>974</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>60</v>
@@ -46585,10 +46505,10 @@
         <v>46469.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>66</v>
@@ -46596,10 +46516,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>644</v>
@@ -46617,10 +46537,10 @@
         <v>46455.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>648</v>
@@ -46628,10 +46548,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>644</v>
@@ -46643,16 +46563,16 @@
         <v>46275</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G16" s="11">
         <v>46455.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>648</v>
@@ -46663,7 +46583,7 @@
         <v>851</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>850</v>
@@ -46681,10 +46601,10 @@
         <v>46449.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>852</v>
@@ -46695,7 +46615,7 @@
         <v>851</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>850</v>
@@ -46707,16 +46627,16 @@
         <v>46269</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G18" s="11">
         <v>46449.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>852</v>
@@ -46727,7 +46647,7 @@
         <v>851</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>850</v>
@@ -46745,10 +46665,10 @@
         <v>46268</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J19" s="0" t="s">
         <v>852</v>
@@ -46759,7 +46679,7 @@
         <v>551</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>34</v>
@@ -46771,19 +46691,19 @@
         <v>46267</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G20" s="11">
         <v>46447.125</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="21">
@@ -46791,7 +46711,7 @@
         <v>551</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>34</v>
@@ -46809,13 +46729,13 @@
         <v>46447.125</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="22">
@@ -46823,7 +46743,7 @@
         <v>869</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>60</v>
@@ -46841,10 +46761,10 @@
         <v>46446.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>610</v>
@@ -46855,7 +46775,7 @@
         <v>872</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>60</v>
@@ -46873,10 +46793,10 @@
         <v>46446.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>610</v>
@@ -46887,7 +46807,7 @@
         <v>553</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>48</v>
@@ -46899,19 +46819,19 @@
         <v>46261</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G24" s="11">
         <v>46441.125</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="25">
@@ -46919,7 +46839,7 @@
         <v>868</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>34</v>
@@ -46931,16 +46851,16 @@
         <v>46260</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G25" s="11">
         <v>46440.125</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>205</v>
@@ -46948,10 +46868,10 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>60</v>
@@ -46969,10 +46889,10 @@
         <v>46440.125</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J26" s="0" t="s">
         <v>66</v>
@@ -46983,7 +46903,7 @@
         <v>867</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>34</v>
@@ -47001,10 +46921,10 @@
         <v>46439.125</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>205</v>
@@ -47015,7 +46935,7 @@
         <v>657</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>34</v>
@@ -47033,10 +46953,10 @@
         <v>46439.125</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>205</v>
@@ -47047,7 +46967,7 @@
         <v>868</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>34</v>
@@ -47065,10 +46985,10 @@
         <v>46439.125</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>205</v>
@@ -47079,7 +46999,7 @@
         <v>653</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>60</v>
@@ -47097,10 +47017,10 @@
         <v>46439.125</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>610</v>
@@ -47111,7 +47031,7 @@
         <v>342</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>60</v>
@@ -47129,10 +47049,10 @@
         <v>46439.125</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>66</v>
@@ -47143,7 +47063,7 @@
         <v>472</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>60</v>
@@ -47155,16 +47075,16 @@
         <v>46255</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G32" s="11">
         <v>46435.125</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>66</v>
@@ -47175,7 +47095,7 @@
         <v>472</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>60</v>
@@ -47193,10 +47113,10 @@
         <v>46435.125</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>66</v>
@@ -47207,7 +47127,7 @@
         <v>651</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>60</v>
@@ -47225,10 +47145,10 @@
         <v>46432.125</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>610</v>
@@ -47239,7 +47159,7 @@
         <v>608</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>60</v>
@@ -47257,10 +47177,10 @@
         <v>46432.125</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>610</v>
@@ -47271,7 +47191,7 @@
         <v>607</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>34</v>
@@ -47289,10 +47209,10 @@
         <v>46432.125</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>45</v>
@@ -47300,10 +47220,10 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>34</v>
@@ -47321,10 +47241,10 @@
         <v>46432.125</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>45</v>
@@ -47335,7 +47255,7 @@
         <v>607</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>34</v>
@@ -47347,16 +47267,16 @@
         <v>46252</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G38" s="11">
         <v>46432.125</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="J38" s="0" t="s">
         <v>45</v>
@@ -47364,10 +47284,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>48</v>
@@ -47379,16 +47299,16 @@
         <v>46251</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G39" s="11">
         <v>46431.125</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="J39" s="0" t="s">
         <v>56</v>
@@ -47396,10 +47316,10 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>48</v>
@@ -47417,10 +47337,10 @@
         <v>46431.125</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J40" s="0" t="s">
         <v>56</v>
@@ -47428,10 +47348,10 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>48</v>
@@ -47449,10 +47369,10 @@
         <v>46431.125</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J41" s="0" t="s">
         <v>56</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="1115">
   <si>
     <t>Geração:</t>
   </si>
@@ -3246,22 +3246,25 @@
     <t>Perfil Responsável</t>
   </si>
   <si>
+    <t>Volkswagen / VW/19.330 CTC 4X2</t>
+  </si>
+  <si>
+    <t>MACAE BRUNE GOMES MELO</t>
+  </si>
+  <si>
+    <t>Transportador Fixo</t>
+  </si>
+  <si>
     <t>M.BENZ/ATEGO 2426 / M.BENZ/ATEGO 2426</t>
   </si>
   <si>
     <t>WANDERSON DE CARVALHO ROCHA</t>
   </si>
   <si>
-    <t>Transportador Fixo</t>
-  </si>
-  <si>
     <t>Checklist de Qualidade Tomate</t>
   </si>
   <si>
     <t>IVECO / IVECO/STRALIS 600S44T</t>
-  </si>
-  <si>
-    <t>MACAE BRUNE GOMES MELO</t>
   </si>
   <si>
     <t>M.BENZ / L 1113</t>
@@ -3546,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46311.34984981482</v>
+        <v>46311.62612400463</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -28850,13 +28853,13 @@
         <v>716</v>
       </c>
       <c r="J298" s="11">
-        <v>46338.125</v>
+        <v>46372.125</v>
       </c>
       <c r="K298" s="0" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="L298" s="0" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="M298" s="0" t="s">
         <v>39</v>
@@ -28871,7 +28874,7 @@
         <v>43</v>
       </c>
       <c r="R298" s="11">
-        <v>46338.125</v>
+        <v>46493.125</v>
       </c>
       <c r="T298" s="0" t="s">
         <v>44</v>
@@ -34048,7 +34051,7 @@
         <v>210</v>
       </c>
       <c r="J359" s="11">
-        <v>46341.125</v>
+        <v>46372.125</v>
       </c>
       <c r="K359" s="0" t="s">
         <v>56</v>
@@ -34063,13 +34066,13 @@
         <v>43</v>
       </c>
       <c r="O359" s="11">
-        <v>46341.125</v>
+        <v>46706.125</v>
       </c>
       <c r="Q359" s="0" t="s">
         <v>43</v>
       </c>
       <c r="R359" s="11">
-        <v>46382.125</v>
+        <v>46493.125</v>
       </c>
       <c r="T359" s="0" t="s">
         <v>44</v>
@@ -35484,7 +35487,7 @@
         <v>76</v>
       </c>
       <c r="L376" s="0" t="s">
-        <v>650</v>
+        <v>77</v>
       </c>
       <c r="M376" s="0" t="s">
         <v>39</v>
@@ -35499,7 +35502,7 @@
         <v>43</v>
       </c>
       <c r="R376" s="11">
-        <v>46338.125</v>
+        <v>46493.125</v>
       </c>
       <c r="T376" s="0" t="s">
         <v>44</v>
@@ -35563,12 +35566,14 @@
       <c r="H377" s="0" t="s">
         <v>716</v>
       </c>
-      <c r="J377" s="11"/>
+      <c r="J377" s="11">
+        <v>46326.125</v>
+      </c>
       <c r="K377" s="0" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="L377" s="0" t="s">
-        <v>682</v>
+        <v>77</v>
       </c>
       <c r="M377" s="0" t="s">
         <v>39</v>
@@ -35583,7 +35588,7 @@
         <v>43</v>
       </c>
       <c r="R377" s="11">
-        <v>46382.125</v>
+        <v>46493.125</v>
       </c>
       <c r="T377" s="0" t="s">
         <v>44</v>
@@ -35613,13 +35618,13 @@
         <v>44</v>
       </c>
       <c r="AH377" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AI377" s="3">
-        <v>46129.41428105324</v>
+        <v>46311.44135987268</v>
       </c>
       <c r="AJ377" s="3">
-        <v>46309</v>
+        <v>46491.125</v>
       </c>
     </row>
     <row r="378">
@@ -35737,10 +35742,10 @@
         <v>46341.125</v>
       </c>
       <c r="K379" s="0" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="L379" s="0" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="M379" s="0" t="s">
         <v>39</v>
@@ -35755,7 +35760,7 @@
         <v>43</v>
       </c>
       <c r="R379" s="11">
-        <v>46360.125</v>
+        <v>46493.125</v>
       </c>
       <c r="T379" s="0" t="s">
         <v>44</v>
@@ -45836,7 +45841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -45876,25 +45881,25 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>1065</v>
+        <v>841</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>1077</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>804</v>
+        <v>641</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="11">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="F2" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="11">
-        <v>46483.125</v>
+        <v>46491.125</v>
       </c>
       <c r="H2" s="0" t="s">
         <v>1078</v>
@@ -45903,7 +45908,7 @@
         <v>1079</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>804</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3">
@@ -45911,25 +45916,25 @@
         <v>1065</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>804</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="11">
         <v>46303</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>1080</v>
+        <v>30</v>
       </c>
       <c r="G3" s="11">
         <v>46483.125</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="I3" s="0" t="s">
         <v>1079</v>
@@ -45940,66 +45945,66 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>877</v>
+        <v>1065</v>
       </c>
       <c r="B4" s="0" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>804</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="11">
+        <v>46303</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G4" s="11">
+        <v>46483.125</v>
+      </c>
+      <c r="H4" s="0" t="s">
         <v>1081</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>641</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="11">
-        <v>46300</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="11">
-        <v>46480.125</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>1082</v>
       </c>
       <c r="I4" s="0" t="s">
         <v>1079</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>645</v>
+        <v>804</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1064</v>
+        <v>877</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>1083</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>224</v>
+        <v>641</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="11">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="F5" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G5" s="11">
-        <v>46476.125</v>
+        <v>46480.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="I5" s="0" t="s">
         <v>1079</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>224</v>
+        <v>645</v>
       </c>
     </row>
     <row r="6">
@@ -46007,25 +46012,25 @@
         <v>1064</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>224</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="11">
         <v>46296</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>1080</v>
+        <v>30</v>
       </c>
       <c r="G6" s="11">
         <v>46476.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="I6" s="0" t="s">
         <v>1079</v>
@@ -46036,42 +46041,42 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B7" s="0" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="11">
+        <v>46296</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G7" s="11">
+        <v>46476.125</v>
+      </c>
+      <c r="H7" s="0" t="s">
         <v>1085</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="11">
-        <v>46294</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="11">
-        <v>46474.125</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>1086</v>
-      </c>
       <c r="I7" s="0" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>34</v>
@@ -46089,10 +46094,10 @@
         <v>46474.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>203</v>
@@ -46100,13 +46105,13 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>876</v>
+        <v>1063</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>641</v>
+        <v>34</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>30</v>
@@ -46121,13 +46126,13 @@
         <v>46474.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1079</v>
+        <v>1088</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>645</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -46135,25 +46140,25 @@
         <v>876</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>641</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="11">
         <v>46294</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>1080</v>
+        <v>30</v>
       </c>
       <c r="G10" s="11">
         <v>46474.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="I10" s="0" t="s">
         <v>1079</v>
@@ -46164,7 +46169,7 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>839</v>
+        <v>876</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>1089</v>
@@ -46173,19 +46178,19 @@
         <v>641</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" s="11">
         <v>46294</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>30</v>
+        <v>1082</v>
       </c>
       <c r="G11" s="11">
         <v>46474.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="I11" s="0" t="s">
         <v>1079</v>
@@ -46199,25 +46204,25 @@
         <v>839</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>641</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="11">
         <v>46294</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>1080</v>
+        <v>30</v>
       </c>
       <c r="G12" s="11">
         <v>46474.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="I12" s="0" t="s">
         <v>1079</v>
@@ -46228,34 +46233,34 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>972</v>
+        <v>839</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>1090</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>61</v>
+        <v>641</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E13" s="11">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="G13" s="11">
-        <v>46469.125</v>
+        <v>46474.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1092</v>
+        <v>1078</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1093</v>
+        <v>1079</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>67</v>
+        <v>645</v>
       </c>
     </row>
     <row r="14">
@@ -46263,28 +46268,28 @@
         <v>972</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>61</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="11">
         <v>46289</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>30</v>
+        <v>1092</v>
       </c>
       <c r="G14" s="11">
         <v>46469.125</v>
       </c>
       <c r="H14" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I14" s="0" t="s">
         <v>1094</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>1087</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>67</v>
@@ -46292,34 +46297,34 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>1058</v>
+        <v>972</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>641</v>
+        <v>61</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="11">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G15" s="11">
-        <v>46455.125</v>
+        <v>46469.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1079</v>
+        <v>1088</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>645</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -46327,25 +46332,25 @@
         <v>1058</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>641</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="11">
         <v>46275</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>1080</v>
+        <v>30</v>
       </c>
       <c r="G16" s="11">
         <v>46455.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="I16" s="0" t="s">
         <v>1079</v>
@@ -46356,34 +46361,34 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>848</v>
+        <v>1058</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>1096</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>847</v>
+        <v>641</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" s="11">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>30</v>
+        <v>1082</v>
       </c>
       <c r="G17" s="11">
-        <v>46449.125</v>
+        <v>46455.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1097</v>
+        <v>1078</v>
       </c>
       <c r="I17" s="0" t="s">
         <v>1079</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>849</v>
+        <v>645</v>
       </c>
     </row>
     <row r="18">
@@ -46391,25 +46396,25 @@
         <v>848</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>847</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" s="11">
         <v>46269</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1080</v>
+        <v>30</v>
       </c>
       <c r="G18" s="11">
         <v>46449.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="I18" s="0" t="s">
         <v>1079</v>
@@ -46423,25 +46428,25 @@
         <v>848</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>847</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" s="11">
         <v>46269</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>30</v>
+        <v>1082</v>
       </c>
       <c r="G19" s="11">
-        <v>46268</v>
+        <v>46449.125</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="I19" s="0" t="s">
         <v>1079</v>
@@ -46452,34 +46457,34 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>548</v>
+        <v>848</v>
       </c>
       <c r="B20" s="0" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>847</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="11">
+        <v>46269</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="11">
+        <v>46268</v>
+      </c>
+      <c r="H20" s="0" t="s">
         <v>1098</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="11">
-        <v>46267</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G20" s="11">
-        <v>46447.125</v>
-      </c>
-      <c r="H20" s="0" t="s">
-        <v>1092</v>
-      </c>
       <c r="I20" s="0" t="s">
-        <v>1093</v>
+        <v>1079</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>1099</v>
+        <v>849</v>
       </c>
     </row>
     <row r="21">
@@ -46487,71 +46492,71 @@
         <v>548</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" s="11">
         <v>46267</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>30</v>
+        <v>1092</v>
       </c>
       <c r="G21" s="11">
         <v>46447.125</v>
       </c>
       <c r="H21" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I21" s="0" t="s">
         <v>1094</v>
       </c>
-      <c r="I21" s="0" t="s">
-        <v>1087</v>
-      </c>
       <c r="J21" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>866</v>
+        <v>548</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="11">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="11">
-        <v>46446.125</v>
+        <v>46447.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>607</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>61</v>
@@ -46569,10 +46574,10 @@
         <v>46446.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>607</v>
@@ -46580,138 +46585,138 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>550</v>
+        <v>869</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>1101</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E24" s="11">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>1091</v>
+        <v>30</v>
       </c>
       <c r="G24" s="11">
-        <v>46441.125</v>
+        <v>46446.125</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>1103</v>
+        <v>607</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>865</v>
+        <v>550</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="11">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="G25" s="11">
-        <v>46440.125</v>
+        <v>46441.125</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>203</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>1056</v>
+        <v>865</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>1105</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" s="11">
         <v>46260</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>30</v>
+        <v>1092</v>
       </c>
       <c r="G26" s="11">
         <v>46440.125</v>
       </c>
       <c r="H26" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I26" s="0" t="s">
         <v>1094</v>
       </c>
-      <c r="I26" s="0" t="s">
-        <v>1087</v>
-      </c>
       <c r="J26" s="0" t="s">
-        <v>67</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>864</v>
+        <v>1056</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>1106</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="11">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F27" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="11">
-        <v>46439.125</v>
+        <v>46440.125</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>203</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>655</v>
+        <v>864</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>34</v>
@@ -46729,10 +46734,10 @@
         <v>46439.125</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>203</v>
@@ -46740,10 +46745,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>865</v>
+        <v>655</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>34</v>
@@ -46761,10 +46766,10 @@
         <v>46439.125</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>203</v>
@@ -46772,13 +46777,13 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>651</v>
+        <v>865</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>30</v>
@@ -46793,18 +46798,18 @@
         <v>46439.125</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J30" s="0" t="s">
-        <v>607</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>340</v>
+        <v>651</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>1108</v>
@@ -46825,18 +46830,18 @@
         <v>46439.125</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>67</v>
+        <v>607</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>470</v>
+        <v>340</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>1109</v>
@@ -46845,22 +46850,22 @@
         <v>61</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E32" s="11">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>1091</v>
+        <v>30</v>
       </c>
       <c r="G32" s="11">
-        <v>46435.125</v>
+        <v>46439.125</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>67</v>
@@ -46871,28 +46876,28 @@
         <v>470</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>61</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E33" s="11">
         <v>46255</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>30</v>
+        <v>1092</v>
       </c>
       <c r="G33" s="11">
         <v>46435.125</v>
       </c>
       <c r="H33" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I33" s="0" t="s">
         <v>1094</v>
-      </c>
-      <c r="I33" s="0" t="s">
-        <v>1087</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>67</v>
@@ -46900,7 +46905,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>648</v>
+        <v>470</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>1110</v>
@@ -46912,27 +46917,27 @@
         <v>30</v>
       </c>
       <c r="E34" s="11">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="F34" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G34" s="11">
-        <v>46432.125</v>
+        <v>46435.125</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>607</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>605</v>
+        <v>648</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>1111</v>
@@ -46953,10 +46958,10 @@
         <v>46432.125</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>607</v>
@@ -46964,13 +46969,13 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>1112</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>30</v>
@@ -46985,18 +46990,18 @@
         <v>46432.125</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>46</v>
+        <v>607</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>995</v>
+        <v>604</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>1113</v>
@@ -47017,10 +47022,10 @@
         <v>46432.125</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>46</v>
@@ -47028,33 +47033,65 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>604</v>
+        <v>995</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>34</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E38" s="11">
         <v>46252</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>1091</v>
+        <v>30</v>
       </c>
       <c r="G38" s="11">
         <v>46432.125</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="J38" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="11">
+        <v>46252</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G39" s="11">
+        <v>46432.125</v>
+      </c>
+      <c r="H39" s="0" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I39" s="0" t="s">
+        <v>1094</v>
+      </c>
+      <c r="J39" s="0" t="s">
         <v>46</v>
       </c>
     </row>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -2634,9 +2634,6 @@
     <t>EGI3E88</t>
   </si>
   <si>
-    <t>Inspeção Checklist de Qualidade pendente / Documento ConsultaCRLV vencendo</t>
-  </si>
-  <si>
     <t>Copel Industria e Comercio de Reciclaveis LTDA</t>
   </si>
   <si>
@@ -3255,6 +3252,18 @@
     <t>Perfil Responsável</t>
   </si>
   <si>
+    <t>SR / IMPERIAL GR000227T0 1</t>
+  </si>
+  <si>
+    <t>Checklist de Qualidade Safra</t>
+  </si>
+  <si>
+    <t>MARCONI BELO SOBRINHO</t>
+  </si>
+  <si>
+    <t>Gestor Heinz</t>
+  </si>
+  <si>
     <t>Volkswagen / VW/19.330 CTC 4X2</t>
   </si>
   <si>
@@ -3300,15 +3309,9 @@
     <t>M. BENZ / L 2013</t>
   </si>
   <si>
-    <t>Checklist de Qualidade Safra</t>
-  </si>
-  <si>
     <t>MARCIO ADRINO GONCALVES</t>
   </si>
   <si>
-    <t>Gestor Heinz</t>
-  </si>
-  <si>
     <t>Denisclea Silva</t>
   </si>
   <si>
@@ -3325,9 +3328,6 @@
   </si>
   <si>
     <t>MILHO | GNOVA TRANSPORTES LTDA;TOMATE | GNOVA TRANSPORTES LTDA</t>
-  </si>
-  <si>
-    <t>SR / IMPERIAL GR000227T0 1</t>
   </si>
   <si>
     <t>SR/IMPERIAL GR000227T0 1 / SR/IMPERIAL GR000227T0 1</t>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46314.33859302083</v>
+        <v>46314.62248803241</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -36620,12 +36620,14 @@
       <c r="G390" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="J390" s="11"/>
+      <c r="J390" s="11">
+        <v>46326.125</v>
+      </c>
       <c r="K390" s="0" t="s">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="L390" s="0" t="s">
-        <v>873</v>
+        <v>206</v>
       </c>
       <c r="M390" s="0" t="s">
         <v>39</v>
@@ -36661,10 +36663,14 @@
         <v>46076.369408252314</v>
       </c>
       <c r="AE390" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF390" s="3"/>
-      <c r="AG390" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="AF390" s="3">
+        <v>46314.364552743056</v>
+      </c>
+      <c r="AG390" s="3">
+        <v>46494.125</v>
+      </c>
       <c r="AH390" s="0" t="s">
         <v>43</v>
       </c>
@@ -36680,22 +36686,22 @@
         <v>860</v>
       </c>
       <c r="B391" s="0" t="s">
+        <v>873</v>
+      </c>
+      <c r="C391" s="0" t="s">
         <v>874</v>
-      </c>
-      <c r="C391" s="0" t="s">
-        <v>875</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E391" s="0" t="s">
+        <v>875</v>
+      </c>
+      <c r="F391" s="0" t="s">
         <v>876</v>
       </c>
-      <c r="F391" s="0" t="s">
-        <v>877</v>
-      </c>
       <c r="G391" s="0" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="J391" s="11">
         <v>46401.125</v>
@@ -36728,7 +36734,7 @@
         <v>45</v>
       </c>
       <c r="AC391" s="0" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AD391" s="11">
         <v>46104.56253545139</v>
@@ -36760,7 +36766,7 @@
         <v>643</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>109</v>
@@ -36846,7 +36852,7 @@
         <v>643</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>63</v>
@@ -36932,13 +36938,13 @@
         <v>61</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E394" s="0" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F394" s="0" t="s">
         <v>60</v>
@@ -36951,7 +36957,7 @@
         <v>40</v>
       </c>
       <c r="L394" s="0" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M394" s="0" t="s">
         <v>39</v>
@@ -37013,7 +37019,7 @@
         <v>643</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>109</v>
@@ -37035,7 +37041,7 @@
         <v>40</v>
       </c>
       <c r="L395" s="0" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M395" s="0" t="s">
         <v>39</v>
@@ -37097,7 +37103,7 @@
         <v>34</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>198</v>
@@ -37183,13 +37189,13 @@
         <v>49</v>
       </c>
       <c r="C397" s="0" t="s">
+        <v>886</v>
+      </c>
+      <c r="D397" s="0" t="s">
         <v>887</v>
       </c>
-      <c r="D397" s="0" t="s">
-        <v>888</v>
-      </c>
       <c r="E397" s="0" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F397" s="0" t="s">
         <v>244</v>
@@ -37198,7 +37204,7 @@
         <v>244</v>
       </c>
       <c r="H397" s="0" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J397" s="11">
         <v>46413.125</v>
@@ -37269,13 +37275,13 @@
         <v>49</v>
       </c>
       <c r="C398" s="0" t="s">
+        <v>889</v>
+      </c>
+      <c r="D398" s="0" t="s">
         <v>890</v>
       </c>
-      <c r="D398" s="0" t="s">
-        <v>891</v>
-      </c>
       <c r="E398" s="0" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F398" s="0" t="s">
         <v>53</v>
@@ -37284,7 +37290,7 @@
         <v>54</v>
       </c>
       <c r="H398" s="0" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J398" s="11">
         <v>46357.125</v>
@@ -37355,7 +37361,7 @@
         <v>34</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>162</v>
@@ -37370,7 +37376,7 @@
         <v>54</v>
       </c>
       <c r="H399" s="0" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="J399" s="11">
         <v>46361.125</v>
@@ -37441,7 +37447,7 @@
         <v>34</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>51</v>
@@ -37456,7 +37462,7 @@
         <v>150</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J400" s="11">
         <v>46365.125</v>
@@ -37527,7 +37533,7 @@
         <v>34</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>51</v>
@@ -37542,7 +37548,7 @@
         <v>134</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J401" s="11">
         <v>46365.125</v>
@@ -37613,7 +37619,7 @@
         <v>34</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>36</v>
@@ -37628,7 +37634,7 @@
         <v>134</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J402" s="11"/>
       <c r="K402" s="0" t="s">
@@ -37697,13 +37703,13 @@
         <v>49</v>
       </c>
       <c r="C403" s="0" t="s">
+        <v>898</v>
+      </c>
+      <c r="D403" s="0" t="s">
         <v>899</v>
       </c>
-      <c r="D403" s="0" t="s">
-        <v>900</v>
-      </c>
       <c r="E403" s="0" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F403" s="0" t="s">
         <v>54</v>
@@ -37712,7 +37718,7 @@
         <v>54</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J403" s="11">
         <v>46365.125</v>
@@ -37783,7 +37789,7 @@
         <v>49</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>322</v>
@@ -37798,7 +37804,7 @@
         <v>134</v>
       </c>
       <c r="H404" s="0" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J404" s="11">
         <v>46362.125</v>
@@ -37869,13 +37875,13 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E405" s="0" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F405" s="0" t="s">
         <v>65</v>
@@ -37955,7 +37961,7 @@
         <v>34</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>36</v>
@@ -38041,7 +38047,7 @@
         <v>34</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>36</v>
@@ -38127,13 +38133,13 @@
         <v>34</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E408" s="0" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F408" s="0" t="s">
         <v>439</v>
@@ -38142,7 +38148,7 @@
         <v>439</v>
       </c>
       <c r="H408" s="0" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J408" s="11"/>
       <c r="K408" s="0" t="s">
@@ -38211,13 +38217,13 @@
         <v>34</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E409" s="0" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F409" s="0" t="s">
         <v>134</v>
@@ -38226,7 +38232,7 @@
         <v>134</v>
       </c>
       <c r="H409" s="0" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J409" s="11"/>
       <c r="K409" s="0" t="s">
@@ -38295,7 +38301,7 @@
         <v>34</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>72</v>
@@ -38382,7 +38388,7 @@
         <v>34</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>51</v>
@@ -38397,7 +38403,7 @@
         <v>339</v>
       </c>
       <c r="H411" s="0" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="J411" s="11">
         <v>46356.125</v>
@@ -38471,13 +38477,13 @@
         <v>34</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>140</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F412" s="0" t="s">
         <v>142</v>
@@ -38486,7 +38492,7 @@
         <v>142</v>
       </c>
       <c r="H412" s="0" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="J412" s="11"/>
       <c r="K412" s="0" t="s">
@@ -38558,13 +38564,13 @@
         <v>34</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E413" s="0" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F413" s="0" t="s">
         <v>93</v>
@@ -38573,7 +38579,7 @@
         <v>93</v>
       </c>
       <c r="H413" s="0" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="J413" s="11"/>
       <c r="K413" s="0" t="s">
@@ -38645,7 +38651,7 @@
         <v>34</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>123</v>
@@ -38660,7 +38666,7 @@
         <v>60</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="J414" s="11"/>
       <c r="K414" s="0" t="s">
@@ -38729,7 +38735,7 @@
         <v>34</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>123</v>
@@ -38744,7 +38750,7 @@
         <v>60</v>
       </c>
       <c r="H415" s="0" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="J415" s="11"/>
       <c r="K415" s="0" t="s">
@@ -38813,13 +38819,13 @@
         <v>49</v>
       </c>
       <c r="C416" s="0" t="s">
+        <v>922</v>
+      </c>
+      <c r="D416" s="0" t="s">
         <v>923</v>
       </c>
-      <c r="D416" s="0" t="s">
-        <v>924</v>
-      </c>
       <c r="E416" s="0" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F416" s="0" t="s">
         <v>200</v>
@@ -38896,7 +38902,7 @@
         <v>34</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>63</v>
@@ -38982,7 +38988,7 @@
         <v>34</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>36</v>
@@ -38997,14 +39003,14 @@
         <v>38</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="J418" s="11"/>
       <c r="K418" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L418" s="0" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M418" s="0" t="s">
         <v>39</v>
@@ -39069,7 +39075,7 @@
         <v>34</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>36</v>
@@ -39084,14 +39090,14 @@
         <v>38</v>
       </c>
       <c r="H419" s="0" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="J419" s="11"/>
       <c r="K419" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L419" s="0" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M419" s="0" t="s">
         <v>39</v>
@@ -39156,13 +39162,13 @@
         <v>49</v>
       </c>
       <c r="C420" s="0" t="s">
+        <v>929</v>
+      </c>
+      <c r="D420" s="0" t="s">
         <v>930</v>
       </c>
-      <c r="D420" s="0" t="s">
-        <v>931</v>
-      </c>
       <c r="E420" s="0" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F420" s="0" t="s">
         <v>65</v>
@@ -39239,7 +39245,7 @@
         <v>49</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>322</v>
@@ -39322,13 +39328,13 @@
         <v>34</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>315</v>
       </c>
       <c r="E422" s="0" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F422" s="0" t="s">
         <v>93</v>
@@ -39337,14 +39343,14 @@
         <v>38</v>
       </c>
       <c r="H422" s="0" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="J422" s="11"/>
       <c r="K422" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L422" s="0" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="M422" s="0" t="s">
         <v>39</v>
@@ -39409,7 +39415,7 @@
         <v>49</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>388</v>
@@ -39492,13 +39498,13 @@
         <v>49</v>
       </c>
       <c r="C424" s="0" t="s">
+        <v>936</v>
+      </c>
+      <c r="D424" s="0" t="s">
         <v>937</v>
       </c>
-      <c r="D424" s="0" t="s">
-        <v>938</v>
-      </c>
       <c r="E424" s="0" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F424" s="0" t="s">
         <v>150</v>
@@ -39575,7 +39581,7 @@
         <v>61</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>51</v>
@@ -39590,7 +39596,7 @@
         <v>168</v>
       </c>
       <c r="H425" s="0" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="J425" s="11"/>
       <c r="K425" s="0" t="s">
@@ -39659,13 +39665,13 @@
         <v>61</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E426" s="0" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F426" s="0" t="s">
         <v>332</v>
@@ -39674,7 +39680,7 @@
         <v>332</v>
       </c>
       <c r="H426" s="0" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="J426" s="11">
         <v>46373.125</v>
@@ -39745,7 +39751,7 @@
         <v>61</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>77</v>
@@ -39760,7 +39766,7 @@
         <v>524</v>
       </c>
       <c r="H427" s="0" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="J427" s="11"/>
       <c r="K427" s="0" t="s">
@@ -39832,13 +39838,13 @@
         <v>61</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E428" s="0" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F428" s="0" t="s">
         <v>169</v>
@@ -39921,7 +39927,7 @@
         <v>61</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>77</v>
@@ -39936,7 +39942,7 @@
         <v>54</v>
       </c>
       <c r="H429" s="0" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="J429" s="11">
         <v>46373.125</v>
@@ -40007,13 +40013,13 @@
         <v>61</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E430" s="0" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="F430" s="0" t="s">
         <v>258</v>
@@ -40022,7 +40028,7 @@
         <v>258</v>
       </c>
       <c r="H430" s="0" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="J430" s="11"/>
       <c r="K430" s="0" t="s">
@@ -40091,7 +40097,7 @@
         <v>61</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>51</v>
@@ -40106,7 +40112,7 @@
         <v>150</v>
       </c>
       <c r="H431" s="0" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="J431" s="11">
         <v>46373.125</v>
@@ -40177,13 +40183,13 @@
         <v>61</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>731</v>
       </c>
       <c r="E432" s="0" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F432" s="0" t="s">
         <v>209</v>
@@ -40261,7 +40267,7 @@
         <v>61</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D433" s="0" t="s">
         <v>250</v>
@@ -40276,7 +40282,7 @@
         <v>327</v>
       </c>
       <c r="H433" s="0" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="J433" s="11"/>
       <c r="K433" s="0" t="s">
@@ -40345,7 +40351,7 @@
         <v>61</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>260</v>
@@ -40360,7 +40366,7 @@
         <v>93</v>
       </c>
       <c r="H434" s="0" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="J434" s="11"/>
       <c r="K434" s="0" t="s">
@@ -40429,13 +40435,13 @@
         <v>61</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>260</v>
       </c>
       <c r="E435" s="0" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F435" s="0" t="s">
         <v>168</v>
@@ -40444,7 +40450,7 @@
         <v>168</v>
       </c>
       <c r="H435" s="0" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="J435" s="11"/>
       <c r="K435" s="0" t="s">
@@ -40516,7 +40522,7 @@
         <v>61</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>250</v>
@@ -40603,13 +40609,13 @@
         <v>61</v>
       </c>
       <c r="C437" s="0" t="s">
+        <v>961</v>
+      </c>
+      <c r="D437" s="0" t="s">
         <v>962</v>
       </c>
-      <c r="D437" s="0" t="s">
+      <c r="E437" s="0" t="s">
         <v>963</v>
-      </c>
-      <c r="E437" s="0" t="s">
-        <v>964</v>
       </c>
       <c r="F437" s="0" t="s">
         <v>294</v>
@@ -40689,7 +40695,7 @@
         <v>61</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>260</v>
@@ -40776,7 +40782,7 @@
         <v>61</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>412</v>
@@ -40791,7 +40797,7 @@
         <v>169</v>
       </c>
       <c r="H439" s="0" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="J439" s="11">
         <v>46373.125</v>
@@ -40862,7 +40868,7 @@
         <v>61</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D440" s="0" t="s">
         <v>260</v>
@@ -40946,7 +40952,7 @@
         <v>61</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>260</v>
@@ -41030,7 +41036,7 @@
         <v>61</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>412</v>
@@ -41045,7 +41051,7 @@
         <v>327</v>
       </c>
       <c r="H442" s="0" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="J442" s="11">
         <v>46373.125</v>
@@ -41116,7 +41122,7 @@
         <v>61</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>260</v>
@@ -41131,7 +41137,7 @@
         <v>74</v>
       </c>
       <c r="H443" s="0" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="J443" s="11"/>
       <c r="K443" s="0" t="s">
@@ -41200,7 +41206,7 @@
         <v>61</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>260</v>
@@ -41287,7 +41293,7 @@
         <v>61</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>412</v>
@@ -41302,7 +41308,7 @@
         <v>169</v>
       </c>
       <c r="H445" s="0" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="J445" s="11">
         <v>46373.125</v>
@@ -41373,7 +41379,7 @@
         <v>61</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>260</v>
@@ -41457,7 +41463,7 @@
         <v>61</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>162</v>
@@ -41472,7 +41478,7 @@
         <v>176</v>
       </c>
       <c r="H447" s="0" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="J447" s="11"/>
       <c r="K447" s="0" t="s">
@@ -41541,13 +41547,13 @@
         <v>61</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E448" s="0" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F448" s="0" t="s">
         <v>502</v>
@@ -41556,7 +41562,7 @@
         <v>502</v>
       </c>
       <c r="H448" s="0" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="J448" s="11">
         <v>46373.125</v>
@@ -41627,7 +41633,7 @@
         <v>61</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>162</v>
@@ -41642,7 +41648,7 @@
         <v>518</v>
       </c>
       <c r="H449" s="0" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="J449" s="11"/>
       <c r="K449" s="0" t="s">
@@ -41711,13 +41717,13 @@
         <v>61</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E450" s="0" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F450" s="0" t="s">
         <v>332</v>
@@ -41726,7 +41732,7 @@
         <v>332</v>
       </c>
       <c r="H450" s="0" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="J450" s="11"/>
       <c r="K450" s="0" t="s">
@@ -41798,7 +41804,7 @@
         <v>61</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>162</v>
@@ -41813,7 +41819,7 @@
         <v>332</v>
       </c>
       <c r="H451" s="0" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="J451" s="11"/>
       <c r="K451" s="0" t="s">
@@ -41879,22 +41885,22 @@
         <v>860</v>
       </c>
       <c r="B452" s="0" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C452" s="0" t="s">
+        <v>986</v>
+      </c>
+      <c r="D452" s="0" t="s">
         <v>987</v>
       </c>
-      <c r="D452" s="0" t="s">
-        <v>988</v>
-      </c>
       <c r="E452" s="0" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F452" s="0" t="s">
         <v>300</v>
       </c>
       <c r="G452" s="0" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="J452" s="11">
         <v>46383.125</v>
@@ -41927,7 +41933,7 @@
         <v>45</v>
       </c>
       <c r="AC452" s="0" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AD452" s="11">
         <v>46203.65469700231</v>
@@ -41959,7 +41965,7 @@
         <v>643</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>63</v>
@@ -42045,7 +42051,7 @@
         <v>643</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>770</v>
@@ -42131,13 +42137,13 @@
         <v>34</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E455" s="0" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F455" s="0" t="s">
         <v>85</v>
@@ -42214,7 +42220,7 @@
         <v>34</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>36</v>
@@ -42297,7 +42303,7 @@
         <v>34</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>123</v>
@@ -42312,7 +42318,7 @@
         <v>74</v>
       </c>
       <c r="H457" s="0" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J457" s="11">
         <v>46387.125</v>
@@ -42383,7 +42389,7 @@
         <v>34</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D458" s="0" t="s">
         <v>123</v>
@@ -42398,7 +42404,7 @@
         <v>74</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J458" s="11">
         <v>46326.125</v>
@@ -42469,7 +42475,7 @@
         <v>34</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>51</v>
@@ -42484,7 +42490,7 @@
         <v>326</v>
       </c>
       <c r="H459" s="0" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J459" s="11">
         <v>46326.125</v>
@@ -42555,13 +42561,13 @@
         <v>34</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E460" s="0" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F460" s="0" t="s">
         <v>131</v>
@@ -42639,13 +42645,13 @@
         <v>34</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>179</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F461" s="0" t="s">
         <v>149</v>
@@ -42654,7 +42660,7 @@
         <v>149</v>
       </c>
       <c r="H461" s="0" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="J461" s="11"/>
       <c r="K461" s="0" t="s">
@@ -42723,13 +42729,13 @@
         <v>61</v>
       </c>
       <c r="C462" s="0" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D462" s="0" t="s">
         <v>1003</v>
       </c>
-      <c r="D462" s="0" t="s">
+      <c r="E462" s="0" t="s">
         <v>1004</v>
-      </c>
-      <c r="E462" s="0" t="s">
-        <v>1005</v>
       </c>
       <c r="F462" s="0" t="s">
         <v>418</v>
@@ -42738,7 +42744,7 @@
         <v>418</v>
       </c>
       <c r="H462" s="0" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="J462" s="11"/>
       <c r="K462" s="0" t="s">
@@ -42804,7 +42810,7 @@
         <v>61</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>77</v>
@@ -42819,7 +42825,7 @@
         <v>332</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="J463" s="11">
         <v>46406.125</v>
@@ -42890,13 +42896,13 @@
         <v>61</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F464" s="0" t="s">
         <v>79</v>
@@ -42905,7 +42911,7 @@
         <v>232</v>
       </c>
       <c r="H464" s="0" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="J464" s="11">
         <v>46407.125</v>
@@ -42976,7 +42982,7 @@
         <v>61</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>250</v>
@@ -42991,7 +42997,7 @@
         <v>134</v>
       </c>
       <c r="H465" s="0" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="J465" s="11">
         <v>46407.125</v>
@@ -43062,7 +43068,7 @@
         <v>61</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>250</v>
@@ -43077,7 +43083,7 @@
         <v>134</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="J466" s="11">
         <v>46407.125</v>
@@ -43148,7 +43154,7 @@
         <v>61</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>770</v>
@@ -43163,7 +43169,7 @@
         <v>54</v>
       </c>
       <c r="H467" s="0" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="J467" s="11">
         <v>46406.125</v>
@@ -43234,7 +43240,7 @@
         <v>61</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>260</v>
@@ -43249,7 +43255,7 @@
         <v>74</v>
       </c>
       <c r="H468" s="0" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="J468" s="11">
         <v>46373.125</v>
@@ -43320,7 +43326,7 @@
         <v>49</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>51</v>
@@ -43406,13 +43412,13 @@
         <v>227</v>
       </c>
       <c r="C470" s="0" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D470" s="0" t="s">
         <v>1018</v>
       </c>
-      <c r="D470" s="0" t="s">
+      <c r="E470" s="0" t="s">
         <v>1019</v>
-      </c>
-      <c r="E470" s="0" t="s">
-        <v>1020</v>
       </c>
       <c r="F470" s="0" t="s">
         <v>142</v>
@@ -43421,7 +43427,7 @@
         <v>142</v>
       </c>
       <c r="H470" s="0" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="J470" s="11">
         <v>46398.125</v>
@@ -43489,13 +43495,13 @@
         <v>807</v>
       </c>
       <c r="C471" s="0" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D471" s="0" t="s">
         <v>1022</v>
       </c>
-      <c r="D471" s="0" t="s">
+      <c r="E471" s="0" t="s">
         <v>1023</v>
-      </c>
-      <c r="E471" s="0" t="s">
-        <v>1024</v>
       </c>
       <c r="F471" s="0" t="s">
         <v>200</v>
@@ -43534,7 +43540,7 @@
         <v>45</v>
       </c>
       <c r="AC471" s="0" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="AD471" s="11">
         <v>46219.55652277778</v>
@@ -43566,7 +43572,7 @@
         <v>49</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>382</v>
@@ -43581,7 +43587,7 @@
         <v>339</v>
       </c>
       <c r="H472" s="0" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="J472" s="11">
         <v>46402.125</v>
@@ -43652,7 +43658,7 @@
         <v>61</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>51</v>
@@ -43667,7 +43673,7 @@
         <v>79</v>
       </c>
       <c r="H473" s="0" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="J473" s="11">
         <v>46346.125</v>
@@ -43738,13 +43744,13 @@
         <v>61</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>250</v>
       </c>
       <c r="E474" s="0" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="F474" s="0" t="s">
         <v>339</v>
@@ -43753,7 +43759,7 @@
         <v>53</v>
       </c>
       <c r="H474" s="0" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="J474" s="11">
         <v>46346.125</v>
@@ -43824,7 +43830,7 @@
         <v>61</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D475" s="0" t="s">
         <v>250</v>
@@ -43839,7 +43845,7 @@
         <v>208</v>
       </c>
       <c r="H475" s="0" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="J475" s="11"/>
       <c r="K475" s="0" t="s">
@@ -43908,7 +43914,7 @@
         <v>61</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>51</v>
@@ -43923,7 +43929,7 @@
         <v>150</v>
       </c>
       <c r="H476" s="0" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="J476" s="11">
         <v>46407.125</v>
@@ -43994,7 +44000,7 @@
         <v>61</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>260</v>
@@ -44009,7 +44015,7 @@
         <v>232</v>
       </c>
       <c r="H477" s="0" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="J477" s="11">
         <v>46407.125</v>
@@ -44080,7 +44086,7 @@
         <v>61</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D478" s="0" t="s">
         <v>260</v>
@@ -44095,7 +44101,7 @@
         <v>232</v>
       </c>
       <c r="H478" s="0" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="J478" s="11">
         <v>46407.125</v>
@@ -44166,7 +44172,7 @@
         <v>621</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D479" s="0" t="s">
         <v>212</v>
@@ -44246,13 +44252,13 @@
         <v>621</v>
       </c>
       <c r="C480" s="0" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D480" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="D480" s="0" t="s">
-        <v>1040</v>
-      </c>
       <c r="E480" s="0" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F480" s="0" t="s">
         <v>439</v>
@@ -44326,13 +44332,13 @@
         <v>49</v>
       </c>
       <c r="C481" s="0" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D481" s="0" t="s">
         <v>1041</v>
       </c>
-      <c r="D481" s="0" t="s">
-        <v>1042</v>
-      </c>
       <c r="E481" s="0" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F481" s="0" t="s">
         <v>98</v>
@@ -44412,13 +44418,13 @@
         <v>34</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F482" s="0" t="s">
         <v>38</v>
@@ -44427,7 +44433,7 @@
         <v>38</v>
       </c>
       <c r="H482" s="0" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="J482" s="11"/>
       <c r="K482" s="0" t="s">
@@ -44496,13 +44502,13 @@
         <v>49</v>
       </c>
       <c r="C483" s="0" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D483" s="0" t="s">
         <v>1046</v>
       </c>
-      <c r="D483" s="0" t="s">
-        <v>1047</v>
-      </c>
       <c r="E483" s="0" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F483" s="0" t="s">
         <v>137</v>
@@ -44579,7 +44585,7 @@
         <v>49</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>345</v>
@@ -44662,7 +44668,7 @@
         <v>49</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>345</v>
@@ -44745,7 +44751,7 @@
         <v>34</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D486" s="0" t="s">
         <v>250</v>
@@ -44760,7 +44766,7 @@
         <v>38</v>
       </c>
       <c r="H486" s="0" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J486" s="11">
         <v>46362.125</v>
@@ -44831,7 +44837,7 @@
         <v>34</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D487" s="0" t="s">
         <v>250</v>
@@ -44846,7 +44852,7 @@
         <v>38</v>
       </c>
       <c r="H487" s="0" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J487" s="11">
         <v>46362.125</v>
@@ -44917,7 +44923,7 @@
         <v>49</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>366</v>
@@ -45000,13 +45006,13 @@
         <v>49</v>
       </c>
       <c r="C489" s="0" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D489" s="0" t="s">
         <v>1053</v>
       </c>
-      <c r="D489" s="0" t="s">
-        <v>1054</v>
-      </c>
       <c r="E489" s="0" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F489" s="0" t="s">
         <v>258</v>
@@ -45083,13 +45089,13 @@
         <v>49</v>
       </c>
       <c r="C490" s="0" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D490" s="0" t="s">
         <v>1055</v>
       </c>
-      <c r="D490" s="0" t="s">
-        <v>1056</v>
-      </c>
       <c r="E490" s="0" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F490" s="0" t="s">
         <v>131</v>
@@ -45166,13 +45172,13 @@
         <v>49</v>
       </c>
       <c r="C491" s="0" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D491" s="0" t="s">
         <v>1057</v>
       </c>
-      <c r="D491" s="0" t="s">
-        <v>1058</v>
-      </c>
       <c r="E491" s="0" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F491" s="0" t="s">
         <v>294</v>
@@ -45249,13 +45255,13 @@
         <v>61</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E492" s="0" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F492" s="0" t="s">
         <v>105</v>
@@ -45333,13 +45339,13 @@
         <v>643</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E493" s="0" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F493" s="0" t="s">
         <v>293</v>
@@ -45419,19 +45425,19 @@
         <v>34</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E494" s="0" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F494" s="0" t="s">
         <v>863</v>
       </c>
       <c r="G494" s="0" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H494" s="0" t="s">
         <v>201</v>
@@ -45505,19 +45511,19 @@
         <v>34</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="D495" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E495" s="0" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F495" s="0" t="s">
         <v>863</v>
       </c>
       <c r="G495" s="0" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H495" s="0" t="s">
         <v>201</v>
@@ -45591,7 +45597,7 @@
         <v>227</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="D496" s="0" t="s">
         <v>526</v>
@@ -45671,13 +45677,13 @@
         <v>807</v>
       </c>
       <c r="C497" s="0" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D497" s="0" t="s">
         <v>1068</v>
       </c>
-      <c r="D497" s="0" t="s">
-        <v>1069</v>
-      </c>
       <c r="E497" s="0" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F497" s="0" t="s">
         <v>294</v>
@@ -45745,13 +45751,13 @@
         <v>850</v>
       </c>
       <c r="C498" s="0" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D498" s="0" t="s">
+        <v>937</v>
+      </c>
+      <c r="E498" s="0" t="s">
         <v>1070</v>
-      </c>
-      <c r="D498" s="0" t="s">
-        <v>938</v>
-      </c>
-      <c r="E498" s="0" t="s">
-        <v>1071</v>
       </c>
       <c r="F498" s="0" t="s">
         <v>168</v>
@@ -45764,7 +45770,7 @@
         <v>40</v>
       </c>
       <c r="L498" s="0" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="M498" s="0" t="s">
         <v>39</v>
@@ -45812,13 +45818,13 @@
         <v>850</v>
       </c>
       <c r="C499" s="0" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D499" s="0" t="s">
         <v>1073</v>
       </c>
-      <c r="D499" s="0" t="s">
-        <v>1074</v>
-      </c>
       <c r="E499" s="0" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F499" s="0" t="s">
         <v>169</v>
@@ -45831,7 +45837,7 @@
         <v>40</v>
       </c>
       <c r="L499" s="0" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="M499" s="0" t="s">
         <v>39</v>
@@ -45907,7 +45913,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -45918,28 +45924,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>1078</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>1079</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -45947,25 +45953,25 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>844</v>
+        <v>872</v>
       </c>
       <c r="B2" s="0" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="11">
+        <v>46314</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>1080</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>643</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="11">
-        <v>46311</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>30</v>
-      </c>
       <c r="G2" s="11">
-        <v>46491.125</v>
+        <v>46494.125</v>
       </c>
       <c r="H2" s="0" t="s">
         <v>1081</v>
@@ -45974,68 +45980,68 @@
         <v>1082</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>647</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>1068</v>
+        <v>844</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>1083</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>807</v>
+        <v>643</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="11">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G3" s="11">
-        <v>46483.125</v>
+        <v>46491.125</v>
       </c>
       <c r="H3" s="0" t="s">
         <v>1084</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>807</v>
+        <v>647</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>807</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="11">
         <v>46303</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>1085</v>
+        <v>30</v>
       </c>
       <c r="G4" s="11">
         <v>46483.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>807</v>
@@ -46043,95 +46049,95 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>880</v>
+        <v>1067</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>1086</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>643</v>
+        <v>807</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" s="11">
-        <v>46300</v>
+        <v>46303</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>30</v>
+        <v>1088</v>
       </c>
       <c r="G5" s="11">
-        <v>46480.125</v>
+        <v>46483.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>647</v>
+        <v>807</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>1067</v>
+        <v>879</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>227</v>
+        <v>643</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E6" s="11">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="11">
-        <v>46476.125</v>
+        <v>46480.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>227</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>227</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="11">
         <v>46296</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>1085</v>
+        <v>30</v>
       </c>
       <c r="G7" s="11">
         <v>46476.125</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>227</v>
@@ -46139,42 +46145,42 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>34</v>
+        <v>227</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="11">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>30</v>
+        <v>1088</v>
       </c>
       <c r="G8" s="11">
-        <v>46474.125</v>
+        <v>46476.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>34</v>
@@ -46192,10 +46198,10 @@
         <v>46474.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>202</v>
@@ -46203,13 +46209,13 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>879</v>
+        <v>1065</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>1092</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>643</v>
+        <v>34</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>30</v>
@@ -46224,42 +46230,42 @@
         <v>46474.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1081</v>
+        <v>1093</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>647</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>643</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="11">
         <v>46294</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>1085</v>
+        <v>30</v>
       </c>
       <c r="G11" s="11">
         <v>46474.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>647</v>
@@ -46267,31 +46273,31 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>842</v>
+        <v>878</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>643</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="11">
         <v>46294</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>30</v>
+        <v>1088</v>
       </c>
       <c r="G12" s="11">
         <v>46474.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>647</v>
@@ -46302,28 +46308,28 @@
         <v>842</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>643</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="11">
         <v>46294</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>1085</v>
+        <v>30</v>
       </c>
       <c r="G13" s="11">
         <v>46474.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>647</v>
@@ -46331,54 +46337,54 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>975</v>
+        <v>842</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>61</v>
+        <v>643</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E14" s="11">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="G14" s="11">
-        <v>46469.125</v>
+        <v>46474.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>67</v>
+        <v>647</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="11">
         <v>46289</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>30</v>
+        <v>1080</v>
       </c>
       <c r="G15" s="11">
         <v>46469.125</v>
@@ -46387,7 +46393,7 @@
         <v>1098</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>67</v>
@@ -46395,63 +46401,63 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>1061</v>
+        <v>974</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>643</v>
+        <v>61</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E16" s="11">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G16" s="11">
-        <v>46455.125</v>
+        <v>46469.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1081</v>
+        <v>1099</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>647</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>643</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" s="11">
         <v>46275</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>1085</v>
+        <v>30</v>
       </c>
       <c r="G17" s="11">
         <v>46455.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>647</v>
@@ -46459,34 +46465,34 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>851</v>
+        <v>1060</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>1100</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>850</v>
+        <v>643</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" s="11">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>30</v>
+        <v>1088</v>
       </c>
       <c r="G18" s="11">
-        <v>46449.125</v>
+        <v>46455.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1101</v>
+        <v>1084</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>852</v>
+        <v>647</v>
       </c>
     </row>
     <row r="19">
@@ -46494,28 +46500,28 @@
         <v>851</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>850</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" s="11">
         <v>46269</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>1085</v>
+        <v>30</v>
       </c>
       <c r="G19" s="11">
         <v>46449.125</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J19" s="0" t="s">
         <v>852</v>
@@ -46526,28 +46532,28 @@
         <v>851</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>850</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" s="11">
         <v>46269</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>30</v>
+        <v>1088</v>
       </c>
       <c r="G20" s="11">
-        <v>46268</v>
+        <v>46449.125</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>852</v>
@@ -46555,34 +46561,34 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>551</v>
+        <v>851</v>
       </c>
       <c r="B21" s="0" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>850</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="11">
+        <v>46269</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="11">
+        <v>46268</v>
+      </c>
+      <c r="H21" s="0" t="s">
         <v>1102</v>
       </c>
-      <c r="C21" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="11">
-        <v>46267</v>
-      </c>
-      <c r="F21" s="0" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G21" s="11">
-        <v>46447.125</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>1096</v>
-      </c>
       <c r="I21" s="0" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>1103</v>
+        <v>852</v>
       </c>
     </row>
     <row r="22">
@@ -46590,19 +46596,19 @@
         <v>551</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" s="11">
         <v>46267</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>30</v>
+        <v>1080</v>
       </c>
       <c r="G22" s="11">
         <v>46447.125</v>
@@ -46611,50 +46617,50 @@
         <v>1098</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>869</v>
+        <v>551</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="11">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G23" s="11">
-        <v>46446.125</v>
+        <v>46447.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>215</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1104</v>
+        <v>1079</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>61</v>
@@ -46672,10 +46678,10 @@
         <v>46446.125</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="J24" s="0" t="s">
         <v>215</v>
@@ -46683,86 +46689,86 @@
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>553</v>
+        <v>872</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1105</v>
+        <v>1079</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E25" s="11">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>1095</v>
+        <v>30</v>
       </c>
       <c r="G25" s="11">
-        <v>46441.125</v>
+        <v>46446.125</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>1107</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>868</v>
+        <v>553</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E26" s="11">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="G26" s="11">
-        <v>46440.125</v>
+        <v>46441.125</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1097</v>
+        <v>1082</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>202</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>1059</v>
+        <v>868</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" s="11">
         <v>46260</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>30</v>
+        <v>1080</v>
       </c>
       <c r="G27" s="11">
         <v>46440.125</v>
@@ -46771,47 +46777,47 @@
         <v>1098</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>867</v>
+        <v>1058</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="11">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G28" s="11">
-        <v>46439.125</v>
+        <v>46440.125</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>1090</v>
+        <v>1099</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>657</v>
+        <v>867</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>1110</v>
@@ -46832,10 +46838,10 @@
         <v>46439.125</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>202</v>
@@ -46843,10 +46849,10 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>868</v>
+        <v>657</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>34</v>
@@ -46864,10 +46870,10 @@
         <v>46439.125</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>202</v>
@@ -46875,13 +46881,13 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>653</v>
+        <v>868</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>30</v>
@@ -46896,21 +46902,21 @@
         <v>46439.125</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>211</v>
+        <v>653</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>61</v>
@@ -46928,10 +46934,10 @@
         <v>46439.125</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>215</v>
@@ -46939,10 +46945,10 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>343</v>
+        <v>211</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>61</v>
@@ -46960,42 +46966,42 @@
         <v>46439.125</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>67</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>473</v>
+        <v>343</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>61</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E34" s="11">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>1095</v>
+        <v>30</v>
       </c>
       <c r="G34" s="11">
-        <v>46435.125</v>
+        <v>46439.125</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>67</v>
@@ -47012,24 +47018,56 @@
         <v>61</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E35" s="11">
         <v>46255</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>30</v>
+        <v>1080</v>
       </c>
       <c r="G35" s="11">
         <v>46435.125</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="J35" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="11">
+        <v>46255</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="11">
+        <v>46435.125</v>
+      </c>
+      <c r="H36" s="0" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I36" s="0" t="s">
+        <v>1094</v>
+      </c>
+      <c r="J36" s="0" t="s">
         <v>67</v>
       </c>
     </row>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="1115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="1114">
   <si>
     <t>Geração:</t>
   </si>
@@ -21,7 +21,7 @@
     <t>Usuário Geração:</t>
   </si>
   <si>
-    <t>Jadson Rubens Rocha de Oliveira</t>
+    <t>GABRIELLE MENDES DE ANDRADE</t>
   </si>
   <si>
     <t>Ambiente:</t>
@@ -3355,9 +3355,6 @@
   </si>
   <si>
     <t>VOLVO/FH 440 6X2T / VOLVO/FH 440 6X2T</t>
-  </si>
-  <si>
-    <t>M. BENZ / L 1113</t>
   </si>
 </sst>
 </file>
@@ -3549,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46314.62248803241</v>
+        <v>46315.359924606484</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -45913,7 +45910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -47007,70 +47004,6 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>473</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="11">
-        <v>46255</v>
-      </c>
-      <c r="F35" s="0" t="s">
-        <v>1080</v>
-      </c>
-      <c r="G35" s="11">
-        <v>46435.125</v>
-      </c>
-      <c r="H35" s="0" t="s">
-        <v>1106</v>
-      </c>
-      <c r="I35" s="0" t="s">
-        <v>1082</v>
-      </c>
-      <c r="J35" s="0" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>473</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="11">
-        <v>46255</v>
-      </c>
-      <c r="F36" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G36" s="11">
-        <v>46435.125</v>
-      </c>
-      <c r="H36" s="0" t="s">
-        <v>1099</v>
-      </c>
-      <c r="I36" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J36" s="0" t="s">
-        <v>67</v>
-      </c>
-    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -657,153 +657,153 @@
     <t>RANDON SRBS IN</t>
   </si>
   <si>
+    <t>MILHO | NOMI &amp; SOUZA TRANSPORTE</t>
+  </si>
+  <si>
+    <t>JMH6792</t>
+  </si>
+  <si>
+    <t>LS 1935</t>
+  </si>
+  <si>
+    <t>054459144</t>
+  </si>
+  <si>
+    <t>HOO6F37</t>
+  </si>
+  <si>
+    <t>RANDON SR CA</t>
+  </si>
+  <si>
+    <t>CZC3H71</t>
+  </si>
+  <si>
+    <t>055676166</t>
+  </si>
+  <si>
+    <t>MFY9341</t>
+  </si>
+  <si>
+    <t>GUERRA AG GR</t>
+  </si>
+  <si>
+    <t>051023788</t>
+  </si>
+  <si>
+    <t>FIXO CARRETA</t>
+  </si>
+  <si>
+    <t>KJ TRANSPORTES</t>
+  </si>
+  <si>
+    <t>HQN7E45</t>
+  </si>
+  <si>
+    <t>REB</t>
+  </si>
+  <si>
+    <t>RANDON SR GR TR</t>
+  </si>
+  <si>
+    <t>NCW0H20</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>059346266</t>
+  </si>
+  <si>
+    <t>KDC0565</t>
+  </si>
+  <si>
+    <t>T113 H 4X2 360</t>
+  </si>
+  <si>
+    <t>059307377</t>
+  </si>
+  <si>
+    <t>GQI5G12</t>
+  </si>
+  <si>
+    <t>RANDON SR CS TR</t>
+  </si>
+  <si>
+    <t>JJD0J37</t>
+  </si>
+  <si>
+    <t>059209700</t>
+  </si>
+  <si>
+    <t>KTR3H97</t>
+  </si>
+  <si>
+    <t>FRUEHAUF</t>
+  </si>
+  <si>
+    <t>REB/FNV</t>
+  </si>
+  <si>
+    <t>1990</t>
+  </si>
+  <si>
+    <t>011090874</t>
+  </si>
+  <si>
+    <t>FIXO CAVALO</t>
+  </si>
+  <si>
+    <t>JSB9C88</t>
+  </si>
+  <si>
+    <t>STRALIHD 740S42TZN</t>
+  </si>
+  <si>
+    <t>NWN5299</t>
+  </si>
+  <si>
+    <t>RANDON</t>
+  </si>
+  <si>
+    <t>059216199</t>
+  </si>
+  <si>
+    <t>NWQ3796</t>
+  </si>
+  <si>
+    <t>FH 440 6X2T</t>
+  </si>
+  <si>
+    <t>MVP4965</t>
+  </si>
+  <si>
+    <t>059253222</t>
+  </si>
+  <si>
+    <t>BWT3310</t>
+  </si>
+  <si>
+    <t>T142 H 4X2</t>
+  </si>
+  <si>
+    <t>1985</t>
+  </si>
+  <si>
+    <t>NFJ5G19</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>SR AG GR</t>
+  </si>
+  <si>
+    <t>059319022</t>
+  </si>
+  <si>
     <t>Documentos ConsultaCRLV, CRLV ausentes ou vencidos</t>
   </si>
   <si>
-    <t>MILHO | NOMI &amp; SOUZA TRANSPORTE</t>
-  </si>
-  <si>
-    <t>JMH6792</t>
-  </si>
-  <si>
-    <t>LS 1935</t>
-  </si>
-  <si>
-    <t>054459144</t>
-  </si>
-  <si>
-    <t>HOO6F37</t>
-  </si>
-  <si>
-    <t>RANDON SR CA</t>
-  </si>
-  <si>
-    <t>CZC3H71</t>
-  </si>
-  <si>
-    <t>055676166</t>
-  </si>
-  <si>
-    <t>MFY9341</t>
-  </si>
-  <si>
-    <t>GUERRA AG GR</t>
-  </si>
-  <si>
-    <t>051023788</t>
-  </si>
-  <si>
-    <t>FIXO CARRETA</t>
-  </si>
-  <si>
-    <t>KJ TRANSPORTES</t>
-  </si>
-  <si>
-    <t>HQN7E45</t>
-  </si>
-  <si>
-    <t>REB</t>
-  </si>
-  <si>
-    <t>RANDON SR GR TR</t>
-  </si>
-  <si>
-    <t>NCW0H20</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>059346266</t>
-  </si>
-  <si>
-    <t>KDC0565</t>
-  </si>
-  <si>
-    <t>T113 H 4X2 360</t>
-  </si>
-  <si>
-    <t>059307377</t>
-  </si>
-  <si>
-    <t>GQI5G12</t>
-  </si>
-  <si>
-    <t>RANDON SR CS TR</t>
-  </si>
-  <si>
-    <t>JJD0J37</t>
-  </si>
-  <si>
-    <t>059209700</t>
-  </si>
-  <si>
-    <t>KTR3H97</t>
-  </si>
-  <si>
-    <t>FRUEHAUF</t>
-  </si>
-  <si>
-    <t>REB/FNV</t>
-  </si>
-  <si>
-    <t>1990</t>
-  </si>
-  <si>
-    <t>011090874</t>
-  </si>
-  <si>
-    <t>FIXO CAVALO</t>
-  </si>
-  <si>
-    <t>JSB9C88</t>
-  </si>
-  <si>
-    <t>STRALIHD 740S42TZN</t>
-  </si>
-  <si>
-    <t>NWN5299</t>
-  </si>
-  <si>
-    <t>RANDON</t>
-  </si>
-  <si>
-    <t>059216199</t>
-  </si>
-  <si>
-    <t>NWQ3796</t>
-  </si>
-  <si>
-    <t>FH 440 6X2T</t>
-  </si>
-  <si>
-    <t>MVP4965</t>
-  </si>
-  <si>
-    <t>059253222</t>
-  </si>
-  <si>
-    <t>BWT3310</t>
-  </si>
-  <si>
-    <t>T142 H 4X2</t>
-  </si>
-  <si>
-    <t>1985</t>
-  </si>
-  <si>
-    <t>NFJ5G19</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>SR AG GR</t>
-  </si>
-  <si>
-    <t>059319022</t>
-  </si>
-  <si>
     <t>ALW4D19</t>
   </si>
   <si>
@@ -2667,9 +2667,6 @@
     <t>BDW4B55</t>
   </si>
   <si>
-    <t>Inspeções Checklist de Qualidade, Checklist de Segurança SESMT vencidas</t>
-  </si>
-  <si>
     <t>EOF7B24</t>
   </si>
   <si>
@@ -3255,6 +3252,24 @@
     <t>SR / IMPERIAL GR000227T0 1</t>
   </si>
   <si>
+    <t>Jaqueline</t>
+  </si>
+  <si>
+    <t>Transportador Safra</t>
+  </si>
+  <si>
+    <t>SR/FACCHINI / SR/FACCHINI SRF LOED</t>
+  </si>
+  <si>
+    <t>MACAE BRUNE GOMES MELO</t>
+  </si>
+  <si>
+    <t>Transportador Fixo</t>
+  </si>
+  <si>
+    <t>Checklist de Qualidade Tomate</t>
+  </si>
+  <si>
     <t>Checklist de Qualidade Safra</t>
   </si>
   <si>
@@ -3267,21 +3282,12 @@
     <t>Volkswagen / VW/19.330 CTC 4X2</t>
   </si>
   <si>
-    <t>MACAE BRUNE GOMES MELO</t>
-  </si>
-  <si>
-    <t>Transportador Fixo</t>
-  </si>
-  <si>
     <t>M.BENZ/ATEGO 2426 / M.BENZ/ATEGO 2426</t>
   </si>
   <si>
     <t>WANDERSON DE CARVALHO ROCHA</t>
   </si>
   <si>
-    <t>Checklist de Qualidade Tomate</t>
-  </si>
-  <si>
     <t>IVECO / IVECO/STRALIS 600S44T</t>
   </si>
   <si>
@@ -3295,12 +3301,6 @@
   </si>
   <si>
     <t>Rafael Modesto</t>
-  </si>
-  <si>
-    <t>Transportador Safra</t>
-  </si>
-  <si>
-    <t>SR/FACCHINI / SR/FACCHINI SRF LOED</t>
   </si>
   <si>
     <t>RANDON / SR/RANDON SR FG LO 3ED</t>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46315.359924606484</v>
+        <v>46315.63989046296</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -8158,27 +8158,29 @@
       <c r="H55" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="J55" s="11"/>
+      <c r="J55" s="11">
+        <v>46400.125</v>
+      </c>
       <c r="K55" s="0" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>214</v>
+        <v>39</v>
       </c>
       <c r="M55" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N55" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O55" s="11">
-        <v>46234.125</v>
+        <v>46599.125</v>
       </c>
       <c r="Q55" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R55" s="11">
-        <v>46258.125</v>
+        <v>46497.125</v>
       </c>
       <c r="T55" s="0" t="s">
         <v>44</v>
@@ -8193,7 +8195,7 @@
         <v>44</v>
       </c>
       <c r="AC55" s="0" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AD55" s="11">
         <v>45435.49804712963</v>
@@ -8225,13 +8227,13 @@
         <v>61</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F56" s="0" t="s">
         <v>53</v>
@@ -8240,7 +8242,7 @@
         <v>53</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J56" s="11"/>
       <c r="K56" s="0" t="s">
@@ -8309,13 +8311,13 @@
         <v>49</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F57" s="0" t="s">
         <v>137</v>
@@ -8395,7 +8397,7 @@
         <v>49</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>162</v>
@@ -8410,7 +8412,7 @@
         <v>168</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J58" s="11">
         <v>46407.125</v>
@@ -8481,13 +8483,13 @@
         <v>61</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D59" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F59" s="0" t="s">
         <v>131</v>
@@ -8496,7 +8498,7 @@
         <v>131</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J59" s="11">
         <v>46395.125</v>
@@ -8564,19 +8566,19 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B60" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="C60" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="C60" s="0" t="s">
+      <c r="D60" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="D60" s="0" t="s">
+      <c r="E60" s="0" t="s">
         <v>229</v>
-      </c>
-      <c r="E60" s="0" t="s">
-        <v>230</v>
       </c>
       <c r="F60" s="0" t="s">
         <v>53</v>
@@ -8621,7 +8623,7 @@
         <v>44</v>
       </c>
       <c r="AC60" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD60" s="11">
         <v>45435.49804712963</v>
@@ -8653,7 +8655,7 @@
         <v>61</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D61" s="0" t="s">
         <v>51</v>
@@ -8662,13 +8664,13 @@
         <v>165</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>149</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J61" s="11">
         <v>46373.125</v>
@@ -8739,13 +8741,13 @@
         <v>61</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F62" s="0" t="s">
         <v>53</v>
@@ -8754,7 +8756,7 @@
         <v>54</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J62" s="11">
         <v>46356.125</v>
@@ -8828,13 +8830,13 @@
         <v>49</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>142</v>
@@ -8914,13 +8916,13 @@
         <v>61</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F64" s="0" t="s">
         <v>53</v>
@@ -8929,7 +8931,7 @@
         <v>53</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J64" s="11">
         <v>46373.125</v>
@@ -8994,28 +8996,28 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B65" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="B65" s="0" t="s">
-        <v>227</v>
-      </c>
       <c r="C65" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="D65" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="E65" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="E65" s="0" t="s">
+      <c r="F65" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="G65" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="H65" s="0" t="s">
         <v>244</v>
-      </c>
-      <c r="G65" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="H65" s="0" t="s">
-        <v>245</v>
       </c>
       <c r="J65" s="11">
         <v>46406.125</v>
@@ -9051,7 +9053,7 @@
         <v>44</v>
       </c>
       <c r="AC65" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD65" s="11">
         <v>45435.49804712963</v>
@@ -9077,19 +9079,19 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="C66" s="0" t="s">
         <v>246</v>
-      </c>
-      <c r="B66" s="0" t="s">
-        <v>227</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>247</v>
       </c>
       <c r="D66" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F66" s="0" t="s">
         <v>93</v>
@@ -9098,7 +9100,7 @@
         <v>38</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J66" s="11">
         <v>46406.125</v>
@@ -9134,7 +9136,7 @@
         <v>45</v>
       </c>
       <c r="AC66" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD66" s="11">
         <v>45435.49804712963</v>
@@ -9166,10 +9168,10 @@
         <v>61</v>
       </c>
       <c r="C67" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="D67" s="0" t="s">
         <v>249</v>
-      </c>
-      <c r="D67" s="0" t="s">
-        <v>250</v>
       </c>
       <c r="E67" s="0" t="s">
         <v>37</v>
@@ -9181,7 +9183,7 @@
         <v>65</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J67" s="11">
         <v>46356.125</v>
@@ -9255,13 +9257,13 @@
         <v>61</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F68" s="0" t="s">
         <v>65</v>
@@ -9270,7 +9272,7 @@
         <v>65</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J68" s="11">
         <v>46356.125</v>
@@ -9344,10 +9346,10 @@
         <v>61</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E69" s="0" t="s">
         <v>37</v>
@@ -9359,7 +9361,7 @@
         <v>137</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J69" s="11">
         <v>46373.125</v>
@@ -9430,22 +9432,22 @@
         <v>61</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E70" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="F70" s="0" t="s">
         <v>257</v>
       </c>
-      <c r="F70" s="0" t="s">
-        <v>258</v>
-      </c>
       <c r="G70" s="0" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J70" s="11"/>
       <c r="K70" s="0" t="s">
@@ -9514,29 +9516,29 @@
         <v>61</v>
       </c>
       <c r="C71" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="D71" s="0" t="s">
         <v>259</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="E71" s="0" t="s">
         <v>260</v>
       </c>
-      <c r="E71" s="0" t="s">
+      <c r="F71" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="H71" s="0" t="s">
         <v>261</v>
-      </c>
-      <c r="F71" s="0" t="s">
-        <v>232</v>
-      </c>
-      <c r="G71" s="0" t="s">
-        <v>232</v>
-      </c>
-      <c r="H71" s="0" t="s">
-        <v>262</v>
       </c>
       <c r="J71" s="11"/>
       <c r="K71" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="M71" s="0" t="s">
         <v>39</v>
@@ -9616,14 +9618,14 @@
         <v>149</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J72" s="11"/>
       <c r="K72" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="M72" s="0" t="s">
         <v>39</v>
@@ -9691,10 +9693,10 @@
         <v>265</v>
       </c>
       <c r="D73" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E73" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E73" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>93</v>
@@ -9775,10 +9777,10 @@
         <v>268</v>
       </c>
       <c r="D74" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E74" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E74" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F74" s="0" t="s">
         <v>93</v>
@@ -10373,7 +10375,7 @@
         <v>280</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E81" s="0" t="s">
         <v>37</v>
@@ -10457,7 +10459,7 @@
         <v>282</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E82" s="0" t="s">
         <v>37</v>
@@ -10544,7 +10546,7 @@
         <v>51</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F83" s="0" t="s">
         <v>38</v>
@@ -10625,10 +10627,10 @@
         <v>285</v>
       </c>
       <c r="D84" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E84" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E84" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F84" s="0" t="s">
         <v>93</v>
@@ -10711,10 +10713,10 @@
         <v>287</v>
       </c>
       <c r="D85" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E85" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E85" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F85" s="0" t="s">
         <v>93</v>
@@ -10797,10 +10799,10 @@
         <v>288</v>
       </c>
       <c r="D86" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E86" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E86" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F86" s="0" t="s">
         <v>74</v>
@@ -10809,7 +10811,7 @@
         <v>65</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J86" s="11">
         <v>46356.125</v>
@@ -10886,10 +10888,10 @@
         <v>289</v>
       </c>
       <c r="D87" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E87" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E87" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F87" s="0" t="s">
         <v>74</v>
@@ -10898,7 +10900,7 @@
         <v>65</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J87" s="11">
         <v>46356.125</v>
@@ -10978,7 +10980,7 @@
         <v>51</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F88" s="0" t="s">
         <v>74</v>
@@ -10987,7 +10989,7 @@
         <v>74</v>
       </c>
       <c r="H88" s="0" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J88" s="11">
         <v>46356.125</v>
@@ -12186,10 +12188,10 @@
         <v>319</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H102" s="0" t="s">
         <v>320</v>
@@ -12948,7 +12950,7 @@
         <v>340</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E111" s="0" t="s">
         <v>37</v>
@@ -13032,7 +13034,7 @@
         <v>342</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E112" s="0" t="s">
         <v>37</v>
@@ -13464,7 +13466,7 @@
         <v>77</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F117" s="0" t="s">
         <v>142</v>
@@ -14066,7 +14068,7 @@
         <v>165</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>149</v>
@@ -15009,7 +15011,7 @@
         <v>307</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>149</v>
@@ -15777,10 +15779,10 @@
         <v>322</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G144" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H144" s="0" t="s">
         <v>39</v>
@@ -15863,10 +15865,10 @@
         <v>322</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G145" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H145" s="0" t="s">
         <v>39</v>
@@ -16035,10 +16037,10 @@
         <v>322</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H147" s="0" t="s">
         <v>39</v>
@@ -16121,10 +16123,10 @@
         <v>322</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H148" s="0" t="s">
         <v>39</v>
@@ -16544,7 +16546,7 @@
         <v>162</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F153" s="0" t="s">
         <v>85</v>
@@ -16882,7 +16884,7 @@
         <v>77</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F157" s="0" t="s">
         <v>53</v>
@@ -16972,10 +16974,10 @@
         <v>345</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H158" s="0" t="s">
         <v>39</v>
@@ -18178,7 +18180,7 @@
         <v>188</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H172" s="0" t="s">
         <v>39</v>
@@ -19035,10 +19037,10 @@
         <v>457</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H182" s="0" t="s">
         <v>39</v>
@@ -19460,7 +19462,7 @@
         <v>464</v>
       </c>
       <c r="D187" s="0" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E187" s="0" t="s">
         <v>465</v>
@@ -19630,7 +19632,7 @@
         <v>468</v>
       </c>
       <c r="D189" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E189" s="0" t="s">
         <v>469</v>
@@ -19722,10 +19724,10 @@
         <v>472</v>
       </c>
       <c r="F190" s="0" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H190" s="0" t="s">
         <v>470</v>
@@ -20055,7 +20057,7 @@
         <v>484</v>
       </c>
       <c r="D194" s="0" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E194" s="0" t="s">
         <v>485</v>
@@ -20307,7 +20309,7 @@
         <v>488</v>
       </c>
       <c r="D197" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E197" s="0" t="s">
         <v>469</v>
@@ -20481,7 +20483,7 @@
         <v>492</v>
       </c>
       <c r="D199" s="0" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E199" s="0" t="s">
         <v>493</v>
@@ -20568,7 +20570,7 @@
         <v>77</v>
       </c>
       <c r="E200" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F200" s="0" t="s">
         <v>142</v>
@@ -20738,7 +20740,7 @@
         <v>77</v>
       </c>
       <c r="E202" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F202" s="0" t="s">
         <v>339</v>
@@ -21675,7 +21677,7 @@
         <v>77</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F213" s="0" t="s">
         <v>339</v>
@@ -21758,7 +21760,7 @@
         <v>533</v>
       </c>
       <c r="D214" s="0" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E214" s="0" t="s">
         <v>534</v>
@@ -22607,7 +22609,7 @@
         <v>212</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F224" s="0" t="s">
         <v>93</v>
@@ -22691,7 +22693,7 @@
         <v>212</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F225" s="0" t="s">
         <v>93</v>
@@ -23035,10 +23037,10 @@
         <v>564</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H229" s="0" t="s">
         <v>565</v>
@@ -23198,7 +23200,7 @@
         <v>271</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F231" s="0" t="s">
         <v>155</v>
@@ -24465,7 +24467,7 @@
         <v>601</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F246" s="0" t="s">
         <v>93</v>
@@ -24638,7 +24640,7 @@
         <v>51</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F248" s="0" t="s">
         <v>93</v>
@@ -24719,7 +24721,7 @@
         <v>607</v>
       </c>
       <c r="D249" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E249" s="0" t="s">
         <v>304</v>
@@ -24851,7 +24853,7 @@
         <v>44</v>
       </c>
       <c r="AC250" s="0" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AD250" s="11">
         <v>45580.69804725694</v>
@@ -24880,7 +24882,7 @@
         <v>610</v>
       </c>
       <c r="B251" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C251" s="0" t="s">
         <v>611</v>
@@ -24934,7 +24936,7 @@
         <v>44</v>
       </c>
       <c r="AC251" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD251" s="11">
         <v>45707.48365465278</v>
@@ -24960,10 +24962,10 @@
     </row>
     <row r="252">
       <c r="A252" s="0" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B252" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C252" s="0" t="s">
         <v>612</v>
@@ -25017,7 +25019,7 @@
         <v>45</v>
       </c>
       <c r="AC252" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD252" s="11">
         <v>45707.48365465278</v>
@@ -25043,10 +25045,10 @@
     </row>
     <row r="253">
       <c r="A253" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B253" s="0" t="s">
         <v>226</v>
-      </c>
-      <c r="B253" s="0" t="s">
-        <v>227</v>
       </c>
       <c r="C253" s="0" t="s">
         <v>614</v>
@@ -25055,7 +25057,7 @@
         <v>615</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F253" s="0" t="s">
         <v>155</v>
@@ -25100,7 +25102,7 @@
         <v>44</v>
       </c>
       <c r="AC253" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD253" s="11">
         <v>45707.48365465278</v>
@@ -25126,10 +25128,10 @@
     </row>
     <row r="254">
       <c r="A254" s="0" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B254" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C254" s="0" t="s">
         <v>616</v>
@@ -25183,7 +25185,7 @@
         <v>45</v>
       </c>
       <c r="AC254" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD254" s="11">
         <v>45707.48365465278</v>
@@ -25212,7 +25214,7 @@
         <v>617</v>
       </c>
       <c r="B255" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C255" s="0" t="s">
         <v>618</v>
@@ -25266,7 +25268,7 @@
         <v>45</v>
       </c>
       <c r="AC255" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD255" s="11">
         <v>45707.48365465278</v>
@@ -25539,7 +25541,7 @@
     </row>
     <row r="259">
       <c r="A259" s="0" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B259" s="0" t="s">
         <v>621</v>
@@ -25554,7 +25556,7 @@
         <v>632</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G259" s="0" t="s">
         <v>439</v>
@@ -26183,7 +26185,7 @@
         <v>45</v>
       </c>
       <c r="AC266" s="0" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AD266" s="11">
         <v>45712.43438770833</v>
@@ -26264,7 +26266,7 @@
         <v>44</v>
       </c>
       <c r="AC267" s="0" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AD267" s="11">
         <v>45741.81156357639</v>
@@ -27384,10 +27386,10 @@
         <v>585</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G281" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H281" s="0" t="s">
         <v>690</v>
@@ -27467,7 +27469,7 @@
         <v>51</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F282" s="0" t="s">
         <v>74</v>
@@ -28991,7 +28993,7 @@
         <v>719</v>
       </c>
       <c r="D300" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E300" s="0" t="s">
         <v>37</v>
@@ -29075,10 +29077,10 @@
         <v>720</v>
       </c>
       <c r="D301" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E301" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E301" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F301" s="0" t="s">
         <v>65</v>
@@ -29087,7 +29089,7 @@
         <v>65</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J301" s="11">
         <v>46407.125</v>
@@ -29247,10 +29249,10 @@
         <v>724</v>
       </c>
       <c r="D303" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E303" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E303" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F303" s="0" t="s">
         <v>60</v>
@@ -29331,10 +29333,10 @@
         <v>725</v>
       </c>
       <c r="D304" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E304" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E304" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F304" s="0" t="s">
         <v>93</v>
@@ -29343,7 +29345,7 @@
         <v>93</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J304" s="11">
         <v>46373.125</v>
@@ -29503,10 +29505,10 @@
         <v>728</v>
       </c>
       <c r="D306" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E306" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E306" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F306" s="0" t="s">
         <v>60</v>
@@ -29676,7 +29678,7 @@
         <v>732</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E308" s="0" t="s">
         <v>37</v>
@@ -29762,10 +29764,10 @@
         <v>733</v>
       </c>
       <c r="D309" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E309" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E309" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F309" s="0" t="s">
         <v>65</v>
@@ -29774,7 +29776,7 @@
         <v>65</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J309" s="11">
         <v>46407.125</v>
@@ -29934,10 +29936,10 @@
         <v>736</v>
       </c>
       <c r="D311" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E311" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E311" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F311" s="0" t="s">
         <v>60</v>
@@ -30020,10 +30022,10 @@
         <v>737</v>
       </c>
       <c r="D312" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E312" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E312" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F312" s="0" t="s">
         <v>93</v>
@@ -30032,7 +30034,7 @@
         <v>93</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J312" s="11">
         <v>46373.125</v>
@@ -30192,10 +30194,10 @@
         <v>739</v>
       </c>
       <c r="D314" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E314" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E314" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F314" s="0" t="s">
         <v>60</v>
@@ -30452,7 +30454,7 @@
         <v>51</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F317" s="0" t="s">
         <v>74</v>
@@ -30538,7 +30540,7 @@
         <v>745</v>
       </c>
       <c r="E318" s="0" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F318" s="0" t="s">
         <v>142</v>
@@ -30547,7 +30549,7 @@
         <v>339</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J318" s="11">
         <v>46373.125</v>
@@ -30621,7 +30623,7 @@
         <v>746</v>
       </c>
       <c r="D319" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E319" s="0" t="s">
         <v>37</v>
@@ -30797,10 +30799,10 @@
         <v>564</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G321" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H321" s="0" t="s">
         <v>750</v>
@@ -31393,7 +31395,7 @@
         <v>51</v>
       </c>
       <c r="E328" s="0" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F328" s="0" t="s">
         <v>74</v>
@@ -31646,7 +31648,7 @@
         <v>765</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E331" s="0" t="s">
         <v>37</v>
@@ -31732,7 +31734,7 @@
         <v>766</v>
       </c>
       <c r="D332" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E332" s="0" t="s">
         <v>37</v>
@@ -31818,7 +31820,7 @@
         <v>767</v>
       </c>
       <c r="D333" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E333" s="0" t="s">
         <v>37</v>
@@ -31904,7 +31906,7 @@
         <v>768</v>
       </c>
       <c r="D334" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E334" s="0" t="s">
         <v>37</v>
@@ -32162,7 +32164,7 @@
         <v>774</v>
       </c>
       <c r="D337" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E337" s="0" t="s">
         <v>37</v>
@@ -32246,7 +32248,7 @@
         <v>775</v>
       </c>
       <c r="D338" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E338" s="0" t="s">
         <v>37</v>
@@ -32330,10 +32332,10 @@
         <v>776</v>
       </c>
       <c r="D339" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E339" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E339" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F339" s="0" t="s">
         <v>93</v>
@@ -32416,10 +32418,10 @@
         <v>778</v>
       </c>
       <c r="D340" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E340" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E340" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F340" s="0" t="s">
         <v>93</v>
@@ -32493,10 +32495,10 @@
     </row>
     <row r="341">
       <c r="A341" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B341" s="0" t="s">
         <v>226</v>
-      </c>
-      <c r="B341" s="0" t="s">
-        <v>227</v>
       </c>
       <c r="C341" s="0" t="s">
         <v>779</v>
@@ -32547,7 +32549,7 @@
         <v>44</v>
       </c>
       <c r="AC341" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD341" s="11">
         <v>45831.61245813657</v>
@@ -33351,7 +33353,7 @@
         <v>162</v>
       </c>
       <c r="E351" s="0" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F351" s="0" t="s">
         <v>524</v>
@@ -33438,7 +33440,7 @@
         <v>141</v>
       </c>
       <c r="F352" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G352" s="0" t="s">
         <v>439</v>
@@ -33519,7 +33521,7 @@
         <v>162</v>
       </c>
       <c r="E353" s="0" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F353" s="0" t="s">
         <v>54</v>
@@ -33602,7 +33604,7 @@
         <v>798</v>
       </c>
       <c r="D354" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E354" s="0" t="s">
         <v>37</v>
@@ -33682,7 +33684,7 @@
         <v>610</v>
       </c>
       <c r="B355" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C355" s="0" t="s">
         <v>799</v>
@@ -33733,7 +33735,7 @@
         <v>44</v>
       </c>
       <c r="AC355" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD355" s="11">
         <v>45839.384970983796</v>
@@ -33771,7 +33773,7 @@
         <v>162</v>
       </c>
       <c r="E356" s="0" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F356" s="0" t="s">
         <v>54</v>
@@ -34436,7 +34438,7 @@
         <v>819</v>
       </c>
       <c r="D364" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E364" s="0" t="s">
         <v>820</v>
@@ -34510,7 +34512,7 @@
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B365" s="0" t="s">
         <v>621</v>
@@ -34683,10 +34685,10 @@
         <v>825</v>
       </c>
       <c r="D367" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="E367" s="0" t="s">
         <v>229</v>
-      </c>
-      <c r="E367" s="0" t="s">
-        <v>230</v>
       </c>
       <c r="F367" s="0" t="s">
         <v>339</v>
@@ -35018,10 +35020,10 @@
     </row>
     <row r="371">
       <c r="A371" s="0" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B371" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C371" s="0" t="s">
         <v>831</v>
@@ -35078,7 +35080,7 @@
         <v>45</v>
       </c>
       <c r="AC371" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD371" s="11">
         <v>45876.367779733795</v>
@@ -35107,7 +35109,7 @@
         <v>833</v>
       </c>
       <c r="B372" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C372" s="0" t="s">
         <v>834</v>
@@ -35158,7 +35160,7 @@
         <v>45</v>
       </c>
       <c r="AC372" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD372" s="11">
         <v>45876.37944880787</v>
@@ -35196,7 +35198,7 @@
         <v>162</v>
       </c>
       <c r="E373" s="0" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F373" s="0" t="s">
         <v>339</v>
@@ -35282,7 +35284,7 @@
         <v>77</v>
       </c>
       <c r="E374" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F374" s="0" t="s">
         <v>54</v>
@@ -35531,7 +35533,7 @@
         <v>842</v>
       </c>
       <c r="D377" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E377" s="0" t="s">
         <v>843</v>
@@ -36575,7 +36577,7 @@
         <v>44</v>
       </c>
       <c r="AC389" s="0" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AD389" s="11">
         <v>46076.3667846875</v>
@@ -36589,10 +36591,10 @@
         <v>43</v>
       </c>
       <c r="AI389" s="3">
-        <v>46266.26996527778</v>
+        <v>46315.43971439815</v>
       </c>
       <c r="AJ389" s="3">
-        <v>46446.125</v>
+        <v>46495.125</v>
       </c>
     </row>
     <row r="390">
@@ -36618,13 +36620,13 @@
         <v>200</v>
       </c>
       <c r="J390" s="11">
-        <v>46326.125</v>
+        <v>46441.125</v>
       </c>
       <c r="K390" s="0" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="L390" s="0" t="s">
-        <v>206</v>
+        <v>39</v>
       </c>
       <c r="M390" s="0" t="s">
         <v>39</v>
@@ -36639,7 +36641,7 @@
         <v>43</v>
       </c>
       <c r="R390" s="11">
-        <v>46326.125</v>
+        <v>46497.125</v>
       </c>
       <c r="T390" s="0" t="s">
         <v>44</v>
@@ -36654,7 +36656,7 @@
         <v>44</v>
       </c>
       <c r="AC390" s="0" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AD390" s="11">
         <v>46076.369408252314</v>
@@ -36984,7 +36986,7 @@
         <v>45</v>
       </c>
       <c r="AC394" s="0" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AD394" s="11">
         <v>46119.44647047454</v>
@@ -37033,12 +37035,14 @@
       <c r="H395" s="0" t="s">
         <v>718</v>
       </c>
-      <c r="J395" s="11"/>
+      <c r="J395" s="11">
+        <v>46362.125</v>
+      </c>
       <c r="K395" s="0" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="L395" s="0" t="s">
-        <v>884</v>
+        <v>39</v>
       </c>
       <c r="M395" s="0" t="s">
         <v>39</v>
@@ -37074,22 +37078,22 @@
         <v>46132.56225560185</v>
       </c>
       <c r="AE395" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AF395" s="3">
-        <v>46132.629845219904</v>
+        <v>46315.36940487268</v>
       </c>
       <c r="AG395" s="3">
-        <v>46312</v>
+        <v>46495.125</v>
       </c>
       <c r="AH395" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AI395" s="3">
-        <v>46132.630682152776</v>
+        <v>46315.37013613426</v>
       </c>
       <c r="AJ395" s="3">
-        <v>46312</v>
+        <v>46495.125</v>
       </c>
     </row>
     <row r="396">
@@ -37100,7 +37104,7 @@
         <v>34</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>198</v>
@@ -37186,22 +37190,22 @@
         <v>49</v>
       </c>
       <c r="C397" s="0" t="s">
+        <v>885</v>
+      </c>
+      <c r="D397" s="0" t="s">
         <v>886</v>
       </c>
-      <c r="D397" s="0" t="s">
+      <c r="E397" s="0" t="s">
+        <v>886</v>
+      </c>
+      <c r="F397" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="G397" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="H397" s="0" t="s">
         <v>887</v>
-      </c>
-      <c r="E397" s="0" t="s">
-        <v>887</v>
-      </c>
-      <c r="F397" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="G397" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="H397" s="0" t="s">
-        <v>888</v>
       </c>
       <c r="J397" s="11">
         <v>46413.125</v>
@@ -37272,13 +37276,13 @@
         <v>49</v>
       </c>
       <c r="C398" s="0" t="s">
+        <v>888</v>
+      </c>
+      <c r="D398" s="0" t="s">
         <v>889</v>
       </c>
-      <c r="D398" s="0" t="s">
-        <v>890</v>
-      </c>
       <c r="E398" s="0" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F398" s="0" t="s">
         <v>53</v>
@@ -37287,7 +37291,7 @@
         <v>54</v>
       </c>
       <c r="H398" s="0" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J398" s="11">
         <v>46357.125</v>
@@ -37358,7 +37362,7 @@
         <v>34</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>162</v>
@@ -37373,7 +37377,7 @@
         <v>54</v>
       </c>
       <c r="H399" s="0" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="J399" s="11">
         <v>46361.125</v>
@@ -37444,7 +37448,7 @@
         <v>34</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>51</v>
@@ -37459,7 +37463,7 @@
         <v>150</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="J400" s="11">
         <v>46365.125</v>
@@ -37530,7 +37534,7 @@
         <v>34</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>51</v>
@@ -37545,7 +37549,7 @@
         <v>134</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J401" s="11">
         <v>46365.125</v>
@@ -37616,7 +37620,7 @@
         <v>34</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>36</v>
@@ -37631,7 +37635,7 @@
         <v>134</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J402" s="11"/>
       <c r="K402" s="0" t="s">
@@ -37700,13 +37704,13 @@
         <v>49</v>
       </c>
       <c r="C403" s="0" t="s">
+        <v>897</v>
+      </c>
+      <c r="D403" s="0" t="s">
         <v>898</v>
       </c>
-      <c r="D403" s="0" t="s">
-        <v>899</v>
-      </c>
       <c r="E403" s="0" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F403" s="0" t="s">
         <v>54</v>
@@ -37715,7 +37719,7 @@
         <v>54</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J403" s="11">
         <v>46365.125</v>
@@ -37786,7 +37790,7 @@
         <v>49</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>322</v>
@@ -37801,7 +37805,7 @@
         <v>134</v>
       </c>
       <c r="H404" s="0" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J404" s="11">
         <v>46362.125</v>
@@ -37872,13 +37876,13 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E405" s="0" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F405" s="0" t="s">
         <v>65</v>
@@ -37958,7 +37962,7 @@
         <v>34</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>36</v>
@@ -38044,7 +38048,7 @@
         <v>34</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>36</v>
@@ -38130,13 +38134,13 @@
         <v>34</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E408" s="0" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F408" s="0" t="s">
         <v>439</v>
@@ -38145,7 +38149,7 @@
         <v>439</v>
       </c>
       <c r="H408" s="0" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="J408" s="11"/>
       <c r="K408" s="0" t="s">
@@ -38214,13 +38218,13 @@
         <v>34</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E409" s="0" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F409" s="0" t="s">
         <v>134</v>
@@ -38229,7 +38233,7 @@
         <v>134</v>
       </c>
       <c r="H409" s="0" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="J409" s="11"/>
       <c r="K409" s="0" t="s">
@@ -38298,7 +38302,7 @@
         <v>34</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>72</v>
@@ -38385,7 +38389,7 @@
         <v>34</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>51</v>
@@ -38400,7 +38404,7 @@
         <v>339</v>
       </c>
       <c r="H411" s="0" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="J411" s="11">
         <v>46356.125</v>
@@ -38474,13 +38478,13 @@
         <v>34</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>140</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F412" s="0" t="s">
         <v>142</v>
@@ -38489,7 +38493,7 @@
         <v>142</v>
       </c>
       <c r="H412" s="0" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="J412" s="11"/>
       <c r="K412" s="0" t="s">
@@ -38561,13 +38565,13 @@
         <v>34</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E413" s="0" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F413" s="0" t="s">
         <v>93</v>
@@ -38576,14 +38580,14 @@
         <v>93</v>
       </c>
       <c r="H413" s="0" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="J413" s="11"/>
       <c r="K413" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L413" s="0" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="M413" s="0" t="s">
         <v>39</v>
@@ -38648,7 +38652,7 @@
         <v>34</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>123</v>
@@ -38663,7 +38667,7 @@
         <v>60</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="J414" s="11"/>
       <c r="K414" s="0" t="s">
@@ -38732,7 +38736,7 @@
         <v>34</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>123</v>
@@ -38747,7 +38751,7 @@
         <v>60</v>
       </c>
       <c r="H415" s="0" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="J415" s="11"/>
       <c r="K415" s="0" t="s">
@@ -38816,13 +38820,13 @@
         <v>49</v>
       </c>
       <c r="C416" s="0" t="s">
+        <v>921</v>
+      </c>
+      <c r="D416" s="0" t="s">
         <v>922</v>
       </c>
-      <c r="D416" s="0" t="s">
-        <v>923</v>
-      </c>
       <c r="E416" s="0" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F416" s="0" t="s">
         <v>200</v>
@@ -38899,7 +38903,7 @@
         <v>34</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>63</v>
@@ -38985,7 +38989,7 @@
         <v>34</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>36</v>
@@ -39000,14 +39004,14 @@
         <v>38</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="J418" s="11"/>
       <c r="K418" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L418" s="0" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="M418" s="0" t="s">
         <v>39</v>
@@ -39072,7 +39076,7 @@
         <v>34</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>36</v>
@@ -39087,14 +39091,14 @@
         <v>38</v>
       </c>
       <c r="H419" s="0" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="J419" s="11"/>
       <c r="K419" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L419" s="0" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="M419" s="0" t="s">
         <v>39</v>
@@ -39159,13 +39163,13 @@
         <v>49</v>
       </c>
       <c r="C420" s="0" t="s">
+        <v>928</v>
+      </c>
+      <c r="D420" s="0" t="s">
         <v>929</v>
       </c>
-      <c r="D420" s="0" t="s">
-        <v>930</v>
-      </c>
       <c r="E420" s="0" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F420" s="0" t="s">
         <v>65</v>
@@ -39242,7 +39246,7 @@
         <v>49</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>322</v>
@@ -39325,13 +39329,13 @@
         <v>34</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>315</v>
       </c>
       <c r="E422" s="0" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="F422" s="0" t="s">
         <v>93</v>
@@ -39340,14 +39344,14 @@
         <v>38</v>
       </c>
       <c r="H422" s="0" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="J422" s="11"/>
       <c r="K422" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L422" s="0" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="M422" s="0" t="s">
         <v>39</v>
@@ -39412,7 +39416,7 @@
         <v>49</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>388</v>
@@ -39495,13 +39499,13 @@
         <v>49</v>
       </c>
       <c r="C424" s="0" t="s">
+        <v>935</v>
+      </c>
+      <c r="D424" s="0" t="s">
         <v>936</v>
       </c>
-      <c r="D424" s="0" t="s">
-        <v>937</v>
-      </c>
       <c r="E424" s="0" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F424" s="0" t="s">
         <v>150</v>
@@ -39578,7 +39582,7 @@
         <v>61</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>51</v>
@@ -39593,7 +39597,7 @@
         <v>168</v>
       </c>
       <c r="H425" s="0" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="J425" s="11"/>
       <c r="K425" s="0" t="s">
@@ -39662,13 +39666,13 @@
         <v>61</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E426" s="0" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F426" s="0" t="s">
         <v>332</v>
@@ -39677,7 +39681,7 @@
         <v>332</v>
       </c>
       <c r="H426" s="0" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="J426" s="11">
         <v>46373.125</v>
@@ -39748,7 +39752,7 @@
         <v>61</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>77</v>
@@ -39763,7 +39767,7 @@
         <v>524</v>
       </c>
       <c r="H427" s="0" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="J427" s="11"/>
       <c r="K427" s="0" t="s">
@@ -39835,13 +39839,13 @@
         <v>61</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E428" s="0" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F428" s="0" t="s">
         <v>169</v>
@@ -39850,7 +39854,7 @@
         <v>169</v>
       </c>
       <c r="H428" s="0" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J428" s="11">
         <v>46373.125</v>
@@ -39924,13 +39928,13 @@
         <v>61</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E429" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F429" s="0" t="s">
         <v>54</v>
@@ -39939,7 +39943,7 @@
         <v>54</v>
       </c>
       <c r="H429" s="0" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="J429" s="11">
         <v>46373.125</v>
@@ -40010,22 +40014,22 @@
         <v>61</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E430" s="0" t="s">
+        <v>949</v>
+      </c>
+      <c r="F430" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="G430" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="H430" s="0" t="s">
         <v>950</v>
-      </c>
-      <c r="F430" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="G430" s="0" t="s">
-        <v>258</v>
-      </c>
-      <c r="H430" s="0" t="s">
-        <v>951</v>
       </c>
       <c r="J430" s="11"/>
       <c r="K430" s="0" t="s">
@@ -40094,7 +40098,7 @@
         <v>61</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>51</v>
@@ -40109,7 +40113,7 @@
         <v>150</v>
       </c>
       <c r="H431" s="0" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="J431" s="11">
         <v>46373.125</v>
@@ -40180,13 +40184,13 @@
         <v>61</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>731</v>
       </c>
       <c r="E432" s="0" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F432" s="0" t="s">
         <v>209</v>
@@ -40264,10 +40268,10 @@
         <v>61</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="D433" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E433" s="0" t="s">
         <v>37</v>
@@ -40279,7 +40283,7 @@
         <v>327</v>
       </c>
       <c r="H433" s="0" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="J433" s="11"/>
       <c r="K433" s="0" t="s">
@@ -40348,13 +40352,13 @@
         <v>61</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D434" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E434" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E434" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F434" s="0" t="s">
         <v>131</v>
@@ -40363,7 +40367,7 @@
         <v>93</v>
       </c>
       <c r="H434" s="0" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="J434" s="11"/>
       <c r="K434" s="0" t="s">
@@ -40432,13 +40436,13 @@
         <v>61</v>
       </c>
       <c r="C435" s="0" t="s">
+        <v>957</v>
+      </c>
+      <c r="D435" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E435" s="0" t="s">
         <v>958</v>
-      </c>
-      <c r="D435" s="0" t="s">
-        <v>260</v>
-      </c>
-      <c r="E435" s="0" t="s">
-        <v>959</v>
       </c>
       <c r="F435" s="0" t="s">
         <v>168</v>
@@ -40447,7 +40451,7 @@
         <v>168</v>
       </c>
       <c r="H435" s="0" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="J435" s="11"/>
       <c r="K435" s="0" t="s">
@@ -40519,10 +40523,10 @@
         <v>61</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D436" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E436" s="0" t="s">
         <v>37</v>
@@ -40534,7 +40538,7 @@
         <v>65</v>
       </c>
       <c r="H436" s="0" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J436" s="11"/>
       <c r="K436" s="0" t="s">
@@ -40606,13 +40610,13 @@
         <v>61</v>
       </c>
       <c r="C437" s="0" t="s">
+        <v>960</v>
+      </c>
+      <c r="D437" s="0" t="s">
         <v>961</v>
       </c>
-      <c r="D437" s="0" t="s">
+      <c r="E437" s="0" t="s">
         <v>962</v>
-      </c>
-      <c r="E437" s="0" t="s">
-        <v>963</v>
       </c>
       <c r="F437" s="0" t="s">
         <v>294</v>
@@ -40692,13 +40696,13 @@
         <v>61</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="D438" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E438" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E438" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F438" s="0" t="s">
         <v>134</v>
@@ -40779,7 +40783,7 @@
         <v>61</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>412</v>
@@ -40794,7 +40798,7 @@
         <v>169</v>
       </c>
       <c r="H439" s="0" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="J439" s="11">
         <v>46373.125</v>
@@ -40865,13 +40869,13 @@
         <v>61</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D440" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E440" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E440" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F440" s="0" t="s">
         <v>74</v>
@@ -40880,7 +40884,7 @@
         <v>65</v>
       </c>
       <c r="H440" s="0" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J440" s="11"/>
       <c r="K440" s="0" t="s">
@@ -40949,13 +40953,13 @@
         <v>61</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="D441" s="0" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E441" s="0" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F441" s="0" t="s">
         <v>53</v>
@@ -41033,7 +41037,7 @@
         <v>61</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>412</v>
@@ -41048,7 +41052,7 @@
         <v>327</v>
       </c>
       <c r="H442" s="0" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="J442" s="11">
         <v>46373.125</v>
@@ -41119,13 +41123,13 @@
         <v>61</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D443" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E443" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E443" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F443" s="0" t="s">
         <v>38</v>
@@ -41134,7 +41138,7 @@
         <v>74</v>
       </c>
       <c r="H443" s="0" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="J443" s="11"/>
       <c r="K443" s="0" t="s">
@@ -41203,13 +41207,13 @@
         <v>61</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D444" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E444" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E444" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F444" s="0" t="s">
         <v>134</v>
@@ -41290,7 +41294,7 @@
         <v>61</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>412</v>
@@ -41305,7 +41309,7 @@
         <v>169</v>
       </c>
       <c r="H445" s="0" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="J445" s="11">
         <v>46373.125</v>
@@ -41376,13 +41380,13 @@
         <v>61</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D446" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E446" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E446" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F446" s="0" t="s">
         <v>74</v>
@@ -41391,7 +41395,7 @@
         <v>65</v>
       </c>
       <c r="H446" s="0" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J446" s="11"/>
       <c r="K446" s="0" t="s">
@@ -41460,7 +41464,7 @@
         <v>61</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>162</v>
@@ -41475,7 +41479,7 @@
         <v>176</v>
       </c>
       <c r="H447" s="0" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="J447" s="11"/>
       <c r="K447" s="0" t="s">
@@ -41544,13 +41548,13 @@
         <v>61</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E448" s="0" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F448" s="0" t="s">
         <v>502</v>
@@ -41559,7 +41563,7 @@
         <v>502</v>
       </c>
       <c r="H448" s="0" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="J448" s="11">
         <v>46373.125</v>
@@ -41630,7 +41634,7 @@
         <v>61</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>162</v>
@@ -41645,7 +41649,7 @@
         <v>518</v>
       </c>
       <c r="H449" s="0" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="J449" s="11"/>
       <c r="K449" s="0" t="s">
@@ -41714,13 +41718,13 @@
         <v>61</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E450" s="0" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F450" s="0" t="s">
         <v>332</v>
@@ -41729,7 +41733,7 @@
         <v>332</v>
       </c>
       <c r="H450" s="0" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="J450" s="11"/>
       <c r="K450" s="0" t="s">
@@ -41801,7 +41805,7 @@
         <v>61</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>162</v>
@@ -41816,7 +41820,7 @@
         <v>332</v>
       </c>
       <c r="H451" s="0" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="J451" s="11"/>
       <c r="K451" s="0" t="s">
@@ -41885,13 +41889,13 @@
         <v>873</v>
       </c>
       <c r="C452" s="0" t="s">
+        <v>985</v>
+      </c>
+      <c r="D452" s="0" t="s">
         <v>986</v>
       </c>
-      <c r="D452" s="0" t="s">
-        <v>987</v>
-      </c>
       <c r="E452" s="0" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F452" s="0" t="s">
         <v>300</v>
@@ -41962,7 +41966,7 @@
         <v>643</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>63</v>
@@ -42048,7 +42052,7 @@
         <v>643</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>770</v>
@@ -42134,13 +42138,13 @@
         <v>34</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E455" s="0" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F455" s="0" t="s">
         <v>85</v>
@@ -42217,7 +42221,7 @@
         <v>34</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>36</v>
@@ -42300,7 +42304,7 @@
         <v>34</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>123</v>
@@ -42315,7 +42319,7 @@
         <v>74</v>
       </c>
       <c r="H457" s="0" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="J457" s="11">
         <v>46387.125</v>
@@ -42386,7 +42390,7 @@
         <v>34</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="D458" s="0" t="s">
         <v>123</v>
@@ -42401,7 +42405,7 @@
         <v>74</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="J458" s="11">
         <v>46326.125</v>
@@ -42472,7 +42476,7 @@
         <v>34</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>51</v>
@@ -42487,7 +42491,7 @@
         <v>326</v>
       </c>
       <c r="H459" s="0" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="J459" s="11">
         <v>46326.125</v>
@@ -42558,13 +42562,13 @@
         <v>34</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E460" s="0" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F460" s="0" t="s">
         <v>131</v>
@@ -42642,13 +42646,13 @@
         <v>34</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>179</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F461" s="0" t="s">
         <v>149</v>
@@ -42657,7 +42661,7 @@
         <v>149</v>
       </c>
       <c r="H461" s="0" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="J461" s="11"/>
       <c r="K461" s="0" t="s">
@@ -42726,13 +42730,13 @@
         <v>61</v>
       </c>
       <c r="C462" s="0" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D462" s="0" t="s">
         <v>1002</v>
       </c>
-      <c r="D462" s="0" t="s">
+      <c r="E462" s="0" t="s">
         <v>1003</v>
-      </c>
-      <c r="E462" s="0" t="s">
-        <v>1004</v>
       </c>
       <c r="F462" s="0" t="s">
         <v>418</v>
@@ -42741,7 +42745,7 @@
         <v>418</v>
       </c>
       <c r="H462" s="0" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="J462" s="11"/>
       <c r="K462" s="0" t="s">
@@ -42807,7 +42811,7 @@
         <v>61</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>77</v>
@@ -42822,7 +42826,7 @@
         <v>332</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="J463" s="11">
         <v>46406.125</v>
@@ -42893,22 +42897,22 @@
         <v>61</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="F464" s="0" t="s">
         <v>79</v>
       </c>
       <c r="G464" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H464" s="0" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="J464" s="11">
         <v>46407.125</v>
@@ -42979,10 +42983,10 @@
         <v>61</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D465" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E465" s="0" t="s">
         <v>37</v>
@@ -42994,7 +42998,7 @@
         <v>134</v>
       </c>
       <c r="H465" s="0" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="J465" s="11">
         <v>46407.125</v>
@@ -43065,10 +43069,10 @@
         <v>61</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D466" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E466" s="0" t="s">
         <v>37</v>
@@ -43080,7 +43084,7 @@
         <v>134</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="J466" s="11">
         <v>46407.125</v>
@@ -43151,7 +43155,7 @@
         <v>61</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>770</v>
@@ -43166,7 +43170,7 @@
         <v>54</v>
       </c>
       <c r="H467" s="0" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="J467" s="11">
         <v>46406.125</v>
@@ -43237,13 +43241,13 @@
         <v>61</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D468" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E468" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E468" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F468" s="0" t="s">
         <v>74</v>
@@ -43252,7 +43256,7 @@
         <v>74</v>
       </c>
       <c r="H468" s="0" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="J468" s="11">
         <v>46373.125</v>
@@ -43323,13 +43327,13 @@
         <v>49</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E469" s="0" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F469" s="0" t="s">
         <v>38</v>
@@ -43403,19 +43407,19 @@
     </row>
     <row r="470">
       <c r="A470" s="0" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B470" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C470" s="0" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D470" s="0" t="s">
         <v>1017</v>
       </c>
-      <c r="D470" s="0" t="s">
+      <c r="E470" s="0" t="s">
         <v>1018</v>
-      </c>
-      <c r="E470" s="0" t="s">
-        <v>1019</v>
       </c>
       <c r="F470" s="0" t="s">
         <v>142</v>
@@ -43424,7 +43428,7 @@
         <v>142</v>
       </c>
       <c r="H470" s="0" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J470" s="11">
         <v>46398.125</v>
@@ -43460,7 +43464,7 @@
         <v>45</v>
       </c>
       <c r="AC470" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD470" s="11">
         <v>46218.81741611111</v>
@@ -43492,13 +43496,13 @@
         <v>807</v>
       </c>
       <c r="C471" s="0" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D471" s="0" t="s">
         <v>1021</v>
       </c>
-      <c r="D471" s="0" t="s">
+      <c r="E471" s="0" t="s">
         <v>1022</v>
-      </c>
-      <c r="E471" s="0" t="s">
-        <v>1023</v>
       </c>
       <c r="F471" s="0" t="s">
         <v>200</v>
@@ -43537,7 +43541,7 @@
         <v>45</v>
       </c>
       <c r="AC471" s="0" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="AD471" s="11">
         <v>46219.55652277778</v>
@@ -43569,7 +43573,7 @@
         <v>49</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>382</v>
@@ -43584,7 +43588,7 @@
         <v>339</v>
       </c>
       <c r="H472" s="0" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="J472" s="11">
         <v>46402.125</v>
@@ -43655,7 +43659,7 @@
         <v>61</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>51</v>
@@ -43670,7 +43674,7 @@
         <v>79</v>
       </c>
       <c r="H473" s="0" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="J473" s="11">
         <v>46346.125</v>
@@ -43741,13 +43745,13 @@
         <v>61</v>
       </c>
       <c r="C474" s="0" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D474" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="E474" s="0" t="s">
         <v>1029</v>
-      </c>
-      <c r="D474" s="0" t="s">
-        <v>250</v>
-      </c>
-      <c r="E474" s="0" t="s">
-        <v>1030</v>
       </c>
       <c r="F474" s="0" t="s">
         <v>339</v>
@@ -43756,7 +43760,7 @@
         <v>53</v>
       </c>
       <c r="H474" s="0" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="J474" s="11">
         <v>46346.125</v>
@@ -43827,10 +43831,10 @@
         <v>61</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="D475" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E475" s="0" t="s">
         <v>37</v>
@@ -43842,7 +43846,7 @@
         <v>208</v>
       </c>
       <c r="H475" s="0" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="J475" s="11"/>
       <c r="K475" s="0" t="s">
@@ -43911,7 +43915,7 @@
         <v>61</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>51</v>
@@ -43926,7 +43930,7 @@
         <v>150</v>
       </c>
       <c r="H476" s="0" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="J476" s="11">
         <v>46407.125</v>
@@ -43997,22 +44001,22 @@
         <v>61</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D477" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E477" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E477" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F477" s="0" t="s">
         <v>79</v>
       </c>
       <c r="G477" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H477" s="0" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="J477" s="11">
         <v>46407.125</v>
@@ -44083,22 +44087,22 @@
         <v>61</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D478" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="E478" s="0" t="s">
         <v>260</v>
-      </c>
-      <c r="E478" s="0" t="s">
-        <v>261</v>
       </c>
       <c r="F478" s="0" t="s">
         <v>79</v>
       </c>
       <c r="G478" s="0" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H478" s="0" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="J478" s="11">
         <v>46407.125</v>
@@ -44169,16 +44173,16 @@
         <v>621</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D479" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E479" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F479" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G479" s="0" t="s">
         <v>439</v>
@@ -44249,13 +44253,13 @@
         <v>621</v>
       </c>
       <c r="C480" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D480" s="0" t="s">
         <v>1038</v>
       </c>
-      <c r="D480" s="0" t="s">
-        <v>1039</v>
-      </c>
       <c r="E480" s="0" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F480" s="0" t="s">
         <v>439</v>
@@ -44329,13 +44333,13 @@
         <v>49</v>
       </c>
       <c r="C481" s="0" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D481" s="0" t="s">
         <v>1040</v>
       </c>
-      <c r="D481" s="0" t="s">
-        <v>1041</v>
-      </c>
       <c r="E481" s="0" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F481" s="0" t="s">
         <v>98</v>
@@ -44415,13 +44419,13 @@
         <v>34</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F482" s="0" t="s">
         <v>38</v>
@@ -44430,7 +44434,7 @@
         <v>38</v>
       </c>
       <c r="H482" s="0" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="J482" s="11"/>
       <c r="K482" s="0" t="s">
@@ -44499,13 +44503,13 @@
         <v>49</v>
       </c>
       <c r="C483" s="0" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D483" s="0" t="s">
         <v>1045</v>
       </c>
-      <c r="D483" s="0" t="s">
-        <v>1046</v>
-      </c>
       <c r="E483" s="0" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F483" s="0" t="s">
         <v>137</v>
@@ -44582,7 +44586,7 @@
         <v>49</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>345</v>
@@ -44665,7 +44669,7 @@
         <v>49</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>345</v>
@@ -44748,10 +44752,10 @@
         <v>34</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D486" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E486" s="0" t="s">
         <v>37</v>
@@ -44763,7 +44767,7 @@
         <v>38</v>
       </c>
       <c r="H486" s="0" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="J486" s="11">
         <v>46362.125</v>
@@ -44834,10 +44838,10 @@
         <v>34</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E487" s="0" t="s">
         <v>37</v>
@@ -44849,7 +44853,7 @@
         <v>38</v>
       </c>
       <c r="H487" s="0" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="J487" s="11">
         <v>46362.125</v>
@@ -44920,7 +44924,7 @@
         <v>49</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>366</v>
@@ -45003,19 +45007,19 @@
         <v>49</v>
       </c>
       <c r="C489" s="0" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D489" s="0" t="s">
         <v>1052</v>
       </c>
-      <c r="D489" s="0" t="s">
-        <v>1053</v>
-      </c>
       <c r="E489" s="0" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F489" s="0" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G489" s="0" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J489" s="11">
         <v>46423.125</v>
@@ -45086,13 +45090,13 @@
         <v>49</v>
       </c>
       <c r="C490" s="0" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D490" s="0" t="s">
         <v>1054</v>
       </c>
-      <c r="D490" s="0" t="s">
-        <v>1055</v>
-      </c>
       <c r="E490" s="0" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F490" s="0" t="s">
         <v>131</v>
@@ -45169,13 +45173,13 @@
         <v>49</v>
       </c>
       <c r="C491" s="0" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D491" s="0" t="s">
         <v>1056</v>
       </c>
-      <c r="D491" s="0" t="s">
-        <v>1057</v>
-      </c>
       <c r="E491" s="0" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F491" s="0" t="s">
         <v>294</v>
@@ -45252,13 +45256,13 @@
         <v>61</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E492" s="0" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F492" s="0" t="s">
         <v>105</v>
@@ -45336,13 +45340,13 @@
         <v>643</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E493" s="0" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F493" s="0" t="s">
         <v>293</v>
@@ -45422,19 +45426,19 @@
         <v>34</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E494" s="0" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F494" s="0" t="s">
         <v>863</v>
       </c>
       <c r="G494" s="0" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H494" s="0" t="s">
         <v>201</v>
@@ -45508,19 +45512,19 @@
         <v>34</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="D495" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E495" s="0" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F495" s="0" t="s">
         <v>863</v>
       </c>
       <c r="G495" s="0" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H495" s="0" t="s">
         <v>201</v>
@@ -45591,10 +45595,10 @@
         <v>610</v>
       </c>
       <c r="B496" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="D496" s="0" t="s">
         <v>526</v>
@@ -45642,7 +45646,7 @@
         <v>44</v>
       </c>
       <c r="AC496" s="0" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD496" s="11">
         <v>46296.42035898148</v>
@@ -45674,13 +45678,13 @@
         <v>807</v>
       </c>
       <c r="C497" s="0" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D497" s="0" t="s">
         <v>1067</v>
       </c>
-      <c r="D497" s="0" t="s">
-        <v>1068</v>
-      </c>
       <c r="E497" s="0" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F497" s="0" t="s">
         <v>294</v>
@@ -45748,13 +45752,13 @@
         <v>850</v>
       </c>
       <c r="C498" s="0" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D498" s="0" t="s">
+        <v>936</v>
+      </c>
+      <c r="E498" s="0" t="s">
         <v>1069</v>
-      </c>
-      <c r="D498" s="0" t="s">
-        <v>937</v>
-      </c>
-      <c r="E498" s="0" t="s">
-        <v>1070</v>
       </c>
       <c r="F498" s="0" t="s">
         <v>168</v>
@@ -45767,7 +45771,7 @@
         <v>40</v>
       </c>
       <c r="L498" s="0" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="M498" s="0" t="s">
         <v>39</v>
@@ -45815,13 +45819,13 @@
         <v>850</v>
       </c>
       <c r="C499" s="0" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D499" s="0" t="s">
         <v>1072</v>
       </c>
-      <c r="D499" s="0" t="s">
-        <v>1073</v>
-      </c>
       <c r="E499" s="0" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F499" s="0" t="s">
         <v>169</v>
@@ -45834,7 +45838,7 @@
         <v>40</v>
       </c>
       <c r="L499" s="0" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="M499" s="0" t="s">
         <v>39</v>
@@ -45910,7 +45914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -45921,28 +45925,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>1077</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>1078</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -45950,42 +45954,42 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>61</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" s="11">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="11">
+        <v>46495.125</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I2" s="0" t="s">
         <v>1080</v>
       </c>
-      <c r="G2" s="11">
-        <v>46494.125</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>1081</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>1082</v>
-      </c>
       <c r="J2" s="0" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>844</v>
+        <v>883</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>643</v>
@@ -45994,19 +45998,19 @@
         <v>30</v>
       </c>
       <c r="E3" s="11">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G3" s="11">
-        <v>46491.125</v>
+        <v>46495.125</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>647</v>
@@ -46014,74 +46018,74 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>1067</v>
+        <v>883</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>807</v>
+        <v>643</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="11">
-        <v>46303</v>
+        <v>46315</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>30</v>
+        <v>1084</v>
       </c>
       <c r="G4" s="11">
-        <v>46483.125</v>
+        <v>46495.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>807</v>
+        <v>647</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>1067</v>
+        <v>872</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>807</v>
+        <v>61</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="11">
-        <v>46303</v>
+        <v>46314</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="G5" s="11">
-        <v>46483.125</v>
+        <v>46494.125</v>
       </c>
       <c r="H5" s="0" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I5" s="0" t="s">
         <v>1087</v>
       </c>
-      <c r="I5" s="0" t="s">
-        <v>1085</v>
-      </c>
       <c r="J5" s="0" t="s">
-        <v>807</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>879</v>
+        <v>844</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>643</v>
@@ -46090,19 +46094,19 @@
         <v>30</v>
       </c>
       <c r="E6" s="11">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="11">
-        <v>46480.125</v>
+        <v>46491.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>647</v>
@@ -46113,31 +46117,31 @@
         <v>1066</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>227</v>
+        <v>807</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="11">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="F7" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G7" s="11">
-        <v>46476.125</v>
+        <v>46483.125</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>227</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8">
@@ -46145,63 +46149,63 @@
         <v>1066</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>227</v>
+        <v>807</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="11">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="G8" s="11">
-        <v>46476.125</v>
+        <v>46483.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>227</v>
+        <v>807</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>1062</v>
+        <v>879</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>34</v>
+        <v>643</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="11">
-        <v>46294</v>
+        <v>46300</v>
       </c>
       <c r="F9" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="11">
-        <v>46474.125</v>
+        <v>46480.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1093</v>
+        <v>1082</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>202</v>
+        <v>647</v>
       </c>
     </row>
     <row r="10">
@@ -46212,103 +46216,103 @@
         <v>1092</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>34</v>
+        <v>226</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="11">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="11">
-        <v>46474.125</v>
+        <v>46476.125</v>
       </c>
       <c r="H10" s="0" t="s">
         <v>1093</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>878</v>
+        <v>1065</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>643</v>
+        <v>226</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" s="11">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>30</v>
+        <v>1084</v>
       </c>
       <c r="G11" s="11">
-        <v>46474.125</v>
+        <v>46476.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1084</v>
+        <v>1093</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>647</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>878</v>
+        <v>1061</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>643</v>
+        <v>34</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="11">
         <v>46294</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>1088</v>
+        <v>30</v>
       </c>
       <c r="G12" s="11">
         <v>46474.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1084</v>
+        <v>1095</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>647</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>842</v>
+        <v>1064</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>643</v>
+        <v>34</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>30</v>
@@ -46323,42 +46327,42 @@
         <v>46474.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1084</v>
+        <v>1095</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>647</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>842</v>
+        <v>878</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1096</v>
+        <v>1081</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>643</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="11">
         <v>46294</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>1088</v>
+        <v>30</v>
       </c>
       <c r="G14" s="11">
         <v>46474.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>647</v>
@@ -46366,95 +46370,95 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>974</v>
+        <v>878</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1097</v>
+        <v>1081</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>61</v>
+        <v>643</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E15" s="11">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="G15" s="11">
-        <v>46469.125</v>
+        <v>46474.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1098</v>
+        <v>1082</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>67</v>
+        <v>647</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>974</v>
+        <v>842</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>61</v>
+        <v>643</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E16" s="11">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G16" s="11">
-        <v>46469.125</v>
+        <v>46474.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1099</v>
+        <v>1082</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>67</v>
+        <v>647</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>1060</v>
+        <v>842</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>643</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" s="11">
-        <v>46275</v>
+        <v>46294</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>30</v>
+        <v>1084</v>
       </c>
       <c r="G17" s="11">
-        <v>46455.125</v>
+        <v>46474.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>647</v>
@@ -46462,330 +46466,330 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>1060</v>
+        <v>973</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>643</v>
+        <v>61</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>29</v>
       </c>
       <c r="E18" s="11">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="G18" s="11">
-        <v>46455.125</v>
+        <v>46469.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1084</v>
+        <v>1098</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>647</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>851</v>
+        <v>973</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>850</v>
+        <v>61</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="11">
-        <v>46269</v>
+        <v>46289</v>
       </c>
       <c r="F19" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G19" s="11">
-        <v>46449.125</v>
+        <v>46469.125</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>852</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>851</v>
+        <v>1059</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>850</v>
+        <v>643</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E20" s="11">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>1088</v>
+        <v>30</v>
       </c>
       <c r="G20" s="11">
-        <v>46449.125</v>
+        <v>46455.125</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>1102</v>
+        <v>1082</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>852</v>
+        <v>647</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>851</v>
+        <v>1059</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>850</v>
+        <v>643</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" s="11">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>30</v>
+        <v>1084</v>
       </c>
       <c r="G21" s="11">
-        <v>46268</v>
+        <v>46455.125</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>1102</v>
+        <v>1082</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>852</v>
+        <v>647</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>551</v>
+        <v>851</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>34</v>
+        <v>850</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="11">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>1080</v>
+        <v>30</v>
       </c>
       <c r="G22" s="11">
-        <v>46447.125</v>
+        <v>46449.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>1104</v>
+        <v>852</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>551</v>
+        <v>851</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>34</v>
+        <v>850</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" s="11">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>30</v>
+        <v>1084</v>
       </c>
       <c r="G23" s="11">
-        <v>46447.125</v>
+        <v>46449.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>1104</v>
+        <v>852</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>869</v>
+        <v>851</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1079</v>
+        <v>1101</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>61</v>
+        <v>850</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E24" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G24" s="11">
-        <v>46446.125</v>
+        <v>46268</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>215</v>
+        <v>852</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>872</v>
+        <v>551</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1079</v>
+        <v>1103</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E25" s="11">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>30</v>
+        <v>1085</v>
       </c>
       <c r="G25" s="11">
-        <v>46446.125</v>
+        <v>46447.125</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>215</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" s="11">
-        <v>46261</v>
+        <v>46267</v>
       </c>
       <c r="F26" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="11">
+        <v>46447.125</v>
+      </c>
+      <c r="H26" s="0" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I26" s="0" t="s">
         <v>1080</v>
       </c>
-      <c r="G26" s="11">
-        <v>46441.125</v>
-      </c>
-      <c r="H26" s="0" t="s">
-        <v>1106</v>
-      </c>
-      <c r="I26" s="0" t="s">
-        <v>1082</v>
-      </c>
       <c r="J26" s="0" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1108</v>
+        <v>1078</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27" s="11">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="F27" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="11">
+        <v>46314</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I27" s="0" t="s">
         <v>1080</v>
       </c>
-      <c r="G27" s="11">
-        <v>46440.125</v>
-      </c>
-      <c r="H27" s="0" t="s">
-        <v>1098</v>
-      </c>
-      <c r="I27" s="0" t="s">
-        <v>1082</v>
-      </c>
       <c r="J27" s="0" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>1058</v>
+        <v>872</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1109</v>
+        <v>1078</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>61</v>
@@ -46794,83 +46798,83 @@
         <v>30</v>
       </c>
       <c r="E28" s="11">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G28" s="11">
-        <v>46440.125</v>
+        <v>46446.125</v>
       </c>
       <c r="H28" s="0" t="s">
         <v>1099</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1094</v>
+        <v>1080</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>67</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>867</v>
+        <v>553</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E29" s="11">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>30</v>
+        <v>1085</v>
       </c>
       <c r="G29" s="11">
-        <v>46439.125</v>
+        <v>46441.125</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>202</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>657</v>
+        <v>868</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>34</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E30" s="11">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>30</v>
+        <v>1085</v>
       </c>
       <c r="G30" s="11">
-        <v>46439.125</v>
+        <v>46440.125</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1093</v>
+        <v>1098</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>202</v>
@@ -46878,45 +46882,45 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>868</v>
+        <v>1057</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>30</v>
       </c>
       <c r="E31" s="11">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F31" s="0" t="s">
         <v>30</v>
       </c>
       <c r="G31" s="11">
-        <v>46439.125</v>
+        <v>46440.125</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>1094</v>
+        <v>1080</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>202</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>653</v>
+        <v>867</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>30</v>
@@ -46931,24 +46935,24 @@
         <v>46439.125</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>1094</v>
+        <v>1080</v>
       </c>
       <c r="J32" s="0" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>211</v>
+        <v>657</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>30</v>
@@ -46963,24 +46967,24 @@
         <v>46439.125</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>1094</v>
+        <v>1080</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>343</v>
+        <v>868</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>30</v>
@@ -46995,12 +46999,108 @@
         <v>46439.125</v>
       </c>
       <c r="H34" s="0" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I34" s="0" t="s">
+        <v>1080</v>
+      </c>
+      <c r="J34" s="0" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>653</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="11">
+        <v>46259</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" s="11">
+        <v>46439.125</v>
+      </c>
+      <c r="H35" s="0" t="s">
         <v>1099</v>
       </c>
-      <c r="I34" s="0" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J34" s="0" t="s">
+      <c r="I35" s="0" t="s">
+        <v>1080</v>
+      </c>
+      <c r="J35" s="0" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="11">
+        <v>46259</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="11">
+        <v>46439.125</v>
+      </c>
+      <c r="H36" s="0" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I36" s="0" t="s">
+        <v>1080</v>
+      </c>
+      <c r="J36" s="0" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="11">
+        <v>46259</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" s="11">
+        <v>46439.125</v>
+      </c>
+      <c r="H37" s="0" t="s">
+        <v>1099</v>
+      </c>
+      <c r="I37" s="0" t="s">
+        <v>1080</v>
+      </c>
+      <c r="J37" s="0" t="s">
         <v>67</v>
       </c>
     </row>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="1116">
   <si>
     <t>Geração:</t>
   </si>
@@ -1975,6 +1975,12 @@
   </si>
   <si>
     <t>FZS1103</t>
+  </si>
+  <si>
+    <t>Documento ConsultaCRLV aguardando validação</t>
+  </si>
+  <si>
+    <t>AV</t>
   </si>
   <si>
     <t>NLO5E70</t>
@@ -3546,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46315.63989046296</v>
+        <v>46316.40538217592</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -13167,7 +13173,7 @@
         <v>45</v>
       </c>
       <c r="AC113" s="0" t="s">
-        <v>67</v>
+        <v>214</v>
       </c>
       <c r="AD113" s="11">
         <v>45436.4303603125</v>
@@ -26236,7 +26242,7 @@
         <v>40</v>
       </c>
       <c r="L267" s="0" t="s">
-        <v>267</v>
+        <v>654</v>
       </c>
       <c r="M267" s="0" t="s">
         <v>39</v>
@@ -26248,10 +26254,10 @@
         <v>46404.125</v>
       </c>
       <c r="Q267" s="0" t="s">
-        <v>42</v>
+        <v>655</v>
       </c>
       <c r="R267" s="11">
-        <v>46265.125</v>
+        <v>46387.125</v>
       </c>
       <c r="T267" s="0" t="s">
         <v>44</v>
@@ -26298,13 +26304,13 @@
         <v>621</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E268" s="0" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="F268" s="0" t="s">
         <v>38</v>
@@ -26376,7 +26382,7 @@
         <v>34</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D269" s="0" t="s">
         <v>51</v>
@@ -26454,13 +26460,13 @@
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B270" s="0" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D270" s="0" t="s">
         <v>427</v>
@@ -26472,14 +26478,14 @@
         <v>497</v>
       </c>
       <c r="G270" s="0" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="J270" s="11"/>
       <c r="K270" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L270" s="0" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M270" s="0" t="s">
         <v>39</v>
@@ -26500,7 +26506,7 @@
         <v>45</v>
       </c>
       <c r="AC270" s="0" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AD270" s="11">
         <v>45817.61092795139</v>
@@ -26526,32 +26532,32 @@
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B271" s="0" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D271" s="0" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="F271" s="0" t="s">
         <v>169</v>
       </c>
       <c r="G271" s="0" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="J271" s="11"/>
       <c r="K271" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L271" s="0" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M271" s="0" t="s">
         <v>39</v>
@@ -26578,7 +26584,7 @@
         <v>45</v>
       </c>
       <c r="AC271" s="0" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AD271" s="11">
         <v>45817.61552398148</v>
@@ -26610,7 +26616,7 @@
         <v>49</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D272" s="0" t="s">
         <v>313</v>
@@ -26625,7 +26631,7 @@
         <v>131</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="J272" s="11">
         <v>46411.125</v>
@@ -26696,7 +26702,7 @@
         <v>49</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D273" s="0" t="s">
         <v>311</v>
@@ -26708,10 +26714,10 @@
         <v>131</v>
       </c>
       <c r="G273" s="0" t="s">
+        <v>674</v>
+      </c>
+      <c r="H273" s="0" t="s">
         <v>672</v>
-      </c>
-      <c r="H273" s="0" t="s">
-        <v>670</v>
       </c>
       <c r="J273" s="11">
         <v>46411.125</v>
@@ -26782,13 +26788,13 @@
         <v>61</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D274" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F274" s="0" t="s">
         <v>65</v>
@@ -26797,7 +26803,7 @@
         <v>65</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="J274" s="11">
         <v>46357.125</v>
@@ -26868,7 +26874,7 @@
         <v>34</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D275" s="0" t="s">
         <v>162</v>
@@ -26883,14 +26889,14 @@
         <v>339</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J275" s="11"/>
       <c r="K275" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L275" s="0" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="M275" s="0" t="s">
         <v>39</v>
@@ -26949,13 +26955,13 @@
         <v>49</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F276" s="0" t="s">
         <v>168</v>
@@ -26964,7 +26970,7 @@
         <v>168</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="J276" s="11">
         <v>46417.125</v>
@@ -27035,13 +27041,13 @@
         <v>34</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D277" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="F277" s="0" t="s">
         <v>200</v>
@@ -27057,7 +27063,7 @@
         <v>40</v>
       </c>
       <c r="L277" s="0" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="M277" s="0" t="s">
         <v>39</v>
@@ -27119,13 +27125,13 @@
         <v>49</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E278" s="0" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F278" s="0" t="s">
         <v>74</v>
@@ -27205,7 +27211,7 @@
         <v>49</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D279" s="0" t="s">
         <v>368</v>
@@ -27291,7 +27297,7 @@
         <v>49</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D280" s="0" t="s">
         <v>370</v>
@@ -27377,7 +27383,7 @@
         <v>49</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D281" s="0" t="s">
         <v>585</v>
@@ -27392,7 +27398,7 @@
         <v>231</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="J281" s="11">
         <v>46374.125</v>
@@ -27463,7 +27469,7 @@
         <v>34</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D282" s="0" t="s">
         <v>51</v>
@@ -27478,7 +27484,7 @@
         <v>74</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="J282" s="11"/>
       <c r="K282" s="0" t="s">
@@ -27547,13 +27553,13 @@
         <v>49</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="F283" s="0" t="s">
         <v>169</v>
@@ -27630,7 +27636,7 @@
         <v>49</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D284" s="0" t="s">
         <v>304</v>
@@ -27716,7 +27722,7 @@
         <v>49</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D285" s="0" t="s">
         <v>304</v>
@@ -27802,7 +27808,7 @@
         <v>34</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D286" s="0" t="s">
         <v>123</v>
@@ -27886,7 +27892,7 @@
         <v>34</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D287" s="0" t="s">
         <v>123</v>
@@ -27970,7 +27976,7 @@
         <v>34</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D288" s="0" t="s">
         <v>72</v>
@@ -28054,7 +28060,7 @@
         <v>34</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D289" s="0" t="s">
         <v>72</v>
@@ -28138,7 +28144,7 @@
         <v>34</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D290" s="0" t="s">
         <v>51</v>
@@ -28222,13 +28228,13 @@
         <v>61</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D291" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="F291" s="0" t="s">
         <v>168</v>
@@ -28237,7 +28243,7 @@
         <v>168</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="J291" s="11">
         <v>46373.125</v>
@@ -28308,7 +28314,7 @@
         <v>61</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D292" s="0" t="s">
         <v>36</v>
@@ -28323,7 +28329,7 @@
         <v>38</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="J292" s="11">
         <v>46373.125</v>
@@ -28394,7 +28400,7 @@
         <v>61</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D293" s="0" t="s">
         <v>36</v>
@@ -28409,7 +28415,7 @@
         <v>38</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="J293" s="11">
         <v>46373.125</v>
@@ -28480,13 +28486,13 @@
         <v>34</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D294" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F294" s="0" t="s">
         <v>168</v>
@@ -28495,7 +28501,7 @@
         <v>169</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="J294" s="11"/>
       <c r="K294" s="0" t="s">
@@ -28564,7 +28570,7 @@
         <v>34</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D295" s="0" t="s">
         <v>77</v>
@@ -28579,7 +28585,7 @@
         <v>137</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="J295" s="11"/>
       <c r="K295" s="0" t="s">
@@ -28648,13 +28654,13 @@
         <v>34</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D296" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F296" s="0" t="s">
         <v>149</v>
@@ -28663,7 +28669,7 @@
         <v>149</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="J296" s="11">
         <v>46365.125</v>
@@ -28734,13 +28740,13 @@
         <v>34</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D297" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F297" s="0" t="s">
         <v>149</v>
@@ -28749,7 +28755,7 @@
         <v>149</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="J297" s="11"/>
       <c r="K297" s="0" t="s">
@@ -28818,7 +28824,7 @@
         <v>61</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D298" s="0" t="s">
         <v>162</v>
@@ -28833,7 +28839,7 @@
         <v>93</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="J298" s="11">
         <v>46373.125</v>
@@ -28904,13 +28910,13 @@
         <v>643</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D299" s="0" t="s">
         <v>626</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="F299" s="0" t="s">
         <v>134</v>
@@ -28919,7 +28925,7 @@
         <v>326</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="J299" s="11">
         <v>46372.125</v>
@@ -28990,7 +28996,7 @@
         <v>61</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D300" s="0" t="s">
         <v>249</v>
@@ -29074,7 +29080,7 @@
         <v>49</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D301" s="0" t="s">
         <v>259</v>
@@ -29160,13 +29166,13 @@
         <v>61</v>
       </c>
       <c r="C302" s="0" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D302" s="0" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="F302" s="0" t="s">
         <v>74</v>
@@ -29246,7 +29252,7 @@
         <v>61</v>
       </c>
       <c r="C303" s="0" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D303" s="0" t="s">
         <v>259</v>
@@ -29330,7 +29336,7 @@
         <v>61</v>
       </c>
       <c r="C304" s="0" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D304" s="0" t="s">
         <v>259</v>
@@ -29416,7 +29422,7 @@
         <v>61</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D305" s="0" t="s">
         <v>412</v>
@@ -29431,7 +29437,7 @@
         <v>326</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="J305" s="11">
         <v>46361.125</v>
@@ -29502,7 +29508,7 @@
         <v>61</v>
       </c>
       <c r="C306" s="0" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D306" s="0" t="s">
         <v>259</v>
@@ -29517,7 +29523,7 @@
         <v>60</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="J306" s="11">
         <v>46326.125</v>
@@ -29526,7 +29532,7 @@
         <v>114</v>
       </c>
       <c r="L306" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M306" s="0" t="s">
         <v>39</v>
@@ -29588,10 +29594,10 @@
         <v>61</v>
       </c>
       <c r="C307" s="0" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E307" s="0" t="s">
         <v>102</v>
@@ -29675,7 +29681,7 @@
         <v>61</v>
       </c>
       <c r="C308" s="0" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D308" s="0" t="s">
         <v>249</v>
@@ -29761,7 +29767,7 @@
         <v>49</v>
       </c>
       <c r="C309" s="0" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D309" s="0" t="s">
         <v>259</v>
@@ -29847,13 +29853,13 @@
         <v>61</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="F310" s="0" t="s">
         <v>74</v>
@@ -29933,7 +29939,7 @@
         <v>61</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D311" s="0" t="s">
         <v>259</v>
@@ -30019,7 +30025,7 @@
         <v>61</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D312" s="0" t="s">
         <v>259</v>
@@ -30105,7 +30111,7 @@
         <v>61</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="D313" s="0" t="s">
         <v>412</v>
@@ -30120,7 +30126,7 @@
         <v>326</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="J313" s="11">
         <v>46359.125</v>
@@ -30191,7 +30197,7 @@
         <v>61</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D314" s="0" t="s">
         <v>259</v>
@@ -30206,7 +30212,7 @@
         <v>60</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="J314" s="11">
         <v>46326.125</v>
@@ -30215,7 +30221,7 @@
         <v>114</v>
       </c>
       <c r="L314" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M314" s="0" t="s">
         <v>39</v>
@@ -30277,10 +30283,10 @@
         <v>61</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D315" s="0" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E315" s="0" t="s">
         <v>97</v>
@@ -30364,7 +30370,7 @@
         <v>61</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D316" s="0" t="s">
         <v>51</v>
@@ -30379,7 +30385,7 @@
         <v>169</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="J316" s="11"/>
       <c r="K316" s="0" t="s">
@@ -30448,7 +30454,7 @@
         <v>61</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D317" s="0" t="s">
         <v>51</v>
@@ -30534,10 +30540,10 @@
         <v>61</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E318" s="0" t="s">
         <v>228</v>
@@ -30620,7 +30626,7 @@
         <v>61</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D319" s="0" t="s">
         <v>249</v>
@@ -30704,7 +30710,7 @@
         <v>49</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D320" s="0" t="s">
         <v>478</v>
@@ -30719,7 +30725,7 @@
         <v>93</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="J320" s="11">
         <v>46370.125</v>
@@ -30790,7 +30796,7 @@
         <v>34</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D321" s="0" t="s">
         <v>162</v>
@@ -30805,7 +30811,7 @@
         <v>243</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="J321" s="11">
         <v>46367.125</v>
@@ -30873,7 +30879,7 @@
         <v>49</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D322" s="0" t="s">
         <v>311</v>
@@ -30888,7 +30894,7 @@
         <v>65</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="J322" s="11">
         <v>46415.125</v>
@@ -30959,7 +30965,7 @@
         <v>49</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D323" s="0" t="s">
         <v>313</v>
@@ -30974,7 +30980,7 @@
         <v>65</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="J323" s="11">
         <v>46415.125</v>
@@ -31045,13 +31051,13 @@
         <v>49</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E324" s="0" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="F324" s="0" t="s">
         <v>169</v>
@@ -31060,7 +31066,7 @@
         <v>169</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="J324" s="11">
         <v>46358.125</v>
@@ -31131,13 +31137,13 @@
         <v>49</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D325" s="0" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E325" s="0" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F325" s="0" t="s">
         <v>65</v>
@@ -31146,7 +31152,7 @@
         <v>65</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="J325" s="11">
         <v>46358.125</v>
@@ -31217,7 +31223,7 @@
         <v>49</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D326" s="0" t="s">
         <v>412</v>
@@ -31303,7 +31309,7 @@
         <v>49</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D327" s="0" t="s">
         <v>412</v>
@@ -31389,7 +31395,7 @@
         <v>61</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D328" s="0" t="s">
         <v>51</v>
@@ -31404,7 +31410,7 @@
         <v>74</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="J328" s="11"/>
       <c r="K328" s="0" t="s">
@@ -31473,7 +31479,7 @@
         <v>61</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D329" s="0" t="s">
         <v>36</v>
@@ -31488,7 +31494,7 @@
         <v>326</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="J329" s="11">
         <v>46373.125</v>
@@ -31559,7 +31565,7 @@
         <v>61</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D330" s="0" t="s">
         <v>36</v>
@@ -31574,7 +31580,7 @@
         <v>326</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="J330" s="11">
         <v>46373.125</v>
@@ -31645,7 +31651,7 @@
         <v>61</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D331" s="0" t="s">
         <v>249</v>
@@ -31731,7 +31737,7 @@
         <v>61</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D332" s="0" t="s">
         <v>249</v>
@@ -31817,7 +31823,7 @@
         <v>61</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D333" s="0" t="s">
         <v>249</v>
@@ -31903,7 +31909,7 @@
         <v>61</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D334" s="0" t="s">
         <v>249</v>
@@ -31989,13 +31995,13 @@
         <v>49</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D335" s="0" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E335" s="0" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="F335" s="0" t="s">
         <v>168</v>
@@ -32004,7 +32010,7 @@
         <v>168</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="J335" s="11">
         <v>46421.125</v>
@@ -32075,13 +32081,13 @@
         <v>49</v>
       </c>
       <c r="C336" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="D336" s="0" t="s">
+        <v>772</v>
+      </c>
+      <c r="E336" s="0" t="s">
         <v>773</v>
-      </c>
-      <c r="D336" s="0" t="s">
-        <v>770</v>
-      </c>
-      <c r="E336" s="0" t="s">
-        <v>771</v>
       </c>
       <c r="F336" s="0" t="s">
         <v>168</v>
@@ -32090,7 +32096,7 @@
         <v>168</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="J336" s="11">
         <v>46421.125</v>
@@ -32161,7 +32167,7 @@
         <v>61</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D337" s="0" t="s">
         <v>249</v>
@@ -32245,7 +32251,7 @@
         <v>61</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D338" s="0" t="s">
         <v>249</v>
@@ -32329,7 +32335,7 @@
         <v>61</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D339" s="0" t="s">
         <v>259</v>
@@ -32344,7 +32350,7 @@
         <v>93</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="J339" s="11">
         <v>46373.125</v>
@@ -32415,7 +32421,7 @@
         <v>61</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D340" s="0" t="s">
         <v>259</v>
@@ -32430,7 +32436,7 @@
         <v>93</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="J340" s="11">
         <v>46373.125</v>
@@ -32501,13 +32507,13 @@
         <v>226</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="E341" s="0" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="F341" s="0" t="s">
         <v>149</v>
@@ -32581,7 +32587,7 @@
         <v>61</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D342" s="0" t="s">
         <v>72</v>
@@ -32668,7 +32674,7 @@
         <v>61</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D343" s="0" t="s">
         <v>412</v>
@@ -32752,7 +32758,7 @@
         <v>34</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D344" s="0" t="s">
         <v>77</v>
@@ -32767,7 +32773,7 @@
         <v>137</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="J344" s="11">
         <v>46366.125</v>
@@ -32838,7 +32844,7 @@
         <v>34</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D345" s="0" t="s">
         <v>96</v>
@@ -32853,14 +32859,14 @@
         <v>74</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="J345" s="11"/>
       <c r="K345" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L345" s="0" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="M345" s="0" t="s">
         <v>39</v>
@@ -32922,7 +32928,7 @@
         <v>34</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D346" s="0" t="s">
         <v>96</v>
@@ -32937,7 +32943,7 @@
         <v>74</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="J346" s="11"/>
       <c r="K346" s="0" t="s">
@@ -33006,7 +33012,7 @@
         <v>49</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D347" s="0" t="s">
         <v>304</v>
@@ -33092,13 +33098,13 @@
         <v>49</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E348" s="0" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="F348" s="0" t="s">
         <v>149</v>
@@ -33175,7 +33181,7 @@
         <v>49</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D349" s="0" t="s">
         <v>304</v>
@@ -33261,7 +33267,7 @@
         <v>49</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D350" s="0" t="s">
         <v>304</v>
@@ -33347,7 +33353,7 @@
         <v>34</v>
       </c>
       <c r="C351" s="0" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D351" s="0" t="s">
         <v>162</v>
@@ -33362,7 +33368,7 @@
         <v>524</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="J351" s="11"/>
       <c r="K351" s="0" t="s">
@@ -33431,7 +33437,7 @@
         <v>34</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D352" s="0" t="s">
         <v>140</v>
@@ -33446,7 +33452,7 @@
         <v>439</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="J352" s="11"/>
       <c r="K352" s="0" t="s">
@@ -33515,7 +33521,7 @@
         <v>61</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D353" s="0" t="s">
         <v>162</v>
@@ -33530,7 +33536,7 @@
         <v>54</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="J353" s="11">
         <v>46373.125</v>
@@ -33601,7 +33607,7 @@
         <v>61</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D354" s="0" t="s">
         <v>249</v>
@@ -33616,7 +33622,7 @@
         <v>326</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="J354" s="11">
         <v>46373.125</v>
@@ -33687,13 +33693,13 @@
         <v>226</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D355" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E355" s="0" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F355" s="0" t="s">
         <v>502</v>
@@ -33767,7 +33773,7 @@
         <v>61</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D356" s="0" t="s">
         <v>162</v>
@@ -33782,7 +33788,7 @@
         <v>54</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="J356" s="11">
         <v>46373.125</v>
@@ -33853,13 +33859,13 @@
         <v>61</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D357" s="0" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E357" s="0" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F357" s="0" t="s">
         <v>60</v>
@@ -33868,7 +33874,7 @@
         <v>134</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="J357" s="11">
         <v>46373.125</v>
@@ -33942,7 +33948,7 @@
         <v>61</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D358" s="0" t="s">
         <v>51</v>
@@ -33957,7 +33963,7 @@
         <v>131</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="J358" s="11"/>
       <c r="K358" s="0" t="s">
@@ -34020,19 +34026,19 @@
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B359" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D359" s="0" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E359" s="0" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="F359" s="0" t="s">
         <v>293</v>
@@ -34071,7 +34077,7 @@
         <v>45</v>
       </c>
       <c r="AC359" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AD359" s="11">
         <v>45847.61793511574</v>
@@ -34097,19 +34103,19 @@
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B360" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D360" s="0" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E360" s="0" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F360" s="0" t="s">
         <v>209</v>
@@ -34180,19 +34186,19 @@
     </row>
     <row r="361">
       <c r="A361" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B361" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D361" s="0" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E361" s="0" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F361" s="0" t="s">
         <v>208</v>
@@ -34263,19 +34269,19 @@
     </row>
     <row r="362">
       <c r="A362" s="0" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B362" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D362" s="0" t="s">
         <v>412</v>
       </c>
       <c r="E362" s="0" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="F362" s="0" t="s">
         <v>134</v>
@@ -34346,19 +34352,19 @@
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B363" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D363" s="0" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E363" s="0" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="F363" s="0" t="s">
         <v>327</v>
@@ -34429,19 +34435,19 @@
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B364" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D364" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E364" s="0" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="F364" s="0" t="s">
         <v>208</v>
@@ -34518,13 +34524,13 @@
         <v>621</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D365" s="0" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F365" s="0" t="s">
         <v>168</v>
@@ -34598,7 +34604,7 @@
         <v>34</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D366" s="0" t="s">
         <v>63</v>
@@ -34682,7 +34688,7 @@
         <v>49</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D367" s="0" t="s">
         <v>228</v>
@@ -34765,7 +34771,7 @@
         <v>49</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D368" s="0" t="s">
         <v>77</v>
@@ -34848,7 +34854,7 @@
         <v>61</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D369" s="0" t="s">
         <v>51</v>
@@ -34863,7 +34869,7 @@
         <v>79</v>
       </c>
       <c r="H369" s="0" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J369" s="11">
         <v>46356.125</v>
@@ -34937,13 +34943,13 @@
         <v>61</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D370" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E370" s="0" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="F370" s="0" t="s">
         <v>149</v>
@@ -34952,7 +34958,7 @@
         <v>149</v>
       </c>
       <c r="H370" s="0" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="J370" s="11">
         <v>46356.125</v>
@@ -35026,7 +35032,7 @@
         <v>226</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D371" s="0" t="s">
         <v>77</v>
@@ -35041,7 +35047,7 @@
         <v>184</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="J371" s="11">
         <v>46392.125</v>
@@ -35106,16 +35112,16 @@
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B372" s="0" t="s">
         <v>226</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="D372" s="0" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="E372" s="0" t="s">
         <v>141</v>
@@ -35127,7 +35133,7 @@
         <v>439</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="J372" s="11">
         <v>46392.125</v>
@@ -35192,7 +35198,7 @@
         <v>61</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D373" s="0" t="s">
         <v>162</v>
@@ -35207,7 +35213,7 @@
         <v>339</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="J373" s="11">
         <v>46326.125</v>
@@ -35216,7 +35222,7 @@
         <v>114</v>
       </c>
       <c r="L373" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M373" s="0" t="s">
         <v>39</v>
@@ -35278,7 +35284,7 @@
         <v>34</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D374" s="0" t="s">
         <v>77</v>
@@ -35293,7 +35299,7 @@
         <v>54</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="J374" s="11"/>
       <c r="K374" s="0" t="s">
@@ -35362,7 +35368,7 @@
         <v>34</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="D375" s="0" t="s">
         <v>36</v>
@@ -35377,7 +35383,7 @@
         <v>60</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="J375" s="11"/>
       <c r="K375" s="0" t="s">
@@ -35446,7 +35452,7 @@
         <v>61</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D376" s="0" t="s">
         <v>51</v>
@@ -35524,19 +35530,19 @@
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B377" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D377" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E377" s="0" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="F377" s="0" t="s">
         <v>208</v>
@@ -35545,7 +35551,7 @@
         <v>209</v>
       </c>
       <c r="H377" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="J377" s="11">
         <v>46326.125</v>
@@ -35554,7 +35560,7 @@
         <v>114</v>
       </c>
       <c r="L377" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M377" s="0" t="s">
         <v>39</v>
@@ -35616,13 +35622,13 @@
         <v>643</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D378" s="0" t="s">
         <v>626</v>
       </c>
       <c r="E378" s="0" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="F378" s="0" t="s">
         <v>134</v>
@@ -35631,7 +35637,7 @@
         <v>326</v>
       </c>
       <c r="H378" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="J378" s="11">
         <v>46326.125</v>
@@ -35640,7 +35646,7 @@
         <v>114</v>
       </c>
       <c r="L378" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M378" s="0" t="s">
         <v>39</v>
@@ -35696,19 +35702,19 @@
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B379" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E379" s="0" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F379" s="0" t="s">
         <v>209</v>
@@ -35717,7 +35723,7 @@
         <v>209</v>
       </c>
       <c r="H379" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="J379" s="11">
         <v>46348.125</v>
@@ -35788,13 +35794,13 @@
         <v>643</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E380" s="0" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="F380" s="0" t="s">
         <v>134</v>
@@ -35803,7 +35809,7 @@
         <v>326</v>
       </c>
       <c r="H380" s="0" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J380" s="11">
         <v>46341.125</v>
@@ -35812,7 +35818,7 @@
         <v>114</v>
       </c>
       <c r="L380" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M380" s="0" t="s">
         <v>39</v>
@@ -35874,7 +35880,7 @@
         <v>49</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>198</v>
@@ -35957,10 +35963,10 @@
         <v>642</v>
       </c>
       <c r="B382" s="0" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D382" s="0" t="s">
         <v>63</v>
@@ -36014,7 +36020,7 @@
         <v>44</v>
       </c>
       <c r="AC382" s="0" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AD382" s="11">
         <v>46037.467388136574</v>
@@ -36043,16 +36049,16 @@
         <v>642</v>
       </c>
       <c r="B383" s="0" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D383" s="0" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="E383" s="0" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="F383" s="0" t="s">
         <v>60</v>
@@ -36061,14 +36067,14 @@
         <v>134</v>
       </c>
       <c r="H383" s="0" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="J383" s="11"/>
       <c r="K383" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L383" s="0" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="M383" s="0" t="s">
         <v>39</v>
@@ -36089,7 +36095,7 @@
         <v>44</v>
       </c>
       <c r="AC383" s="0" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AD383" s="11">
         <v>46038.63016152778</v>
@@ -36121,19 +36127,19 @@
         <v>49</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D384" s="0" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="E384" s="0" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="F384" s="0" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="G384" s="0" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="H384" s="0" t="s">
         <v>132</v>
@@ -36201,25 +36207,25 @@
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B385" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D385" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E385" s="0" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F385" s="0" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="G385" s="0" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="J385" s="11">
         <v>46409.125</v>
@@ -36252,7 +36258,7 @@
         <v>45</v>
       </c>
       <c r="AC385" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AD385" s="11">
         <v>46051.66783503472</v>
@@ -36278,25 +36284,25 @@
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B386" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D386" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="F386" s="0" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="G386" s="0" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="J386" s="11">
         <v>46413.125</v>
@@ -36326,7 +36332,7 @@
         <v>45</v>
       </c>
       <c r="AC386" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AD386" s="11">
         <v>46052.455825081015</v>
@@ -36358,7 +36364,7 @@
         <v>34</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D387" s="0" t="s">
         <v>51</v>
@@ -36442,7 +36448,7 @@
         <v>34</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D388" s="0" t="s">
         <v>36</v>
@@ -36528,13 +36534,13 @@
         <v>61</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E389" s="0" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F389" s="0" t="s">
         <v>200</v>
@@ -36547,7 +36553,7 @@
         <v>40</v>
       </c>
       <c r="L389" s="0" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="M389" s="0" t="s">
         <v>39</v>
@@ -36605,13 +36611,13 @@
         <v>61</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E390" s="0" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F390" s="0" t="s">
         <v>200</v>
@@ -36682,25 +36688,25 @@
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B391" s="0" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E391" s="0" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="F391" s="0" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="G391" s="0" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="J391" s="11">
         <v>46401.125</v>
@@ -36733,7 +36739,7 @@
         <v>45</v>
       </c>
       <c r="AC391" s="0" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="AD391" s="11">
         <v>46104.56253545139</v>
@@ -36759,19 +36765,19 @@
     </row>
     <row r="392">
       <c r="A392" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B392" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E392" s="0" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F392" s="0" t="s">
         <v>209</v>
@@ -36780,7 +36786,7 @@
         <v>209</v>
       </c>
       <c r="H392" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="J392" s="11">
         <v>46372.125</v>
@@ -36851,13 +36857,13 @@
         <v>643</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="F393" s="0" t="s">
         <v>327</v>
@@ -36866,7 +36872,7 @@
         <v>327</v>
       </c>
       <c r="H393" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="J393" s="11">
         <v>46372.125</v>
@@ -36937,13 +36943,13 @@
         <v>61</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E394" s="0" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="F394" s="0" t="s">
         <v>60</v>
@@ -36956,7 +36962,7 @@
         <v>40</v>
       </c>
       <c r="L394" s="0" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="M394" s="0" t="s">
         <v>39</v>
@@ -37012,19 +37018,19 @@
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B395" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E395" s="0" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F395" s="0" t="s">
         <v>209</v>
@@ -37033,7 +37039,7 @@
         <v>209</v>
       </c>
       <c r="H395" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="J395" s="11">
         <v>46362.125</v>
@@ -37104,7 +37110,7 @@
         <v>34</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>198</v>
@@ -37190,13 +37196,13 @@
         <v>49</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="D397" s="0" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="F397" s="0" t="s">
         <v>243</v>
@@ -37205,7 +37211,7 @@
         <v>243</v>
       </c>
       <c r="H397" s="0" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="J397" s="11">
         <v>46413.125</v>
@@ -37276,13 +37282,13 @@
         <v>49</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="D398" s="0" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F398" s="0" t="s">
         <v>53</v>
@@ -37291,7 +37297,7 @@
         <v>54</v>
       </c>
       <c r="H398" s="0" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="J398" s="11">
         <v>46357.125</v>
@@ -37362,7 +37368,7 @@
         <v>34</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>162</v>
@@ -37377,7 +37383,7 @@
         <v>54</v>
       </c>
       <c r="H399" s="0" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="J399" s="11">
         <v>46361.125</v>
@@ -37448,7 +37454,7 @@
         <v>34</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>51</v>
@@ -37463,7 +37469,7 @@
         <v>150</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="J400" s="11">
         <v>46365.125</v>
@@ -37534,7 +37540,7 @@
         <v>34</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>51</v>
@@ -37549,7 +37555,7 @@
         <v>134</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="J401" s="11">
         <v>46365.125</v>
@@ -37620,7 +37626,7 @@
         <v>34</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>36</v>
@@ -37635,7 +37641,7 @@
         <v>134</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="J402" s="11"/>
       <c r="K402" s="0" t="s">
@@ -37704,13 +37710,13 @@
         <v>49</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D403" s="0" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="E403" s="0" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="F403" s="0" t="s">
         <v>54</v>
@@ -37719,7 +37725,7 @@
         <v>54</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="J403" s="11">
         <v>46365.125</v>
@@ -37790,7 +37796,7 @@
         <v>49</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>322</v>
@@ -37805,7 +37811,7 @@
         <v>134</v>
       </c>
       <c r="H404" s="0" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="J404" s="11">
         <v>46362.125</v>
@@ -37876,13 +37882,13 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E405" s="0" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="F405" s="0" t="s">
         <v>65</v>
@@ -37962,7 +37968,7 @@
         <v>34</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>36</v>
@@ -38048,7 +38054,7 @@
         <v>34</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>36</v>
@@ -38134,13 +38140,13 @@
         <v>34</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E408" s="0" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="F408" s="0" t="s">
         <v>439</v>
@@ -38149,7 +38155,7 @@
         <v>439</v>
       </c>
       <c r="H408" s="0" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="J408" s="11"/>
       <c r="K408" s="0" t="s">
@@ -38218,13 +38224,13 @@
         <v>34</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E409" s="0" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="F409" s="0" t="s">
         <v>134</v>
@@ -38233,7 +38239,7 @@
         <v>134</v>
       </c>
       <c r="H409" s="0" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="J409" s="11"/>
       <c r="K409" s="0" t="s">
@@ -38302,7 +38308,7 @@
         <v>34</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>72</v>
@@ -38389,7 +38395,7 @@
         <v>34</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>51</v>
@@ -38404,7 +38410,7 @@
         <v>339</v>
       </c>
       <c r="H411" s="0" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="J411" s="11">
         <v>46356.125</v>
@@ -38478,13 +38484,13 @@
         <v>34</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>140</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="F412" s="0" t="s">
         <v>142</v>
@@ -38493,7 +38499,7 @@
         <v>142</v>
       </c>
       <c r="H412" s="0" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="J412" s="11"/>
       <c r="K412" s="0" t="s">
@@ -38565,13 +38571,13 @@
         <v>34</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E413" s="0" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="F413" s="0" t="s">
         <v>93</v>
@@ -38580,7 +38586,7 @@
         <v>93</v>
       </c>
       <c r="H413" s="0" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J413" s="11"/>
       <c r="K413" s="0" t="s">
@@ -38652,7 +38658,7 @@
         <v>34</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>123</v>
@@ -38667,7 +38673,7 @@
         <v>60</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J414" s="11"/>
       <c r="K414" s="0" t="s">
@@ -38736,7 +38742,7 @@
         <v>34</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>123</v>
@@ -38751,7 +38757,7 @@
         <v>60</v>
       </c>
       <c r="H415" s="0" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J415" s="11"/>
       <c r="K415" s="0" t="s">
@@ -38820,13 +38826,13 @@
         <v>49</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D416" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E416" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="F416" s="0" t="s">
         <v>200</v>
@@ -38903,7 +38909,7 @@
         <v>34</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>63</v>
@@ -38989,7 +38995,7 @@
         <v>34</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>36</v>
@@ -39004,14 +39010,14 @@
         <v>38</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="J418" s="11"/>
       <c r="K418" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L418" s="0" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="M418" s="0" t="s">
         <v>39</v>
@@ -39076,7 +39082,7 @@
         <v>34</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>36</v>
@@ -39091,14 +39097,14 @@
         <v>38</v>
       </c>
       <c r="H419" s="0" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="J419" s="11"/>
       <c r="K419" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L419" s="0" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="M419" s="0" t="s">
         <v>39</v>
@@ -39163,13 +39169,13 @@
         <v>49</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="D420" s="0" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="E420" s="0" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="F420" s="0" t="s">
         <v>65</v>
@@ -39246,7 +39252,7 @@
         <v>49</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>322</v>
@@ -39329,13 +39335,13 @@
         <v>34</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>315</v>
       </c>
       <c r="E422" s="0" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="F422" s="0" t="s">
         <v>93</v>
@@ -39344,14 +39350,14 @@
         <v>38</v>
       </c>
       <c r="H422" s="0" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="J422" s="11"/>
       <c r="K422" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L422" s="0" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="M422" s="0" t="s">
         <v>39</v>
@@ -39416,7 +39422,7 @@
         <v>49</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>388</v>
@@ -39499,13 +39505,13 @@
         <v>49</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D424" s="0" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="E424" s="0" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="F424" s="0" t="s">
         <v>150</v>
@@ -39582,7 +39588,7 @@
         <v>61</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>51</v>
@@ -39597,7 +39603,7 @@
         <v>168</v>
       </c>
       <c r="H425" s="0" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="J425" s="11"/>
       <c r="K425" s="0" t="s">
@@ -39666,13 +39672,13 @@
         <v>61</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E426" s="0" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="F426" s="0" t="s">
         <v>332</v>
@@ -39681,7 +39687,7 @@
         <v>332</v>
       </c>
       <c r="H426" s="0" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="J426" s="11">
         <v>46373.125</v>
@@ -39752,7 +39758,7 @@
         <v>61</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>77</v>
@@ -39767,7 +39773,7 @@
         <v>524</v>
       </c>
       <c r="H427" s="0" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="J427" s="11"/>
       <c r="K427" s="0" t="s">
@@ -39839,13 +39845,13 @@
         <v>61</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E428" s="0" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="F428" s="0" t="s">
         <v>169</v>
@@ -39928,7 +39934,7 @@
         <v>61</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>77</v>
@@ -39943,7 +39949,7 @@
         <v>54</v>
       </c>
       <c r="H429" s="0" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="J429" s="11">
         <v>46373.125</v>
@@ -40014,13 +40020,13 @@
         <v>61</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E430" s="0" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="F430" s="0" t="s">
         <v>257</v>
@@ -40029,7 +40035,7 @@
         <v>257</v>
       </c>
       <c r="H430" s="0" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="J430" s="11"/>
       <c r="K430" s="0" t="s">
@@ -40098,7 +40104,7 @@
         <v>61</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>51</v>
@@ -40113,7 +40119,7 @@
         <v>150</v>
       </c>
       <c r="H431" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="J431" s="11">
         <v>46373.125</v>
@@ -40184,13 +40190,13 @@
         <v>61</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D432" s="0" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E432" s="0" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="F432" s="0" t="s">
         <v>209</v>
@@ -40199,7 +40205,7 @@
         <v>209</v>
       </c>
       <c r="H432" s="0" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="J432" s="11"/>
       <c r="K432" s="0" t="s">
@@ -40268,7 +40274,7 @@
         <v>61</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D433" s="0" t="s">
         <v>249</v>
@@ -40283,7 +40289,7 @@
         <v>327</v>
       </c>
       <c r="H433" s="0" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="J433" s="11"/>
       <c r="K433" s="0" t="s">
@@ -40352,7 +40358,7 @@
         <v>61</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>259</v>
@@ -40367,7 +40373,7 @@
         <v>93</v>
       </c>
       <c r="H434" s="0" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="J434" s="11"/>
       <c r="K434" s="0" t="s">
@@ -40436,13 +40442,13 @@
         <v>61</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>259</v>
       </c>
       <c r="E435" s="0" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="F435" s="0" t="s">
         <v>168</v>
@@ -40451,7 +40457,7 @@
         <v>168</v>
       </c>
       <c r="H435" s="0" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="J435" s="11"/>
       <c r="K435" s="0" t="s">
@@ -40523,7 +40529,7 @@
         <v>61</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>249</v>
@@ -40610,13 +40616,13 @@
         <v>61</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D437" s="0" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="E437" s="0" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="F437" s="0" t="s">
         <v>294</v>
@@ -40696,7 +40702,7 @@
         <v>61</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>259</v>
@@ -40711,7 +40717,7 @@
         <v>326</v>
       </c>
       <c r="H438" s="0" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J438" s="11"/>
       <c r="K438" s="0" t="s">
@@ -40783,7 +40789,7 @@
         <v>61</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>412</v>
@@ -40798,7 +40804,7 @@
         <v>169</v>
       </c>
       <c r="H439" s="0" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="J439" s="11">
         <v>46373.125</v>
@@ -40869,7 +40875,7 @@
         <v>61</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D440" s="0" t="s">
         <v>259</v>
@@ -40953,7 +40959,7 @@
         <v>61</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>259</v>
@@ -40968,7 +40974,7 @@
         <v>54</v>
       </c>
       <c r="H441" s="0" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="J441" s="11"/>
       <c r="K441" s="0" t="s">
@@ -41037,7 +41043,7 @@
         <v>61</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>412</v>
@@ -41052,7 +41058,7 @@
         <v>327</v>
       </c>
       <c r="H442" s="0" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="J442" s="11">
         <v>46373.125</v>
@@ -41123,7 +41129,7 @@
         <v>61</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>259</v>
@@ -41138,7 +41144,7 @@
         <v>74</v>
       </c>
       <c r="H443" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="J443" s="11"/>
       <c r="K443" s="0" t="s">
@@ -41207,7 +41213,7 @@
         <v>61</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>259</v>
@@ -41222,7 +41228,7 @@
         <v>326</v>
       </c>
       <c r="H444" s="0" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J444" s="11"/>
       <c r="K444" s="0" t="s">
@@ -41294,7 +41300,7 @@
         <v>61</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>412</v>
@@ -41309,7 +41315,7 @@
         <v>169</v>
       </c>
       <c r="H445" s="0" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="J445" s="11">
         <v>46373.125</v>
@@ -41380,7 +41386,7 @@
         <v>61</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>259</v>
@@ -41464,7 +41470,7 @@
         <v>61</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>162</v>
@@ -41479,7 +41485,7 @@
         <v>176</v>
       </c>
       <c r="H447" s="0" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="J447" s="11"/>
       <c r="K447" s="0" t="s">
@@ -41548,13 +41554,13 @@
         <v>61</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E448" s="0" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="F448" s="0" t="s">
         <v>502</v>
@@ -41563,7 +41569,7 @@
         <v>502</v>
       </c>
       <c r="H448" s="0" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="J448" s="11">
         <v>46373.125</v>
@@ -41634,7 +41640,7 @@
         <v>61</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>162</v>
@@ -41649,7 +41655,7 @@
         <v>518</v>
       </c>
       <c r="H449" s="0" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="J449" s="11"/>
       <c r="K449" s="0" t="s">
@@ -41718,13 +41724,13 @@
         <v>61</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E450" s="0" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="F450" s="0" t="s">
         <v>332</v>
@@ -41733,7 +41739,7 @@
         <v>332</v>
       </c>
       <c r="H450" s="0" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="J450" s="11"/>
       <c r="K450" s="0" t="s">
@@ -41805,7 +41811,7 @@
         <v>61</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>162</v>
@@ -41820,14 +41826,14 @@
         <v>332</v>
       </c>
       <c r="H451" s="0" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="J451" s="11"/>
       <c r="K451" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L451" s="0" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="M451" s="0" t="s">
         <v>39</v>
@@ -41883,25 +41889,25 @@
     </row>
     <row r="452">
       <c r="A452" s="0" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B452" s="0" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D452" s="0" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="E452" s="0" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="F452" s="0" t="s">
         <v>300</v>
       </c>
       <c r="G452" s="0" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="J452" s="11">
         <v>46383.125</v>
@@ -41934,7 +41940,7 @@
         <v>45</v>
       </c>
       <c r="AC452" s="0" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="AD452" s="11">
         <v>46203.65469700231</v>
@@ -41966,13 +41972,13 @@
         <v>643</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E453" s="0" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="F453" s="0" t="s">
         <v>327</v>
@@ -41981,7 +41987,7 @@
         <v>327</v>
       </c>
       <c r="H453" s="0" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J453" s="11">
         <v>46365.125</v>
@@ -42046,19 +42052,19 @@
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B454" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D454" s="0" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E454" s="0" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="F454" s="0" t="s">
         <v>208</v>
@@ -42067,7 +42073,7 @@
         <v>209</v>
       </c>
       <c r="H454" s="0" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J454" s="11">
         <v>46365.125</v>
@@ -42138,13 +42144,13 @@
         <v>34</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E455" s="0" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="F455" s="0" t="s">
         <v>85</v>
@@ -42221,7 +42227,7 @@
         <v>34</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>36</v>
@@ -42304,7 +42310,7 @@
         <v>34</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>123</v>
@@ -42319,7 +42325,7 @@
         <v>74</v>
       </c>
       <c r="H457" s="0" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="J457" s="11">
         <v>46387.125</v>
@@ -42390,7 +42396,7 @@
         <v>34</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D458" s="0" t="s">
         <v>123</v>
@@ -42405,7 +42411,7 @@
         <v>74</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="J458" s="11">
         <v>46326.125</v>
@@ -42414,7 +42420,7 @@
         <v>114</v>
       </c>
       <c r="L458" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M458" s="0" t="s">
         <v>39</v>
@@ -42476,7 +42482,7 @@
         <v>34</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>51</v>
@@ -42491,7 +42497,7 @@
         <v>326</v>
       </c>
       <c r="H459" s="0" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="J459" s="11">
         <v>46326.125</v>
@@ -42500,7 +42506,7 @@
         <v>114</v>
       </c>
       <c r="L459" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M459" s="0" t="s">
         <v>39</v>
@@ -42562,13 +42568,13 @@
         <v>34</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E460" s="0" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F460" s="0" t="s">
         <v>131</v>
@@ -42646,13 +42652,13 @@
         <v>34</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>179</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="F461" s="0" t="s">
         <v>149</v>
@@ -42661,7 +42667,7 @@
         <v>149</v>
       </c>
       <c r="H461" s="0" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="J461" s="11"/>
       <c r="K461" s="0" t="s">
@@ -42730,13 +42736,13 @@
         <v>61</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D462" s="0" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="E462" s="0" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="F462" s="0" t="s">
         <v>418</v>
@@ -42745,7 +42751,7 @@
         <v>418</v>
       </c>
       <c r="H462" s="0" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="J462" s="11"/>
       <c r="K462" s="0" t="s">
@@ -42811,7 +42817,7 @@
         <v>61</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>77</v>
@@ -42826,7 +42832,7 @@
         <v>332</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="J463" s="11">
         <v>46406.125</v>
@@ -42897,13 +42903,13 @@
         <v>61</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="F464" s="0" t="s">
         <v>79</v>
@@ -42912,7 +42918,7 @@
         <v>231</v>
       </c>
       <c r="H464" s="0" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="J464" s="11">
         <v>46407.125</v>
@@ -42983,7 +42989,7 @@
         <v>61</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>249</v>
@@ -42998,7 +43004,7 @@
         <v>134</v>
       </c>
       <c r="H465" s="0" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="J465" s="11">
         <v>46407.125</v>
@@ -43069,7 +43075,7 @@
         <v>61</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>249</v>
@@ -43084,7 +43090,7 @@
         <v>134</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="J466" s="11">
         <v>46407.125</v>
@@ -43155,13 +43161,13 @@
         <v>61</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="D467" s="0" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E467" s="0" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="F467" s="0" t="s">
         <v>54</v>
@@ -43170,7 +43176,7 @@
         <v>54</v>
       </c>
       <c r="H467" s="0" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="J467" s="11">
         <v>46406.125</v>
@@ -43241,7 +43247,7 @@
         <v>61</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>259</v>
@@ -43256,7 +43262,7 @@
         <v>74</v>
       </c>
       <c r="H468" s="0" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="J468" s="11">
         <v>46373.125</v>
@@ -43327,7 +43333,7 @@
         <v>49</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>51</v>
@@ -43413,13 +43419,13 @@
         <v>226</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D470" s="0" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="E470" s="0" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="F470" s="0" t="s">
         <v>142</v>
@@ -43428,7 +43434,7 @@
         <v>142</v>
       </c>
       <c r="H470" s="0" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="J470" s="11">
         <v>46398.125</v>
@@ -43490,19 +43496,19 @@
     </row>
     <row r="471">
       <c r="A471" s="0" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B471" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="D471" s="0" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="E471" s="0" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="F471" s="0" t="s">
         <v>200</v>
@@ -43517,7 +43523,7 @@
         <v>114</v>
       </c>
       <c r="L471" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="M471" s="0" t="s">
         <v>39</v>
@@ -43541,7 +43547,7 @@
         <v>45</v>
       </c>
       <c r="AC471" s="0" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="AD471" s="11">
         <v>46219.55652277778</v>
@@ -43573,7 +43579,7 @@
         <v>49</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>382</v>
@@ -43588,7 +43594,7 @@
         <v>339</v>
       </c>
       <c r="H472" s="0" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="J472" s="11">
         <v>46402.125</v>
@@ -43659,7 +43665,7 @@
         <v>61</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>51</v>
@@ -43674,7 +43680,7 @@
         <v>79</v>
       </c>
       <c r="H473" s="0" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="J473" s="11">
         <v>46346.125</v>
@@ -43745,13 +43751,13 @@
         <v>61</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E474" s="0" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="F474" s="0" t="s">
         <v>339</v>
@@ -43760,7 +43766,7 @@
         <v>53</v>
       </c>
       <c r="H474" s="0" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="J474" s="11">
         <v>46346.125</v>
@@ -43831,7 +43837,7 @@
         <v>61</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D475" s="0" t="s">
         <v>249</v>
@@ -43846,14 +43852,14 @@
         <v>208</v>
       </c>
       <c r="H475" s="0" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="J475" s="11"/>
       <c r="K475" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L475" s="0" t="s">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="M475" s="0" t="s">
         <v>39</v>
@@ -43915,7 +43921,7 @@
         <v>61</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>51</v>
@@ -43930,7 +43936,7 @@
         <v>150</v>
       </c>
       <c r="H476" s="0" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="J476" s="11">
         <v>46407.125</v>
@@ -44001,7 +44007,7 @@
         <v>61</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>259</v>
@@ -44016,7 +44022,7 @@
         <v>231</v>
       </c>
       <c r="H477" s="0" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="J477" s="11">
         <v>46407.125</v>
@@ -44087,7 +44093,7 @@
         <v>61</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="D478" s="0" t="s">
         <v>259</v>
@@ -44102,7 +44108,7 @@
         <v>231</v>
       </c>
       <c r="H478" s="0" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="J478" s="11">
         <v>46407.125</v>
@@ -44167,13 +44173,13 @@
     </row>
     <row r="479">
       <c r="A479" s="0" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B479" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D479" s="0" t="s">
         <v>212</v>
@@ -44253,13 +44259,13 @@
         <v>621</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D480" s="0" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="E480" s="0" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="F480" s="0" t="s">
         <v>439</v>
@@ -44333,13 +44339,13 @@
         <v>49</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D481" s="0" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="E481" s="0" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F481" s="0" t="s">
         <v>98</v>
@@ -44419,13 +44425,13 @@
         <v>34</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="F482" s="0" t="s">
         <v>38</v>
@@ -44434,7 +44440,7 @@
         <v>38</v>
       </c>
       <c r="H482" s="0" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="J482" s="11"/>
       <c r="K482" s="0" t="s">
@@ -44503,13 +44509,13 @@
         <v>49</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D483" s="0" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E483" s="0" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="F483" s="0" t="s">
         <v>137</v>
@@ -44586,7 +44592,7 @@
         <v>49</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>345</v>
@@ -44669,7 +44675,7 @@
         <v>49</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>345</v>
@@ -44752,7 +44758,7 @@
         <v>34</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D486" s="0" t="s">
         <v>249</v>
@@ -44767,7 +44773,7 @@
         <v>38</v>
       </c>
       <c r="H486" s="0" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="J486" s="11">
         <v>46362.125</v>
@@ -44838,7 +44844,7 @@
         <v>34</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="D487" s="0" t="s">
         <v>249</v>
@@ -44853,7 +44859,7 @@
         <v>38</v>
       </c>
       <c r="H487" s="0" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="J487" s="11">
         <v>46362.125</v>
@@ -44924,7 +44930,7 @@
         <v>49</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>366</v>
@@ -45007,13 +45013,13 @@
         <v>49</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D489" s="0" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="E489" s="0" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="F489" s="0" t="s">
         <v>257</v>
@@ -45090,13 +45096,13 @@
         <v>49</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D490" s="0" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E490" s="0" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="F490" s="0" t="s">
         <v>131</v>
@@ -45173,13 +45179,13 @@
         <v>49</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D491" s="0" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="E491" s="0" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="F491" s="0" t="s">
         <v>294</v>
@@ -45256,13 +45262,13 @@
         <v>61</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E492" s="0" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="F492" s="0" t="s">
         <v>105</v>
@@ -45334,19 +45340,19 @@
     </row>
     <row r="493">
       <c r="A493" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B493" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E493" s="0" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="F493" s="0" t="s">
         <v>293</v>
@@ -45355,7 +45361,7 @@
         <v>293</v>
       </c>
       <c r="H493" s="0" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="J493" s="11">
         <v>46372.125</v>
@@ -45426,19 +45432,19 @@
         <v>34</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E494" s="0" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="F494" s="0" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="G494" s="0" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="H494" s="0" t="s">
         <v>201</v>
@@ -45512,19 +45518,19 @@
         <v>34</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="D495" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E495" s="0" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="F495" s="0" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="G495" s="0" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="H495" s="0" t="s">
         <v>201</v>
@@ -45598,7 +45604,7 @@
         <v>226</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D496" s="0" t="s">
         <v>526</v>
@@ -45672,19 +45678,19 @@
     </row>
     <row r="497">
       <c r="A497" s="0" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B497" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D497" s="0" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="E497" s="0" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="F497" s="0" t="s">
         <v>294</v>
@@ -45720,7 +45726,7 @@
         <v>45</v>
       </c>
       <c r="AC497" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AD497" s="11">
         <v>46301.476280462964</v>
@@ -45746,19 +45752,19 @@
     </row>
     <row r="498">
       <c r="A498" s="0" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B498" s="0" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D498" s="0" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="E498" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="F498" s="0" t="s">
         <v>168</v>
@@ -45771,7 +45777,7 @@
         <v>40</v>
       </c>
       <c r="L498" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="M498" s="0" t="s">
         <v>39</v>
@@ -45795,7 +45801,7 @@
         <v>44</v>
       </c>
       <c r="AC498" s="0" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AD498" s="11">
         <v>46303.38590450231</v>
@@ -45813,19 +45819,19 @@
     </row>
     <row r="499">
       <c r="A499" s="0" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B499" s="0" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="D499" s="0" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="E499" s="0" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="F499" s="0" t="s">
         <v>169</v>
@@ -45838,7 +45844,7 @@
         <v>40</v>
       </c>
       <c r="L499" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="M499" s="0" t="s">
         <v>39</v>
@@ -45862,7 +45868,7 @@
         <v>44</v>
       </c>
       <c r="AC499" s="0" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="AD499" s="11">
         <v>46303.38891412037</v>
@@ -45925,28 +45931,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -45954,10 +45960,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>61</v>
@@ -45975,10 +45981,10 @@
         <v>46495.125</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>214</v>
@@ -45986,10 +45992,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>643</v>
@@ -46007,10 +46013,10 @@
         <v>46495.125</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>647</v>
@@ -46018,10 +46024,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>643</v>
@@ -46033,16 +46039,16 @@
         <v>46315</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G4" s="11">
         <v>46495.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>647</v>
@@ -46050,10 +46056,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>61</v>
@@ -46065,16 +46071,16 @@
         <v>46314</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="G5" s="11">
         <v>46494.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>214</v>
@@ -46082,10 +46088,10 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>643</v>
@@ -46103,10 +46109,10 @@
         <v>46491.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>647</v>
@@ -46114,13 +46120,13 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>30</v>
@@ -46135,24 +46141,24 @@
         <v>46483.125</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>29</v>
@@ -46161,27 +46167,27 @@
         <v>46303</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G8" s="11">
         <v>46483.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>643</v>
@@ -46199,10 +46205,10 @@
         <v>46480.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>647</v>
@@ -46210,10 +46216,10 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>226</v>
@@ -46231,10 +46237,10 @@
         <v>46476.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>226</v>
@@ -46242,10 +46248,10 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>226</v>
@@ -46257,16 +46263,16 @@
         <v>46296</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G11" s="11">
         <v>46476.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>226</v>
@@ -46274,10 +46280,10 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>34</v>
@@ -46295,10 +46301,10 @@
         <v>46474.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>202</v>
@@ -46306,10 +46312,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>34</v>
@@ -46327,10 +46333,10 @@
         <v>46474.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>202</v>
@@ -46338,10 +46344,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>643</v>
@@ -46359,10 +46365,10 @@
         <v>46474.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>647</v>
@@ -46370,10 +46376,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>643</v>
@@ -46385,16 +46391,16 @@
         <v>46294</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G15" s="11">
         <v>46474.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>647</v>
@@ -46402,10 +46408,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>643</v>
@@ -46423,10 +46429,10 @@
         <v>46474.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>647</v>
@@ -46434,10 +46440,10 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>643</v>
@@ -46449,16 +46455,16 @@
         <v>46294</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G17" s="11">
         <v>46474.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>647</v>
@@ -46466,10 +46472,10 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>61</v>
@@ -46481,16 +46487,16 @@
         <v>46289</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="G18" s="11">
         <v>46469.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>67</v>
@@ -46498,10 +46504,10 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>61</v>
@@ -46519,10 +46525,10 @@
         <v>46469.125</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J19" s="0" t="s">
         <v>67</v>
@@ -46530,10 +46536,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>643</v>
@@ -46551,10 +46557,10 @@
         <v>46455.125</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>647</v>
@@ -46562,10 +46568,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>643</v>
@@ -46577,16 +46583,16 @@
         <v>46275</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G21" s="11">
         <v>46455.125</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J21" s="0" t="s">
         <v>647</v>
@@ -46594,13 +46600,13 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>30</v>
@@ -46615,24 +46621,24 @@
         <v>46449.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>29</v>
@@ -46641,30 +46647,30 @@
         <v>46269</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="G23" s="11">
         <v>46449.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>30</v>
@@ -46679,13 +46685,13 @@
         <v>46268</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="25">
@@ -46693,7 +46699,7 @@
         <v>551</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>34</v>
@@ -46705,19 +46711,19 @@
         <v>46267</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="G25" s="11">
         <v>46447.125</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="26">
@@ -46725,7 +46731,7 @@
         <v>551</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>34</v>
@@ -46743,21 +46749,21 @@
         <v>46447.125</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>61</v>
@@ -46775,10 +46781,10 @@
         <v>46314</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>214</v>
@@ -46786,10 +46792,10 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>61</v>
@@ -46807,10 +46813,10 @@
         <v>46446.125</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>214</v>
@@ -46821,7 +46827,7 @@
         <v>553</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>49</v>
@@ -46833,27 +46839,27 @@
         <v>46261</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="G29" s="11">
         <v>46441.125</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>34</v>
@@ -46865,16 +46871,16 @@
         <v>46260</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="G30" s="11">
         <v>46440.125</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>202</v>
@@ -46882,10 +46888,10 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>61</v>
@@ -46903,10 +46909,10 @@
         <v>46440.125</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>67</v>
@@ -46914,10 +46920,10 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>34</v>
@@ -46935,10 +46941,10 @@
         <v>46439.125</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>202</v>
@@ -46946,10 +46952,10 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>34</v>
@@ -46967,10 +46973,10 @@
         <v>46439.125</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>202</v>
@@ -46978,10 +46984,10 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>34</v>
@@ -46999,10 +47005,10 @@
         <v>46439.125</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>202</v>
@@ -47013,7 +47019,7 @@
         <v>653</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>61</v>
@@ -47031,10 +47037,10 @@
         <v>46439.125</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>214</v>
@@ -47045,7 +47051,7 @@
         <v>211</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>61</v>
@@ -47063,10 +47069,10 @@
         <v>46439.125</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>214</v>
@@ -47077,7 +47083,7 @@
         <v>343</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>61</v>
@@ -47095,13 +47101,13 @@
         <v>46439.125</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>67</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="1114">
   <si>
     <t>Geração:</t>
   </si>
@@ -1975,12 +1975,6 @@
   </si>
   <si>
     <t>FZS1103</t>
-  </si>
-  <si>
-    <t>Documento ConsultaCRLV aguardando validação</t>
-  </si>
-  <si>
-    <t>AV</t>
   </si>
   <si>
     <t>NLO5E70</t>
@@ -3552,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46316.40538217592</v>
+        <v>46316.6776916088</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -26237,12 +26231,14 @@
       <c r="G267" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="J267" s="11"/>
+      <c r="J267" s="11">
+        <v>46400.125</v>
+      </c>
       <c r="K267" s="0" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="L267" s="0" t="s">
-        <v>654</v>
+        <v>39</v>
       </c>
       <c r="M267" s="0" t="s">
         <v>39</v>
@@ -26251,13 +26247,13 @@
         <v>43</v>
       </c>
       <c r="O267" s="11">
-        <v>46404.125</v>
+        <v>46624.125</v>
       </c>
       <c r="Q267" s="0" t="s">
-        <v>655</v>
+        <v>43</v>
       </c>
       <c r="R267" s="11">
-        <v>46387.125</v>
+        <v>46438.125</v>
       </c>
       <c r="T267" s="0" t="s">
         <v>44</v>
@@ -26304,13 +26300,13 @@
         <v>621</v>
       </c>
       <c r="C268" s="0" t="s">
+        <v>654</v>
+      </c>
+      <c r="D268" s="0" t="s">
+        <v>655</v>
+      </c>
+      <c r="E268" s="0" t="s">
         <v>656</v>
-      </c>
-      <c r="D268" s="0" t="s">
-        <v>657</v>
-      </c>
-      <c r="E268" s="0" t="s">
-        <v>658</v>
       </c>
       <c r="F268" s="0" t="s">
         <v>38</v>
@@ -26382,7 +26378,7 @@
         <v>34</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D269" s="0" t="s">
         <v>51</v>
@@ -26460,13 +26456,13 @@
     </row>
     <row r="270">
       <c r="A270" s="0" t="s">
+        <v>658</v>
+      </c>
+      <c r="B270" s="0" t="s">
+        <v>659</v>
+      </c>
+      <c r="C270" s="0" t="s">
         <v>660</v>
-      </c>
-      <c r="B270" s="0" t="s">
-        <v>661</v>
-      </c>
-      <c r="C270" s="0" t="s">
-        <v>662</v>
       </c>
       <c r="D270" s="0" t="s">
         <v>427</v>
@@ -26478,14 +26474,14 @@
         <v>497</v>
       </c>
       <c r="G270" s="0" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="J270" s="11"/>
       <c r="K270" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L270" s="0" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="M270" s="0" t="s">
         <v>39</v>
@@ -26506,7 +26502,7 @@
         <v>45</v>
       </c>
       <c r="AC270" s="0" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="AD270" s="11">
         <v>45817.61092795139</v>
@@ -26532,32 +26528,32 @@
     </row>
     <row r="271">
       <c r="A271" s="0" t="s">
+        <v>664</v>
+      </c>
+      <c r="B271" s="0" t="s">
+        <v>659</v>
+      </c>
+      <c r="C271" s="0" t="s">
+        <v>665</v>
+      </c>
+      <c r="D271" s="0" t="s">
         <v>666</v>
       </c>
-      <c r="B271" s="0" t="s">
-        <v>661</v>
-      </c>
-      <c r="C271" s="0" t="s">
-        <v>667</v>
-      </c>
-      <c r="D271" s="0" t="s">
-        <v>668</v>
-      </c>
       <c r="E271" s="0" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F271" s="0" t="s">
         <v>169</v>
       </c>
       <c r="G271" s="0" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="J271" s="11"/>
       <c r="K271" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L271" s="0" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="M271" s="0" t="s">
         <v>39</v>
@@ -26584,7 +26580,7 @@
         <v>45</v>
       </c>
       <c r="AC271" s="0" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="AD271" s="11">
         <v>45817.61552398148</v>
@@ -26616,7 +26612,7 @@
         <v>49</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D272" s="0" t="s">
         <v>313</v>
@@ -26631,7 +26627,7 @@
         <v>131</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="J272" s="11">
         <v>46411.125</v>
@@ -26702,7 +26698,7 @@
         <v>49</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D273" s="0" t="s">
         <v>311</v>
@@ -26714,10 +26710,10 @@
         <v>131</v>
       </c>
       <c r="G273" s="0" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="J273" s="11">
         <v>46411.125</v>
@@ -26788,13 +26784,13 @@
         <v>61</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D274" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F274" s="0" t="s">
         <v>65</v>
@@ -26803,7 +26799,7 @@
         <v>65</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="J274" s="11">
         <v>46357.125</v>
@@ -26874,7 +26870,7 @@
         <v>34</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D275" s="0" t="s">
         <v>162</v>
@@ -26889,14 +26885,14 @@
         <v>339</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="J275" s="11"/>
       <c r="K275" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L275" s="0" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="M275" s="0" t="s">
         <v>39</v>
@@ -26955,13 +26951,13 @@
         <v>49</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D276" s="0" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F276" s="0" t="s">
         <v>168</v>
@@ -26970,7 +26966,7 @@
         <v>168</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J276" s="11">
         <v>46417.125</v>
@@ -27041,13 +27037,13 @@
         <v>34</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D277" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F277" s="0" t="s">
         <v>200</v>
@@ -27063,7 +27059,7 @@
         <v>40</v>
       </c>
       <c r="L277" s="0" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="M277" s="0" t="s">
         <v>39</v>
@@ -27125,13 +27121,13 @@
         <v>49</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D278" s="0" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E278" s="0" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F278" s="0" t="s">
         <v>74</v>
@@ -27211,7 +27207,7 @@
         <v>49</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D279" s="0" t="s">
         <v>368</v>
@@ -27297,7 +27293,7 @@
         <v>49</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D280" s="0" t="s">
         <v>370</v>
@@ -27383,7 +27379,7 @@
         <v>49</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D281" s="0" t="s">
         <v>585</v>
@@ -27398,7 +27394,7 @@
         <v>231</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="J281" s="11">
         <v>46374.125</v>
@@ -27469,7 +27465,7 @@
         <v>34</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D282" s="0" t="s">
         <v>51</v>
@@ -27484,7 +27480,7 @@
         <v>74</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="J282" s="11"/>
       <c r="K282" s="0" t="s">
@@ -27553,13 +27549,13 @@
         <v>49</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D283" s="0" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F283" s="0" t="s">
         <v>169</v>
@@ -27636,7 +27632,7 @@
         <v>49</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D284" s="0" t="s">
         <v>304</v>
@@ -27722,7 +27718,7 @@
         <v>49</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D285" s="0" t="s">
         <v>304</v>
@@ -27808,7 +27804,7 @@
         <v>34</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D286" s="0" t="s">
         <v>123</v>
@@ -27892,7 +27888,7 @@
         <v>34</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D287" s="0" t="s">
         <v>123</v>
@@ -27976,7 +27972,7 @@
         <v>34</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D288" s="0" t="s">
         <v>72</v>
@@ -28060,7 +28056,7 @@
         <v>34</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D289" s="0" t="s">
         <v>72</v>
@@ -28144,7 +28140,7 @@
         <v>34</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D290" s="0" t="s">
         <v>51</v>
@@ -28228,13 +28224,13 @@
         <v>61</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D291" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F291" s="0" t="s">
         <v>168</v>
@@ -28243,7 +28239,7 @@
         <v>168</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="J291" s="11">
         <v>46373.125</v>
@@ -28314,7 +28310,7 @@
         <v>61</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D292" s="0" t="s">
         <v>36</v>
@@ -28329,7 +28325,7 @@
         <v>38</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="J292" s="11">
         <v>46373.125</v>
@@ -28400,7 +28396,7 @@
         <v>61</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D293" s="0" t="s">
         <v>36</v>
@@ -28415,7 +28411,7 @@
         <v>38</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="J293" s="11">
         <v>46373.125</v>
@@ -28486,13 +28482,13 @@
         <v>34</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D294" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F294" s="0" t="s">
         <v>168</v>
@@ -28501,7 +28497,7 @@
         <v>169</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="J294" s="11"/>
       <c r="K294" s="0" t="s">
@@ -28570,7 +28566,7 @@
         <v>34</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D295" s="0" t="s">
         <v>77</v>
@@ -28585,7 +28581,7 @@
         <v>137</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="J295" s="11"/>
       <c r="K295" s="0" t="s">
@@ -28654,13 +28650,13 @@
         <v>34</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D296" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F296" s="0" t="s">
         <v>149</v>
@@ -28669,7 +28665,7 @@
         <v>149</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="J296" s="11">
         <v>46365.125</v>
@@ -28740,13 +28736,13 @@
         <v>34</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D297" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F297" s="0" t="s">
         <v>149</v>
@@ -28755,7 +28751,7 @@
         <v>149</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="J297" s="11"/>
       <c r="K297" s="0" t="s">
@@ -28824,7 +28820,7 @@
         <v>61</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D298" s="0" t="s">
         <v>162</v>
@@ -28839,7 +28835,7 @@
         <v>93</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="J298" s="11">
         <v>46373.125</v>
@@ -28910,13 +28906,13 @@
         <v>643</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D299" s="0" t="s">
         <v>626</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F299" s="0" t="s">
         <v>134</v>
@@ -28925,7 +28921,7 @@
         <v>326</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="J299" s="11">
         <v>46372.125</v>
@@ -28996,7 +28992,7 @@
         <v>61</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D300" s="0" t="s">
         <v>249</v>
@@ -29080,7 +29076,7 @@
         <v>49</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D301" s="0" t="s">
         <v>259</v>
@@ -29166,13 +29162,13 @@
         <v>61</v>
       </c>
       <c r="C302" s="0" t="s">
+        <v>721</v>
+      </c>
+      <c r="D302" s="0" t="s">
+        <v>722</v>
+      </c>
+      <c r="E302" s="0" t="s">
         <v>723</v>
-      </c>
-      <c r="D302" s="0" t="s">
-        <v>724</v>
-      </c>
-      <c r="E302" s="0" t="s">
-        <v>725</v>
       </c>
       <c r="F302" s="0" t="s">
         <v>74</v>
@@ -29252,7 +29248,7 @@
         <v>61</v>
       </c>
       <c r="C303" s="0" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D303" s="0" t="s">
         <v>259</v>
@@ -29336,7 +29332,7 @@
         <v>61</v>
       </c>
       <c r="C304" s="0" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D304" s="0" t="s">
         <v>259</v>
@@ -29422,7 +29418,7 @@
         <v>61</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D305" s="0" t="s">
         <v>412</v>
@@ -29437,7 +29433,7 @@
         <v>326</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="J305" s="11">
         <v>46361.125</v>
@@ -29508,7 +29504,7 @@
         <v>61</v>
       </c>
       <c r="C306" s="0" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D306" s="0" t="s">
         <v>259</v>
@@ -29523,7 +29519,7 @@
         <v>60</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="J306" s="11">
         <v>46326.125</v>
@@ -29532,7 +29528,7 @@
         <v>114</v>
       </c>
       <c r="L306" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="M306" s="0" t="s">
         <v>39</v>
@@ -29594,10 +29590,10 @@
         <v>61</v>
       </c>
       <c r="C307" s="0" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D307" s="0" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E307" s="0" t="s">
         <v>102</v>
@@ -29681,7 +29677,7 @@
         <v>61</v>
       </c>
       <c r="C308" s="0" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D308" s="0" t="s">
         <v>249</v>
@@ -29767,7 +29763,7 @@
         <v>49</v>
       </c>
       <c r="C309" s="0" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D309" s="0" t="s">
         <v>259</v>
@@ -29853,13 +29849,13 @@
         <v>61</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D310" s="0" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="F310" s="0" t="s">
         <v>74</v>
@@ -29939,7 +29935,7 @@
         <v>61</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D311" s="0" t="s">
         <v>259</v>
@@ -30025,7 +30021,7 @@
         <v>61</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D312" s="0" t="s">
         <v>259</v>
@@ -30111,7 +30107,7 @@
         <v>61</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D313" s="0" t="s">
         <v>412</v>
@@ -30126,7 +30122,7 @@
         <v>326</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="J313" s="11">
         <v>46359.125</v>
@@ -30197,7 +30193,7 @@
         <v>61</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D314" s="0" t="s">
         <v>259</v>
@@ -30212,7 +30208,7 @@
         <v>60</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="J314" s="11">
         <v>46326.125</v>
@@ -30221,7 +30217,7 @@
         <v>114</v>
       </c>
       <c r="L314" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="M314" s="0" t="s">
         <v>39</v>
@@ -30283,10 +30279,10 @@
         <v>61</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D315" s="0" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E315" s="0" t="s">
         <v>97</v>
@@ -30370,7 +30366,7 @@
         <v>61</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D316" s="0" t="s">
         <v>51</v>
@@ -30385,7 +30381,7 @@
         <v>169</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="J316" s="11"/>
       <c r="K316" s="0" t="s">
@@ -30454,7 +30450,7 @@
         <v>61</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D317" s="0" t="s">
         <v>51</v>
@@ -30540,10 +30536,10 @@
         <v>61</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D318" s="0" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E318" s="0" t="s">
         <v>228</v>
@@ -30626,7 +30622,7 @@
         <v>61</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D319" s="0" t="s">
         <v>249</v>
@@ -30710,7 +30706,7 @@
         <v>49</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D320" s="0" t="s">
         <v>478</v>
@@ -30725,7 +30721,7 @@
         <v>93</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="J320" s="11">
         <v>46370.125</v>
@@ -30796,7 +30792,7 @@
         <v>34</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D321" s="0" t="s">
         <v>162</v>
@@ -30811,7 +30807,7 @@
         <v>243</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="J321" s="11">
         <v>46367.125</v>
@@ -30879,7 +30875,7 @@
         <v>49</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D322" s="0" t="s">
         <v>311</v>
@@ -30894,7 +30890,7 @@
         <v>65</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="J322" s="11">
         <v>46415.125</v>
@@ -30965,7 +30961,7 @@
         <v>49</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D323" s="0" t="s">
         <v>313</v>
@@ -30980,7 +30976,7 @@
         <v>65</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="J323" s="11">
         <v>46415.125</v>
@@ -31051,13 +31047,13 @@
         <v>49</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E324" s="0" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="F324" s="0" t="s">
         <v>169</v>
@@ -31066,7 +31062,7 @@
         <v>169</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="J324" s="11">
         <v>46358.125</v>
@@ -31137,13 +31133,13 @@
         <v>49</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D325" s="0" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E325" s="0" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F325" s="0" t="s">
         <v>65</v>
@@ -31152,7 +31148,7 @@
         <v>65</v>
       </c>
       <c r="H325" s="0" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="J325" s="11">
         <v>46358.125</v>
@@ -31223,7 +31219,7 @@
         <v>49</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D326" s="0" t="s">
         <v>412</v>
@@ -31309,7 +31305,7 @@
         <v>49</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D327" s="0" t="s">
         <v>412</v>
@@ -31395,7 +31391,7 @@
         <v>61</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D328" s="0" t="s">
         <v>51</v>
@@ -31410,7 +31406,7 @@
         <v>74</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J328" s="11"/>
       <c r="K328" s="0" t="s">
@@ -31479,7 +31475,7 @@
         <v>61</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D329" s="0" t="s">
         <v>36</v>
@@ -31494,7 +31490,7 @@
         <v>326</v>
       </c>
       <c r="H329" s="0" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J329" s="11">
         <v>46373.125</v>
@@ -31565,7 +31561,7 @@
         <v>61</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D330" s="0" t="s">
         <v>36</v>
@@ -31580,7 +31576,7 @@
         <v>326</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J330" s="11">
         <v>46373.125</v>
@@ -31651,7 +31647,7 @@
         <v>61</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D331" s="0" t="s">
         <v>249</v>
@@ -31737,7 +31733,7 @@
         <v>61</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D332" s="0" t="s">
         <v>249</v>
@@ -31823,7 +31819,7 @@
         <v>61</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D333" s="0" t="s">
         <v>249</v>
@@ -31909,7 +31905,7 @@
         <v>61</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D334" s="0" t="s">
         <v>249</v>
@@ -31995,13 +31991,13 @@
         <v>49</v>
       </c>
       <c r="C335" s="0" t="s">
+        <v>769</v>
+      </c>
+      <c r="D335" s="0" t="s">
+        <v>770</v>
+      </c>
+      <c r="E335" s="0" t="s">
         <v>771</v>
-      </c>
-      <c r="D335" s="0" t="s">
-        <v>772</v>
-      </c>
-      <c r="E335" s="0" t="s">
-        <v>773</v>
       </c>
       <c r="F335" s="0" t="s">
         <v>168</v>
@@ -32010,7 +32006,7 @@
         <v>168</v>
       </c>
       <c r="H335" s="0" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="J335" s="11">
         <v>46421.125</v>
@@ -32081,13 +32077,13 @@
         <v>49</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E336" s="0" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="F336" s="0" t="s">
         <v>168</v>
@@ -32096,7 +32092,7 @@
         <v>168</v>
       </c>
       <c r="H336" s="0" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="J336" s="11">
         <v>46421.125</v>
@@ -32167,7 +32163,7 @@
         <v>61</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D337" s="0" t="s">
         <v>249</v>
@@ -32251,7 +32247,7 @@
         <v>61</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D338" s="0" t="s">
         <v>249</v>
@@ -32335,7 +32331,7 @@
         <v>61</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D339" s="0" t="s">
         <v>259</v>
@@ -32350,7 +32346,7 @@
         <v>93</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="J339" s="11">
         <v>46373.125</v>
@@ -32421,7 +32417,7 @@
         <v>61</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D340" s="0" t="s">
         <v>259</v>
@@ -32436,7 +32432,7 @@
         <v>93</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="J340" s="11">
         <v>46373.125</v>
@@ -32507,13 +32503,13 @@
         <v>226</v>
       </c>
       <c r="C341" s="0" t="s">
+        <v>779</v>
+      </c>
+      <c r="D341" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="E341" s="0" t="s">
         <v>781</v>
-      </c>
-      <c r="D341" s="0" t="s">
-        <v>782</v>
-      </c>
-      <c r="E341" s="0" t="s">
-        <v>783</v>
       </c>
       <c r="F341" s="0" t="s">
         <v>149</v>
@@ -32587,7 +32583,7 @@
         <v>61</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D342" s="0" t="s">
         <v>72</v>
@@ -32674,7 +32670,7 @@
         <v>61</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D343" s="0" t="s">
         <v>412</v>
@@ -32758,7 +32754,7 @@
         <v>34</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D344" s="0" t="s">
         <v>77</v>
@@ -32773,7 +32769,7 @@
         <v>137</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J344" s="11">
         <v>46366.125</v>
@@ -32844,7 +32840,7 @@
         <v>34</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D345" s="0" t="s">
         <v>96</v>
@@ -32859,14 +32855,14 @@
         <v>74</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J345" s="11"/>
       <c r="K345" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L345" s="0" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="M345" s="0" t="s">
         <v>39</v>
@@ -32928,7 +32924,7 @@
         <v>34</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D346" s="0" t="s">
         <v>96</v>
@@ -32943,7 +32939,7 @@
         <v>74</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J346" s="11"/>
       <c r="K346" s="0" t="s">
@@ -33012,7 +33008,7 @@
         <v>49</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D347" s="0" t="s">
         <v>304</v>
@@ -33098,13 +33094,13 @@
         <v>49</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E348" s="0" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F348" s="0" t="s">
         <v>149</v>
@@ -33181,7 +33177,7 @@
         <v>49</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D349" s="0" t="s">
         <v>304</v>
@@ -33267,7 +33263,7 @@
         <v>49</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D350" s="0" t="s">
         <v>304</v>
@@ -33353,7 +33349,7 @@
         <v>34</v>
       </c>
       <c r="C351" s="0" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D351" s="0" t="s">
         <v>162</v>
@@ -33368,7 +33364,7 @@
         <v>524</v>
       </c>
       <c r="H351" s="0" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="J351" s="11"/>
       <c r="K351" s="0" t="s">
@@ -33437,7 +33433,7 @@
         <v>34</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D352" s="0" t="s">
         <v>140</v>
@@ -33452,7 +33448,7 @@
         <v>439</v>
       </c>
       <c r="H352" s="0" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="J352" s="11"/>
       <c r="K352" s="0" t="s">
@@ -33521,7 +33517,7 @@
         <v>61</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D353" s="0" t="s">
         <v>162</v>
@@ -33536,7 +33532,7 @@
         <v>54</v>
       </c>
       <c r="H353" s="0" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="J353" s="11">
         <v>46373.125</v>
@@ -33607,7 +33603,7 @@
         <v>61</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D354" s="0" t="s">
         <v>249</v>
@@ -33622,7 +33618,7 @@
         <v>326</v>
       </c>
       <c r="H354" s="0" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="J354" s="11">
         <v>46373.125</v>
@@ -33693,13 +33689,13 @@
         <v>226</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D355" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E355" s="0" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F355" s="0" t="s">
         <v>502</v>
@@ -33773,7 +33769,7 @@
         <v>61</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D356" s="0" t="s">
         <v>162</v>
@@ -33788,7 +33784,7 @@
         <v>54</v>
       </c>
       <c r="H356" s="0" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="J356" s="11">
         <v>46373.125</v>
@@ -33859,13 +33855,13 @@
         <v>61</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D357" s="0" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E357" s="0" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="F357" s="0" t="s">
         <v>60</v>
@@ -33874,7 +33870,7 @@
         <v>134</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="J357" s="11">
         <v>46373.125</v>
@@ -33948,7 +33944,7 @@
         <v>61</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D358" s="0" t="s">
         <v>51</v>
@@ -33963,7 +33959,7 @@
         <v>131</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="J358" s="11"/>
       <c r="K358" s="0" t="s">
@@ -34026,19 +34022,19 @@
     </row>
     <row r="359">
       <c r="A359" s="0" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B359" s="0" t="s">
+        <v>807</v>
+      </c>
+      <c r="C359" s="0" t="s">
+        <v>808</v>
+      </c>
+      <c r="D359" s="0" t="s">
         <v>809</v>
       </c>
-      <c r="C359" s="0" t="s">
-        <v>810</v>
-      </c>
-      <c r="D359" s="0" t="s">
-        <v>811</v>
-      </c>
       <c r="E359" s="0" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F359" s="0" t="s">
         <v>293</v>
@@ -34077,7 +34073,7 @@
         <v>45</v>
       </c>
       <c r="AC359" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="AD359" s="11">
         <v>45847.61793511574</v>
@@ -34103,19 +34099,19 @@
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B360" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D360" s="0" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E360" s="0" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F360" s="0" t="s">
         <v>209</v>
@@ -34186,19 +34182,19 @@
     </row>
     <row r="361">
       <c r="A361" s="0" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B361" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D361" s="0" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E361" s="0" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F361" s="0" t="s">
         <v>208</v>
@@ -34269,19 +34265,19 @@
     </row>
     <row r="362">
       <c r="A362" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B362" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D362" s="0" t="s">
         <v>412</v>
       </c>
       <c r="E362" s="0" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="F362" s="0" t="s">
         <v>134</v>
@@ -34352,19 +34348,19 @@
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B363" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D363" s="0" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E363" s="0" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="F363" s="0" t="s">
         <v>327</v>
@@ -34435,19 +34431,19 @@
     </row>
     <row r="364">
       <c r="A364" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B364" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D364" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E364" s="0" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="F364" s="0" t="s">
         <v>208</v>
@@ -34524,13 +34520,13 @@
         <v>621</v>
       </c>
       <c r="C365" s="0" t="s">
+        <v>821</v>
+      </c>
+      <c r="D365" s="0" t="s">
+        <v>822</v>
+      </c>
+      <c r="E365" s="0" t="s">
         <v>823</v>
-      </c>
-      <c r="D365" s="0" t="s">
-        <v>824</v>
-      </c>
-      <c r="E365" s="0" t="s">
-        <v>825</v>
       </c>
       <c r="F365" s="0" t="s">
         <v>168</v>
@@ -34604,7 +34600,7 @@
         <v>34</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D366" s="0" t="s">
         <v>63</v>
@@ -34688,7 +34684,7 @@
         <v>49</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D367" s="0" t="s">
         <v>228</v>
@@ -34771,7 +34767,7 @@
         <v>49</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D368" s="0" t="s">
         <v>77</v>
@@ -34854,7 +34850,7 @@
         <v>61</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D369" s="0" t="s">
         <v>51</v>
@@ -34869,7 +34865,7 @@
         <v>79</v>
       </c>
       <c r="H369" s="0" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="J369" s="11">
         <v>46356.125</v>
@@ -34943,13 +34939,13 @@
         <v>61</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D370" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E370" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F370" s="0" t="s">
         <v>149</v>
@@ -34958,7 +34954,7 @@
         <v>149</v>
       </c>
       <c r="H370" s="0" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="J370" s="11">
         <v>46356.125</v>
@@ -35032,7 +35028,7 @@
         <v>226</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D371" s="0" t="s">
         <v>77</v>
@@ -35047,7 +35043,7 @@
         <v>184</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="J371" s="11">
         <v>46392.125</v>
@@ -35112,16 +35108,16 @@
     </row>
     <row r="372">
       <c r="A372" s="0" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B372" s="0" t="s">
         <v>226</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D372" s="0" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E372" s="0" t="s">
         <v>141</v>
@@ -35133,7 +35129,7 @@
         <v>439</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="J372" s="11">
         <v>46392.125</v>
@@ -35198,7 +35194,7 @@
         <v>61</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D373" s="0" t="s">
         <v>162</v>
@@ -35213,7 +35209,7 @@
         <v>339</v>
       </c>
       <c r="H373" s="0" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J373" s="11">
         <v>46326.125</v>
@@ -35222,7 +35218,7 @@
         <v>114</v>
       </c>
       <c r="L373" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="M373" s="0" t="s">
         <v>39</v>
@@ -35284,7 +35280,7 @@
         <v>34</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D374" s="0" t="s">
         <v>77</v>
@@ -35299,7 +35295,7 @@
         <v>54</v>
       </c>
       <c r="H374" s="0" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="J374" s="11"/>
       <c r="K374" s="0" t="s">
@@ -35368,7 +35364,7 @@
         <v>34</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D375" s="0" t="s">
         <v>36</v>
@@ -35383,7 +35379,7 @@
         <v>60</v>
       </c>
       <c r="H375" s="0" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="J375" s="11"/>
       <c r="K375" s="0" t="s">
@@ -35452,7 +35448,7 @@
         <v>61</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D376" s="0" t="s">
         <v>51</v>
@@ -35530,19 +35526,19 @@
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B377" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D377" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E377" s="0" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="F377" s="0" t="s">
         <v>208</v>
@@ -35551,7 +35547,7 @@
         <v>209</v>
       </c>
       <c r="H377" s="0" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="J377" s="11">
         <v>46326.125</v>
@@ -35560,7 +35556,7 @@
         <v>114</v>
       </c>
       <c r="L377" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="M377" s="0" t="s">
         <v>39</v>
@@ -35622,13 +35618,13 @@
         <v>643</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D378" s="0" t="s">
         <v>626</v>
       </c>
       <c r="E378" s="0" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F378" s="0" t="s">
         <v>134</v>
@@ -35637,7 +35633,7 @@
         <v>326</v>
       </c>
       <c r="H378" s="0" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="J378" s="11">
         <v>46326.125</v>
@@ -35646,7 +35642,7 @@
         <v>114</v>
       </c>
       <c r="L378" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="M378" s="0" t="s">
         <v>39</v>
@@ -35702,19 +35698,19 @@
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B379" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E379" s="0" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F379" s="0" t="s">
         <v>209</v>
@@ -35723,7 +35719,7 @@
         <v>209</v>
       </c>
       <c r="H379" s="0" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="J379" s="11">
         <v>46348.125</v>
@@ -35794,13 +35790,13 @@
         <v>643</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E380" s="0" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="F380" s="0" t="s">
         <v>134</v>
@@ -35809,7 +35805,7 @@
         <v>326</v>
       </c>
       <c r="H380" s="0" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="J380" s="11">
         <v>46341.125</v>
@@ -35818,7 +35814,7 @@
         <v>114</v>
       </c>
       <c r="L380" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="M380" s="0" t="s">
         <v>39</v>
@@ -35880,7 +35876,7 @@
         <v>49</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>198</v>
@@ -35963,10 +35959,10 @@
         <v>642</v>
       </c>
       <c r="B382" s="0" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D382" s="0" t="s">
         <v>63</v>
@@ -36020,7 +36016,7 @@
         <v>44</v>
       </c>
       <c r="AC382" s="0" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="AD382" s="11">
         <v>46037.467388136574</v>
@@ -36049,16 +36045,16 @@
         <v>642</v>
       </c>
       <c r="B383" s="0" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C383" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="D383" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="E383" s="0" t="s">
         <v>855</v>
-      </c>
-      <c r="D383" s="0" t="s">
-        <v>856</v>
-      </c>
-      <c r="E383" s="0" t="s">
-        <v>857</v>
       </c>
       <c r="F383" s="0" t="s">
         <v>60</v>
@@ -36067,14 +36063,14 @@
         <v>134</v>
       </c>
       <c r="H383" s="0" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="J383" s="11"/>
       <c r="K383" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L383" s="0" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="M383" s="0" t="s">
         <v>39</v>
@@ -36095,7 +36091,7 @@
         <v>44</v>
       </c>
       <c r="AC383" s="0" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="AD383" s="11">
         <v>46038.63016152778</v>
@@ -36127,19 +36123,19 @@
         <v>49</v>
       </c>
       <c r="C384" s="0" t="s">
+        <v>857</v>
+      </c>
+      <c r="D384" s="0" t="s">
+        <v>858</v>
+      </c>
+      <c r="E384" s="0" t="s">
+        <v>858</v>
+      </c>
+      <c r="F384" s="0" t="s">
         <v>859</v>
       </c>
-      <c r="D384" s="0" t="s">
-        <v>860</v>
-      </c>
-      <c r="E384" s="0" t="s">
-        <v>860</v>
-      </c>
-      <c r="F384" s="0" t="s">
-        <v>861</v>
-      </c>
       <c r="G384" s="0" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="H384" s="0" t="s">
         <v>132</v>
@@ -36207,25 +36203,25 @@
     </row>
     <row r="385">
       <c r="A385" s="0" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B385" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D385" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E385" s="0" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F385" s="0" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G385" s="0" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="J385" s="11">
         <v>46409.125</v>
@@ -36258,7 +36254,7 @@
         <v>45</v>
       </c>
       <c r="AC385" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="AD385" s="11">
         <v>46051.66783503472</v>
@@ -36284,25 +36280,25 @@
     </row>
     <row r="386">
       <c r="A386" s="0" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B386" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D386" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F386" s="0" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G386" s="0" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="J386" s="11">
         <v>46413.125</v>
@@ -36332,7 +36328,7 @@
         <v>45</v>
       </c>
       <c r="AC386" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="AD386" s="11">
         <v>46052.455825081015</v>
@@ -36364,7 +36360,7 @@
         <v>34</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D387" s="0" t="s">
         <v>51</v>
@@ -36448,7 +36444,7 @@
         <v>34</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="D388" s="0" t="s">
         <v>36</v>
@@ -36534,13 +36530,13 @@
         <v>61</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E389" s="0" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="F389" s="0" t="s">
         <v>200</v>
@@ -36553,7 +36549,7 @@
         <v>40</v>
       </c>
       <c r="L389" s="0" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="M389" s="0" t="s">
         <v>39</v>
@@ -36611,13 +36607,13 @@
         <v>61</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E390" s="0" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="F390" s="0" t="s">
         <v>200</v>
@@ -36688,25 +36684,25 @@
     </row>
     <row r="391">
       <c r="A391" s="0" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B391" s="0" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E391" s="0" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F391" s="0" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G391" s="0" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="J391" s="11">
         <v>46401.125</v>
@@ -36739,7 +36735,7 @@
         <v>45</v>
       </c>
       <c r="AC391" s="0" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="AD391" s="11">
         <v>46104.56253545139</v>
@@ -36765,19 +36761,19 @@
     </row>
     <row r="392">
       <c r="A392" s="0" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B392" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E392" s="0" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F392" s="0" t="s">
         <v>209</v>
@@ -36786,7 +36782,7 @@
         <v>209</v>
       </c>
       <c r="H392" s="0" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="J392" s="11">
         <v>46372.125</v>
@@ -36857,13 +36853,13 @@
         <v>643</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="F393" s="0" t="s">
         <v>327</v>
@@ -36872,7 +36868,7 @@
         <v>327</v>
       </c>
       <c r="H393" s="0" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="J393" s="11">
         <v>46372.125</v>
@@ -36943,13 +36939,13 @@
         <v>61</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E394" s="0" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="F394" s="0" t="s">
         <v>60</v>
@@ -36962,7 +36958,7 @@
         <v>40</v>
       </c>
       <c r="L394" s="0" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="M394" s="0" t="s">
         <v>39</v>
@@ -37018,19 +37014,19 @@
     </row>
     <row r="395">
       <c r="A395" s="0" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B395" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E395" s="0" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F395" s="0" t="s">
         <v>209</v>
@@ -37039,7 +37035,7 @@
         <v>209</v>
       </c>
       <c r="H395" s="0" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="J395" s="11">
         <v>46362.125</v>
@@ -37110,7 +37106,7 @@
         <v>34</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>198</v>
@@ -37196,13 +37192,13 @@
         <v>49</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D397" s="0" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="F397" s="0" t="s">
         <v>243</v>
@@ -37211,7 +37207,7 @@
         <v>243</v>
       </c>
       <c r="H397" s="0" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="J397" s="11">
         <v>46413.125</v>
@@ -37282,13 +37278,13 @@
         <v>49</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D398" s="0" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="F398" s="0" t="s">
         <v>53</v>
@@ -37297,7 +37293,7 @@
         <v>54</v>
       </c>
       <c r="H398" s="0" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="J398" s="11">
         <v>46357.125</v>
@@ -37368,7 +37364,7 @@
         <v>34</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>162</v>
@@ -37383,7 +37379,7 @@
         <v>54</v>
       </c>
       <c r="H399" s="0" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="J399" s="11">
         <v>46361.125</v>
@@ -37454,7 +37450,7 @@
         <v>34</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>51</v>
@@ -37469,7 +37465,7 @@
         <v>150</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="J400" s="11">
         <v>46365.125</v>
@@ -37540,7 +37536,7 @@
         <v>34</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>51</v>
@@ -37555,7 +37551,7 @@
         <v>134</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="J401" s="11">
         <v>46365.125</v>
@@ -37626,7 +37622,7 @@
         <v>34</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>36</v>
@@ -37641,7 +37637,7 @@
         <v>134</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="J402" s="11"/>
       <c r="K402" s="0" t="s">
@@ -37710,13 +37706,13 @@
         <v>49</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="D403" s="0" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E403" s="0" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="F403" s="0" t="s">
         <v>54</v>
@@ -37725,7 +37721,7 @@
         <v>54</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="J403" s="11">
         <v>46365.125</v>
@@ -37796,7 +37792,7 @@
         <v>49</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>322</v>
@@ -37811,7 +37807,7 @@
         <v>134</v>
       </c>
       <c r="H404" s="0" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="J404" s="11">
         <v>46362.125</v>
@@ -37882,13 +37878,13 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E405" s="0" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="F405" s="0" t="s">
         <v>65</v>
@@ -37968,7 +37964,7 @@
         <v>34</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>36</v>
@@ -38054,7 +38050,7 @@
         <v>34</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>36</v>
@@ -38140,13 +38136,13 @@
         <v>34</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E408" s="0" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="F408" s="0" t="s">
         <v>439</v>
@@ -38155,7 +38151,7 @@
         <v>439</v>
       </c>
       <c r="H408" s="0" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="J408" s="11"/>
       <c r="K408" s="0" t="s">
@@ -38224,13 +38220,13 @@
         <v>34</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E409" s="0" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="F409" s="0" t="s">
         <v>134</v>
@@ -38239,7 +38235,7 @@
         <v>134</v>
       </c>
       <c r="H409" s="0" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="J409" s="11"/>
       <c r="K409" s="0" t="s">
@@ -38308,7 +38304,7 @@
         <v>34</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>72</v>
@@ -38395,7 +38391,7 @@
         <v>34</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>51</v>
@@ -38410,7 +38406,7 @@
         <v>339</v>
       </c>
       <c r="H411" s="0" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="J411" s="11">
         <v>46356.125</v>
@@ -38484,13 +38480,13 @@
         <v>34</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>140</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="F412" s="0" t="s">
         <v>142</v>
@@ -38499,7 +38495,7 @@
         <v>142</v>
       </c>
       <c r="H412" s="0" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="J412" s="11"/>
       <c r="K412" s="0" t="s">
@@ -38571,13 +38567,13 @@
         <v>34</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E413" s="0" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="F413" s="0" t="s">
         <v>93</v>
@@ -38586,7 +38582,7 @@
         <v>93</v>
       </c>
       <c r="H413" s="0" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="J413" s="11"/>
       <c r="K413" s="0" t="s">
@@ -38658,7 +38654,7 @@
         <v>34</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>123</v>
@@ -38673,7 +38669,7 @@
         <v>60</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="J414" s="11"/>
       <c r="K414" s="0" t="s">
@@ -38742,7 +38738,7 @@
         <v>34</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>123</v>
@@ -38757,7 +38753,7 @@
         <v>60</v>
       </c>
       <c r="H415" s="0" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="J415" s="11"/>
       <c r="K415" s="0" t="s">
@@ -38826,13 +38822,13 @@
         <v>49</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="D416" s="0" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="E416" s="0" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="F416" s="0" t="s">
         <v>200</v>
@@ -38909,7 +38905,7 @@
         <v>34</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>63</v>
@@ -38995,7 +38991,7 @@
         <v>34</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>36</v>
@@ -39010,14 +39006,14 @@
         <v>38</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="J418" s="11"/>
       <c r="K418" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L418" s="0" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="M418" s="0" t="s">
         <v>39</v>
@@ -39082,7 +39078,7 @@
         <v>34</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>36</v>
@@ -39097,14 +39093,14 @@
         <v>38</v>
       </c>
       <c r="H419" s="0" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="J419" s="11"/>
       <c r="K419" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L419" s="0" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="M419" s="0" t="s">
         <v>39</v>
@@ -39169,13 +39165,13 @@
         <v>49</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D420" s="0" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="E420" s="0" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="F420" s="0" t="s">
         <v>65</v>
@@ -39252,7 +39248,7 @@
         <v>49</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>322</v>
@@ -39335,13 +39331,13 @@
         <v>34</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>315</v>
       </c>
       <c r="E422" s="0" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="F422" s="0" t="s">
         <v>93</v>
@@ -39350,14 +39346,14 @@
         <v>38</v>
       </c>
       <c r="H422" s="0" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="J422" s="11"/>
       <c r="K422" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L422" s="0" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="M422" s="0" t="s">
         <v>39</v>
@@ -39422,7 +39418,7 @@
         <v>49</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>388</v>
@@ -39505,13 +39501,13 @@
         <v>49</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="D424" s="0" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="E424" s="0" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="F424" s="0" t="s">
         <v>150</v>
@@ -39588,7 +39584,7 @@
         <v>61</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>51</v>
@@ -39603,7 +39599,7 @@
         <v>168</v>
       </c>
       <c r="H425" s="0" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="J425" s="11"/>
       <c r="K425" s="0" t="s">
@@ -39672,13 +39668,13 @@
         <v>61</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E426" s="0" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="F426" s="0" t="s">
         <v>332</v>
@@ -39687,7 +39683,7 @@
         <v>332</v>
       </c>
       <c r="H426" s="0" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="J426" s="11">
         <v>46373.125</v>
@@ -39758,7 +39754,7 @@
         <v>61</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>77</v>
@@ -39773,7 +39769,7 @@
         <v>524</v>
       </c>
       <c r="H427" s="0" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="J427" s="11"/>
       <c r="K427" s="0" t="s">
@@ -39845,13 +39841,13 @@
         <v>61</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E428" s="0" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="F428" s="0" t="s">
         <v>169</v>
@@ -39934,7 +39930,7 @@
         <v>61</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>77</v>
@@ -39949,7 +39945,7 @@
         <v>54</v>
       </c>
       <c r="H429" s="0" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="J429" s="11">
         <v>46373.125</v>
@@ -40020,13 +40016,13 @@
         <v>61</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E430" s="0" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="F430" s="0" t="s">
         <v>257</v>
@@ -40035,7 +40031,7 @@
         <v>257</v>
       </c>
       <c r="H430" s="0" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="J430" s="11"/>
       <c r="K430" s="0" t="s">
@@ -40104,7 +40100,7 @@
         <v>61</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>51</v>
@@ -40119,7 +40115,7 @@
         <v>150</v>
       </c>
       <c r="H431" s="0" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="J431" s="11">
         <v>46373.125</v>
@@ -40190,13 +40186,13 @@
         <v>61</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="D432" s="0" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E432" s="0" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="F432" s="0" t="s">
         <v>209</v>
@@ -40205,7 +40201,7 @@
         <v>209</v>
       </c>
       <c r="H432" s="0" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="J432" s="11"/>
       <c r="K432" s="0" t="s">
@@ -40274,7 +40270,7 @@
         <v>61</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="D433" s="0" t="s">
         <v>249</v>
@@ -40289,7 +40285,7 @@
         <v>327</v>
       </c>
       <c r="H433" s="0" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="J433" s="11"/>
       <c r="K433" s="0" t="s">
@@ -40358,7 +40354,7 @@
         <v>61</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>259</v>
@@ -40373,7 +40369,7 @@
         <v>93</v>
       </c>
       <c r="H434" s="0" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="J434" s="11"/>
       <c r="K434" s="0" t="s">
@@ -40442,13 +40438,13 @@
         <v>61</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>259</v>
       </c>
       <c r="E435" s="0" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="F435" s="0" t="s">
         <v>168</v>
@@ -40457,7 +40453,7 @@
         <v>168</v>
       </c>
       <c r="H435" s="0" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="J435" s="11"/>
       <c r="K435" s="0" t="s">
@@ -40529,7 +40525,7 @@
         <v>61</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>249</v>
@@ -40616,13 +40612,13 @@
         <v>61</v>
       </c>
       <c r="C437" s="0" t="s">
+        <v>960</v>
+      </c>
+      <c r="D437" s="0" t="s">
+        <v>961</v>
+      </c>
+      <c r="E437" s="0" t="s">
         <v>962</v>
-      </c>
-      <c r="D437" s="0" t="s">
-        <v>963</v>
-      </c>
-      <c r="E437" s="0" t="s">
-        <v>964</v>
       </c>
       <c r="F437" s="0" t="s">
         <v>294</v>
@@ -40702,7 +40698,7 @@
         <v>61</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>259</v>
@@ -40717,7 +40713,7 @@
         <v>326</v>
       </c>
       <c r="H438" s="0" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="J438" s="11"/>
       <c r="K438" s="0" t="s">
@@ -40789,7 +40785,7 @@
         <v>61</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>412</v>
@@ -40804,7 +40800,7 @@
         <v>169</v>
       </c>
       <c r="H439" s="0" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="J439" s="11">
         <v>46373.125</v>
@@ -40875,7 +40871,7 @@
         <v>61</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="D440" s="0" t="s">
         <v>259</v>
@@ -40959,7 +40955,7 @@
         <v>61</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>259</v>
@@ -40974,7 +40970,7 @@
         <v>54</v>
       </c>
       <c r="H441" s="0" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="J441" s="11"/>
       <c r="K441" s="0" t="s">
@@ -41043,7 +41039,7 @@
         <v>61</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>412</v>
@@ -41058,7 +41054,7 @@
         <v>327</v>
       </c>
       <c r="H442" s="0" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="J442" s="11">
         <v>46373.125</v>
@@ -41129,7 +41125,7 @@
         <v>61</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>259</v>
@@ -41144,7 +41140,7 @@
         <v>74</v>
       </c>
       <c r="H443" s="0" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="J443" s="11"/>
       <c r="K443" s="0" t="s">
@@ -41213,7 +41209,7 @@
         <v>61</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>259</v>
@@ -41228,7 +41224,7 @@
         <v>326</v>
       </c>
       <c r="H444" s="0" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="J444" s="11"/>
       <c r="K444" s="0" t="s">
@@ -41300,7 +41296,7 @@
         <v>61</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>412</v>
@@ -41315,7 +41311,7 @@
         <v>169</v>
       </c>
       <c r="H445" s="0" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="J445" s="11">
         <v>46373.125</v>
@@ -41386,7 +41382,7 @@
         <v>61</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>259</v>
@@ -41470,7 +41466,7 @@
         <v>61</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>162</v>
@@ -41485,7 +41481,7 @@
         <v>176</v>
       </c>
       <c r="H447" s="0" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="J447" s="11"/>
       <c r="K447" s="0" t="s">
@@ -41554,13 +41550,13 @@
         <v>61</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E448" s="0" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F448" s="0" t="s">
         <v>502</v>
@@ -41569,7 +41565,7 @@
         <v>502</v>
       </c>
       <c r="H448" s="0" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="J448" s="11">
         <v>46373.125</v>
@@ -41640,7 +41636,7 @@
         <v>61</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>162</v>
@@ -41655,7 +41651,7 @@
         <v>518</v>
       </c>
       <c r="H449" s="0" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="J449" s="11"/>
       <c r="K449" s="0" t="s">
@@ -41724,13 +41720,13 @@
         <v>61</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E450" s="0" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="F450" s="0" t="s">
         <v>332</v>
@@ -41739,7 +41735,7 @@
         <v>332</v>
       </c>
       <c r="H450" s="0" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="J450" s="11"/>
       <c r="K450" s="0" t="s">
@@ -41811,7 +41807,7 @@
         <v>61</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>162</v>
@@ -41826,14 +41822,14 @@
         <v>332</v>
       </c>
       <c r="H451" s="0" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="J451" s="11"/>
       <c r="K451" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L451" s="0" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="M451" s="0" t="s">
         <v>39</v>
@@ -41889,25 +41885,25 @@
     </row>
     <row r="452">
       <c r="A452" s="0" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B452" s="0" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D452" s="0" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="E452" s="0" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F452" s="0" t="s">
         <v>300</v>
       </c>
       <c r="G452" s="0" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="J452" s="11">
         <v>46383.125</v>
@@ -41940,7 +41936,7 @@
         <v>45</v>
       </c>
       <c r="AC452" s="0" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="AD452" s="11">
         <v>46203.65469700231</v>
@@ -41972,13 +41968,13 @@
         <v>643</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E453" s="0" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="F453" s="0" t="s">
         <v>327</v>
@@ -41987,7 +41983,7 @@
         <v>327</v>
       </c>
       <c r="H453" s="0" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="J453" s="11">
         <v>46365.125</v>
@@ -42052,19 +42048,19 @@
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B454" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="D454" s="0" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E454" s="0" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F454" s="0" t="s">
         <v>208</v>
@@ -42073,7 +42069,7 @@
         <v>209</v>
       </c>
       <c r="H454" s="0" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="J454" s="11">
         <v>46365.125</v>
@@ -42144,13 +42140,13 @@
         <v>34</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E455" s="0" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="F455" s="0" t="s">
         <v>85</v>
@@ -42227,7 +42223,7 @@
         <v>34</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>36</v>
@@ -42310,7 +42306,7 @@
         <v>34</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>123</v>
@@ -42325,7 +42321,7 @@
         <v>74</v>
       </c>
       <c r="H457" s="0" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="J457" s="11">
         <v>46387.125</v>
@@ -42396,7 +42392,7 @@
         <v>34</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="D458" s="0" t="s">
         <v>123</v>
@@ -42411,7 +42407,7 @@
         <v>74</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="J458" s="11">
         <v>46326.125</v>
@@ -42420,7 +42416,7 @@
         <v>114</v>
       </c>
       <c r="L458" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="M458" s="0" t="s">
         <v>39</v>
@@ -42482,7 +42478,7 @@
         <v>34</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>51</v>
@@ -42497,7 +42493,7 @@
         <v>326</v>
       </c>
       <c r="H459" s="0" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="J459" s="11">
         <v>46326.125</v>
@@ -42506,7 +42502,7 @@
         <v>114</v>
       </c>
       <c r="L459" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="M459" s="0" t="s">
         <v>39</v>
@@ -42568,13 +42564,13 @@
         <v>34</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E460" s="0" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="F460" s="0" t="s">
         <v>131</v>
@@ -42652,13 +42648,13 @@
         <v>34</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>179</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="F461" s="0" t="s">
         <v>149</v>
@@ -42667,7 +42663,7 @@
         <v>149</v>
       </c>
       <c r="H461" s="0" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="J461" s="11"/>
       <c r="K461" s="0" t="s">
@@ -42736,13 +42732,13 @@
         <v>61</v>
       </c>
       <c r="C462" s="0" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D462" s="0" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E462" s="0" t="s">
         <v>1003</v>
-      </c>
-      <c r="D462" s="0" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E462" s="0" t="s">
-        <v>1005</v>
       </c>
       <c r="F462" s="0" t="s">
         <v>418</v>
@@ -42751,7 +42747,7 @@
         <v>418</v>
       </c>
       <c r="H462" s="0" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="J462" s="11"/>
       <c r="K462" s="0" t="s">
@@ -42817,7 +42813,7 @@
         <v>61</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>77</v>
@@ -42832,7 +42828,7 @@
         <v>332</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="J463" s="11">
         <v>46406.125</v>
@@ -42903,13 +42899,13 @@
         <v>61</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F464" s="0" t="s">
         <v>79</v>
@@ -42918,7 +42914,7 @@
         <v>231</v>
       </c>
       <c r="H464" s="0" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="J464" s="11">
         <v>46407.125</v>
@@ -42989,7 +42985,7 @@
         <v>61</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>249</v>
@@ -43004,7 +43000,7 @@
         <v>134</v>
       </c>
       <c r="H465" s="0" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="J465" s="11">
         <v>46407.125</v>
@@ -43075,7 +43071,7 @@
         <v>61</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>249</v>
@@ -43090,7 +43086,7 @@
         <v>134</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="J466" s="11">
         <v>46407.125</v>
@@ -43161,13 +43157,13 @@
         <v>61</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D467" s="0" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E467" s="0" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="F467" s="0" t="s">
         <v>54</v>
@@ -43176,7 +43172,7 @@
         <v>54</v>
       </c>
       <c r="H467" s="0" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="J467" s="11">
         <v>46406.125</v>
@@ -43247,7 +43243,7 @@
         <v>61</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>259</v>
@@ -43262,7 +43258,7 @@
         <v>74</v>
       </c>
       <c r="H468" s="0" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="J468" s="11">
         <v>46373.125</v>
@@ -43333,7 +43329,7 @@
         <v>49</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>51</v>
@@ -43419,13 +43415,13 @@
         <v>226</v>
       </c>
       <c r="C470" s="0" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D470" s="0" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E470" s="0" t="s">
         <v>1018</v>
-      </c>
-      <c r="D470" s="0" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E470" s="0" t="s">
-        <v>1020</v>
       </c>
       <c r="F470" s="0" t="s">
         <v>142</v>
@@ -43434,7 +43430,7 @@
         <v>142</v>
       </c>
       <c r="H470" s="0" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="J470" s="11">
         <v>46398.125</v>
@@ -43496,19 +43492,19 @@
     </row>
     <row r="471">
       <c r="A471" s="0" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B471" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C471" s="0" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D471" s="0" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E471" s="0" t="s">
         <v>1022</v>
-      </c>
-      <c r="D471" s="0" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E471" s="0" t="s">
-        <v>1024</v>
       </c>
       <c r="F471" s="0" t="s">
         <v>200</v>
@@ -43523,7 +43519,7 @@
         <v>114</v>
       </c>
       <c r="L471" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="M471" s="0" t="s">
         <v>39</v>
@@ -43547,7 +43543,7 @@
         <v>45</v>
       </c>
       <c r="AC471" s="0" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="AD471" s="11">
         <v>46219.55652277778</v>
@@ -43579,7 +43575,7 @@
         <v>49</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>382</v>
@@ -43594,7 +43590,7 @@
         <v>339</v>
       </c>
       <c r="H472" s="0" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="J472" s="11">
         <v>46402.125</v>
@@ -43665,7 +43661,7 @@
         <v>61</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>51</v>
@@ -43680,7 +43676,7 @@
         <v>79</v>
       </c>
       <c r="H473" s="0" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="J473" s="11">
         <v>46346.125</v>
@@ -43751,13 +43747,13 @@
         <v>61</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E474" s="0" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="F474" s="0" t="s">
         <v>339</v>
@@ -43766,7 +43762,7 @@
         <v>53</v>
       </c>
       <c r="H474" s="0" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="J474" s="11">
         <v>46346.125</v>
@@ -43837,7 +43833,7 @@
         <v>61</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="D475" s="0" t="s">
         <v>249</v>
@@ -43852,7 +43848,7 @@
         <v>208</v>
       </c>
       <c r="H475" s="0" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="J475" s="11"/>
       <c r="K475" s="0" t="s">
@@ -43921,7 +43917,7 @@
         <v>61</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>51</v>
@@ -43936,7 +43932,7 @@
         <v>150</v>
       </c>
       <c r="H476" s="0" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="J476" s="11">
         <v>46407.125</v>
@@ -44007,7 +44003,7 @@
         <v>61</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>259</v>
@@ -44022,7 +44018,7 @@
         <v>231</v>
       </c>
       <c r="H477" s="0" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="J477" s="11">
         <v>46407.125</v>
@@ -44093,7 +44089,7 @@
         <v>61</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="D478" s="0" t="s">
         <v>259</v>
@@ -44108,7 +44104,7 @@
         <v>231</v>
       </c>
       <c r="H478" s="0" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="J478" s="11">
         <v>46407.125</v>
@@ -44173,13 +44169,13 @@
     </row>
     <row r="479">
       <c r="A479" s="0" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B479" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="D479" s="0" t="s">
         <v>212</v>
@@ -44259,13 +44255,13 @@
         <v>621</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D480" s="0" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="E480" s="0" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="F480" s="0" t="s">
         <v>439</v>
@@ -44339,13 +44335,13 @@
         <v>49</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D481" s="0" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="E481" s="0" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="F481" s="0" t="s">
         <v>98</v>
@@ -44425,13 +44421,13 @@
         <v>34</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="F482" s="0" t="s">
         <v>38</v>
@@ -44440,7 +44436,7 @@
         <v>38</v>
       </c>
       <c r="H482" s="0" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="J482" s="11"/>
       <c r="K482" s="0" t="s">
@@ -44509,13 +44505,13 @@
         <v>49</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D483" s="0" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="E483" s="0" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="F483" s="0" t="s">
         <v>137</v>
@@ -44592,7 +44588,7 @@
         <v>49</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>345</v>
@@ -44675,7 +44671,7 @@
         <v>49</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>345</v>
@@ -44758,7 +44754,7 @@
         <v>34</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D486" s="0" t="s">
         <v>249</v>
@@ -44773,7 +44769,7 @@
         <v>38</v>
       </c>
       <c r="H486" s="0" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="J486" s="11">
         <v>46362.125</v>
@@ -44844,7 +44840,7 @@
         <v>34</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D487" s="0" t="s">
         <v>249</v>
@@ -44859,7 +44855,7 @@
         <v>38</v>
       </c>
       <c r="H487" s="0" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="J487" s="11">
         <v>46362.125</v>
@@ -44930,7 +44926,7 @@
         <v>49</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>366</v>
@@ -45013,13 +45009,13 @@
         <v>49</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D489" s="0" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E489" s="0" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F489" s="0" t="s">
         <v>257</v>
@@ -45096,13 +45092,13 @@
         <v>49</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D490" s="0" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="E490" s="0" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F490" s="0" t="s">
         <v>131</v>
@@ -45179,13 +45175,13 @@
         <v>49</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D491" s="0" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="E491" s="0" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F491" s="0" t="s">
         <v>294</v>
@@ -45262,13 +45258,13 @@
         <v>61</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E492" s="0" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="F492" s="0" t="s">
         <v>105</v>
@@ -45340,19 +45336,19 @@
     </row>
     <row r="493">
       <c r="A493" s="0" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B493" s="0" t="s">
         <v>643</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E493" s="0" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="F493" s="0" t="s">
         <v>293</v>
@@ -45361,7 +45357,7 @@
         <v>293</v>
       </c>
       <c r="H493" s="0" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="J493" s="11">
         <v>46372.125</v>
@@ -45432,19 +45428,19 @@
         <v>34</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E494" s="0" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F494" s="0" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G494" s="0" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="H494" s="0" t="s">
         <v>201</v>
@@ -45518,19 +45514,19 @@
         <v>34</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="D495" s="0" t="s">
         <v>587</v>
       </c>
       <c r="E495" s="0" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F495" s="0" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G495" s="0" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="H495" s="0" t="s">
         <v>201</v>
@@ -45604,7 +45600,7 @@
         <v>226</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="D496" s="0" t="s">
         <v>526</v>
@@ -45678,19 +45674,19 @@
     </row>
     <row r="497">
       <c r="A497" s="0" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B497" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D497" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E497" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="F497" s="0" t="s">
         <v>294</v>
@@ -45726,7 +45722,7 @@
         <v>45</v>
       </c>
       <c r="AC497" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="AD497" s="11">
         <v>46301.476280462964</v>
@@ -45752,19 +45748,19 @@
     </row>
     <row r="498">
       <c r="A498" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B498" s="0" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="D498" s="0" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="E498" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="F498" s="0" t="s">
         <v>168</v>
@@ -45777,7 +45773,7 @@
         <v>40</v>
       </c>
       <c r="L498" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="M498" s="0" t="s">
         <v>39</v>
@@ -45801,7 +45797,7 @@
         <v>44</v>
       </c>
       <c r="AC498" s="0" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="AD498" s="11">
         <v>46303.38590450231</v>
@@ -45819,19 +45815,19 @@
     </row>
     <row r="499">
       <c r="A499" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B499" s="0" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="D499" s="0" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="E499" s="0" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="F499" s="0" t="s">
         <v>169</v>
@@ -45844,7 +45840,7 @@
         <v>40</v>
       </c>
       <c r="L499" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="M499" s="0" t="s">
         <v>39</v>
@@ -45868,7 +45864,7 @@
         <v>44</v>
       </c>
       <c r="AC499" s="0" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="AD499" s="11">
         <v>46303.38891412037</v>
@@ -45931,28 +45927,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -45960,10 +45956,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>61</v>
@@ -45981,10 +45977,10 @@
         <v>46495.125</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>214</v>
@@ -45992,10 +45988,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>643</v>
@@ -46013,10 +46009,10 @@
         <v>46495.125</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>647</v>
@@ -46024,10 +46020,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>643</v>
@@ -46039,16 +46035,16 @@
         <v>46315</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G4" s="11">
         <v>46495.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>647</v>
@@ -46056,10 +46052,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>61</v>
@@ -46071,16 +46067,16 @@
         <v>46314</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G5" s="11">
         <v>46494.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>214</v>
@@ -46088,10 +46084,10 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>643</v>
@@ -46109,10 +46105,10 @@
         <v>46491.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>647</v>
@@ -46120,13 +46116,13 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>30</v>
@@ -46141,24 +46137,24 @@
         <v>46483.125</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>29</v>
@@ -46167,27 +46163,27 @@
         <v>46303</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G8" s="11">
         <v>46483.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>643</v>
@@ -46205,10 +46201,10 @@
         <v>46480.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>647</v>
@@ -46216,10 +46212,10 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>226</v>
@@ -46237,10 +46233,10 @@
         <v>46476.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>226</v>
@@ -46248,10 +46244,10 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>226</v>
@@ -46263,16 +46259,16 @@
         <v>46296</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G11" s="11">
         <v>46476.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>226</v>
@@ -46280,10 +46276,10 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>34</v>
@@ -46301,10 +46297,10 @@
         <v>46474.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>202</v>
@@ -46312,10 +46308,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>34</v>
@@ -46333,10 +46329,10 @@
         <v>46474.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>202</v>
@@ -46344,10 +46340,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>643</v>
@@ -46365,10 +46361,10 @@
         <v>46474.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>647</v>
@@ -46376,10 +46372,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>643</v>
@@ -46391,16 +46387,16 @@
         <v>46294</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G15" s="11">
         <v>46474.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>647</v>
@@ -46408,10 +46404,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>643</v>
@@ -46429,10 +46425,10 @@
         <v>46474.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>647</v>
@@ -46440,10 +46436,10 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>643</v>
@@ -46455,16 +46451,16 @@
         <v>46294</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G17" s="11">
         <v>46474.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>647</v>
@@ -46472,10 +46468,10 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>61</v>
@@ -46487,16 +46483,16 @@
         <v>46289</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G18" s="11">
         <v>46469.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>67</v>
@@ -46504,10 +46500,10 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>61</v>
@@ -46525,10 +46521,10 @@
         <v>46469.125</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J19" s="0" t="s">
         <v>67</v>
@@ -46536,10 +46532,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>643</v>
@@ -46557,10 +46553,10 @@
         <v>46455.125</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>647</v>
@@ -46568,10 +46564,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>643</v>
@@ -46583,16 +46579,16 @@
         <v>46275</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G21" s="11">
         <v>46455.125</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J21" s="0" t="s">
         <v>647</v>
@@ -46600,13 +46596,13 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>30</v>
@@ -46621,24 +46617,24 @@
         <v>46449.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>29</v>
@@ -46647,30 +46643,30 @@
         <v>46269</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G23" s="11">
         <v>46449.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>30</v>
@@ -46685,13 +46681,13 @@
         <v>46268</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="25">
@@ -46699,7 +46695,7 @@
         <v>551</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>34</v>
@@ -46711,19 +46707,19 @@
         <v>46267</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G25" s="11">
         <v>46447.125</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="26">
@@ -46731,7 +46727,7 @@
         <v>551</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>34</v>
@@ -46749,21 +46745,21 @@
         <v>46447.125</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>61</v>
@@ -46781,10 +46777,10 @@
         <v>46314</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J27" s="0" t="s">
         <v>214</v>
@@ -46792,10 +46788,10 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>61</v>
@@ -46813,10 +46809,10 @@
         <v>46446.125</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>214</v>
@@ -46827,7 +46823,7 @@
         <v>553</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>49</v>
@@ -46839,27 +46835,27 @@
         <v>46261</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G29" s="11">
         <v>46441.125</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>34</v>
@@ -46871,16 +46867,16 @@
         <v>46260</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G30" s="11">
         <v>46440.125</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="J30" s="0" t="s">
         <v>202</v>
@@ -46888,10 +46884,10 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>61</v>
@@ -46909,10 +46905,10 @@
         <v>46440.125</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>67</v>
@@ -46920,10 +46916,10 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>34</v>
@@ -46941,10 +46937,10 @@
         <v>46439.125</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>202</v>
@@ -46952,10 +46948,10 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>34</v>
@@ -46973,10 +46969,10 @@
         <v>46439.125</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>202</v>
@@ -46984,10 +46980,10 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>34</v>
@@ -47005,10 +47001,10 @@
         <v>46439.125</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>202</v>
@@ -47019,7 +47015,7 @@
         <v>653</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>61</v>
@@ -47037,10 +47033,10 @@
         <v>46439.125</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>214</v>
@@ -47051,7 +47047,7 @@
         <v>211</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>61</v>
@@ -47069,10 +47065,10 @@
         <v>46439.125</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>214</v>
@@ -47083,7 +47079,7 @@
         <v>343</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>61</v>
@@ -47101,10 +47097,10 @@
         <v>46439.125</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>214</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46317.36198971065</v>
+        <v>46317.66598842593</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="1096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="1100">
   <si>
     <t>Geração:</t>
   </si>
@@ -3178,6 +3178,18 @@
   </si>
   <si>
     <t>REB/FACCHINI-IR RER FR</t>
+  </si>
+  <si>
+    <t>JUS2J56</t>
+  </si>
+  <si>
+    <t>SR /GUERRA AG BS</t>
+  </si>
+  <si>
+    <t>GUERRA AG BS</t>
+  </si>
+  <si>
+    <t>Inspeções Checklist de Qualidade, Checklist de Segurança SESMT pendentes</t>
   </si>
   <si>
     <t>Marca / Modelo</t>
@@ -3481,7 +3493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ488"/>
+  <dimension ref="A1:AJ489"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -3492,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46317.66598842593</v>
+        <v>46318.37395836806</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -44891,6 +44903,70 @@
       </c>
       <c r="AI488" s="3"/>
       <c r="AJ488" s="3"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="0" t="s">
+        <v>815</v>
+      </c>
+      <c r="B489" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="C489" s="0" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D489" s="0" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E489" s="0" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F489" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="G489" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="J489" s="11"/>
+      <c r="K489" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="L489" s="0" t="s">
+        <v>1058</v>
+      </c>
+      <c r="M489" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="N489" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q489" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="T489" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="W489" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z489" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC489" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="AD489" s="11">
+        <v>46317.68723200232</v>
+      </c>
+      <c r="AE489" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF489" s="3"/>
+      <c r="AG489" s="3"/>
+      <c r="AH489" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI489" s="3"/>
+      <c r="AJ489" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -44939,28 +45015,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -44971,7 +45047,7 @@
         <v>851</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>61</v>
@@ -44983,16 +45059,16 @@
         <v>46316</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="G2" s="11">
         <v>46496.125</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>214</v>
@@ -45003,7 +45079,7 @@
         <v>851</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>61</v>
@@ -45021,10 +45097,10 @@
         <v>46495.125</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>214</v>
@@ -45035,7 +45111,7 @@
         <v>864</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>626</v>
@@ -45053,10 +45129,10 @@
         <v>46495.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>630</v>
@@ -45067,7 +45143,7 @@
         <v>864</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>626</v>
@@ -45079,16 +45155,16 @@
         <v>46315</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="G5" s="11">
         <v>46495.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>630</v>
@@ -45099,7 +45175,7 @@
         <v>853</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>61</v>
@@ -45111,16 +45187,16 @@
         <v>46314</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="G6" s="11">
         <v>46494.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>214</v>
@@ -45131,7 +45207,7 @@
         <v>826</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>626</v>
@@ -45149,10 +45225,10 @@
         <v>46491.125</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>630</v>
@@ -45163,7 +45239,7 @@
         <v>1048</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>788</v>
@@ -45181,10 +45257,10 @@
         <v>46483.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J8" s="0" t="s">
         <v>788</v>
@@ -45195,7 +45271,7 @@
         <v>1048</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>788</v>
@@ -45207,16 +45283,16 @@
         <v>46303</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="G9" s="11">
         <v>46483.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J9" s="0" t="s">
         <v>788</v>
@@ -45227,7 +45303,7 @@
         <v>860</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>626</v>
@@ -45245,10 +45321,10 @@
         <v>46480.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>630</v>
@@ -45259,7 +45335,7 @@
         <v>1047</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>226</v>
@@ -45277,10 +45353,10 @@
         <v>46476.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>226</v>
@@ -45291,7 +45367,7 @@
         <v>1047</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>226</v>
@@ -45303,16 +45379,16 @@
         <v>46296</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="G12" s="11">
         <v>46476.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>226</v>
@@ -45323,7 +45399,7 @@
         <v>1043</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>34</v>
@@ -45341,10 +45417,10 @@
         <v>46474.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>202</v>
@@ -45355,7 +45431,7 @@
         <v>1046</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>34</v>
@@ -45373,10 +45449,10 @@
         <v>46474.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>202</v>
@@ -45387,7 +45463,7 @@
         <v>859</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>626</v>
@@ -45405,10 +45481,10 @@
         <v>46474.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>630</v>
@@ -45419,7 +45495,7 @@
         <v>859</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>626</v>
@@ -45431,16 +45507,16 @@
         <v>46294</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="G16" s="11">
         <v>46474.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>630</v>
@@ -45451,7 +45527,7 @@
         <v>824</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>626</v>
@@ -45469,10 +45545,10 @@
         <v>46474.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>630</v>
@@ -45483,7 +45559,7 @@
         <v>824</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>626</v>
@@ -45495,16 +45571,16 @@
         <v>46294</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="G18" s="11">
         <v>46474.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>630</v>
@@ -45515,7 +45591,7 @@
         <v>955</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>61</v>
@@ -45527,16 +45603,16 @@
         <v>46289</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="G19" s="11">
         <v>46469.125</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="J19" s="0" t="s">
         <v>67</v>
@@ -45547,7 +45623,7 @@
         <v>955</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>61</v>
@@ -45565,10 +45641,10 @@
         <v>46469.125</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>67</v>
@@ -45579,7 +45655,7 @@
         <v>1041</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>626</v>
@@ -45597,10 +45673,10 @@
         <v>46455.125</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J21" s="0" t="s">
         <v>630</v>
@@ -45611,7 +45687,7 @@
         <v>1041</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>626</v>
@@ -45623,16 +45699,16 @@
         <v>46275</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="G22" s="11">
         <v>46455.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>630</v>
@@ -45643,7 +45719,7 @@
         <v>833</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>832</v>
@@ -45661,10 +45737,10 @@
         <v>46449.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J23" s="0" t="s">
         <v>834</v>
@@ -45675,7 +45751,7 @@
         <v>833</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>832</v>
@@ -45687,16 +45763,16 @@
         <v>46269</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="G24" s="11">
         <v>46449.125</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J24" s="0" t="s">
         <v>834</v>
@@ -45707,7 +45783,7 @@
         <v>833</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>832</v>
@@ -45725,10 +45801,10 @@
         <v>46268</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="J25" s="0" t="s">
         <v>834</v>
@@ -45739,7 +45815,7 @@
         <v>539</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>34</v>
@@ -45751,19 +45827,19 @@
         <v>46267</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="G26" s="11">
         <v>46447.125</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="27">
@@ -45771,7 +45847,7 @@
         <v>539</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>34</v>
@@ -45789,13 +45865,13 @@
         <v>46447.125</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="28">
@@ -45803,7 +45879,7 @@
         <v>851</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>61</v>
@@ -45821,10 +45897,10 @@
         <v>46314</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>214</v>
@@ -45835,7 +45911,7 @@
         <v>853</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>61</v>
@@ -45853,10 +45929,10 @@
         <v>46446.125</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>214</v>
@@ -45867,7 +45943,7 @@
         <v>541</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>49</v>
@@ -45879,19 +45955,19 @@
         <v>46261</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="G30" s="11">
         <v>46441.125</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="J30" s="0" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="31">
@@ -45899,7 +45975,7 @@
         <v>850</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>34</v>
@@ -45911,16 +45987,16 @@
         <v>46260</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="G31" s="11">
         <v>46440.125</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="J31" s="0" t="s">
         <v>202</v>
@@ -45931,7 +46007,7 @@
         <v>1039</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>61</v>
@@ -45949,10 +46025,10 @@
         <v>46440.125</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J32" s="0" t="s">
         <v>67</v>
@@ -45963,7 +46039,7 @@
         <v>849</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>34</v>
@@ -45981,10 +46057,10 @@
         <v>46439.125</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J33" s="0" t="s">
         <v>202</v>
@@ -45995,7 +46071,7 @@
         <v>640</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>34</v>
@@ -46013,10 +46089,10 @@
         <v>46439.125</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J34" s="0" t="s">
         <v>202</v>
@@ -46027,7 +46103,7 @@
         <v>850</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>34</v>
@@ -46045,10 +46121,10 @@
         <v>46439.125</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J35" s="0" t="s">
         <v>202</v>
@@ -46059,7 +46135,7 @@
         <v>636</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>61</v>
@@ -46077,10 +46153,10 @@
         <v>46439.125</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>214</v>
@@ -46091,7 +46167,7 @@
         <v>211</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>61</v>
@@ -46109,10 +46185,10 @@
         <v>46439.125</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>214</v>
@@ -46123,7 +46199,7 @@
         <v>336</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>61</v>
@@ -46141,10 +46217,10 @@
         <v>46439.125</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="J38" s="0" t="s">
         <v>214</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -3504,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46318.37395836806</v>
+        <v>46318.66441013889</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -34568,13 +34568,13 @@
         <v>698</v>
       </c>
       <c r="J366" s="11">
-        <v>46326.125</v>
+        <v>46372.125</v>
       </c>
       <c r="K366" s="0" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="L366" s="0" t="s">
-        <v>710</v>
+        <v>39</v>
       </c>
       <c r="M366" s="0" t="s">
         <v>39</v>
@@ -34583,7 +34583,7 @@
         <v>43</v>
       </c>
       <c r="O366" s="11">
-        <v>46326.125</v>
+        <v>46691.125</v>
       </c>
       <c r="Q366" s="0" t="s">
         <v>43</v>
@@ -34654,13 +34654,13 @@
         <v>698</v>
       </c>
       <c r="J367" s="11">
-        <v>46326.125</v>
+        <v>46372.125</v>
       </c>
       <c r="K367" s="0" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="L367" s="0" t="s">
-        <v>710</v>
+        <v>39</v>
       </c>
       <c r="M367" s="0" t="s">
         <v>39</v>
@@ -34669,7 +34669,7 @@
         <v>43</v>
       </c>
       <c r="O367" s="11">
-        <v>46326.125</v>
+        <v>46691.125</v>
       </c>
       <c r="Q367" s="0" t="s">
         <v>43</v>
@@ -34826,13 +34826,13 @@
         <v>830</v>
       </c>
       <c r="J369" s="11">
-        <v>46341.125</v>
+        <v>46356.125</v>
       </c>
       <c r="K369" s="0" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="L369" s="0" t="s">
-        <v>710</v>
+        <v>39</v>
       </c>
       <c r="M369" s="0" t="s">
         <v>39</v>
@@ -34841,7 +34841,7 @@
         <v>43</v>
       </c>
       <c r="O369" s="11">
-        <v>46341.125</v>
+        <v>46706.125</v>
       </c>
       <c r="Q369" s="0" t="s">
         <v>43</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1089">
   <si>
     <t>Geração:</t>
   </si>
@@ -3280,15 +3280,6 @@
   </si>
   <si>
     <t>MILHO | GNOVA TRANSPORTES LTDA;TOMATE | GNOVA TRANSPORTES LTDA</t>
-  </si>
-  <si>
-    <t>SR/IMPERIAL GR000227T0 1 / SR/IMPERIAL GR000227T0 1</t>
-  </si>
-  <si>
-    <t>Weverson Cavalcante Da Silva</t>
-  </si>
-  <si>
-    <t>MILHO | ITUM ARMAZENS GERAIS E SERVIÇOS LTDA;TOMATE | ITUM ARMAZENS GERAIS E SERVIÇOS LTDA</t>
   </si>
 </sst>
 </file>
@@ -3480,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46321.38724898148</v>
+        <v>46321.62844402778</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -44890,7 +44881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" customWidth="1"/>
@@ -45824,38 +45815,6 @@
         <v>214</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>536</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="11">
-        <v>46261</v>
-      </c>
-      <c r="F30" s="0" t="s">
-        <v>1063</v>
-      </c>
-      <c r="G30" s="11">
-        <v>46441.125</v>
-      </c>
-      <c r="H30" s="0" t="s">
-        <v>1090</v>
-      </c>
-      <c r="I30" s="0" t="s">
-        <v>1065</v>
-      </c>
-      <c r="J30" s="0" t="s">
-        <v>1091</v>
-      </c>
-    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46321.62844402778</v>
+        <v>46322.37704277778</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -24473,10 +24473,10 @@
         <v>46351.125</v>
       </c>
       <c r="K247" s="0" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="L247" s="0" t="s">
-        <v>39</v>
+        <v>206</v>
       </c>
       <c r="M247" s="0" t="s">
         <v>39</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="1091">
   <si>
     <t>Geração:</t>
   </si>
@@ -1921,6 +1921,12 @@
   </si>
   <si>
     <t>RBI8D41</t>
+  </si>
+  <si>
+    <t>Documento CRLV aguardando validação</t>
+  </si>
+  <si>
+    <t>AV</t>
   </si>
   <si>
     <t>FIXO POLIGUINDASTE</t>
@@ -3471,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46322.37704277778</v>
+        <v>46322.74272458333</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -25550,16 +25556,16 @@
         <v>40</v>
       </c>
       <c r="L260" s="0" t="s">
-        <v>41</v>
+        <v>636</v>
       </c>
       <c r="M260" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N260" s="0" t="s">
-        <v>42</v>
+        <v>637</v>
       </c>
       <c r="O260" s="11">
-        <v>46302.125</v>
+        <v>46645.125</v>
       </c>
       <c r="Q260" s="0" t="s">
         <v>43</v>
@@ -25606,13 +25612,13 @@
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B261" s="0" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D261" s="0" t="s">
         <v>416</v>
@@ -25624,14 +25630,14 @@
         <v>479</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="J261" s="11"/>
       <c r="K261" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L261" s="0" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="M261" s="0" t="s">
         <v>39</v>
@@ -25652,7 +25658,7 @@
         <v>45</v>
       </c>
       <c r="AC261" s="0" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AD261" s="11">
         <v>45817.61092795139</v>
@@ -25678,32 +25684,32 @@
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B262" s="0" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D262" s="0" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="F262" s="0" t="s">
         <v>169</v>
       </c>
       <c r="G262" s="0" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="J262" s="11"/>
       <c r="K262" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L262" s="0" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="M262" s="0" t="s">
         <v>39</v>
@@ -25730,7 +25736,7 @@
         <v>45</v>
       </c>
       <c r="AC262" s="0" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AD262" s="11">
         <v>45817.61552398148</v>
@@ -25762,7 +25768,7 @@
         <v>49</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D263" s="0" t="s">
         <v>313</v>
@@ -25777,7 +25783,7 @@
         <v>131</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="J263" s="11">
         <v>46411.125</v>
@@ -25848,7 +25854,7 @@
         <v>49</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D264" s="0" t="s">
         <v>311</v>
@@ -25860,10 +25866,10 @@
         <v>131</v>
       </c>
       <c r="G264" s="0" t="s">
+        <v>652</v>
+      </c>
+      <c r="H264" s="0" t="s">
         <v>650</v>
-      </c>
-      <c r="H264" s="0" t="s">
-        <v>648</v>
       </c>
       <c r="J264" s="11">
         <v>46411.125</v>
@@ -25934,13 +25940,13 @@
         <v>61</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D265" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F265" s="0" t="s">
         <v>65</v>
@@ -25949,7 +25955,7 @@
         <v>65</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="J265" s="11">
         <v>46357.125</v>
@@ -26020,7 +26026,7 @@
         <v>34</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D266" s="0" t="s">
         <v>162</v>
@@ -26035,14 +26041,14 @@
         <v>332</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="J266" s="11"/>
       <c r="K266" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L266" s="0" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M266" s="0" t="s">
         <v>39</v>
@@ -26101,13 +26107,13 @@
         <v>49</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E267" s="0" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F267" s="0" t="s">
         <v>168</v>
@@ -26116,7 +26122,7 @@
         <v>168</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="J267" s="11">
         <v>46417.125</v>
@@ -26187,13 +26193,13 @@
         <v>34</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D268" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E268" s="0" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F268" s="0" t="s">
         <v>200</v>
@@ -26209,7 +26215,7 @@
         <v>40</v>
       </c>
       <c r="L268" s="0" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M268" s="0" t="s">
         <v>39</v>
@@ -26271,13 +26277,13 @@
         <v>49</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E269" s="0" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F269" s="0" t="s">
         <v>74</v>
@@ -26357,7 +26363,7 @@
         <v>49</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D270" s="0" t="s">
         <v>362</v>
@@ -26443,7 +26449,7 @@
         <v>49</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D271" s="0" t="s">
         <v>364</v>
@@ -26523,13 +26529,13 @@
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B272" s="0" t="s">
         <v>49</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D272" s="0" t="s">
         <v>563</v>
@@ -26544,7 +26550,7 @@
         <v>231</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="J272" s="11">
         <v>46374.125</v>
@@ -26615,7 +26621,7 @@
         <v>34</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D273" s="0" t="s">
         <v>51</v>
@@ -26630,7 +26636,7 @@
         <v>74</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="J273" s="11"/>
       <c r="K273" s="0" t="s">
@@ -26699,7 +26705,7 @@
         <v>34</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D274" s="0" t="s">
         <v>123</v>
@@ -26783,7 +26789,7 @@
         <v>34</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D275" s="0" t="s">
         <v>123</v>
@@ -26867,7 +26873,7 @@
         <v>34</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D276" s="0" t="s">
         <v>72</v>
@@ -26951,7 +26957,7 @@
         <v>34</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D277" s="0" t="s">
         <v>72</v>
@@ -27035,7 +27041,7 @@
         <v>34</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D278" s="0" t="s">
         <v>51</v>
@@ -27119,13 +27125,13 @@
         <v>61</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D279" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F279" s="0" t="s">
         <v>168</v>
@@ -27134,7 +27140,7 @@
         <v>168</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J279" s="11">
         <v>46373.125</v>
@@ -27205,7 +27211,7 @@
         <v>61</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D280" s="0" t="s">
         <v>36</v>
@@ -27220,7 +27226,7 @@
         <v>38</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J280" s="11">
         <v>46373.125</v>
@@ -27291,7 +27297,7 @@
         <v>61</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D281" s="0" t="s">
         <v>36</v>
@@ -27306,7 +27312,7 @@
         <v>38</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J281" s="11">
         <v>46373.125</v>
@@ -27377,13 +27383,13 @@
         <v>34</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D282" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="F282" s="0" t="s">
         <v>168</v>
@@ -27392,7 +27398,7 @@
         <v>169</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="J282" s="11"/>
       <c r="K282" s="0" t="s">
@@ -27461,7 +27467,7 @@
         <v>34</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D283" s="0" t="s">
         <v>77</v>
@@ -27476,7 +27482,7 @@
         <v>137</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="J283" s="11"/>
       <c r="K283" s="0" t="s">
@@ -27545,13 +27551,13 @@
         <v>34</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D284" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F284" s="0" t="s">
         <v>149</v>
@@ -27560,7 +27566,7 @@
         <v>149</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="J284" s="11">
         <v>46365.125</v>
@@ -27631,13 +27637,13 @@
         <v>34</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D285" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F285" s="0" t="s">
         <v>149</v>
@@ -27646,7 +27652,7 @@
         <v>149</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="J285" s="11"/>
       <c r="K285" s="0" t="s">
@@ -27715,7 +27721,7 @@
         <v>61</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D286" s="0" t="s">
         <v>162</v>
@@ -27730,7 +27736,7 @@
         <v>93</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="J286" s="11">
         <v>46373.125</v>
@@ -27801,13 +27807,13 @@
         <v>621</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D287" s="0" t="s">
         <v>604</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="F287" s="0" t="s">
         <v>134</v>
@@ -27816,7 +27822,7 @@
         <v>526</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="J287" s="11">
         <v>46372.125</v>
@@ -27887,7 +27893,7 @@
         <v>61</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D288" s="0" t="s">
         <v>249</v>
@@ -27971,7 +27977,7 @@
         <v>49</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D289" s="0" t="s">
         <v>259</v>
@@ -28057,13 +28063,13 @@
         <v>61</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D290" s="0" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E290" s="0" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F290" s="0" t="s">
         <v>74</v>
@@ -28143,7 +28149,7 @@
         <v>61</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D291" s="0" t="s">
         <v>259</v>
@@ -28227,7 +28233,7 @@
         <v>61</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D292" s="0" t="s">
         <v>259</v>
@@ -28313,10 +28319,10 @@
         <v>61</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E293" s="0" t="s">
         <v>73</v>
@@ -28328,7 +28334,7 @@
         <v>526</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J293" s="11">
         <v>46361.125</v>
@@ -28399,7 +28405,7 @@
         <v>61</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D294" s="0" t="s">
         <v>259</v>
@@ -28414,7 +28420,7 @@
         <v>60</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J294" s="11">
         <v>46326.125</v>
@@ -28423,7 +28429,7 @@
         <v>114</v>
       </c>
       <c r="L294" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M294" s="0" t="s">
         <v>39</v>
@@ -28485,10 +28491,10 @@
         <v>61</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E295" s="0" t="s">
         <v>102</v>
@@ -28572,7 +28578,7 @@
         <v>61</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D296" s="0" t="s">
         <v>249</v>
@@ -28658,7 +28664,7 @@
         <v>49</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D297" s="0" t="s">
         <v>259</v>
@@ -28744,13 +28750,13 @@
         <v>61</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="F298" s="0" t="s">
         <v>74</v>
@@ -28830,7 +28836,7 @@
         <v>61</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D299" s="0" t="s">
         <v>259</v>
@@ -28916,7 +28922,7 @@
         <v>61</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D300" s="0" t="s">
         <v>259</v>
@@ -29002,10 +29008,10 @@
         <v>61</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E301" s="0" t="s">
         <v>87</v>
@@ -29017,7 +29023,7 @@
         <v>526</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J301" s="11">
         <v>46359.125</v>
@@ -29088,7 +29094,7 @@
         <v>61</v>
       </c>
       <c r="C302" s="0" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D302" s="0" t="s">
         <v>259</v>
@@ -29103,7 +29109,7 @@
         <v>60</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="J302" s="11">
         <v>46326.125</v>
@@ -29112,7 +29118,7 @@
         <v>114</v>
       </c>
       <c r="L302" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M302" s="0" t="s">
         <v>39</v>
@@ -29174,10 +29180,10 @@
         <v>61</v>
       </c>
       <c r="C303" s="0" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E303" s="0" t="s">
         <v>97</v>
@@ -29261,7 +29267,7 @@
         <v>61</v>
       </c>
       <c r="C304" s="0" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D304" s="0" t="s">
         <v>51</v>
@@ -29276,7 +29282,7 @@
         <v>169</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="J304" s="11"/>
       <c r="K304" s="0" t="s">
@@ -29345,7 +29351,7 @@
         <v>61</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D305" s="0" t="s">
         <v>51</v>
@@ -29431,10 +29437,10 @@
         <v>61</v>
       </c>
       <c r="C306" s="0" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E306" s="0" t="s">
         <v>228</v>
@@ -29517,7 +29523,7 @@
         <v>61</v>
       </c>
       <c r="C307" s="0" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D307" s="0" t="s">
         <v>249</v>
@@ -29595,19 +29601,19 @@
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B308" s="0" t="s">
         <v>49</v>
       </c>
       <c r="C308" s="0" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D308" s="0" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="F308" s="0" t="s">
         <v>93</v>
@@ -29616,7 +29622,7 @@
         <v>93</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="J308" s="11">
         <v>46370.125</v>
@@ -29687,7 +29693,7 @@
         <v>34</v>
       </c>
       <c r="C309" s="0" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D309" s="0" t="s">
         <v>162</v>
@@ -29702,7 +29708,7 @@
         <v>243</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="J309" s="11">
         <v>46367.125</v>
@@ -29770,7 +29776,7 @@
         <v>49</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D310" s="0" t="s">
         <v>311</v>
@@ -29785,7 +29791,7 @@
         <v>65</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="J310" s="11">
         <v>46415.125</v>
@@ -29856,7 +29862,7 @@
         <v>49</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D311" s="0" t="s">
         <v>313</v>
@@ -29871,7 +29877,7 @@
         <v>65</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="J311" s="11">
         <v>46415.125</v>
@@ -29942,13 +29948,13 @@
         <v>49</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D312" s="0" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="F312" s="0" t="s">
         <v>169</v>
@@ -29957,7 +29963,7 @@
         <v>169</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="J312" s="11">
         <v>46358.125</v>
@@ -30028,13 +30034,13 @@
         <v>49</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D313" s="0" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E313" s="0" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="F313" s="0" t="s">
         <v>65</v>
@@ -30043,7 +30049,7 @@
         <v>65</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="J313" s="11">
         <v>46358.125</v>
@@ -30114,10 +30120,10 @@
         <v>49</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="D314" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E314" s="0" t="s">
         <v>87</v>
@@ -30200,10 +30206,10 @@
         <v>49</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D315" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E315" s="0" t="s">
         <v>73</v>
@@ -30286,7 +30292,7 @@
         <v>61</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D316" s="0" t="s">
         <v>51</v>
@@ -30301,7 +30307,7 @@
         <v>74</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="J316" s="11"/>
       <c r="K316" s="0" t="s">
@@ -30370,7 +30376,7 @@
         <v>61</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D317" s="0" t="s">
         <v>36</v>
@@ -30385,7 +30391,7 @@
         <v>526</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="J317" s="11">
         <v>46373.125</v>
@@ -30456,7 +30462,7 @@
         <v>61</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D318" s="0" t="s">
         <v>36</v>
@@ -30471,7 +30477,7 @@
         <v>526</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="J318" s="11">
         <v>46373.125</v>
@@ -30542,7 +30548,7 @@
         <v>61</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D319" s="0" t="s">
         <v>249</v>
@@ -30628,7 +30634,7 @@
         <v>61</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D320" s="0" t="s">
         <v>249</v>
@@ -30714,7 +30720,7 @@
         <v>61</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D321" s="0" t="s">
         <v>249</v>
@@ -30800,7 +30806,7 @@
         <v>61</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D322" s="0" t="s">
         <v>249</v>
@@ -30886,13 +30892,13 @@
         <v>49</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D323" s="0" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E323" s="0" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F323" s="0" t="s">
         <v>168</v>
@@ -30901,7 +30907,7 @@
         <v>168</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="J323" s="11">
         <v>46421.125</v>
@@ -30972,13 +30978,13 @@
         <v>49</v>
       </c>
       <c r="C324" s="0" t="s">
+        <v>754</v>
+      </c>
+      <c r="D324" s="0" t="s">
+        <v>751</v>
+      </c>
+      <c r="E324" s="0" t="s">
         <v>752</v>
-      </c>
-      <c r="D324" s="0" t="s">
-        <v>749</v>
-      </c>
-      <c r="E324" s="0" t="s">
-        <v>750</v>
       </c>
       <c r="F324" s="0" t="s">
         <v>168</v>
@@ -30987,7 +30993,7 @@
         <v>168</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="J324" s="11">
         <v>46421.125</v>
@@ -31058,7 +31064,7 @@
         <v>61</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D325" s="0" t="s">
         <v>249</v>
@@ -31142,7 +31148,7 @@
         <v>61</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D326" s="0" t="s">
         <v>249</v>
@@ -31226,7 +31232,7 @@
         <v>61</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D327" s="0" t="s">
         <v>259</v>
@@ -31241,7 +31247,7 @@
         <v>93</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="J327" s="11">
         <v>46373.125</v>
@@ -31312,7 +31318,7 @@
         <v>61</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D328" s="0" t="s">
         <v>259</v>
@@ -31327,7 +31333,7 @@
         <v>93</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="J328" s="11">
         <v>46373.125</v>
@@ -31398,13 +31404,13 @@
         <v>226</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D329" s="0" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E329" s="0" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="F329" s="0" t="s">
         <v>149</v>
@@ -31478,7 +31484,7 @@
         <v>61</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D330" s="0" t="s">
         <v>72</v>
@@ -31565,10 +31571,10 @@
         <v>61</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E331" s="0" t="s">
         <v>73</v>
@@ -31649,7 +31655,7 @@
         <v>34</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D332" s="0" t="s">
         <v>77</v>
@@ -31664,7 +31670,7 @@
         <v>137</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="J332" s="11">
         <v>46366.125</v>
@@ -31735,7 +31741,7 @@
         <v>34</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D333" s="0" t="s">
         <v>96</v>
@@ -31750,14 +31756,14 @@
         <v>74</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="J333" s="11"/>
       <c r="K333" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L333" s="0" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M333" s="0" t="s">
         <v>39</v>
@@ -31819,7 +31825,7 @@
         <v>34</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D334" s="0" t="s">
         <v>96</v>
@@ -31834,7 +31840,7 @@
         <v>74</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="J334" s="11"/>
       <c r="K334" s="0" t="s">
@@ -31903,7 +31909,7 @@
         <v>49</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D335" s="0" t="s">
         <v>304</v>
@@ -31989,13 +31995,13 @@
         <v>49</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="E336" s="0" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="F336" s="0" t="s">
         <v>149</v>
@@ -32072,7 +32078,7 @@
         <v>49</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D337" s="0" t="s">
         <v>304</v>
@@ -32158,7 +32164,7 @@
         <v>49</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D338" s="0" t="s">
         <v>304</v>
@@ -32244,7 +32250,7 @@
         <v>34</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D339" s="0" t="s">
         <v>162</v>
@@ -32259,7 +32265,7 @@
         <v>506</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="J339" s="11"/>
       <c r="K339" s="0" t="s">
@@ -32328,7 +32334,7 @@
         <v>34</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D340" s="0" t="s">
         <v>140</v>
@@ -32343,7 +32349,7 @@
         <v>428</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="J340" s="11"/>
       <c r="K340" s="0" t="s">
@@ -32412,7 +32418,7 @@
         <v>61</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D341" s="0" t="s">
         <v>162</v>
@@ -32427,7 +32433,7 @@
         <v>54</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="J341" s="11">
         <v>46373.125</v>
@@ -32498,7 +32504,7 @@
         <v>61</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D342" s="0" t="s">
         <v>249</v>
@@ -32513,7 +32519,7 @@
         <v>526</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="J342" s="11">
         <v>46373.125</v>
@@ -32584,13 +32590,13 @@
         <v>226</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D343" s="0" t="s">
         <v>508</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="F343" s="0" t="s">
         <v>484</v>
@@ -32664,7 +32670,7 @@
         <v>61</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D344" s="0" t="s">
         <v>162</v>
@@ -32679,7 +32685,7 @@
         <v>54</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="J344" s="11">
         <v>46373.125</v>
@@ -32750,13 +32756,13 @@
         <v>61</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F345" s="0" t="s">
         <v>60</v>
@@ -32765,7 +32771,7 @@
         <v>134</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="J345" s="11">
         <v>46373.125</v>
@@ -32839,7 +32845,7 @@
         <v>61</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D346" s="0" t="s">
         <v>51</v>
@@ -32854,7 +32860,7 @@
         <v>131</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="J346" s="11"/>
       <c r="K346" s="0" t="s">
@@ -32917,19 +32923,19 @@
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B347" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D347" s="0" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="E347" s="0" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F347" s="0" t="s">
         <v>293</v>
@@ -32968,7 +32974,7 @@
         <v>45</v>
       </c>
       <c r="AC347" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AD347" s="11">
         <v>45847.61793511574</v>
@@ -32994,19 +33000,19 @@
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B348" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E348" s="0" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F348" s="0" t="s">
         <v>209</v>
@@ -33077,19 +33083,19 @@
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B349" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E349" s="0" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F349" s="0" t="s">
         <v>208</v>
@@ -33160,19 +33166,19 @@
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B350" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D350" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E350" s="0" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F350" s="0" t="s">
         <v>134</v>
@@ -33243,22 +33249,22 @@
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B351" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C351" s="0" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D351" s="0" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E351" s="0" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="F351" s="0" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>105</v>
@@ -33326,19 +33332,19 @@
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B352" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D352" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E352" s="0" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F352" s="0" t="s">
         <v>208</v>
@@ -33415,13 +33421,13 @@
         <v>599</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D353" s="0" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="E353" s="0" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="F353" s="0" t="s">
         <v>168</v>
@@ -33495,7 +33501,7 @@
         <v>34</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D354" s="0" t="s">
         <v>63</v>
@@ -33579,7 +33585,7 @@
         <v>49</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D355" s="0" t="s">
         <v>228</v>
@@ -33662,7 +33668,7 @@
         <v>49</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D356" s="0" t="s">
         <v>77</v>
@@ -33745,7 +33751,7 @@
         <v>61</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D357" s="0" t="s">
         <v>51</v>
@@ -33760,7 +33766,7 @@
         <v>79</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="J357" s="11">
         <v>46356.125</v>
@@ -33834,13 +33840,13 @@
         <v>61</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D358" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E358" s="0" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="F358" s="0" t="s">
         <v>149</v>
@@ -33849,7 +33855,7 @@
         <v>149</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="J358" s="11">
         <v>46356.125</v>
@@ -33923,7 +33929,7 @@
         <v>226</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D359" s="0" t="s">
         <v>77</v>
@@ -33938,7 +33944,7 @@
         <v>184</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="J359" s="11">
         <v>46392.125</v>
@@ -34003,16 +34009,16 @@
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B360" s="0" t="s">
         <v>226</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D360" s="0" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="E360" s="0" t="s">
         <v>141</v>
@@ -34024,7 +34030,7 @@
         <v>428</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="J360" s="11">
         <v>46392.125</v>
@@ -34089,7 +34095,7 @@
         <v>61</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D361" s="0" t="s">
         <v>162</v>
@@ -34104,7 +34110,7 @@
         <v>332</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="J361" s="11">
         <v>46326.125</v>
@@ -34113,7 +34119,7 @@
         <v>114</v>
       </c>
       <c r="L361" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M361" s="0" t="s">
         <v>39</v>
@@ -34175,7 +34181,7 @@
         <v>34</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D362" s="0" t="s">
         <v>77</v>
@@ -34190,7 +34196,7 @@
         <v>54</v>
       </c>
       <c r="H362" s="0" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="J362" s="11"/>
       <c r="K362" s="0" t="s">
@@ -34259,7 +34265,7 @@
         <v>34</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D363" s="0" t="s">
         <v>36</v>
@@ -34274,7 +34280,7 @@
         <v>60</v>
       </c>
       <c r="H363" s="0" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="J363" s="11"/>
       <c r="K363" s="0" t="s">
@@ -34343,7 +34349,7 @@
         <v>61</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D364" s="0" t="s">
         <v>51</v>
@@ -34421,19 +34427,19 @@
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B365" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D365" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F365" s="0" t="s">
         <v>208</v>
@@ -34442,7 +34448,7 @@
         <v>209</v>
       </c>
       <c r="H365" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="J365" s="11">
         <v>46372.125</v>
@@ -34513,13 +34519,13 @@
         <v>621</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D366" s="0" t="s">
         <v>604</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="F366" s="0" t="s">
         <v>134</v>
@@ -34528,7 +34534,7 @@
         <v>526</v>
       </c>
       <c r="H366" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="J366" s="11">
         <v>46372.125</v>
@@ -34593,19 +34599,19 @@
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B367" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D367" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E367" s="0" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F367" s="0" t="s">
         <v>209</v>
@@ -34614,7 +34620,7 @@
         <v>209</v>
       </c>
       <c r="H367" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="J367" s="11">
         <v>46348.125</v>
@@ -34685,13 +34691,13 @@
         <v>621</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D368" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E368" s="0" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="F368" s="0" t="s">
         <v>134</v>
@@ -34700,7 +34706,7 @@
         <v>526</v>
       </c>
       <c r="H368" s="0" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J368" s="11">
         <v>46356.125</v>
@@ -34771,7 +34777,7 @@
         <v>49</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D369" s="0" t="s">
         <v>198</v>
@@ -34854,10 +34860,10 @@
         <v>620</v>
       </c>
       <c r="B370" s="0" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D370" s="0" t="s">
         <v>63</v>
@@ -34911,7 +34917,7 @@
         <v>44</v>
       </c>
       <c r="AC370" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AD370" s="11">
         <v>46037.467388136574</v>
@@ -34940,16 +34946,16 @@
         <v>620</v>
       </c>
       <c r="B371" s="0" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D371" s="0" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="E371" s="0" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="F371" s="0" t="s">
         <v>60</v>
@@ -34958,14 +34964,14 @@
         <v>134</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="J371" s="11"/>
       <c r="K371" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L371" s="0" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="M371" s="0" t="s">
         <v>39</v>
@@ -34986,7 +34992,7 @@
         <v>44</v>
       </c>
       <c r="AC371" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AD371" s="11">
         <v>46038.63016152778</v>
@@ -35018,19 +35024,19 @@
         <v>49</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D372" s="0" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E372" s="0" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="F372" s="0" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G372" s="0" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="H372" s="0" t="s">
         <v>132</v>
@@ -35098,25 +35104,25 @@
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B373" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D373" s="0" t="s">
         <v>508</v>
       </c>
       <c r="E373" s="0" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="F373" s="0" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G373" s="0" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="J373" s="11">
         <v>46409.125</v>
@@ -35149,7 +35155,7 @@
         <v>45</v>
       </c>
       <c r="AC373" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AD373" s="11">
         <v>46051.66783503472</v>
@@ -35175,25 +35181,25 @@
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B374" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D374" s="0" t="s">
         <v>508</v>
       </c>
       <c r="E374" s="0" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="F374" s="0" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G374" s="0" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="J374" s="11">
         <v>46413.125</v>
@@ -35223,7 +35229,7 @@
         <v>45</v>
       </c>
       <c r="AC374" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AD374" s="11">
         <v>46052.455825081015</v>
@@ -35255,7 +35261,7 @@
         <v>34</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D375" s="0" t="s">
         <v>51</v>
@@ -35277,16 +35283,16 @@
         <v>40</v>
       </c>
       <c r="L375" s="0" t="s">
-        <v>41</v>
+        <v>636</v>
       </c>
       <c r="M375" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N375" s="0" t="s">
-        <v>42</v>
+        <v>637</v>
       </c>
       <c r="O375" s="11">
-        <v>46275.125</v>
+        <v>46645.125</v>
       </c>
       <c r="Q375" s="0" t="s">
         <v>43</v>
@@ -35339,7 +35345,7 @@
         <v>34</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D376" s="0" t="s">
         <v>36</v>
@@ -35425,13 +35431,13 @@
         <v>61</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D377" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E377" s="0" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F377" s="0" t="s">
         <v>200</v>
@@ -35508,13 +35514,13 @@
         <v>61</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D378" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E378" s="0" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F378" s="0" t="s">
         <v>200</v>
@@ -35585,25 +35591,25 @@
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B379" s="0" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>565</v>
       </c>
       <c r="E379" s="0" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="F379" s="0" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G379" s="0" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="J379" s="11">
         <v>46401.125</v>
@@ -35636,7 +35642,7 @@
         <v>45</v>
       </c>
       <c r="AC379" s="0" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="AD379" s="11">
         <v>46104.56253545139</v>
@@ -35662,19 +35668,19 @@
     </row>
     <row r="380">
       <c r="A380" s="0" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B380" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E380" s="0" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F380" s="0" t="s">
         <v>209</v>
@@ -35683,7 +35689,7 @@
         <v>209</v>
       </c>
       <c r="H380" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="J380" s="11">
         <v>46372.125</v>
@@ -35754,22 +35760,22 @@
         <v>621</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E381" s="0" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="F381" s="0" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G381" s="0" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="H381" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="J381" s="11">
         <v>46372.125</v>
@@ -35840,13 +35846,13 @@
         <v>61</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D382" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E382" s="0" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="F382" s="0" t="s">
         <v>60</v>
@@ -35859,7 +35865,7 @@
         <v>40</v>
       </c>
       <c r="L382" s="0" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="M382" s="0" t="s">
         <v>39</v>
@@ -35915,19 +35921,19 @@
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B383" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D383" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E383" s="0" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F383" s="0" t="s">
         <v>209</v>
@@ -35936,7 +35942,7 @@
         <v>209</v>
       </c>
       <c r="H383" s="0" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="J383" s="11">
         <v>46362.125</v>
@@ -36007,7 +36013,7 @@
         <v>34</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D384" s="0" t="s">
         <v>198</v>
@@ -36093,13 +36099,13 @@
         <v>49</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D385" s="0" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="E385" s="0" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="F385" s="0" t="s">
         <v>243</v>
@@ -36108,7 +36114,7 @@
         <v>243</v>
       </c>
       <c r="H385" s="0" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="J385" s="11">
         <v>46413.125</v>
@@ -36179,13 +36185,13 @@
         <v>49</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D386" s="0" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="F386" s="0" t="s">
         <v>53</v>
@@ -36194,7 +36200,7 @@
         <v>54</v>
       </c>
       <c r="H386" s="0" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="J386" s="11">
         <v>46357.125</v>
@@ -36265,7 +36271,7 @@
         <v>34</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D387" s="0" t="s">
         <v>162</v>
@@ -36280,7 +36286,7 @@
         <v>54</v>
       </c>
       <c r="H387" s="0" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="J387" s="11">
         <v>46361.125</v>
@@ -36351,7 +36357,7 @@
         <v>34</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D388" s="0" t="s">
         <v>51</v>
@@ -36366,7 +36372,7 @@
         <v>150</v>
       </c>
       <c r="H388" s="0" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="J388" s="11">
         <v>46365.125</v>
@@ -36437,7 +36443,7 @@
         <v>34</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>51</v>
@@ -36452,7 +36458,7 @@
         <v>134</v>
       </c>
       <c r="H389" s="0" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="J389" s="11">
         <v>46365.125</v>
@@ -36523,7 +36529,7 @@
         <v>34</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>36</v>
@@ -36538,7 +36544,7 @@
         <v>134</v>
       </c>
       <c r="H390" s="0" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="J390" s="11"/>
       <c r="K390" s="0" t="s">
@@ -36607,13 +36613,13 @@
         <v>49</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D391" s="0" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="E391" s="0" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F391" s="0" t="s">
         <v>54</v>
@@ -36622,7 +36628,7 @@
         <v>54</v>
       </c>
       <c r="H391" s="0" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="J391" s="11">
         <v>46365.125</v>
@@ -36693,7 +36699,7 @@
         <v>49</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>322</v>
@@ -36708,7 +36714,7 @@
         <v>134</v>
       </c>
       <c r="H392" s="0" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="J392" s="11">
         <v>46362.125</v>
@@ -36779,13 +36785,13 @@
         <v>34</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="F393" s="0" t="s">
         <v>65</v>
@@ -36865,7 +36871,7 @@
         <v>34</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>36</v>
@@ -36951,7 +36957,7 @@
         <v>34</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>36</v>
@@ -37037,13 +37043,13 @@
         <v>34</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E396" s="0" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F396" s="0" t="s">
         <v>428</v>
@@ -37052,7 +37058,7 @@
         <v>428</v>
       </c>
       <c r="H396" s="0" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="J396" s="11"/>
       <c r="K396" s="0" t="s">
@@ -37121,13 +37127,13 @@
         <v>34</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D397" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="F397" s="0" t="s">
         <v>134</v>
@@ -37136,7 +37142,7 @@
         <v>134</v>
       </c>
       <c r="H397" s="0" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="J397" s="11"/>
       <c r="K397" s="0" t="s">
@@ -37205,13 +37211,13 @@
         <v>34</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D398" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="F398" s="0" t="s">
         <v>169</v>
@@ -37292,7 +37298,7 @@
         <v>34</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>51</v>
@@ -37307,7 +37313,7 @@
         <v>332</v>
       </c>
       <c r="H399" s="0" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="J399" s="11">
         <v>46356.125</v>
@@ -37381,13 +37387,13 @@
         <v>34</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>140</v>
       </c>
       <c r="E400" s="0" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F400" s="0" t="s">
         <v>142</v>
@@ -37396,7 +37402,7 @@
         <v>142</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="J400" s="11"/>
       <c r="K400" s="0" t="s">
@@ -37468,13 +37474,13 @@
         <v>34</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E401" s="0" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="F401" s="0" t="s">
         <v>93</v>
@@ -37483,7 +37489,7 @@
         <v>93</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="J401" s="11"/>
       <c r="K401" s="0" t="s">
@@ -37555,7 +37561,7 @@
         <v>34</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>123</v>
@@ -37570,7 +37576,7 @@
         <v>60</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="J402" s="11"/>
       <c r="K402" s="0" t="s">
@@ -37639,7 +37645,7 @@
         <v>34</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="D403" s="0" t="s">
         <v>123</v>
@@ -37654,7 +37660,7 @@
         <v>60</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="J403" s="11"/>
       <c r="K403" s="0" t="s">
@@ -37723,13 +37729,13 @@
         <v>49</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D404" s="0" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="E404" s="0" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="F404" s="0" t="s">
         <v>200</v>
@@ -37806,7 +37812,7 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>63</v>
@@ -37892,7 +37898,7 @@
         <v>34</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>36</v>
@@ -37907,14 +37913,14 @@
         <v>38</v>
       </c>
       <c r="H406" s="0" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J406" s="11"/>
       <c r="K406" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L406" s="0" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="M406" s="0" t="s">
         <v>39</v>
@@ -37979,7 +37985,7 @@
         <v>34</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>36</v>
@@ -37994,14 +38000,14 @@
         <v>38</v>
       </c>
       <c r="H407" s="0" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J407" s="11"/>
       <c r="K407" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L407" s="0" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="M407" s="0" t="s">
         <v>39</v>
@@ -38066,13 +38072,13 @@
         <v>49</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D408" s="0" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="E408" s="0" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="F408" s="0" t="s">
         <v>65</v>
@@ -38149,7 +38155,7 @@
         <v>49</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>322</v>
@@ -38232,13 +38238,13 @@
         <v>34</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>315</v>
       </c>
       <c r="E410" s="0" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="F410" s="0" t="s">
         <v>93</v>
@@ -38247,14 +38253,14 @@
         <v>38</v>
       </c>
       <c r="H410" s="0" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J410" s="11"/>
       <c r="K410" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L410" s="0" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="M410" s="0" t="s">
         <v>39</v>
@@ -38319,7 +38325,7 @@
         <v>49</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>382</v>
@@ -38402,13 +38408,13 @@
         <v>49</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="D412" s="0" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="F412" s="0" t="s">
         <v>150</v>
@@ -38485,7 +38491,7 @@
         <v>61</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>51</v>
@@ -38500,7 +38506,7 @@
         <v>168</v>
       </c>
       <c r="H413" s="0" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J413" s="11"/>
       <c r="K413" s="0" t="s">
@@ -38569,13 +38575,13 @@
         <v>61</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E414" s="0" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="F414" s="0" t="s">
         <v>327</v>
@@ -38584,7 +38590,7 @@
         <v>327</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="J414" s="11">
         <v>46373.125</v>
@@ -38655,7 +38661,7 @@
         <v>61</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>77</v>
@@ -38670,7 +38676,7 @@
         <v>506</v>
       </c>
       <c r="H415" s="0" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="J415" s="11"/>
       <c r="K415" s="0" t="s">
@@ -38742,13 +38748,13 @@
         <v>61</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D416" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E416" s="0" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="F416" s="0" t="s">
         <v>169</v>
@@ -38831,7 +38837,7 @@
         <v>61</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>77</v>
@@ -38846,7 +38852,7 @@
         <v>54</v>
       </c>
       <c r="H417" s="0" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="J417" s="11">
         <v>46373.125</v>
@@ -38917,13 +38923,13 @@
         <v>61</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E418" s="0" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="F418" s="0" t="s">
         <v>257</v>
@@ -38932,7 +38938,7 @@
         <v>257</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="J418" s="11"/>
       <c r="K418" s="0" t="s">
@@ -39001,7 +39007,7 @@
         <v>61</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>51</v>
@@ -39016,7 +39022,7 @@
         <v>150</v>
       </c>
       <c r="H419" s="0" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J419" s="11">
         <v>46373.125</v>
@@ -39087,13 +39093,13 @@
         <v>61</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D420" s="0" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E420" s="0" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="F420" s="0" t="s">
         <v>209</v>
@@ -39102,7 +39108,7 @@
         <v>209</v>
       </c>
       <c r="H420" s="0" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="J420" s="11"/>
       <c r="K420" s="0" t="s">
@@ -39171,7 +39177,7 @@
         <v>61</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>249</v>
@@ -39180,13 +39186,13 @@
         <v>37</v>
       </c>
       <c r="F421" s="0" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G421" s="0" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="H421" s="0" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J421" s="11"/>
       <c r="K421" s="0" t="s">
@@ -39255,7 +39261,7 @@
         <v>61</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>259</v>
@@ -39270,7 +39276,7 @@
         <v>93</v>
       </c>
       <c r="H422" s="0" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="J422" s="11"/>
       <c r="K422" s="0" t="s">
@@ -39339,13 +39345,13 @@
         <v>61</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>259</v>
       </c>
       <c r="E423" s="0" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="F423" s="0" t="s">
         <v>168</v>
@@ -39354,7 +39360,7 @@
         <v>168</v>
       </c>
       <c r="H423" s="0" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="J423" s="11"/>
       <c r="K423" s="0" t="s">
@@ -39426,7 +39432,7 @@
         <v>61</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D424" s="0" t="s">
         <v>249</v>
@@ -39513,13 +39519,13 @@
         <v>61</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D425" s="0" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="E425" s="0" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="F425" s="0" t="s">
         <v>294</v>
@@ -39599,7 +39605,7 @@
         <v>61</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>259</v>
@@ -39614,7 +39620,7 @@
         <v>526</v>
       </c>
       <c r="H426" s="0" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="J426" s="11"/>
       <c r="K426" s="0" t="s">
@@ -39686,10 +39692,10 @@
         <v>61</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="D427" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E427" s="0" t="s">
         <v>73</v>
@@ -39701,7 +39707,7 @@
         <v>169</v>
       </c>
       <c r="H427" s="0" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="J427" s="11">
         <v>46373.125</v>
@@ -39772,7 +39778,7 @@
         <v>61</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>259</v>
@@ -39856,7 +39862,7 @@
         <v>61</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>259</v>
@@ -39871,7 +39877,7 @@
         <v>54</v>
       </c>
       <c r="H429" s="0" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="J429" s="11"/>
       <c r="K429" s="0" t="s">
@@ -39940,22 +39946,22 @@
         <v>61</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D430" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E430" s="0" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="F430" s="0" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G430" s="0" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="H430" s="0" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="J430" s="11">
         <v>46373.125</v>
@@ -40026,7 +40032,7 @@
         <v>61</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>259</v>
@@ -40041,7 +40047,7 @@
         <v>74</v>
       </c>
       <c r="H431" s="0" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="J431" s="11"/>
       <c r="K431" s="0" t="s">
@@ -40110,7 +40116,7 @@
         <v>61</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>259</v>
@@ -40125,7 +40131,7 @@
         <v>526</v>
       </c>
       <c r="H432" s="0" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="J432" s="11"/>
       <c r="K432" s="0" t="s">
@@ -40197,10 +40203,10 @@
         <v>61</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="D433" s="0" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E433" s="0" t="s">
         <v>87</v>
@@ -40212,7 +40218,7 @@
         <v>169</v>
       </c>
       <c r="H433" s="0" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="J433" s="11">
         <v>46373.125</v>
@@ -40283,7 +40289,7 @@
         <v>61</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>259</v>
@@ -40367,7 +40373,7 @@
         <v>61</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>162</v>
@@ -40382,7 +40388,7 @@
         <v>176</v>
       </c>
       <c r="H435" s="0" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="J435" s="11"/>
       <c r="K435" s="0" t="s">
@@ -40451,13 +40457,13 @@
         <v>61</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E436" s="0" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="F436" s="0" t="s">
         <v>484</v>
@@ -40466,7 +40472,7 @@
         <v>484</v>
       </c>
       <c r="H436" s="0" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="J436" s="11">
         <v>46373.125</v>
@@ -40537,7 +40543,7 @@
         <v>61</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D437" s="0" t="s">
         <v>162</v>
@@ -40552,7 +40558,7 @@
         <v>500</v>
       </c>
       <c r="H437" s="0" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="J437" s="11"/>
       <c r="K437" s="0" t="s">
@@ -40621,13 +40627,13 @@
         <v>61</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E438" s="0" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="F438" s="0" t="s">
         <v>327</v>
@@ -40636,7 +40642,7 @@
         <v>327</v>
       </c>
       <c r="H438" s="0" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="J438" s="11"/>
       <c r="K438" s="0" t="s">
@@ -40708,7 +40714,7 @@
         <v>61</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>162</v>
@@ -40723,14 +40729,14 @@
         <v>327</v>
       </c>
       <c r="H439" s="0" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="J439" s="11"/>
       <c r="K439" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L439" s="0" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M439" s="0" t="s">
         <v>39</v>
@@ -40786,25 +40792,25 @@
     </row>
     <row r="440">
       <c r="A440" s="0" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B440" s="0" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D440" s="0" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="E440" s="0" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="F440" s="0" t="s">
         <v>300</v>
       </c>
       <c r="G440" s="0" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="J440" s="11">
         <v>46383.125</v>
@@ -40837,7 +40843,7 @@
         <v>45</v>
       </c>
       <c r="AC440" s="0" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="AD440" s="11">
         <v>46203.65469700231</v>
@@ -40869,22 +40875,22 @@
         <v>621</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E441" s="0" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="F441" s="0" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G441" s="0" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="H441" s="0" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J441" s="11">
         <v>46365.125</v>
@@ -40949,19 +40955,19 @@
     </row>
     <row r="442">
       <c r="A442" s="0" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B442" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="D442" s="0" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E442" s="0" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F442" s="0" t="s">
         <v>208</v>
@@ -40970,7 +40976,7 @@
         <v>209</v>
       </c>
       <c r="H442" s="0" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J442" s="11">
         <v>46365.125</v>
@@ -41041,13 +41047,13 @@
         <v>34</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E443" s="0" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="F443" s="0" t="s">
         <v>85</v>
@@ -41124,7 +41130,7 @@
         <v>34</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>36</v>
@@ -41207,7 +41213,7 @@
         <v>34</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>123</v>
@@ -41222,7 +41228,7 @@
         <v>74</v>
       </c>
       <c r="H445" s="0" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="J445" s="11">
         <v>46387.125</v>
@@ -41293,7 +41299,7 @@
         <v>34</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>123</v>
@@ -41308,7 +41314,7 @@
         <v>74</v>
       </c>
       <c r="H446" s="0" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="J446" s="11">
         <v>46326.125</v>
@@ -41317,7 +41323,7 @@
         <v>114</v>
       </c>
       <c r="L446" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M446" s="0" t="s">
         <v>39</v>
@@ -41379,7 +41385,7 @@
         <v>34</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>51</v>
@@ -41394,7 +41400,7 @@
         <v>526</v>
       </c>
       <c r="H447" s="0" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="J447" s="11">
         <v>46326.125</v>
@@ -41403,7 +41409,7 @@
         <v>114</v>
       </c>
       <c r="L447" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M447" s="0" t="s">
         <v>39</v>
@@ -41465,13 +41471,13 @@
         <v>34</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E448" s="0" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="F448" s="0" t="s">
         <v>131</v>
@@ -41549,13 +41555,13 @@
         <v>34</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>179</v>
       </c>
       <c r="E449" s="0" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="F449" s="0" t="s">
         <v>149</v>
@@ -41564,7 +41570,7 @@
         <v>149</v>
       </c>
       <c r="H449" s="0" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="J449" s="11"/>
       <c r="K449" s="0" t="s">
@@ -41633,13 +41639,13 @@
         <v>61</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D450" s="0" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="E450" s="0" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="F450" s="0" t="s">
         <v>407</v>
@@ -41648,7 +41654,7 @@
         <v>407</v>
       </c>
       <c r="H450" s="0" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="J450" s="11"/>
       <c r="K450" s="0" t="s">
@@ -41714,7 +41720,7 @@
         <v>61</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>77</v>
@@ -41729,7 +41735,7 @@
         <v>327</v>
       </c>
       <c r="H451" s="0" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="J451" s="11">
         <v>46406.125</v>
@@ -41800,13 +41806,13 @@
         <v>61</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D452" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E452" s="0" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="F452" s="0" t="s">
         <v>79</v>
@@ -41815,7 +41821,7 @@
         <v>231</v>
       </c>
       <c r="H452" s="0" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="J452" s="11">
         <v>46407.125</v>
@@ -41886,7 +41892,7 @@
         <v>61</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>249</v>
@@ -41901,7 +41907,7 @@
         <v>134</v>
       </c>
       <c r="H453" s="0" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="J453" s="11">
         <v>46407.125</v>
@@ -41972,7 +41978,7 @@
         <v>61</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>249</v>
@@ -41987,7 +41993,7 @@
         <v>134</v>
       </c>
       <c r="H454" s="0" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="J454" s="11">
         <v>46407.125</v>
@@ -42058,13 +42064,13 @@
         <v>61</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D455" s="0" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E455" s="0" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F455" s="0" t="s">
         <v>54</v>
@@ -42073,7 +42079,7 @@
         <v>54</v>
       </c>
       <c r="H455" s="0" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="J455" s="11">
         <v>46406.125</v>
@@ -42144,7 +42150,7 @@
         <v>61</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>259</v>
@@ -42159,7 +42165,7 @@
         <v>74</v>
       </c>
       <c r="H456" s="0" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="J456" s="11">
         <v>46373.125</v>
@@ -42230,7 +42236,7 @@
         <v>49</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>51</v>
@@ -42316,13 +42322,13 @@
         <v>226</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D458" s="0" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E458" s="0" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="F458" s="0" t="s">
         <v>142</v>
@@ -42331,7 +42337,7 @@
         <v>142</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="J458" s="11">
         <v>46398.125</v>
@@ -42393,19 +42399,19 @@
     </row>
     <row r="459">
       <c r="A459" s="0" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B459" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D459" s="0" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="E459" s="0" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="F459" s="0" t="s">
         <v>200</v>
@@ -42420,7 +42426,7 @@
         <v>114</v>
       </c>
       <c r="L459" s="0" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M459" s="0" t="s">
         <v>39</v>
@@ -42444,7 +42450,7 @@
         <v>45</v>
       </c>
       <c r="AC459" s="0" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="AD459" s="11">
         <v>46219.55652277778</v>
@@ -42476,7 +42482,7 @@
         <v>49</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>376</v>
@@ -42491,7 +42497,7 @@
         <v>332</v>
       </c>
       <c r="H460" s="0" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="J460" s="11">
         <v>46402.125</v>
@@ -42562,7 +42568,7 @@
         <v>61</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>51</v>
@@ -42577,7 +42583,7 @@
         <v>79</v>
       </c>
       <c r="H461" s="0" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="J461" s="11">
         <v>46346.125</v>
@@ -42648,13 +42654,13 @@
         <v>61</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D462" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E462" s="0" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="F462" s="0" t="s">
         <v>332</v>
@@ -42663,7 +42669,7 @@
         <v>53</v>
       </c>
       <c r="H462" s="0" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="J462" s="11">
         <v>46346.125</v>
@@ -42734,7 +42740,7 @@
         <v>61</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>249</v>
@@ -42749,7 +42755,7 @@
         <v>208</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="J463" s="11"/>
       <c r="K463" s="0" t="s">
@@ -42818,7 +42824,7 @@
         <v>61</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>51</v>
@@ -42833,7 +42839,7 @@
         <v>150</v>
       </c>
       <c r="H464" s="0" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="J464" s="11">
         <v>46407.125</v>
@@ -42904,7 +42910,7 @@
         <v>61</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>259</v>
@@ -42919,7 +42925,7 @@
         <v>231</v>
       </c>
       <c r="H465" s="0" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="J465" s="11">
         <v>46407.125</v>
@@ -42990,7 +42996,7 @@
         <v>61</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>259</v>
@@ -43005,7 +43011,7 @@
         <v>231</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="J466" s="11">
         <v>46407.125</v>
@@ -43070,13 +43076,13 @@
     </row>
     <row r="467">
       <c r="A467" s="0" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B467" s="0" t="s">
         <v>599</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>212</v>
@@ -43156,13 +43162,13 @@
         <v>599</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="D468" s="0" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="E468" s="0" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="F468" s="0" t="s">
         <v>428</v>
@@ -43236,13 +43242,13 @@
         <v>49</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D469" s="0" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="E469" s="0" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="F469" s="0" t="s">
         <v>98</v>
@@ -43322,13 +43328,13 @@
         <v>34</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D470" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E470" s="0" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="F470" s="0" t="s">
         <v>38</v>
@@ -43337,7 +43343,7 @@
         <v>38</v>
       </c>
       <c r="H470" s="0" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="J470" s="11"/>
       <c r="K470" s="0" t="s">
@@ -43406,13 +43412,13 @@
         <v>49</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="D471" s="0" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E471" s="0" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="F471" s="0" t="s">
         <v>137</v>
@@ -43489,7 +43495,7 @@
         <v>49</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>339</v>
@@ -43572,7 +43578,7 @@
         <v>49</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>339</v>
@@ -43655,7 +43661,7 @@
         <v>34</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>249</v>
@@ -43670,7 +43676,7 @@
         <v>38</v>
       </c>
       <c r="H474" s="0" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="J474" s="11">
         <v>46362.125</v>
@@ -43741,7 +43747,7 @@
         <v>34</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="D475" s="0" t="s">
         <v>249</v>
@@ -43756,7 +43762,7 @@
         <v>38</v>
       </c>
       <c r="H475" s="0" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="J475" s="11">
         <v>46362.125</v>
@@ -43827,7 +43833,7 @@
         <v>49</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>360</v>
@@ -43910,13 +43916,13 @@
         <v>49</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="D477" s="0" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="E477" s="0" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="F477" s="0" t="s">
         <v>257</v>
@@ -43993,13 +43999,13 @@
         <v>49</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D478" s="0" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="E478" s="0" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F478" s="0" t="s">
         <v>131</v>
@@ -44076,13 +44082,13 @@
         <v>49</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="D479" s="0" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="E479" s="0" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="F479" s="0" t="s">
         <v>294</v>
@@ -44159,13 +44165,13 @@
         <v>61</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D480" s="0" t="s">
         <v>508</v>
       </c>
       <c r="E480" s="0" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="F480" s="0" t="s">
         <v>105</v>
@@ -44237,19 +44243,19 @@
     </row>
     <row r="481">
       <c r="A481" s="0" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B481" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D481" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E481" s="0" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F481" s="0" t="s">
         <v>293</v>
@@ -44258,7 +44264,7 @@
         <v>293</v>
       </c>
       <c r="H481" s="0" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="J481" s="11">
         <v>46372.125</v>
@@ -44329,19 +44335,19 @@
         <v>34</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>565</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="F482" s="0" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="G482" s="0" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="H482" s="0" t="s">
         <v>201</v>
@@ -44415,19 +44421,19 @@
         <v>34</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D483" s="0" t="s">
         <v>565</v>
       </c>
       <c r="E483" s="0" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="F483" s="0" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="G483" s="0" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="H483" s="0" t="s">
         <v>201</v>
@@ -44501,7 +44507,7 @@
         <v>226</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>508</v>
@@ -44575,19 +44581,19 @@
     </row>
     <row r="485">
       <c r="A485" s="0" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B485" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D485" s="0" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="E485" s="0" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="F485" s="0" t="s">
         <v>294</v>
@@ -44623,7 +44629,7 @@
         <v>45</v>
       </c>
       <c r="AC485" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AD485" s="11">
         <v>46301.476280462964</v>
@@ -44649,19 +44655,19 @@
     </row>
     <row r="486">
       <c r="A486" s="0" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B486" s="0" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D486" s="0" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="E486" s="0" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="F486" s="0" t="s">
         <v>168</v>
@@ -44674,7 +44680,7 @@
         <v>40</v>
       </c>
       <c r="L486" s="0" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="M486" s="0" t="s">
         <v>39</v>
@@ -44698,7 +44704,7 @@
         <v>44</v>
       </c>
       <c r="AC486" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AD486" s="11">
         <v>46303.38590450231</v>
@@ -44716,19 +44722,19 @@
     </row>
     <row r="487">
       <c r="A487" s="0" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B487" s="0" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="E487" s="0" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="F487" s="0" t="s">
         <v>169</v>
@@ -44741,7 +44747,7 @@
         <v>40</v>
       </c>
       <c r="L487" s="0" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="M487" s="0" t="s">
         <v>39</v>
@@ -44765,7 +44771,7 @@
         <v>44</v>
       </c>
       <c r="AC487" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AD487" s="11">
         <v>46303.38891412037</v>
@@ -44783,19 +44789,19 @@
     </row>
     <row r="488">
       <c r="A488" s="0" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B488" s="0" t="s">
         <v>599</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D488" s="0" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E488" s="0" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="F488" s="0" t="s">
         <v>93</v>
@@ -44808,7 +44814,7 @@
         <v>40</v>
       </c>
       <c r="L488" s="0" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="M488" s="0" t="s">
         <v>39</v>
@@ -44892,28 +44898,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -44921,10 +44927,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>61</v>
@@ -44936,16 +44942,16 @@
         <v>46316</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="G2" s="11">
         <v>46496.125</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>214</v>
@@ -44953,10 +44959,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>61</v>
@@ -44974,10 +44980,10 @@
         <v>46495.125</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>214</v>
@@ -44985,10 +44991,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>621</v>
@@ -45006,10 +45012,10 @@
         <v>46495.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>625</v>
@@ -45017,10 +45023,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>621</v>
@@ -45032,16 +45038,16 @@
         <v>46315</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G5" s="11">
         <v>46495.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>625</v>
@@ -45049,10 +45055,10 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>61</v>
@@ -45064,16 +45070,16 @@
         <v>46314</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="G6" s="11">
         <v>46494.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>214</v>
@@ -45081,10 +45087,10 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>621</v>
@@ -45102,10 +45108,10 @@
         <v>46491.125</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>625</v>
@@ -45113,13 +45119,13 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>30</v>
@@ -45134,24 +45140,24 @@
         <v>46483.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>29</v>
@@ -45160,27 +45166,27 @@
         <v>46303</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G9" s="11">
         <v>46483.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>621</v>
@@ -45198,10 +45204,10 @@
         <v>46480.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>625</v>
@@ -45209,10 +45215,10 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>226</v>
@@ -45230,10 +45236,10 @@
         <v>46476.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>226</v>
@@ -45241,10 +45247,10 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>226</v>
@@ -45256,16 +45262,16 @@
         <v>46296</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G12" s="11">
         <v>46476.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>226</v>
@@ -45273,10 +45279,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>34</v>
@@ -45294,10 +45300,10 @@
         <v>46474.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>202</v>
@@ -45305,10 +45311,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>34</v>
@@ -45326,10 +45332,10 @@
         <v>46474.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>202</v>
@@ -45337,10 +45343,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>621</v>
@@ -45358,10 +45364,10 @@
         <v>46474.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>625</v>
@@ -45369,10 +45375,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>621</v>
@@ -45384,16 +45390,16 @@
         <v>46294</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G16" s="11">
         <v>46474.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>625</v>
@@ -45401,10 +45407,10 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>621</v>
@@ -45422,10 +45428,10 @@
         <v>46474.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>625</v>
@@ -45433,10 +45439,10 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>621</v>
@@ -45448,16 +45454,16 @@
         <v>46294</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G18" s="11">
         <v>46474.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>625</v>
@@ -45465,10 +45471,10 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>61</v>
@@ -45480,16 +45486,16 @@
         <v>46289</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="G19" s="11">
         <v>46469.125</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="J19" s="0" t="s">
         <v>67</v>
@@ -45497,10 +45503,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>61</v>
@@ -45518,10 +45524,10 @@
         <v>46469.125</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>67</v>
@@ -45529,10 +45535,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>621</v>
@@ -45550,10 +45556,10 @@
         <v>46455.125</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J21" s="0" t="s">
         <v>625</v>
@@ -45561,10 +45567,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>621</v>
@@ -45576,16 +45582,16 @@
         <v>46275</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G22" s="11">
         <v>46455.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>625</v>
@@ -45593,13 +45599,13 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>30</v>
@@ -45614,24 +45620,24 @@
         <v>46449.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>29</v>
@@ -45640,30 +45646,30 @@
         <v>46269</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="G24" s="11">
         <v>46449.125</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>30</v>
@@ -45678,13 +45684,13 @@
         <v>46268</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="26">
@@ -45692,7 +45698,7 @@
         <v>534</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>34</v>
@@ -45704,19 +45710,19 @@
         <v>46267</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="G26" s="11">
         <v>46447.125</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="27">
@@ -45724,7 +45730,7 @@
         <v>534</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>34</v>
@@ -45742,21 +45748,21 @@
         <v>46447.125</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>61</v>
@@ -45774,10 +45780,10 @@
         <v>46314</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>214</v>
@@ -45785,10 +45791,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>61</v>
@@ -45806,10 +45812,10 @@
         <v>46446.125</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>214</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="1091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1089">
   <si>
     <t>Geração:</t>
   </si>
@@ -1921,12 +1921,6 @@
   </si>
   <si>
     <t>RBI8D41</t>
-  </si>
-  <si>
-    <t>Documento CRLV aguardando validação</t>
-  </si>
-  <si>
-    <t>AV</t>
   </si>
   <si>
     <t>FIXO POLIGUINDASTE</t>
@@ -3477,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46322.74272458333</v>
+        <v>46323.35050244213</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -25551,18 +25545,20 @@
       <c r="H260" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="J260" s="11"/>
+      <c r="J260" s="11">
+        <v>46439.125</v>
+      </c>
       <c r="K260" s="0" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="L260" s="0" t="s">
-        <v>636</v>
+        <v>39</v>
       </c>
       <c r="M260" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N260" s="0" t="s">
-        <v>637</v>
+        <v>43</v>
       </c>
       <c r="O260" s="11">
         <v>46645.125</v>
@@ -25571,7 +25567,7 @@
         <v>43</v>
       </c>
       <c r="R260" s="11">
-        <v>46388.125</v>
+        <v>46504.125</v>
       </c>
       <c r="T260" s="0" t="s">
         <v>44</v>
@@ -25612,13 +25608,13 @@
     </row>
     <row r="261">
       <c r="A261" s="0" t="s">
+        <v>636</v>
+      </c>
+      <c r="B261" s="0" t="s">
+        <v>637</v>
+      </c>
+      <c r="C261" s="0" t="s">
         <v>638</v>
-      </c>
-      <c r="B261" s="0" t="s">
-        <v>639</v>
-      </c>
-      <c r="C261" s="0" t="s">
-        <v>640</v>
       </c>
       <c r="D261" s="0" t="s">
         <v>416</v>
@@ -25630,14 +25626,14 @@
         <v>479</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="J261" s="11"/>
       <c r="K261" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L261" s="0" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="M261" s="0" t="s">
         <v>39</v>
@@ -25658,7 +25654,7 @@
         <v>45</v>
       </c>
       <c r="AC261" s="0" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AD261" s="11">
         <v>45817.61092795139</v>
@@ -25684,32 +25680,32 @@
     </row>
     <row r="262">
       <c r="A262" s="0" t="s">
+        <v>642</v>
+      </c>
+      <c r="B262" s="0" t="s">
+        <v>637</v>
+      </c>
+      <c r="C262" s="0" t="s">
+        <v>643</v>
+      </c>
+      <c r="D262" s="0" t="s">
         <v>644</v>
       </c>
-      <c r="B262" s="0" t="s">
-        <v>639</v>
-      </c>
-      <c r="C262" s="0" t="s">
-        <v>645</v>
-      </c>
-      <c r="D262" s="0" t="s">
-        <v>646</v>
-      </c>
       <c r="E262" s="0" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F262" s="0" t="s">
         <v>169</v>
       </c>
       <c r="G262" s="0" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="J262" s="11"/>
       <c r="K262" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L262" s="0" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="M262" s="0" t="s">
         <v>39</v>
@@ -25736,7 +25732,7 @@
         <v>45</v>
       </c>
       <c r="AC262" s="0" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AD262" s="11">
         <v>45817.61552398148</v>
@@ -25768,7 +25764,7 @@
         <v>49</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D263" s="0" t="s">
         <v>313</v>
@@ -25783,7 +25779,7 @@
         <v>131</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="J263" s="11">
         <v>46411.125</v>
@@ -25854,7 +25850,7 @@
         <v>49</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D264" s="0" t="s">
         <v>311</v>
@@ -25866,10 +25862,10 @@
         <v>131</v>
       </c>
       <c r="G264" s="0" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="J264" s="11">
         <v>46411.125</v>
@@ -25940,13 +25936,13 @@
         <v>61</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D265" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F265" s="0" t="s">
         <v>65</v>
@@ -25955,7 +25951,7 @@
         <v>65</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="J265" s="11">
         <v>46357.125</v>
@@ -26026,7 +26022,7 @@
         <v>34</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D266" s="0" t="s">
         <v>162</v>
@@ -26041,14 +26037,14 @@
         <v>332</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="J266" s="11"/>
       <c r="K266" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L266" s="0" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="M266" s="0" t="s">
         <v>39</v>
@@ -26107,13 +26103,13 @@
         <v>49</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D267" s="0" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E267" s="0" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F267" s="0" t="s">
         <v>168</v>
@@ -26122,7 +26118,7 @@
         <v>168</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="J267" s="11">
         <v>46417.125</v>
@@ -26193,13 +26189,13 @@
         <v>34</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D268" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E268" s="0" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F268" s="0" t="s">
         <v>200</v>
@@ -26215,7 +26211,7 @@
         <v>40</v>
       </c>
       <c r="L268" s="0" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="M268" s="0" t="s">
         <v>39</v>
@@ -26277,13 +26273,13 @@
         <v>49</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D269" s="0" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E269" s="0" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F269" s="0" t="s">
         <v>74</v>
@@ -26363,7 +26359,7 @@
         <v>49</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D270" s="0" t="s">
         <v>362</v>
@@ -26449,7 +26445,7 @@
         <v>49</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D271" s="0" t="s">
         <v>364</v>
@@ -26529,13 +26525,13 @@
     </row>
     <row r="272">
       <c r="A272" s="0" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B272" s="0" t="s">
         <v>49</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D272" s="0" t="s">
         <v>563</v>
@@ -26550,7 +26546,7 @@
         <v>231</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J272" s="11">
         <v>46374.125</v>
@@ -26621,7 +26617,7 @@
         <v>34</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D273" s="0" t="s">
         <v>51</v>
@@ -26636,7 +26632,7 @@
         <v>74</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="J273" s="11"/>
       <c r="K273" s="0" t="s">
@@ -26705,7 +26701,7 @@
         <v>34</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D274" s="0" t="s">
         <v>123</v>
@@ -26789,7 +26785,7 @@
         <v>34</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D275" s="0" t="s">
         <v>123</v>
@@ -26873,7 +26869,7 @@
         <v>34</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D276" s="0" t="s">
         <v>72</v>
@@ -26957,7 +26953,7 @@
         <v>34</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D277" s="0" t="s">
         <v>72</v>
@@ -27041,7 +27037,7 @@
         <v>34</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D278" s="0" t="s">
         <v>51</v>
@@ -27125,13 +27121,13 @@
         <v>61</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D279" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F279" s="0" t="s">
         <v>168</v>
@@ -27140,7 +27136,7 @@
         <v>168</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="J279" s="11">
         <v>46373.125</v>
@@ -27211,7 +27207,7 @@
         <v>61</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D280" s="0" t="s">
         <v>36</v>
@@ -27226,7 +27222,7 @@
         <v>38</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="J280" s="11">
         <v>46373.125</v>
@@ -27297,7 +27293,7 @@
         <v>61</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D281" s="0" t="s">
         <v>36</v>
@@ -27312,7 +27308,7 @@
         <v>38</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="J281" s="11">
         <v>46373.125</v>
@@ -27383,13 +27379,13 @@
         <v>34</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D282" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F282" s="0" t="s">
         <v>168</v>
@@ -27398,7 +27394,7 @@
         <v>169</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="J282" s="11"/>
       <c r="K282" s="0" t="s">
@@ -27467,7 +27463,7 @@
         <v>34</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D283" s="0" t="s">
         <v>77</v>
@@ -27482,7 +27478,7 @@
         <v>137</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J283" s="11"/>
       <c r="K283" s="0" t="s">
@@ -27551,13 +27547,13 @@
         <v>34</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D284" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F284" s="0" t="s">
         <v>149</v>
@@ -27566,7 +27562,7 @@
         <v>149</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J284" s="11">
         <v>46365.125</v>
@@ -27637,13 +27633,13 @@
         <v>34</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D285" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F285" s="0" t="s">
         <v>149</v>
@@ -27652,7 +27648,7 @@
         <v>149</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J285" s="11"/>
       <c r="K285" s="0" t="s">
@@ -27721,7 +27717,7 @@
         <v>61</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D286" s="0" t="s">
         <v>162</v>
@@ -27736,7 +27732,7 @@
         <v>93</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="J286" s="11">
         <v>46373.125</v>
@@ -27807,13 +27803,13 @@
         <v>621</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D287" s="0" t="s">
         <v>604</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F287" s="0" t="s">
         <v>134</v>
@@ -27822,7 +27818,7 @@
         <v>526</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J287" s="11">
         <v>46372.125</v>
@@ -27893,7 +27889,7 @@
         <v>61</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D288" s="0" t="s">
         <v>249</v>
@@ -27977,7 +27973,7 @@
         <v>49</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D289" s="0" t="s">
         <v>259</v>
@@ -28063,13 +28059,13 @@
         <v>61</v>
       </c>
       <c r="C290" s="0" t="s">
+        <v>697</v>
+      </c>
+      <c r="D290" s="0" t="s">
+        <v>698</v>
+      </c>
+      <c r="E290" s="0" t="s">
         <v>699</v>
-      </c>
-      <c r="D290" s="0" t="s">
-        <v>700</v>
-      </c>
-      <c r="E290" s="0" t="s">
-        <v>701</v>
       </c>
       <c r="F290" s="0" t="s">
         <v>74</v>
@@ -28149,7 +28145,7 @@
         <v>61</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D291" s="0" t="s">
         <v>259</v>
@@ -28233,7 +28229,7 @@
         <v>61</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D292" s="0" t="s">
         <v>259</v>
@@ -28319,10 +28315,10 @@
         <v>61</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D293" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E293" s="0" t="s">
         <v>73</v>
@@ -28334,7 +28330,7 @@
         <v>526</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="J293" s="11">
         <v>46361.125</v>
@@ -28405,7 +28401,7 @@
         <v>61</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D294" s="0" t="s">
         <v>259</v>
@@ -28420,7 +28416,7 @@
         <v>60</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="J294" s="11">
         <v>46326.125</v>
@@ -28429,7 +28425,7 @@
         <v>114</v>
       </c>
       <c r="L294" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="M294" s="0" t="s">
         <v>39</v>
@@ -28491,10 +28487,10 @@
         <v>61</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D295" s="0" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E295" s="0" t="s">
         <v>102</v>
@@ -28578,7 +28574,7 @@
         <v>61</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D296" s="0" t="s">
         <v>249</v>
@@ -28664,7 +28660,7 @@
         <v>49</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D297" s="0" t="s">
         <v>259</v>
@@ -28750,13 +28746,13 @@
         <v>61</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D298" s="0" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F298" s="0" t="s">
         <v>74</v>
@@ -28836,7 +28832,7 @@
         <v>61</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D299" s="0" t="s">
         <v>259</v>
@@ -28922,7 +28918,7 @@
         <v>61</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D300" s="0" t="s">
         <v>259</v>
@@ -29008,10 +29004,10 @@
         <v>61</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D301" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E301" s="0" t="s">
         <v>87</v>
@@ -29023,7 +29019,7 @@
         <v>526</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="J301" s="11">
         <v>46359.125</v>
@@ -29094,7 +29090,7 @@
         <v>61</v>
       </c>
       <c r="C302" s="0" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D302" s="0" t="s">
         <v>259</v>
@@ -29109,7 +29105,7 @@
         <v>60</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="J302" s="11">
         <v>46326.125</v>
@@ -29118,7 +29114,7 @@
         <v>114</v>
       </c>
       <c r="L302" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="M302" s="0" t="s">
         <v>39</v>
@@ -29180,10 +29176,10 @@
         <v>61</v>
       </c>
       <c r="C303" s="0" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D303" s="0" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E303" s="0" t="s">
         <v>97</v>
@@ -29267,7 +29263,7 @@
         <v>61</v>
       </c>
       <c r="C304" s="0" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D304" s="0" t="s">
         <v>51</v>
@@ -29282,7 +29278,7 @@
         <v>169</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="J304" s="11"/>
       <c r="K304" s="0" t="s">
@@ -29351,7 +29347,7 @@
         <v>61</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D305" s="0" t="s">
         <v>51</v>
@@ -29437,10 +29433,10 @@
         <v>61</v>
       </c>
       <c r="C306" s="0" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D306" s="0" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E306" s="0" t="s">
         <v>228</v>
@@ -29523,7 +29519,7 @@
         <v>61</v>
       </c>
       <c r="C307" s="0" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D307" s="0" t="s">
         <v>249</v>
@@ -29601,19 +29597,19 @@
     </row>
     <row r="308">
       <c r="A308" s="0" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B308" s="0" t="s">
         <v>49</v>
       </c>
       <c r="C308" s="0" t="s">
+        <v>724</v>
+      </c>
+      <c r="D308" s="0" t="s">
+        <v>725</v>
+      </c>
+      <c r="E308" s="0" t="s">
         <v>726</v>
-      </c>
-      <c r="D308" s="0" t="s">
-        <v>727</v>
-      </c>
-      <c r="E308" s="0" t="s">
-        <v>728</v>
       </c>
       <c r="F308" s="0" t="s">
         <v>93</v>
@@ -29622,7 +29618,7 @@
         <v>93</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="J308" s="11">
         <v>46370.125</v>
@@ -29693,7 +29689,7 @@
         <v>34</v>
       </c>
       <c r="C309" s="0" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D309" s="0" t="s">
         <v>162</v>
@@ -29708,7 +29704,7 @@
         <v>243</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="J309" s="11">
         <v>46367.125</v>
@@ -29776,7 +29772,7 @@
         <v>49</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D310" s="0" t="s">
         <v>311</v>
@@ -29791,7 +29787,7 @@
         <v>65</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="J310" s="11">
         <v>46415.125</v>
@@ -29862,7 +29858,7 @@
         <v>49</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D311" s="0" t="s">
         <v>313</v>
@@ -29877,7 +29873,7 @@
         <v>65</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="J311" s="11">
         <v>46415.125</v>
@@ -29948,13 +29944,13 @@
         <v>49</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D312" s="0" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="F312" s="0" t="s">
         <v>169</v>
@@ -29963,7 +29959,7 @@
         <v>169</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="J312" s="11">
         <v>46358.125</v>
@@ -30034,13 +30030,13 @@
         <v>49</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D313" s="0" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E313" s="0" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F313" s="0" t="s">
         <v>65</v>
@@ -30049,7 +30045,7 @@
         <v>65</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="J313" s="11">
         <v>46358.125</v>
@@ -30120,10 +30116,10 @@
         <v>49</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D314" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E314" s="0" t="s">
         <v>87</v>
@@ -30206,10 +30202,10 @@
         <v>49</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D315" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E315" s="0" t="s">
         <v>73</v>
@@ -30292,7 +30288,7 @@
         <v>61</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D316" s="0" t="s">
         <v>51</v>
@@ -30307,7 +30303,7 @@
         <v>74</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="J316" s="11"/>
       <c r="K316" s="0" t="s">
@@ -30376,7 +30372,7 @@
         <v>61</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D317" s="0" t="s">
         <v>36</v>
@@ -30391,7 +30387,7 @@
         <v>526</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="J317" s="11">
         <v>46373.125</v>
@@ -30462,7 +30458,7 @@
         <v>61</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D318" s="0" t="s">
         <v>36</v>
@@ -30477,7 +30473,7 @@
         <v>526</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="J318" s="11">
         <v>46373.125</v>
@@ -30548,7 +30544,7 @@
         <v>61</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D319" s="0" t="s">
         <v>249</v>
@@ -30634,7 +30630,7 @@
         <v>61</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D320" s="0" t="s">
         <v>249</v>
@@ -30720,7 +30716,7 @@
         <v>61</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D321" s="0" t="s">
         <v>249</v>
@@ -30806,7 +30802,7 @@
         <v>61</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D322" s="0" t="s">
         <v>249</v>
@@ -30892,13 +30888,13 @@
         <v>49</v>
       </c>
       <c r="C323" s="0" t="s">
+        <v>748</v>
+      </c>
+      <c r="D323" s="0" t="s">
+        <v>749</v>
+      </c>
+      <c r="E323" s="0" t="s">
         <v>750</v>
-      </c>
-      <c r="D323" s="0" t="s">
-        <v>751</v>
-      </c>
-      <c r="E323" s="0" t="s">
-        <v>752</v>
       </c>
       <c r="F323" s="0" t="s">
         <v>168</v>
@@ -30907,7 +30903,7 @@
         <v>168</v>
       </c>
       <c r="H323" s="0" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="J323" s="11">
         <v>46421.125</v>
@@ -30978,13 +30974,13 @@
         <v>49</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D324" s="0" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E324" s="0" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="F324" s="0" t="s">
         <v>168</v>
@@ -30993,7 +30989,7 @@
         <v>168</v>
       </c>
       <c r="H324" s="0" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="J324" s="11">
         <v>46421.125</v>
@@ -31064,7 +31060,7 @@
         <v>61</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D325" s="0" t="s">
         <v>249</v>
@@ -31148,7 +31144,7 @@
         <v>61</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D326" s="0" t="s">
         <v>249</v>
@@ -31232,7 +31228,7 @@
         <v>61</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D327" s="0" t="s">
         <v>259</v>
@@ -31247,7 +31243,7 @@
         <v>93</v>
       </c>
       <c r="H327" s="0" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="J327" s="11">
         <v>46373.125</v>
@@ -31318,7 +31314,7 @@
         <v>61</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D328" s="0" t="s">
         <v>259</v>
@@ -31333,7 +31329,7 @@
         <v>93</v>
       </c>
       <c r="H328" s="0" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="J328" s="11">
         <v>46373.125</v>
@@ -31404,13 +31400,13 @@
         <v>226</v>
       </c>
       <c r="C329" s="0" t="s">
+        <v>758</v>
+      </c>
+      <c r="D329" s="0" t="s">
+        <v>759</v>
+      </c>
+      <c r="E329" s="0" t="s">
         <v>760</v>
-      </c>
-      <c r="D329" s="0" t="s">
-        <v>761</v>
-      </c>
-      <c r="E329" s="0" t="s">
-        <v>762</v>
       </c>
       <c r="F329" s="0" t="s">
         <v>149</v>
@@ -31484,7 +31480,7 @@
         <v>61</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D330" s="0" t="s">
         <v>72</v>
@@ -31571,10 +31567,10 @@
         <v>61</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D331" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E331" s="0" t="s">
         <v>73</v>
@@ -31655,7 +31651,7 @@
         <v>34</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D332" s="0" t="s">
         <v>77</v>
@@ -31670,7 +31666,7 @@
         <v>137</v>
       </c>
       <c r="H332" s="0" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="J332" s="11">
         <v>46366.125</v>
@@ -31741,7 +31737,7 @@
         <v>34</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D333" s="0" t="s">
         <v>96</v>
@@ -31756,14 +31752,14 @@
         <v>74</v>
       </c>
       <c r="H333" s="0" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="J333" s="11"/>
       <c r="K333" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L333" s="0" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="M333" s="0" t="s">
         <v>39</v>
@@ -31825,7 +31821,7 @@
         <v>34</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D334" s="0" t="s">
         <v>96</v>
@@ -31840,7 +31836,7 @@
         <v>74</v>
       </c>
       <c r="H334" s="0" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="J334" s="11"/>
       <c r="K334" s="0" t="s">
@@ -31909,7 +31905,7 @@
         <v>49</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D335" s="0" t="s">
         <v>304</v>
@@ -31995,13 +31991,13 @@
         <v>49</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D336" s="0" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E336" s="0" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F336" s="0" t="s">
         <v>149</v>
@@ -32078,7 +32074,7 @@
         <v>49</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D337" s="0" t="s">
         <v>304</v>
@@ -32164,7 +32160,7 @@
         <v>49</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D338" s="0" t="s">
         <v>304</v>
@@ -32250,7 +32246,7 @@
         <v>34</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D339" s="0" t="s">
         <v>162</v>
@@ -32265,7 +32261,7 @@
         <v>506</v>
       </c>
       <c r="H339" s="0" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="J339" s="11"/>
       <c r="K339" s="0" t="s">
@@ -32334,7 +32330,7 @@
         <v>34</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D340" s="0" t="s">
         <v>140</v>
@@ -32349,7 +32345,7 @@
         <v>428</v>
       </c>
       <c r="H340" s="0" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="J340" s="11"/>
       <c r="K340" s="0" t="s">
@@ -32418,7 +32414,7 @@
         <v>61</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D341" s="0" t="s">
         <v>162</v>
@@ -32433,7 +32429,7 @@
         <v>54</v>
       </c>
       <c r="H341" s="0" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="J341" s="11">
         <v>46373.125</v>
@@ -32504,7 +32500,7 @@
         <v>61</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D342" s="0" t="s">
         <v>249</v>
@@ -32519,7 +32515,7 @@
         <v>526</v>
       </c>
       <c r="H342" s="0" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="J342" s="11">
         <v>46373.125</v>
@@ -32590,13 +32586,13 @@
         <v>226</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D343" s="0" t="s">
         <v>508</v>
       </c>
       <c r="E343" s="0" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="F343" s="0" t="s">
         <v>484</v>
@@ -32670,7 +32666,7 @@
         <v>61</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D344" s="0" t="s">
         <v>162</v>
@@ -32685,7 +32681,7 @@
         <v>54</v>
       </c>
       <c r="H344" s="0" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="J344" s="11">
         <v>46373.125</v>
@@ -32756,13 +32752,13 @@
         <v>61</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D345" s="0" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E345" s="0" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F345" s="0" t="s">
         <v>60</v>
@@ -32771,7 +32767,7 @@
         <v>134</v>
       </c>
       <c r="H345" s="0" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="J345" s="11">
         <v>46373.125</v>
@@ -32845,7 +32841,7 @@
         <v>61</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D346" s="0" t="s">
         <v>51</v>
@@ -32860,7 +32856,7 @@
         <v>131</v>
       </c>
       <c r="H346" s="0" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J346" s="11"/>
       <c r="K346" s="0" t="s">
@@ -32923,19 +32919,19 @@
     </row>
     <row r="347">
       <c r="A347" s="0" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B347" s="0" t="s">
+        <v>786</v>
+      </c>
+      <c r="C347" s="0" t="s">
+        <v>787</v>
+      </c>
+      <c r="D347" s="0" t="s">
         <v>788</v>
       </c>
-      <c r="C347" s="0" t="s">
-        <v>789</v>
-      </c>
-      <c r="D347" s="0" t="s">
-        <v>790</v>
-      </c>
       <c r="E347" s="0" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F347" s="0" t="s">
         <v>293</v>
@@ -32974,7 +32970,7 @@
         <v>45</v>
       </c>
       <c r="AC347" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AD347" s="11">
         <v>45847.61793511574</v>
@@ -33000,19 +32996,19 @@
     </row>
     <row r="348">
       <c r="A348" s="0" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B348" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="D348" s="0" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E348" s="0" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F348" s="0" t="s">
         <v>209</v>
@@ -33083,19 +33079,19 @@
     </row>
     <row r="349">
       <c r="A349" s="0" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B349" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D349" s="0" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E349" s="0" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F349" s="0" t="s">
         <v>208</v>
@@ -33166,19 +33162,19 @@
     </row>
     <row r="350">
       <c r="A350" s="0" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B350" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D350" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E350" s="0" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F350" s="0" t="s">
         <v>134</v>
@@ -33249,22 +33245,22 @@
     </row>
     <row r="351">
       <c r="A351" s="0" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B351" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C351" s="0" t="s">
+        <v>796</v>
+      </c>
+      <c r="D351" s="0" t="s">
+        <v>749</v>
+      </c>
+      <c r="E351" s="0" t="s">
+        <v>797</v>
+      </c>
+      <c r="F351" s="0" t="s">
         <v>798</v>
-      </c>
-      <c r="D351" s="0" t="s">
-        <v>751</v>
-      </c>
-      <c r="E351" s="0" t="s">
-        <v>799</v>
-      </c>
-      <c r="F351" s="0" t="s">
-        <v>800</v>
       </c>
       <c r="G351" s="0" t="s">
         <v>105</v>
@@ -33332,19 +33328,19 @@
     </row>
     <row r="352">
       <c r="A352" s="0" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B352" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D352" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E352" s="0" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F352" s="0" t="s">
         <v>208</v>
@@ -33421,13 +33417,13 @@
         <v>599</v>
       </c>
       <c r="C353" s="0" t="s">
+        <v>801</v>
+      </c>
+      <c r="D353" s="0" t="s">
+        <v>802</v>
+      </c>
+      <c r="E353" s="0" t="s">
         <v>803</v>
-      </c>
-      <c r="D353" s="0" t="s">
-        <v>804</v>
-      </c>
-      <c r="E353" s="0" t="s">
-        <v>805</v>
       </c>
       <c r="F353" s="0" t="s">
         <v>168</v>
@@ -33501,7 +33497,7 @@
         <v>34</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D354" s="0" t="s">
         <v>63</v>
@@ -33585,7 +33581,7 @@
         <v>49</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D355" s="0" t="s">
         <v>228</v>
@@ -33668,7 +33664,7 @@
         <v>49</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D356" s="0" t="s">
         <v>77</v>
@@ -33751,7 +33747,7 @@
         <v>61</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D357" s="0" t="s">
         <v>51</v>
@@ -33766,7 +33762,7 @@
         <v>79</v>
       </c>
       <c r="H357" s="0" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="J357" s="11">
         <v>46356.125</v>
@@ -33840,13 +33836,13 @@
         <v>61</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D358" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E358" s="0" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F358" s="0" t="s">
         <v>149</v>
@@ -33855,7 +33851,7 @@
         <v>149</v>
       </c>
       <c r="H358" s="0" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="J358" s="11">
         <v>46356.125</v>
@@ -33929,7 +33925,7 @@
         <v>226</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D359" s="0" t="s">
         <v>77</v>
@@ -33944,7 +33940,7 @@
         <v>184</v>
       </c>
       <c r="H359" s="0" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="J359" s="11">
         <v>46392.125</v>
@@ -34009,16 +34005,16 @@
     </row>
     <row r="360">
       <c r="A360" s="0" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B360" s="0" t="s">
         <v>226</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D360" s="0" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E360" s="0" t="s">
         <v>141</v>
@@ -34030,7 +34026,7 @@
         <v>428</v>
       </c>
       <c r="H360" s="0" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="J360" s="11">
         <v>46392.125</v>
@@ -34095,7 +34091,7 @@
         <v>61</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D361" s="0" t="s">
         <v>162</v>
@@ -34110,7 +34106,7 @@
         <v>332</v>
       </c>
       <c r="H361" s="0" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="J361" s="11">
         <v>46326.125</v>
@@ -34119,7 +34115,7 @@
         <v>114</v>
       </c>
       <c r="L361" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="M361" s="0" t="s">
         <v>39</v>
@@ -34181,7 +34177,7 @@
         <v>34</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D362" s="0" t="s">
         <v>77</v>
@@ -34196,7 +34192,7 @@
         <v>54</v>
       </c>
       <c r="H362" s="0" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="J362" s="11"/>
       <c r="K362" s="0" t="s">
@@ -34265,7 +34261,7 @@
         <v>34</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D363" s="0" t="s">
         <v>36</v>
@@ -34280,7 +34276,7 @@
         <v>60</v>
       </c>
       <c r="H363" s="0" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="J363" s="11"/>
       <c r="K363" s="0" t="s">
@@ -34349,7 +34345,7 @@
         <v>61</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D364" s="0" t="s">
         <v>51</v>
@@ -34427,19 +34423,19 @@
     </row>
     <row r="365">
       <c r="A365" s="0" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B365" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D365" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E365" s="0" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F365" s="0" t="s">
         <v>208</v>
@@ -34448,7 +34444,7 @@
         <v>209</v>
       </c>
       <c r="H365" s="0" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J365" s="11">
         <v>46372.125</v>
@@ -34519,13 +34515,13 @@
         <v>621</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D366" s="0" t="s">
         <v>604</v>
       </c>
       <c r="E366" s="0" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F366" s="0" t="s">
         <v>134</v>
@@ -34534,7 +34530,7 @@
         <v>526</v>
       </c>
       <c r="H366" s="0" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J366" s="11">
         <v>46372.125</v>
@@ -34599,19 +34595,19 @@
     </row>
     <row r="367">
       <c r="A367" s="0" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B367" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D367" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E367" s="0" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F367" s="0" t="s">
         <v>209</v>
@@ -34620,7 +34616,7 @@
         <v>209</v>
       </c>
       <c r="H367" s="0" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J367" s="11">
         <v>46348.125</v>
@@ -34691,13 +34687,13 @@
         <v>621</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D368" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E368" s="0" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F368" s="0" t="s">
         <v>134</v>
@@ -34706,7 +34702,7 @@
         <v>526</v>
       </c>
       <c r="H368" s="0" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="J368" s="11">
         <v>46356.125</v>
@@ -34777,7 +34773,7 @@
         <v>49</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D369" s="0" t="s">
         <v>198</v>
@@ -34860,10 +34856,10 @@
         <v>620</v>
       </c>
       <c r="B370" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D370" s="0" t="s">
         <v>63</v>
@@ -34917,7 +34913,7 @@
         <v>44</v>
       </c>
       <c r="AC370" s="0" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="AD370" s="11">
         <v>46037.467388136574</v>
@@ -34946,16 +34942,16 @@
         <v>620</v>
       </c>
       <c r="B371" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C371" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="D371" s="0" t="s">
+        <v>834</v>
+      </c>
+      <c r="E371" s="0" t="s">
         <v>835</v>
-      </c>
-      <c r="D371" s="0" t="s">
-        <v>836</v>
-      </c>
-      <c r="E371" s="0" t="s">
-        <v>837</v>
       </c>
       <c r="F371" s="0" t="s">
         <v>60</v>
@@ -34964,14 +34960,14 @@
         <v>134</v>
       </c>
       <c r="H371" s="0" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="J371" s="11"/>
       <c r="K371" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L371" s="0" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="M371" s="0" t="s">
         <v>39</v>
@@ -34992,7 +34988,7 @@
         <v>44</v>
       </c>
       <c r="AC371" s="0" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="AD371" s="11">
         <v>46038.63016152778</v>
@@ -35024,19 +35020,19 @@
         <v>49</v>
       </c>
       <c r="C372" s="0" t="s">
+        <v>837</v>
+      </c>
+      <c r="D372" s="0" t="s">
+        <v>838</v>
+      </c>
+      <c r="E372" s="0" t="s">
+        <v>838</v>
+      </c>
+      <c r="F372" s="0" t="s">
         <v>839</v>
       </c>
-      <c r="D372" s="0" t="s">
-        <v>840</v>
-      </c>
-      <c r="E372" s="0" t="s">
-        <v>840</v>
-      </c>
-      <c r="F372" s="0" t="s">
-        <v>841</v>
-      </c>
       <c r="G372" s="0" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="H372" s="0" t="s">
         <v>132</v>
@@ -35104,25 +35100,25 @@
     </row>
     <row r="373">
       <c r="A373" s="0" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B373" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D373" s="0" t="s">
         <v>508</v>
       </c>
       <c r="E373" s="0" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="F373" s="0" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G373" s="0" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="J373" s="11">
         <v>46409.125</v>
@@ -35155,7 +35151,7 @@
         <v>45</v>
       </c>
       <c r="AC373" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AD373" s="11">
         <v>46051.66783503472</v>
@@ -35181,25 +35177,25 @@
     </row>
     <row r="374">
       <c r="A374" s="0" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B374" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D374" s="0" t="s">
         <v>508</v>
       </c>
       <c r="E374" s="0" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="F374" s="0" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G374" s="0" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="J374" s="11">
         <v>46413.125</v>
@@ -35229,7 +35225,7 @@
         <v>45</v>
       </c>
       <c r="AC374" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AD374" s="11">
         <v>46052.455825081015</v>
@@ -35261,7 +35257,7 @@
         <v>34</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D375" s="0" t="s">
         <v>51</v>
@@ -35278,18 +35274,20 @@
       <c r="H375" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="J375" s="11"/>
+      <c r="J375" s="11">
+        <v>46420.125</v>
+      </c>
       <c r="K375" s="0" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="L375" s="0" t="s">
-        <v>636</v>
+        <v>39</v>
       </c>
       <c r="M375" s="0" t="s">
         <v>39</v>
       </c>
       <c r="N375" s="0" t="s">
-        <v>637</v>
+        <v>43</v>
       </c>
       <c r="O375" s="11">
         <v>46645.125</v>
@@ -35298,7 +35296,7 @@
         <v>43</v>
       </c>
       <c r="R375" s="11">
-        <v>46393.125</v>
+        <v>46504.125</v>
       </c>
       <c r="T375" s="0" t="s">
         <v>44</v>
@@ -35345,7 +35343,7 @@
         <v>34</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D376" s="0" t="s">
         <v>36</v>
@@ -35431,13 +35429,13 @@
         <v>61</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D377" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E377" s="0" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="F377" s="0" t="s">
         <v>200</v>
@@ -35514,13 +35512,13 @@
         <v>61</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D378" s="0" t="s">
         <v>212</v>
       </c>
       <c r="E378" s="0" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="F378" s="0" t="s">
         <v>200</v>
@@ -35591,25 +35589,25 @@
     </row>
     <row r="379">
       <c r="A379" s="0" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B379" s="0" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>565</v>
       </c>
       <c r="E379" s="0" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="F379" s="0" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G379" s="0" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="J379" s="11">
         <v>46401.125</v>
@@ -35642,7 +35640,7 @@
         <v>45</v>
       </c>
       <c r="AC379" s="0" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="AD379" s="11">
         <v>46104.56253545139</v>
@@ -35668,19 +35666,19 @@
     </row>
     <row r="380">
       <c r="A380" s="0" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B380" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E380" s="0" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F380" s="0" t="s">
         <v>209</v>
@@ -35689,7 +35687,7 @@
         <v>209</v>
       </c>
       <c r="H380" s="0" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J380" s="11">
         <v>46372.125</v>
@@ -35760,22 +35758,22 @@
         <v>621</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E381" s="0" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F381" s="0" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G381" s="0" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="H381" s="0" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J381" s="11">
         <v>46372.125</v>
@@ -35846,13 +35844,13 @@
         <v>61</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="D382" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E382" s="0" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="F382" s="0" t="s">
         <v>60</v>
@@ -35865,7 +35863,7 @@
         <v>40</v>
       </c>
       <c r="L382" s="0" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="M382" s="0" t="s">
         <v>39</v>
@@ -35921,19 +35919,19 @@
     </row>
     <row r="383">
       <c r="A383" s="0" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B383" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D383" s="0" t="s">
         <v>109</v>
       </c>
       <c r="E383" s="0" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F383" s="0" t="s">
         <v>209</v>
@@ -35942,7 +35940,7 @@
         <v>209</v>
       </c>
       <c r="H383" s="0" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="J383" s="11">
         <v>46362.125</v>
@@ -36013,7 +36011,7 @@
         <v>34</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D384" s="0" t="s">
         <v>198</v>
@@ -36099,13 +36097,13 @@
         <v>49</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="D385" s="0" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E385" s="0" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="F385" s="0" t="s">
         <v>243</v>
@@ -36114,7 +36112,7 @@
         <v>243</v>
       </c>
       <c r="H385" s="0" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="J385" s="11">
         <v>46413.125</v>
@@ -36185,13 +36183,13 @@
         <v>49</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D386" s="0" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="E386" s="0" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="F386" s="0" t="s">
         <v>53</v>
@@ -36200,7 +36198,7 @@
         <v>54</v>
       </c>
       <c r="H386" s="0" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="J386" s="11">
         <v>46357.125</v>
@@ -36271,7 +36269,7 @@
         <v>34</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D387" s="0" t="s">
         <v>162</v>
@@ -36286,7 +36284,7 @@
         <v>54</v>
       </c>
       <c r="H387" s="0" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="J387" s="11">
         <v>46361.125</v>
@@ -36357,7 +36355,7 @@
         <v>34</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D388" s="0" t="s">
         <v>51</v>
@@ -36372,7 +36370,7 @@
         <v>150</v>
       </c>
       <c r="H388" s="0" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="J388" s="11">
         <v>46365.125</v>
@@ -36443,7 +36441,7 @@
         <v>34</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>51</v>
@@ -36458,7 +36456,7 @@
         <v>134</v>
       </c>
       <c r="H389" s="0" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="J389" s="11">
         <v>46365.125</v>
@@ -36529,7 +36527,7 @@
         <v>34</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>36</v>
@@ -36544,7 +36542,7 @@
         <v>134</v>
       </c>
       <c r="H390" s="0" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="J390" s="11"/>
       <c r="K390" s="0" t="s">
@@ -36613,13 +36611,13 @@
         <v>49</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="D391" s="0" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E391" s="0" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="F391" s="0" t="s">
         <v>54</v>
@@ -36628,7 +36626,7 @@
         <v>54</v>
       </c>
       <c r="H391" s="0" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="J391" s="11">
         <v>46365.125</v>
@@ -36699,7 +36697,7 @@
         <v>49</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>322</v>
@@ -36714,7 +36712,7 @@
         <v>134</v>
       </c>
       <c r="H392" s="0" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="J392" s="11">
         <v>46362.125</v>
@@ -36785,13 +36783,13 @@
         <v>34</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E393" s="0" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="F393" s="0" t="s">
         <v>65</v>
@@ -36871,7 +36869,7 @@
         <v>34</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>36</v>
@@ -36957,7 +36955,7 @@
         <v>34</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>36</v>
@@ -37043,13 +37041,13 @@
         <v>34</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E396" s="0" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="F396" s="0" t="s">
         <v>428</v>
@@ -37058,7 +37056,7 @@
         <v>428</v>
       </c>
       <c r="H396" s="0" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="J396" s="11"/>
       <c r="K396" s="0" t="s">
@@ -37127,13 +37125,13 @@
         <v>34</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D397" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E397" s="0" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="F397" s="0" t="s">
         <v>134</v>
@@ -37142,7 +37140,7 @@
         <v>134</v>
       </c>
       <c r="H397" s="0" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="J397" s="11"/>
       <c r="K397" s="0" t="s">
@@ -37211,13 +37209,13 @@
         <v>34</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D398" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="F398" s="0" t="s">
         <v>169</v>
@@ -37298,7 +37296,7 @@
         <v>34</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>51</v>
@@ -37313,7 +37311,7 @@
         <v>332</v>
       </c>
       <c r="H399" s="0" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="J399" s="11">
         <v>46356.125</v>
@@ -37387,13 +37385,13 @@
         <v>34</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>140</v>
       </c>
       <c r="E400" s="0" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F400" s="0" t="s">
         <v>142</v>
@@ -37402,7 +37400,7 @@
         <v>142</v>
       </c>
       <c r="H400" s="0" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="J400" s="11"/>
       <c r="K400" s="0" t="s">
@@ -37474,13 +37472,13 @@
         <v>34</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E401" s="0" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="F401" s="0" t="s">
         <v>93</v>
@@ -37489,7 +37487,7 @@
         <v>93</v>
       </c>
       <c r="H401" s="0" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="J401" s="11"/>
       <c r="K401" s="0" t="s">
@@ -37561,7 +37559,7 @@
         <v>34</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>123</v>
@@ -37576,7 +37574,7 @@
         <v>60</v>
       </c>
       <c r="H402" s="0" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="J402" s="11"/>
       <c r="K402" s="0" t="s">
@@ -37645,7 +37643,7 @@
         <v>34</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D403" s="0" t="s">
         <v>123</v>
@@ -37660,7 +37658,7 @@
         <v>60</v>
       </c>
       <c r="H403" s="0" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="J403" s="11"/>
       <c r="K403" s="0" t="s">
@@ -37729,13 +37727,13 @@
         <v>49</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D404" s="0" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="E404" s="0" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="F404" s="0" t="s">
         <v>200</v>
@@ -37812,7 +37810,7 @@
         <v>34</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>63</v>
@@ -37898,7 +37896,7 @@
         <v>34</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>36</v>
@@ -37913,14 +37911,14 @@
         <v>38</v>
       </c>
       <c r="H406" s="0" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="J406" s="11"/>
       <c r="K406" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L406" s="0" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="M406" s="0" t="s">
         <v>39</v>
@@ -37985,7 +37983,7 @@
         <v>34</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>36</v>
@@ -38000,14 +37998,14 @@
         <v>38</v>
       </c>
       <c r="H407" s="0" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="J407" s="11"/>
       <c r="K407" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L407" s="0" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="M407" s="0" t="s">
         <v>39</v>
@@ -38072,13 +38070,13 @@
         <v>49</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D408" s="0" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="E408" s="0" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="F408" s="0" t="s">
         <v>65</v>
@@ -38155,7 +38153,7 @@
         <v>49</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>322</v>
@@ -38238,13 +38236,13 @@
         <v>34</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>315</v>
       </c>
       <c r="E410" s="0" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="F410" s="0" t="s">
         <v>93</v>
@@ -38253,14 +38251,14 @@
         <v>38</v>
       </c>
       <c r="H410" s="0" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="J410" s="11"/>
       <c r="K410" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L410" s="0" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="M410" s="0" t="s">
         <v>39</v>
@@ -38325,7 +38323,7 @@
         <v>49</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>382</v>
@@ -38408,13 +38406,13 @@
         <v>49</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="D412" s="0" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E412" s="0" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="F412" s="0" t="s">
         <v>150</v>
@@ -38491,7 +38489,7 @@
         <v>61</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>51</v>
@@ -38506,7 +38504,7 @@
         <v>168</v>
       </c>
       <c r="H413" s="0" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="J413" s="11"/>
       <c r="K413" s="0" t="s">
@@ -38575,13 +38573,13 @@
         <v>61</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E414" s="0" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="F414" s="0" t="s">
         <v>327</v>
@@ -38590,7 +38588,7 @@
         <v>327</v>
       </c>
       <c r="H414" s="0" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="J414" s="11">
         <v>46373.125</v>
@@ -38661,7 +38659,7 @@
         <v>61</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>77</v>
@@ -38676,7 +38674,7 @@
         <v>506</v>
       </c>
       <c r="H415" s="0" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="J415" s="11"/>
       <c r="K415" s="0" t="s">
@@ -38748,13 +38746,13 @@
         <v>61</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D416" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E416" s="0" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="F416" s="0" t="s">
         <v>169</v>
@@ -38837,7 +38835,7 @@
         <v>61</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>77</v>
@@ -38852,7 +38850,7 @@
         <v>54</v>
       </c>
       <c r="H417" s="0" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="J417" s="11">
         <v>46373.125</v>
@@ -38923,13 +38921,13 @@
         <v>61</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E418" s="0" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="F418" s="0" t="s">
         <v>257</v>
@@ -38938,7 +38936,7 @@
         <v>257</v>
       </c>
       <c r="H418" s="0" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="J418" s="11"/>
       <c r="K418" s="0" t="s">
@@ -39007,7 +39005,7 @@
         <v>61</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>51</v>
@@ -39022,7 +39020,7 @@
         <v>150</v>
       </c>
       <c r="H419" s="0" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="J419" s="11">
         <v>46373.125</v>
@@ -39093,13 +39091,13 @@
         <v>61</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="D420" s="0" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E420" s="0" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="F420" s="0" t="s">
         <v>209</v>
@@ -39108,7 +39106,7 @@
         <v>209</v>
       </c>
       <c r="H420" s="0" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J420" s="11"/>
       <c r="K420" s="0" t="s">
@@ -39177,7 +39175,7 @@
         <v>61</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>249</v>
@@ -39186,13 +39184,13 @@
         <v>37</v>
       </c>
       <c r="F421" s="0" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G421" s="0" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="H421" s="0" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="J421" s="11"/>
       <c r="K421" s="0" t="s">
@@ -39261,7 +39259,7 @@
         <v>61</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>259</v>
@@ -39276,7 +39274,7 @@
         <v>93</v>
       </c>
       <c r="H422" s="0" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="J422" s="11"/>
       <c r="K422" s="0" t="s">
@@ -39345,13 +39343,13 @@
         <v>61</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>259</v>
       </c>
       <c r="E423" s="0" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="F423" s="0" t="s">
         <v>168</v>
@@ -39360,7 +39358,7 @@
         <v>168</v>
       </c>
       <c r="H423" s="0" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="J423" s="11"/>
       <c r="K423" s="0" t="s">
@@ -39432,7 +39430,7 @@
         <v>61</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="D424" s="0" t="s">
         <v>249</v>
@@ -39519,13 +39517,13 @@
         <v>61</v>
       </c>
       <c r="C425" s="0" t="s">
+        <v>940</v>
+      </c>
+      <c r="D425" s="0" t="s">
+        <v>941</v>
+      </c>
+      <c r="E425" s="0" t="s">
         <v>942</v>
-      </c>
-      <c r="D425" s="0" t="s">
-        <v>943</v>
-      </c>
-      <c r="E425" s="0" t="s">
-        <v>944</v>
       </c>
       <c r="F425" s="0" t="s">
         <v>294</v>
@@ -39605,7 +39603,7 @@
         <v>61</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>259</v>
@@ -39620,7 +39618,7 @@
         <v>526</v>
       </c>
       <c r="H426" s="0" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="J426" s="11"/>
       <c r="K426" s="0" t="s">
@@ -39692,10 +39690,10 @@
         <v>61</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D427" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E427" s="0" t="s">
         <v>73</v>
@@ -39707,7 +39705,7 @@
         <v>169</v>
       </c>
       <c r="H427" s="0" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="J427" s="11">
         <v>46373.125</v>
@@ -39778,7 +39776,7 @@
         <v>61</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>259</v>
@@ -39862,7 +39860,7 @@
         <v>61</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>259</v>
@@ -39877,7 +39875,7 @@
         <v>54</v>
       </c>
       <c r="H429" s="0" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="J429" s="11"/>
       <c r="K429" s="0" t="s">
@@ -39946,22 +39944,22 @@
         <v>61</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="D430" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E430" s="0" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="F430" s="0" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G430" s="0" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="H430" s="0" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="J430" s="11">
         <v>46373.125</v>
@@ -40032,7 +40030,7 @@
         <v>61</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>259</v>
@@ -40047,7 +40045,7 @@
         <v>74</v>
       </c>
       <c r="H431" s="0" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="J431" s="11"/>
       <c r="K431" s="0" t="s">
@@ -40116,7 +40114,7 @@
         <v>61</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>259</v>
@@ -40131,7 +40129,7 @@
         <v>526</v>
       </c>
       <c r="H432" s="0" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="J432" s="11"/>
       <c r="K432" s="0" t="s">
@@ -40203,10 +40201,10 @@
         <v>61</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="D433" s="0" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E433" s="0" t="s">
         <v>87</v>
@@ -40218,7 +40216,7 @@
         <v>169</v>
       </c>
       <c r="H433" s="0" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="J433" s="11">
         <v>46373.125</v>
@@ -40289,7 +40287,7 @@
         <v>61</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>259</v>
@@ -40373,7 +40371,7 @@
         <v>61</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>162</v>
@@ -40388,7 +40386,7 @@
         <v>176</v>
       </c>
       <c r="H435" s="0" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="J435" s="11"/>
       <c r="K435" s="0" t="s">
@@ -40457,13 +40455,13 @@
         <v>61</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E436" s="0" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="F436" s="0" t="s">
         <v>484</v>
@@ -40472,7 +40470,7 @@
         <v>484</v>
       </c>
       <c r="H436" s="0" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="J436" s="11">
         <v>46373.125</v>
@@ -40543,7 +40541,7 @@
         <v>61</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D437" s="0" t="s">
         <v>162</v>
@@ -40558,7 +40556,7 @@
         <v>500</v>
       </c>
       <c r="H437" s="0" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="J437" s="11"/>
       <c r="K437" s="0" t="s">
@@ -40627,13 +40625,13 @@
         <v>61</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>162</v>
       </c>
       <c r="E438" s="0" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F438" s="0" t="s">
         <v>327</v>
@@ -40642,7 +40640,7 @@
         <v>327</v>
       </c>
       <c r="H438" s="0" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="J438" s="11"/>
       <c r="K438" s="0" t="s">
@@ -40714,7 +40712,7 @@
         <v>61</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>162</v>
@@ -40729,14 +40727,14 @@
         <v>327</v>
       </c>
       <c r="H439" s="0" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="J439" s="11"/>
       <c r="K439" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L439" s="0" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="M439" s="0" t="s">
         <v>39</v>
@@ -40792,25 +40790,25 @@
     </row>
     <row r="440">
       <c r="A440" s="0" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B440" s="0" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="D440" s="0" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="E440" s="0" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="F440" s="0" t="s">
         <v>300</v>
       </c>
       <c r="G440" s="0" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="J440" s="11">
         <v>46383.125</v>
@@ -40843,7 +40841,7 @@
         <v>45</v>
       </c>
       <c r="AC440" s="0" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="AD440" s="11">
         <v>46203.65469700231</v>
@@ -40875,22 +40873,22 @@
         <v>621</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E441" s="0" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F441" s="0" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G441" s="0" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="H441" s="0" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="J441" s="11">
         <v>46365.125</v>
@@ -40955,19 +40953,19 @@
     </row>
     <row r="442">
       <c r="A442" s="0" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B442" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="D442" s="0" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E442" s="0" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F442" s="0" t="s">
         <v>208</v>
@@ -40976,7 +40974,7 @@
         <v>209</v>
       </c>
       <c r="H442" s="0" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="J442" s="11">
         <v>46365.125</v>
@@ -41047,13 +41045,13 @@
         <v>34</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E443" s="0" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F443" s="0" t="s">
         <v>85</v>
@@ -41130,7 +41128,7 @@
         <v>34</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>36</v>
@@ -41213,7 +41211,7 @@
         <v>34</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>123</v>
@@ -41228,7 +41226,7 @@
         <v>74</v>
       </c>
       <c r="H445" s="0" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="J445" s="11">
         <v>46387.125</v>
@@ -41299,7 +41297,7 @@
         <v>34</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>123</v>
@@ -41314,7 +41312,7 @@
         <v>74</v>
       </c>
       <c r="H446" s="0" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="J446" s="11">
         <v>46326.125</v>
@@ -41323,7 +41321,7 @@
         <v>114</v>
       </c>
       <c r="L446" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="M446" s="0" t="s">
         <v>39</v>
@@ -41385,7 +41383,7 @@
         <v>34</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>51</v>
@@ -41400,7 +41398,7 @@
         <v>526</v>
       </c>
       <c r="H447" s="0" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="J447" s="11">
         <v>46326.125</v>
@@ -41409,7 +41407,7 @@
         <v>114</v>
       </c>
       <c r="L447" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="M447" s="0" t="s">
         <v>39</v>
@@ -41471,13 +41469,13 @@
         <v>34</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E448" s="0" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="F448" s="0" t="s">
         <v>131</v>
@@ -41555,13 +41553,13 @@
         <v>34</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>179</v>
       </c>
       <c r="E449" s="0" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="F449" s="0" t="s">
         <v>149</v>
@@ -41570,7 +41568,7 @@
         <v>149</v>
       </c>
       <c r="H449" s="0" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="J449" s="11"/>
       <c r="K449" s="0" t="s">
@@ -41639,13 +41637,13 @@
         <v>61</v>
       </c>
       <c r="C450" s="0" t="s">
+        <v>981</v>
+      </c>
+      <c r="D450" s="0" t="s">
+        <v>982</v>
+      </c>
+      <c r="E450" s="0" t="s">
         <v>983</v>
-      </c>
-      <c r="D450" s="0" t="s">
-        <v>984</v>
-      </c>
-      <c r="E450" s="0" t="s">
-        <v>985</v>
       </c>
       <c r="F450" s="0" t="s">
         <v>407</v>
@@ -41654,7 +41652,7 @@
         <v>407</v>
       </c>
       <c r="H450" s="0" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="J450" s="11"/>
       <c r="K450" s="0" t="s">
@@ -41720,7 +41718,7 @@
         <v>61</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>77</v>
@@ -41735,7 +41733,7 @@
         <v>327</v>
       </c>
       <c r="H451" s="0" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="J451" s="11">
         <v>46406.125</v>
@@ -41806,13 +41804,13 @@
         <v>61</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="D452" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E452" s="0" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F452" s="0" t="s">
         <v>79</v>
@@ -41821,7 +41819,7 @@
         <v>231</v>
       </c>
       <c r="H452" s="0" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="J452" s="11">
         <v>46407.125</v>
@@ -41892,7 +41890,7 @@
         <v>61</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>249</v>
@@ -41907,7 +41905,7 @@
         <v>134</v>
       </c>
       <c r="H453" s="0" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="J453" s="11">
         <v>46407.125</v>
@@ -41978,7 +41976,7 @@
         <v>61</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>249</v>
@@ -41993,7 +41991,7 @@
         <v>134</v>
       </c>
       <c r="H454" s="0" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="J454" s="11">
         <v>46407.125</v>
@@ -42064,13 +42062,13 @@
         <v>61</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="D455" s="0" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E455" s="0" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="F455" s="0" t="s">
         <v>54</v>
@@ -42079,7 +42077,7 @@
         <v>54</v>
       </c>
       <c r="H455" s="0" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="J455" s="11">
         <v>46406.125</v>
@@ -42150,7 +42148,7 @@
         <v>61</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>259</v>
@@ -42165,7 +42163,7 @@
         <v>74</v>
       </c>
       <c r="H456" s="0" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="J456" s="11">
         <v>46373.125</v>
@@ -42236,7 +42234,7 @@
         <v>49</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>51</v>
@@ -42322,13 +42320,13 @@
         <v>226</v>
       </c>
       <c r="C458" s="0" t="s">
+        <v>996</v>
+      </c>
+      <c r="D458" s="0" t="s">
+        <v>997</v>
+      </c>
+      <c r="E458" s="0" t="s">
         <v>998</v>
-      </c>
-      <c r="D458" s="0" t="s">
-        <v>999</v>
-      </c>
-      <c r="E458" s="0" t="s">
-        <v>1000</v>
       </c>
       <c r="F458" s="0" t="s">
         <v>142</v>
@@ -42337,7 +42335,7 @@
         <v>142</v>
       </c>
       <c r="H458" s="0" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="J458" s="11">
         <v>46398.125</v>
@@ -42399,19 +42397,19 @@
     </row>
     <row r="459">
       <c r="A459" s="0" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B459" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C459" s="0" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D459" s="0" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E459" s="0" t="s">
         <v>1002</v>
-      </c>
-      <c r="D459" s="0" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E459" s="0" t="s">
-        <v>1004</v>
       </c>
       <c r="F459" s="0" t="s">
         <v>200</v>
@@ -42426,7 +42424,7 @@
         <v>114</v>
       </c>
       <c r="L459" s="0" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="M459" s="0" t="s">
         <v>39</v>
@@ -42450,7 +42448,7 @@
         <v>45</v>
       </c>
       <c r="AC459" s="0" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="AD459" s="11">
         <v>46219.55652277778</v>
@@ -42482,7 +42480,7 @@
         <v>49</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>376</v>
@@ -42497,7 +42495,7 @@
         <v>332</v>
       </c>
       <c r="H460" s="0" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="J460" s="11">
         <v>46402.125</v>
@@ -42568,7 +42566,7 @@
         <v>61</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>51</v>
@@ -42583,7 +42581,7 @@
         <v>79</v>
       </c>
       <c r="H461" s="0" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="J461" s="11">
         <v>46346.125</v>
@@ -42654,13 +42652,13 @@
         <v>61</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D462" s="0" t="s">
         <v>249</v>
       </c>
       <c r="E462" s="0" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="F462" s="0" t="s">
         <v>332</v>
@@ -42669,7 +42667,7 @@
         <v>53</v>
       </c>
       <c r="H462" s="0" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="J462" s="11">
         <v>46346.125</v>
@@ -42740,7 +42738,7 @@
         <v>61</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>249</v>
@@ -42755,7 +42753,7 @@
         <v>208</v>
       </c>
       <c r="H463" s="0" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="J463" s="11"/>
       <c r="K463" s="0" t="s">
@@ -42824,7 +42822,7 @@
         <v>61</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>51</v>
@@ -42839,7 +42837,7 @@
         <v>150</v>
       </c>
       <c r="H464" s="0" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="J464" s="11">
         <v>46407.125</v>
@@ -42910,7 +42908,7 @@
         <v>61</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>259</v>
@@ -42925,7 +42923,7 @@
         <v>231</v>
       </c>
       <c r="H465" s="0" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="J465" s="11">
         <v>46407.125</v>
@@ -42996,7 +42994,7 @@
         <v>61</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>259</v>
@@ -43011,7 +43009,7 @@
         <v>231</v>
       </c>
       <c r="H466" s="0" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="J466" s="11">
         <v>46407.125</v>
@@ -43076,13 +43074,13 @@
     </row>
     <row r="467">
       <c r="A467" s="0" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B467" s="0" t="s">
         <v>599</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>212</v>
@@ -43100,10 +43098,10 @@
         <v>46352.125</v>
       </c>
       <c r="K467" s="0" t="s">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="L467" s="0" t="s">
-        <v>39</v>
+        <v>206</v>
       </c>
       <c r="M467" s="0" t="s">
         <v>39</v>
@@ -43162,13 +43160,13 @@
         <v>599</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D468" s="0" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="E468" s="0" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="F468" s="0" t="s">
         <v>428</v>
@@ -43242,13 +43240,13 @@
         <v>49</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="D469" s="0" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E469" s="0" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="F469" s="0" t="s">
         <v>98</v>
@@ -43328,13 +43326,13 @@
         <v>34</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="D470" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E470" s="0" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F470" s="0" t="s">
         <v>38</v>
@@ -43343,7 +43341,7 @@
         <v>38</v>
       </c>
       <c r="H470" s="0" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="J470" s="11"/>
       <c r="K470" s="0" t="s">
@@ -43412,13 +43410,13 @@
         <v>49</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="D471" s="0" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="E471" s="0" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="F471" s="0" t="s">
         <v>137</v>
@@ -43495,7 +43493,7 @@
         <v>49</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>339</v>
@@ -43578,7 +43576,7 @@
         <v>49</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>339</v>
@@ -43661,7 +43659,7 @@
         <v>34</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>249</v>
@@ -43676,7 +43674,7 @@
         <v>38</v>
       </c>
       <c r="H474" s="0" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="J474" s="11">
         <v>46362.125</v>
@@ -43747,7 +43745,7 @@
         <v>34</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D475" s="0" t="s">
         <v>249</v>
@@ -43762,7 +43760,7 @@
         <v>38</v>
       </c>
       <c r="H475" s="0" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="J475" s="11">
         <v>46362.125</v>
@@ -43833,7 +43831,7 @@
         <v>49</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>360</v>
@@ -43916,13 +43914,13 @@
         <v>49</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="D477" s="0" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="E477" s="0" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="F477" s="0" t="s">
         <v>257</v>
@@ -43999,13 +43997,13 @@
         <v>49</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="D478" s="0" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="E478" s="0" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F478" s="0" t="s">
         <v>131</v>
@@ -44082,13 +44080,13 @@
         <v>49</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="D479" s="0" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="E479" s="0" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="F479" s="0" t="s">
         <v>294</v>
@@ -44165,13 +44163,13 @@
         <v>61</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D480" s="0" t="s">
         <v>508</v>
       </c>
       <c r="E480" s="0" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="F480" s="0" t="s">
         <v>105</v>
@@ -44243,19 +44241,19 @@
     </row>
     <row r="481">
       <c r="A481" s="0" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B481" s="0" t="s">
         <v>621</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D481" s="0" t="s">
         <v>72</v>
       </c>
       <c r="E481" s="0" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="F481" s="0" t="s">
         <v>293</v>
@@ -44264,7 +44262,7 @@
         <v>293</v>
       </c>
       <c r="H481" s="0" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="J481" s="11">
         <v>46372.125</v>
@@ -44335,19 +44333,19 @@
         <v>34</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>565</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="F482" s="0" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="G482" s="0" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="H482" s="0" t="s">
         <v>201</v>
@@ -44421,19 +44419,19 @@
         <v>34</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D483" s="0" t="s">
         <v>565</v>
       </c>
       <c r="E483" s="0" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="F483" s="0" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="G483" s="0" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="H483" s="0" t="s">
         <v>201</v>
@@ -44507,7 +44505,7 @@
         <v>226</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>508</v>
@@ -44581,19 +44579,19 @@
     </row>
     <row r="485">
       <c r="A485" s="0" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B485" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D485" s="0" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="E485" s="0" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F485" s="0" t="s">
         <v>294</v>
@@ -44629,7 +44627,7 @@
         <v>45</v>
       </c>
       <c r="AC485" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AD485" s="11">
         <v>46301.476280462964</v>
@@ -44655,19 +44653,19 @@
     </row>
     <row r="486">
       <c r="A486" s="0" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B486" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="D486" s="0" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E486" s="0" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F486" s="0" t="s">
         <v>168</v>
@@ -44680,7 +44678,7 @@
         <v>40</v>
       </c>
       <c r="L486" s="0" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="M486" s="0" t="s">
         <v>39</v>
@@ -44704,7 +44702,7 @@
         <v>44</v>
       </c>
       <c r="AC486" s="0" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="AD486" s="11">
         <v>46303.38590450231</v>
@@ -44722,19 +44720,19 @@
     </row>
     <row r="487">
       <c r="A487" s="0" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B487" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D487" s="0" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E487" s="0" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F487" s="0" t="s">
         <v>169</v>
@@ -44747,7 +44745,7 @@
         <v>40</v>
       </c>
       <c r="L487" s="0" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="M487" s="0" t="s">
         <v>39</v>
@@ -44771,7 +44769,7 @@
         <v>44</v>
       </c>
       <c r="AC487" s="0" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="AD487" s="11">
         <v>46303.38891412037</v>
@@ -44789,19 +44787,19 @@
     </row>
     <row r="488">
       <c r="A488" s="0" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B488" s="0" t="s">
         <v>599</v>
       </c>
       <c r="C488" s="0" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D488" s="0" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E488" s="0" t="s">
         <v>1055</v>
-      </c>
-      <c r="D488" s="0" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E488" s="0" t="s">
-        <v>1057</v>
       </c>
       <c r="F488" s="0" t="s">
         <v>93</v>
@@ -44814,7 +44812,7 @@
         <v>40</v>
       </c>
       <c r="L488" s="0" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="M488" s="0" t="s">
         <v>39</v>
@@ -44898,28 +44896,28 @@
         <v>15</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>10</v>
@@ -44927,10 +44925,10 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>61</v>
@@ -44942,16 +44940,16 @@
         <v>46316</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G2" s="11">
         <v>46496.125</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="J2" s="0" t="s">
         <v>214</v>
@@ -44959,10 +44957,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>61</v>
@@ -44980,10 +44978,10 @@
         <v>46495.125</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="J3" s="0" t="s">
         <v>214</v>
@@ -44991,10 +44989,10 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>621</v>
@@ -45012,10 +45010,10 @@
         <v>46495.125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J4" s="0" t="s">
         <v>625</v>
@@ -45023,10 +45021,10 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>621</v>
@@ -45038,16 +45036,16 @@
         <v>46315</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G5" s="11">
         <v>46495.125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>625</v>
@@ -45055,10 +45053,10 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>61</v>
@@ -45070,16 +45068,16 @@
         <v>46314</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G6" s="11">
         <v>46494.125</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="J6" s="0" t="s">
         <v>214</v>
@@ -45087,10 +45085,10 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>621</v>
@@ -45108,10 +45106,10 @@
         <v>46491.125</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J7" s="0" t="s">
         <v>625</v>
@@ -45119,13 +45117,13 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>30</v>
@@ -45140,24 +45138,24 @@
         <v>46483.125</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>29</v>
@@ -45166,27 +45164,27 @@
         <v>46303</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G9" s="11">
         <v>46483.125</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>621</v>
@@ -45204,10 +45202,10 @@
         <v>46480.125</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J10" s="0" t="s">
         <v>625</v>
@@ -45215,10 +45213,10 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>226</v>
@@ -45236,10 +45234,10 @@
         <v>46476.125</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J11" s="0" t="s">
         <v>226</v>
@@ -45247,10 +45245,10 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>226</v>
@@ -45262,16 +45260,16 @@
         <v>46296</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G12" s="11">
         <v>46476.125</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J12" s="0" t="s">
         <v>226</v>
@@ -45279,10 +45277,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>34</v>
@@ -45300,10 +45298,10 @@
         <v>46474.125</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="J13" s="0" t="s">
         <v>202</v>
@@ -45311,10 +45309,10 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>34</v>
@@ -45332,10 +45330,10 @@
         <v>46474.125</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="J14" s="0" t="s">
         <v>202</v>
@@ -45343,10 +45341,10 @@
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>621</v>
@@ -45364,10 +45362,10 @@
         <v>46474.125</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J15" s="0" t="s">
         <v>625</v>
@@ -45375,10 +45373,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>621</v>
@@ -45390,16 +45388,16 @@
         <v>46294</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G16" s="11">
         <v>46474.125</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J16" s="0" t="s">
         <v>625</v>
@@ -45407,10 +45405,10 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>621</v>
@@ -45428,10 +45426,10 @@
         <v>46474.125</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J17" s="0" t="s">
         <v>625</v>
@@ -45439,10 +45437,10 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>621</v>
@@ -45454,16 +45452,16 @@
         <v>46294</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G18" s="11">
         <v>46474.125</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J18" s="0" t="s">
         <v>625</v>
@@ -45471,10 +45469,10 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>61</v>
@@ -45486,16 +45484,16 @@
         <v>46289</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G19" s="11">
         <v>46469.125</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="J19" s="0" t="s">
         <v>67</v>
@@ -45503,10 +45501,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>61</v>
@@ -45524,10 +45522,10 @@
         <v>46469.125</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="J20" s="0" t="s">
         <v>67</v>
@@ -45535,10 +45533,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>621</v>
@@ -45556,10 +45554,10 @@
         <v>46455.125</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J21" s="0" t="s">
         <v>625</v>
@@ -45567,10 +45565,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>621</v>
@@ -45582,16 +45580,16 @@
         <v>46275</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G22" s="11">
         <v>46455.125</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J22" s="0" t="s">
         <v>625</v>
@@ -45599,13 +45597,13 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>30</v>
@@ -45620,24 +45618,24 @@
         <v>46449.125</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>29</v>
@@ -45646,30 +45644,30 @@
         <v>46269</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G24" s="11">
         <v>46449.125</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>30</v>
@@ -45684,13 +45682,13 @@
         <v>46268</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="26">
@@ -45698,7 +45696,7 @@
         <v>534</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>34</v>
@@ -45710,19 +45708,19 @@
         <v>46267</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G26" s="11">
         <v>46447.125</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="27">
@@ -45730,7 +45728,7 @@
         <v>534</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>34</v>
@@ -45748,21 +45746,21 @@
         <v>46447.125</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>61</v>
@@ -45780,10 +45778,10 @@
         <v>46314</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="J28" s="0" t="s">
         <v>214</v>
@@ -45791,10 +45789,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>61</v>
@@ -45812,10 +45810,10 @@
         <v>46446.125</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>214</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46323.35050244213</v>
+        <v>46323.623424074074</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46323.623424074074</v>
+        <v>46324.3432096875</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46324.3432096875</v>
+        <v>46324.64689034722</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -375,157 +375,157 @@
     <t>HRO6A06</t>
   </si>
   <si>
+    <t>SAFRA CARRETA</t>
+  </si>
+  <si>
+    <t>HDI7046</t>
+  </si>
+  <si>
+    <t>SR/GUERRA</t>
+  </si>
+  <si>
+    <t>AG GR</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>059472922</t>
+  </si>
+  <si>
+    <t>JHX7603</t>
+  </si>
+  <si>
+    <t>STRALIS 570S41T</t>
+  </si>
+  <si>
+    <t>KIT8J31</t>
+  </si>
+  <si>
+    <t>FH 400 6X2T</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>054682677</t>
+  </si>
+  <si>
+    <t>OMP3E05</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>059315199</t>
+  </si>
+  <si>
+    <t>KDO7124</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>SAFRA CARRETA ARRENDADO</t>
+  </si>
+  <si>
+    <t>BWZ6507</t>
+  </si>
+  <si>
+    <t>REB/RANDON</t>
+  </si>
+  <si>
+    <t>SR GR TR</t>
+  </si>
+  <si>
+    <t>1994</t>
+  </si>
+  <si>
+    <t>059765333</t>
+  </si>
+  <si>
+    <t>JLG6E58</t>
+  </si>
+  <si>
+    <t>NL12 360 4X2</t>
+  </si>
+  <si>
+    <t>048941358</t>
+  </si>
+  <si>
+    <t>LVD0G76</t>
+  </si>
+  <si>
+    <t>R124 LA6X2NA 400</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>059510688</t>
+  </si>
+  <si>
+    <t>SAFRA CAVALO ARRENDADO</t>
+  </si>
+  <si>
+    <t>BRF1J56</t>
+  </si>
+  <si>
+    <t>R113 H 4X2 360</t>
+  </si>
+  <si>
+    <t>1993</t>
+  </si>
+  <si>
+    <t>059297444</t>
+  </si>
+  <si>
+    <t>BWM2D91</t>
+  </si>
+  <si>
+    <t>REB/FACCHINI</t>
+  </si>
+  <si>
+    <t>SRF GR</t>
+  </si>
+  <si>
+    <t>049357788</t>
+  </si>
+  <si>
+    <t>HOA0E87</t>
+  </si>
+  <si>
+    <t>M. BENZ</t>
+  </si>
+  <si>
+    <t>AXOR 2035 S</t>
+  </si>
+  <si>
+    <t>IMI4C27</t>
+  </si>
+  <si>
+    <t>FH12 380 4X2T</t>
+  </si>
+  <si>
+    <t>058966088</t>
+  </si>
+  <si>
+    <t>JMU5F59</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>059703044</t>
+  </si>
+  <si>
     <t>Documento CRLV ausente ou vencido / Documento ConsultaCRLV vencendo</t>
-  </si>
-  <si>
-    <t>SAFRA CARRETA</t>
-  </si>
-  <si>
-    <t>HDI7046</t>
-  </si>
-  <si>
-    <t>SR/GUERRA</t>
-  </si>
-  <si>
-    <t>AG GR</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>059472922</t>
-  </si>
-  <si>
-    <t>JHX7603</t>
-  </si>
-  <si>
-    <t>STRALIS 570S41T</t>
-  </si>
-  <si>
-    <t>KIT8J31</t>
-  </si>
-  <si>
-    <t>FH 400 6X2T</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>054682677</t>
-  </si>
-  <si>
-    <t>OMP3E05</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>059315199</t>
-  </si>
-  <si>
-    <t>KDO7124</t>
-  </si>
-  <si>
-    <t>1999</t>
-  </si>
-  <si>
-    <t>SAFRA CARRETA ARRENDADO</t>
-  </si>
-  <si>
-    <t>BWZ6507</t>
-  </si>
-  <si>
-    <t>REB/RANDON</t>
-  </si>
-  <si>
-    <t>SR GR TR</t>
-  </si>
-  <si>
-    <t>1994</t>
-  </si>
-  <si>
-    <t>059765333</t>
-  </si>
-  <si>
-    <t>JLG6E58</t>
-  </si>
-  <si>
-    <t>NL12 360 4X2</t>
-  </si>
-  <si>
-    <t>048941358</t>
-  </si>
-  <si>
-    <t>LVD0G76</t>
-  </si>
-  <si>
-    <t>R124 LA6X2NA 400</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>059510688</t>
-  </si>
-  <si>
-    <t>SAFRA CAVALO ARRENDADO</t>
-  </si>
-  <si>
-    <t>BRF1J56</t>
-  </si>
-  <si>
-    <t>R113 H 4X2 360</t>
-  </si>
-  <si>
-    <t>1993</t>
-  </si>
-  <si>
-    <t>059297444</t>
-  </si>
-  <si>
-    <t>BWM2D91</t>
-  </si>
-  <si>
-    <t>REB/FACCHINI</t>
-  </si>
-  <si>
-    <t>SRF GR</t>
-  </si>
-  <si>
-    <t>049357788</t>
-  </si>
-  <si>
-    <t>HOA0E87</t>
-  </si>
-  <si>
-    <t>M. BENZ</t>
-  </si>
-  <si>
-    <t>AXOR 2035 S</t>
-  </si>
-  <si>
-    <t>IMI4C27</t>
-  </si>
-  <si>
-    <t>FH12 380 4X2T</t>
-  </si>
-  <si>
-    <t>058966088</t>
-  </si>
-  <si>
-    <t>JMU5F59</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>059703044</t>
   </si>
   <si>
     <t>NFK8A40</t>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46324.64689034722</v>
+        <v>46325.35281707176</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -5874,7 +5874,7 @@
         <v>40</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="M29" s="0" t="s">
         <v>39</v>
@@ -5886,7 +5886,7 @@
         <v>46310.125</v>
       </c>
       <c r="Q29" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R29" s="11">
         <v>46324.125</v>
@@ -5930,28 +5930,28 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C30" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="E30" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="F30" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="G30" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="0" t="s">
         <v>125</v>
-      </c>
-      <c r="G30" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="H30" s="0" t="s">
-        <v>126</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="0" t="s">
@@ -6020,13 +6020,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>63</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F31" s="0" t="s">
         <v>74</v>
@@ -6035,7 +6035,7 @@
         <v>74</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J31" s="11"/>
       <c r="K31" s="0" t="s">
@@ -6104,22 +6104,22 @@
         <v>49</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E32" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="G32" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="F32" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="G32" s="0" t="s">
+      <c r="H32" s="0" t="s">
         <v>131</v>
-      </c>
-      <c r="H32" s="0" t="s">
-        <v>132</v>
       </c>
       <c r="J32" s="11">
         <v>46391.125</v>
@@ -6184,13 +6184,13 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>36</v>
@@ -6202,10 +6202,10 @@
         <v>60</v>
       </c>
       <c r="G33" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="H33" s="0" t="s">
         <v>134</v>
-      </c>
-      <c r="H33" s="0" t="s">
-        <v>135</v>
       </c>
       <c r="J33" s="11"/>
       <c r="K33" s="0" t="s">
@@ -6274,7 +6274,7 @@
         <v>34</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>51</v>
@@ -6286,10 +6286,10 @@
         <v>85</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="0" t="s">
@@ -6352,28 +6352,28 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>61</v>
       </c>
       <c r="C35" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="0" t="s">
         <v>139</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="E35" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="F35" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="G35" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="H35" s="0" t="s">
         <v>142</v>
-      </c>
-      <c r="G35" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="H35" s="0" t="s">
-        <v>143</v>
       </c>
       <c r="J35" s="11">
         <v>46367.125</v>
@@ -6447,22 +6447,22 @@
         <v>49</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E36" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="G36" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="H36" s="0" t="s">
         <v>145</v>
-      </c>
-      <c r="F36" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="G36" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="H36" s="0" t="s">
-        <v>146</v>
       </c>
       <c r="J36" s="11">
         <v>46361.125</v>
@@ -6533,22 +6533,22 @@
         <v>49</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E37" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="G37" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="G37" s="0" t="s">
+      <c r="H37" s="0" t="s">
         <v>150</v>
-      </c>
-      <c r="H37" s="0" t="s">
-        <v>151</v>
       </c>
       <c r="J37" s="11">
         <v>46374.125</v>
@@ -6613,28 +6613,28 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>61</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>77</v>
       </c>
       <c r="E38" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="F38" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="G38" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="H38" s="0" t="s">
         <v>155</v>
-      </c>
-      <c r="G38" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="H38" s="0" t="s">
-        <v>156</v>
       </c>
       <c r="J38" s="11">
         <v>46356.125</v>
@@ -6702,28 +6702,28 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C39" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="E39" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="F39" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="G39" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="H39" s="0" t="s">
         <v>159</v>
-      </c>
-      <c r="F39" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="G39" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="H39" s="0" t="s">
-        <v>160</v>
       </c>
       <c r="J39" s="11">
         <v>46390.125</v>
@@ -6794,13 +6794,13 @@
         <v>34</v>
       </c>
       <c r="C40" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="E40" s="0" t="s">
         <v>162</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>163</v>
       </c>
       <c r="F40" s="0" t="s">
         <v>74</v>
@@ -6809,7 +6809,7 @@
         <v>65</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="0" t="s">
@@ -6872,28 +6872,28 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>61</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>51</v>
       </c>
       <c r="E41" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="G41" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="H41" s="0" t="s">
         <v>165</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="G41" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="H41" s="0" t="s">
-        <v>166</v>
       </c>
       <c r="J41" s="11"/>
       <c r="K41" s="0" t="s">
@@ -6959,35 +6959,35 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B42" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C42" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="F42" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="D42" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="F42" s="0" t="s">
+      <c r="G42" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="H42" s="0" t="s">
         <v>169</v>
-      </c>
-      <c r="H42" s="0" t="s">
-        <v>170</v>
       </c>
       <c r="J42" s="11"/>
       <c r="K42" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L42" s="0" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="M42" s="0" t="s">
         <v>39</v>
@@ -7052,26 +7052,26 @@
         <v>171</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E43" s="0" t="s">
         <v>172</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J43" s="11"/>
       <c r="K43" s="0" t="s">
         <v>40</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="M43" s="0" t="s">
         <v>39</v>
@@ -7136,7 +7136,7 @@
         <v>174</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E44" s="0" t="s">
         <v>175</v>
@@ -7303,7 +7303,7 @@
         <v>182</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E46" s="0" t="s">
         <v>183</v>
@@ -7387,7 +7387,7 @@
         <v>186</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47" s="0" t="s">
         <v>187</v>
@@ -7555,7 +7555,7 @@
         <v>194</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E49" s="0" t="s">
         <v>195</v>
@@ -7632,7 +7632,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>34</v>
@@ -7718,7 +7718,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>34</v>
@@ -7804,7 +7804,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>34</v>
@@ -7974,7 +7974,7 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>49</v>
@@ -7989,13 +7989,13 @@
         <v>72</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J54" s="11">
         <v>46374.125</v>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>61</v>
@@ -8155,7 +8155,7 @@
         <v>215</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E56" s="0" t="s">
         <v>216</v>
@@ -8245,10 +8245,10 @@
         <v>219</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H57" s="0" t="s">
         <v>39</v>
@@ -8325,16 +8325,16 @@
         <v>220</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E58" s="0" t="s">
         <v>172</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H58" s="0" t="s">
         <v>221</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B59" s="0" t="s">
         <v>61</v>
@@ -8417,10 +8417,10 @@
         <v>223</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H59" s="0" t="s">
         <v>224</v>
@@ -8586,13 +8586,13 @@
         <v>51</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>231</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H61" s="0" t="s">
         <v>232</v>
@@ -8660,7 +8660,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>61</v>
@@ -8764,10 +8764,10 @@
         <v>237</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H63" s="0" t="s">
         <v>39</v>
@@ -9087,7 +9087,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B67" s="0" t="s">
         <v>61</v>
@@ -9176,7 +9176,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>61</v>
@@ -9265,7 +9265,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>61</v>
@@ -9280,10 +9280,10 @@
         <v>37</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H69" s="0" t="s">
         <v>254</v>
@@ -9435,7 +9435,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>61</v>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>61</v>
@@ -9537,10 +9537,10 @@
         <v>264</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H72" s="0" t="s">
         <v>261</v>
@@ -9609,7 +9609,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>34</v>
@@ -9693,7 +9693,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>34</v>
@@ -9789,13 +9789,13 @@
         <v>51</v>
       </c>
       <c r="E75" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="F75" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="F75" s="0" t="s">
-        <v>131</v>
-      </c>
       <c r="G75" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H75" s="0" t="s">
         <v>266</v>
@@ -9876,10 +9876,10 @@
         <v>272</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H76" s="0" t="s">
         <v>273</v>
@@ -9962,10 +9962,10 @@
         <v>275</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H77" s="0" t="s">
         <v>273</v>
@@ -10045,13 +10045,13 @@
         <v>51</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H78" s="0" t="s">
         <v>273</v>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>61</v>
@@ -10134,10 +10134,10 @@
         <v>272</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H79" s="0" t="s">
         <v>278</v>
@@ -10205,7 +10205,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>61</v>
@@ -10220,10 +10220,10 @@
         <v>275</v>
       </c>
       <c r="F80" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H80" s="0" t="s">
         <v>278</v>
@@ -10291,7 +10291,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>61</v>
@@ -10375,7 +10375,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>61</v>
@@ -10715,7 +10715,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>61</v>
@@ -10804,7 +10804,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>61</v>
@@ -10893,7 +10893,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>61</v>
@@ -11261,7 +11261,7 @@
         <v>200</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J92" s="11">
         <v>46391.125</v>
@@ -11427,10 +11427,10 @@
         <v>304</v>
       </c>
       <c r="F94" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H94" s="0" t="s">
         <v>39</v>
@@ -11513,10 +11513,10 @@
         <v>304</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H95" s="0" t="s">
         <v>39</v>
@@ -11599,10 +11599,10 @@
         <v>307</v>
       </c>
       <c r="F96" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="G96" s="0" t="s">
         <v>149</v>
-      </c>
-      <c r="G96" s="0" t="s">
-        <v>150</v>
       </c>
       <c r="H96" s="0" t="s">
         <v>39</v>
@@ -12029,10 +12029,10 @@
         <v>316</v>
       </c>
       <c r="F101" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G101" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H101" s="0" t="s">
         <v>317</v>
@@ -12199,10 +12199,10 @@
         <v>322</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G103" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H103" s="0" t="s">
         <v>39</v>
@@ -12283,10 +12283,10 @@
         <v>322</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H104" s="0" t="s">
         <v>39</v>
@@ -12696,7 +12696,7 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B109" s="0" t="s">
         <v>61</v>
@@ -12780,7 +12780,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B110" s="0" t="s">
         <v>61</v>
@@ -12948,7 +12948,7 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B112" s="0" t="s">
         <v>61</v>
@@ -13034,7 +13034,7 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B113" s="0" t="s">
         <v>61</v>
@@ -13055,7 +13055,7 @@
         <v>79</v>
       </c>
       <c r="H113" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J113" s="11">
         <v>46356.125</v>
@@ -13209,7 +13209,7 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B115" s="0" t="s">
         <v>34</v>
@@ -13224,10 +13224,10 @@
         <v>234</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H115" s="0" t="s">
         <v>344</v>
@@ -13311,7 +13311,7 @@
         <v>346</v>
       </c>
       <c r="F116" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G116" s="0" t="s">
         <v>93</v>
@@ -13820,13 +13820,13 @@
         <v>51</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F122" s="0" t="s">
         <v>231</v>
       </c>
       <c r="G122" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H122" s="0" t="s">
         <v>352</v>
@@ -13901,13 +13901,13 @@
         <v>355</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E123" s="0" t="s">
         <v>356</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G123" s="0" t="s">
         <v>79</v>
@@ -13985,13 +13985,13 @@
         <v>358</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E124" s="0" t="s">
         <v>356</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G124" s="0" t="s">
         <v>79</v>
@@ -14077,10 +14077,10 @@
         <v>360</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G125" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H125" s="0" t="s">
         <v>357</v>
@@ -14333,10 +14333,10 @@
         <v>366</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G128" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H128" s="0" t="s">
         <v>39</v>
@@ -14662,7 +14662,7 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B132" s="0" t="s">
         <v>61</v>
@@ -14683,7 +14683,7 @@
         <v>38</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J132" s="11">
         <v>46356.125</v>
@@ -14769,7 +14769,7 @@
         <v>231</v>
       </c>
       <c r="G133" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H133" s="0" t="s">
         <v>39</v>
@@ -14852,10 +14852,10 @@
         <v>304</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G134" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H134" s="0" t="s">
         <v>39</v>
@@ -14938,10 +14938,10 @@
         <v>304</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G135" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H135" s="0" t="s">
         <v>39</v>
@@ -15107,7 +15107,7 @@
         <v>51</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F137" s="0" t="s">
         <v>79</v>
@@ -15196,10 +15196,10 @@
         <v>339</v>
       </c>
       <c r="F138" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H138" s="0" t="s">
         <v>39</v>
@@ -16050,10 +16050,10 @@
         <v>396</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H148" s="0" t="s">
         <v>39</v>
@@ -16298,7 +16298,7 @@
         <v>401</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E151" s="0" t="s">
         <v>216</v>
@@ -16388,10 +16388,10 @@
         <v>371</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H152" s="0" t="s">
         <v>39</v>
@@ -16715,7 +16715,7 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B156" s="0" t="s">
         <v>61</v>
@@ -16736,7 +16736,7 @@
         <v>192</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J156" s="11">
         <v>46367.125</v>
@@ -16819,10 +16819,10 @@
         <v>411</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G157" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H157" s="0" t="s">
         <v>39</v>
@@ -16985,10 +16985,10 @@
         <v>413</v>
       </c>
       <c r="D159" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E159" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E159" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F159" s="0" t="s">
         <v>74</v>
@@ -17161,10 +17161,10 @@
         <v>419</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H161" s="0" t="s">
         <v>39</v>
@@ -17247,10 +17247,10 @@
         <v>311</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H162" s="0" t="s">
         <v>39</v>
@@ -18191,7 +18191,7 @@
         <v>337</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>93</v>
@@ -18449,10 +18449,10 @@
         <v>304</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H176" s="0" t="s">
         <v>39</v>
@@ -18710,10 +18710,10 @@
         <v>304</v>
       </c>
       <c r="F179" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H179" s="0" t="s">
         <v>39</v>
@@ -18951,7 +18951,7 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B182" s="0" t="s">
         <v>34</v>
@@ -18966,10 +18966,10 @@
         <v>452</v>
       </c>
       <c r="F182" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H182" s="0" t="s">
         <v>450</v>
@@ -19044,16 +19044,16 @@
         <v>453</v>
       </c>
       <c r="D183" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E183" s="0" t="s">
         <v>187</v>
       </c>
       <c r="F183" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G183" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H183" s="0" t="s">
         <v>454</v>
@@ -19121,7 +19121,7 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B184" s="0" t="s">
         <v>61</v>
@@ -19302,7 +19302,7 @@
         <v>460</v>
       </c>
       <c r="D186" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E186" s="0" t="s">
         <v>461</v>
@@ -19391,10 +19391,10 @@
         <v>464</v>
       </c>
       <c r="F187" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H187" s="0" t="s">
         <v>465</v>
@@ -19460,7 +19460,7 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B188" s="0" t="s">
         <v>34</v>
@@ -19475,10 +19475,10 @@
         <v>467</v>
       </c>
       <c r="F188" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G188" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H188" s="0" t="s">
         <v>465</v>
@@ -19553,10 +19553,10 @@
         <v>468</v>
       </c>
       <c r="D189" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E189" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E189" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F189" s="0" t="s">
         <v>38</v>
@@ -19637,10 +19637,10 @@
         <v>469</v>
       </c>
       <c r="D190" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E190" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E190" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F190" s="0" t="s">
         <v>38</v>
@@ -19712,7 +19712,7 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B191" s="0" t="s">
         <v>61</v>
@@ -19799,7 +19799,7 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B192" s="0" t="s">
         <v>61</v>
@@ -19808,7 +19808,7 @@
         <v>472</v>
       </c>
       <c r="D192" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E192" s="0" t="s">
         <v>473</v>
@@ -19886,7 +19886,7 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B193" s="0" t="s">
         <v>61</v>
@@ -19985,10 +19985,10 @@
         <v>234</v>
       </c>
       <c r="F194" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H194" s="0" t="s">
         <v>476</v>
@@ -20063,7 +20063,7 @@
         <v>478</v>
       </c>
       <c r="D195" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E195" s="0" t="s">
         <v>183</v>
@@ -20233,7 +20233,7 @@
         <v>483</v>
       </c>
       <c r="D197" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E197" s="0" t="s">
         <v>175</v>
@@ -20319,16 +20319,16 @@
         <v>486</v>
       </c>
       <c r="D198" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E198" s="0" t="s">
         <v>487</v>
       </c>
       <c r="F198" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H198" s="0" t="s">
         <v>488</v>
@@ -20489,7 +20489,7 @@
         <v>492</v>
       </c>
       <c r="D200" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E200" s="0" t="s">
         <v>175</v>
@@ -20579,7 +20579,7 @@
         <v>496</v>
       </c>
       <c r="F201" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G201" s="0" t="s">
         <v>93</v>
@@ -20659,7 +20659,7 @@
         <v>498</v>
       </c>
       <c r="D202" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E202" s="0" t="s">
         <v>499</v>
@@ -20754,10 +20754,10 @@
         <v>503</v>
       </c>
       <c r="F203" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G203" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H203" s="0" t="s">
         <v>504</v>
@@ -20823,7 +20823,7 @@
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B204" s="0" t="s">
         <v>34</v>
@@ -20832,16 +20832,16 @@
         <v>505</v>
       </c>
       <c r="D204" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E204" s="0" t="s">
         <v>140</v>
-      </c>
-      <c r="E204" s="0" t="s">
-        <v>141</v>
       </c>
       <c r="F204" s="0" t="s">
         <v>506</v>
       </c>
       <c r="G204" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H204" s="0" t="s">
         <v>504</v>
@@ -20924,10 +20924,10 @@
         <v>187</v>
       </c>
       <c r="F205" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H205" s="0" t="s">
         <v>509</v>
@@ -21008,10 +21008,10 @@
         <v>511</v>
       </c>
       <c r="F206" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G206" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H206" s="0" t="s">
         <v>512</v>
@@ -21163,7 +21163,7 @@
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B208" s="0" t="s">
         <v>34</v>
@@ -21178,10 +21178,10 @@
         <v>516</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H208" s="0" t="s">
         <v>514</v>
@@ -21348,13 +21348,13 @@
         <v>521</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J210" s="11">
         <v>46373.125</v>
@@ -21428,10 +21428,10 @@
         <v>522</v>
       </c>
       <c r="D211" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E211" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E211" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F211" s="0" t="s">
         <v>38</v>
@@ -21512,10 +21512,10 @@
         <v>524</v>
       </c>
       <c r="D212" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E212" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E212" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F212" s="0" t="s">
         <v>38</v>
@@ -21587,7 +21587,7 @@
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B213" s="0" t="s">
         <v>34</v>
@@ -21596,10 +21596,10 @@
         <v>525</v>
       </c>
       <c r="D213" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E213" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E213" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F213" s="0" t="s">
         <v>526</v>
@@ -21755,7 +21755,7 @@
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B215" s="0" t="s">
         <v>34</v>
@@ -21839,7 +21839,7 @@
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B216" s="0" t="s">
         <v>34</v>
@@ -21848,13 +21848,13 @@
         <v>534</v>
       </c>
       <c r="D216" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E216" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="E216" s="0" t="s">
+      <c r="F216" s="0" t="s">
         <v>141</v>
-      </c>
-      <c r="F216" s="0" t="s">
-        <v>142</v>
       </c>
       <c r="G216" s="0" t="s">
         <v>332</v>
@@ -21944,7 +21944,7 @@
         <v>200</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J217" s="11">
         <v>46384.125</v>
@@ -22273,13 +22273,13 @@
         <v>51</v>
       </c>
       <c r="E221" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="F221" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="F221" s="0" t="s">
-        <v>131</v>
-      </c>
       <c r="G221" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H221" s="0" t="s">
         <v>543</v>
@@ -22347,7 +22347,7 @@
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B222" s="0" t="s">
         <v>61</v>
@@ -22362,13 +22362,13 @@
         <v>545</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J222" s="11"/>
       <c r="K222" s="0" t="s">
@@ -22530,10 +22530,10 @@
         <v>550</v>
       </c>
       <c r="F224" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J224" s="11">
         <v>46419.125</v>
@@ -22598,7 +22598,7 @@
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B225" s="0" t="s">
         <v>61</v>
@@ -22613,13 +22613,13 @@
         <v>228</v>
       </c>
       <c r="F225" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="G225" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="H225" s="0" t="s">
         <v>155</v>
-      </c>
-      <c r="G225" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="H225" s="0" t="s">
-        <v>156</v>
       </c>
       <c r="J225" s="11"/>
       <c r="K225" s="0" t="s">
@@ -22783,10 +22783,10 @@
         <v>556</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G227" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H227" s="0" t="s">
         <v>557</v>
@@ -22869,10 +22869,10 @@
         <v>559</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H228" s="0" t="s">
         <v>557</v>
@@ -23041,10 +23041,10 @@
         <v>563</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J230" s="11">
         <v>46416.125</v>
@@ -23202,16 +23202,16 @@
         <v>568</v>
       </c>
       <c r="D232" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E232" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="E232" s="0" t="s">
+      <c r="F232" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="F232" s="0" t="s">
-        <v>125</v>
-      </c>
       <c r="G232" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H232" s="0" t="s">
         <v>567</v>
@@ -23286,16 +23286,16 @@
         <v>569</v>
       </c>
       <c r="D233" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E233" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="E233" s="0" t="s">
+      <c r="F233" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="F233" s="0" t="s">
-        <v>125</v>
-      </c>
       <c r="G233" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H233" s="0" t="s">
         <v>567</v>
@@ -23533,16 +23533,16 @@
         <v>576</v>
       </c>
       <c r="D236" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E236" s="0" t="s">
         <v>487</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H236" s="0" t="s">
         <v>577</v>
@@ -23693,7 +23693,7 @@
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B238" s="0" t="s">
         <v>61</v>
@@ -23864,7 +23864,7 @@
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B240" s="0" t="s">
         <v>34</v>
@@ -23879,10 +23879,10 @@
         <v>304</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G240" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H240" s="0" t="s">
         <v>535</v>
@@ -23948,7 +23948,7 @@
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B241" s="0" t="s">
         <v>61</v>
@@ -24212,10 +24212,10 @@
         <v>259</v>
       </c>
       <c r="F244" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G244" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H244" s="0" t="s">
         <v>39</v>
@@ -24292,7 +24292,7 @@
         <v>51</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F245" s="0" t="s">
         <v>79</v>
@@ -24630,7 +24630,7 @@
         <v>60</v>
       </c>
       <c r="G249" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H249" s="0" t="s">
         <v>39</v>
@@ -24640,7 +24640,7 @@
         <v>40</v>
       </c>
       <c r="L249" s="0" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="M249" s="0" t="s">
         <v>39</v>
@@ -24791,10 +24791,10 @@
         <v>613</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G251" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H251" s="0" t="s">
         <v>39</v>
@@ -24957,7 +24957,7 @@
         <v>618</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G253" s="0" t="s">
         <v>526</v>
@@ -25123,10 +25123,10 @@
         <v>624</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H255" s="0" t="s">
         <v>39</v>
@@ -25361,7 +25361,7 @@
     </row>
     <row r="258">
       <c r="A258" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B258" s="0" t="s">
         <v>61</v>
@@ -25695,7 +25695,7 @@
         <v>644</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G262" s="0" t="s">
         <v>645</v>
@@ -25773,10 +25773,10 @@
         <v>313</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G263" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H263" s="0" t="s">
         <v>648</v>
@@ -25859,7 +25859,7 @@
         <v>311</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G264" s="0" t="s">
         <v>650</v>
@@ -26025,7 +26025,7 @@
         <v>654</v>
       </c>
       <c r="D266" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E266" s="0" t="s">
         <v>187</v>
@@ -26112,10 +26112,10 @@
         <v>658</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H267" s="0" t="s">
         <v>659</v>
@@ -26192,7 +26192,7 @@
         <v>660</v>
       </c>
       <c r="D268" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E268" s="0" t="s">
         <v>661</v>
@@ -26704,10 +26704,10 @@
         <v>672</v>
       </c>
       <c r="D274" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E274" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E274" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F274" s="0" t="s">
         <v>38</v>
@@ -26788,10 +26788,10 @@
         <v>673</v>
       </c>
       <c r="D275" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E275" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E275" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F275" s="0" t="s">
         <v>38</v>
@@ -27049,7 +27049,7 @@
         <v>60</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H278" s="0" t="s">
         <v>384</v>
@@ -27130,10 +27130,10 @@
         <v>678</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H279" s="0" t="s">
         <v>679</v>
@@ -27201,7 +27201,7 @@
     </row>
     <row r="280">
       <c r="A280" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B280" s="0" t="s">
         <v>61</v>
@@ -27287,7 +27287,7 @@
     </row>
     <row r="281">
       <c r="A281" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B281" s="0" t="s">
         <v>61</v>
@@ -27388,10 +27388,10 @@
         <v>683</v>
       </c>
       <c r="F282" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="G282" s="0" t="s">
         <v>168</v>
-      </c>
-      <c r="G282" s="0" t="s">
-        <v>169</v>
       </c>
       <c r="H282" s="0" t="s">
         <v>684</v>
@@ -27472,10 +27472,10 @@
         <v>84</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G283" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H283" s="0" t="s">
         <v>686</v>
@@ -27556,10 +27556,10 @@
         <v>688</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G284" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H284" s="0" t="s">
         <v>686</v>
@@ -27642,10 +27642,10 @@
         <v>688</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G285" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H285" s="0" t="s">
         <v>686</v>
@@ -27720,13 +27720,13 @@
         <v>690</v>
       </c>
       <c r="D286" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E286" s="0" t="s">
         <v>487</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G286" s="0" t="s">
         <v>93</v>
@@ -27812,7 +27812,7 @@
         <v>693</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G287" s="0" t="s">
         <v>526</v>
@@ -27883,7 +27883,7 @@
     </row>
     <row r="288">
       <c r="A288" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B288" s="0" t="s">
         <v>61</v>
@@ -28053,7 +28053,7 @@
     </row>
     <row r="290">
       <c r="A290" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B290" s="0" t="s">
         <v>61</v>
@@ -28139,7 +28139,7 @@
     </row>
     <row r="291">
       <c r="A291" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B291" s="0" t="s">
         <v>61</v>
@@ -28223,7 +28223,7 @@
     </row>
     <row r="292">
       <c r="A292" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B292" s="0" t="s">
         <v>61</v>
@@ -28309,7 +28309,7 @@
     </row>
     <row r="293">
       <c r="A293" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B293" s="0" t="s">
         <v>61</v>
@@ -28324,7 +28324,7 @@
         <v>73</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G293" s="0" t="s">
         <v>526</v>
@@ -28395,7 +28395,7 @@
     </row>
     <row r="294">
       <c r="A294" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B294" s="0" t="s">
         <v>61</v>
@@ -28481,7 +28481,7 @@
     </row>
     <row r="295">
       <c r="A295" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B295" s="0" t="s">
         <v>61</v>
@@ -28502,7 +28502,7 @@
         <v>93</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J295" s="11"/>
       <c r="K295" s="0" t="s">
@@ -28568,7 +28568,7 @@
     </row>
     <row r="296">
       <c r="A296" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B296" s="0" t="s">
         <v>61</v>
@@ -28740,7 +28740,7 @@
     </row>
     <row r="298">
       <c r="A298" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B298" s="0" t="s">
         <v>61</v>
@@ -28826,7 +28826,7 @@
     </row>
     <row r="299">
       <c r="A299" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B299" s="0" t="s">
         <v>61</v>
@@ -28912,7 +28912,7 @@
     </row>
     <row r="300">
       <c r="A300" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B300" s="0" t="s">
         <v>61</v>
@@ -28998,7 +28998,7 @@
     </row>
     <row r="301">
       <c r="A301" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B301" s="0" t="s">
         <v>61</v>
@@ -29013,7 +29013,7 @@
         <v>87</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G301" s="0" t="s">
         <v>526</v>
@@ -29084,7 +29084,7 @@
     </row>
     <row r="302">
       <c r="A302" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B302" s="0" t="s">
         <v>61</v>
@@ -29170,7 +29170,7 @@
     </row>
     <row r="303">
       <c r="A303" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B303" s="0" t="s">
         <v>61</v>
@@ -29191,7 +29191,7 @@
         <v>93</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J303" s="11"/>
       <c r="K303" s="0" t="s">
@@ -29269,13 +29269,13 @@
         <v>51</v>
       </c>
       <c r="E304" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H304" s="0" t="s">
         <v>719</v>
@@ -29427,7 +29427,7 @@
     </row>
     <row r="306">
       <c r="A306" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B306" s="0" t="s">
         <v>61</v>
@@ -29442,7 +29442,7 @@
         <v>228</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G306" s="0" t="s">
         <v>332</v>
@@ -29513,7 +29513,7 @@
     </row>
     <row r="307">
       <c r="A307" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B307" s="0" t="s">
         <v>61</v>
@@ -29692,7 +29692,7 @@
         <v>728</v>
       </c>
       <c r="D309" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E309" s="0" t="s">
         <v>547</v>
@@ -29953,10 +29953,10 @@
         <v>734</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G312" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H312" s="0" t="s">
         <v>731</v>
@@ -30110,7 +30110,7 @@
     </row>
     <row r="314">
       <c r="A314" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B314" s="0" t="s">
         <v>49</v>
@@ -30196,7 +30196,7 @@
     </row>
     <row r="315">
       <c r="A315" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B315" s="0" t="s">
         <v>49</v>
@@ -30366,7 +30366,7 @@
     </row>
     <row r="317">
       <c r="A317" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B317" s="0" t="s">
         <v>61</v>
@@ -30452,7 +30452,7 @@
     </row>
     <row r="318">
       <c r="A318" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B318" s="0" t="s">
         <v>61</v>
@@ -30538,7 +30538,7 @@
     </row>
     <row r="319">
       <c r="A319" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B319" s="0" t="s">
         <v>61</v>
@@ -30553,10 +30553,10 @@
         <v>37</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G319" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H319" s="0" t="s">
         <v>543</v>
@@ -30624,7 +30624,7 @@
     </row>
     <row r="320">
       <c r="A320" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B320" s="0" t="s">
         <v>61</v>
@@ -30639,10 +30639,10 @@
         <v>37</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G320" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H320" s="0" t="s">
         <v>543</v>
@@ -30710,7 +30710,7 @@
     </row>
     <row r="321">
       <c r="A321" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B321" s="0" t="s">
         <v>61</v>
@@ -30725,10 +30725,10 @@
         <v>37</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G321" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H321" s="0" t="s">
         <v>402</v>
@@ -30796,7 +30796,7 @@
     </row>
     <row r="322">
       <c r="A322" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B322" s="0" t="s">
         <v>61</v>
@@ -30811,10 +30811,10 @@
         <v>37</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G322" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H322" s="0" t="s">
         <v>402</v>
@@ -30897,10 +30897,10 @@
         <v>750</v>
       </c>
       <c r="F323" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G323" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H323" s="0" t="s">
         <v>751</v>
@@ -30983,10 +30983,10 @@
         <v>750</v>
       </c>
       <c r="F324" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G324" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H324" s="0" t="s">
         <v>751</v>
@@ -31054,7 +31054,7 @@
     </row>
     <row r="325">
       <c r="A325" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B325" s="0" t="s">
         <v>61</v>
@@ -31138,7 +31138,7 @@
     </row>
     <row r="326">
       <c r="A326" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B326" s="0" t="s">
         <v>61</v>
@@ -31222,7 +31222,7 @@
     </row>
     <row r="327">
       <c r="A327" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B327" s="0" t="s">
         <v>61</v>
@@ -31308,7 +31308,7 @@
     </row>
     <row r="328">
       <c r="A328" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B328" s="0" t="s">
         <v>61</v>
@@ -31409,10 +31409,10 @@
         <v>760</v>
       </c>
       <c r="F329" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="G329" s="0" t="s">
         <v>149</v>
-      </c>
-      <c r="G329" s="0" t="s">
-        <v>150</v>
       </c>
       <c r="J329" s="11">
         <v>46386.125</v>
@@ -31474,7 +31474,7 @@
     </row>
     <row r="330">
       <c r="A330" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B330" s="0" t="s">
         <v>61</v>
@@ -31489,13 +31489,13 @@
         <v>87</v>
       </c>
       <c r="F330" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G330" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H330" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J330" s="11"/>
       <c r="K330" s="0" t="s">
@@ -31561,7 +31561,7 @@
     </row>
     <row r="331">
       <c r="A331" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B331" s="0" t="s">
         <v>61</v>
@@ -31576,13 +31576,13 @@
         <v>73</v>
       </c>
       <c r="F331" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G331" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H331" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J331" s="11"/>
       <c r="K331" s="0" t="s">
@@ -31663,7 +31663,7 @@
         <v>85</v>
       </c>
       <c r="G332" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H332" s="0" t="s">
         <v>764</v>
@@ -32000,10 +32000,10 @@
         <v>769</v>
       </c>
       <c r="F336" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G336" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J336" s="11">
         <v>46403.125</v>
@@ -32083,7 +32083,7 @@
         <v>304</v>
       </c>
       <c r="F337" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G337" s="0" t="s">
         <v>79</v>
@@ -32169,7 +32169,7 @@
         <v>304</v>
       </c>
       <c r="F338" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G338" s="0" t="s">
         <v>79</v>
@@ -32249,7 +32249,7 @@
         <v>772</v>
       </c>
       <c r="D339" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E339" s="0" t="s">
         <v>216</v>
@@ -32324,7 +32324,7 @@
     </row>
     <row r="340">
       <c r="A340" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B340" s="0" t="s">
         <v>34</v>
@@ -32333,10 +32333,10 @@
         <v>774</v>
       </c>
       <c r="D340" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="E340" s="0" t="s">
         <v>140</v>
-      </c>
-      <c r="E340" s="0" t="s">
-        <v>141</v>
       </c>
       <c r="F340" s="0" t="s">
         <v>243</v>
@@ -32417,7 +32417,7 @@
         <v>775</v>
       </c>
       <c r="D341" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E341" s="0" t="s">
         <v>216</v>
@@ -32494,7 +32494,7 @@
     </row>
     <row r="342">
       <c r="A342" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B342" s="0" t="s">
         <v>61</v>
@@ -32509,7 +32509,7 @@
         <v>37</v>
       </c>
       <c r="F342" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G342" s="0" t="s">
         <v>526</v>
@@ -32669,7 +32669,7 @@
         <v>780</v>
       </c>
       <c r="D344" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E344" s="0" t="s">
         <v>216</v>
@@ -32746,7 +32746,7 @@
     </row>
     <row r="345">
       <c r="A345" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B345" s="0" t="s">
         <v>61</v>
@@ -32764,7 +32764,7 @@
         <v>60</v>
       </c>
       <c r="G345" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H345" s="0" t="s">
         <v>781</v>
@@ -32847,13 +32847,13 @@
         <v>51</v>
       </c>
       <c r="E346" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="F346" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="F346" s="0" t="s">
-        <v>131</v>
-      </c>
       <c r="G346" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H346" s="0" t="s">
         <v>785</v>
@@ -33177,7 +33177,7 @@
         <v>795</v>
       </c>
       <c r="F350" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G350" s="0" t="s">
         <v>526</v>
@@ -33426,10 +33426,10 @@
         <v>803</v>
       </c>
       <c r="F353" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G353" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J353" s="11">
         <v>46399.125</v>
@@ -33491,7 +33491,7 @@
     </row>
     <row r="354">
       <c r="A354" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B354" s="0" t="s">
         <v>34</v>
@@ -33741,7 +33741,7 @@
     </row>
     <row r="357">
       <c r="A357" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B357" s="0" t="s">
         <v>61</v>
@@ -33753,7 +33753,7 @@
         <v>51</v>
       </c>
       <c r="E357" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F357" s="0" t="s">
         <v>79</v>
@@ -33830,7 +33830,7 @@
     </row>
     <row r="358">
       <c r="A358" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B358" s="0" t="s">
         <v>61</v>
@@ -33845,10 +33845,10 @@
         <v>810</v>
       </c>
       <c r="F358" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G358" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H358" s="0" t="s">
         <v>756</v>
@@ -34017,7 +34017,7 @@
         <v>815</v>
       </c>
       <c r="E360" s="0" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F360" s="0" t="s">
         <v>428</v>
@@ -34094,7 +34094,7 @@
         <v>816</v>
       </c>
       <c r="D361" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E361" s="0" t="s">
         <v>216</v>
@@ -34255,7 +34255,7 @@
     </row>
     <row r="363">
       <c r="A363" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B363" s="0" t="s">
         <v>34</v>
@@ -34354,10 +34354,10 @@
         <v>511</v>
       </c>
       <c r="F364" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G364" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H364" s="0" t="s">
         <v>281</v>
@@ -34524,7 +34524,7 @@
         <v>693</v>
       </c>
       <c r="F366" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G366" s="0" t="s">
         <v>526</v>
@@ -34696,7 +34696,7 @@
         <v>827</v>
       </c>
       <c r="F368" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G368" s="0" t="s">
         <v>526</v>
@@ -34788,7 +34788,7 @@
         <v>200</v>
       </c>
       <c r="H369" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J369" s="11">
         <v>46391.125</v>
@@ -34865,7 +34865,7 @@
         <v>63</v>
       </c>
       <c r="E370" s="0" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F370" s="0" t="s">
         <v>74</v>
@@ -34957,7 +34957,7 @@
         <v>60</v>
       </c>
       <c r="G371" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H371" s="0" t="s">
         <v>834</v>
@@ -35035,7 +35035,7 @@
         <v>839</v>
       </c>
       <c r="H372" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J372" s="11">
         <v>46391.125</v>
@@ -35337,7 +35337,7 @@
     </row>
     <row r="376">
       <c r="A376" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B376" s="0" t="s">
         <v>34</v>
@@ -35423,7 +35423,7 @@
     </row>
     <row r="377">
       <c r="A377" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B377" s="0" t="s">
         <v>61</v>
@@ -35506,7 +35506,7 @@
     </row>
     <row r="378">
       <c r="A378" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B378" s="0" t="s">
         <v>61</v>
@@ -35856,7 +35856,7 @@
         <v>60</v>
       </c>
       <c r="G382" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J382" s="11"/>
       <c r="K382" s="0" t="s">
@@ -36005,7 +36005,7 @@
     </row>
     <row r="384">
       <c r="A384" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B384" s="0" t="s">
         <v>34</v>
@@ -36272,7 +36272,7 @@
         <v>869</v>
       </c>
       <c r="D387" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E387" s="0" t="s">
         <v>487</v>
@@ -36364,10 +36364,10 @@
         <v>503</v>
       </c>
       <c r="F388" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="G388" s="0" t="s">
         <v>149</v>
-      </c>
-      <c r="G388" s="0" t="s">
-        <v>150</v>
       </c>
       <c r="H388" s="0" t="s">
         <v>872</v>
@@ -36450,10 +36450,10 @@
         <v>59</v>
       </c>
       <c r="F389" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G389" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H389" s="0" t="s">
         <v>874</v>
@@ -36521,7 +36521,7 @@
     </row>
     <row r="390">
       <c r="A390" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B390" s="0" t="s">
         <v>34</v>
@@ -36536,10 +36536,10 @@
         <v>37</v>
       </c>
       <c r="F390" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G390" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H390" s="0" t="s">
         <v>874</v>
@@ -36706,10 +36706,10 @@
         <v>322</v>
       </c>
       <c r="F392" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G392" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H392" s="0" t="s">
         <v>878</v>
@@ -37119,7 +37119,7 @@
     </row>
     <row r="397">
       <c r="A397" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B397" s="0" t="s">
         <v>34</v>
@@ -37134,10 +37134,10 @@
         <v>888</v>
       </c>
       <c r="F397" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G397" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H397" s="0" t="s">
         <v>886</v>
@@ -37203,7 +37203,7 @@
     </row>
     <row r="398">
       <c r="A398" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B398" s="0" t="s">
         <v>34</v>
@@ -37218,10 +37218,10 @@
         <v>890</v>
       </c>
       <c r="F398" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G398" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H398" s="0" t="s">
         <v>344</v>
@@ -37290,7 +37290,7 @@
     </row>
     <row r="399">
       <c r="A399" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B399" s="0" t="s">
         <v>34</v>
@@ -37302,10 +37302,10 @@
         <v>51</v>
       </c>
       <c r="E399" s="0" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F399" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G399" s="0" t="s">
         <v>332</v>
@@ -37379,7 +37379,7 @@
     </row>
     <row r="400">
       <c r="A400" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B400" s="0" t="s">
         <v>34</v>
@@ -37388,16 +37388,16 @@
         <v>893</v>
       </c>
       <c r="D400" s="0" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E400" s="0" t="s">
         <v>894</v>
       </c>
       <c r="F400" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G400" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H400" s="0" t="s">
         <v>895</v>
@@ -37466,7 +37466,7 @@
     </row>
     <row r="401">
       <c r="A401" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B401" s="0" t="s">
         <v>34</v>
@@ -37475,7 +37475,7 @@
         <v>896</v>
       </c>
       <c r="D401" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E401" s="0" t="s">
         <v>897</v>
@@ -37562,10 +37562,10 @@
         <v>899</v>
       </c>
       <c r="D402" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E402" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E402" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F402" s="0" t="s">
         <v>60</v>
@@ -37646,10 +37646,10 @@
         <v>900</v>
       </c>
       <c r="D403" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E403" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E403" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F403" s="0" t="s">
         <v>60</v>
@@ -37819,10 +37819,10 @@
         <v>92</v>
       </c>
       <c r="F405" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G405" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H405" s="0" t="s">
         <v>527</v>
@@ -37890,7 +37890,7 @@
     </row>
     <row r="406">
       <c r="A406" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B406" s="0" t="s">
         <v>34</v>
@@ -37977,7 +37977,7 @@
     </row>
     <row r="407">
       <c r="A407" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B407" s="0" t="s">
         <v>34</v>
@@ -38162,10 +38162,10 @@
         <v>322</v>
       </c>
       <c r="F409" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G409" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J409" s="11">
         <v>46407.125</v>
@@ -38230,7 +38230,7 @@
     </row>
     <row r="410">
       <c r="A410" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B410" s="0" t="s">
         <v>34</v>
@@ -38415,10 +38415,10 @@
         <v>916</v>
       </c>
       <c r="F412" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G412" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J412" s="11">
         <v>46399.125</v>
@@ -38498,10 +38498,10 @@
         <v>521</v>
       </c>
       <c r="F413" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G413" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H413" s="0" t="s">
         <v>918</v>
@@ -38653,7 +38653,7 @@
     </row>
     <row r="415">
       <c r="A415" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B415" s="0" t="s">
         <v>61</v>
@@ -38740,7 +38740,7 @@
     </row>
     <row r="416">
       <c r="A416" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B416" s="0" t="s">
         <v>61</v>
@@ -38749,16 +38749,16 @@
         <v>924</v>
       </c>
       <c r="D416" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E416" s="0" t="s">
         <v>925</v>
       </c>
       <c r="F416" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G416" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H416" s="0" t="s">
         <v>224</v>
@@ -38924,7 +38924,7 @@
         <v>928</v>
       </c>
       <c r="D418" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E418" s="0" t="s">
         <v>929</v>
@@ -39011,13 +39011,13 @@
         <v>51</v>
       </c>
       <c r="E419" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F419" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G419" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H419" s="0" t="s">
         <v>932</v>
@@ -39085,7 +39085,7 @@
     </row>
     <row r="420">
       <c r="A420" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B420" s="0" t="s">
         <v>61</v>
@@ -39169,7 +39169,7 @@
     </row>
     <row r="421">
       <c r="A421" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B421" s="0" t="s">
         <v>61</v>
@@ -39253,7 +39253,7 @@
     </row>
     <row r="422">
       <c r="A422" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B422" s="0" t="s">
         <v>61</v>
@@ -39268,7 +39268,7 @@
         <v>260</v>
       </c>
       <c r="F422" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G422" s="0" t="s">
         <v>93</v>
@@ -39337,7 +39337,7 @@
     </row>
     <row r="423">
       <c r="A423" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B423" s="0" t="s">
         <v>61</v>
@@ -39352,10 +39352,10 @@
         <v>938</v>
       </c>
       <c r="F423" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G423" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H423" s="0" t="s">
         <v>923</v>
@@ -39424,7 +39424,7 @@
     </row>
     <row r="424">
       <c r="A424" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B424" s="0" t="s">
         <v>61</v>
@@ -39511,7 +39511,7 @@
     </row>
     <row r="425">
       <c r="A425" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B425" s="0" t="s">
         <v>61</v>
@@ -39532,7 +39532,7 @@
         <v>300</v>
       </c>
       <c r="H425" s="0" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J425" s="11">
         <v>46373.125</v>
@@ -39597,7 +39597,7 @@
     </row>
     <row r="426">
       <c r="A426" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B426" s="0" t="s">
         <v>61</v>
@@ -39612,7 +39612,7 @@
         <v>260</v>
       </c>
       <c r="F426" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G426" s="0" t="s">
         <v>526</v>
@@ -39684,7 +39684,7 @@
     </row>
     <row r="427">
       <c r="A427" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B427" s="0" t="s">
         <v>61</v>
@@ -39699,10 +39699,10 @@
         <v>73</v>
       </c>
       <c r="F427" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G427" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H427" s="0" t="s">
         <v>945</v>
@@ -39770,7 +39770,7 @@
     </row>
     <row r="428">
       <c r="A428" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B428" s="0" t="s">
         <v>61</v>
@@ -39854,7 +39854,7 @@
     </row>
     <row r="429">
       <c r="A429" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B429" s="0" t="s">
         <v>61</v>
@@ -39938,7 +39938,7 @@
     </row>
     <row r="430">
       <c r="A430" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B430" s="0" t="s">
         <v>61</v>
@@ -40024,7 +40024,7 @@
     </row>
     <row r="431">
       <c r="A431" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B431" s="0" t="s">
         <v>61</v>
@@ -40108,7 +40108,7 @@
     </row>
     <row r="432">
       <c r="A432" s="0" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B432" s="0" t="s">
         <v>61</v>
@@ -40123,7 +40123,7 @@
         <v>260</v>
       </c>
       <c r="F432" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G432" s="0" t="s">
         <v>526</v>
@@ -40195,7 +40195,7 @@
     </row>
     <row r="433">
       <c r="A433" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B433" s="0" t="s">
         <v>61</v>
@@ -40210,10 +40210,10 @@
         <v>87</v>
       </c>
       <c r="F433" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G433" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H433" s="0" t="s">
         <v>945</v>
@@ -40281,7 +40281,7 @@
     </row>
     <row r="434">
       <c r="A434" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B434" s="0" t="s">
         <v>61</v>
@@ -40374,7 +40374,7 @@
         <v>953</v>
       </c>
       <c r="D435" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E435" s="0" t="s">
         <v>175</v>
@@ -40458,7 +40458,7 @@
         <v>955</v>
       </c>
       <c r="D436" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E436" s="0" t="s">
         <v>956</v>
@@ -40544,7 +40544,7 @@
         <v>958</v>
       </c>
       <c r="D437" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E437" s="0" t="s">
         <v>175</v>
@@ -40628,7 +40628,7 @@
         <v>960</v>
       </c>
       <c r="D438" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E438" s="0" t="s">
         <v>961</v>
@@ -40715,7 +40715,7 @@
         <v>963</v>
       </c>
       <c r="D439" s="0" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E439" s="0" t="s">
         <v>191</v>
@@ -41122,7 +41122,7 @@
     </row>
     <row r="444">
       <c r="A444" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B444" s="0" t="s">
         <v>34</v>
@@ -41137,10 +41137,10 @@
         <v>37</v>
       </c>
       <c r="F444" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G444" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J444" s="11">
         <v>46394.125</v>
@@ -41214,10 +41214,10 @@
         <v>972</v>
       </c>
       <c r="D445" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E445" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E445" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F445" s="0" t="s">
         <v>38</v>
@@ -41300,10 +41300,10 @@
         <v>974</v>
       </c>
       <c r="D446" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="E446" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="E446" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="F446" s="0" t="s">
         <v>38</v>
@@ -41478,10 +41478,10 @@
         <v>977</v>
       </c>
       <c r="F448" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G448" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H448" s="0" t="s">
         <v>535</v>
@@ -41562,10 +41562,10 @@
         <v>979</v>
       </c>
       <c r="F449" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G449" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H449" s="0" t="s">
         <v>980</v>
@@ -41575,7 +41575,7 @@
         <v>40</v>
       </c>
       <c r="L449" s="0" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="M449" s="0" t="s">
         <v>39</v>
@@ -41884,7 +41884,7 @@
     </row>
     <row r="453">
       <c r="A453" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B453" s="0" t="s">
         <v>61</v>
@@ -41899,10 +41899,10 @@
         <v>37</v>
       </c>
       <c r="F453" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G453" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H453" s="0" t="s">
         <v>989</v>
@@ -41970,7 +41970,7 @@
     </row>
     <row r="454">
       <c r="A454" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B454" s="0" t="s">
         <v>61</v>
@@ -41985,10 +41985,10 @@
         <v>37</v>
       </c>
       <c r="F454" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G454" s="0" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H454" s="0" t="s">
         <v>989</v>
@@ -42056,7 +42056,7 @@
     </row>
     <row r="455">
       <c r="A455" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B455" s="0" t="s">
         <v>61</v>
@@ -42142,7 +42142,7 @@
     </row>
     <row r="456">
       <c r="A456" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B456" s="0" t="s">
         <v>61</v>
@@ -42249,7 +42249,7 @@
         <v>74</v>
       </c>
       <c r="H457" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J457" s="11">
         <v>46399.125</v>
@@ -42329,10 +42329,10 @@
         <v>998</v>
       </c>
       <c r="F458" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G458" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H458" s="0" t="s">
         <v>999</v>
@@ -42646,7 +42646,7 @@
     </row>
     <row r="462">
       <c r="A462" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B462" s="0" t="s">
         <v>61</v>
@@ -42732,7 +42732,7 @@
     </row>
     <row r="463">
       <c r="A463" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B463" s="0" t="s">
         <v>61</v>
@@ -42760,7 +42760,7 @@
         <v>40</v>
       </c>
       <c r="L463" s="0" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="M463" s="0" t="s">
         <v>39</v>
@@ -42828,13 +42828,13 @@
         <v>51</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F464" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G464" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H464" s="0" t="s">
         <v>1013</v>
@@ -42902,7 +42902,7 @@
     </row>
     <row r="465">
       <c r="A465" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B465" s="0" t="s">
         <v>61</v>
@@ -42988,7 +42988,7 @@
     </row>
     <row r="466">
       <c r="A466" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B466" s="0" t="s">
         <v>61</v>
@@ -43419,10 +43419,10 @@
         <v>1025</v>
       </c>
       <c r="F471" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G471" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J471" s="11">
         <v>46360.125</v>
@@ -43502,10 +43502,10 @@
         <v>339</v>
       </c>
       <c r="F472" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G472" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J472" s="11">
         <v>46356.125</v>
@@ -43585,10 +43585,10 @@
         <v>339</v>
       </c>
       <c r="F473" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G473" s="0" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J473" s="11">
         <v>46356.125</v>
@@ -44006,10 +44006,10 @@
         <v>1034</v>
       </c>
       <c r="F478" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G478" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J478" s="11">
         <v>46369.125</v>
@@ -44157,7 +44157,7 @@
     </row>
     <row r="480">
       <c r="A480" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B480" s="0" t="s">
         <v>61</v>
@@ -44668,10 +44668,10 @@
         <v>1049</v>
       </c>
       <c r="F486" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G486" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J486" s="11"/>
       <c r="K486" s="0" t="s">
@@ -44735,10 +44735,10 @@
         <v>1052</v>
       </c>
       <c r="F487" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G487" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J487" s="11"/>
       <c r="K487" s="0" t="s">

--- a/dados/prontuario-equipamentos_1.xlsx
+++ b/dados/prontuario-equipamentos_1.xlsx
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46325.35281707176</v>
+        <v>46325.64655670139</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
